--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -842,7 +842,7 @@
         <v>100.63</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.19914064</v>
+        <v>0.199141</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -975,19 +975,19 @@
         <v>6.042</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>8.52</v>
+        <v>8.398999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.5478725</v>
+        <v>3.6184447</v>
       </c>
       <c r="L7" s="7" t="n">
         <v>9.823980000000001</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>7.094</v>
+        <v>6.994</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>1.22</v>
@@ -1034,16 +1034,16 @@
         <v>6.011</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>11.061</v>
+        <v>11.05</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.294895</v>
+        <v>16.325756</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>11.609365</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>11.562</v>
+        <v>11.55</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>9.800000000000001</v>
@@ -1078,7 +1078,7 @@
         <v>57.77</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.32997328</v>
+        <v>0.329973</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1198,7 +1198,7 @@
         <v>18.18</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>-0.025723448</v>
+        <v>-0.0257234</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>32.22</v>
@@ -1216,7 +1216,7 @@
         <v>5.157</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>50.5</v>
+        <v>51.94286</v>
       </c>
       <c r="L11" s="7" t="n">
         <v>22.35407</v>
@@ -1381,7 +1381,7 @@
         <v>5.61</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.3577814</v>
+        <v>0.357781</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>10.15</v>
@@ -1440,7 +1440,7 @@
         <v>13.98</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>-0.023060856</v>
+        <v>-0.0230609</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20.61</v>
@@ -1501,7 +1501,7 @@
         <v>98.43000000000001</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>-0.019719183</v>
+        <v>-0.0197192</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>113.88</v>
@@ -1809,13 +1809,13 @@
         <v>0.0379939</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>10.29</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>6.505</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.336</v>
+        <v>-0.314</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0.184</v>
@@ -1880,7 +1880,7 @@
         <v>0.093</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.596</v>
+        <v>0.594</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>-6.2926826</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>12.968</v>
+        <v>12.945</v>
       </c>
       <c r="N22" s="7" t="n">
         <v>9.300000000000001</v>
@@ -2434,7 +2434,7 @@
         <v>100.63</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.19914064</v>
+        <v>0.199141</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>-0.177</v>
@@ -2622,7 +2622,7 @@
         <v>57.77</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.32997328</v>
+        <v>0.329973</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>-0.068</v>
@@ -2716,7 +2716,7 @@
         <v>18.18</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-0.025723448</v>
+        <v>-0.0257234</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>-0.22</v>
@@ -2857,7 +2857,7 @@
         <v>5.61</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.3577814</v>
+        <v>0.357781</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>-0.253</v>
@@ -2904,7 +2904,7 @@
         <v>13.98</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-0.023060856</v>
+        <v>-0.0230609</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>-0.059</v>
@@ -2951,7 +2951,7 @@
         <v>98.43000000000001</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.019719183</v>
+        <v>-0.0197192</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0.028</v>
@@ -3206,7 +3206,7 @@
         <v>-0.205</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.336</v>
+        <v>-0.314</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>1.206</v>
@@ -3650,7 +3650,7 @@
         <v>1.1629317</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>-1.74</v>
+        <v>-1.75</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>10.80017</v>
@@ -3843,19 +3843,19 @@
         <v>6.042</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.5478725</v>
+        <v>3.6184447</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>9.823980000000001</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>7.094</v>
+        <v>6.994</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>2.082</v>
+        <v>2.053</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>2.343297</v>
@@ -3864,7 +3864,7 @@
         <v>1.4766403</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>22.56</v>
+        <v>22.12</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>8.147410000000001</v>
@@ -3896,19 +3896,19 @@
         <v>6.011</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>16.294895</v>
+        <v>16.325756</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>11.609365</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>11.562</v>
+        <v>11.55</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>3.781</v>
+        <v>3.777</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>5.941959</v>
@@ -3917,7 +3917,7 @@
         <v>2.0542798</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>5.29</v>
+        <v>5.28</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>7.42504</v>
@@ -4025,7 +4025,7 @@
         <v>0.48263726</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-2.42</v>
+        <v>-2.34</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.925</v>
@@ -4057,7 +4057,7 @@
         <v>5.38</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>50.5</v>
+        <v>51.94286</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>22.35407</v>
@@ -4078,7 +4078,7 @@
         <v>4.1709666</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>0.81327474</v>
@@ -4408,7 +4408,7 @@
         <v>1.9130899</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.43</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0.99</v>
@@ -4571,7 +4571,7 @@
         <v>0.25303388</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-13.26</v>
+        <v>-13.39</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-1.49</v>
@@ -4664,13 +4664,13 @@
         <v>-6.2926826</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>12.968</v>
+        <v>12.945</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.97</v>
+        <v>1.966</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>6.564885</v>
@@ -4679,7 +4679,7 @@
         <v>0.30820388</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.09</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>-0.41</v>
@@ -7053,7 +7053,7 @@
         <v>0.68579</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="P5" s="5" t="n">
         <v>0.3185</v>
@@ -7369,13 +7369,13 @@
         <v>21</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>28.680185</v>
+        <v>28.690083</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>36.99057</v>
+        <v>37.003334</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>21.818075</v>
+        <v>21.825605</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>0.578</v>
@@ -7685,7 +7685,7 @@
         <v>0.64761</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P16" s="5" t="n">
         <v>0.221</v>
@@ -8714,7 +8714,7 @@
         <v>6.011</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>16.294895</v>
+        <v>16.325756</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.067</v>
@@ -8729,7 +8729,7 @@
         <v>-0.23</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>11.562</v>
+        <v>11.55</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>9.800000000000001</v>
@@ -8758,7 +8758,7 @@
         <v>6.042</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3.5478725</v>
+        <v>3.6184447</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.02</v>
@@ -8773,10 +8773,10 @@
         <v>-0.07099999999999999</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>7.094</v>
+        <v>6.994</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L11" s="7" t="n">
         <v>64.3</v>
@@ -8999,7 +8999,7 @@
         <v>0.032</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>12.968</v>
+        <v>12.945</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>9.300000000000001</v>
@@ -9136,7 +9136,7 @@
         <v>5.38</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>50.5</v>
+        <v>51.94286</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -11340,7 +11340,7 @@
         <v>1237.26</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1234.13</v>
+        <v>1234.12</v>
       </c>
       <c r="D14" s="13" t="n">
         <v>1047.95</v>
@@ -11580,7 +11580,7 @@
         <v>1120.5</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1240.57</v>
+        <v>1240.56</v>
       </c>
       <c r="D29" s="13" t="n">
         <v>996.5599999999999</v>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>53.7</v>
+        <v>54.15</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0372587</v>
+        <v>0.83799</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,34 +670,34 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.238</v>
+        <v>-0.231</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>36.308</v>
+        <v>36.613</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>48.617</v>
+        <v>48.919</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.851065</v>
+        <v>23.042555</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.2912655</v>
+        <v>14.411025</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>10.725</v>
+        <v>10.792</v>
       </c>
       <c r="N2" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>0.888</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.255</v>
+        <v>0.277</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>-0.172</v>
+        <v>-0.165</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>108.67</v>
+        <v>109.25</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.276825</v>
+        <v>0.533728</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -729,13 +729,13 @@
         <v>99.95999999999999</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-0.654</v>
+        <v>-0.652</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>19.052</v>
+        <v>19.168</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>30.731</v>
+        <v>30.833</v>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>10.061878</v>
+        <v>10.1155815</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>14.414</v>
+        <v>14.462</v>
       </c>
       <c r="N3" s="7" t="n">
         <v>9.9</v>
@@ -755,10 +755,10 @@
         <v>1.177</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>-0.546</v>
+        <v>-0.5329999999999999</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>-0.502</v>
+        <v>-0.499</v>
       </c>
     </row>
     <row r="4">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24.89</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>-0.0376885</v>
+        <v>25.22</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.0130548</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -790,13 +790,13 @@
         <v>21.01</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.49</v>
+        <v>-0.483</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>12.392</v>
+        <v>12.554</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>13.035</v>
+        <v>13.196</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
@@ -804,22 +804,22 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>12.765685</v>
+        <v>12.95792</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>47.769</v>
+        <v>48.356</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>1.682</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>-0.357</v>
+        <v>-0.317</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>-0.302</v>
+        <v>-0.293</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>100.63</v>
+        <v>103.33</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.199141</v>
+        <v>0.026831</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,34 +851,34 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.253</v>
+        <v>-0.233</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.494</v>
+        <v>10.776</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>19.813</v>
+        <v>20.09</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.047768</v>
+        <v>32.907642</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>16.824804</v>
+        <v>17.390442</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>11.324</v>
+        <v>11.483</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>1.034</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.175</v>
+        <v>0.221</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>-0.177</v>
+        <v>-0.155</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>35.98</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>-0.019084</v>
+        <v>36.86</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.0244581</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,34 +910,34 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.104</v>
+        <v>-0.08199999999999999</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>9.840999999999999</v>
+        <v>10.081</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>39.332</v>
+        <v>39.557</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>47.342106</v>
+        <v>48.5</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>15.332299</v>
+        <v>15.707298</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>16.705</v>
+        <v>16.8</v>
       </c>
       <c r="N6" s="7" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>1.396</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q6" s="9" t="n">
-        <v>-0.014</v>
+        <v>0.157</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>80.04000000000001</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>-0.0171906</v>
+        <v>81.83</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.0223638</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -969,45 +969,45 @@
         <v>58.94</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.042</v>
+        <v>6.178</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>8.398999999999999</v>
+        <v>8.534000000000001</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.6184447</v>
+        <v>3.6272166</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>9.823980000000001</v>
+        <v>10.043682</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>6.994</v>
+        <v>7.106</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>1.22</v>
       </c>
-      <c r="P7" s="4" t="n">
-        <v>0.161</v>
+      <c r="P7" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.048</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1016,57 +1016,57 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>-0.185275</v>
+        <v>58.99</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.0211182</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>118.46</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>80.23999999999999</v>
+        <v>35.09</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.272</v>
+        <v>-0.145</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.011</v>
+        <v>6.066</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>11.05</v>
+        <v>6.9</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.325756</v>
+        <v>18.907053</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>11.609365</v>
+        <v>17.952301</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>11.55</v>
+        <v>8.478</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="P8" s="9" t="n">
-        <v>-0.225</v>
+        <v>1.453</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>-0.23</v>
+        <v>-0.045</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1075,46 +1075,46 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>57.77</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0.329973</v>
+        <v>85.94</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>-0.301618</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>68.98999999999999</v>
+        <v>118.46</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>35.09</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.163</v>
+        <v>-0.275</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.94</v>
+        <v>5.992</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>6.829</v>
+        <v>11.032</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>18.516026</v>
+        <v>16.245747</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>17.58102</v>
+        <v>11.574349</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>8.391</v>
+        <v>11.532</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>1.453</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0.338</v>
+        <v>0.66</v>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>-0.218</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>-0.068</v>
+        <v>-0.232</v>
       </c>
     </row>
     <row r="10">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>-0.0320741</v>
+        <v>27.33</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0.6259209999999999</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>31.58</v>
@@ -1146,13 +1146,13 @@
         <v>17.86</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.14</v>
+        <v>-0.135</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.544</v>
+        <v>5.578</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>30.445</v>
+        <v>30.479</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="L10" s="7" t="n">
-        <v>29.362162</v>
+        <v>29.545946</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>8.711</v>
+        <v>8.721</v>
       </c>
       <c r="N10" s="7" t="n">
         <v>7.3</v>
@@ -1172,21 +1172,21 @@
         <v>1.977</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>-0.033</v>
+        <v>-0.008</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.153</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1195,57 +1195,57 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>-0.0257234</v>
+        <v>10.67</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0.012334</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>32.22</v>
+        <v>14.38</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>15.725</v>
+        <v>5.59</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.436</v>
+        <v>-0.258</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.38</v>
+        <v>5.395</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>5.157</v>
+        <v>4.988</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>51.94286</v>
+        <v>25.404762</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>22.35407</v>
+        <v>12.300988</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>10.163</v>
+        <v>10.165</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>2.002</v>
-      </c>
-      <c r="P11" s="9" t="n">
-        <v>-0.107</v>
+        <v>1.1</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0.588</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>-0.22</v>
+        <v>-0.079</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1254,46 +1254,46 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.54</v>
+        <v>18.11</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-0.0131086</v>
+        <v>-0.385037</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>14.38</v>
+        <v>32.22</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>5.59</v>
+        <v>15.725</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.267</v>
+        <v>-0.4379999999999999</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.329</v>
+        <v>5.36</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>4.922</v>
+        <v>5.136</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>25.09524</v>
+        <v>51.74286</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>12.151116</v>
+        <v>22.197506</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>10.031</v>
+        <v>10.121</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0.5770000000000001</v>
+        <v>2.002</v>
+      </c>
+      <c r="P12" s="9" t="n">
+        <v>-0.098</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>-0.095</v>
+        <v>-0.223</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>-0.296294</v>
+        <v>20.53</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0.01684</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.109</v>
+        <v>-0.094</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>4.7</v>
+        <v>4.779</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>65.129036</v>
+        <v>66.22581</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>26.980076</v>
+        <v>27.434422</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.8640000000000001</v>
+        <v>0.9259999999999999</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.046</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="14">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5.61</v>
+        <v>5.68</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.357781</v>
+        <v>0.0124777</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>10.15</v>
@@ -1390,34 +1390,34 @@
         <v>4.55</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-0.447</v>
+        <v>-0.44</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.192</v>
+        <v>2.219</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>12.92</v>
+        <v>13.009</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>12.195652</v>
+        <v>12.347825</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>7.051371</v>
+        <v>7.1393557</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>11.314</v>
+        <v>10.786</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>0.603</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>-0.024</v>
+        <v>-0.012</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>-0.253</v>
+        <v>-0.244</v>
       </c>
     </row>
     <row r="15">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>13.98</v>
+        <v>13.97</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>-0.0230609</v>
+        <v>-0.07152559999999999</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20.61</v>
@@ -1452,10 +1452,10 @@
         <v>-0.322</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.867</v>
+        <v>1.866</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>12.352</v>
+        <v>12.351</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="L15" s="7" t="n">
-        <v>8.032036</v>
+        <v>8.026291000000001</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>17.104</v>
+        <v>17.102</v>
       </c>
       <c r="N15" s="7" t="n">
         <v>10.8</v>
@@ -1475,7 +1475,7 @@
         <v>1.364</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>-0.19</v>
+        <v>-0.155</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>-0.059</v>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>98.43000000000001</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>-0.0197192</v>
+        <v>-0.0126994</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>113.88</v>
@@ -1510,34 +1510,34 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.136</v>
+        <v>-0.147</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.761</v>
+        <v>1.738</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1.677</v>
+        <v>1.655</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>18.127073</v>
+        <v>17.89687</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>16.55677</v>
+        <v>16.34651</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>8.795</v>
+        <v>8.678000000000001</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>1.376</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.028</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="17">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.2</v>
+        <v>4.99</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>-0.0243903</v>
+        <v>-0.0403846</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>13.73</v>
@@ -1569,13 +1569,13 @@
         <v>4.96</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.621</v>
+        <v>-0.637</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.281</v>
+        <v>1.229</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.031</v>
+        <v>0.979</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="L17" s="7" t="n">
-        <v>5.252525</v>
+        <v>5.040404</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>-14.546</v>
+        <v>-13.816</v>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         <v>1.993</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>-0.451</v>
+        <v>-0.466</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>-0.518</v>
+        <v>-0.537</v>
       </c>
     </row>
     <row r="18">
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>11.15</v>
+        <v>11.05</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>-0.0124004</v>
+        <v>-0.896856</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.31</v>
@@ -1632,22 +1632,22 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.162</v>
+        <v>-0.17</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.928</v>
+        <v>0.919</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1.233</v>
+        <v>1.225</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>18.583332</v>
+        <v>18.416666</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>12.040647</v>
+        <v>11.932659</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>6.522</v>
+        <v>6.478</v>
       </c>
       <c r="N18" s="7" t="n">
         <v>4.6</v>
@@ -1656,10 +1656,10 @@
         <v>1.07</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.135</v>
+        <v>0.115</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>-0.019</v>
+        <v>-0.028</v>
       </c>
     </row>
     <row r="19">
@@ -1681,8 +1681,8 @@
       <c r="D19" s="3" t="n">
         <v>27.66</v>
       </c>
-      <c r="E19" s="4" t="n">
-        <v>0.217389</v>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>32.74</v>
@@ -1717,7 +1717,7 @@
         <v>1.412</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.053</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0.013</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>0.0102443</v>
+        <v>12.76</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>-0.4680150000000001</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>20.74</v>
@@ -1752,13 +1752,13 @@
         <v>8.455</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.382</v>
+        <v>-0.385</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.63</v>
+        <v>0.627</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>6.134</v>
+        <v>6.131</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>-8.604027</v>
+        <v>-8.563758999999999</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>18.962</v>
+        <v>18.953</v>
       </c>
       <c r="N20" s="7" t="n">
         <v>13</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>-0.291</v>
+        <v>-0.242</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>-0.23</v>
+        <v>-0.233</v>
       </c>
     </row>
     <row r="21">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.83</v>
+        <v>6.96</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.0379939</v>
+        <v>0.0190337</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>9.949999999999999</v>
@@ -1815,22 +1815,22 @@
         <v>6.505</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.314</v>
+        <v>-0.301</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.184</v>
+        <v>0.187</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.516</v>
+        <v>0.519</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>3.4846938</v>
+        <v>3.5510204</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>9.116878</v>
+        <v>9.290405</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>6.938</v>
+        <v>6.986</v>
       </c>
       <c r="N21" s="7" t="n">
         <v>5.6</v>
@@ -1839,10 +1839,10 @@
         <v>1.206</v>
       </c>
       <c r="P21" s="9" t="n">
-        <v>-0.255</v>
+        <v>-0.193</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>-0.239</v>
+        <v>-0.224</v>
       </c>
     </row>
     <row r="22">
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>-0.0114942</v>
+        <v>-0.387597</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>4.95</v>
@@ -1874,7 +1874,7 @@
         <v>2.02</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.479</v>
+        <v>-0.481</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0.093</v>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>-6.2926826</v>
+        <v>-6.2682924</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>12.945</v>
+        <v>12.937</v>
       </c>
       <c r="N22" s="7" t="n">
         <v>9.300000000000001</v>
@@ -1903,7 +1903,7 @@
         <v>-0.358</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.032</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="23">
@@ -2290,34 +2290,34 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>53.7</v>
+        <v>54.15</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0372587</v>
+        <v>0.83799</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.172</v>
+        <v>-0.165</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.255</v>
+        <v>0.277</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>55.6</v>
+        <v>55.3</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.073</v>
+        <v>-0.057</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.031</v>
+        <v>-0.025</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.238</v>
+        <v>-0.231</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
       </c>
       <c r="M2" s="10" t="n">
-        <v>3730880</v>
+        <v>3494820</v>
       </c>
     </row>
     <row r="3">
@@ -2337,34 +2337,34 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>108.67</v>
+        <v>109.25</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.276825</v>
+        <v>0.533728</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0.502</v>
+        <v>-0.499</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.546</v>
+        <v>-0.5329999999999999</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-49.4</v>
+        <v>-50.7</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.298</v>
+        <v>-0.274</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.535</v>
+        <v>-0.529</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.654</v>
+        <v>-0.652</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>1.177</v>
       </c>
       <c r="M3" s="10" t="n">
-        <v>4034930</v>
+        <v>3453730</v>
       </c>
     </row>
     <row r="4">
@@ -2384,34 +2384,34 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24.89</v>
+        <v>25.22</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.0376885</v>
+        <v>0.0130548</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.302</v>
+        <v>-0.293</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.357</v>
+        <v>-0.317</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-32.6</v>
+        <v>-33.1</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.117</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.308</v>
+        <v>-0.297</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.49</v>
+        <v>-0.483</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
       </c>
       <c r="M4" s="10" t="n">
-        <v>14780350</v>
+        <v>14410330</v>
       </c>
     </row>
     <row r="5">
@@ -2431,34 +2431,34 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>100.63</v>
+        <v>103.33</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.199141</v>
+        <v>0.026831</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.177</v>
+        <v>-0.155</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.175</v>
+        <v>0.221</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>38.7</v>
+        <v>38.1</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.099</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.117</v>
+        <v>-0.095</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.253</v>
+        <v>-0.233</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>1.034</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>2562290</v>
+        <v>2397320</v>
       </c>
     </row>
     <row r="6">
@@ -2478,34 +2478,34 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>35.98</v>
+        <v>36.86</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.019084</v>
+        <v>0.0244581</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-0.014</v>
+        <v>0.01</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.11</v>
+        <v>0.157</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>11.9</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.017</v>
+        <v>0.042</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.027</v>
+        <v>0.05</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.104</v>
+        <v>-0.08199999999999999</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>1.396</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>4927380</v>
+        <v>4941190</v>
       </c>
     </row>
     <row r="7">
@@ -2525,45 +2525,45 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>80.04000000000001</v>
+        <v>81.83</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-0.0171906</v>
+        <v>0.0223638</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.048</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>22.1</v>
+        <v/>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.029</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.031</v>
+        <v>-0.01</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>1.22</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>1037530</v>
+        <v>913940</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2572,45 +2572,45 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>86.2</v>
+        <v>58.99</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.185275</v>
+        <v>0.0211182</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.23</v>
+        <v>-0.045</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.225</v>
+        <v>0</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>-2.4</v>
+        <v/>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.116</v>
+        <v>-0.046</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.148</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.272</v>
+        <v>-0.145</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.66</v>
+        <v>1.453</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>1255360</v>
+        <v>797070</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2619,34 +2619,34 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>57.77</v>
+        <v>85.94</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.329973</v>
+        <v>-0.301618</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.068</v>
+        <v>-0.232</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.338</v>
+        <v>-0.218</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>41.2</v>
+        <v>-2.5</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.068</v>
+        <v>-0.108</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.012</v>
+        <v>-0.15</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.163</v>
+        <v>-0.275</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>1.453</v>
+        <v>0.66</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>921060</v>
+        <v>1226060</v>
       </c>
     </row>
     <row r="10">
@@ -2666,45 +2666,45 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.16</v>
+        <v>27.33</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.0320741</v>
+        <v>0.6259209999999999</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.153</v>
+        <v>0.16</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.033</v>
+        <v>-0.008</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-25.4</v>
+        <v>-24.9</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0.177</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.102</v>
+        <v>0.109</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.14</v>
+        <v>-0.135</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>1.977</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>6430020</v>
+        <v>6441400</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2713,45 +2713,45 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>18.18</v>
+        <v>10.67</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-0.0257234</v>
+        <v>0.012334</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.22</v>
+        <v>-0.079</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.107</v>
+        <v>0.588</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-24</v>
+        <v>31.3</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>-0.031</v>
+        <v>0.057</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.262</v>
+        <v>-0.048</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.436</v>
+        <v>-0.258</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>2.002</v>
+        <v>1.1</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>2877430</v>
+        <v>2102710</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2760,34 +2760,34 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.54</v>
+        <v>18.11</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.0131086</v>
+        <v>-0.385037</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-0.095</v>
+        <v>-0.223</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.5770000000000001</v>
+        <v>-0.098</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>32.1</v>
+        <v>-25</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.039</v>
+        <v>-0.024</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.058</v>
+        <v>-0.263</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.267</v>
+        <v>-0.4379999999999999</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>1.1</v>
+        <v>2.002</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>2477770</v>
+        <v>2260380</v>
       </c>
     </row>
     <row r="13">
@@ -2807,34 +2807,34 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>20.19</v>
+        <v>20.53</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-0.296294</v>
+        <v>0.01684</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.046</v>
+        <v>0.063</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.8640000000000001</v>
+        <v>0.9259999999999999</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>53.2</v>
+        <v>52.7</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.081</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.116</v>
+        <v>0.13</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.109</v>
+        <v>-0.094</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>1500550</v>
+        <v>1436220</v>
       </c>
     </row>
     <row r="14">
@@ -2854,34 +2854,34 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5.61</v>
+        <v>5.68</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.357781</v>
+        <v>0.0124777</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.253</v>
+        <v>-0.244</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.012</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.096</v>
+        <v>-0.073</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.287</v>
+        <v>-0.278</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-0.447</v>
+        <v>-0.44</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>0.603</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>2234280</v>
+        <v>1626740</v>
       </c>
     </row>
     <row r="15">
@@ -2901,22 +2901,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>13.98</v>
+        <v>13.97</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-0.0230609</v>
+        <v>-0.07152559999999999</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>-0.059</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.19</v>
+        <v>-0.155</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-18.4</v>
+        <v>-18.6</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.011</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>-0.141</v>
@@ -2928,7 +2928,7 @@
         <v>1.364</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>4547870</v>
+        <v>4252200</v>
       </c>
     </row>
     <row r="16">
@@ -2948,34 +2948,34 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>98.43000000000001</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.0197192</v>
+        <v>-0.0126994</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.028</v>
+        <v>0.015</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.04</v>
+        <v>0.026</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.027</v>
+        <v>0.013</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.136</v>
+        <v>-0.147</v>
       </c>
       <c r="L16" s="8" t="n">
         <v>1.376</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>133860</v>
+        <v>129210</v>
       </c>
     </row>
     <row r="17">
@@ -2995,34 +2995,34 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.2</v>
+        <v>4.99</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-0.0243903</v>
+        <v>-0.0403846</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-0.518</v>
+        <v>-0.537</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.451</v>
+        <v>-0.466</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-23.9</v>
+        <v>-25.3</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.333</v>
+        <v>-0.34</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.4970000000000001</v>
+        <v>-0.515</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.621</v>
+        <v>-0.637</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.993</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>7879890</v>
+        <v>7968370</v>
       </c>
     </row>
     <row r="18">
@@ -3042,34 +3042,34 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>11.15</v>
+        <v>11.05</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.0124004</v>
+        <v>-0.896856</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.019</v>
+        <v>-0.028</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.135</v>
+        <v>0.115</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.025</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.014</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.162</v>
+        <v>-0.17</v>
       </c>
       <c r="L18" s="8" t="n">
         <v>1.07</v>
       </c>
       <c r="M18" s="10" t="n">
-        <v>646330</v>
+        <v>615730</v>
       </c>
     </row>
     <row r="19">
@@ -3092,19 +3092,19 @@
         <v>27.66</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.217389</v>
+        <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>0.013</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.053</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>5</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.011</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>0.028</v>
@@ -3116,7 +3116,7 @@
         <v>1.412</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>129150</v>
+        <v>124940</v>
       </c>
     </row>
     <row r="20">
@@ -3136,28 +3136,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.82</v>
+        <v>12.76</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.0102443</v>
+        <v>-0.4680150000000001</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.23</v>
+        <v>-0.233</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.291</v>
+        <v>-0.242</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>35.4</v>
+        <v>36.3</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.143</v>
+        <v>-0.139</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.031</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.382</v>
+        <v>-0.385</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="M20" s="10" t="n">
-        <v>121900</v>
+        <v>118930</v>
       </c>
     </row>
     <row r="21">
@@ -3185,34 +3185,34 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.83</v>
+        <v>6.96</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.0379939</v>
+        <v>0.0190337</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.239</v>
+        <v>-0.224</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.255</v>
+        <v>-0.193</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.209</v>
+        <v>-0.185</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.205</v>
+        <v>-0.189</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.314</v>
+        <v>-0.301</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>1.206</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>144690</v>
+        <v>185650</v>
       </c>
     </row>
     <row r="22">
@@ -3232,34 +3232,34 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.0114942</v>
+        <v>-0.387597</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.032</v>
+        <v>0.028</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>-0.358</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>-53.2</v>
+        <v>-53.1</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.064</v>
+        <v>0.059</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.168</v>
+        <v>-0.169</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.479</v>
+        <v>-0.481</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.327</v>
       </c>
       <c r="M22" s="10" t="n">
-        <v>174160</v>
+        <v>175460</v>
       </c>
     </row>
     <row r="23">
@@ -3336,7 +3336,7 @@
         <v>-0.239</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>-283</v>
+        <v>-287.6</v>
       </c>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
@@ -3568,31 +3568,31 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>53.7</v>
+        <v>54.15</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>36.308</v>
+        <v>36.613</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>22.851065</v>
+        <v>23.042555</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.2912655</v>
+        <v>14.411025</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>10.725</v>
+        <v>10.792</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>3.735</v>
+        <v>3.758</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.79287</v>
+        <v>22.983871</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.789308</v>
+        <v>2.812682</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3621,10 +3621,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>108.67</v>
+        <v>109.25</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>19.052</v>
+        <v>19.168</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3632,22 +3632,22 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>10.061878</v>
+        <v>10.1155815</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>14.414</v>
+        <v>14.462</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>9.9</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.876</v>
+        <v>1.882</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.1068242</v>
+        <v>2.118069</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1629317</v>
+        <v>1.169992</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24.89</v>
+        <v>25.22</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>12.392</v>
+        <v>12.554</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3687,28 +3687,28 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>12.765685</v>
+        <v>12.95792</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>47.769</v>
+        <v>48.356</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>2.153</v>
+        <v>2.179</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>19.510187</v>
+        <v>19.764889</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>2.0467412</v>
+        <v>2.073461</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1.95015</v>
+        <v>1.9463</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>1.276</v>
@@ -3731,37 +3731,37 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>100.63</v>
+        <v>103.33</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.494</v>
+        <v>10.776</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.047768</v>
+        <v>32.907642</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>16.824804</v>
+        <v>17.390442</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>11.324</v>
+        <v>11.483</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>2.776</v>
+        <v>2.815</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-37.436756</v>
+        <v>-38.441223</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.4701791</v>
+        <v>1.5096254</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>5.98105</v>
+        <v>5.94177</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>-2.688</v>
@@ -3784,31 +3784,31 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>35.98</v>
+        <v>36.86</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9.840999999999999</v>
+        <v>10.081</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>47.342106</v>
+        <v>48.5</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>15.332299</v>
+        <v>15.707298</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>16.705</v>
+        <v>16.8</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>2.243</v>
+        <v>2.256</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.8248115</v>
+        <v>3.9183588</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.5611209</v>
+        <v>0.57484484</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3837,34 +3837,34 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>80.04000000000001</v>
+        <v>81.83</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.042</v>
+        <v>6.178</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.6184447</v>
+        <v>3.6272166</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>9.823980000000001</v>
+        <v>10.043682</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>6.994</v>
+        <v>7.106</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>2.053</v>
+        <v>2.086</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.343297</v>
+        <v>2.3957021</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.4766403</v>
+        <v>1.5096637</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>22.12</v>
+        <v>22.56</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>8.147410000000001</v>
@@ -3876,12 +3876,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3890,51 +3890,51 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>86.2</v>
+        <v>58.99</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.011</v>
+        <v>6.066</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>16.325756</v>
+        <v>18.907053</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>11.609365</v>
+        <v>17.952301</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>11.55</v>
+        <v>8.478</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>3.777</v>
+        <v>3.43</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>5.941959</v>
+        <v>16.514559</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.0542798</v>
+        <v>3.0155654</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>5.28</v>
+        <v>3.12</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>7.42504</v>
+        <v>3.28593</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>14.507</v>
+        <v>3.572</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3943,40 +3943,40 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>57.77</v>
+        <v>85.94</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.94</v>
+        <v>5.992</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>18.516026</v>
+        <v>16.245747</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>17.58102</v>
+        <v>11.574349</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>8.391</v>
+        <v>11.532</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>3.395</v>
+        <v>3.771</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.173012</v>
+        <v>5.924037</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.9531991</v>
+        <v>2.0480838</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>3.12</v>
+        <v>5.29</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>3.28593</v>
+        <v>7.42504</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>3.572</v>
+        <v>14.507</v>
       </c>
     </row>
     <row r="10">
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.16</v>
+        <v>27.33</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.544</v>
+        <v>5.578</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -4007,25 +4007,25 @@
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>29.362162</v>
+        <v>29.545946</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>8.711</v>
+        <v>8.721</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>7.3</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>2.651</v>
+        <v>2.654</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>1.5705777</v>
+        <v>1.5804083</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.48263726</v>
+        <v>0.48565817</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-2.34</v>
+        <v>-2.42</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.925</v>
@@ -4037,12 +4037,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4051,51 +4051,51 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>18.18</v>
+        <v>10.67</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.38</v>
+        <v>5.395</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>51.94286</v>
+        <v>25.404762</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>22.35407</v>
+        <v>12.300988</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10.163</v>
+        <v>10.165</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>3.998</v>
+        <v>2.129</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>4.8683567</v>
+        <v>7.24372</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>4.1709666</v>
+        <v>2.3027554</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.81327474</v>
+        <v>0.86741</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>3.7343197</v>
+        <v>1.473</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -4104,40 +4104,40 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.54</v>
+        <v>18.11</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.329</v>
+        <v>5.36</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>25.09524</v>
+        <v>51.74286</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>12.151116</v>
+        <v>22.197506</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10.031</v>
+        <v>10.121</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>2.101</v>
+        <v>3.982</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>7.1554646</v>
+        <v>4.83426</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>2.2746992</v>
+        <v>4.1549067</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.86741</v>
+        <v>0.81585747</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>1.473</v>
+        <v>3.7461786</v>
       </c>
     </row>
     <row r="13">
@@ -4157,16 +4157,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>20.19</v>
+        <v>20.53</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4.7</v>
+        <v>4.779</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>65.129036</v>
+        <v>66.22581</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>26.980076</v>
+        <v>27.434422</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>13.706721</v>
+        <v>13.937542</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.142987</v>
+        <v>4.212755</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -4216,31 +4216,31 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5.61</v>
+        <v>5.68</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.192</v>
+        <v>2.219</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>12.195652</v>
+        <v>12.347825</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>7.051371</v>
+        <v>7.1393557</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>11.314</v>
+        <v>10.786</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>2.502</v>
+        <v>2.519</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>-1.7580696</v>
+        <v>-1.7800062</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.42448518</v>
+        <v>0.42978176</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0.46</v>
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>13.98</v>
+        <v>13.97</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1.867</v>
+        <v>1.866</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>8.032036</v>
+        <v>8.026291000000001</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>17.104</v>
+        <v>17.102</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>10.8</v>
@@ -4292,10 +4292,10 @@
         <v>1.774</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.9623459</v>
+        <v>0.9616576</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.26820526</v>
+        <v>0.26801342</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>-5.83</v>
@@ -4324,31 +4324,31 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>98.43000000000001</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.761</v>
+        <v>1.738</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>18.127073</v>
+        <v>17.89687</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>16.55677</v>
+        <v>16.34651</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>8.795</v>
+        <v>8.678000000000001</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>3.077</v>
+        <v>3.036</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>3.26208</v>
+        <v>3.2206535</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>3.2295911</v>
+        <v>3.1885774</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>5.43</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.2</v>
+        <v>4.99</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.281</v>
+        <v>1.229</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>5.252525</v>
+        <v>5.040404</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-14.546</v>
+        <v>-13.816</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -4399,16 +4399,16 @@
         </is>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.54</v>
+        <v>1.462</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>1.768106</v>
+        <v>1.6967018</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>1.9130899</v>
+        <v>1.8358303</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.44</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0.99</v>
@@ -4434,31 +4434,31 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>11.15</v>
+        <v>11.05</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.928</v>
+        <v>0.919</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>18.583332</v>
+        <v>18.416666</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>12.040647</v>
+        <v>11.932659</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>6.522</v>
+        <v>6.478</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>4.6</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.927</v>
+        <v>0.92</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>3.4025023</v>
+        <v>3.3719866</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.69706714</v>
+        <v>0.6908155</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>0.6</v>
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.82</v>
+        <v>12.76</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.63</v>
+        <v>0.627</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -4553,25 +4553,25 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>-8.604027</v>
+        <v>-8.563758999999999</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>18.962</v>
+        <v>18.953</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>13</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>2.462</v>
+        <v>2.461</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.2077249</v>
+        <v>1.2020726</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.25303388</v>
+        <v>0.25184965</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-13.39</v>
+        <v>-13.33</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-1.49</v>
@@ -4597,31 +4597,31 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.83</v>
+        <v>6.96</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.184</v>
+        <v>0.187</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>3.4846938</v>
+        <v>3.5510204</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>9.116878</v>
+        <v>9.290405</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>6.938</v>
+        <v>6.986</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>5.6</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.695</v>
+        <v>1.707</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>-11.3267</v>
+        <v>-11.542289</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.6047698</v>
+        <v>0.61628085</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>1.96</v>
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0.093</v>
@@ -4661,25 +4661,25 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>-6.2926826</v>
+        <v>-6.2682924</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>12.945</v>
+        <v>12.937</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.966</v>
+        <v>1.965</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>6.564885</v>
+        <v>6.53944</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.30820388</v>
+        <v>0.30700928</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>-1.09</v>
+        <v>-1.11</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>-0.41</v>
@@ -5462,12 +5462,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -5476,57 +5476,57 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2.926</v>
+        <v>2.011</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.067</v>
+        <v>0.032</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.33583</v>
+        <v>0.6747</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.18802</v>
+        <v>0.31768</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.1309</v>
+        <v>0.0935</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.32698002</v>
+        <v>0.4046</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.35709</v>
+        <v>1.113</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.06236</v>
+        <v>0.09383000399999999</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.957</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.082</v>
+        <v>0.193</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>5.197</v>
+        <v>3.475</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.201</v>
+        <v>0.142</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>492.233</v>
+        <v>1045.932</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>0.604</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -5535,46 +5535,46 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2.011</v>
+        <v>2.926</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.032</v>
+        <v>0.067</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.6747</v>
+        <v>0.33583</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.31768</v>
+        <v>0.18802</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.0935</v>
+        <v>0.1309</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.4046</v>
+        <v>0.32698002</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>1.113</v>
+        <v>0.35709</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.09383000399999999</v>
+        <v>0.06236</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.193</v>
+        <v>0.082</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>3.475</v>
+        <v>5.197</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.142</v>
+        <v>0.201</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>1045.932</v>
+        <v>492.233</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>0.79</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="10">
@@ -5639,12 +5639,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -5653,57 +5653,59 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1.29</v>
+        <v>2.343</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.201</v>
+        <v>0.178</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.26816</v>
+        <v>0.51058</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.15614</v>
+        <v>0.23518999</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.07777000000000001</v>
+        <v>0.09804</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.39339</v>
+        <v>0.20945999</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.10515001</v>
+        <v>0.32813</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.04121</v>
+        <v>0.23642</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>0.341</v>
+        <v>0.491</v>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.063</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.365</v>
+        <v>0.478</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>6.424</v>
+        <v>9.69</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>1.167</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -5712,48 +5714,46 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2.343</v>
+        <v>1.29</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.178</v>
+        <v>0.201</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.51058</v>
+        <v>0.26816</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.23518999</v>
+        <v>0.15614</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.09804</v>
+        <v>0.07777000000000001</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.20945999</v>
+        <v>0.39339</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.32813</v>
+        <v>0.10515001</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.23642</v>
+        <v>0.04121</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.507</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0.341</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.478</v>
+        <v>0.365</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>9.69</v>
+        <v>6.424</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>1.75</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="13">
@@ -5844,16 +5844,16 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.36734</v>
+        <v>0.37937</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.11319</v>
+        <v>0.16118999</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0.03584</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.22117001</v>
+        <v>0.23358</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
@@ -5861,18 +5861,16 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.04816</v>
+        <v>0.05314</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>1.142</v>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1.206</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>0.425</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>7.025</v>
+        <v>7.032</v>
       </c>
       <c r="O14" s="6" t="n">
         <v>1.023</v>
@@ -6843,7 +6841,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>53.7</v>
+        <v>54.15</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6866,7 +6864,7 @@
         <v>58</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.301</v>
+        <v>0.29</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>1.8</v>
@@ -6878,10 +6876,10 @@
         <v>0.57722</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>0.41689</v>
+        <v>0.41693002</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="P2" s="5" t="n">
         <v>0.4255</v>
@@ -6899,7 +6897,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>108.67</v>
+        <v>109.25</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6922,7 +6920,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.958</v>
+        <v>0.9470000000000001</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>1.72</v>
@@ -6931,10 +6929,10 @@
         <v>0.0517</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>0.18747</v>
+        <v>0.18808001</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>0.90977997</v>
+        <v>0.90976</v>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
@@ -6957,7 +6955,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>24.89</v>
+        <v>25.22</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6980,7 +6978,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.451</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -7015,7 +7013,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>100.63</v>
+        <v>103.33</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -7038,7 +7036,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.409</v>
+        <v>0.373</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.24</v>
@@ -7050,10 +7048,10 @@
         <v>0.27027</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0.68579</v>
+        <v>0.68582</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="P5" s="5" t="n">
         <v>0.3185</v>
@@ -7071,7 +7069,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>35.98</v>
+        <v>36.86</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -7094,7 +7092,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.186</v>
+        <v>0.158</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.2</v>
@@ -7106,7 +7104,7 @@
         <v>0.27018</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>0.73443</v>
+        <v>0.73407</v>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
@@ -7129,7 +7127,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>80.04000000000001</v>
+        <v>81.83</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -7152,7 +7150,7 @@
         <v>84</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.18</v>
+        <v>0.154</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.32</v>
@@ -7164,10 +7162,10 @@
         <v>0.32334998</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>0.7323499999999999</v>
+        <v>0.73223</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="P7" s="5" t="n">
         <v>0.0319</v>
@@ -7176,113 +7174,113 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>86.2</v>
+        <v>58.99</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>strong_buy</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>135.5</v>
+        <v>73.33333</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.243</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>2.68</v>
+        <v>3.89</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.044499997</v>
+        <v>0.0762</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.06136</v>
+        <v>0.07935</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0.83892995</v>
+        <v>0.889</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>0.51</v>
+        <v>1.76</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.0828</v>
+        <v>0.32369998</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>57.77</v>
+        <v>85.94</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>73.33333</v>
+        <v>135.5</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.269</v>
+        <v>0.5770000000000001</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>3.89</v>
+        <v>2.68</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.0762</v>
+        <v>0.044499997</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.07935</v>
+        <v>0.06136</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0.889</v>
+        <v>0.81711</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>1.8</v>
+        <v>0.51</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.32369998</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="10">
@@ -7297,7 +7295,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>27.16</v>
+        <v>27.33</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -7320,7 +7318,7 @@
         <v>22</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.177</v>
+        <v>0.169</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>3.8</v>
@@ -7346,117 +7344,117 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>18.18</v>
+        <v>10.67</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>strong_buy</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>1.33333</v>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>28.690083</v>
+        <v>17.375</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>37.003334</v>
+        <v>20</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>21.825605</v>
+        <v>16</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.578</v>
+        <v>0.628</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>4.19</v>
+        <v>4.92</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.1088</v>
+        <v>0.1039</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.01337</v>
+        <v>0.68889</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.9164</v>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.19123</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>1.59</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>0</v>
+        <v>0.2831</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>10.54</v>
+        <v>18.11</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>strong_buy</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1.33333</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>17.375</v>
+        <v>28.769512</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>20</v>
+        <v>37.105778</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>16</v>
+        <v>21.88603</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.648</v>
+        <v>0.589</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>4.92</v>
+        <v>4.19</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.1039</v>
+        <v>0.1088</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.68889</v>
+        <v>0.01337</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0.19123</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>1.58</v>
+        <v>0.9164</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.2831</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7471,7 +7469,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>20.19</v>
+        <v>20.53</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -7494,7 +7492,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.228</v>
+        <v>0.208</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.71</v>
@@ -7529,7 +7527,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>5.61</v>
+        <v>5.68</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -7552,7 +7550,7 @@
         <v>6.4</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.716</v>
+        <v>0.695</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>2.08</v>
@@ -7564,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.33803</v>
+        <v>0.32466</v>
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
@@ -7587,7 +7585,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>13.98</v>
+        <v>13.97</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7610,7 +7608,7 @@
         <v>15</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>4.18</v>
@@ -7645,7 +7643,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>98.43000000000001</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7670,7 +7668,7 @@
         <v>93</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.094</v>
+        <v>0.108</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>2.53</v>
@@ -7685,7 +7683,7 @@
         <v>0.64761</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P16" s="5" t="n">
         <v>0.221</v>
@@ -7703,7 +7701,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>5.2</v>
+        <v>4.99</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7726,7 +7724,7 @@
         <v>6</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.262</v>
+        <v>1.358</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>1.77</v>
@@ -7761,7 +7759,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>11.15</v>
+        <v>11.05</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -7784,7 +7782,7 @@
         <v>14</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.39</v>
+        <v>0.403</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>3.68</v>
@@ -7793,7 +7791,7 @@
         <v>0.028099999</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.17429</v>
+        <v>0.17445</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>0.76091003</v>
@@ -7875,7 +7873,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>12.82</v>
+        <v>12.76</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7898,7 +7896,7 @@
         <v>11</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.268</v>
+        <v>0.274</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>9.16</v>
@@ -7910,7 +7908,7 @@
         <v>0.12553</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.77327</v>
+        <v>0.77101</v>
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
@@ -7933,7 +7931,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>6.83</v>
+        <v>6.96</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -7956,7 +7954,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.9520000000000001</v>
+        <v>0.9159999999999999</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>13.9</v>
@@ -7991,7 +7989,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -8014,7 +8012,7 @@
         <v>2.5</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.26</v>
+        <v>0.265</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>5.72</v>
@@ -8467,10 +8465,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>36.308</v>
+        <v>36.613</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>22.851065</v>
+        <v>23.042555</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -8482,16 +8480,16 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.172</v>
+        <v>-0.165</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>10.725</v>
+        <v>10.792</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>86.09999999999999</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
@@ -8511,7 +8509,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.544</v>
+        <v>5.578</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -8528,10 +8526,10 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.153</v>
+        <v>0.16</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>8.711</v>
+        <v>8.721</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>7.3</v>
@@ -8543,12 +8541,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MLCO</t>
+          <t>WYNN</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Melco Resorts</t>
+          <t>Wynn Resorts</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -8557,16 +8555,16 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.192</v>
+        <v>10.776</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>12.195652</v>
+        <v>32.907642</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.22117001</v>
+        <v>0.24510999</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -8574,27 +8572,27 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.253</v>
+        <v>-0.155</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>11.314</v>
+        <v>11.483</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>40</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MGM</t>
+          <t>MLCO</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Melco Resorts</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -8603,42 +8601,44 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>9.840999999999999</v>
+        <v>2.219</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>47.342106</v>
+        <v>12.347825</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.06</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.13426</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>0.1489</v>
+        <v>0.23358</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.244</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>16.705</v>
+        <v>10.786</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>MGM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Wynn Resorts</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -8647,33 +8647,31 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.494</v>
+        <v>10.081</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>32.047768</v>
+        <v>48.5</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.015</v>
+        <v>0.06</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.24510999</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.13426</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.1489</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.177</v>
+        <v>0.01</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>11.324</v>
+        <v>16.8</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>9.1</v>
+        <v>11.6</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>36.7</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="9">
@@ -8697,12 +8695,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Boyd Gaming</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -8711,42 +8709,42 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.011</v>
+        <v>6.178</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>16.325756</v>
+        <v>3.6272166</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.067</v>
+        <v>0.02</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.32698002</v>
+        <v>0.29349002</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.35709</v>
+        <v>0.87788004</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-0.23</v>
+        <v>-0.048</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>11.55</v>
+        <v>7.106</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>9.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>65.90000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Boyd Gaming</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -8755,42 +8753,42 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6.042</v>
+        <v>5.992</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3.6184447</v>
+        <v>16.245747</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.02</v>
+        <v>0.067</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.29349002</v>
+        <v>0.32698002</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.87788004</v>
+        <v>0.35709</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.232</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>6.994</v>
+        <v>11.532</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>5.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>64.3</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Monarch Casino &amp; Resort</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -8799,42 +8797,42 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1.761</v>
+        <v>6.066</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>18.127073</v>
+        <v>18.907053</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.041</v>
+        <v>0.032</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.34986</v>
+        <v>0.4046</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.19214001</v>
+        <v>1.113</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.045</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>8.795</v>
+        <v>8.478</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>60.3</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Monarch Casino &amp; Resort</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -8843,31 +8841,31 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5.94</v>
+        <v>1.738</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.516026</v>
+        <v>17.89687</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.032</v>
+        <v>0.041</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.4046</v>
+        <v>0.34986</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>1.113</v>
+        <v>0.19214001</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.068</v>
+        <v>0.015</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>8.391</v>
+        <v>8.678000000000001</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>57.1</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="14">
@@ -8887,7 +8885,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.867</v>
+        <v>1.866</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8907,13 +8905,13 @@
         <v>-0.059</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>17.104</v>
+        <v>17.102</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>10.8</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>48.6</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="15">
@@ -8996,10 +8994,10 @@
         <v>-1.4696201</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.032</v>
+        <v>0.028</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>12.945</v>
+        <v>12.937</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>9.300000000000001</v>
@@ -9025,7 +9023,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.63</v>
+        <v>0.627</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -9042,10 +9040,10 @@
         <v>-1.1563</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.23</v>
+        <v>-0.233</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>18.962</v>
+        <v>18.953</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>13</v>
@@ -9089,10 +9087,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.329</v>
+        <v>5.395</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.09524</v>
+        <v>25.404762</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -9104,27 +9102,27 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.095</v>
+        <v>-0.079</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>10.031</v>
+        <v>10.165</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>66.7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>RSI</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Rush Street Interactive</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -9133,42 +9131,46 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.38</v>
+        <v>4.779</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>51.94286</v>
+        <v>66.22581</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.201</v>
+        <v>0.888</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.39339</v>
+        <v>0.11229999</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.10515001</v>
+        <v>0.29505</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>10.163</v>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>8.800000000000001</v>
+        <v>0.063</v>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>58.3</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RSI</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Rush Street Interactive</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -9177,35 +9179,31 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4.7</v>
+        <v>5.36</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>65.129036</v>
+        <v>51.74286</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.888</v>
+        <v>0.201</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.11229999</v>
+        <v>0.39339</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.29505</v>
+        <v>0.10515001</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-0.223</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>10.121</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>56.7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
@@ -9225,7 +9223,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>12.392</v>
+        <v>12.554</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -9242,13 +9240,13 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.302</v>
+        <v>-0.293</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>47.769</v>
+        <v>48.356</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="L23" s="7" t="n">
         <v>52</v>
@@ -9271,7 +9269,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>19.052</v>
+        <v>19.168</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -9288,10 +9286,10 @@
         <v>-0.038829997</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-0.502</v>
+        <v>-0.499</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>14.414</v>
+        <v>14.462</v>
       </c>
       <c r="K24" s="7" t="n">
         <v>9.9</v>
@@ -9317,7 +9315,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.281</v>
+        <v>1.229</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -9334,10 +9332,10 @@
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.518</v>
+        <v>-0.537</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>-14.546</v>
+        <v>-13.816</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
@@ -9439,10 +9437,10 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.184</v>
+        <v>0.187</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>3.4846938</v>
+        <v>3.5510204</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>-0.07000000000000001</v>
@@ -9456,16 +9454,16 @@
         </is>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.239</v>
+        <v>-0.224</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>6.938</v>
+        <v>6.986</v>
       </c>
       <c r="K29" s="7" t="n">
         <v>5.6</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
@@ -9541,10 +9539,10 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.928</v>
+        <v>0.919</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>18.583332</v>
+        <v>18.416666</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>0.075</v>
@@ -9556,10 +9554,10 @@
         <v>0.19236</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>-0.019</v>
+        <v>-0.028</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>6.522</v>
+        <v>6.478</v>
       </c>
       <c r="K31" s="7" t="n">
         <v>4.6</v>
@@ -9571,12 +9569,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LNW</t>
+          <t>AGS</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Light &amp; Wonder</t>
+          <t>PlayAGS</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -9608,7 +9606,7 @@
         </is>
       </c>
       <c r="I32" s="5" t="n">
-        <v>-0.239</v>
+        <v>0</v>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
@@ -9627,12 +9625,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AGS</t>
+          <t>LNW</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>PlayAGS</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -9664,7 +9662,7 @@
         </is>
       </c>
       <c r="I33" s="5" t="n">
-        <v>0</v>
+        <v>-0.239</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
@@ -9677,7 +9675,7 @@
         </is>
       </c>
       <c r="L33" s="7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -9732,22 +9730,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BALY</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Bally's Corporation</t>
+          <t>Monarch Casino &amp; Resort</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -9759,17 +9757,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>LVS</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Monarch Casino &amp; Resort</t>
+          <t>Las Vegas Sands</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -9779,19 +9777,19 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LVS</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Las Vegas Sands</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9806,24 +9804,24 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Regional Operators</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Boyd Gaming</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -9840,17 +9838,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Boyd Gaming</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -9860,24 +9858,24 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>MGM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -9894,12 +9892,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MGM</t>
+          <t>RSI</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Rush Street Interactive</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -9909,51 +9907,51 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RSI</t>
+          <t>MLCO</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Rush Street Interactive</t>
+          <t>Melco Resorts</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>MLCO</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Melco Resorts</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -9968,24 +9966,24 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Regional Operators</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>GENI</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -9995,19 +9993,19 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GENI</t>
+          <t>ACEL</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>Accel Entertainment</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10022,24 +10020,24 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ACEL</t>
+          <t>WYNN</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Accel Entertainment</t>
+          <t>Wynn Resorts</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -10049,19 +10047,19 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>FLUT</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Wynn Resorts</t>
+          <t>Flutter Entertainment</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10076,19 +10074,19 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FLUT</t>
+          <t>LNW</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Flutter Entertainment</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10096,49 +10094,49 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LNW</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Light &amp; Wonder</t>
+          <t>Penn Entertainment</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n"/>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Regional Operators</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>GDEN</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Penn Entertainment</t>
+          <t>Golden Entertainment</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10160,12 +10158,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GDEN</t>
+          <t>FLL</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Golden Entertainment</t>
+          <t>Full House Resorts</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10187,12 +10185,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FLL</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Full House Resorts</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10207,19 +10205,19 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -10229,7 +10227,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10241,12 +10239,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>INSE</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Inspired Entertainment</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10256,39 +10254,39 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>INSE</t>
+          <t>BALY</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Inspired Entertainment</t>
+          <t>Bally's Corporation</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Regional Operators</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10393,7 @@
         <v>0.57722</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.41689</v>
+        <v>0.41693002</v>
       </c>
       <c r="E2" s="7" t="n">
         <v>1.8</v>
@@ -10419,10 +10417,10 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.18747</v>
+        <v>0.18808001</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.90977997</v>
+        <v>0.90976</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>1.72</v>
@@ -10476,7 +10474,7 @@
         <v>0.27027</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.68579</v>
+        <v>0.68582</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>3.24</v>
@@ -10503,7 +10501,7 @@
         <v>0.27018</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.73443</v>
+        <v>0.73407</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>4.2</v>
@@ -10530,7 +10528,7 @@
         <v>0.32334998</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.7323499999999999</v>
+        <v>0.73223</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>3.32</v>
@@ -10545,55 +10543,55 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.06136</v>
+        <v>0.07935</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.83892995</v>
+        <v>0.889</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>2.68</v>
+        <v>3.89</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.044499997</v>
+        <v>0.0762</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>2574942</v>
+        <v>3025746</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.07935</v>
+        <v>0.06136</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.889</v>
+        <v>0.81711</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3.89</v>
+        <v>2.68</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.0762</v>
+        <v>0.044499997</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>3025746</v>
+        <v>2574942</v>
       </c>
     </row>
     <row r="10">
@@ -10626,55 +10624,55 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.01337</v>
+        <v>0.68889</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.9164</v>
+        <v>0.19123</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>4.19</v>
+        <v>4.92</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.1088</v>
+        <v>0.1039</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>11183802</v>
+        <v>16337061</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.68889</v>
+        <v>0.01337</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.19123</v>
+        <v>0.9164</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>4.92</v>
+        <v>4.19</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1039</v>
+        <v>0.1088</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>16337061</v>
+        <v>11183802</v>
       </c>
     </row>
     <row r="13">
@@ -10719,7 +10717,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.33803</v>
+        <v>0.32466</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2.08</v>
@@ -10824,7 +10822,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.17429</v>
+        <v>0.17445</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>0.76091003</v>
@@ -10881,7 +10879,7 @@
         <v>0.12553</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.77327</v>
+        <v>0.77101</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>9.16</v>
@@ -11141,955 +11139,955 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1256.85</v>
+        <v>1284.25</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>1194.19</v>
+        <v>1203.2</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>1045.98</v>
+        <v>1050.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1271.03</v>
+        <v>1286.26</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1203.2</v>
+        <v>1214.11</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>1050.47</v>
+        <v>1051.72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1273.68</v>
+        <v>1291.62</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1214.11</v>
+        <v>1221.67</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>1051.72</v>
+        <v>1060.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1279.13</v>
+        <v>1275.63</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1221.67</v>
+        <v>1227.26</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1060.61</v>
+        <v>1059.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1263.09</v>
+        <v>1276.23</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1227.26</v>
+        <v>1231.57</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1059.06</v>
+        <v>1061.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1262.99</v>
+        <v>1281.42</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1231.57</v>
+        <v>1231.45</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1061.38</v>
+        <v>1062.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1269.05</v>
+        <v>1270.4</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1231.45</v>
+        <v>1227.06</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1062.16</v>
+        <v>1054.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1258.94</v>
+        <v>1265.08</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1227.06</v>
+        <v>1225.56</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1054.67</v>
+        <v>1052.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1254.27</v>
+        <v>1258.23</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1225.56</v>
+        <v>1216.48</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1052.86</v>
+        <v>1055.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1246.67</v>
+        <v>1262.5</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>1216.48</v>
+        <v>1218.71</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1055.44</v>
+        <v>1056.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1251.87</v>
+        <v>1263.36</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1218.71</v>
+        <v>1226.83</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1056.48</v>
+        <v>1054.41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1253.03</v>
+        <v>1246.07</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1226.83</v>
+        <v>1234.12</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>1054.41</v>
+        <v>1047.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1237.26</v>
+        <v>1196.46</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1234.12</v>
+        <v>1230.15</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>1047.95</v>
+        <v>1028.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1190.64</v>
+        <v>1220.22</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1230.15</v>
+        <v>1230.02</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1028.84</v>
+        <v>1045.89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1215.67</v>
+        <v>1190.53</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1230.02</v>
+        <v>1238.16</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1045.89</v>
+        <v>1038.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1187.66</v>
+        <v>1185.99</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1238.16</v>
+        <v>1240.1</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>1038.4</v>
+        <v>1034.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1182.73</v>
+        <v>1176.4</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1240.1</v>
+        <v>1237.62</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1034.27</v>
+        <v>1022.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1174.83</v>
+        <v>1174.78</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>1237.62</v>
+        <v>1231.54</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>1022.13</v>
+        <v>1024.71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1172.49</v>
+        <v>1192.83</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1231.54</v>
+        <v>1234.89</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1024.71</v>
+        <v>1036.07</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1191.61</v>
+        <v>1152.83</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1234.89</v>
+        <v>1233.86</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>1036.07</v>
+        <v>1015.93</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1154.75</v>
+        <v>1130.58</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1233.86</v>
+        <v>1208.74</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1015.93</v>
+        <v>999.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1131.31</v>
+        <v>1136.66</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>1208.74</v>
+        <v>1222.69</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>999.4</v>
+        <v>1001.21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1137.25</v>
+        <v>1142.92</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>1222.69</v>
+        <v>1229.08</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1001.21</v>
+        <v>1009.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1142.2</v>
+        <v>1126.26</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>1229.08</v>
+        <v>1229.52</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>1009.22</v>
+        <v>1002.24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1126.4</v>
+        <v>1132.44</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>1229.52</v>
+        <v>1235.77</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>1002.24</v>
+        <v>1007.93</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1131.96</v>
+        <v>1119.85</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>1235.77</v>
+        <v>1240.69</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>1007.93</v>
+        <v>1004.31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1118.77</v>
+        <v>1119.85</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>1240.69</v>
+        <v>1240.56</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>1004.31</v>
+        <v>996.5599999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1120.5</v>
+        <v>1063.19</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1240.56</v>
+        <v>1238.1</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>996.5599999999999</v>
+        <v>980.29</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1070.86</v>
+        <v>1047.24</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>1238.1</v>
+        <v>1234.41</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>980.29</v>
+        <v>959.12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1057.51</v>
+        <v>1065.92</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>1234.41</v>
+        <v>1240.55</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>959.12</v>
+        <v>968.41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1074.61</v>
+        <v>1062.22</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>1240.55</v>
+        <v>1230.06</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>968.41</v>
+        <v>957.5700000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1070.47</v>
+        <v>1083.61</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>1230.06</v>
+        <v>1224.1</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>957.5700000000001</v>
+        <v>978.74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1091.14</v>
+        <v>1057.65</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>1224.1</v>
+        <v>1208.81</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>978.74</v>
+        <v>959.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1065.74</v>
+        <v>1084.62</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>1208.81</v>
+        <v>1232</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>959.63</v>
+        <v>977.71</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1092.41</v>
+        <v>1087.5</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>1232</v>
+        <v>1237.94</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>977.71</v>
+        <v>984.9400000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1094.75</v>
+        <v>1081.36</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>1237.94</v>
+        <v>1234.68</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>984.9400000000001</v>
+        <v>986.75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1091.55</v>
+        <v>1067.11</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>1234.68</v>
+        <v>1234.39</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>986.75</v>
+        <v>979.26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1076.3</v>
+        <v>1030.68</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>1234.39</v>
+        <v>1215.32</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>979.26</v>
+        <v>945.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1040.23</v>
+        <v>1018.83</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>1215.32</v>
+        <v>1216.18</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>945.17</v>
+        <v>933.04</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1029.29</v>
+        <v>1032.96</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>1216.18</v>
+        <v>1218.14</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>933.04</v>
+        <v>934.84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1044.31</v>
+        <v>1066.36</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>1218.14</v>
+        <v>1224.28</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>934.84</v>
+        <v>960.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1077.55</v>
+        <v>1059.78</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>1224.28</v>
+        <v>1221.05</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>960.15</v>
+        <v>955.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1072.45</v>
+        <v>1060.31</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>1221.05</v>
+        <v>1229.88</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>955.5</v>
+        <v>953.1799999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1072.72</v>
+        <v>1018.71</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>1229.88</v>
+        <v>1217.32</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>953.1799999999999</v>
+        <v>931.74</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1030.25</v>
+        <v>1032.23</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>1217.32</v>
+        <v>1226.17</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>931.74</v>
+        <v>939.75</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1044.65</v>
+        <v>1037.32</v>
       </c>
       <c r="C47" s="13" t="n">
-        <v>1226.17</v>
+        <v>1236.52</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>939.75</v>
+        <v>941.04</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1048.76</v>
+        <v>1066.75</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>1236.52</v>
+        <v>1229.65</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>941.04</v>
+        <v>943.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1077.86</v>
+        <v>1057.54</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>1229.65</v>
+        <v>1223.74</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>943.36</v>
+        <v>947.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1064.77</v>
+        <v>1052.84</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>1223.74</v>
+        <v>1224.44</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>947.5</v>
+        <v>938.97</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1060.26</v>
+        <v>1049.46</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>1224.44</v>
+        <v>1213.65</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>938.97</v>
+        <v>932.52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1056.52</v>
+        <v>1067.33</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>1213.65</v>
+        <v>1222.21</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>932.52</v>
+        <v>938.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1072.35</v>
+        <v>1065.41</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>1222.21</v>
+        <v>1215.39</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>938.2</v>
+        <v>932.26</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1070.15</v>
+        <v>1034.34</v>
       </c>
       <c r="C54" s="13" t="n">
-        <v>1215.39</v>
+        <v>1199.46</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>932.26</v>
+        <v>922.71</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1038.83</v>
+        <v>1035.28</v>
       </c>
       <c r="C55" s="13" t="n">
-        <v>1199.46</v>
+        <v>1209.97</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>922.71</v>
+        <v>924.77</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1040.36</v>
+        <v>1034.42</v>
       </c>
       <c r="C56" s="13" t="n">
-        <v>1209.97</v>
+        <v>1208.03</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>924.77</v>
+        <v>922.96</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1039.48</v>
+        <v>1047.79</v>
       </c>
       <c r="C57" s="13" t="n">
-        <v>1208.03</v>
+        <v>1206.51</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>922.96</v>
+        <v>927.35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1053.89</v>
+        <v>1035.29</v>
       </c>
       <c r="C58" s="13" t="n">
-        <v>1206.51</v>
+        <v>1188.19</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>927.35</v>
+        <v>916.25</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1040.47</v>
+        <v>1037.18</v>
       </c>
       <c r="C59" s="13" t="n">
-        <v>1188.19</v>
+        <v>1181.46</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>916.25</v>
+        <v>914.1799999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1042.47</v>
+        <v>1028.97</v>
       </c>
       <c r="C60" s="13" t="n">
-        <v>1181.46</v>
+        <v>1193.49</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>914.1799999999999</v>
+        <v>911.34</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1033.77</v>
+        <v>1039.99</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -12101,7 +12099,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1033.77</v>
+        <v>1039.99</v>
       </c>
     </row>
     <row r="64">
@@ -12112,7 +12110,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-17.42%</t>
+          <t>-17.62%</t>
         </is>
       </c>
     </row>
@@ -12133,7 +12131,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>136.7</v>
+        <v>138.1</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -61,13 +61,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00FF0000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FF0000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.15</v>
+        <v>53.69</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.83799</v>
+        <v>-0.44502443</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,22 +670,22 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.231</v>
+        <v>-0.238</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>36.613</v>
+        <v>36.302</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>48.919</v>
+        <v>48.771</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.042555</v>
+        <v>22.84681</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.411025</v>
+        <v>14.288604</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>10.792</v>
+        <v>10.759</v>
       </c>
       <c r="N2" s="7" t="n">
         <v>9.199999999999999</v>
@@ -693,11 +693,11 @@
       <c r="O2" s="8" t="n">
         <v>0.888</v>
       </c>
-      <c r="P2" s="4" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="Q2" s="9" t="n">
-        <v>-0.165</v>
+      <c r="P2" s="9" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>-0.172</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>109.25</v>
+        <v>104.75</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.533728</v>
+        <v>-0.016431925</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -729,13 +729,13 @@
         <v>99.95999999999999</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-0.652</v>
+        <v>-0.6659999999999999</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>19.168</v>
+        <v>18.378</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>30.833</v>
+        <v>30.351</v>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>10.1155815</v>
+        <v>9.698921</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>14.462</v>
+        <v>14.236</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>1.177</v>
       </c>
-      <c r="P3" s="9" t="n">
-        <v>-0.5329999999999999</v>
-      </c>
-      <c r="Q3" s="9" t="n">
-        <v>-0.499</v>
+      <c r="P3" s="4" t="n">
+        <v>-0.5670000000000001</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="4">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>25.22</v>
+        <v>24.74</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.0130548</v>
+        <v>-0.021360795</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -790,13 +790,13 @@
         <v>21.01</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.483</v>
+        <v>-0.493</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>12.554</v>
+        <v>12.315</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>13.196</v>
+        <v>13.225</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
@@ -804,22 +804,22 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>12.95792</v>
+        <v>12.711298</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>48.356</v>
+        <v>48.464</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>1.682</v>
       </c>
-      <c r="P4" s="9" t="n">
-        <v>-0.317</v>
-      </c>
-      <c r="Q4" s="9" t="n">
-        <v>-0.293</v>
+      <c r="P4" s="4" t="n">
+        <v>-0.358</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>-0.306</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>103.33</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0.026831</v>
+        <v>101.69</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0.06888378000000001</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,34 +851,34 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.233</v>
+        <v>-0.245</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.776</v>
+        <v>10.605</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>20.09</v>
+        <v>19.915</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.907642</v>
+        <v>32.38535</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>17.390442</v>
+        <v>17.11443</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>11.483</v>
+        <v>11.382</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>1.034</v>
       </c>
-      <c r="P5" s="4" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="Q5" s="9" t="n">
-        <v>-0.155</v>
+      <c r="P5" s="9" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>-0.169</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.86</v>
+        <v>36.13</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.0244581</v>
+        <v>-0.6598787</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,22 +910,22 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.08199999999999999</v>
+        <v>-0.1</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10.081</v>
+        <v>9.882</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>39.557</v>
+        <v>39.432</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>48.5</v>
+        <v>47.539474</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>15.707298</v>
+        <v>15.39622</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>16.8</v>
+        <v>16.747</v>
       </c>
       <c r="N6" s="7" t="n">
         <v>11.6</v>
@@ -933,11 +933,11 @@
       <c r="O6" s="8" t="n">
         <v>1.396</v>
       </c>
-      <c r="P6" s="4" t="n">
-        <v>0.157</v>
+      <c r="P6" s="9" t="n">
+        <v>0.105</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="7">
@@ -959,8 +959,8 @@
       <c r="D7" s="3" t="n">
         <v>81.83</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>0.0223638</v>
+      <c r="E7" s="9" t="n">
+        <v>0.12235222</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -975,7 +975,7 @@
         <v>6.178</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>8.534000000000001</v>
+        <v>8.526999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.6272166</v>
@@ -984,7 +984,7 @@
         <v>10.043682</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>7.106</v>
+        <v>7.1</v>
       </c>
       <c r="N7" s="7" t="n">
         <v>5.9</v>
@@ -992,10 +992,10 @@
       <c r="O7" s="8" t="n">
         <v>1.22</v>
       </c>
-      <c r="P7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="9" t="n">
+      <c r="P7" s="9" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="Q7" s="4" t="n">
         <v>-0.048</v>
       </c>
     </row>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.99</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0.0211182</v>
+        <v>58.74</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.010146176</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1028,34 +1028,34 @@
         <v>35.09</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.145</v>
+        <v>-0.149</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.066</v>
+        <v>6.04</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>6.9</v>
+        <v>6.851</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>18.907053</v>
+        <v>18.826923</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>17.952301</v>
+        <v>17.876219</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>8.478</v>
+        <v>8.417999999999999</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>1.453</v>
       </c>
-      <c r="P8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9" t="n">
-        <v>-0.045</v>
+      <c r="P8" s="9" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>-0.049</v>
       </c>
     </row>
     <row r="9">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.94</v>
+        <v>86.25</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>-0.301618</v>
+        <v>0.5127636</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>118.46</v>
@@ -1087,22 +1087,22 @@
         <v>80.23999999999999</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.275</v>
+        <v>-0.272</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.992</v>
+        <v>6.011</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>11.032</v>
+        <v>11.023</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.245747</v>
+        <v>16.304348</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>11.574349</v>
+        <v>11.616099</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>11.532</v>
+        <v>11.522</v>
       </c>
       <c r="N9" s="7" t="n">
         <v>9.699999999999999</v>
@@ -1110,11 +1110,11 @@
       <c r="O9" s="8" t="n">
         <v>0.66</v>
       </c>
-      <c r="P9" s="9" t="n">
-        <v>-0.218</v>
-      </c>
-      <c r="Q9" s="9" t="n">
-        <v>-0.232</v>
+      <c r="P9" s="4" t="n">
+        <v>-0.234</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.33</v>
+        <v>27.11</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.6259209999999999</v>
+        <v>-0.011666048</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>31.58</v>
@@ -1146,13 +1146,13 @@
         <v>17.86</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.135</v>
+        <v>-0.142</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.578</v>
+        <v>5.533</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>30.479</v>
+        <v>30.5</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="L10" s="7" t="n">
-        <v>29.545946</v>
+        <v>29.30811</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>8.721</v>
+        <v>8.727</v>
       </c>
       <c r="N10" s="7" t="n">
         <v>7.3</v>
@@ -1171,22 +1171,22 @@
       <c r="O10" s="8" t="n">
         <v>1.977</v>
       </c>
-      <c r="P10" s="9" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>0.16</v>
+      <c r="P10" s="4" t="n">
+        <v>-0.06900000000000001</v>
+      </c>
+      <c r="Q10" s="9" t="n">
+        <v>0.151</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1195,57 +1195,57 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0.012334</v>
+        <v>18.67</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.016884502</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>14.38</v>
+        <v>32.22</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5.59</v>
+        <v>15.725</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.258</v>
+        <v>-0.421</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.395</v>
+        <v>5.525</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>4.988</v>
+        <v>5.211</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>25.404762</v>
+        <v>51.86111</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12.300988</v>
+        <v>22.80457</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>10.165</v>
+        <v>10.269</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>1.1</v>
+        <v>2.002</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="Q11" s="9" t="n">
-        <v>-0.079</v>
+        <v>-0.181</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>-0.199</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1254,46 +1254,46 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>18.11</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>-0.385037</v>
+        <v>10.32</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>-0.02272734</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>32.22</v>
+        <v>14.38</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>15.725</v>
+        <v>5.59</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.4379999999999999</v>
+        <v>-0.282</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.36</v>
+        <v>5.218</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>5.136</v>
+        <v>4.932</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>51.74286</v>
+        <v>24.571428</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>22.197506</v>
+        <v>11.897488</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>10.121</v>
+        <v>10.051</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>2.002</v>
+        <v>1.1</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>-0.098</v>
-      </c>
-      <c r="Q12" s="9" t="n">
-        <v>-0.223</v>
+        <v>0.498</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>-0.109</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>20.53</v>
+        <v>20.19</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.01684</v>
+        <v>-0.013678495</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.109</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>4.779</v>
+        <v>4.7</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>66.22581</v>
+        <v>65.129036</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>27.434422</v>
+        <v>26.980076</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1354,11 +1354,11 @@
       <c r="O13" s="8" t="n">
         <v>1.552</v>
       </c>
-      <c r="P13" s="4" t="n">
-        <v>0.9259999999999999</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>0.063</v>
+      <c r="P13" s="9" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>0.046</v>
       </c>
     </row>
     <row r="14">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5.68</v>
+        <v>5.5</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.0124777</v>
+        <v>-0.011680154</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>10.15</v>
@@ -1390,34 +1390,34 @@
         <v>4.55</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-0.44</v>
+        <v>-0.458</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.219</v>
+        <v>2.147</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>13.009</v>
+        <v>12.868</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>12.347825</v>
+        <v>11.945652</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>7.1393557</v>
+        <v>6.9068236</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>10.786</v>
+        <v>10.669</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>0.603</v>
       </c>
-      <c r="P14" s="9" t="n">
-        <v>-0.012</v>
-      </c>
-      <c r="Q14" s="9" t="n">
-        <v>-0.244</v>
+      <c r="P14" s="4" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>-0.268</v>
       </c>
     </row>
     <row r="15">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>13.97</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>-0.07152559999999999</v>
+        <v>13.84</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>-0.036127996</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20.61</v>
@@ -1449,13 +1449,13 @@
         <v>11.65</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.322</v>
+        <v>-0.328</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.866</v>
+        <v>1.848</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>12.351</v>
+        <v>12.334</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="L15" s="7" t="n">
-        <v>8.026291000000001</v>
+        <v>7.948728</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>17.102</v>
+        <v>17.079</v>
       </c>
       <c r="N15" s="7" t="n">
         <v>10.8</v>
@@ -1474,11 +1474,11 @@
       <c r="O15" s="8" t="n">
         <v>1.364</v>
       </c>
-      <c r="P15" s="9" t="n">
-        <v>-0.155</v>
-      </c>
-      <c r="Q15" s="9" t="n">
-        <v>-0.059</v>
+      <c r="P15" s="4" t="n">
+        <v>-0.205</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>-0.068</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>97.18000000000001</v>
+        <v>96.67</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>-0.0126994</v>
+        <v>0.2852713</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>113.88</v>
@@ -1510,34 +1510,34 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.147</v>
+        <v>-0.151</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.738</v>
+        <v>1.729</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1.655</v>
+        <v>1.641</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>17.89687</v>
+        <v>17.80387</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>16.34651</v>
+        <v>16.261564</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>8.678000000000001</v>
+        <v>8.605</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>1.376</v>
       </c>
-      <c r="P16" s="4" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="Q16" s="4" t="n">
-        <v>0.015</v>
+      <c r="P16" s="9" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="Q16" s="9" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="17">
@@ -1557,25 +1557,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>-0.0403846</v>
+        <v>4.7</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>-0.016736735</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>13.73</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>4.96</v>
+        <v>4.68</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.637</v>
+        <v>-0.6579999999999999</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.229</v>
+        <v>1.155</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.979</v>
+        <v>0.925</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="L17" s="7" t="n">
-        <v>5.040404</v>
+        <v>4.737374</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>-13.816</v>
+        <v>-7.671</v>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
@@ -1596,11 +1596,11 @@
       <c r="O17" s="8" t="n">
         <v>1.993</v>
       </c>
-      <c r="P17" s="9" t="n">
-        <v>-0.466</v>
-      </c>
-      <c r="Q17" s="9" t="n">
-        <v>-0.537</v>
+      <c r="P17" s="4" t="n">
+        <v>-0.513</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>-0.5639999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>11.05</v>
+        <v>10.96</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>-0.896856</v>
+        <v>0.016697617</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.31</v>
@@ -1632,34 +1632,34 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.17</v>
+        <v>-0.177</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.919</v>
+        <v>0.912</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1.225</v>
+        <v>1.203</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>18.416666</v>
+        <v>18.266666</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>11.932659</v>
+        <v>11.83547</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>6.478</v>
+        <v>6.362</v>
       </c>
       <c r="N18" s="7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>1.07</v>
       </c>
-      <c r="P18" s="4" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="Q18" s="9" t="n">
-        <v>-0.028</v>
+      <c r="P18" s="9" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>-0.036</v>
       </c>
     </row>
     <row r="19">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>27.66</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>27.16</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>0.64839256</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>32.74</v>
@@ -1691,13 +1691,13 @@
         <v>19.57</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.155</v>
+        <v>-0.17</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.73</v>
+        <v>0.717</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.187</v>
+        <v>1.17</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
@@ -1705,22 +1705,22 @@
         </is>
       </c>
       <c r="L19" s="7" t="n">
-        <v>22.859503</v>
+        <v>22.450413</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>9.728</v>
+        <v>9.584</v>
       </c>
       <c r="N19" s="7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>1.412</v>
       </c>
-      <c r="P19" s="4" t="n">
-        <v>0.05599999999999999</v>
-      </c>
-      <c r="Q19" s="4" t="n">
-        <v>0.013</v>
+      <c r="P19" s="9" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="Q19" s="9" t="n">
+        <v>0.004</v>
       </c>
     </row>
     <row r="20">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.76</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>-0.4680150000000001</v>
+        <v>12.25</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-0.013687607</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>20.74</v>
@@ -1752,13 +1752,13 @@
         <v>8.455</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.385</v>
+        <v>-0.409</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.627</v>
+        <v>0.602</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>6.131</v>
+        <v>6.114</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>-8.563758999999999</v>
+        <v>-8.221477</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>18.953</v>
+        <v>18.901</v>
       </c>
       <c r="N20" s="7" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="O20" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="P20" s="9" t="n">
-        <v>-0.242</v>
-      </c>
-      <c r="Q20" s="9" t="n">
-        <v>-0.233</v>
+      <c r="P20" s="4" t="n">
+        <v>-0.246</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>-0.264</v>
       </c>
     </row>
     <row r="21">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.96</v>
+        <v>6.74</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.0190337</v>
+        <v>-0.14815153</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>9.949999999999999</v>
@@ -1815,34 +1815,36 @@
         <v>6.505</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.301</v>
+        <v>-0.323</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.187</v>
+        <v>0.182</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>3.5510204</v>
+        <v>0.513</v>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>9.290405</v>
+        <v>8.996743</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>6.986</v>
+        <v>6.909</v>
       </c>
       <c r="N21" s="7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>1.206</v>
       </c>
-      <c r="P21" s="9" t="n">
-        <v>-0.193</v>
-      </c>
-      <c r="Q21" s="9" t="n">
-        <v>-0.224</v>
+      <c r="P21" s="4" t="n">
+        <v>-0.266</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>-0.249</v>
       </c>
     </row>
     <row r="22">
@@ -1862,10 +1864,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>-0.387597</v>
+        <v>2.46</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-0.017928318</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>4.95</v>
@@ -1874,13 +1876,13 @@
         <v>2.02</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.481</v>
+        <v>-0.503</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.093</v>
+        <v>0.089</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.594</v>
+        <v>0.592</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
@@ -1888,22 +1890,22 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>-6.2682924</v>
+        <v>-6.012195</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>12.937</v>
+        <v>12.89</v>
       </c>
       <c r="N22" s="7" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>1.327</v>
       </c>
-      <c r="P22" s="9" t="n">
-        <v>-0.358</v>
+      <c r="P22" s="4" t="n">
+        <v>-0.406</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.028</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="23">
@@ -2035,10 +2037,10 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="P24" s="9" t="n">
+      <c r="P24" s="4" t="n">
         <v>-0.239</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="4" t="n">
         <v>-0.239</v>
       </c>
     </row>
@@ -2290,34 +2292,34 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.15</v>
+        <v>53.69</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.83799</v>
+        <v>-0.44502443</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.172</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.277</v>
+        <v>0.248</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>55.3</v>
+        <v>54.3</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.057</v>
+        <v>-0.062</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.025</v>
+        <v>-0.034</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.231</v>
+        <v>-0.238</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
       </c>
       <c r="M2" s="10" t="n">
-        <v>3494820</v>
+        <v>3657680</v>
       </c>
     </row>
     <row r="3">
@@ -2337,34 +2339,34 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>109.25</v>
+        <v>104.75</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.533728</v>
+        <v>-0.016431925</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0.499</v>
+        <v>-0.52</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.5329999999999999</v>
+        <v>-0.5670000000000001</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-50.7</v>
+        <v>-52.9</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.274</v>
+        <v>-0.294</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.529</v>
+        <v>-0.547</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.652</v>
+        <v>-0.6659999999999999</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>1.177</v>
       </c>
       <c r="M3" s="10" t="n">
-        <v>3453730</v>
+        <v>3371670</v>
       </c>
     </row>
     <row r="4">
@@ -2384,34 +2386,34 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>25.22</v>
+        <v>24.74</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.0130548</v>
+        <v>-0.021360795</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.293</v>
+        <v>-0.306</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.317</v>
+        <v>-0.358</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-33.1</v>
+        <v>-34.1</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.09300000000000001</v>
+        <v>-0.103</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.297</v>
+        <v>-0.309</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.483</v>
+        <v>-0.493</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
       </c>
       <c r="M4" s="10" t="n">
-        <v>14410330</v>
+        <v>13953270</v>
       </c>
     </row>
     <row r="5">
@@ -2431,34 +2433,34 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>103.33</v>
+        <v>101.69</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.026831</v>
+        <v>0.06888378000000001</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.155</v>
+        <v>-0.169</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.221</v>
+        <v>0.207</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>38.1</v>
+        <v>36.9</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.095</v>
+        <v>-0.109</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.233</v>
+        <v>-0.245</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>1.034</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>2397320</v>
+        <v>2211770</v>
       </c>
     </row>
     <row r="6">
@@ -2478,34 +2480,34 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.86</v>
+        <v>36.13</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.0244581</v>
+        <v>-0.6598787</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.157</v>
+        <v>0.105</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>11.9</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.042</v>
+        <v>0.021</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.05</v>
+        <v>0.029</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.08199999999999999</v>
+        <v>-0.1</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>1.396</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>4941190</v>
+        <v>4843830</v>
       </c>
     </row>
     <row r="7">
@@ -2528,22 +2530,22 @@
         <v>81.83</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.0223638</v>
+        <v>0.12235222</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>-0.048</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v/>
+        <v>21.4</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.027</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.011</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>-0.09</v>
@@ -2552,7 +2554,7 @@
         <v>1.22</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>913940</v>
+        <v>918240</v>
       </c>
     </row>
     <row r="8">
@@ -2572,34 +2574,34 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.99</v>
+        <v>58.74</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.0211182</v>
+        <v>0.010146176</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.045</v>
+        <v>-0.049</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v/>
+        <v>40.2</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.046</v>
+        <v>-0.049</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.145</v>
+        <v>-0.149</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>1.453</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>797070</v>
+        <v>813400</v>
       </c>
     </row>
     <row r="9">
@@ -2619,34 +2621,34 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.94</v>
+        <v>86.25</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-0.301618</v>
+        <v>0.5127636</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.232</v>
+        <v>-0.23</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.218</v>
+        <v>-0.234</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-2.5</v>
+        <v>-2.9</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.108</v>
+        <v>-0.1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.146</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.275</v>
+        <v>-0.272</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>0.66</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>1226060</v>
+        <v>1211900</v>
       </c>
     </row>
     <row r="10">
@@ -2666,45 +2668,45 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.33</v>
+        <v>27.11</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.6259209999999999</v>
+        <v>-0.011666048</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.16</v>
+        <v>0.151</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-24.9</v>
+        <v>-24</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.177</v>
+        <v>0.164</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.109</v>
+        <v>0.099</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.135</v>
+        <v>-0.142</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>1.977</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>6441400</v>
+        <v>6400370</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2713,45 +2715,45 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.67</v>
+        <v>18.67</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.012334</v>
+        <v>0.016884502</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.199</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.588</v>
+        <v>-0.181</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>31.3</v>
+        <v>-26.3</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.057</v>
+        <v>0.012</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.048</v>
+        <v>-0.24</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.258</v>
+        <v>-0.421</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>1.1</v>
+        <v>2.002</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>2102710</v>
+        <v>2197460</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2760,34 +2762,34 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>18.11</v>
+        <v>10.32</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.385037</v>
+        <v>-0.02272734</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-0.223</v>
+        <v>-0.109</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.098</v>
+        <v>0.498</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-25</v>
+        <v>30</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.025</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.263</v>
+        <v>-0.08</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.4379999999999999</v>
+        <v>-0.282</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>2.002</v>
+        <v>1.1</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>2260380</v>
+        <v>1869320</v>
       </c>
     </row>
     <row r="13">
@@ -2807,34 +2809,34 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>20.53</v>
+        <v>20.19</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.01684</v>
+        <v>-0.013678495</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.063</v>
+        <v>0.046</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.9259999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>52.7</v>
+        <v>52</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.13</v>
+        <v>0.109</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.109</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>1436220</v>
+        <v>1498110</v>
       </c>
     </row>
     <row r="14">
@@ -2854,34 +2856,34 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5.68</v>
+        <v>5.5</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.0124777</v>
+        <v>-0.011680154</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.244</v>
+        <v>-0.268</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.012</v>
+        <v>-0.049</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>14</v>
+        <v>12.1</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.073</v>
+        <v>-0.09699999999999999</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.278</v>
+        <v>-0.3</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-0.44</v>
+        <v>-0.458</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>0.603</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>1626740</v>
+        <v>1467500</v>
       </c>
     </row>
     <row r="15">
@@ -2901,34 +2903,34 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>13.97</v>
+        <v>13.84</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-0.07152559999999999</v>
+        <v>-0.036127996</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.059</v>
+        <v>-0.068</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.155</v>
+        <v>-0.205</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-18.6</v>
+        <v>-19</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.141</v>
+        <v>-0.149</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.322</v>
+        <v>-0.328</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>1.364</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>4252200</v>
+        <v>4104850</v>
       </c>
     </row>
     <row r="16">
@@ -2948,34 +2950,34 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>97.18000000000001</v>
+        <v>96.67</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.0126994</v>
+        <v>0.2852713</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.21</v>
+        <v>0.191</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.013</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.147</v>
+        <v>-0.151</v>
       </c>
       <c r="L16" s="8" t="n">
         <v>1.376</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>129210</v>
+        <v>132400</v>
       </c>
     </row>
     <row r="17">
@@ -2995,34 +2997,34 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.99</v>
+        <v>4.7</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-0.0403846</v>
+        <v>-0.016736735</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-0.537</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.466</v>
+        <v>-0.513</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-25.3</v>
+        <v>-27.9</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.34</v>
+        <v>-0.368</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.515</v>
+        <v>-0.542</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.637</v>
+        <v>-0.6579999999999999</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.993</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>7968370</v>
+        <v>7512390</v>
       </c>
     </row>
     <row r="18">
@@ -3042,34 +3044,34 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>11.05</v>
+        <v>10.96</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.896856</v>
+        <v>0.016697617</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.036</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.115</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.025</v>
+        <v>-0.032</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.022</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.17</v>
+        <v>-0.177</v>
       </c>
       <c r="L18" s="8" t="n">
         <v>1.07</v>
       </c>
       <c r="M18" s="10" t="n">
-        <v>615730</v>
+        <v>512850</v>
       </c>
     </row>
     <row r="19">
@@ -3089,34 +3091,34 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>27.66</v>
+        <v>27.16</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>0.64839256</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.029</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.028</v>
+        <v>0.01</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.155</v>
+        <v>-0.17</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.412</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>124940</v>
+        <v>123770</v>
       </c>
     </row>
     <row r="20">
@@ -3136,28 +3138,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.76</v>
+        <v>12.25</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.4680150000000001</v>
+        <v>-0.013687607</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.233</v>
+        <v>-0.264</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.242</v>
+        <v>-0.246</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>36.3</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.139</v>
+        <v>-0.168</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.076</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.385</v>
+        <v>-0.409</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -3165,7 +3167,7 @@
         </is>
       </c>
       <c r="M20" s="10" t="n">
-        <v>118930</v>
+        <v>117850</v>
       </c>
     </row>
     <row r="21">
@@ -3185,34 +3187,34 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.96</v>
+        <v>6.74</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.0190337</v>
+        <v>-0.14815153</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.224</v>
+        <v>-0.249</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.193</v>
+        <v>-0.266</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>6.7</v>
+        <v>5.7</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.185</v>
+        <v>-0.207</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.189</v>
+        <v>-0.214</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.301</v>
+        <v>-0.323</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>1.206</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>185650</v>
+        <v>200300</v>
       </c>
     </row>
     <row r="22">
@@ -3232,34 +3234,34 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.387597</v>
+        <v>-0.017928318</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.014</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.358</v>
+        <v>-0.406</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>-53.1</v>
+        <v>-53</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.059</v>
+        <v>0.015</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.169</v>
+        <v>-0.204</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.481</v>
+        <v>-0.503</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.327</v>
       </c>
       <c r="M22" s="10" t="n">
-        <v>175460</v>
+        <v>164910</v>
       </c>
     </row>
     <row r="23">
@@ -3336,7 +3338,7 @@
         <v>-0.239</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>-287.6</v>
+        <v>-291</v>
       </c>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
@@ -3568,31 +3570,31 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.15</v>
+        <v>53.69</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>36.613</v>
+        <v>36.302</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>23.042555</v>
+        <v>22.84681</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.411025</v>
+        <v>14.288604</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>10.792</v>
+        <v>10.759</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>3.758</v>
+        <v>3.747</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.983871</v>
+        <v>22.788624</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.812682</v>
+        <v>2.7887886</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3621,10 +3623,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>109.25</v>
+        <v>104.75</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>19.168</v>
+        <v>18.378</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3632,22 +3634,22 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>10.1155815</v>
+        <v>9.698921</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>14.462</v>
+        <v>14.236</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.882</v>
+        <v>1.853</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.118069</v>
+        <v>2.0308259</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.169992</v>
+        <v>1.1218</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3676,10 +3678,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>25.22</v>
+        <v>24.74</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>12.554</v>
+        <v>12.315</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3687,22 +3689,22 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>12.95792</v>
+        <v>12.711298</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>48.356</v>
+        <v>48.464</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>2.179</v>
+        <v>2.184</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>19.764889</v>
+        <v>19.388714</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>2.073461</v>
+        <v>2.033998</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3731,31 +3733,31 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>103.33</v>
+        <v>101.69</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.776</v>
+        <v>10.605</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.907642</v>
+        <v>32.38535</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>17.390442</v>
+        <v>17.11443</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>11.483</v>
+        <v>11.382</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>2.815</v>
+        <v>2.79</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-38.441223</v>
+        <v>-37.831104</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.5096254</v>
+        <v>1.4856654</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3784,31 +3786,31 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.86</v>
+        <v>36.13</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.081</v>
+        <v>9.882</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>48.5</v>
+        <v>47.539474</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>15.707298</v>
+        <v>15.39622</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>16.8</v>
+        <v>16.747</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>11.6</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>2.256</v>
+        <v>2.248</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.9183588</v>
+        <v>3.8407571</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.57484484</v>
+        <v>0.56346023</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3849,13 +3851,13 @@
         <v>10.043682</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>7.106</v>
+        <v>7.1</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>5.9</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>2.086</v>
+        <v>2.084</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>2.3957021</v>
@@ -3890,31 +3892,31 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.99</v>
+        <v>58.74</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.066</v>
+        <v>6.04</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>18.907053</v>
+        <v>18.826923</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>17.952301</v>
+        <v>17.876219</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>8.478</v>
+        <v>8.417999999999999</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>3.43</v>
+        <v>3.406</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.514559</v>
+        <v>16.444569</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>3.0155654</v>
+        <v>3.0027857</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>3.12</v>
@@ -3943,31 +3945,31 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.94</v>
+        <v>86.25</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.992</v>
+        <v>6.011</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>16.245747</v>
+        <v>16.304348</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>11.574349</v>
+        <v>11.616099</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>11.532</v>
+        <v>11.522</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>3.771</v>
+        <v>3.767</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>5.924037</v>
+        <v>5.9454055</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.0480838</v>
+        <v>2.0545175</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>5.29</v>
@@ -3996,10 +3998,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.33</v>
+        <v>27.11</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.578</v>
+        <v>5.533</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -4007,22 +4009,22 @@
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>29.545946</v>
+        <v>29.30811</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>8.721</v>
+        <v>8.727</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>7.3</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>2.654</v>
+        <v>2.655</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>1.5804083</v>
+        <v>1.5676864</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.48565817</v>
+        <v>0.48174876</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>-2.42</v>
@@ -4037,12 +4039,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4051,51 +4053,51 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.67</v>
+        <v>18.67</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.395</v>
+        <v>5.525</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>25.404762</v>
+        <v>51.86111</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>12.300988</v>
+        <v>22.80457</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10.165</v>
+        <v>10.269</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>2.129</v>
+        <v>4.04</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.24372</v>
+        <v>4.966468</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2.3027554</v>
+        <v>4.2833853</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.86741</v>
+        <v>0.8186956</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1.473</v>
+        <v>3.7592108</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -4104,40 +4106,40 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>18.11</v>
+        <v>10.32</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.36</v>
+        <v>5.218</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>51.74286</v>
+        <v>24.571428</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>22.197506</v>
+        <v>11.897488</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10.121</v>
+        <v>10.051</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>3.982</v>
+        <v>2.105</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>4.83426</v>
+        <v>7.0061097</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>4.1549067</v>
+        <v>2.2272198</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.81585747</v>
+        <v>0.86741</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>3.7461786</v>
+        <v>1.473</v>
       </c>
     </row>
     <row r="13">
@@ -4157,16 +4159,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>20.53</v>
+        <v>20.19</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4.779</v>
+        <v>4.7</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>66.22581</v>
+        <v>65.129036</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>27.434422</v>
+        <v>26.980076</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -4184,10 +4186,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>13.937542</v>
+        <v>13.706721</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.212755</v>
+        <v>4.142987</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -4216,31 +4218,31 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5.68</v>
+        <v>5.5</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.219</v>
+        <v>2.147</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>12.347825</v>
+        <v>11.945652</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>7.1393557</v>
+        <v>6.9068236</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>10.786</v>
+        <v>10.669</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>2.519</v>
+        <v>2.492</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>-1.7800062</v>
+        <v>-1.7220306</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.42978176</v>
+        <v>0.41578358</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0.46</v>
@@ -4269,10 +4271,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>13.97</v>
+        <v>13.84</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1.866</v>
+        <v>1.848</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4280,22 +4282,22 @@
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>8.026291000000001</v>
+        <v>7.948728</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>17.102</v>
+        <v>17.079</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>10.8</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.774</v>
+        <v>1.772</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.9616576</v>
+        <v>0.95236456</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.26801342</v>
+        <v>0.26542345</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>-5.83</v>
@@ -4324,31 +4326,31 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>97.18000000000001</v>
+        <v>96.67</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.738</v>
+        <v>1.729</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>17.89687</v>
+        <v>17.80387</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>16.34651</v>
+        <v>16.261564</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>8.678000000000001</v>
+        <v>8.605</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>3.036</v>
+        <v>3.01</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>3.2206535</v>
+        <v>3.2039175</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>3.1885774</v>
+        <v>3.1720078</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>5.43</v>
@@ -4377,10 +4379,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.99</v>
+        <v>4.7</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.229</v>
+        <v>1.155</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -4388,10 +4390,10 @@
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>5.040404</v>
+        <v>4.737374</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-13.816</v>
+        <v>-7.671</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -4399,13 +4401,13 @@
         </is>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.462</v>
+        <v>1.381</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>1.6967018</v>
+        <v>1.5946957</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>1.8358303</v>
+        <v>1.7272995</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0.44</v>
@@ -4434,31 +4436,31 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>11.05</v>
+        <v>10.96</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.919</v>
+        <v>0.912</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>18.416666</v>
+        <v>18.266666</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>11.932659</v>
+        <v>11.83547</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>6.478</v>
+        <v>6.362</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.92</v>
+        <v>0.904</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>3.3719866</v>
+        <v>3.3445225</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.6908155</v>
+        <v>0.6851889</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>0.6</v>
@@ -4487,10 +4489,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>27.66</v>
+        <v>27.16</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.73</v>
+        <v>0.717</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
@@ -4498,22 +4500,22 @@
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>22.859503</v>
+        <v>22.450413</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>9.728</v>
+        <v>9.584</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.87</v>
+        <v>1.842</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>1.7207913</v>
+        <v>1.6899964</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>1.1500685</v>
+        <v>1.1294872</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>-0.23</v>
@@ -4542,10 +4544,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.76</v>
+        <v>12.25</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.627</v>
+        <v>0.602</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -4553,25 +4555,25 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>-8.563758999999999</v>
+        <v>-8.221477</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>18.953</v>
+        <v>18.901</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>2.461</v>
+        <v>2.455</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.2020726</v>
+        <v>1.1540273</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.25184965</v>
+        <v>0.24178354</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-13.33</v>
+        <v>-12.97</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-1.49</v>
@@ -4597,34 +4599,36 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.96</v>
+        <v>6.74</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>3.5510204</v>
+        <v>0.182</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>9.290405</v>
+        <v>8.996743</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>6.986</v>
+        <v>6.909</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.707</v>
+        <v>1.688</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>-11.542289</v>
+        <v>-11.177446</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.61628085</v>
+        <v>0.5997419</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>1.96</v>
+        <v>-0.58</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>0.74916</v>
@@ -4650,10 +4654,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.093</v>
+        <v>0.089</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -4661,22 +4665,22 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>-6.2682924</v>
+        <v>-6.012195</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>12.937</v>
+        <v>12.89</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.965</v>
+        <v>1.958</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>6.53944</v>
+        <v>6.2722645</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.30700928</v>
+        <v>0.2944661</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>-1.11</v>
@@ -5639,12 +5643,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -5653,59 +5657,57 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2.343</v>
+        <v>1.29</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.178</v>
+        <v>0.201</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.51058</v>
+        <v>0.26816</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.23518999</v>
+        <v>0.15614</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.09804</v>
+        <v>0.07777000000000001</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.20945999</v>
+        <v>0.39339</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.32813</v>
+        <v>0.10515001</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.23642</v>
+        <v>0.04121</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.507</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>0.341</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.478</v>
+        <v>0.365</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>9.69</v>
+        <v>6.424</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>1.75</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -5714,46 +5716,48 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1.29</v>
+        <v>2.343</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.201</v>
+        <v>0.178</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.26816</v>
+        <v>0.51058</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.15614</v>
+        <v>0.23518999</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.07777000000000001</v>
+        <v>0.09804</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.39339</v>
+        <v>0.20945999</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.10515001</v>
+        <v>0.32813</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.04121</v>
+        <v>0.23642</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>0.341</v>
+        <v>0.491</v>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.063</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.365</v>
+        <v>0.478</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>6.424</v>
+        <v>9.69</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>1.167</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="13">
@@ -6025,16 +6029,16 @@
         <v>0.37</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.22979</v>
+        <v>0.22986999</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.083620004</v>
+        <v>-0.18139</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>-0.16667</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.10584</v>
+        <v>-0.18008</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>-0.17208</v>
@@ -6043,10 +6047,10 @@
         <v>-0.09192</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.121</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.122</v>
+        <v>0.107</v>
       </c>
       <c r="N17" s="6" t="n">
         <v>0.03</v>
@@ -6841,7 +6845,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>54.15</v>
+        <v>53.69</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6863,8 +6867,8 @@
       <c r="I2" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>0.29</v>
+      <c r="J2" s="9" t="n">
+        <v>0.301</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>1.8</v>
@@ -6879,7 +6883,7 @@
         <v>0.41693002</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="P2" s="5" t="n">
         <v>0.4255</v>
@@ -6897,7 +6901,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>109.25</v>
+        <v>104.75</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6919,8 +6923,8 @@
       <c r="I3" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>0.9470000000000001</v>
+      <c r="J3" s="9" t="n">
+        <v>1.031</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>1.72</v>
@@ -6929,10 +6933,10 @@
         <v>0.0517</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>0.18808001</v>
+        <v>0.18817</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>0.90976</v>
+        <v>0.90992</v>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
@@ -6955,7 +6959,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>25.22</v>
+        <v>24.74</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6963,7 +6967,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>1.54286</v>
+        <v>1.6</v>
       </c>
       <c r="F4" s="10" t="n">
         <v>34</v>
@@ -6977,8 +6981,8 @@
       <c r="I4" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>0.4320000000000001</v>
+      <c r="J4" s="9" t="n">
+        <v>0.46</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -6990,7 +6994,7 @@
         <v>0.02999</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0.88236</v>
+        <v>0.88253</v>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
@@ -7013,7 +7017,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>103.33</v>
+        <v>101.69</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -7035,8 +7039,8 @@
       <c r="I5" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>0.373</v>
+      <c r="J5" s="9" t="n">
+        <v>0.395</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.24</v>
@@ -7048,10 +7052,10 @@
         <v>0.27027</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0.68582</v>
+        <v>0.68544996</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="P5" s="5" t="n">
         <v>0.3185</v>
@@ -7069,7 +7073,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>36.86</v>
+        <v>36.13</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -7091,8 +7095,8 @@
       <c r="I6" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>0.158</v>
+      <c r="J6" s="9" t="n">
+        <v>0.181</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.2</v>
@@ -7104,7 +7108,7 @@
         <v>0.27018</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>0.73407</v>
+        <v>0.73356</v>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
@@ -7149,7 +7153,7 @@
       <c r="I7" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="9" t="n">
         <v>0.154</v>
       </c>
       <c r="K7" s="7" t="n">
@@ -7162,10 +7166,10 @@
         <v>0.32334998</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>0.73223</v>
+        <v>0.73223996</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="P7" s="5" t="n">
         <v>0.0319</v>
@@ -7183,7 +7187,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>58.99</v>
+        <v>58.74</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -7205,8 +7209,8 @@
       <c r="I8" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>0.243</v>
+      <c r="J8" s="9" t="n">
+        <v>0.248</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>3.89</v>
@@ -7218,10 +7222,10 @@
         <v>0.07935</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0.889</v>
+        <v>0.88903</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="P8" s="5" t="n">
         <v>0.32369998</v>
@@ -7239,7 +7243,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>85.94</v>
+        <v>86.25</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -7261,8 +7265,8 @@
       <c r="I9" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>0.5770000000000001</v>
+      <c r="J9" s="9" t="n">
+        <v>0.5710000000000001</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>2.68</v>
@@ -7274,7 +7278,7 @@
         <v>0.06136</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0.81711</v>
+        <v>0.81709</v>
       </c>
       <c r="O9" s="5" t="n">
         <v>0.51</v>
@@ -7295,7 +7299,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>27.33</v>
+        <v>27.11</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -7317,8 +7321,8 @@
       <c r="I10" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>0.169</v>
+      <c r="J10" s="9" t="n">
+        <v>0.179</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>3.8</v>
@@ -7330,7 +7334,7 @@
         <v>0.02256</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>1.11971</v>
+        <v>1.11968</v>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
@@ -7344,117 +7348,117 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10.67</v>
+        <v>18.67</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>strong_buy</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>1.33333</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>17.375</v>
+        <v>28.726435</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>20</v>
+        <v>37.05022</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0.628</v>
+        <v>21.85326</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.539</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>4.92</v>
+        <v>4.19</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.1039</v>
+        <v>0.1088</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.68889</v>
+        <v>0.01337</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.19123</v>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>1.59</v>
+        <v>0.91643</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="P11" s="5" t="n">
-        <v>0.2831</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>18.11</v>
+        <v>10.32</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>strong_buy</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>1.33333</v>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>28.769512</v>
+        <v>17.375</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>37.105778</v>
+        <v>20</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>21.88603</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0.589</v>
+        <v>16</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.6840000000000001</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>4.19</v>
+        <v>4.92</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.1088</v>
+        <v>0.1039</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.01337</v>
+        <v>0.68889</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0.9164</v>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.19124001</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>1.61</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0</v>
+        <v>0.2831</v>
       </c>
     </row>
     <row r="13">
@@ -7469,7 +7473,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>20.53</v>
+        <v>20.19</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -7491,8 +7495,8 @@
       <c r="I13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>0.208</v>
+      <c r="J13" s="9" t="n">
+        <v>0.228</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.71</v>
@@ -7504,7 +7508,7 @@
         <v>0.07383000000000001</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0.93141997</v>
+        <v>0.93144995</v>
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
@@ -7527,7 +7531,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>5.68</v>
+        <v>5.5</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -7538,10 +7542,10 @@
         <v>1.78571</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>9.625</v>
+        <v>9.442310000000001</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>12.3</v>
@@ -7549,8 +7553,8 @@
       <c r="I14" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>0.695</v>
+      <c r="J14" s="9" t="n">
+        <v>0.7170000000000001</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>2.08</v>
@@ -7562,7 +7566,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.32466</v>
+        <v>0.32467</v>
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
@@ -7585,7 +7589,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>13.97</v>
+        <v>13.84</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7607,8 +7611,8 @@
       <c r="I15" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J15" s="4" t="n">
-        <v>0.368</v>
+      <c r="J15" s="9" t="n">
+        <v>0.381</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>4.18</v>
@@ -7620,7 +7624,7 @@
         <v>0.01867</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0.98657995</v>
+        <v>0.9865699999999999</v>
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
@@ -7643,7 +7647,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>97.18000000000001</v>
+        <v>96.67</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7667,8 +7671,8 @@
       <c r="I16" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="J16" s="4" t="n">
-        <v>0.108</v>
+      <c r="J16" s="9" t="n">
+        <v>0.114</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>2.53</v>
@@ -7680,10 +7684,10 @@
         <v>0.3204</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0.64761</v>
+        <v>0.64762</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P16" s="5" t="n">
         <v>0.221</v>
@@ -7701,7 +7705,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4.99</v>
+        <v>4.7</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7723,8 +7727,8 @@
       <c r="I17" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="J17" s="4" t="n">
-        <v>1.358</v>
+      <c r="J17" s="9" t="n">
+        <v>1.503</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>1.77</v>
@@ -7733,10 +7737,10 @@
         <v>0.0636</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0.08167000000000001</v>
+        <v>0.09754</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.95787</v>
+        <v>0.95424</v>
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
@@ -7759,7 +7763,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>11.05</v>
+        <v>10.96</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -7781,8 +7785,8 @@
       <c r="I18" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="J18" s="4" t="n">
-        <v>0.403</v>
+      <c r="J18" s="9" t="n">
+        <v>0.414</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>3.68</v>
@@ -7791,10 +7795,10 @@
         <v>0.028099999</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.17445</v>
+        <v>0.17495</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.76091003</v>
+        <v>0.76093</v>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
@@ -7817,7 +7821,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.66</v>
+        <v>27.16</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7839,8 +7843,8 @@
       <c r="I19" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>0.103</v>
+      <c r="J19" s="9" t="n">
+        <v>0.123</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>2.5</v>
@@ -7852,10 +7856,10 @@
         <v>0.27324</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.68558997</v>
+        <v>0.68561995</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>3.62</v>
+        <v>3.71</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>4.5455</v>
@@ -7873,7 +7877,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>12.76</v>
+        <v>12.25</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7884,10 +7888,10 @@
         <v>3.2</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>16.25</v>
+        <v>15.66667</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>18</v>
@@ -7895,8 +7899,8 @@
       <c r="I20" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>0.274</v>
+      <c r="J20" s="9" t="n">
+        <v>0.279</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>9.16</v>
@@ -7931,7 +7935,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>6.96</v>
+        <v>6.74</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -7953,8 +7957,8 @@
       <c r="I21" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="J21" s="4" t="n">
-        <v>0.9159999999999999</v>
+      <c r="J21" s="9" t="n">
+        <v>0.978</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>13.9</v>
@@ -7966,7 +7970,7 @@
         <v>0.07083</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.80919</v>
+        <v>0.80924004</v>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
@@ -7989,7 +7993,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -8011,8 +8015,8 @@
       <c r="I22" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J22" s="4" t="n">
-        <v>0.265</v>
+      <c r="J22" s="9" t="n">
+        <v>0.321</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>5.72</v>
@@ -8021,10 +8025,10 @@
         <v>0.024300002</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>0.0678</v>
+        <v>0.06769</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0.40694</v>
+        <v>0.40625</v>
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
@@ -8465,10 +8469,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>36.613</v>
+        <v>36.302</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>23.042555</v>
+        <v>22.84681</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -8480,10 +8484,10 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.172</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>10.792</v>
+        <v>10.759</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>9.199999999999999</v>
@@ -8509,7 +8513,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.578</v>
+        <v>5.533</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -8526,10 +8530,10 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.16</v>
+        <v>0.151</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>8.721</v>
+        <v>8.727</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>7.3</v>
@@ -8555,10 +8559,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>10.776</v>
+        <v>10.605</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>32.907642</v>
+        <v>32.38535</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.015</v>
@@ -8572,13 +8576,13 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.155</v>
+        <v>-0.169</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>11.483</v>
+        <v>11.382</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="L5" s="7" t="n">
         <v>41.7</v>
@@ -8601,10 +8605,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2.219</v>
+        <v>2.147</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>12.347825</v>
+        <v>11.945652</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -8618,13 +8622,13 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-0.244</v>
+        <v>-0.268</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>10.786</v>
+        <v>10.669</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="L6" s="7" t="n">
         <v>40</v>
@@ -8647,10 +8651,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.081</v>
+        <v>9.882</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>48.5</v>
+        <v>47.539474</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.06</v>
@@ -8662,10 +8666,10 @@
         <v>0.1489</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>16.8</v>
+        <v>16.747</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>11.6</v>
@@ -8727,13 +8731,13 @@
         <v>-0.048</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.106</v>
+        <v>7.1</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>5.9</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>66.7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -8753,10 +8757,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5.992</v>
+        <v>6.011</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>16.245747</v>
+        <v>16.304348</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.067</v>
@@ -8768,10 +8772,10 @@
         <v>0.35709</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>-0.232</v>
+        <v>-0.23</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>11.532</v>
+        <v>11.522</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>9.699999999999999</v>
@@ -8783,12 +8787,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Monarch Casino &amp; Resort</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -8797,42 +8801,42 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>6.066</v>
+        <v>1.729</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>18.907053</v>
+        <v>17.80387</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.032</v>
+        <v>0.041</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.4046</v>
+        <v>0.34986</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1.113</v>
+        <v>0.19214001</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>-0.045</v>
+        <v>0.01</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>8.478</v>
+        <v>8.605</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>61.9</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Monarch Casino &amp; Resort</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -8841,31 +8845,31 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1.738</v>
+        <v>6.04</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>17.89687</v>
+        <v>18.826923</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.041</v>
+        <v>0.032</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.34986</v>
+        <v>0.4046</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.19214001</v>
+        <v>1.113</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.015</v>
+        <v>-0.049</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>8.678000000000001</v>
+        <v>8.417999999999999</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>60.3</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="14">
@@ -8885,7 +8889,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.866</v>
+        <v>1.848</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8902,10 +8906,10 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.059</v>
+        <v>-0.068</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>17.102</v>
+        <v>17.079</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>10.8</v>
@@ -8931,7 +8935,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.73</v>
+        <v>0.717</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -8948,16 +8952,16 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>9.728</v>
+        <v>9.584</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>37.2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -8977,7 +8981,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.093</v>
+        <v>0.089</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -8994,16 +8998,16 @@
         <v>-1.4696201</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.014</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>12.937</v>
+        <v>12.89</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>34.3</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="17">
@@ -9023,7 +9027,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.627</v>
+        <v>0.602</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -9040,13 +9044,13 @@
         <v>-1.1563</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.233</v>
+        <v>-0.264</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>18.953</v>
+        <v>18.901</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="L17" s="7" t="n">
         <v>22.9</v>
@@ -9087,10 +9091,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.395</v>
+        <v>5.218</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.404762</v>
+        <v>24.571428</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -9102,27 +9106,27 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.109</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>10.165</v>
+        <v>10.051</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>70</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RSI</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Rush Street Interactive</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -9131,46 +9135,42 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>4.779</v>
+        <v>5.525</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>66.22581</v>
+        <v>51.86111</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.888</v>
+        <v>0.201</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.11229999</v>
+        <v>0.39339</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.29505</v>
+        <v>0.10515001</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-0.199</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>10.269</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>8.9</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>56.7</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>RSI</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Rush Street Interactive</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -9179,31 +9179,35 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.36</v>
+        <v>4.7</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>51.74286</v>
+        <v>65.129036</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.201</v>
+        <v>0.888</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.39339</v>
+        <v>0.11229999</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.10515001</v>
+        <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.223</v>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>10.121</v>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>8.800000000000001</v>
+        <v>0.046</v>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>55</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="23">
@@ -9223,7 +9227,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>12.554</v>
+        <v>12.315</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -9240,13 +9244,13 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.293</v>
+        <v>-0.306</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>48.356</v>
+        <v>48.464</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="L23" s="7" t="n">
         <v>52</v>
@@ -9269,7 +9273,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>19.168</v>
+        <v>18.378</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -9286,13 +9290,13 @@
         <v>-0.038829997</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-0.499</v>
+        <v>-0.52</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>14.462</v>
+        <v>14.236</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L24" s="7" t="n">
         <v>48</v>
@@ -9315,7 +9319,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.229</v>
+        <v>1.155</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -9326,16 +9330,16 @@
         <v>0.37</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.10584</v>
+        <v>-0.18008</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.537</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>-13.816</v>
+        <v>-7.671</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
@@ -9423,12 +9427,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>INSE</t>
+          <t>ACEL</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Inspired Entertainment</t>
+          <t>Accel Entertainment</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -9437,33 +9441,31 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.187</v>
+        <v>0.912</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>3.5510204</v>
+        <v>18.266666</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.24433</v>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.14208001</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0.19236</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.224</v>
+        <v>-0.036</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>6.986</v>
+        <v>6.362</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>60</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="30">
@@ -9525,12 +9527,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ACEL</t>
+          <t>INSE</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Accel Entertainment</t>
+          <t>Inspired Entertainment</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -9539,42 +9541,46 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>18.416666</v>
+        <v>0.182</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.075</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.14208001</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>0.19236</v>
+        <v>0.24433</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="I31" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.249</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>6.478</v>
+        <v>6.909</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>48.3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>AGS</t>
+          <t>LNW</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>PlayAGS</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -9606,7 +9612,7 @@
         </is>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0</v>
+        <v>-0.239</v>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
@@ -9625,12 +9631,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LNW</t>
+          <t>AGS</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Light &amp; Wonder</t>
+          <t>PlayAGS</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -9662,7 +9668,7 @@
         </is>
       </c>
       <c r="I33" s="5" t="n">
-        <v>-0.239</v>
+        <v>0</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
@@ -9675,7 +9681,7 @@
         </is>
       </c>
       <c r="L33" s="7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -10417,10 +10423,10 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.18808001</v>
+        <v>0.18817</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.90976</v>
+        <v>0.90992</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>1.72</v>
@@ -10447,7 +10453,7 @@
         <v>0.02999</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.88236</v>
+        <v>0.88253</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>1.74</v>
@@ -10474,7 +10480,7 @@
         <v>0.27027</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.68582</v>
+        <v>0.68544996</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>3.24</v>
@@ -10501,7 +10507,7 @@
         <v>0.27018</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.73407</v>
+        <v>0.73356</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>4.2</v>
@@ -10528,7 +10534,7 @@
         <v>0.32334998</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.73223</v>
+        <v>0.73223996</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>3.32</v>
@@ -10555,7 +10561,7 @@
         <v>0.07935</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.889</v>
+        <v>0.88903</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>3.89</v>
@@ -10582,7 +10588,7 @@
         <v>0.06136</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.81711</v>
+        <v>0.81709</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2.68</v>
@@ -10609,7 +10615,7 @@
         <v>0.02256</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1.11971</v>
+        <v>1.11968</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>3.8</v>
@@ -10624,55 +10630,55 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.68889</v>
+        <v>0.01337</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.19123</v>
+        <v>0.91643</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>4.92</v>
+        <v>4.19</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.1039</v>
+        <v>0.1088</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>16337061</v>
+        <v>11183802</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.01337</v>
+        <v>0.68889</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.9164</v>
+        <v>0.19124001</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>4.19</v>
+        <v>4.92</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1088</v>
+        <v>0.1039</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>11183802</v>
+        <v>16337061</v>
       </c>
     </row>
     <row r="13">
@@ -10690,7 +10696,7 @@
         <v>0.07383000000000001</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.93141997</v>
+        <v>0.93144995</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>1.71</v>
@@ -10717,7 +10723,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.32466</v>
+        <v>0.32467</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2.08</v>
@@ -10744,7 +10750,7 @@
         <v>0.01867</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.98657995</v>
+        <v>0.9865699999999999</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>4.18</v>
@@ -10771,7 +10777,7 @@
         <v>0.3204</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.64761</v>
+        <v>0.64762</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2.53</v>
@@ -10795,10 +10801,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.08167000000000001</v>
+        <v>0.09754</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.95787</v>
+        <v>0.95424</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>1.77</v>
@@ -10822,10 +10828,10 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.17445</v>
+        <v>0.17495</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.76091003</v>
+        <v>0.76093</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>3.68</v>
@@ -10852,7 +10858,7 @@
         <v>0.27324</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.68558997</v>
+        <v>0.68561995</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2.5</v>
@@ -10906,7 +10912,7 @@
         <v>0.07083</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.80919</v>
+        <v>0.80924004</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>13.9</v>
@@ -10930,10 +10936,10 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.0678</v>
+        <v>0.06769</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.40694</v>
+        <v>0.40625</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>5.72</v>
@@ -11139,955 +11145,955 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1284.25</v>
+        <v>1268.42</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>1203.2</v>
+        <v>1221.72</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>1050.47</v>
+        <v>1052.19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1286.26</v>
+        <v>1252.54</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1214.11</v>
+        <v>1227.3</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>1051.72</v>
+        <v>1050.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1291.62</v>
+        <v>1252.44</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1221.67</v>
+        <v>1231.62</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>1060.61</v>
+        <v>1052.96</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1275.63</v>
+        <v>1258.42</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1227.26</v>
+        <v>1231.49</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1059.06</v>
+        <v>1053.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1276.23</v>
+        <v>1248.27</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1231.57</v>
+        <v>1227.1</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1061.38</v>
+        <v>1046.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1281.42</v>
+        <v>1243.43</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1231.45</v>
+        <v>1225.61</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1062.16</v>
+        <v>1044.51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1270.4</v>
+        <v>1235.99</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1227.06</v>
+        <v>1216.53</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1054.67</v>
+        <v>1047.07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1265.08</v>
+        <v>1241.47</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1225.56</v>
+        <v>1218.76</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1052.86</v>
+        <v>1048.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1258.23</v>
+        <v>1242.31</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1216.48</v>
+        <v>1226.87</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1055.44</v>
+        <v>1046.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1262.5</v>
+        <v>1227.01</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>1218.71</v>
+        <v>1234.17</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1056.48</v>
+        <v>1039.64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1263.36</v>
+        <v>1181.05</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1226.83</v>
+        <v>1230.19</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1054.41</v>
+        <v>1020.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1246.07</v>
+        <v>1205.83</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1234.12</v>
+        <v>1230.07</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>1047.95</v>
+        <v>1037.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1196.46</v>
+        <v>1177.94</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1230.15</v>
+        <v>1238.2</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>1028.84</v>
+        <v>1030.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1220.22</v>
+        <v>1173.38</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1230.02</v>
+        <v>1240.14</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1045.89</v>
+        <v>1026.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1190.53</v>
+        <v>1165.7</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1238.16</v>
+        <v>1237.67</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1038.4</v>
+        <v>1014.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1185.99</v>
+        <v>1163.52</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1240.1</v>
+        <v>1231.58</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>1034.27</v>
+        <v>1016.58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1176.4</v>
+        <v>1182.53</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1237.62</v>
+        <v>1234.94</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1022.13</v>
+        <v>1027.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1174.78</v>
+        <v>1146.14</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>1231.54</v>
+        <v>1233.9</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>1024.71</v>
+        <v>1007.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1192.83</v>
+        <v>1122.89</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1234.89</v>
+        <v>1208.78</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1036.07</v>
+        <v>991.48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1152.83</v>
+        <v>1129</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1233.86</v>
+        <v>1222.73</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>1015.93</v>
+        <v>993.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1130.58</v>
+        <v>1133.89</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1208.74</v>
+        <v>1229.12</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>999.4</v>
+        <v>1001.21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1136.66</v>
+        <v>1118.33</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>1222.69</v>
+        <v>1229.57</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>1001.21</v>
+        <v>994.29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1142.92</v>
+        <v>1123.98</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>1229.08</v>
+        <v>1235.81</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1009.22</v>
+        <v>999.9299999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1126.26</v>
+        <v>1110.85</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>1229.52</v>
+        <v>1240.73</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>1002.24</v>
+        <v>996.34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1132.44</v>
+        <v>1112.66</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>1235.77</v>
+        <v>1240.61</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>1007.93</v>
+        <v>988.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1119.85</v>
+        <v>1062.87</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>1240.69</v>
+        <v>1238.15</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>1004.31</v>
+        <v>972.52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1119.85</v>
+        <v>1049.95</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>1240.56</v>
+        <v>1234.45</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>996.5599999999999</v>
+        <v>951.51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1063.19</v>
+        <v>1067.16</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1238.1</v>
+        <v>1240.59</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>980.29</v>
+        <v>960.73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1047.24</v>
+        <v>1063.4</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>1234.41</v>
+        <v>1230.1</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>959.12</v>
+        <v>949.97</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1065.92</v>
+        <v>1084.18</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>1240.55</v>
+        <v>1224.14</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>968.41</v>
+        <v>970.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1062.22</v>
+        <v>1059.36</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>1230.06</v>
+        <v>1208.85</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>957.5700000000001</v>
+        <v>952.02</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1083.61</v>
+        <v>1085.97</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>1224.1</v>
+        <v>1232.05</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>978.74</v>
+        <v>969.96</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1057.65</v>
+        <v>1088.12</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>1208.81</v>
+        <v>1237.99</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>959.63</v>
+        <v>977.13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1084.62</v>
+        <v>1085.13</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>1232</v>
+        <v>1234.72</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>977.71</v>
+        <v>978.92</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1087.5</v>
+        <v>1070.19</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>1237.94</v>
+        <v>1234.44</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>984.9400000000001</v>
+        <v>971.49</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1081.36</v>
+        <v>1034.14</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>1234.68</v>
+        <v>1215.37</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>986.75</v>
+        <v>937.6799999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1067.11</v>
+        <v>1023.65</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>1234.39</v>
+        <v>1216.22</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>979.26</v>
+        <v>925.63</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1030.68</v>
+        <v>1038.48</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>1215.32</v>
+        <v>1218.18</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>945.17</v>
+        <v>927.4299999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1018.83</v>
+        <v>1071.5</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>1216.18</v>
+        <v>1224.32</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>933.04</v>
+        <v>952.53</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1032.96</v>
+        <v>1066.3</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>1218.14</v>
+        <v>1221.09</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>934.84</v>
+        <v>947.92</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1066.36</v>
+        <v>1066.44</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>1224.28</v>
+        <v>1229.92</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>960.15</v>
+        <v>945.62</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1059.78</v>
+        <v>1024.05</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>1221.05</v>
+        <v>1217.36</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>955.5</v>
+        <v>924.35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1060.31</v>
+        <v>1038.1</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>1229.88</v>
+        <v>1226.21</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>953.1799999999999</v>
+        <v>932.29</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1018.71</v>
+        <v>1042.01</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>1217.32</v>
+        <v>1236.56</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>931.74</v>
+        <v>933.58</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1032.23</v>
+        <v>1070.74</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>1226.17</v>
+        <v>1229.69</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>939.75</v>
+        <v>935.88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1037.32</v>
+        <v>1057.96</v>
       </c>
       <c r="C47" s="13" t="n">
-        <v>1236.52</v>
+        <v>1223.79</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>941.04</v>
+        <v>939.98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1066.75</v>
+        <v>1052.99</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>1229.65</v>
+        <v>1224.48</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>943.36</v>
+        <v>931.53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1057.54</v>
+        <v>1049.34</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>1223.74</v>
+        <v>1213.69</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>947.5</v>
+        <v>925.12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1052.84</v>
+        <v>1064.77</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>1224.44</v>
+        <v>1222.25</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>938.97</v>
+        <v>930.76</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1049.46</v>
+        <v>1062.65</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>1213.65</v>
+        <v>1215.44</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>932.52</v>
+        <v>924.87</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1067.33</v>
+        <v>1031.55</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>1222.21</v>
+        <v>1199.51</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>938.2</v>
+        <v>915.39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1065.41</v>
+        <v>1033.09</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>1215.39</v>
+        <v>1210.01</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>932.26</v>
+        <v>917.4400000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1034.34</v>
+        <v>1032.38</v>
       </c>
       <c r="C54" s="13" t="n">
-        <v>1199.46</v>
+        <v>1208.07</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>922.71</v>
+        <v>915.64</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1035.28</v>
+        <v>1046.6</v>
       </c>
       <c r="C55" s="13" t="n">
-        <v>1209.97</v>
+        <v>1206.55</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>924.77</v>
+        <v>920</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1034.42</v>
+        <v>1033.08</v>
       </c>
       <c r="C56" s="13" t="n">
-        <v>1208.03</v>
+        <v>1188.23</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>922.96</v>
+        <v>908.98</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1047.79</v>
+        <v>1035.22</v>
       </c>
       <c r="C57" s="13" t="n">
-        <v>1206.51</v>
+        <v>1181.51</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>927.35</v>
+        <v>906.9299999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1035.29</v>
+        <v>1027.35</v>
       </c>
       <c r="C58" s="13" t="n">
-        <v>1188.19</v>
+        <v>1193.53</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>916.25</v>
+        <v>904.11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1037.18</v>
+        <v>1039.64</v>
       </c>
       <c r="C59" s="13" t="n">
-        <v>1181.46</v>
+        <v>1196.67</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>914.1799999999999</v>
+        <v>903.34</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1028.97</v>
+        <v>1031.87</v>
       </c>
       <c r="C60" s="13" t="n">
-        <v>1193.49</v>
+        <v>1179.97</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>911.34</v>
+        <v>893.35</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1039.99</v>
+        <v>1025.34</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -12099,7 +12105,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1039.99</v>
+        <v>1025.34</v>
       </c>
     </row>
     <row r="64">
@@ -12110,7 +12116,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-17.62%</t>
+          <t>-17.41%</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12137,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>138.1</v>
+        <v>136.1</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>53.69</v>
+        <v>53.48</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.44502443</v>
+        <v>-0.010545785</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,22 +670,22 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.238</v>
+        <v>-0.241</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>36.302</v>
+        <v>36.16</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>48.771</v>
+        <v>48.852</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.84681</v>
+        <v>22.757448</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.288604</v>
+        <v>14.232716</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>10.759</v>
+        <v>10.777</v>
       </c>
       <c r="N2" s="7" t="n">
         <v>9.199999999999999</v>
@@ -694,10 +694,10 @@
         <v>0.888</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0.248</v>
+        <v>0.273</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>-0.172</v>
+        <v>-0.176</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>104.75</v>
+        <v>104.79</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.016431925</v>
+        <v>-0.015224159</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -732,10 +732,10 @@
         <v>-0.6659999999999999</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.378</v>
+        <v>18.385</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>30.351</v>
+        <v>30.335</v>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.698921</v>
+        <v>9.702624999999999</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>14.236</v>
+        <v>14.228</v>
       </c>
       <c r="N3" s="7" t="n">
         <v>9.699999999999999</v>
@@ -755,7 +755,7 @@
         <v>1.177</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>-0.5670000000000001</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="Q3" s="4" t="n">
         <v>-0.52</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24.74</v>
+        <v>24.09</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.021360795</v>
+        <v>-0.032918494</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -790,13 +790,13 @@
         <v>21.01</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.493</v>
+        <v>-0.506</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>12.315</v>
+        <v>11.991</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>13.225</v>
+        <v>13.043</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
@@ -804,22 +804,22 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>12.711298</v>
+        <v>12.377331</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>48.464</v>
+        <v>47.796</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>1.682</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.358</v>
+        <v>-0.373</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>-0.306</v>
+        <v>-0.324</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>101.69</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0.06888378000000001</v>
+        <v>100.74</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>-0.02345876</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,34 +851,34 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.245</v>
+        <v>-0.252</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.605</v>
+        <v>10.505</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>19.915</v>
+        <v>20.073</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.38535</v>
+        <v>32.0828</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>17.11443</v>
+        <v>16.954544</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>11.382</v>
+        <v>11.473</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>1.034</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>0.207</v>
+        <v>0.224</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>-0.169</v>
+        <v>-0.176</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.13</v>
+        <v>36.22</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.6598787</v>
+        <v>-0.024771087</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,22 +910,22 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.1</v>
+        <v>-0.098</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>9.882</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>39.432</v>
+        <v>39.629</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>47.539474</v>
+        <v>47.657898</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>15.39622</v>
+        <v>15.434572</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>16.747</v>
+        <v>16.831</v>
       </c>
       <c r="N6" s="7" t="n">
         <v>11.6</v>
@@ -934,10 +934,10 @@
         <v>1.396</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.105</v>
+        <v>0.113</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.006999999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>81.83</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0.12235222</v>
+        <v>82.3</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>-0.9149946</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -969,34 +969,34 @@
         <v>58.94</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.09</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.178</v>
+        <v>6.213</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>8.526999999999999</v>
+        <v>8.627000000000001</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.6272166</v>
+        <v>3.6480498</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.043682</v>
+        <v>10.10137</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>7.1</v>
+        <v>7.184</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>1.22</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0.193</v>
+        <v>0.226</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.048</v>
+        <v>-0.043</v>
       </c>
     </row>
     <row r="8">
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.74</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>0.010146176</v>
+        <v>58.16</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-0.028390126</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1028,213 +1028,213 @@
         <v>35.09</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.149</v>
+        <v>-0.157</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.04</v>
+        <v>5.98</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>6.851</v>
+        <v>6.951</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>18.826923</v>
+        <v>18.641026</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>17.876219</v>
+        <v>17.699707</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>8.417999999999999</v>
+        <v>8.541</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>1.453</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.049</v>
+        <v>-0.058</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>86.25</v>
+        <v>19.97</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.5127636</v>
+        <v>0.014220355</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>118.46</v>
+        <v>32.22</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>80.23999999999999</v>
+        <v>15.725</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.272</v>
+        <v>-0.38</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>6.011</v>
+        <v>5.91</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>11.023</v>
+        <v>5.611</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.304348</v>
+        <v>55.472218</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>11.616099</v>
+        <v>24.552261</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>11.522</v>
+        <v>11.056</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>0.66</v>
+        <v>2.002</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.234</v>
+        <v>-0.104</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.23</v>
+        <v>-0.144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.11</v>
+        <v>84.39</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.011666048</v>
+        <v>-0.039223495</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>31.58</v>
+        <v>118.46</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>17.86</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.142</v>
+        <v>-0.288</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.533</v>
+        <v>5.881</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>11.164</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>15.951797</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>29.30811</v>
+        <v>11.364923</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>8.727</v>
+        <v>11.669</v>
       </c>
       <c r="N10" s="7" t="n">
-        <v>7.3</v>
+        <v>9.9</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>1.977</v>
+        <v>0.66</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.06900000000000001</v>
-      </c>
-      <c r="Q10" s="9" t="n">
-        <v>0.151</v>
+        <v>-0.244</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>-0.246</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>18.67</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>0.016884502</v>
+        <v>27.05</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>-0.01439506</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>32.22</v>
+        <v>31.58</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>15.725</v>
+        <v>17.86</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.421</v>
+        <v>-0.143</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.525</v>
+        <v>5.52</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>5.211</v>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>51.86111</v>
+        <v>30.502</v>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L11" s="7" t="n">
-        <v>22.80457</v>
+        <v>29.237837</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>10.269</v>
+        <v>8.727</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>2.002</v>
+        <v>1.977</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.181</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>-0.199</v>
+        <v>-0.043</v>
+      </c>
+      <c r="Q11" s="9" t="n">
+        <v>0.148</v>
       </c>
     </row>
     <row r="12">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.32</v>
+        <v>10.42</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.02272734</v>
+        <v>-0.02251405</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>14.38</v>
@@ -1266,34 +1266,34 @@
         <v>5.59</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.282</v>
+        <v>-0.275</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.218</v>
+        <v>5.269</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>4.932</v>
+        <v>4.983</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>24.571428</v>
+        <v>24.809525</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>11.897488</v>
+        <v>12.0127735</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>10.051</v>
+        <v>10.154</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>1.1</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0.498</v>
+        <v>0.506</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.109</v>
+        <v>-0.101</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>20.19</v>
+        <v>21.02</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.013678495</v>
+        <v>-0.010593238</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.109</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>4.7</v>
+        <v>4.892</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>65.129036</v>
+        <v>67.79031999999999</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>26.980076</v>
+        <v>28.08253</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.9229999999999999</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>0.046</v>
+        <v>0.08800000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1380,8 +1380,8 @@
       <c r="D14" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>-0.011680154</v>
+      <c r="E14" s="9" t="n">
+        <v>0.090964094</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>10.15</v>
@@ -1393,31 +1393,31 @@
         <v>-0.458</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.147</v>
+        <v>2.239</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>12.868</v>
+        <v>12.798</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>11.945652</v>
+        <v>11.967391</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>6.9068236</v>
+        <v>6.9193935</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>10.669</v>
+        <v>10.611</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>0.603</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.049</v>
+        <v>-0.013</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.268</v>
+        <v>-0.267</v>
       </c>
     </row>
     <row r="15">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>13.84</v>
+        <v>14.03</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.036127996</v>
+        <v>-0.9180798999999999</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20.61</v>
@@ -1449,13 +1449,13 @@
         <v>11.65</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.328</v>
+        <v>-0.319</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.848</v>
+        <v>1.874</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>12.334</v>
+        <v>12.375</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="L15" s="7" t="n">
-        <v>7.948728</v>
+        <v>8.060763</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>17.079</v>
+        <v>17.135</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>1.364</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.205</v>
+        <v>-0.182</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.068</v>
+        <v>-0.055</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>96.67</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>0.2852713</v>
+        <v>96.36</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-0.012653695</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>113.88</v>
@@ -1510,34 +1510,34 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.151</v>
+        <v>-0.154</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.729</v>
+        <v>1.724</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1.641</v>
+        <v>1.663</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>17.80387</v>
+        <v>17.746777</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>16.261564</v>
+        <v>16.20942</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>8.605</v>
+        <v>8.717000000000001</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>1.376</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0.191</v>
+        <v>0.202</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>0.01</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1557,25 +1557,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.016736735</v>
+        <v>-0.017021261</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>13.73</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>4.68</v>
+        <v>4.6</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.6579999999999999</v>
+        <v>-0.664</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.155</v>
+        <v>1.138</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.925</v>
+        <v>0.908</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="L17" s="7" t="n">
-        <v>4.737374</v>
+        <v>4.6666665</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>-7.671</v>
+        <v>-7.528</v>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         <v>1.993</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.513</v>
+        <v>-0.54</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5710000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.016697617</v>
+        <v>11</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>-0.6323369</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.31</v>
@@ -1632,34 +1632,34 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.177</v>
+        <v>-0.174</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.912</v>
+        <v>0.915</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1.203</v>
+        <v>1.227</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>18.266666</v>
+        <v>18.333332</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>11.83547</v>
+        <v>11.878665</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>6.362</v>
+        <v>6.487</v>
       </c>
       <c r="N18" s="7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>1.07</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.036</v>
+        <v>-0.033</v>
       </c>
     </row>
     <row r="19">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>0.64839256</v>
+        <v>26.62</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>-0.021858902</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>32.74</v>
@@ -1691,13 +1691,13 @@
         <v>19.57</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.17</v>
+        <v>-0.187</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.717</v>
+        <v>0.703</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.17</v>
+        <v>1.176</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="L19" s="7" t="n">
-        <v>22.450413</v>
+        <v>22.004131</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>9.584</v>
+        <v>9.632999999999999</v>
       </c>
       <c r="N19" s="7" t="n">
         <v>7.3</v>
@@ -1716,11 +1716,11 @@
       <c r="O19" s="8" t="n">
         <v>1.412</v>
       </c>
-      <c r="P19" s="9" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="Q19" s="9" t="n">
-        <v>0.004</v>
+      <c r="P19" s="4" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>-0.016</v>
       </c>
     </row>
     <row r="20">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-0.013687607</v>
+        <v>12.24</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.28664905</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>20.74</v>
@@ -1752,13 +1752,13 @@
         <v>8.455</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.409</v>
+        <v>-0.41</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0.602</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>6.114</v>
+        <v>6.104</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>-8.221477</v>
+        <v>-8.218121</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>18.901</v>
+        <v>18.869</v>
       </c>
       <c r="N20" s="7" t="n">
         <v>12.9</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.246</v>
+        <v>-0.283</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>-0.264</v>
@@ -1803,25 +1803,25 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.74</v>
+        <v>6.42</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.14815153</v>
+        <v>-0.02061072</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>6.505</v>
+        <v>6.38</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.323</v>
+        <v>-0.355</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.182</v>
+        <v>0.174</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.513</v>
+        <v>0.508</v>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>8.996743</v>
+        <v>8.562923</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>6.909</v>
+        <v>6.836</v>
       </c>
       <c r="N21" s="7" t="n">
         <v>5.5</v>
@@ -1841,10 +1841,10 @@
         <v>1.206</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.266</v>
+        <v>-0.295</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.249</v>
+        <v>-0.285</v>
       </c>
     </row>
     <row r="22">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.017928318</v>
+        <v>-0.040650463</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>4.95</v>
@@ -1876,13 +1876,13 @@
         <v>2.02</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.503</v>
+        <v>-0.521</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.089</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.592</v>
+        <v>0.583</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
@@ -1890,22 +1890,22 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>-6.012195</v>
+        <v>-5.7804875</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>12.89</v>
+        <v>12.657</v>
       </c>
       <c r="N22" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>1.327</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.406</v>
+        <v>-0.43</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.014</v>
+        <v>-0.052</v>
       </c>
     </row>
     <row r="23">
@@ -2292,28 +2292,28 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>53.69</v>
+        <v>53.48</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.44502443</v>
+        <v>-0.010545785</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.172</v>
+        <v>-0.176</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.248</v>
+        <v>0.273</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>54.3</v>
+        <v>54</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.062</v>
+        <v>-0.066</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.034</v>
+        <v>-0.038</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.238</v>
+        <v>-0.241</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
@@ -2339,22 +2339,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>104.75</v>
+        <v>104.79</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.016431925</v>
+        <v>-0.015224159</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>-0.52</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.5670000000000001</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-52.9</v>
+        <v>-54.2</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.294</v>
+        <v>-0.293</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>-0.547</v>
@@ -2386,34 +2386,34 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24.74</v>
+        <v>24.09</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.021360795</v>
+        <v>-0.032918494</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.306</v>
+        <v>-0.324</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.358</v>
+        <v>-0.373</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-34.1</v>
+        <v>-34.8</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.103</v>
+        <v>-0.127</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.309</v>
+        <v>-0.327</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.493</v>
+        <v>-0.506</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
       </c>
       <c r="M4" s="10" t="n">
-        <v>13953270</v>
+        <v>13953350</v>
       </c>
     </row>
     <row r="5">
@@ -2433,28 +2433,28 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>101.69</v>
+        <v>100.74</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.06888378000000001</v>
+        <v>-0.02345876</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.169</v>
+        <v>-0.176</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.207</v>
+        <v>0.224</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>36.9</v>
+        <v>36.2</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.08</v>
+        <v>-0.08900000000000001</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.109</v>
+        <v>-0.118</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.245</v>
+        <v>-0.252</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>1.034</v>
@@ -2480,28 +2480,28 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.13</v>
+        <v>36.22</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.6598787</v>
+        <v>-0.024771087</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.105</v>
+        <v>0.113</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.1</v>
+        <v>-0.098</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>1.396</v>
@@ -2527,28 +2527,28 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>81.83</v>
+        <v>82.3</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.12235222</v>
+        <v>-0.9149946</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0.048</v>
+        <v>-0.043</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.193</v>
+        <v>0.226</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.022</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.09</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>1.22</v>
@@ -2574,28 +2574,28 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.74</v>
+        <v>58.16</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.010146176</v>
+        <v>-0.028390126</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.049</v>
+        <v>-0.058</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>40.2</v>
+        <v>39.9</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.049</v>
+        <v>-0.058</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.008</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.149</v>
+        <v>-0.157</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>1.453</v>
@@ -2607,142 +2607,142 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>86.25</v>
+        <v>19.97</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.5127636</v>
+        <v>0.014220355</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.23</v>
+        <v>-0.144</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.234</v>
+        <v>-0.104</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-2.9</v>
+        <v>-26.7</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.1</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.146</v>
+        <v>-0.187</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.272</v>
+        <v>-0.38</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.66</v>
+        <v>2.002</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>1211900</v>
+        <v>2197460</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.11</v>
+        <v>84.39</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.011666048</v>
+        <v>-0.039223495</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.151</v>
+        <v>-0.246</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.244</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-24</v>
+        <v>-3</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.164</v>
+        <v>-0.119</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.099</v>
+        <v>-0.165</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.142</v>
+        <v>-0.288</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>1.977</v>
+        <v>0.66</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>6400370</v>
+        <v>1211900</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>18.67</v>
+        <v>27.05</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.016884502</v>
+        <v>-0.01439506</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.199</v>
+        <v>0.148</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.181</v>
+        <v>-0.043</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-26.3</v>
+        <v>-23.4</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.012</v>
+        <v>0.161</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.24</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.421</v>
+        <v>-0.143</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>2.002</v>
+        <v>1.977</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>2197460</v>
+        <v>6401490</v>
       </c>
     </row>
     <row r="12">
@@ -2762,34 +2762,34 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.32</v>
+        <v>10.42</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.02272734</v>
+        <v>-0.02251405</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-0.109</v>
+        <v>-0.101</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.498</v>
+        <v>0.506</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>30</v>
+        <v>29.2</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.08</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.282</v>
+        <v>-0.275</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>1.1</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>1869320</v>
+        <v>1869380</v>
       </c>
     </row>
     <row r="13">
@@ -2809,28 +2809,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>20.19</v>
+        <v>21.02</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-0.013678495</v>
+        <v>-0.010593238</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.046</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.9229999999999999</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.078</v>
+        <v>0.122</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.109</v>
+        <v>0.155</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.109</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2859,16 +2859,16 @@
         <v>5.5</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.011680154</v>
+        <v>0.090964094</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.268</v>
+        <v>-0.267</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.049</v>
+        <v>-0.013</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>-0.09699999999999999</v>
@@ -2903,34 +2903,34 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>13.84</v>
+        <v>14.03</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-0.036127996</v>
+        <v>-0.9180798999999999</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.068</v>
+        <v>-0.055</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.205</v>
+        <v>-0.182</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>-19</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.003</v>
+        <v>0.017</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.149</v>
+        <v>-0.137</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.328</v>
+        <v>-0.319</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>1.364</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>4104850</v>
+        <v>4104950</v>
       </c>
     </row>
     <row r="16">
@@ -2950,28 +2950,28 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>96.67</v>
+        <v>96.36</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.2852713</v>
+        <v>-0.012653695</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.01</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.191</v>
+        <v>0.202</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.151</v>
+        <v>-0.154</v>
       </c>
       <c r="L16" s="8" t="n">
         <v>1.376</v>
@@ -2997,34 +2997,34 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-0.016736735</v>
+        <v>-0.017021261</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5710000000000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.513</v>
+        <v>-0.54</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-27.9</v>
+        <v>-29.4</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.368</v>
+        <v>-0.379</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.542</v>
+        <v>-0.55</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.6579999999999999</v>
+        <v>-0.664</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.993</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>7512390</v>
+        <v>7512840</v>
       </c>
     </row>
     <row r="18">
@@ -3044,28 +3044,28 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>10.96</v>
+        <v>11</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.016697617</v>
+        <v>-0.6323369</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.036</v>
+        <v>-0.033</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.032</v>
+        <v>-0.028</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.022</v>
+        <v>-0.018</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.177</v>
+        <v>-0.174</v>
       </c>
       <c r="L18" s="8" t="n">
         <v>1.07</v>
@@ -3091,28 +3091,28 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>27.16</v>
+        <v>26.62</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.64839256</v>
+        <v>-0.021858902</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.016</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.009000000000000001</v>
+        <v>-0.006</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.048</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.17</v>
+        <v>-0.187</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.412</v>
@@ -3138,28 +3138,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.25</v>
+        <v>12.24</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.013687607</v>
+        <v>0.28664905</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>-0.264</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.246</v>
+        <v>-0.283</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>36.3</v>
+        <v>36.7</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>-0.168</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.076</v>
+        <v>-0.077</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.409</v>
+        <v>-0.41</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -3187,28 +3187,28 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.74</v>
+        <v>6.42</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-0.14815153</v>
+        <v>-0.02061072</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.249</v>
+        <v>-0.285</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.266</v>
+        <v>-0.295</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.207</v>
+        <v>-0.244</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.214</v>
+        <v>-0.252</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.323</v>
+        <v>-0.355</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>1.206</v>
@@ -3234,28 +3234,28 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.017928318</v>
+        <v>-0.040650463</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.052</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.406</v>
+        <v>-0.43</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>-53</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.015</v>
+        <v>-0.022</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.204</v>
+        <v>-0.233</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.503</v>
+        <v>-0.521</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.327</v>
@@ -3338,7 +3338,7 @@
         <v>-0.239</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>-291</v>
+        <v>-291.2</v>
       </c>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
@@ -3570,31 +3570,31 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>53.69</v>
+        <v>53.48</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>36.302</v>
+        <v>36.16</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>22.84681</v>
+        <v>22.757448</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.288604</v>
+        <v>14.232716</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>10.759</v>
+        <v>10.777</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>3.747</v>
+        <v>3.753</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.788624</v>
+        <v>22.699492</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.7887886</v>
+        <v>2.7778807</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>104.75</v>
+        <v>104.79</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.378</v>
+        <v>18.385</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.698921</v>
+        <v>9.702624999999999</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>14.236</v>
+        <v>14.228</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.853</v>
+        <v>1.852</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.0308259</v>
+        <v>2.0316014</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1218</v>
+        <v>1.1222284</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24.74</v>
+        <v>24.09</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>12.315</v>
+        <v>11.991</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3689,22 +3689,22 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>12.711298</v>
+        <v>12.377331</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>48.464</v>
+        <v>47.796</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>2.184</v>
+        <v>2.154</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>19.388714</v>
+        <v>18.87931</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>2.033998</v>
+        <v>1.9805584</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3733,31 +3733,31 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>101.69</v>
+        <v>100.74</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.605</v>
+        <v>10.505</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.38535</v>
+        <v>32.0828</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>17.11443</v>
+        <v>16.954544</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>11.382</v>
+        <v>11.473</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>2.79</v>
+        <v>2.812</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-37.831104</v>
+        <v>-37.477676</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.4856654</v>
+        <v>1.4717863</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3786,31 +3786,31 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.13</v>
+        <v>36.22</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9.882</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>47.539474</v>
+        <v>47.657898</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>15.39622</v>
+        <v>15.434572</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>16.747</v>
+        <v>16.831</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>11.6</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>2.248</v>
+        <v>2.26</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.8407571</v>
+        <v>3.8503246</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.56346023</v>
+        <v>0.56486386</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3839,31 +3839,31 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>81.83</v>
+        <v>82.3</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.178</v>
+        <v>6.213</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.6272166</v>
+        <v>3.6480498</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.043682</v>
+        <v>10.10137</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>7.1</v>
+        <v>7.184</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>2.084</v>
+        <v>2.108</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.3957021</v>
+        <v>2.4094622</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5096637</v>
+        <v>1.5183347</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>22.56</v>
@@ -3892,31 +3892,31 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.74</v>
+        <v>58.16</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.04</v>
+        <v>5.98</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>18.826923</v>
+        <v>18.641026</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>17.876219</v>
+        <v>17.699707</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>8.417999999999999</v>
+        <v>8.541</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>3.406</v>
+        <v>3.456</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.444569</v>
+        <v>16.282194</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>3.0027857</v>
+        <v>2.973136</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>3.12</v>
@@ -3931,162 +3931,162 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>86.25</v>
+        <v>19.97</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>6.011</v>
+        <v>5.91</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>16.304348</v>
+        <v>55.472218</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>11.616099</v>
+        <v>24.552261</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>11.522</v>
+        <v>11.056</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>3.767</v>
+        <v>4.35</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>5.9454055</v>
+        <v>5.347088</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.0545175</v>
+        <v>4.581639</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>5.29</v>
+        <v>0.36</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>7.42504</v>
+        <v>0.813367</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>14.507</v>
+        <v>3.734743</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>27.11</v>
+        <v>84.39</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>5.881</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>15.951797</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>29.30811</v>
+        <v>11.364923</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>8.727</v>
+        <v>11.669</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>7.3</v>
+        <v>9.9</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>2.655</v>
+        <v>3.816</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>1.5676864</v>
+        <v>5.8168473</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.48174876</v>
+        <v>2.010092</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-2.42</v>
+        <v>5.29</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.925</v>
+        <v>7.42504</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>17.293</v>
+        <v>14.507</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>18.67</v>
+        <v>27.05</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.525</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>51.86111</v>
+        <v>5.52</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>22.80457</v>
+        <v>29.237837</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10.269</v>
+        <v>8.727</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>4.04</v>
+        <v>2.656</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>4.966468</v>
+        <v>1.5639277</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>4.2833853</v>
+        <v>0.4805937</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.36</v>
+        <v>-2.42</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.8186956</v>
+        <v>0.925</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>3.7592108</v>
+        <v>17.293</v>
       </c>
     </row>
     <row r="12">
@@ -4106,31 +4106,31 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.32</v>
+        <v>10.42</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.218</v>
+        <v>5.269</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>24.571428</v>
+        <v>24.809525</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11.897488</v>
+        <v>12.0127735</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10.051</v>
+        <v>10.154</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>2.105</v>
+        <v>2.127</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>7.0061097</v>
+        <v>7.0739985</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>2.2272198</v>
+        <v>2.2488015</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0.42</v>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>20.19</v>
+        <v>21.02</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4.7</v>
+        <v>4.892</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>65.129036</v>
+        <v>67.79031999999999</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>26.980076</v>
+        <v>28.08253</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>13.706721</v>
+        <v>14.266802</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.142987</v>
+        <v>4.312277</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -4221,28 +4221,28 @@
         <v>5.5</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.147</v>
+        <v>2.239</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>11.945652</v>
+        <v>11.967391</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>6.9068236</v>
+        <v>6.9193935</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>10.669</v>
+        <v>10.611</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>2.492</v>
+        <v>2.479</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>-1.7220306</v>
+        <v>-1.7251645</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.41578358</v>
+        <v>0.43371302</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0.46</v>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>13.84</v>
+        <v>14.03</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1.848</v>
+        <v>1.874</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4282,22 +4282,22 @@
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>7.948728</v>
+        <v>8.060763</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>17.079</v>
+        <v>17.135</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.772</v>
+        <v>1.778</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.95236456</v>
+        <v>0.96578777</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.26542345</v>
+        <v>0.2691645</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>-5.83</v>
@@ -4326,31 +4326,31 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>96.67</v>
+        <v>96.36</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.729</v>
+        <v>1.724</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>17.80387</v>
+        <v>17.746777</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>16.261564</v>
+        <v>16.20942</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>8.605</v>
+        <v>8.717000000000001</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>3.2039175</v>
+        <v>3.1936436</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>3.1720078</v>
+        <v>3.1618361</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>5.43</v>
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.155</v>
+        <v>1.138</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4.737374</v>
+        <v>4.6666665</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-7.671</v>
+        <v>-7.528</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -4401,13 +4401,13 @@
         </is>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.381</v>
+        <v>1.356</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>1.5946957</v>
+        <v>1.5708942</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>1.7272995</v>
+        <v>1.6997067</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0.44</v>
@@ -4436,31 +4436,31 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>10.96</v>
+        <v>11</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.912</v>
+        <v>0.915</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>18.266666</v>
+        <v>18.333332</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>11.83547</v>
+        <v>11.878665</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>6.362</v>
+        <v>6.487</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.904</v>
+        <v>0.922</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>3.3445225</v>
+        <v>3.3567288</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.6851889</v>
+        <v>0.6876896</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>0.6</v>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>27.16</v>
+        <v>26.62</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.717</v>
+        <v>0.703</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
@@ -4500,22 +4500,22 @@
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>22.450413</v>
+        <v>22.004131</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>9.584</v>
+        <v>9.632999999999999</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>7.3</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.842</v>
+        <v>1.852</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>1.6899964</v>
+        <v>1.6564018</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>1.1294872</v>
+        <v>1.1070344</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>-0.23</v>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.25</v>
+        <v>12.24</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0.602</v>
@@ -4555,25 +4555,25 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>-8.221477</v>
+        <v>-8.218121</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>18.901</v>
+        <v>18.869</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>12.9</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>2.455</v>
+        <v>2.45</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.1540273</v>
+        <v>1.1535563</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.24178354</v>
+        <v>0.24168485</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-12.97</v>
+        <v>-12.75</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-1.49</v>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.74</v>
+        <v>6.42</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.182</v>
+        <v>0.174</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -4610,22 +4610,22 @@
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>8.996743</v>
+        <v>8.562923</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>6.909</v>
+        <v>6.836</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>5.5</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.688</v>
+        <v>1.67</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>-11.177446</v>
+        <v>-10.638474</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.5997419</v>
+        <v>0.5708226</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>-0.58</v>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.089</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -4665,31 +4665,31 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>-6.012195</v>
+        <v>-5.7804875</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>12.89</v>
+        <v>12.657</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.958</v>
+        <v>1.929</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>6.2722645</v>
+        <v>33.85714</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.2944661</v>
+        <v>0.28311753</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.12</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>-0.41</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.393</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -5525,178 +5525,178 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2.926</v>
+        <v>1.29</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.067</v>
+        <v>0.201</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.33583</v>
+        <v>0.26816</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.18802</v>
+        <v>0.15614</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.1309</v>
+        <v>0.07777000000000001</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.32698002</v>
+        <v>0.39339</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.35709</v>
+        <v>0.10515001</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.06236</v>
+        <v>0.04121</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.957</v>
+        <v>0.507</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.082</v>
+        <v>0.341</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>5.197</v>
+        <v>0.063</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.201</v>
+        <v>0.365</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>492.233</v>
+        <v>6.424</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>0.604</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>11.486</v>
+        <v>2.926</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.042</v>
+        <v>0.067</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.5</v>
+        <v>0.33583</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1893</v>
+        <v>0.18802</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.043709997</v>
+        <v>0.1309</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.30427998</v>
+        <v>0.32698002</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-0.10840999</v>
+        <v>0.35709</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.04044</v>
+        <v>0.06236</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>3.495</v>
+        <v>0.957</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>25.622</v>
+        <v>5.197</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.887</v>
+        <v>0.201</v>
       </c>
       <c r="P10" s="7" t="n">
-        <v>695.117</v>
+        <v>492.233</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>0.8</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1.29</v>
+        <v>11.486</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.201</v>
+        <v>0.042</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.26816</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.15614</v>
+        <v>0.1893</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.07777000000000001</v>
+        <v>-0.043709997</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.39339</v>
+        <v>0.30427998</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.10515001</v>
+        <v>-0.10840999</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.04121</v>
+        <v>0.04044</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.507</v>
+        <v>3.495</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.341</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.063</v>
+        <v>25.622</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.365</v>
+        <v>0.887</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>6.424</v>
+        <v>695.117</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>1.167</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
@@ -6337,37 +6337,31 @@
         <v>-0.13294</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.15188</v>
+        <v>0.15241</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-1.4696201</v>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-1.8681101</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0.00328</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>0.046</v>
       </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="M22" s="6" t="n">
+        <v>0.014</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.532</v>
+        <v>0.535</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.031</v>
+        <v>0.041</v>
       </c>
       <c r="P22" s="7" t="n">
-        <v>3746.09</v>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>21063.79</v>
+      </c>
+      <c r="Q22" s="7" t="n">
+        <v>0.721</v>
       </c>
     </row>
     <row r="23">
@@ -6845,7 +6839,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>53.69</v>
+        <v>53.48</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6868,7 +6862,7 @@
         <v>58</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>0.301</v>
+        <v>0.307</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>1.8</v>
@@ -6883,7 +6877,7 @@
         <v>0.41693002</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="P2" s="5" t="n">
         <v>0.4255</v>
@@ -6901,7 +6895,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>104.75</v>
+        <v>104.79</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6924,7 +6918,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>1.031</v>
+        <v>1.03</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>1.72</v>
@@ -6933,10 +6927,10 @@
         <v>0.0517</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>0.18817</v>
+        <v>0.18823999</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>0.90992</v>
+        <v>0.91029</v>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
@@ -6959,7 +6953,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>24.74</v>
+        <v>24.09</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6982,7 +6976,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.46</v>
+        <v>0.499</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -7017,7 +7011,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>101.69</v>
+        <v>100.74</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -7040,7 +7034,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.395</v>
+        <v>0.408</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.24</v>
@@ -7052,10 +7046,10 @@
         <v>0.27027</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0.68544996</v>
+        <v>0.68558997</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="P5" s="5" t="n">
         <v>0.3185</v>
@@ -7073,7 +7067,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>36.13</v>
+        <v>36.22</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -7096,7 +7090,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.181</v>
+        <v>0.178</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.2</v>
@@ -7131,7 +7125,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>81.83</v>
+        <v>82.3</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -7154,7 +7148,7 @@
         <v>84</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.154</v>
+        <v>0.148</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.32</v>
@@ -7169,7 +7163,7 @@
         <v>0.73223996</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="P7" s="5" t="n">
         <v>0.0319</v>
@@ -7187,7 +7181,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>58.74</v>
+        <v>58.16</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -7210,7 +7204,7 @@
         <v>59</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.248</v>
+        <v>0.261</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>3.89</v>
@@ -7225,7 +7219,7 @@
         <v>0.88903</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="P8" s="5" t="n">
         <v>0.32369998</v>
@@ -7234,16 +7228,16 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>86.25</v>
+        <v>19.97</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -7251,148 +7245,148 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1.25</v>
+        <v>1.33333</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>135.5</v>
+        <v>28.806065</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>152</v>
+        <v>37.152924</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>110</v>
+        <v>21.913837</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.5710000000000001</v>
+        <v>0.442</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>2.68</v>
+        <v>4.19</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.044499997</v>
+        <v>0.1088</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.06136</v>
+        <v>0.01337</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0.81709</v>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v>0.51</v>
+        <v>0.91643</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.0828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>27.11</v>
+        <v>84.39</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1.82353</v>
+        <v>1.25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>31.95778</v>
+        <v>135.5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>41</v>
+        <v>152</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.179</v>
+        <v>0.606</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>3.8</v>
+        <v>2.68</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.1713</v>
+        <v>0.044499997</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>0.02256</v>
+        <v>0.06136</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>1.11968</v>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.81711</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>18.67</v>
+        <v>27.05</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>strong_buy</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1.33333</v>
+        <v>1.82353</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>28.726435</v>
+        <v>31.95778</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>37.05022</v>
+        <v>41</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>21.85326</v>
+        <v>22</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.539</v>
+        <v>0.181</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>4.19</v>
+        <v>3.8</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.1088</v>
+        <v>0.1713</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.01337</v>
+        <v>0.010570001</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.91643</v>
+        <v>1.11968</v>
       </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
@@ -7415,7 +7409,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>10.32</v>
+        <v>10.42</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -7440,7 +7434,7 @@
         <v>16</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>4.92</v>
@@ -7455,7 +7449,7 @@
         <v>0.19124001</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="P12" s="5" t="n">
         <v>0.2831</v>
@@ -7473,7 +7467,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>20.19</v>
+        <v>21.02</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -7496,7 +7490,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.228</v>
+        <v>0.18</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.71</v>
@@ -7505,7 +7499,7 @@
         <v>0.0498</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>0.07383000000000001</v>
+        <v>0.07047</v>
       </c>
       <c r="N13" s="5" t="n">
         <v>0.93144995</v>
@@ -7589,7 +7583,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>13.84</v>
+        <v>14.03</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7612,7 +7606,7 @@
         <v>15</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.381</v>
+        <v>0.362</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>4.18</v>
@@ -7647,7 +7641,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>96.67</v>
+        <v>96.36</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7672,7 +7666,7 @@
         <v>93</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.114</v>
+        <v>0.117</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>2.53</v>
@@ -7687,7 +7681,7 @@
         <v>0.64762</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P16" s="5" t="n">
         <v>0.221</v>
@@ -7705,7 +7699,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7728,7 +7722,7 @@
         <v>6</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1.503</v>
+        <v>1.546</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>1.77</v>
@@ -7763,7 +7757,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>10.96</v>
+        <v>11</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -7786,7 +7780,7 @@
         <v>14</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.414</v>
+        <v>0.409</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>3.68</v>
@@ -7821,7 +7815,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.16</v>
+        <v>26.62</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7844,7 +7838,7 @@
         <v>30</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.123</v>
+        <v>0.146</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>2.5</v>
@@ -7859,7 +7853,7 @@
         <v>0.68561995</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>4.5455</v>
@@ -7877,7 +7871,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>12.25</v>
+        <v>12.24</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7900,7 +7894,7 @@
         <v>11</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.279</v>
+        <v>0.28</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>9.16</v>
@@ -7935,7 +7929,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>6.74</v>
+        <v>6.42</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -7958,7 +7952,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.978</v>
+        <v>1.077</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>13.9</v>
@@ -7993,7 +7987,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -8016,7 +8010,7 @@
         <v>2.5</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.321</v>
+        <v>0.371</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>5.72</v>
@@ -8469,10 +8463,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>36.302</v>
+        <v>36.16</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>22.84681</v>
+        <v>22.757448</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -8484,10 +8478,10 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.172</v>
+        <v>-0.176</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>10.759</v>
+        <v>10.777</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>9.199999999999999</v>
@@ -8513,7 +8507,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.533</v>
+        <v>5.52</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -8530,7 +8524,7 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.151</v>
+        <v>0.148</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>8.727</v>
@@ -8559,10 +8553,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>10.605</v>
+        <v>10.505</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>32.38535</v>
+        <v>32.0828</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.015</v>
@@ -8576,13 +8570,13 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.169</v>
+        <v>-0.176</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>11.382</v>
+        <v>11.473</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L5" s="7" t="n">
         <v>41.7</v>
@@ -8605,10 +8599,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2.147</v>
+        <v>2.239</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>11.945652</v>
+        <v>11.967391</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -8622,13 +8616,13 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-0.268</v>
+        <v>-0.267</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>10.669</v>
+        <v>10.611</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="L6" s="7" t="n">
         <v>40</v>
@@ -8651,10 +8645,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>9.882</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>47.539474</v>
+        <v>47.657898</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.06</v>
@@ -8666,10 +8660,10 @@
         <v>0.1489</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>16.747</v>
+        <v>16.831</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>11.6</v>
@@ -8713,10 +8707,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.178</v>
+        <v>6.213</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.6272166</v>
+        <v>3.6480498</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -8728,16 +8722,16 @@
         <v>0.87788004</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-0.048</v>
+        <v>-0.043</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.1</v>
+        <v>7.184</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>69</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -8757,10 +8751,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6.011</v>
+        <v>5.881</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>16.304348</v>
+        <v>15.951797</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.067</v>
@@ -8772,13 +8766,13 @@
         <v>0.35709</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>-0.23</v>
+        <v>-0.246</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>11.522</v>
+        <v>11.669</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="L11" s="7" t="n">
         <v>63.5</v>
@@ -8801,10 +8795,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1.729</v>
+        <v>1.724</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>17.80387</v>
+        <v>17.746777</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.041</v>
@@ -8816,13 +8810,13 @@
         <v>0.19214001</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.01</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>8.605</v>
+        <v>8.717000000000001</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="L12" s="7" t="n">
         <v>62.7</v>
@@ -8845,10 +8839,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6.04</v>
+        <v>5.98</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.826923</v>
+        <v>18.641026</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8860,16 +8854,16 @@
         <v>1.113</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.049</v>
+        <v>-0.058</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>8.417999999999999</v>
+        <v>8.541</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>59.5</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="14">
@@ -8889,7 +8883,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.848</v>
+        <v>1.874</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8906,16 +8900,16 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.068</v>
+        <v>-0.055</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>17.079</v>
+        <v>17.135</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>42.9</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="15">
@@ -8935,7 +8929,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.717</v>
+        <v>0.703</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -8952,10 +8946,10 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.016</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>9.584</v>
+        <v>9.632999999999999</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>7.3</v>
@@ -8981,7 +8975,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.089</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -8992,22 +8986,22 @@
         <v>0.034</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.15188</v>
+        <v>0.15241</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-1.4696201</v>
+        <v>-1.8681101</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.052</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>12.89</v>
+        <v>12.657</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>28.6</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="17">
@@ -9047,7 +9041,7 @@
         <v>-0.264</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>18.901</v>
+        <v>18.869</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>12.9</v>
@@ -9091,10 +9085,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.218</v>
+        <v>5.269</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>24.571428</v>
+        <v>24.809525</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -9106,13 +9100,13 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.109</v>
+        <v>-0.101</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>10.051</v>
+        <v>10.154</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="L20" s="7" t="n">
         <v>66.7</v>
@@ -9135,10 +9129,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.525</v>
+        <v>5.91</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>51.86111</v>
+        <v>55.472218</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -9150,13 +9144,13 @@
         <v>0.10515001</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.199</v>
+        <v>-0.144</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>10.269</v>
+        <v>11.056</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>58.3</v>
@@ -9179,10 +9173,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4.7</v>
+        <v>4.892</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>65.129036</v>
+        <v>67.79031999999999</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -9194,7 +9188,7 @@
         <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.046</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
@@ -9227,7 +9221,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>12.315</v>
+        <v>11.991</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -9244,13 +9238,13 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.306</v>
+        <v>-0.324</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>48.464</v>
+        <v>47.796</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="L23" s="7" t="n">
         <v>52</v>
@@ -9273,7 +9267,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.378</v>
+        <v>18.385</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -9293,7 +9287,7 @@
         <v>-0.52</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>14.236</v>
+        <v>14.228</v>
       </c>
       <c r="K24" s="7" t="n">
         <v>9.699999999999999</v>
@@ -9319,7 +9313,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.155</v>
+        <v>1.138</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -9336,10 +9330,10 @@
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5710000000000001</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>-7.671</v>
+        <v>-7.528</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
@@ -9441,10 +9435,10 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.912</v>
+        <v>0.915</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>18.266666</v>
+        <v>18.333332</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>0.075</v>
@@ -9456,13 +9450,13 @@
         <v>0.19236</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.036</v>
+        <v>-0.033</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>6.362</v>
+        <v>6.487</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L29" s="7" t="n">
         <v>56.7</v>
@@ -9541,7 +9535,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.182</v>
+        <v>0.174</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -9560,10 +9554,10 @@
         </is>
       </c>
       <c r="I31" s="5" t="n">
-        <v>-0.249</v>
+        <v>-0.285</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>6.909</v>
+        <v>6.836</v>
       </c>
       <c r="K31" s="7" t="n">
         <v>5.5</v>
@@ -10423,10 +10417,10 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.18817</v>
+        <v>0.18823999</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.90992</v>
+        <v>0.91029</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>1.72</v>
@@ -10480,7 +10474,7 @@
         <v>0.27027</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.68544996</v>
+        <v>0.68558997</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>3.24</v>
@@ -10576,82 +10570,82 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.06136</v>
+        <v>0.01337</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.81709</v>
+        <v>0.91643</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2.68</v>
+        <v>4.19</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.044499997</v>
+        <v>0.1088</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>2574942</v>
+        <v>11183802</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.02256</v>
+        <v>0.06136</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1.11968</v>
+        <v>0.81711</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.8</v>
+        <v>2.68</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.1713</v>
+        <v>0.044499997</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>30537844</v>
+        <v>2574942</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.01337</v>
+        <v>0.010570001</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.91643</v>
+        <v>1.11968</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>4.19</v>
+        <v>3.8</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.1088</v>
+        <v>0.1713</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>11183802</v>
+        <v>30537844</v>
       </c>
     </row>
     <row r="12">
@@ -10693,7 +10687,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.07383000000000001</v>
+        <v>0.07047</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>0.93144995</v>
@@ -11145,955 +11139,955 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1268.42</v>
+        <v>1272.49</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>1221.72</v>
+        <v>1230.86</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>1052.19</v>
+        <v>1068.94</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1252.54</v>
+        <v>1272.41</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1227.3</v>
+        <v>1235.19</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>1050.66</v>
+        <v>1071.29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1252.44</v>
+        <v>1278.47</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1231.62</v>
+        <v>1235.06</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>1052.96</v>
+        <v>1072.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1258.42</v>
+        <v>1268.25</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1231.49</v>
+        <v>1230.66</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1053.73</v>
+        <v>1064.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1248.27</v>
+        <v>1263.39</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1227.1</v>
+        <v>1229.16</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1046.3</v>
+        <v>1062.69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1243.43</v>
+        <v>1255.76</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1225.61</v>
+        <v>1220.05</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1044.51</v>
+        <v>1065.29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1235.99</v>
+        <v>1261.15</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1216.53</v>
+        <v>1222.29</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1047.07</v>
+        <v>1066.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1241.47</v>
+        <v>1261.92</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1218.76</v>
+        <v>1230.43</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1048.1</v>
+        <v>1064.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1242.31</v>
+        <v>1246.35</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1226.87</v>
+        <v>1237.75</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1046.05</v>
+        <v>1057.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1227.01</v>
+        <v>1199.5</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>1234.17</v>
+        <v>1233.76</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1039.64</v>
+        <v>1038.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1181.05</v>
+        <v>1224.57</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1230.19</v>
+        <v>1233.63</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1020.68</v>
+        <v>1055.65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1205.83</v>
+        <v>1196.22</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1230.07</v>
+        <v>1241.79</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>1037.59</v>
+        <v>1048.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1177.94</v>
+        <v>1191.64</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1238.2</v>
+        <v>1243.74</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>1030.16</v>
+        <v>1043.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1173.38</v>
+        <v>1183.88</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1240.14</v>
+        <v>1241.25</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1026.06</v>
+        <v>1031.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1165.7</v>
+        <v>1181.68</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1237.67</v>
+        <v>1235.15</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1014.02</v>
+        <v>1034.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1163.52</v>
+        <v>1200.97</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1231.58</v>
+        <v>1238.52</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>1016.58</v>
+        <v>1045.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1182.53</v>
+        <v>1164.07</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1234.94</v>
+        <v>1237.48</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1027.86</v>
+        <v>1025.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1146.14</v>
+        <v>1140.49</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>1233.9</v>
+        <v>1212.29</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>1007.87</v>
+        <v>1008.73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1122.89</v>
+        <v>1146.66</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1208.78</v>
+        <v>1226.28</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>991.48</v>
+        <v>1010.55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1129</v>
+        <v>1151.63</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1222.73</v>
+        <v>1232.68</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>993.27</v>
+        <v>1018.63</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1133.89</v>
+        <v>1135.9</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1229.12</v>
+        <v>1233.13</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1001.21</v>
+        <v>1011.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1118.33</v>
+        <v>1141.6</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>1229.57</v>
+        <v>1239.39</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>994.29</v>
+        <v>1017.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1123.98</v>
+        <v>1128.39</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>1235.81</v>
+        <v>1244.33</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>999.9299999999999</v>
+        <v>1013.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1110.85</v>
+        <v>1130.26</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>1240.73</v>
+        <v>1244.21</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>996.34</v>
+        <v>1005.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1112.66</v>
+        <v>1079.54</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>1240.61</v>
+        <v>1241.74</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>988.66</v>
+        <v>989.4400000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1062.87</v>
+        <v>1066.63</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>1238.15</v>
+        <v>1238.03</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>972.52</v>
+        <v>968.0700000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1049.95</v>
+        <v>1084.35</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>1234.45</v>
+        <v>1244.19</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>951.51</v>
+        <v>977.45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1067.16</v>
+        <v>1080.55</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1240.59</v>
+        <v>1233.67</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>960.73</v>
+        <v>966.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1063.4</v>
+        <v>1101.57</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>1230.1</v>
+        <v>1227.69</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>949.97</v>
+        <v>987.88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1084.18</v>
+        <v>1076.51</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>1224.14</v>
+        <v>1212.36</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>970.98</v>
+        <v>968.59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1059.36</v>
+        <v>1103.52</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>1208.85</v>
+        <v>1235.62</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>952.02</v>
+        <v>986.84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1085.97</v>
+        <v>1105.66</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>1232.05</v>
+        <v>1241.58</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>969.96</v>
+        <v>994.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1088.12</v>
+        <v>1102.58</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>1237.99</v>
+        <v>1238.3</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>977.13</v>
+        <v>995.96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1085.13</v>
+        <v>1087.52</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>1234.72</v>
+        <v>1238.02</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>978.92</v>
+        <v>988.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1070.19</v>
+        <v>1050.74</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>1234.44</v>
+        <v>1218.89</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>971.49</v>
+        <v>953.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1034.14</v>
+        <v>1040.57</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>1215.37</v>
+        <v>1219.75</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>937.6799999999999</v>
+        <v>941.74</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1023.65</v>
+        <v>1055.74</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>1216.22</v>
+        <v>1221.72</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>925.63</v>
+        <v>943.5700000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1038.48</v>
+        <v>1089.36</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>1218.18</v>
+        <v>1227.87</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>927.4299999999999</v>
+        <v>969.11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1071.5</v>
+        <v>1084.28</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>1224.32</v>
+        <v>1224.63</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>952.53</v>
+        <v>964.42</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1066.3</v>
+        <v>1084.48</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>1221.09</v>
+        <v>1233.49</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>947.92</v>
+        <v>962.0700000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1066.44</v>
+        <v>1041.42</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>1229.92</v>
+        <v>1220.89</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>945.62</v>
+        <v>940.4400000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1024.05</v>
+        <v>1055.67</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>1217.36</v>
+        <v>1229.77</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>924.35</v>
+        <v>948.52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1038.1</v>
+        <v>1059.6</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>1226.21</v>
+        <v>1240.15</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>932.29</v>
+        <v>949.8200000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1042.01</v>
+        <v>1088.98</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>1236.56</v>
+        <v>1233.26</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>933.58</v>
+        <v>952.17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1070.74</v>
+        <v>1076.12</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>1229.69</v>
+        <v>1227.34</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>935.88</v>
+        <v>956.34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1057.96</v>
+        <v>1071.27</v>
       </c>
       <c r="C47" s="13" t="n">
-        <v>1223.79</v>
+        <v>1228.03</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>939.98</v>
+        <v>947.74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1052.99</v>
+        <v>1067.19</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>1224.48</v>
+        <v>1217.21</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>931.53</v>
+        <v>941.22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1049.34</v>
+        <v>1083.01</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>1213.69</v>
+        <v>1225.8</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>925.12</v>
+        <v>946.96</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1064.77</v>
+        <v>1080.92</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>1222.25</v>
+        <v>1218.96</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>930.76</v>
+        <v>940.96</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1062.65</v>
+        <v>1049.4</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>1215.44</v>
+        <v>1202.98</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>924.87</v>
+        <v>931.3200000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1031.55</v>
+        <v>1051</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>1199.51</v>
+        <v>1213.52</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>915.39</v>
+        <v>933.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1033.09</v>
+        <v>1050.24</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>1210.01</v>
+        <v>1211.57</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>917.4400000000001</v>
+        <v>931.58</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1032.38</v>
+        <v>1064.68</v>
       </c>
       <c r="C54" s="13" t="n">
-        <v>1208.07</v>
+        <v>1210.05</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>915.64</v>
+        <v>936.01</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1046.6</v>
+        <v>1051.08</v>
       </c>
       <c r="C55" s="13" t="n">
-        <v>1206.55</v>
+        <v>1191.68</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>920</v>
+        <v>924.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1033.08</v>
+        <v>1053.04</v>
       </c>
       <c r="C56" s="13" t="n">
-        <v>1188.23</v>
+        <v>1184.93</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>908.98</v>
+        <v>922.71</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1035.22</v>
+        <v>1045.06</v>
       </c>
       <c r="C57" s="13" t="n">
-        <v>1181.51</v>
+        <v>1196.99</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>906.9299999999999</v>
+        <v>919.85</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1027.35</v>
+        <v>1057.56</v>
       </c>
       <c r="C58" s="13" t="n">
-        <v>1193.53</v>
+        <v>1200.14</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>904.11</v>
+        <v>919.0700000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1039.64</v>
+        <v>1049.74</v>
       </c>
       <c r="C59" s="13" t="n">
-        <v>1196.67</v>
+        <v>1183.39</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>903.34</v>
+        <v>908.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1031.87</v>
+        <v>1062.28</v>
       </c>
       <c r="C60" s="13" t="n">
-        <v>1179.97</v>
+        <v>1180.48</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>893.35</v>
+        <v>915.9400000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1025.34</v>
+        <v>1045.5</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -12105,7 +12099,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1025.34</v>
+        <v>1045.5</v>
       </c>
     </row>
     <row r="64">
@@ -12116,7 +12110,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-17.41%</t>
+          <t>-17.10%</t>
         </is>
       </c>
     </row>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>53.48</v>
+        <v>52.93</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.010545785</v>
+        <v>-0.0207215</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,34 +670,34 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.241</v>
+        <v>-0.249</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>36.16</v>
+        <v>35.788</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>48.852</v>
+        <v>48.099</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.757448</v>
+        <v>23.013044</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.232716</v>
+        <v>14.086344</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>10.777</v>
+        <v>10.611</v>
       </c>
       <c r="N2" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>0.888</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0.273</v>
+        <v>0.289</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>-0.176</v>
+        <v>-0.184</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>104.79</v>
+        <v>104.81</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.015224159</v>
+        <v>-0.0150362</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -732,10 +732,10 @@
         <v>-0.6659999999999999</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.385</v>
+        <v>18.372</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>30.335</v>
+        <v>30.054</v>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.702624999999999</v>
+        <v>9.704476</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>14.228</v>
+        <v>14.097</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>1.177</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24.09</v>
+        <v>23.67</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.032918494</v>
+        <v>-0.0497792</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -790,13 +790,13 @@
         <v>21.01</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.506</v>
+        <v>-0.515</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11.991</v>
+        <v>11.782</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>13.043</v>
+        <v>12.431</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
@@ -804,22 +804,22 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>12.377331</v>
+        <v>12.161537</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>47.796</v>
+        <v>45.556</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>1.682</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.373</v>
+        <v>-0.401</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>-0.324</v>
+        <v>-0.336</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>100.74</v>
+        <v>99.98</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.02345876</v>
+        <v>-0.0308259</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,34 +851,34 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.252</v>
+        <v>-0.258</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.505</v>
+        <v>10.426</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>20.073</v>
+        <v>19.75</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.0828</v>
+        <v>32.88816</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>16.954544</v>
+        <v>16.826635</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>11.473</v>
+        <v>11.288</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>1.034</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>0.224</v>
+        <v>0.221</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>-0.176</v>
+        <v>-0.183</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.22</v>
+        <v>35.37</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.024771087</v>
+        <v>-0.0476575</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,34 +910,34 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.098</v>
+        <v>-0.119</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>9.906000000000001</v>
+        <v>9.673999999999999</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>39.629</v>
+        <v>39.176</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>47.657898</v>
+        <v>48.452053</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>15.434572</v>
+        <v>15.072357</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>16.831</v>
+        <v>16.638</v>
       </c>
       <c r="N6" s="7" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>1.396</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.113</v>
+        <v>0.126</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.031</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>82.3</v>
+        <v>81.06</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.9149946</v>
+        <v>-0.024079</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -969,34 +969,34 @@
         <v>58.94</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.099</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.213</v>
+        <v>6.119</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>8.627000000000001</v>
+        <v>8.476000000000001</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.6480498</v>
+        <v>3.6811988</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.10137</v>
+        <v>9.949173</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>7.184</v>
+        <v>7.058</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>1.22</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0.226</v>
+        <v>0.204</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.043</v>
+        <v>-0.057</v>
       </c>
     </row>
     <row r="8">
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.16</v>
+        <v>57.52</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.028390126</v>
+        <v>-0.0390912</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1028,152 +1028,152 @@
         <v>35.09</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.157</v>
+        <v>-0.166</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>5.98</v>
+        <v>5.915</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>6.951</v>
+        <v>6.815</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>18.641026</v>
+        <v>19.173334</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>17.699707</v>
+        <v>17.504938</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>8.541</v>
+        <v>8.374000000000001</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>1.453</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0.367</v>
+        <v>0.373</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.058</v>
+        <v>-0.068</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>0.014220355</v>
+        <v>83.73</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>-0.0466811</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>32.22</v>
+        <v>118.46</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>15.725</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.38</v>
+        <v>-0.293</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.91</v>
+        <v>5.836</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>5.611</v>
+        <v>10.88</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>55.472218</v>
+        <v>16.613096</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>24.552261</v>
+        <v>11.276708</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>11.056</v>
+        <v>11.373</v>
       </c>
       <c r="N9" s="7" t="n">
         <v>9.6</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>2.002</v>
+        <v>0.66</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.104</v>
+        <v>-0.25</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.144</v>
+        <v>-0.252</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>84.39</v>
+        <v>19.61</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.039223495</v>
+        <v>-0.406297</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>118.46</v>
+        <v>32.22</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>80.23999999999999</v>
+        <v>15.725</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.288</v>
+        <v>-0.391</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.881</v>
+        <v>5.804</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>11.164</v>
+        <v>5.593</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>15.951797</v>
+        <v>54.47222</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>11.364923</v>
+        <v>23.874111</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>11.669</v>
+        <v>11.021</v>
       </c>
       <c r="N10" s="7" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>0.66</v>
+        <v>2.002</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.244</v>
+        <v>-0.121</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.246</v>
+        <v>-0.159</v>
       </c>
     </row>
     <row r="11">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>27.05</v>
+        <v>26.76</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.01439506</v>
+        <v>-0.0247814</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>31.58</v>
@@ -1205,13 +1205,13 @@
         <v>17.86</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.143</v>
+        <v>-0.153</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.52</v>
+        <v>5.462</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>30.502</v>
+        <v>30.363</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="L11" s="7" t="n">
-        <v>29.237837</v>
+        <v>28.92973</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>8.727</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="N11" s="7" t="n">
         <v>7.3</v>
@@ -1231,10 +1231,10 @@
         <v>1.977</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.043</v>
+        <v>-0.022</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>0.148</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="12">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.42</v>
+        <v>10.46</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.02251405</v>
+        <v>-0.0187617</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>14.38</v>
@@ -1266,34 +1266,34 @@
         <v>5.59</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.275</v>
+        <v>-0.273</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.269</v>
+        <v>5.289</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>4.983</v>
+        <v>4.882</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>24.809525</v>
+        <v>24.904762</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>12.0127735</v>
+        <v>12.0588875</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>10.154</v>
+        <v>9.948</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>1.1</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0.506</v>
+        <v>0.545</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.101</v>
+        <v>-0.09699999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.02</v>
+        <v>20.7</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.010593238</v>
+        <v>-0.0254237</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>4.892</v>
+        <v>4.819</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>67.79031999999999</v>
+        <v>69</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>28.08253</v>
+        <v>27.661594</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0.9229999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.07200000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>0.090964094</v>
+        <v>5.46</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>-0.7272719999999999</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>10.15</v>
@@ -1390,22 +1390,22 @@
         <v>4.55</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-0.458</v>
+        <v>-0.462</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.239</v>
+        <v>2.221</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>12.798</v>
+        <v>12.751</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>11.967391</v>
+        <v>11.869565</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>6.9193935</v>
+        <v>6.8628316</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>10.611</v>
+        <v>10.572</v>
       </c>
       <c r="N14" s="7" t="n">
         <v>8.4</v>
@@ -1414,10 +1414,10 @@
         <v>0.603</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.013</v>
+        <v>-0.014</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.267</v>
+        <v>-0.273</v>
       </c>
     </row>
     <row r="15">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14.03</v>
+        <v>13.67</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.9180798999999999</v>
+        <v>-0.0346045</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20.61</v>
@@ -1449,13 +1449,13 @@
         <v>11.65</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.319</v>
+        <v>-0.337</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.874</v>
+        <v>1.826</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>12.375</v>
+        <v>12.314</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="L15" s="7" t="n">
-        <v>8.060763</v>
+        <v>7.8539295</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>17.135</v>
+        <v>17.051</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>1.364</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.182</v>
+        <v>-0.213</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.055</v>
+        <v>-0.079</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>96.36</v>
+        <v>96.5</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.012653695</v>
+        <v>-0.0112705</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>113.88</v>
@@ -1510,22 +1510,22 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.153</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.724</v>
+        <v>1.726</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1.663</v>
+        <v>1.643</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>17.746777</v>
+        <v>17.970205</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>16.20942</v>
+        <v>16.232128</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>8.717000000000001</v>
+        <v>8.614000000000001</v>
       </c>
       <c r="N16" s="7" t="n">
         <v>7.4</v>
@@ -1534,10 +1534,10 @@
         <v>1.376</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0.202</v>
+        <v>0.204</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="17">
@@ -1557,25 +1557,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.62</v>
+        <v>4.53</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.017021261</v>
+        <v>-0.0361701</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>13.73</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>4.6</v>
+        <v>4.51</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.664</v>
+        <v>-0.67</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.138</v>
+        <v>1.165</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.908</v>
+        <v>0.866</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="L17" s="7" t="n">
-        <v>4.6666665</v>
+        <v>4.575758</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>-7.528</v>
+        <v>-7.181</v>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         <v>1.993</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.54</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.5710000000000001</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="18">
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>11</v>
+        <v>10.92</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.6323369</v>
+        <v>-0.0135501</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.31</v>
@@ -1632,34 +1632,34 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.174</v>
+        <v>-0.18</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.915</v>
+        <v>0.909</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1.227</v>
+        <v>1.214</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>18.333332</v>
+        <v>18.199999</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>11.878665</v>
+        <v>11.792274</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>6.487</v>
+        <v>6.422</v>
       </c>
       <c r="N18" s="7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>1.07</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.033</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="19">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>26.62</v>
+        <v>26.2</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.021858902</v>
+        <v>-0.0374724</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>32.74</v>
@@ -1691,13 +1691,13 @@
         <v>19.57</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.187</v>
+        <v>-0.2</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.703</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.176</v>
+        <v>1.149</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
@@ -1705,22 +1705,22 @@
         </is>
       </c>
       <c r="L19" s="7" t="n">
-        <v>22.004131</v>
+        <v>21.652893</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>9.632999999999999</v>
+        <v>9.414</v>
       </c>
       <c r="N19" s="7" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>1.412</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.006</v>
+        <v>-0.005</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.016</v>
+        <v>-0.032</v>
       </c>
     </row>
     <row r="20">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>0.28664905</v>
+        <v>12.04</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-0.013923</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>20.74</v>
@@ -1752,13 +1752,13 @@
         <v>8.455</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.41</v>
+        <v>-0.419</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.602</v>
+        <v>0.592</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>6.104</v>
+        <v>6.095</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>-8.218121</v>
+        <v>-8.080537</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>18.869</v>
+        <v>18.843</v>
       </c>
       <c r="N20" s="7" t="n">
         <v>12.9</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.283</v>
+        <v>-0.34</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.264</v>
+        <v>-0.276</v>
       </c>
     </row>
     <row r="21">
@@ -1803,25 +1803,25 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.42</v>
+        <v>6.11</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.02061072</v>
+        <v>-0.0671756</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>6.38</v>
+        <v>6.1</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.355</v>
+        <v>-0.386</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.174</v>
+        <v>0.165</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.508</v>
+        <v>0.496</v>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
@@ -1829,22 +1829,22 @@
         </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>8.562923</v>
+        <v>8.155802</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>6.836</v>
+        <v>6.676</v>
       </c>
       <c r="N21" s="7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>1.206</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.295</v>
+        <v>-0.309</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.285</v>
+        <v>-0.319</v>
       </c>
     </row>
     <row r="22">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.040650463</v>
+        <v>-0.0607288</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>4.95</v>
@@ -1876,13 +1876,13 @@
         <v>2.02</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.521</v>
+        <v>-0.531</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.583</v>
+        <v>0.578</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
@@ -1890,22 +1890,22 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>-5.7804875</v>
+        <v>-5.6585364</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>12.657</v>
+        <v>12.539</v>
       </c>
       <c r="N22" s="7" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>1.327</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.43</v>
+        <v>-0.458</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.052</v>
+        <v>-0.07200000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -2292,34 +2292,34 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>53.48</v>
+        <v>52.93</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.010545785</v>
+        <v>-0.0207215</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.176</v>
+        <v>-0.184</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.273</v>
+        <v>0.289</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>54</v>
+        <v>54.1</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.066</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.038</v>
+        <v>-0.05</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.241</v>
+        <v>-0.249</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
       </c>
       <c r="M2" s="10" t="n">
-        <v>3657680</v>
+        <v>3958140</v>
       </c>
     </row>
     <row r="3">
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>104.79</v>
+        <v>104.81</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.015224159</v>
+        <v>-0.0150362</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>-0.52</v>
@@ -2351,13 +2351,13 @@
         <v>-0.5649999999999999</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-54.2</v>
+        <v>-54.8</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.293</v>
+        <v>-0.272</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.547</v>
+        <v>-0.544</v>
       </c>
       <c r="K3" s="5" t="n">
         <v>-0.6659999999999999</v>
@@ -2366,7 +2366,7 @@
         <v>1.177</v>
       </c>
       <c r="M3" s="10" t="n">
-        <v>3371670</v>
+        <v>3297370</v>
       </c>
     </row>
     <row r="4">
@@ -2386,34 +2386,34 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24.09</v>
+        <v>23.67</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.032918494</v>
+        <v>-0.0497792</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.324</v>
+        <v>-0.336</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.373</v>
+        <v>-0.401</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-34.8</v>
+        <v>-35</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.127</v>
+        <v>-0.128</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.327</v>
+        <v>-0.337</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.506</v>
+        <v>-0.515</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
       </c>
       <c r="M4" s="10" t="n">
-        <v>13953350</v>
+        <v>13781570</v>
       </c>
     </row>
     <row r="5">
@@ -2433,34 +2433,34 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>100.74</v>
+        <v>99.98</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-0.02345876</v>
+        <v>-0.0308259</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.176</v>
+        <v>-0.183</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.224</v>
+        <v>0.221</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.08900000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.118</v>
+        <v>-0.125</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.252</v>
+        <v>-0.258</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>1.034</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>2211770</v>
+        <v>2163700</v>
       </c>
     </row>
     <row r="6">
@@ -2480,34 +2480,34 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.22</v>
+        <v>35.37</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.024771087</v>
+        <v>-0.0476575</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.031</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.113</v>
+        <v>0.126</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.023</v>
+        <v>-0.002</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.031</v>
+        <v>0.006</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.098</v>
+        <v>-0.119</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>1.396</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>4843830</v>
+        <v>5265930</v>
       </c>
     </row>
     <row r="7">
@@ -2527,34 +2527,34 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>82.3</v>
+        <v>81.06</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-0.9149946</v>
+        <v>-0.024079</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0.043</v>
+        <v>-0.057</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.226</v>
+        <v>0.204</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.022</v>
+        <v>-0.034</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.021</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.099</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>1.22</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>918240</v>
+        <v>1090120</v>
       </c>
     </row>
     <row r="8">
@@ -2574,128 +2574,128 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.16</v>
+        <v>57.52</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.028390126</v>
+        <v>-0.0390912</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.058</v>
+        <v>-0.068</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.367</v>
+        <v>0.373</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.058</v>
+        <v>-0.067</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.02</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.157</v>
+        <v>-0.166</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>1.453</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>813400</v>
+        <v>941430</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>19.97</v>
+        <v>83.73</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.014220355</v>
+        <v>-0.0466811</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.144</v>
+        <v>-0.252</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.104</v>
+        <v>-0.25</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-26.7</v>
+        <v>-2.8</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.08199999999999999</v>
+        <v>-0.117</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.187</v>
+        <v>-0.171</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.38</v>
+        <v>-0.293</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>2.002</v>
+        <v>0.66</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>2197460</v>
+        <v>1091240</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>84.39</v>
+        <v>19.61</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.039223495</v>
+        <v>-0.406297</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.246</v>
+        <v>-0.159</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.244</v>
+        <v>-0.121</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-3</v>
+        <v>-27.3</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-0.119</v>
+        <v>0.067</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.2</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.288</v>
+        <v>-0.391</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.66</v>
+        <v>2.002</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>1211900</v>
+        <v>2485880</v>
       </c>
     </row>
     <row r="11">
@@ -2715,34 +2715,34 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>27.05</v>
+        <v>26.76</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-0.01439506</v>
+        <v>-0.0247814</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.148</v>
+        <v>0.136</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.043</v>
+        <v>-0.022</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>-23.4</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.161</v>
+        <v>0.141</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.143</v>
+        <v>-0.153</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>1.977</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>6401490</v>
+        <v>6358500</v>
       </c>
     </row>
     <row r="12">
@@ -2762,34 +2762,34 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.42</v>
+        <v>10.46</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.02251405</v>
+        <v>-0.0187617</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-0.101</v>
+        <v>-0.09699999999999999</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.506</v>
+        <v>0.545</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>29.2</v>
+        <v>28.7</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.035</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.275</v>
+        <v>-0.273</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>1.1</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>1869380</v>
+        <v>1926430</v>
       </c>
     </row>
     <row r="13">
@@ -2809,34 +2809,34 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.02</v>
+        <v>20.7</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-0.010593238</v>
+        <v>-0.0254237</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.9229999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.122</v>
+        <v>0.1</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.155</v>
+        <v>0.132</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>1498110</v>
+        <v>1505260</v>
       </c>
     </row>
     <row r="14">
@@ -2856,34 +2856,34 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.090964094</v>
+        <v>-0.7272719999999999</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.267</v>
+        <v>-0.273</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.013</v>
+        <v>-0.014</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.09699999999999999</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.3</v>
+        <v>-0.305</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-0.458</v>
+        <v>-0.462</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>0.603</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>1467500</v>
+        <v>1478700</v>
       </c>
     </row>
     <row r="15">
@@ -2903,34 +2903,34 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14.03</v>
+        <v>13.67</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-0.9180798999999999</v>
+        <v>-0.0346045</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.055</v>
+        <v>-0.079</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.182</v>
+        <v>-0.213</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-19</v>
+        <v>-19.2</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.017</v>
+        <v>-0.008</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.137</v>
+        <v>-0.159</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.319</v>
+        <v>-0.337</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>1.364</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>4104950</v>
+        <v>4084830</v>
       </c>
     </row>
     <row r="16">
@@ -2950,19 +2950,19 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>96.36</v>
+        <v>96.5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.012653695</v>
+        <v>-0.0112705</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.202</v>
+        <v>0.204</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0.017</v>
@@ -2971,13 +2971,13 @@
         <v>0.004</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.153</v>
       </c>
       <c r="L16" s="8" t="n">
         <v>1.376</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>132400</v>
+        <v>158160</v>
       </c>
     </row>
     <row r="17">
@@ -2997,34 +2997,34 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.62</v>
+        <v>4.53</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-0.017021261</v>
+        <v>-0.0361701</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-0.5710000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.54</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-29.4</v>
+        <v>-29.8</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.379</v>
+        <v>-0.371</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.55</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.664</v>
+        <v>-0.67</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.993</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>7512840</v>
+        <v>7109690</v>
       </c>
     </row>
     <row r="18">
@@ -3044,34 +3044,34 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>11</v>
+        <v>10.92</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.6323369</v>
+        <v>-0.0135501</v>
       </c>
       <c r="F18" s="5" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I18" s="5" t="n">
         <v>-0.033</v>
       </c>
-      <c r="G18" s="5" t="n">
-        <v>0.09699999999999999</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>-0.028</v>
-      </c>
       <c r="J18" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.025</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.174</v>
+        <v>-0.18</v>
       </c>
       <c r="L18" s="8" t="n">
         <v>1.07</v>
       </c>
       <c r="M18" s="10" t="n">
-        <v>512850</v>
+        <v>453170</v>
       </c>
     </row>
     <row r="19">
@@ -3091,34 +3091,34 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>26.62</v>
+        <v>26.2</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-0.021858902</v>
+        <v>-0.0374724</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.032</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.005</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.048</v>
+        <v>-0.062</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.025</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.187</v>
+        <v>-0.2</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.412</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>123770</v>
+        <v>143220</v>
       </c>
     </row>
     <row r="20">
@@ -3138,28 +3138,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.24</v>
+        <v>12.04</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.28664905</v>
+        <v>-0.013923</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.264</v>
+        <v>-0.276</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.283</v>
+        <v>-0.34</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>36.7</v>
+        <v>37.8</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.168</v>
+        <v>-0.171</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.077</v>
+        <v>-0.094</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.41</v>
+        <v>-0.419</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="M20" s="10" t="n">
-        <v>117850</v>
+        <v>107850</v>
       </c>
     </row>
     <row r="21">
@@ -3187,34 +3187,34 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.42</v>
+        <v>6.11</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-0.02061072</v>
+        <v>-0.0671756</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.285</v>
+        <v>-0.319</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.295</v>
+        <v>-0.309</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.244</v>
+        <v>-0.271</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.252</v>
+        <v>-0.286</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.355</v>
+        <v>-0.386</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>1.206</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>200300</v>
+        <v>226360</v>
       </c>
     </row>
     <row r="22">
@@ -3234,34 +3234,34 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.040650463</v>
+        <v>-0.0607288</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.43</v>
+        <v>-0.458</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>-53</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.022</v>
+        <v>-0.039</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.233</v>
+        <v>-0.247</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.521</v>
+        <v>-0.531</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.327</v>
       </c>
       <c r="M22" s="10" t="n">
-        <v>164910</v>
+        <v>112720</v>
       </c>
     </row>
     <row r="23">
@@ -3338,7 +3338,7 @@
         <v>-0.239</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>-291.2</v>
+        <v>-293.6</v>
       </c>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
@@ -3570,34 +3570,34 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>53.48</v>
+        <v>52.93</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>36.16</v>
+        <v>35.788</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>22.757448</v>
+        <v>23.013044</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.232716</v>
+        <v>14.086344</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>10.777</v>
+        <v>10.611</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>3.753</v>
+        <v>3.695</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.699492</v>
+        <v>22.466045</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.7778807</v>
+        <v>2.7493122</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>3.75754</v>
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>104.79</v>
+        <v>104.81</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.385</v>
+        <v>18.372</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3634,25 +3634,25 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.702624999999999</v>
+        <v>9.704476</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>14.228</v>
+        <v>14.097</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.852</v>
+        <v>1.834</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.0316014</v>
+        <v>2.031989</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1222284</v>
+        <v>1.1214118</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.72</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>10.80017</v>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24.09</v>
+        <v>23.67</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.991</v>
+        <v>11.782</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3689,22 +3689,22 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>12.377331</v>
+        <v>12.161537</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>47.796</v>
+        <v>45.556</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>2.154</v>
+        <v>2.053</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>18.87931</v>
+        <v>18.550156</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.9805584</v>
+        <v>1.946028</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3733,34 +3733,34 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>100.74</v>
+        <v>99.98</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.505</v>
+        <v>10.426</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.0828</v>
+        <v>32.88816</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>16.954544</v>
+        <v>16.826635</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>11.473</v>
+        <v>11.288</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>2.812</v>
+        <v>2.767</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-37.477676</v>
+        <v>-37.194942</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.4717863</v>
+        <v>1.4606829</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>5.94177</v>
@@ -3786,34 +3786,34 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.22</v>
+        <v>35.37</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9.906000000000001</v>
+        <v>9.673999999999999</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>47.657898</v>
+        <v>48.452053</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>15.434572</v>
+        <v>15.072357</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>16.831</v>
+        <v>16.638</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>2.26</v>
+        <v>2.234</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.8503246</v>
+        <v>3.7599661</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.56486386</v>
+        <v>0.5516078</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>2.34668</v>
@@ -3839,34 +3839,34 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>82.3</v>
+        <v>81.06</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.213</v>
+        <v>6.119</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.6480498</v>
+        <v>3.6811988</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.10137</v>
+        <v>9.949173</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>7.184</v>
+        <v>7.058</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>2.108</v>
+        <v>2.071</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.4094622</v>
+        <v>2.3731592</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5183347</v>
+        <v>1.4954581</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>22.56</v>
+        <v>22.02</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>8.147410000000001</v>
@@ -3892,34 +3892,34 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.16</v>
+        <v>57.52</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>5.98</v>
+        <v>5.915</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>18.641026</v>
+        <v>19.173334</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>17.699707</v>
+        <v>17.504938</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>8.541</v>
+        <v>8.374000000000001</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>3.456</v>
+        <v>3.388</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.282194</v>
+        <v>16.103024</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.973136</v>
+        <v>2.940419</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>3.28593</v>
@@ -3931,107 +3931,107 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>19.97</v>
+        <v>83.73</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.91</v>
+        <v>5.836</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>55.472218</v>
+        <v>16.613096</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>24.552261</v>
+        <v>11.276708</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>11.056</v>
+        <v>11.373</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>9.6</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>4.35</v>
+        <v>3.719</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>5.347088</v>
+        <v>5.7716966</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>4.581639</v>
+        <v>1.9944898</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.36</v>
+        <v>5.04</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.813367</v>
+        <v>7.42504</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>3.734743</v>
+        <v>14.507</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>84.39</v>
+        <v>19.61</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.881</v>
+        <v>5.804</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>15.951797</v>
+        <v>54.47222</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>11.364923</v>
+        <v>23.874111</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>11.669</v>
+        <v>11.021</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>3.816</v>
+        <v>4.336</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.8168473</v>
+        <v>5.199397</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>2.010092</v>
+        <v>4.499046</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>5.29</v>
+        <v>0.36</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>7.42504</v>
+        <v>0.8213919</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>14.507</v>
+        <v>3.7715912</v>
       </c>
     </row>
     <row r="11">
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>27.05</v>
+        <v>26.76</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.52</v>
+        <v>5.462</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -4062,25 +4062,25 @@
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>29.237837</v>
+        <v>28.92973</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>8.727</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>7.3</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>2.656</v>
+        <v>2.643</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>1.5639277</v>
+        <v>1.547447</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.4805937</v>
+        <v>0.4755292</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-2.42</v>
+        <v>-2.36</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>0.925</v>
@@ -4106,31 +4106,31 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.42</v>
+        <v>10.46</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.269</v>
+        <v>5.289</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>24.809525</v>
+        <v>24.904762</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>12.0127735</v>
+        <v>12.0588875</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10.154</v>
+        <v>9.948</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>2.127</v>
+        <v>2.084</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>7.0739985</v>
+        <v>7.101154</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>2.2488015</v>
+        <v>2.257434</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0.42</v>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.02</v>
+        <v>20.7</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4.892</v>
+        <v>4.819</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>67.79031999999999</v>
+        <v>69</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>28.08253</v>
+        <v>27.661594</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -4186,13 +4186,13 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>14.266802</v>
+        <v>14.052953</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.312277</v>
+        <v>4.2476387</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>0.7483300000000001</v>
@@ -4218,31 +4218,31 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.239</v>
+        <v>2.221</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>11.967391</v>
+        <v>11.869565</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>6.9193935</v>
+        <v>6.8628316</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>10.611</v>
+        <v>10.572</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>8.4</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>2.479</v>
+        <v>2.47</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>-1.7251645</v>
+        <v>-1.7110624</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.43371302</v>
+        <v>0.4301677</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0.46</v>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14.03</v>
+        <v>13.67</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1.874</v>
+        <v>1.826</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4282,22 +4282,22 @@
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>8.060763</v>
+        <v>7.8539295</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>17.135</v>
+        <v>17.051</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.778</v>
+        <v>1.769</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.96578777</v>
+        <v>0.94100636</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.2691645</v>
+        <v>0.26225796</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>-5.83</v>
@@ -4326,34 +4326,34 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>96.36</v>
+        <v>96.5</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.724</v>
+        <v>1.726</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>17.746777</v>
+        <v>17.970205</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>16.20942</v>
+        <v>16.232128</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>8.717000000000001</v>
+        <v>8.614000000000001</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>7.4</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>3.05</v>
+        <v>3.014</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>3.1936436</v>
+        <v>3.1981175</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>3.1618361</v>
+        <v>3.1662657</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>5.43</v>
+        <v>5.37</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>5.945</v>
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.62</v>
+        <v>4.53</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.138</v>
+        <v>1.165</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4.6666665</v>
+        <v>4.575758</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-7.528</v>
+        <v>-7.181</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -4401,16 +4401,16 @@
         </is>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.356</v>
+        <v>1.293</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>1.5708942</v>
+        <v>1.5402925</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>1.6997067</v>
+        <v>1.740646</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.42</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0.99</v>
@@ -4436,31 +4436,31 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>11</v>
+        <v>10.92</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.915</v>
+        <v>0.909</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>18.333332</v>
+        <v>18.199999</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>11.878665</v>
+        <v>11.792274</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>6.487</v>
+        <v>6.422</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.922</v>
+        <v>0.912</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>3.3567288</v>
+        <v>3.3323162</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.6876896</v>
+        <v>0.6826883</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>0.6</v>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>26.62</v>
+        <v>26.2</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.703</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
@@ -4500,25 +4500,25 @@
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>22.004131</v>
+        <v>21.652893</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>9.632999999999999</v>
+        <v>9.414</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.852</v>
+        <v>1.81</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>1.6564018</v>
+        <v>1.6299615</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>1.1070344</v>
+        <v>1.0893636</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>1.21</v>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.24</v>
+        <v>12.04</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.602</v>
+        <v>0.592</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -4555,25 +4555,25 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>-8.218121</v>
+        <v>-8.080537</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>18.869</v>
+        <v>18.843</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>12.9</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>2.45</v>
+        <v>2.447</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.1535563</v>
+        <v>1.134244</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.24168485</v>
+        <v>0.2376387</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-12.75</v>
+        <v>-12.58</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-1.49</v>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.42</v>
+        <v>6.11</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.174</v>
+        <v>0.165</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -4610,22 +4610,22 @@
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>8.562923</v>
+        <v>8.155802</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>6.836</v>
+        <v>6.676</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.67</v>
+        <v>1.631</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>-10.638474</v>
+        <v>-10.13267</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.5708226</v>
+        <v>0.54368293</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>-0.58</v>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -4665,25 +4665,25 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>-5.7804875</v>
+        <v>-5.6585364</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>12.657</v>
+        <v>12.539</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.929</v>
+        <v>1.911</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>33.85714</v>
+        <v>33.142857</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.28311753</v>
+        <v>0.27761704</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.05</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>-0.41</v>
@@ -5525,119 +5525,119 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1.29</v>
+        <v>2.926</v>
       </c>
       <c r="E9" s="5" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.18802</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.32698002</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0.06236</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>5.197</v>
+      </c>
+      <c r="O9" s="6" t="n">
         <v>0.201</v>
       </c>
-      <c r="F9" s="5" t="n">
-        <v>0.26816</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0.15614</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>0.07777000000000001</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>0.39339</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>0.10515001</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>0.04121</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="O9" s="6" t="n">
-        <v>0.365</v>
-      </c>
       <c r="P9" s="7" t="n">
-        <v>6.424</v>
+        <v>492.233</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>1.167</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2.926</v>
+        <v>1.29</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.067</v>
+        <v>0.201</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.33583</v>
+        <v>0.26816</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.18802</v>
+        <v>0.15614</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.1309</v>
+        <v>0.07777000000000001</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.32698002</v>
+        <v>0.39339</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.35709</v>
+        <v>0.10515001</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.06236</v>
+        <v>0.04121</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.957</v>
+        <v>0.507</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.082</v>
+        <v>0.341</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>5.197</v>
+        <v>0.063</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.201</v>
+        <v>0.365</v>
       </c>
       <c r="P10" s="7" t="n">
-        <v>492.233</v>
+        <v>6.424</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>0.604</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="11">
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>53.48</v>
+        <v>52.93</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>58</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>0.307</v>
+        <v>0.32</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>1.8</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>104.79</v>
+        <v>104.81</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>24.09</v>
+        <v>23.67</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.499</v>
+        <v>0.526</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>100.74</v>
+        <v>99.98</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.408</v>
+        <v>0.419</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.24</v>
@@ -7067,7 +7067,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>36.22</v>
+        <v>35.37</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.178</v>
+        <v>0.206</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.2</v>
@@ -7125,7 +7125,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>82.3</v>
+        <v>81.06</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>84</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.148</v>
+        <v>0.165</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.32</v>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>58.16</v>
+        <v>57.52</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>59</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.261</v>
+        <v>0.275</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>3.89</v>
@@ -7228,16 +7228,16 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>19.97</v>
+        <v>83.73</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -7245,57 +7245,55 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1.33333</v>
+        <v>1.25</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>28.806065</v>
+        <v>135.5</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>37.152924</v>
+        <v>152</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>21.913837</v>
+        <v>110</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.442</v>
+        <v>0.618</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>4.19</v>
+        <v>2.68</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.1088</v>
+        <v>0.044499997</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.01337</v>
+        <v>0.06136</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0.91643</v>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.81711</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>84.39</v>
+        <v>19.61</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -7303,40 +7301,42 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1.25</v>
+        <v>1.33333</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>135.5</v>
+        <v>28.87972</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>152</v>
+        <v>37.234634</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>110</v>
+        <v>21.962032</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.606</v>
+        <v>0.473</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>2.68</v>
+        <v>4.19</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.044499997</v>
+        <v>0.1088</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>0.06136</v>
+        <v>0.01337</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0.81711</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>0.5</v>
+        <v>0.91643</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.0828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>27.05</v>
+        <v>26.76</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>22</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.181</v>
+        <v>0.194</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>3.8</v>
@@ -7409,17 +7409,15 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>10.42</v>
+        <v>10.46</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>strong_buy</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1.25</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>8</v>
@@ -7434,7 +7432,7 @@
         <v>16</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.667</v>
+        <v>0.6609999999999999</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>4.92</v>
@@ -7467,7 +7465,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>21.02</v>
+        <v>20.7</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -7490,7 +7488,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.18</v>
+        <v>0.198</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.71</v>
@@ -7525,7 +7523,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -7533,22 +7531,22 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1.78571</v>
+        <v>1.84615</v>
       </c>
       <c r="F14" s="10" t="n">
         <v>13</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>9.442310000000001</v>
+        <v>9.27308</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.7170000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>2.08</v>
@@ -7583,7 +7581,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>14.03</v>
+        <v>13.67</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7606,7 +7604,7 @@
         <v>15</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.362</v>
+        <v>0.398</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>4.18</v>
@@ -7641,7 +7639,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>96.36</v>
+        <v>96.5</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7666,7 +7664,7 @@
         <v>93</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.117</v>
+        <v>0.116</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>2.53</v>
@@ -7699,7 +7697,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4.62</v>
+        <v>4.53</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7722,7 +7720,7 @@
         <v>6</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1.546</v>
+        <v>1.597</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>1.77</v>
@@ -7757,7 +7755,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>11</v>
+        <v>10.92</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -7780,7 +7778,7 @@
         <v>14</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.409</v>
+        <v>0.419</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>3.68</v>
@@ -7815,7 +7813,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>26.62</v>
+        <v>26.2</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7838,7 +7836,7 @@
         <v>30</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.146</v>
+        <v>0.164</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>2.5</v>
@@ -7871,7 +7869,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>12.24</v>
+        <v>12.04</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7894,7 +7892,7 @@
         <v>11</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.28</v>
+        <v>0.301</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>9.16</v>
@@ -7929,7 +7927,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>6.42</v>
+        <v>6.11</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -7952,7 +7950,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.077</v>
+        <v>1.182</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>13.9</v>
@@ -7987,7 +7985,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -8010,7 +8008,7 @@
         <v>2.5</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.371</v>
+        <v>0.401</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>5.72</v>
@@ -8463,10 +8461,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>36.16</v>
+        <v>35.788</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>22.757448</v>
+        <v>23.013044</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -8478,13 +8476,13 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.176</v>
+        <v>-0.184</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>10.777</v>
+        <v>10.611</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>82</v>
@@ -8507,7 +8505,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.52</v>
+        <v>5.462</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -8524,10 +8522,10 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.148</v>
+        <v>0.136</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>8.727</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>7.3</v>
@@ -8553,10 +8551,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>10.505</v>
+        <v>10.426</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>32.0828</v>
+        <v>32.88816</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.015</v>
@@ -8570,13 +8568,13 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.176</v>
+        <v>-0.183</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>11.473</v>
+        <v>11.288</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="L5" s="7" t="n">
         <v>41.7</v>
@@ -8599,10 +8597,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2.239</v>
+        <v>2.221</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>11.967391</v>
+        <v>11.869565</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -8616,10 +8614,10 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-0.267</v>
+        <v>-0.273</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>10.611</v>
+        <v>10.572</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>8.4</v>
@@ -8645,10 +8643,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>9.906000000000001</v>
+        <v>9.673999999999999</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>47.657898</v>
+        <v>48.452053</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.06</v>
@@ -8660,13 +8658,13 @@
         <v>0.1489</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.031</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>16.831</v>
+        <v>16.638</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="L7" s="7" t="n">
         <v>37.5</v>
@@ -8707,10 +8705,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.213</v>
+        <v>6.119</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.6480498</v>
+        <v>3.6811988</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -8722,13 +8720,13 @@
         <v>0.87788004</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-0.043</v>
+        <v>-0.057</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.184</v>
+        <v>7.058</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L10" s="7" t="n">
         <v>71.40000000000001</v>
@@ -8751,10 +8749,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5.881</v>
+        <v>5.836</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>15.951797</v>
+        <v>16.613096</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.067</v>
@@ -8766,13 +8764,13 @@
         <v>0.35709</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>-0.246</v>
+        <v>-0.252</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>11.669</v>
+        <v>11.373</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="L11" s="7" t="n">
         <v>63.5</v>
@@ -8795,10 +8793,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1.724</v>
+        <v>1.726</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>17.746777</v>
+        <v>17.970205</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.041</v>
@@ -8810,10 +8808,10 @@
         <v>0.19214001</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>8.717000000000001</v>
+        <v>8.614000000000001</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>7.4</v>
@@ -8839,10 +8837,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5.98</v>
+        <v>5.915</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.641026</v>
+        <v>19.173334</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8854,16 +8852,16 @@
         <v>1.113</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.058</v>
+        <v>-0.068</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>8.541</v>
+        <v>8.374000000000001</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>57.1</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="14">
@@ -8883,7 +8881,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.874</v>
+        <v>1.826</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8900,16 +8898,16 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.055</v>
+        <v>-0.079</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>17.135</v>
+        <v>17.051</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>45.7</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="15">
@@ -8929,7 +8927,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.703</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -8946,13 +8944,13 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.032</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>9.632999999999999</v>
+        <v>9.414</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="L15" s="7" t="n">
         <v>40</v>
@@ -8975,7 +8973,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -8992,16 +8990,16 @@
         <v>-1.8681101</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>12.657</v>
+        <v>12.539</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>25.7</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="17">
@@ -9021,7 +9019,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.602</v>
+        <v>0.592</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -9038,10 +9036,10 @@
         <v>-1.1563</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.264</v>
+        <v>-0.276</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>18.869</v>
+        <v>18.843</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>12.9</v>
@@ -9085,10 +9083,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.269</v>
+        <v>5.289</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>24.809525</v>
+        <v>24.904762</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -9100,13 +9098,13 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.101</v>
+        <v>-0.09699999999999999</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>10.154</v>
+        <v>9.948</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="L20" s="7" t="n">
         <v>66.7</v>
@@ -9129,10 +9127,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.91</v>
+        <v>5.804</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>55.472218</v>
+        <v>54.47222</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -9144,10 +9142,10 @@
         <v>0.10515001</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.144</v>
+        <v>-0.159</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>11.056</v>
+        <v>11.021</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>9.6</v>
@@ -9173,10 +9171,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4.892</v>
+        <v>4.819</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>67.79031999999999</v>
+        <v>69</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -9188,7 +9186,7 @@
         <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
@@ -9221,7 +9219,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>11.991</v>
+        <v>11.782</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -9238,13 +9236,13 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.324</v>
+        <v>-0.336</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>47.796</v>
+        <v>45.556</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="L23" s="7" t="n">
         <v>52</v>
@@ -9267,7 +9265,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.385</v>
+        <v>18.372</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -9287,10 +9285,10 @@
         <v>-0.52</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>14.228</v>
+        <v>14.097</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="L24" s="7" t="n">
         <v>48</v>
@@ -9313,7 +9311,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.138</v>
+        <v>1.165</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -9330,10 +9328,10 @@
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.5710000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>-7.528</v>
+        <v>-7.181</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
@@ -9435,10 +9433,10 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.915</v>
+        <v>0.909</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>18.333332</v>
+        <v>18.199999</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>0.075</v>
@@ -9450,13 +9448,13 @@
         <v>0.19236</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.033</v>
+        <v>-0.04</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>6.487</v>
+        <v>6.422</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L29" s="7" t="n">
         <v>56.7</v>
@@ -9535,7 +9533,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.174</v>
+        <v>0.165</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -9554,13 +9552,13 @@
         </is>
       </c>
       <c r="I31" s="5" t="n">
-        <v>-0.285</v>
+        <v>-0.319</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>6.836</v>
+        <v>6.676</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L31" s="7" t="n">
         <v>45</v>
@@ -10570,55 +10568,55 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.01337</v>
+        <v>0.06136</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.91643</v>
+        <v>0.81711</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>4.19</v>
+        <v>2.68</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.1088</v>
+        <v>0.044499997</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>11183802</v>
+        <v>2574942</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.06136</v>
+        <v>0.01337</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.81711</v>
+        <v>0.91643</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2.68</v>
+        <v>4.19</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.044499997</v>
+        <v>0.1088</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2574942</v>
+        <v>11183802</v>
       </c>
     </row>
     <row r="11">
@@ -11143,13 +11141,13 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1272.49</v>
+        <v>1286.26</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>1230.86</v>
+        <v>1230.45</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>1068.94</v>
+        <v>1074.91</v>
       </c>
     </row>
     <row r="3">
@@ -11159,13 +11157,13 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1272.41</v>
+        <v>1286.2</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1235.19</v>
+        <v>1234.78</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>1071.29</v>
+        <v>1077.26</v>
       </c>
     </row>
     <row r="4">
@@ -11175,13 +11173,13 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1278.47</v>
+        <v>1292.25</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1235.06</v>
+        <v>1234.66</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>1072.07</v>
+        <v>1078.05</v>
       </c>
     </row>
     <row r="5">
@@ -11191,13 +11189,13 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1268.25</v>
+        <v>1281.91</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1230.66</v>
+        <v>1230.26</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1064.51</v>
+        <v>1070.45</v>
       </c>
     </row>
     <row r="6">
@@ -11207,13 +11205,13 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1263.39</v>
+        <v>1276.85</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1229.16</v>
+        <v>1228.75</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1062.69</v>
+        <v>1068.61</v>
       </c>
     </row>
     <row r="7">
@@ -11223,13 +11221,13 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1255.76</v>
+        <v>1269.24</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1220.05</v>
+        <v>1219.65</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1065.29</v>
+        <v>1071.24</v>
       </c>
     </row>
     <row r="8">
@@ -11239,13 +11237,13 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1261.15</v>
+        <v>1274.55</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1222.29</v>
+        <v>1221.89</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1066.33</v>
+        <v>1072.28</v>
       </c>
     </row>
     <row r="9">
@@ -11255,13 +11253,13 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1261.92</v>
+        <v>1275.17</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1230.43</v>
+        <v>1230.02</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1064.25</v>
+        <v>1070.19</v>
       </c>
     </row>
     <row r="10">
@@ -11271,13 +11269,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1246.35</v>
+        <v>1259.54</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1237.75</v>
+        <v>1237.34</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1057.73</v>
+        <v>1063.63</v>
       </c>
     </row>
     <row r="11">
@@ -11287,13 +11285,13 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1199.5</v>
+        <v>1211.99</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>1233.76</v>
+        <v>1233.35</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1038.44</v>
+        <v>1044.24</v>
       </c>
     </row>
     <row r="12">
@@ -11303,13 +11301,13 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1224.57</v>
+        <v>1237.25</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1233.63</v>
+        <v>1233.23</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1055.65</v>
+        <v>1061.54</v>
       </c>
     </row>
     <row r="13">
@@ -11319,13 +11317,13 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1196.22</v>
+        <v>1208.45</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1241.79</v>
+        <v>1241.38</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>1048.09</v>
+        <v>1053.94</v>
       </c>
     </row>
     <row r="14">
@@ -11335,13 +11333,13 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1191.64</v>
+        <v>1203.95</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1243.74</v>
+        <v>1243.33</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>1043.92</v>
+        <v>1049.74</v>
       </c>
     </row>
     <row r="15">
@@ -11351,13 +11349,13 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1183.88</v>
+        <v>1196.19</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1241.25</v>
+        <v>1240.85</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1031.67</v>
+        <v>1037.42</v>
       </c>
     </row>
     <row r="16">
@@ -11367,13 +11365,13 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1181.68</v>
+        <v>1193.91</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1235.15</v>
+        <v>1234.75</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1034.27</v>
+        <v>1040.04</v>
       </c>
     </row>
     <row r="17">
@@ -11383,13 +11381,13 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1200.97</v>
+        <v>1213.3</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1238.52</v>
+        <v>1238.11</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>1045.74</v>
+        <v>1051.58</v>
       </c>
     </row>
     <row r="18">
@@ -11399,13 +11397,13 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1164.07</v>
+        <v>1176.22</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1237.48</v>
+        <v>1237.07</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1025.41</v>
+        <v>1031.13</v>
       </c>
     </row>
     <row r="19">
@@ -11415,13 +11413,13 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1140.49</v>
+        <v>1152.41</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>1212.29</v>
+        <v>1211.89</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>1008.73</v>
+        <v>1014.36</v>
       </c>
     </row>
     <row r="20">
@@ -11431,13 +11429,13 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1146.66</v>
+        <v>1158.88</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1226.28</v>
+        <v>1225.88</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1010.55</v>
+        <v>1016.19</v>
       </c>
     </row>
     <row r="21">
@@ -11447,13 +11445,13 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1151.63</v>
+        <v>1163.97</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1232.68</v>
+        <v>1232.28</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>1018.63</v>
+        <v>1024.32</v>
       </c>
     </row>
     <row r="22">
@@ -11463,13 +11461,13 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1135.9</v>
+        <v>1148.26</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1233.13</v>
+        <v>1232.73</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1011.6</v>
+        <v>1017.24</v>
       </c>
     </row>
     <row r="23">
@@ -11479,13 +11477,13 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1141.6</v>
+        <v>1154.02</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>1239.39</v>
+        <v>1238.99</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>1017.33</v>
+        <v>1023.01</v>
       </c>
     </row>
     <row r="24">
@@ -11495,13 +11493,13 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1128.39</v>
+        <v>1140.68</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>1244.33</v>
+        <v>1243.92</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1013.68</v>
+        <v>1019.34</v>
       </c>
     </row>
     <row r="25">
@@ -11511,13 +11509,13 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1130.26</v>
+        <v>1142.68</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>1244.21</v>
+        <v>1243.8</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>1005.86</v>
+        <v>1011.48</v>
       </c>
     </row>
     <row r="26">
@@ -11527,13 +11525,13 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1079.54</v>
+        <v>1090.78</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>1241.74</v>
+        <v>1241.33</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>989.4400000000001</v>
+        <v>994.96</v>
       </c>
     </row>
     <row r="27">
@@ -11543,13 +11541,13 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1066.63</v>
+        <v>1077.92</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>1238.03</v>
+        <v>1237.63</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>968.0700000000001</v>
+        <v>973.47</v>
       </c>
     </row>
     <row r="28">
@@ -11559,13 +11557,13 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1084.35</v>
+        <v>1096.04</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>1244.19</v>
+        <v>1243.78</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>977.45</v>
+        <v>982.91</v>
       </c>
     </row>
     <row r="29">
@@ -11575,13 +11573,13 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1080.55</v>
+        <v>1092.43</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1233.67</v>
+        <v>1233.26</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>966.5</v>
+        <v>971.9</v>
       </c>
     </row>
     <row r="30">
@@ -11591,13 +11589,13 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1101.57</v>
+        <v>1113.71</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>1227.69</v>
+        <v>1227.29</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>987.88</v>
+        <v>993.39</v>
       </c>
     </row>
     <row r="31">
@@ -11607,13 +11605,13 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1076.51</v>
+        <v>1088.55</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>1212.36</v>
+        <v>1211.96</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>968.59</v>
+        <v>973.99</v>
       </c>
     </row>
     <row r="32">
@@ -11623,13 +11621,13 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1103.52</v>
+        <v>1115.8</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>1235.62</v>
+        <v>1235.21</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>986.84</v>
+        <v>992.34</v>
       </c>
     </row>
     <row r="33">
@@ -11639,13 +11637,13 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1105.66</v>
+        <v>1117.9</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>1241.58</v>
+        <v>1241.17</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>994.13</v>
+        <v>999.6799999999999</v>
       </c>
     </row>
     <row r="34">
@@ -11655,13 +11653,13 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1102.58</v>
+        <v>1114.71</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>1238.3</v>
+        <v>1237.89</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>995.96</v>
+        <v>1001.51</v>
       </c>
     </row>
     <row r="35">
@@ -11671,13 +11669,13 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1087.52</v>
+        <v>1099.59</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>1238.02</v>
+        <v>1237.61</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>988.4</v>
+        <v>993.91</v>
       </c>
     </row>
     <row r="36">
@@ -11687,13 +11685,13 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1050.74</v>
+        <v>1062.6</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>1218.89</v>
+        <v>1218.49</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>953.99</v>
+        <v>959.3200000000001</v>
       </c>
     </row>
     <row r="37">
@@ -11703,13 +11701,13 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1040.57</v>
+        <v>1052.71</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>1219.75</v>
+        <v>1219.35</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>941.74</v>
+        <v>947</v>
       </c>
     </row>
     <row r="38">
@@ -11719,13 +11717,13 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1055.74</v>
+        <v>1068.01</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>1221.72</v>
+        <v>1221.31</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>943.5700000000001</v>
+        <v>948.83</v>
       </c>
     </row>
     <row r="39">
@@ -11735,13 +11733,13 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1089.36</v>
+        <v>1102</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>1227.87</v>
+        <v>1227.47</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>969.11</v>
+        <v>974.52</v>
       </c>
     </row>
     <row r="40">
@@ -11751,13 +11749,13 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1084.28</v>
+        <v>1096.86</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>1224.63</v>
+        <v>1224.23</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>964.42</v>
+        <v>969.8</v>
       </c>
     </row>
     <row r="41">
@@ -11767,13 +11765,13 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1084.48</v>
+        <v>1097.1</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>1233.49</v>
+        <v>1233.08</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>962.0700000000001</v>
+        <v>967.4400000000001</v>
       </c>
     </row>
     <row r="42">
@@ -11783,13 +11781,13 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1041.42</v>
+        <v>1053.44</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>1220.89</v>
+        <v>1220.49</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>940.4400000000001</v>
+        <v>945.6900000000001</v>
       </c>
     </row>
     <row r="43">
@@ -11799,13 +11797,13 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1055.67</v>
+        <v>1067.81</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>1229.77</v>
+        <v>1229.36</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>948.52</v>
+        <v>953.8099999999999</v>
       </c>
     </row>
     <row r="44">
@@ -11815,13 +11813,13 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1059.6</v>
+        <v>1071.76</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>1240.15</v>
+        <v>1239.74</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>949.8200000000001</v>
+        <v>955.12</v>
       </c>
     </row>
     <row r="45">
@@ -11831,13 +11829,13 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1088.98</v>
+        <v>1101.52</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>1233.26</v>
+        <v>1232.85</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>952.17</v>
+        <v>957.48</v>
       </c>
     </row>
     <row r="46">
@@ -11847,13 +11845,13 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1076.12</v>
+        <v>1088.52</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>1227.34</v>
+        <v>1226.93</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>956.34</v>
+        <v>961.67</v>
       </c>
     </row>
     <row r="47">
@@ -11863,13 +11861,13 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1071.27</v>
+        <v>1083.59</v>
       </c>
       <c r="C47" s="13" t="n">
-        <v>1228.03</v>
+        <v>1227.63</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>947.74</v>
+        <v>953.02</v>
       </c>
     </row>
     <row r="48">
@@ -11879,13 +11877,13 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1067.19</v>
+        <v>1079.45</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>1217.21</v>
+        <v>1216.81</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>941.22</v>
+        <v>946.47</v>
       </c>
     </row>
     <row r="49">
@@ -11895,13 +11893,13 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1083.01</v>
+        <v>1095.38</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>1225.8</v>
+        <v>1225.39</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>946.96</v>
+        <v>952.24</v>
       </c>
     </row>
     <row r="50">
@@ -11911,13 +11909,13 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1080.92</v>
+        <v>1093.13</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>1218.96</v>
+        <v>1218.56</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>940.96</v>
+        <v>946.21</v>
       </c>
     </row>
     <row r="51">
@@ -11927,13 +11925,13 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1049.4</v>
+        <v>1061.18</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>1202.98</v>
+        <v>1202.59</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>931.3200000000001</v>
+        <v>936.51</v>
       </c>
     </row>
     <row r="52">
@@ -11943,13 +11941,13 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1051</v>
+        <v>1062.83</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>1213.52</v>
+        <v>1213.12</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>933.4</v>
+        <v>938.61</v>
       </c>
     </row>
     <row r="53">
@@ -11959,13 +11957,13 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1050.24</v>
+        <v>1062.16</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>1211.57</v>
+        <v>1211.17</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>931.58</v>
+        <v>936.77</v>
       </c>
     </row>
     <row r="54">
@@ -11975,13 +11973,13 @@
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1064.68</v>
+        <v>1076.79</v>
       </c>
       <c r="C54" s="13" t="n">
-        <v>1210.05</v>
+        <v>1209.65</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>936.01</v>
+        <v>941.23</v>
       </c>
     </row>
     <row r="55">
@@ -11991,13 +11989,13 @@
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1051.08</v>
+        <v>1062.96</v>
       </c>
       <c r="C55" s="13" t="n">
-        <v>1191.68</v>
+        <v>1191.28</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>924.8</v>
+        <v>929.96</v>
       </c>
     </row>
     <row r="56">
@@ -12007,13 +12005,13 @@
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1053.04</v>
+        <v>1064.93</v>
       </c>
       <c r="C56" s="13" t="n">
-        <v>1184.93</v>
+        <v>1184.54</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>922.71</v>
+        <v>927.86</v>
       </c>
     </row>
     <row r="57">
@@ -12023,13 +12021,13 @@
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1045.06</v>
+        <v>1056.95</v>
       </c>
       <c r="C57" s="13" t="n">
-        <v>1196.99</v>
+        <v>1196.6</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>919.85</v>
+        <v>924.98</v>
       </c>
     </row>
     <row r="58">
@@ -12039,13 +12037,13 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1057.56</v>
+        <v>1069.59</v>
       </c>
       <c r="C58" s="13" t="n">
-        <v>1200.14</v>
+        <v>1199.74</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>919.0700000000001</v>
+        <v>924.1900000000001</v>
       </c>
     </row>
     <row r="59">
@@ -12055,13 +12053,13 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1049.74</v>
+        <v>1061.65</v>
       </c>
       <c r="C59" s="13" t="n">
-        <v>1183.39</v>
+        <v>1183</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>908.9</v>
+        <v>913.97</v>
       </c>
     </row>
     <row r="60">
@@ -12071,13 +12069,13 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1062.28</v>
+        <v>1074.29</v>
       </c>
       <c r="C60" s="13" t="n">
-        <v>1180.48</v>
+        <v>1180.09</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>915.9400000000001</v>
+        <v>921.05</v>
       </c>
     </row>
     <row r="61">
@@ -12087,7 +12085,7 @@
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1045.5</v>
+        <v>1045.61</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -12099,7 +12097,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1045.5</v>
+        <v>1045.61</v>
       </c>
     </row>
     <row r="64">
@@ -12110,7 +12108,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-17.10%</t>
+          <t>-17.96%</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12129,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>136.1</v>
+        <v>134.7</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -679,7 +679,7 @@
         <v>48.099</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.013044</v>
+        <v>22.523405</v>
       </c>
       <c r="L2" s="7" t="n">
         <v>14.086344</v>
@@ -857,16 +857,16 @@
         <v>10.426</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>19.75</v>
+        <v>19.746</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.88816</v>
+        <v>31.840765</v>
       </c>
       <c r="L5" s="7" t="n">
         <v>16.826635</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>11.288</v>
+        <v>11.286</v>
       </c>
       <c r="N5" s="7" t="n">
         <v>9.1</v>
@@ -919,10 +919,10 @@
         <v>39.176</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>48.452053</v>
+        <v>46.539474</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>15.072357</v>
+        <v>15.095321</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>16.638</v>
@@ -978,7 +978,7 @@
         <v>8.476000000000001</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.6811988</v>
+        <v>3.593085</v>
       </c>
       <c r="L7" s="7" t="n">
         <v>9.949173</v>
@@ -1034,16 +1034,16 @@
         <v>5.915</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>6.815</v>
+        <v>6.814</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>19.173334</v>
+        <v>18.435898</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>17.504938</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>8.374000000000001</v>
+        <v>8.372999999999999</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>7.3</v>
@@ -1093,16 +1093,16 @@
         <v>5.836</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>10.88</v>
+        <v>10.878</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.613096</v>
+        <v>15.827978</v>
       </c>
       <c r="L9" s="7" t="n">
         <v>11.276708</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>11.373</v>
+        <v>11.371</v>
       </c>
       <c r="N9" s="7" t="n">
         <v>9.6</v>
@@ -1137,7 +1137,7 @@
         <v>19.61</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.406297</v>
+        <v>-0.4062972000000001</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>32.22</v>
@@ -1152,7 +1152,7 @@
         <v>5.804</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>5.593</v>
+        <v>5.587</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>54.47222</v>
@@ -1161,7 +1161,7 @@
         <v>23.874111</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>11.021</v>
+        <v>11.009</v>
       </c>
       <c r="N10" s="7" t="n">
         <v>9.6</v>
@@ -1196,7 +1196,7 @@
         <v>26.76</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.0247814</v>
+        <v>-0.02478135</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>31.58</v>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>69</v>
+        <v>66.77419</v>
       </c>
       <c r="L13" s="7" t="n">
         <v>27.661594</v>
@@ -1440,7 +1440,7 @@
         <v>13.67</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.0346045</v>
+        <v>-0.034604504</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20.61</v>
@@ -1455,7 +1455,7 @@
         <v>1.826</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>12.314</v>
+        <v>12.313</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>7.8539295</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>17.051</v>
+        <v>17.049</v>
       </c>
       <c r="N15" s="7" t="n">
         <v>10.8</v>
@@ -1501,7 +1501,7 @@
         <v>96.5</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.0112705</v>
+        <v>-0.011270477</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>113.88</v>
@@ -1519,7 +1519,7 @@
         <v>1.643</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>17.970205</v>
+        <v>17.771639</v>
       </c>
       <c r="L16" s="7" t="n">
         <v>16.232128</v>
@@ -1867,7 +1867,7 @@
         <v>2.32</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.0607288</v>
+        <v>-0.06072878399999999</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>4.95</v>
@@ -2671,7 +2671,7 @@
         <v>19.61</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.406297</v>
+        <v>-0.4062972000000001</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>-0.159</v>
@@ -2718,7 +2718,7 @@
         <v>26.76</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-0.0247814</v>
+        <v>-0.02478135</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.136</v>
@@ -2906,7 +2906,7 @@
         <v>13.67</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-0.0346045</v>
+        <v>-0.034604504</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>-0.079</v>
@@ -2953,7 +2953,7 @@
         <v>96.5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.0112705</v>
+        <v>-0.011270477</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0.008</v>
@@ -3237,7 +3237,7 @@
         <v>2.32</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.0607288</v>
+        <v>-0.06072878399999999</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>-0.07200000000000001</v>
@@ -3576,7 +3576,7 @@
         <v>35.788</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>23.013044</v>
+        <v>22.523405</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>14.086344</v>
@@ -3597,7 +3597,7 @@
         <v>2.7493122</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>3.75754</v>
@@ -3652,7 +3652,7 @@
         <v>1.1214118</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>-1.72</v>
+        <v>-1.75</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>10.80017</v>
@@ -3739,19 +3739,19 @@
         <v>10.426</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.88816</v>
+        <v>31.840765</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>16.826635</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>11.288</v>
+        <v>11.286</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>9.1</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>2.767</v>
+        <v>2.766</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>-37.194942</v>
@@ -3760,7 +3760,7 @@
         <v>1.4606829</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>5.94177</v>
@@ -3792,10 +3792,10 @@
         <v>9.673999999999999</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>48.452053</v>
+        <v>46.539474</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>15.072357</v>
+        <v>15.095321</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>16.638</v>
@@ -3813,10 +3813,10 @@
         <v>0.5516078</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>2.34668</v>
+        <v>2.34311</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>9.407</v>
@@ -3845,7 +3845,7 @@
         <v>6.119</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.6811988</v>
+        <v>3.593085</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>9.949173</v>
@@ -3866,7 +3866,7 @@
         <v>1.4954581</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>22.02</v>
+        <v>22.56</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>8.147410000000001</v>
@@ -3898,13 +3898,13 @@
         <v>5.915</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>19.173334</v>
+        <v>18.435898</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>17.504938</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>8.374000000000001</v>
+        <v>8.372999999999999</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>7.3</v>
@@ -3919,7 +3919,7 @@
         <v>2.940419</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>3.28593</v>
@@ -3951,19 +3951,19 @@
         <v>5.836</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>16.613096</v>
+        <v>15.827978</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>11.276708</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>11.373</v>
+        <v>11.371</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>9.6</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>3.719</v>
+        <v>3.718</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>5.7716966</v>
@@ -3972,7 +3972,7 @@
         <v>1.9944898</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>5.04</v>
+        <v>5.29</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>7.42504</v>
@@ -4010,13 +4010,13 @@
         <v>23.874111</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>11.021</v>
+        <v>11.009</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>9.6</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>4.336</v>
+        <v>4.331</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>5.199397</v>
@@ -4080,7 +4080,7 @@
         <v>0.4755292</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-2.36</v>
+        <v>-2.42</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>0.925</v>
@@ -4165,7 +4165,7 @@
         <v>4.819</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>69</v>
+        <v>66.77419</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>27.661594</v>
@@ -4192,7 +4192,7 @@
         <v>4.2476387</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>0.7483300000000001</v>
@@ -4285,7 +4285,7 @@
         <v>7.8539295</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>17.051</v>
+        <v>17.049</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>10.8</v>
@@ -4332,7 +4332,7 @@
         <v>1.726</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>17.970205</v>
+        <v>17.771639</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>16.232128</v>
@@ -4353,7 +4353,7 @@
         <v>3.1662657</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>5.37</v>
+        <v>5.43</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>5.945</v>
@@ -4410,7 +4410,7 @@
         <v>1.740646</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0.99</v>
@@ -4518,7 +4518,7 @@
         <v>1.0893636</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>1.21</v>
@@ -4683,7 +4683,7 @@
         <v>0.27761704</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.12</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>-0.41</v>
@@ -6877,7 +6877,7 @@
         <v>0.41693002</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="P2" s="5" t="n">
         <v>0.4255</v>
@@ -6930,7 +6930,7 @@
         <v>0.18823999</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>0.91029</v>
+        <v>0.9117</v>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
@@ -7046,10 +7046,10 @@
         <v>0.27027</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0.68558997</v>
+        <v>0.68557</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="P5" s="5" t="n">
         <v>0.3185</v>
@@ -7163,7 +7163,7 @@
         <v>0.73223996</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="P7" s="5" t="n">
         <v>0.0319</v>
@@ -7216,10 +7216,10 @@
         <v>0.07935</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0.88903</v>
+        <v>0.88882005</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="P8" s="5" t="n">
         <v>0.32369998</v>
@@ -7275,7 +7275,7 @@
         <v>0.81711</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="P9" s="5" t="n">
         <v>0.0828</v>
@@ -7447,7 +7447,7 @@
         <v>0.19124001</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="P12" s="5" t="n">
         <v>0.2831</v>
@@ -7497,7 +7497,7 @@
         <v>0.0498</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>0.07047</v>
+        <v>0.07084</v>
       </c>
       <c r="N13" s="5" t="n">
         <v>0.93144995</v>
@@ -7679,7 +7679,7 @@
         <v>0.64762</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P16" s="5" t="n">
         <v>0.221</v>
@@ -7787,10 +7787,10 @@
         <v>0.028099999</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.17495</v>
+        <v>0.13798</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.76093</v>
+        <v>0.76087</v>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>0.68561995</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>3.67</v>
+        <v>3.81</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>4.5455</v>
@@ -8464,7 +8464,7 @@
         <v>35.788</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>23.013044</v>
+        <v>22.523405</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -8554,7 +8554,7 @@
         <v>10.426</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>32.88816</v>
+        <v>31.840765</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.015</v>
@@ -8571,7 +8571,7 @@
         <v>-0.183</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>11.288</v>
+        <v>11.286</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>9.1</v>
@@ -8646,7 +8646,7 @@
         <v>9.673999999999999</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>48.452053</v>
+        <v>46.539474</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.06</v>
@@ -8708,7 +8708,7 @@
         <v>6.119</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.6811988</v>
+        <v>3.593085</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -8752,7 +8752,7 @@
         <v>5.836</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>16.613096</v>
+        <v>15.827978</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.067</v>
@@ -8767,7 +8767,7 @@
         <v>-0.252</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>11.373</v>
+        <v>11.371</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>9.6</v>
@@ -8796,7 +8796,7 @@
         <v>1.726</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>17.970205</v>
+        <v>17.771639</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.041</v>
@@ -8840,7 +8840,7 @@
         <v>5.915</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>19.173334</v>
+        <v>18.435898</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8855,7 +8855,7 @@
         <v>-0.068</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>8.374000000000001</v>
+        <v>8.372999999999999</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>7.3</v>
@@ -8901,7 +8901,7 @@
         <v>-0.079</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>17.051</v>
+        <v>17.049</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>10.8</v>
@@ -9145,7 +9145,7 @@
         <v>-0.159</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>11.021</v>
+        <v>11.009</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>9.6</v>
@@ -9174,7 +9174,7 @@
         <v>4.819</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>69</v>
+        <v>66.77419</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -10418,7 +10418,7 @@
         <v>0.18823999</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.91029</v>
+        <v>0.9117</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>1.72</v>
@@ -10472,7 +10472,7 @@
         <v>0.27027</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.68558997</v>
+        <v>0.68557</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>3.24</v>
@@ -10553,7 +10553,7 @@
         <v>0.07935</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.88903</v>
+        <v>0.88882005</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>3.89</v>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.07047</v>
+        <v>0.07084</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>0.93144995</v>
@@ -10820,10 +10820,10 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.17495</v>
+        <v>0.13798</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.76093</v>
+        <v>0.76087</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>3.68</v>
@@ -12087,8 +12087,12 @@
       <c r="B61" s="13" t="n">
         <v>1045.61</v>
       </c>
-      <c r="C61" s="13" t="n"/>
-      <c r="D61" s="13" t="n"/>
+      <c r="C61" s="13" t="n">
+        <v>1163.17</v>
+      </c>
+      <c r="D61" s="13" t="n">
+        <v>893.28</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="inlineStr">

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -1158,7 +1158,7 @@
         <v>54.47222</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>23.874111</v>
+        <v>23.848154</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>11.009</v>
@@ -4007,7 +4007,7 @@
         <v>54.47222</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>23.874111</v>
+        <v>23.848154</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>11.009</v>
@@ -4019,7 +4019,7 @@
         <v>4.331</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.199397</v>
+        <v>5.193744</v>
       </c>
       <c r="L10" s="7" t="n">
         <v>4.499046</v>
@@ -4028,10 +4028,10 @@
         <v>0.36</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.8213919</v>
+        <v>0.8222859</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>3.7715912</v>
+        <v>3.7756963</v>
       </c>
     </row>
     <row r="11">

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -781,7 +781,7 @@
         <v>23.67</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.0497792</v>
+        <v>-0.049779196</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -842,7 +842,7 @@
         <v>99.98</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.0308259</v>
+        <v>-0.030825903</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -1019,7 +1019,7 @@
         <v>57.52</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.0390912</v>
+        <v>-0.039091215</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>83.73</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.0466811</v>
+        <v>-0.046013675</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>118.46</v>
@@ -1090,16 +1090,16 @@
         <v>-0.293</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.836</v>
+        <v>5.838</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>10.878</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>15.827978</v>
+        <v>15.833649</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>11.276708</v>
+        <v>11.280748</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>11.371</v>
@@ -1158,7 +1158,7 @@
         <v>54.47222</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>23.848154</v>
+        <v>23.858448</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>11.009</v>
@@ -1381,7 +1381,7 @@
         <v>5.46</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.7272719999999999</v>
+        <v>-0.7272720300000001</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>10.15</v>
@@ -1682,7 +1682,7 @@
         <v>26.2</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.0374724</v>
+        <v>-0.03747246</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>32.74</v>
@@ -1806,7 +1806,7 @@
         <v>6.11</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.0671756</v>
+        <v>-0.067175584</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>9.949999999999999</v>
@@ -2389,7 +2389,7 @@
         <v>23.67</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.0497792</v>
+        <v>-0.049779196</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>-0.336</v>
@@ -2436,7 +2436,7 @@
         <v>99.98</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-0.0308259</v>
+        <v>-0.030825903</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>-0.183</v>
@@ -2577,7 +2577,7 @@
         <v>57.52</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.0390912</v>
+        <v>-0.039091215</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>-0.068</v>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>83.73</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-0.0466811</v>
+        <v>-0.046013675</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>-0.252</v>
@@ -2636,10 +2636,10 @@
         <v>-2.8</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.117</v>
+        <v>-0.116</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.171</v>
+        <v>-0.17</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>-0.293</v>
@@ -2859,7 +2859,7 @@
         <v>5.46</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.7272719999999999</v>
+        <v>-0.7272720300000001</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>-0.273</v>
@@ -3094,7 +3094,7 @@
         <v>26.2</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-0.0374724</v>
+        <v>-0.03747246</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>-0.032</v>
@@ -3190,7 +3190,7 @@
         <v>6.11</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-0.0671756</v>
+        <v>-0.067175584</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>-0.319</v>
@@ -3945,16 +3945,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>83.73</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.836</v>
+        <v>5.838</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>15.827978</v>
+        <v>15.833649</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>11.276708</v>
+        <v>11.280748</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>11.371</v>
@@ -3966,10 +3966,10 @@
         <v>3.718</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>5.7716966</v>
+        <v>5.7737646</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>1.9944898</v>
+        <v>1.9952044</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>5.29</v>
@@ -4007,7 +4007,7 @@
         <v>54.47222</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>23.848154</v>
+        <v>23.858448</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>11.009</v>
@@ -4019,7 +4019,7 @@
         <v>4.331</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.193744</v>
+        <v>5.1959863</v>
       </c>
       <c r="L10" s="7" t="n">
         <v>4.499046</v>
@@ -4028,10 +4028,10 @@
         <v>0.36</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.8222859</v>
+        <v>0.8219311</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>3.7756963</v>
+        <v>3.7740672</v>
       </c>
     </row>
     <row r="11">
@@ -6967,7 +6967,7 @@
         <v>34</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>36.11471</v>
+        <v>36.17353</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>76</v>
@@ -6976,7 +6976,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.526</v>
+        <v>0.528</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>83.73</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -7307,16 +7307,16 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.87972</v>
+        <v>28.826334</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.234634</v>
+        <v>37.165802</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>21.962032</v>
+        <v>21.921434</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.473</v>
+        <v>0.47</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>4.19</v>
@@ -8749,10 +8749,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5.836</v>
+        <v>5.838</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>15.827978</v>
+        <v>15.833649</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.067</v>
@@ -11221,7 +11221,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1269.24</v>
+        <v>1269.23</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1219.65</v>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1274.55</v>
+        <v>1274.54</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1221.89</v>
@@ -11269,7 +11269,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1259.54</v>
+        <v>1259.53</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1237.34</v>
@@ -11317,7 +11317,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1208.45</v>
+        <v>1208.44</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>1241.38</v>
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1158.88</v>
+        <v>1158.87</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>1225.88</v>
@@ -11445,7 +11445,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1163.97</v>
+        <v>1163.96</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>1232.28</v>
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1142.68</v>
+        <v>1142.67</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1243.8</v>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1115.8</v>
+        <v>1115.79</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>1235.21</v>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1114.71</v>
+        <v>1114.7</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>1237.89</v>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1088.52</v>
+        <v>1088.51</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>1226.93</v>
@@ -11861,7 +11861,7 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1083.59</v>
+        <v>1083.58</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1227.63</v>
@@ -11877,7 +11877,7 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1079.45</v>
+        <v>1079.44</v>
       </c>
       <c r="C48" s="13" t="n">
         <v>1216.81</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1095.38</v>
+        <v>1095.37</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1225.39</v>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1093.13</v>
+        <v>1093.12</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>1218.56</v>
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1061.18</v>
+        <v>1061.17</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>1202.59</v>
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1062.16</v>
+        <v>1062.15</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>1211.17</v>
@@ -12021,7 +12021,7 @@
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1056.95</v>
+        <v>1056.94</v>
       </c>
       <c r="C57" s="13" t="n">
         <v>1196.6</v>
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1069.59</v>
+        <v>1069.58</v>
       </c>
       <c r="C58" s="13" t="n">
         <v>1199.74</v>
@@ -12069,7 +12069,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1074.29</v>
+        <v>1074.28</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>1180.09</v>
@@ -12085,7 +12085,7 @@
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1045.61</v>
+        <v>1045.62</v>
       </c>
       <c r="C61" s="13" t="n">
         <v>1163.17</v>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1045.61</v>
+        <v>1045.62</v>
       </c>
     </row>
     <row r="64">

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -7307,13 +7307,13 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.826334</v>
+        <v>28.819672</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.165802</v>
+        <v>37.15721</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>21.921434</v>
+        <v>21.916367</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>0.47</v>
@@ -11432,7 +11432,7 @@
         <v>1158.87</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1225.88</v>
+        <v>1225.87</v>
       </c>
       <c r="D20" s="13" t="n">
         <v>1016.19</v>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -61,13 +61,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FF0000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00FF0000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>52.93</v>
+        <v>54.77</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.0207215</v>
+        <v>0.034762897</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,19 +670,19 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.249</v>
+        <v>-0.223</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>35.788</v>
+        <v>37.032</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>48.099</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.523405</v>
+        <v>23.306385</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.086344</v>
+        <v>14.576026</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>10.611</v>
@@ -693,11 +693,11 @@
       <c r="O2" s="8" t="n">
         <v>0.888</v>
       </c>
-      <c r="P2" s="9" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="Q2" s="4" t="n">
-        <v>-0.184</v>
+      <c r="P2" s="4" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="Q2" s="9" t="n">
+        <v>-0.156</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>104.81</v>
+        <v>111.03</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.0150362</v>
+        <v>0.059345493</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -729,10 +729,10 @@
         <v>99.95999999999999</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-0.6659999999999999</v>
+        <v>-0.6459999999999999</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.372</v>
+        <v>19.462</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>30.054</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.704476</v>
+        <v>10.280394</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14.097</v>
@@ -754,11 +754,11 @@
       <c r="O3" s="8" t="n">
         <v>1.177</v>
       </c>
-      <c r="P3" s="4" t="n">
-        <v>-0.5649999999999999</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>-0.52</v>
+      <c r="P3" s="9" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="Q3" s="9" t="n">
+        <v>-0.491</v>
       </c>
     </row>
     <row r="4">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.67</v>
+        <v>24.44</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.049779196</v>
+        <v>0.03251691</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -790,10 +790,10 @@
         <v>21.01</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.515</v>
+        <v>-0.499</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11.782</v>
+        <v>12.166</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>12.431</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>12.161537</v>
+        <v>12.557159</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>45.556</v>
@@ -815,11 +815,11 @@
       <c r="O4" s="8" t="n">
         <v>1.682</v>
       </c>
-      <c r="P4" s="4" t="n">
-        <v>-0.401</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>-0.336</v>
+      <c r="P4" s="9" t="n">
+        <v>-0.397</v>
+      </c>
+      <c r="Q4" s="9" t="n">
+        <v>-0.315</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>99.98</v>
+        <v>104.03</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.030825903</v>
+        <v>0.040508056</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,19 +851,19 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.258</v>
+        <v>-0.228</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.426</v>
+        <v>10.849</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>19.746</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>31.840765</v>
+        <v>33.130573</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>16.826635</v>
+        <v>17.508251</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>11.286</v>
@@ -874,11 +874,11 @@
       <c r="O5" s="8" t="n">
         <v>1.034</v>
       </c>
-      <c r="P5" s="9" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>-0.183</v>
+      <c r="P5" s="4" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="Q5" s="9" t="n">
+        <v>-0.149</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>35.37</v>
+        <v>37.72</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.0476575</v>
+        <v>0.066440554</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,19 +910,19 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.119</v>
+        <v>-0.061</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>9.673999999999999</v>
+        <v>10.317</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>39.176</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>46.539474</v>
+        <v>49.63158</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>15.095321</v>
+        <v>16.098263</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>16.638</v>
@@ -933,11 +933,11 @@
       <c r="O6" s="8" t="n">
         <v>1.396</v>
       </c>
-      <c r="P6" s="9" t="n">
-        <v>0.126</v>
+      <c r="P6" s="4" t="n">
+        <v>0.163</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.031</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>81.06</v>
+        <v>84.55</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.024079</v>
+        <v>0.043054595</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -969,19 +969,19 @@
         <v>58.94</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.099</v>
+        <v>-0.06</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.119</v>
+        <v>6.383</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>8.476000000000001</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.593085</v>
+        <v>3.747784</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>9.949173</v>
+        <v>10.377531</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>7.058</v>
@@ -992,11 +992,11 @@
       <c r="O7" s="8" t="n">
         <v>1.22</v>
       </c>
-      <c r="P7" s="9" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>-0.057</v>
+      <c r="P7" s="4" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>-0.017</v>
       </c>
     </row>
     <row r="8">
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>57.52</v>
+        <v>59.98</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.039091215</v>
+        <v>0.042767715</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1028,19 +1028,19 @@
         <v>35.09</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.166</v>
+        <v>-0.131</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>5.915</v>
+        <v>6.168</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>6.814</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>18.435898</v>
+        <v>19.22436</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>17.504938</v>
+        <v>18.253584</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>8.372999999999999</v>
@@ -1051,11 +1051,11 @@
       <c r="O8" s="8" t="n">
         <v>1.453</v>
       </c>
-      <c r="P8" s="9" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>-0.068</v>
+      <c r="P8" s="4" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>-0.028</v>
       </c>
     </row>
     <row r="9">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>83.76000000000001</v>
+        <v>85.87</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.046013675</v>
+        <v>0.025191028</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>118.46</v>
@@ -1087,19 +1087,19 @@
         <v>80.23999999999999</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.293</v>
+        <v>-0.275</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.838</v>
+        <v>5.985</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>10.878</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>15.833649</v>
+        <v>16.232515</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>11.280748</v>
+        <v>11.564921</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>11.371</v>
@@ -1110,11 +1110,11 @@
       <c r="O9" s="8" t="n">
         <v>0.66</v>
       </c>
-      <c r="P9" s="4" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>-0.252</v>
+      <c r="P9" s="9" t="n">
+        <v>-0.242</v>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>-0.233</v>
       </c>
     </row>
     <row r="10">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.61</v>
+        <v>19.82</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4062972000000001</v>
+        <v>0.010708776</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>32.22</v>
@@ -1146,19 +1146,19 @@
         <v>15.725</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.391</v>
+        <v>-0.385</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.804</v>
+        <v>5.866</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>5.587</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>54.47222</v>
+        <v>55.055553</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>23.858448</v>
+        <v>24.113943</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>11.009</v>
@@ -1169,11 +1169,11 @@
       <c r="O10" s="8" t="n">
         <v>2.002</v>
       </c>
-      <c r="P10" s="4" t="n">
-        <v>-0.121</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>-0.159</v>
+      <c r="P10" s="9" t="n">
+        <v>-0.138</v>
+      </c>
+      <c r="Q10" s="9" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="11">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>26.76</v>
+        <v>27.18</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.02478135</v>
+        <v>0.015508184</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>31.58</v>
@@ -1205,10 +1205,10 @@
         <v>17.86</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.153</v>
+        <v>-0.139</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.462</v>
+        <v>5.547</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>30.363</v>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="L11" s="7" t="n">
-        <v>28.92973</v>
+        <v>29.378378</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>8.688000000000001</v>
@@ -1230,11 +1230,11 @@
       <c r="O11" s="8" t="n">
         <v>1.977</v>
       </c>
-      <c r="P11" s="4" t="n">
-        <v>-0.022</v>
-      </c>
-      <c r="Q11" s="9" t="n">
-        <v>0.136</v>
+      <c r="P11" s="9" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>0.153</v>
       </c>
     </row>
     <row r="12">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.46</v>
+        <v>10.77</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.0187617</v>
+        <v>0.02963675</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>14.38</v>
@@ -1266,19 +1266,19 @@
         <v>5.59</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.273</v>
+        <v>-0.251</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.289</v>
+        <v>5.446</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>4.882</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>24.904762</v>
+        <v>25.642859</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>12.0588875</v>
+        <v>12.416274</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>9.948</v>
@@ -1289,11 +1289,11 @@
       <c r="O12" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="P12" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>-0.09699999999999999</v>
+      <c r="P12" s="4" t="n">
+        <v>0.5479999999999999</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.0254237</v>
+        <v>0.033816369</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.055</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>4.819</v>
+        <v>4.982</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>66.77419</v>
+        <v>69.03225999999999</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>27.661594</v>
+        <v>28.59701</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1354,142 +1354,142 @@
       <c r="O13" s="8" t="n">
         <v>1.552</v>
       </c>
-      <c r="P13" s="9" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="Q13" s="9" t="n">
-        <v>0.07200000000000001</v>
+      <c r="P13" s="4" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0.108</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MLCO</t>
+          <t>BRSL</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Melco Resorts</t>
+          <t>Brightstar Lottery</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5.46</v>
+        <v>13.23</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.7272720300000001</v>
+        <v>0.034401844</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>10.15</v>
+        <v>18.57</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>4.55</v>
+        <v>12.53</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-0.462</v>
+        <v>-0.288</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.221</v>
+        <v>2.441</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>12.751</v>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>11.869565</v>
+        <v>5.928</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L14" s="7" t="n">
-        <v>6.8628316</v>
+        <v>12.277966</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>10.572</v>
+        <v>6.721</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v>-0.014</v>
-      </c>
-      <c r="Q14" s="4" t="n">
-        <v>-0.273</v>
+        <v>1.082</v>
+      </c>
+      <c r="P14" s="9" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>MLCO</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Penn Entertainment</t>
+          <t>Melco Resorts</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>13.67</v>
+        <v>5.54</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.034604504</v>
+        <v>0.014413931</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>20.61</v>
+        <v>10.15</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>11.65</v>
+        <v>4.55</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.337</v>
+        <v>-0.454</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.826</v>
+        <v>2.253</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>12.313</v>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>12.751</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>12.040652</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>7.8539295</v>
+        <v>6.961752</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>17.049</v>
+        <v>10.572</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>10.8</v>
+        <v>8.4</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>1.364</v>
-      </c>
-      <c r="P15" s="4" t="n">
-        <v>-0.213</v>
-      </c>
-      <c r="Q15" s="4" t="n">
-        <v>-0.079</v>
+        <v>0.603</v>
+      </c>
+      <c r="P15" s="9" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="Q15" s="9" t="n">
+        <v>-0.262</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Monarch Casino &amp; Resort</t>
+          <t>Penn Entertainment</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1498,240 +1498,240 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>96.5</v>
+        <v>14.76</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.011270477</v>
+        <v>0.079370885</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>113.88</v>
+        <v>20.61</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>69.98999999999999</v>
+        <v>11.65</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.153</v>
+        <v>-0.284</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.726</v>
+        <v>1.97</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1.643</v>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>17.771639</v>
+        <v>12.313</v>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>16.232128</v>
+        <v>8.477302999999999</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>8.614000000000001</v>
+        <v>17.049</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>1.376</v>
+        <v>1.364</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0.204</v>
+        <v>-0.15</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>0.008</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GENI</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>Monarch Casino &amp; Resort</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.53</v>
+        <v>99.19</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.0361701</v>
+        <v>0.027875674</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>13.73</v>
+        <v>113.88</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>4.51</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.67</v>
+        <v>-0.129</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.165</v>
+        <v>1.774</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.866</v>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1.643</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>18.267036</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>4.575758</v>
+        <v>16.684608</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>-7.181</v>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>8.614000000000001</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>7.4</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>1.993</v>
+        <v>1.376</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.238</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.58</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ACEL</t>
+          <t>GENI</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Accel Entertainment</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>10.92</v>
+        <v>4.74</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.0135501</v>
+        <v>0.045253844</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>13.31</v>
+        <v>13.73</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>9.015000000000001</v>
+        <v>4.51</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.18</v>
+        <v>-0.655</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.909</v>
+        <v>1.218</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1.214</v>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>18.199999</v>
+        <v>0.866</v>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>11.792274</v>
+        <v>4.7828283</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>6.422</v>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>4.5</v>
+        <v>-7.181</v>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O18" s="8" t="n">
-        <v>1.07</v>
+        <v>1.993</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="Q18" s="4" t="n">
-        <v>-0.04</v>
+        <v>-0.5710000000000001</v>
+      </c>
+      <c r="Q18" s="9" t="n">
+        <v>-0.5610000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GDEN</t>
+          <t>ACEL</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Golden Entertainment</t>
+          <t>Accel Entertainment</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>26.2</v>
+        <v>11.33</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.03747246</v>
+        <v>0.037545774</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>32.74</v>
+        <v>13.31</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19.57</v>
+        <v>9.015000000000001</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.2</v>
+        <v>-0.149</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.149</v>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1.214</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>18.883333</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>21.652893</v>
+        <v>12.235025</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>9.414</v>
+        <v>6.422</v>
       </c>
       <c r="N19" s="7" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>1.412</v>
+        <v>1.07</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="Q19" s="4" t="n">
-        <v>-0.032</v>
+        <v>0.114</v>
+      </c>
+      <c r="Q19" s="9" t="n">
+        <v>-0.004</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BALY</t>
+          <t>GDEN</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bally's Corporation</t>
+          <t>Golden Entertainment</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1740,25 +1740,25 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.04</v>
+        <v>26.58</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.013923</v>
+        <v>0.014503784</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>20.74</v>
+        <v>32.74</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.455</v>
+        <v>19.57</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.419</v>
+        <v>-0.188</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.592</v>
+        <v>0.702</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>6.095</v>
+        <v>1.149</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
@@ -1766,62 +1766,60 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>-8.080537</v>
+        <v>21.966942</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>18.843</v>
+        <v>9.414</v>
       </c>
       <c r="N20" s="7" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="Q20" s="4" t="n">
-        <v>-0.276</v>
+        <v>7.2</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="P20" s="9" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>-0.017</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>INSE</t>
+          <t>BALY</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Inspired Entertainment</t>
+          <t>Bally's Corporation</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.11</v>
+        <v>12.34</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.067175584</v>
+        <v>0.02491696</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>9.949999999999999</v>
+        <v>20.74</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>6.1</v>
+        <v>8.455</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.386</v>
+        <v>-0.405</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.165</v>
+        <v>0.607</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.496</v>
+        <v>6.095</v>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
@@ -1829,60 +1827,62 @@
         </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>8.155802</v>
+        <v>-8.281879</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>6.676</v>
+        <v>18.843</v>
       </c>
       <c r="N21" s="7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>1.206</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>-0.309</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>-0.319</v>
+        <v>12.9</v>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="9" t="n">
+        <v>-0.296</v>
+      </c>
+      <c r="Q21" s="9" t="n">
+        <v>-0.258</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FLL</t>
+          <t>INSE</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Full House Resorts</t>
+          <t>Inspired Entertainment</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.32</v>
+        <v>6.44</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.06072878399999999</v>
+        <v>0.054009805</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>4.95</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2.02</v>
+        <v>6.1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.531</v>
+        <v>-0.353</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.174</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.578</v>
+        <v>0.496</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
@@ -1890,89 +1890,83 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>-5.6585364</v>
+        <v>8.596294</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>12.539</v>
+        <v>6.676</v>
       </c>
       <c r="N22" s="7" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="O22" s="8" t="n">
-        <v>1.327</v>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v>-0.458</v>
-      </c>
-      <c r="Q22" s="4" t="n">
-        <v>-0.07200000000000001</v>
+        <v>1.206</v>
+      </c>
+      <c r="P22" s="9" t="n">
+        <v>-0.296</v>
+      </c>
+      <c r="Q22" s="9" t="n">
+        <v>-0.282</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>FLL</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>International Game Technology</t>
+          <t>Full House Resorts</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="E23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="5" t="n"/>
       <c r="F23" s="3" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5" t="n"/>
+        <v>2.02</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.531</v>
+      </c>
       <c r="I23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>0.578</v>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="5" t="n">
-        <v>0</v>
+      <c r="L23" s="7" t="n">
+        <v>-5.6585364</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>12.539</v>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>1.327</v>
+      </c>
+      <c r="P23" s="9" t="n">
+        <v>-0.481</v>
+      </c>
+      <c r="Q23" s="9" t="n">
+        <v>-0.07200000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -2037,145 +2031,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="P24" s="4" t="n">
+      <c r="P24" s="9" t="n">
         <v>-0.239</v>
       </c>
-      <c r="Q24" s="4" t="n">
+      <c r="Q24" s="9" t="n">
         <v>-0.239</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>EVRI</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Everi Holdings</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Gaming Equipment</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>AGS</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>PlayAGS</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Gaming Equipment</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2190,7 +2050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2292,28 +2152,28 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>52.93</v>
+        <v>54.77</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.0207215</v>
+        <v>0.034762897</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.184</v>
+        <v>-0.156</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.289</v>
+        <v>0.347</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>54.1</v>
+        <v>53.7</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.05</v>
+        <v>-0.017</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.249</v>
+        <v>-0.223</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
@@ -2339,28 +2199,28 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>104.81</v>
+        <v>111.03</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.0150362</v>
+        <v>0.059345493</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0.52</v>
+        <v>-0.491</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.55</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-54.8</v>
+        <v>-56</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.272</v>
+        <v>-0.228</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.544</v>
+        <v>-0.517</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.6659999999999999</v>
+        <v>-0.6459999999999999</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>1.177</v>
@@ -2386,28 +2246,28 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.67</v>
+        <v>24.44</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.049779196</v>
+        <v>0.03251691</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.336</v>
+        <v>-0.315</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.401</v>
+        <v>-0.397</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-35</v>
+        <v>-35.6</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.128</v>
+        <v>-0.1</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.337</v>
+        <v>-0.316</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.515</v>
+        <v>-0.499</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
@@ -2433,28 +2293,28 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>99.98</v>
+        <v>104.03</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-0.030825903</v>
+        <v>0.040508056</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.183</v>
+        <v>-0.149</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.221</v>
+        <v>0.237</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>36</v>
+        <v>35.3</v>
       </c>
       <c r="I5" s="5" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="J5" s="5" t="n">
         <v>-0.09</v>
       </c>
-      <c r="J5" s="5" t="n">
-        <v>-0.125</v>
-      </c>
       <c r="K5" s="5" t="n">
-        <v>-0.258</v>
+        <v>-0.228</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>1.034</v>
@@ -2480,28 +2340,28 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>35.37</v>
+        <v>37.72</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.0476575</v>
+        <v>0.066440554</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-0.031</v>
+        <v>0.034</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.126</v>
+        <v>0.163</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>11.9</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.064</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.006</v>
+        <v>0.073</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.119</v>
+        <v>-0.061</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>1.396</v>
@@ -2527,28 +2387,28 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>81.06</v>
+        <v>84.55</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-0.024079</v>
+        <v>0.043054595</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0.057</v>
+        <v>-0.017</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.204</v>
+        <v>0.233</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.034</v>
+        <v>0.008</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.021</v>
+        <v>0.021</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.099</v>
+        <v>-0.06</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>1.22</v>
@@ -2574,28 +2434,28 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>57.52</v>
+        <v>59.98</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.039091215</v>
+        <v>0.042767715</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.068</v>
+        <v>-0.028</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.373</v>
+        <v>0.403</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>39.8</v>
+        <v>39.5</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.027</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.022</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.166</v>
+        <v>-0.131</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>1.453</v>
@@ -2621,28 +2481,28 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>83.76000000000001</v>
+        <v>85.87</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-0.046013675</v>
+        <v>0.025191028</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.252</v>
+        <v>-0.233</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.25</v>
+        <v>-0.242</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>-2.8</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.116</v>
+        <v>-0.094</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.17</v>
+        <v>-0.149</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.293</v>
+        <v>-0.275</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>0.66</v>
@@ -2668,28 +2528,28 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.61</v>
+        <v>19.82</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.4062972000000001</v>
+        <v>0.010708776</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.159</v>
+        <v>-0.15</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.121</v>
+        <v>-0.138</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-27.3</v>
+        <v>-27.9</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.067</v>
+        <v>0.078</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-0.2</v>
+        <v>-0.191</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.391</v>
+        <v>-0.385</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>2.002</v>
@@ -2715,28 +2575,28 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>26.76</v>
+        <v>27.18</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-0.02478135</v>
+        <v>0.015508184</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.136</v>
+        <v>0.153</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.022</v>
+        <v>-0.034</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-23.4</v>
+        <v>-23</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.141</v>
+        <v>0.159</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.102</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.153</v>
+        <v>-0.139</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>1.977</v>
@@ -2762,28 +2622,28 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.46</v>
+        <v>10.77</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.0187617</v>
+        <v>0.02963675</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-0.09699999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.545</v>
+        <v>0.5479999999999999</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.273</v>
+        <v>-0.251</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>1.1</v>
@@ -2809,28 +2669,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-0.0254237</v>
+        <v>0.033816369</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.108</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.889</v>
+        <v>0.887</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>51.5</v>
+        <v>51.1</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.1</v>
+        <v>0.138</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.132</v>
+        <v>0.17</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.055</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2842,106 +2702,106 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MLCO</t>
+          <t>BRSL</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Melco Resorts</t>
+          <t>Brightstar Lottery</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5.46</v>
+        <v>13.23</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.7272720300000001</v>
+        <v>0.034401844</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.273</v>
+        <v>-0.12</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.016</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>10.5</v>
+        <v>13.8</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.09300000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.305</v>
+        <v>-0.144</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-0.462</v>
+        <v>-0.288</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.603</v>
+        <v>1.082</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>1478700</v>
+        <v>1136690</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>MLCO</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Penn Entertainment</t>
+          <t>Melco Resorts</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>13.67</v>
+        <v>5.54</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-0.034604504</v>
+        <v>0.014413931</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.262</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.213</v>
+        <v>-0.006</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-19.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.08</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.159</v>
+        <v>-0.294</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.337</v>
+        <v>-0.454</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>1.364</v>
+        <v>0.603</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>4084830</v>
+        <v>1478700</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Monarch Casino &amp; Resort</t>
+          <t>Penn Entertainment</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2950,186 +2810,186 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>96.5</v>
+        <v>14.76</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.011270477</v>
+        <v>0.079370885</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.006</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.204</v>
+        <v>-0.15</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>20.8</v>
+        <v>-19.2</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.017</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.091</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.153</v>
+        <v>-0.284</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>1.376</v>
+        <v>1.364</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>158160</v>
+        <v>4084830</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GENI</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>Monarch Casino &amp; Resort</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.53</v>
+        <v>99.19</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-0.0361701</v>
+        <v>0.027875674</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-0.58</v>
+        <v>0.036</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.238</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-29.8</v>
+        <v>20.7</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.371</v>
+        <v>0.045</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.67</v>
+        <v>-0.129</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>1.993</v>
+        <v>1.376</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>7109690</v>
+        <v>158160</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ACEL</t>
+          <t>GENI</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Accel Entertainment</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>10.92</v>
+        <v>4.74</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.0135501</v>
+        <v>0.045253844</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.04</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.101</v>
+        <v>-0.5710000000000001</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-1</v>
+        <v>-31.1</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.033</v>
+        <v>-0.342</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.025</v>
+        <v>-0.536</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.18</v>
+        <v>-0.655</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>1.07</v>
+        <v>1.993</v>
       </c>
       <c r="M18" s="10" t="n">
-        <v>453170</v>
+        <v>7109690</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GDEN</t>
+          <t>ACEL</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Golden Entertainment</t>
+          <t>Accel Entertainment</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>26.2</v>
+        <v>11.33</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-0.03747246</v>
+        <v>0.037545774</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.032</v>
+        <v>-0.004</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.114</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>5.3</v>
+        <v>-1.2</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.062</v>
+        <v>0.003</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.025</v>
+        <v>0.012</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.2</v>
+        <v>-0.149</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>1.412</v>
+        <v>1.07</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>143220</v>
+        <v>453170</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BALY</t>
+          <t>GDEN</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bally's Corporation</t>
+          <t>Golden Entertainment</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3138,175 +2998,177 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.04</v>
+        <v>26.58</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.013923</v>
+        <v>0.014503784</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.276</v>
+        <v>-0.017</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.34</v>
+        <v>-0.016</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>37.8</v>
+        <v>5.3</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.171</v>
+        <v>-0.049</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.011</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.419</v>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-0.188</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>1.412</v>
       </c>
       <c r="M20" s="10" t="n">
-        <v>107850</v>
+        <v>143220</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>INSE</t>
+          <t>BALY</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Inspired Entertainment</t>
+          <t>Bally's Corporation</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.11</v>
+        <v>12.34</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-0.067175584</v>
+        <v>0.02491696</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.319</v>
+        <v>-0.258</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.309</v>
+        <v>-0.296</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>5.5</v>
+        <v>38.7</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.271</v>
+        <v>-0.15</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.286</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.386</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>1.206</v>
+        <v>-0.405</v>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M21" s="10" t="n">
-        <v>226360</v>
+        <v>107850</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FLL</t>
+          <t>INSE</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Full House Resorts</t>
+          <t>Inspired Entertainment</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.32</v>
+        <v>6.44</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.06072878399999999</v>
+        <v>0.054009805</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.282</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.458</v>
+        <v>-0.296</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>-53</v>
+        <v>5</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.039</v>
+        <v>-0.231</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.247</v>
+        <v>-0.248</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.531</v>
+        <v>-0.353</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.327</v>
+        <v>1.206</v>
       </c>
       <c r="M22" s="10" t="n">
-        <v>112720</v>
+        <v>226360</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>FLL</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>International Game Technology</t>
+          <t>Full House Resorts</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="E23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n">
-        <v>0</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-0.481</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>-52.9</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>-0.247</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>-0.531</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>1.327</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>112720</v>
       </c>
     </row>
     <row r="24">
@@ -3349,96 +3211,6 @@
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>EVRI</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Everi Holdings</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Gaming Equipment</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>AGS</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>PlayAGS</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Gaming Equipment</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3456,7 +3228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3570,16 +3342,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>52.93</v>
+        <v>54.77</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>35.788</v>
+        <v>37.032</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>22.523405</v>
+        <v>23.306385</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.086344</v>
+        <v>14.576026</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>10.611</v>
@@ -3591,10 +3363,10 @@
         <v>3.695</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.466045</v>
+        <v>23.24703</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.7493122</v>
+        <v>2.8448865</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3623,10 +3395,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>104.81</v>
+        <v>111.03</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.372</v>
+        <v>19.462</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3634,7 +3406,7 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.704476</v>
+        <v>10.280394</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>14.097</v>
@@ -3646,10 +3418,10 @@
         <v>1.834</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.031989</v>
+        <v>2.1525784</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1214118</v>
+        <v>1.1879625</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3678,10 +3450,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.67</v>
+        <v>24.44</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.782</v>
+        <v>12.166</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3461,7 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>12.161537</v>
+        <v>12.557159</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>45.556</v>
@@ -3701,10 +3473,10 @@
         <v>2.053</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>18.550156</v>
+        <v>19.153605</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.946028</v>
+        <v>2.0093336</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3733,16 +3505,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>99.98</v>
+        <v>104.03</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.426</v>
+        <v>10.849</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>31.840765</v>
+        <v>33.130573</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>16.826635</v>
+        <v>17.508251</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>11.286</v>
@@ -3754,10 +3526,10 @@
         <v>2.766</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-37.194942</v>
+        <v>-38.701637</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.4606829</v>
+        <v>1.5198523</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3786,16 +3558,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>35.37</v>
+        <v>37.72</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9.673999999999999</v>
+        <v>10.317</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>46.539474</v>
+        <v>49.63158</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>15.095321</v>
+        <v>16.098263</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>16.638</v>
@@ -3807,10 +3579,10 @@
         <v>2.234</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.7599661</v>
+        <v>4.0097804</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.5516078</v>
+        <v>0.5882569</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3839,16 +3611,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>81.06</v>
+        <v>84.55</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.119</v>
+        <v>6.383</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.593085</v>
+        <v>3.747784</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>9.949173</v>
+        <v>10.377531</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>7.058</v>
@@ -3860,10 +3632,10 @@
         <v>2.071</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.3731592</v>
+        <v>2.4753344</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.4954581</v>
+        <v>1.5598445</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>22.56</v>
@@ -3892,16 +3664,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>57.52</v>
+        <v>59.98</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>5.915</v>
+        <v>6.168</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>18.435898</v>
+        <v>19.22436</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>17.504938</v>
+        <v>18.253584</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>8.372999999999999</v>
@@ -3913,10 +3685,10 @@
         <v>3.388</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.103024</v>
+        <v>16.791714</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.940419</v>
+        <v>3.066174</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>3.12</v>
@@ -3945,16 +3717,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>83.76000000000001</v>
+        <v>85.87</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.838</v>
+        <v>5.985</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>15.833649</v>
+        <v>16.232515</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>11.280748</v>
+        <v>11.564921</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>11.371</v>
@@ -3966,10 +3738,10 @@
         <v>3.718</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>5.7737646</v>
+        <v>5.9192114</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>1.9952044</v>
+        <v>2.0454657</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>5.29</v>
@@ -3998,16 +3770,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.61</v>
+        <v>19.82</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.804</v>
+        <v>5.866</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>54.47222</v>
+        <v>55.055553</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>23.858448</v>
+        <v>24.113943</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>11.009</v>
@@ -4019,10 +3791,10 @@
         <v>4.331</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.1959863</v>
+        <v>5.251629</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>4.499046</v>
+        <v>4.5472255</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.36</v>
@@ -4051,10 +3823,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>26.76</v>
+        <v>27.18</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.462</v>
+        <v>5.547</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -4062,7 +3834,7 @@
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>28.92973</v>
+        <v>29.378378</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>8.688000000000001</v>
@@ -4074,10 +3846,10 @@
         <v>2.643</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>1.547447</v>
+        <v>1.5714451</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.4755292</v>
+        <v>0.4829038</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>-2.42</v>
@@ -4106,16 +3878,16 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.46</v>
+        <v>10.77</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.289</v>
+        <v>5.446</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>24.904762</v>
+        <v>25.642859</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>12.0588875</v>
+        <v>12.416274</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>9.948</v>
@@ -4127,10 +3899,10 @@
         <v>2.084</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>7.101154</v>
+        <v>7.311609</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>2.257434</v>
+        <v>2.324337</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0.42</v>
@@ -4159,16 +3931,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4.819</v>
+        <v>4.982</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>66.77419</v>
+        <v>69.03225999999999</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>27.661594</v>
+        <v>28.59701</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -4186,10 +3958,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>14.052953</v>
+        <v>14.528173</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.2476387</v>
+        <v>4.3912787</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -4204,120 +3976,120 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MLCO</t>
+          <t>BRSL</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Melco Resorts</t>
+          <t>Brightstar Lottery</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5.46</v>
+        <v>13.23</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.221</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>11.869565</v>
+        <v>2.441</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>6.8628316</v>
+        <v>12.277966</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>10.572</v>
+        <v>6.721</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>2.47</v>
+        <v>2.361</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>-1.7110624</v>
+        <v>2.8251119</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.4301677</v>
+        <v>0.9722474</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.46</v>
+        <v>-0.01</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.79559</v>
+        <v>1.07754</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>-3.191</v>
+        <v>4.683</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>MLCO</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Penn Entertainment</t>
+          <t>Melco Resorts</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>13.67</v>
+        <v>5.54</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>2.253</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>12.040652</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>7.8539295</v>
+        <v>6.961752</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>17.049</v>
+        <v>10.572</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>10.8</v>
+        <v>8.4</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.769</v>
+        <v>2.47</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.94100636</v>
+        <v>-1.7357255</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.26225796</v>
+        <v>0.4363681</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>-5.83</v>
+        <v>0.46</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.74053</v>
+        <v>0.79559</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>14.527</v>
+        <v>-3.191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Monarch Casino &amp; Resort</t>
+          <t>Penn Entertainment</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4326,216 +4098,216 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>96.5</v>
+        <v>14.76</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.726</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>17.771639</v>
+        <v>1.97</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>16.232128</v>
+        <v>8.477302999999999</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>8.614000000000001</v>
+        <v>17.049</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>3.014</v>
+        <v>1.769</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>3.1981175</v>
+        <v>1.0156949</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>3.1662657</v>
+        <v>0.2830736</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>5.43</v>
+        <v>-5.83</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5.945</v>
+        <v>1.74053</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>30.174</v>
+        <v>14.527</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GENI</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>Monarch Casino &amp; Resort</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.53</v>
+        <v>99.19</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.165</v>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1.774</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>18.267036</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4.575758</v>
+        <v>16.684608</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-7.181</v>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>8.614000000000001</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>7.4</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.293</v>
+        <v>3.014</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>1.5402925</v>
+        <v>3.2872672</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>1.740646</v>
+        <v>3.2545276</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0.44</v>
+        <v>5.43</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.99</v>
+        <v>5.945</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>2.941</v>
+        <v>30.174</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ACEL</t>
+          <t>GENI</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Accel Entertainment</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>10.92</v>
+        <v>4.74</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>18.199999</v>
+        <v>1.218</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>11.792274</v>
+        <v>4.7828283</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>6.422</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>4.5</v>
+        <v>-7.181</v>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.912</v>
+        <v>1.293</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>3.3323162</v>
+        <v>1.6099967</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.6826883</v>
+        <v>1.8194169</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.6</v>
+        <v>-0.44</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.92603</v>
+        <v>0.99</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>3.277</v>
+        <v>2.941</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GDEN</t>
+          <t>ACEL</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Golden Entertainment</t>
+          <t>Accel Entertainment</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>26.2</v>
+        <v>11.33</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>18.883333</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>21.652893</v>
+        <v>12.235025</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>9.414</v>
+        <v>6.422</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.81</v>
+        <v>0.912</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>1.6299615</v>
+        <v>3.4574306</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>1.0893636</v>
+        <v>0.7083203</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>-0.23</v>
+        <v>0.6</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>1.21</v>
+        <v>0.92603</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>16.074</v>
+        <v>3.277</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BALY</t>
+          <t>GDEN</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bally's Corporation</t>
+          <t>Golden Entertainment</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -4544,10 +4316,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.04</v>
+        <v>26.58</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.592</v>
+        <v>0.702</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -4555,54 +4327,54 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>-8.080537</v>
+        <v>21.966942</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>18.843</v>
+        <v>9.414</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>12.9</v>
+        <v>7.2</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>2.447</v>
+        <v>1.81</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.134244</v>
+        <v>1.6536021</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.2376387</v>
+        <v>1.1051636</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-12.58</v>
+        <v>-0.23</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-1.49</v>
+        <v>1.21</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>10.615</v>
+        <v>16.074</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>INSE</t>
+          <t>BALY</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Inspired Entertainment</t>
+          <t>Bally's Corporation</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.11</v>
+        <v>12.34</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.165</v>
+        <v>0.607</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -4610,54 +4382,54 @@
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>8.155802</v>
+        <v>-8.281879</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>6.676</v>
+        <v>18.843</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>5.4</v>
+        <v>12.9</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.631</v>
+        <v>2.447</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>-10.13267</v>
+        <v>1.162506</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.54368293</v>
+        <v>0.24355991</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.58</v>
+        <v>-12.58</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0.74916</v>
+        <v>-1.49</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-0.603</v>
+        <v>10.615</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FLL</t>
+          <t>INSE</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Full House Resorts</t>
+          <t>Inspired Entertainment</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.32</v>
+        <v>6.44</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.174</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -4665,104 +4437,86 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>-5.6585364</v>
+        <v>8.596294</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>12.539</v>
+        <v>6.676</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.911</v>
+        <v>1.631</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>33.142857</v>
+        <v>-10.679934</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.27761704</v>
+        <v>0.57304716</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>-1.12</v>
+        <v>-0.58</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>-0.41</v>
+        <v>0.74916</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.603</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>FLL</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>International Game Technology</t>
+          <t>Full House Resorts</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G23" s="7" t="n">
+        <v>-5.6585364</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>12.539</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>1.911</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>33.142857</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>0.27761704</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -4833,152 +4587,6 @@
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>EVRI</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Everi Holdings</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Gaming Equipment</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>AGS</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>PlayAGS</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Gaming Equipment</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4996,7 +4604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5828,134 +5436,134 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MLCO</t>
+          <t>BRSL</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Melco Resorts</t>
+          <t>Brightstar Lottery</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5.163</v>
+        <v>2.511</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.37937</v>
+        <v>0.50458</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.16118999</v>
+        <v>0.26198</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.03584</v>
+        <v>0.05854</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.23358</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.35125</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>0.07395</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.05314</v>
+        <v>0.04251</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>1.206</v>
+        <v>0.882</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.425</v>
+        <v>5.592</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>7.032</v>
+        <v>4.299</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.023</v>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1.446</v>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>270.377</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>1.072</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>MLCO</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Penn Entertainment</t>
+          <t>Melco Resorts</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>6.961</v>
+        <v>5.163</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.082</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.33793998</v>
+        <v>0.37937</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.04911</v>
+        <v>0.16118999</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.121120006</v>
+        <v>0.03584</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.10375</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>-0.36078</v>
+        <v>0.23358</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.01165</v>
+        <v>0.05314</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.722</v>
+        <v>1.206</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>-0.294</v>
+        <v>0.425</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>11.272</v>
+        <v>7.032</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="P15" s="7" t="n">
-        <v>616.8099999999999</v>
+        <v>1.023</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>0.79</v>
+        <v>1.072</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Monarch Casino &amp; Resort</t>
+          <t>Penn Entertainment</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5964,234 +5572,234 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.545</v>
+        <v>6.961</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.041</v>
+        <v>0.082</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.67957</v>
+        <v>0.33793998</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.26003</v>
+        <v>0.04911</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.186</v>
+        <v>-0.121120006</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.34986</v>
+        <v>0.10375</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.19214001</v>
+        <v>-0.36078</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.12166</v>
+        <v>0.01165</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.191</v>
+        <v>0.722</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.114</v>
+        <v>-0.294</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.013</v>
+        <v>11.272</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.096</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="P16" s="7" t="n">
-        <v>2.473</v>
+        <v>616.8099999999999</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>0.861</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GENI</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>Monarch Casino &amp; Resort</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.669</v>
+        <v>0.545</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.37</v>
+        <v>0.041</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.22986999</v>
+        <v>0.67957</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.18139</v>
+        <v>0.26003</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.16667</v>
+        <v>0.186</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.18008</v>
+        <v>0.34986</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.17208</v>
+        <v>0.19214001</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.09192</v>
+        <v>0.12166</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>-0.121</v>
+        <v>0.191</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.107</v>
+        <v>0.114</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.03</v>
+        <v>0.013</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.281</v>
+        <v>0.096</v>
       </c>
       <c r="P17" s="7" t="n">
-        <v>4.209</v>
+        <v>2.473</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>1.558</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ACEL</t>
+          <t>GENI</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Accel Entertainment</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1.331</v>
+        <v>0.669</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.075</v>
+        <v>0.37</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.31347</v>
+        <v>0.22986999</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.09969</v>
+        <v>-0.18139</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.03867</v>
+        <v>-0.16667</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.14208001</v>
+        <v>-0.18008</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.19236</v>
+        <v>-0.17208</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.06608</v>
+        <v>-0.09192</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.189</v>
+        <v>-0.121</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.041</v>
+        <v>0.107</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.617</v>
+        <v>0.03</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.297</v>
+        <v>0.281</v>
       </c>
       <c r="P18" s="7" t="n">
-        <v>225.248</v>
+        <v>4.209</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>2.609</v>
+        <v>1.558</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GDEN</t>
+          <t>ACEL</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Golden Entertainment</t>
+          <t>Accel Entertainment</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.635</v>
+        <v>1.331</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-0.052</v>
+        <v>0.075</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.53745</v>
+        <v>0.31347</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.03824</v>
+        <v>0.09969</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.009520000000000001</v>
+        <v>0.03867</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.19224001</v>
+        <v>0.14208001</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.0135</v>
+        <v>0.19236</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.01893</v>
+        <v>0.06608</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.122</v>
+        <v>0.189</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.038</v>
+        <v>0.041</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.518</v>
+        <v>0.617</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.055</v>
+        <v>0.297</v>
       </c>
       <c r="P19" s="7" t="n">
-        <v>123.06</v>
+        <v>225.248</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>1.165</v>
+        <v>2.609</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BALY</t>
+          <t>GDEN</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bally's Corporation</t>
+          <t>Golden Entertainment</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -6200,255 +5808,227 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2.491</v>
+        <v>0.635</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.054</v>
+        <v>-0.052</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.5516</v>
+        <v>0.53745</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.046469998</v>
+        <v>0.03824</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.1741</v>
+        <v>-0.009520000000000001</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.12987</v>
+        <v>0.19224001</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-1.1563</v>
+        <v>-0.0135</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.00361</v>
+        <v>0.01893</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.323</v>
+        <v>0.122</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>-0.211</v>
+        <v>0.038</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>5.664</v>
+        <v>0.518</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.161</v>
+        <v>0.055</v>
       </c>
       <c r="P20" s="7" t="n">
-        <v>1085.198</v>
+        <v>123.06</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.165</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>INSE</t>
+          <t>BALY</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Inspired Entertainment</t>
+          <t>Bally's Corporation</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
+          <t>Regional Operators</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.304</v>
+        <v>2.491</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.054</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.71555</v>
+        <v>0.5516</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.34326</v>
+        <v>0.046469998</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.0559</v>
+        <v>-0.1741</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.24433</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.12987</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>-1.1563</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.07428999999999999</v>
+        <v>0.00361</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.074</v>
+        <v>0.323</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.027</v>
+        <v>-0.211</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.373</v>
+        <v>5.664</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.161</v>
+      </c>
+      <c r="P21" s="7" t="n">
+        <v>1085.198</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>2.232</v>
+        <v>0.6830000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FLL</t>
+          <t>INSE</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Full House Resorts</t>
+          <t>Inspired Entertainment</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Regional Operators</t>
+          <t>Gaming Equipment</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.302</v>
+        <v>0.304</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.51523995</v>
+        <v>0.71555</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.01112</v>
+        <v>0.34326</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.13294</v>
+        <v>-0.0559</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.15241</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>-1.8681101</v>
+        <v>0.24433</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.00328</v>
+        <v>0.07428999999999999</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.046</v>
+        <v>0.074</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.014</v>
+        <v>0.027</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.535</v>
+        <v>0.373</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="P22" s="7" t="n">
-        <v>21063.79</v>
+        <v>0.042</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>0.721</v>
+        <v>2.232</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>FLL</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>International Game Technology</t>
+          <t>Full House Resorts</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Gaming Equipment</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Regional Operators</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.51523995</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.01112</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.13294</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0.15241</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>-1.8681101</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.00328</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="P23" s="7" t="n">
+        <v>21063.79</v>
+      </c>
+      <c r="Q23" s="7" t="n">
+        <v>0.721</v>
       </c>
     </row>
     <row r="24">
@@ -6533,180 +6113,6 @@
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>EVRI</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Everi Holdings</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Gaming Equipment</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>AGS</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>PlayAGS</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Gaming Equipment</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6724,7 +6130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6839,7 +6245,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>52.93</v>
+        <v>54.77</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6861,8 +6267,8 @@
       <c r="I2" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="J2" s="9" t="n">
-        <v>0.32</v>
+      <c r="J2" s="4" t="n">
+        <v>0.276</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>1.8</v>
@@ -6895,7 +6301,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>104.81</v>
+        <v>111.03</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6917,8 +6323,8 @@
       <c r="I3" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="J3" s="9" t="n">
-        <v>1.03</v>
+      <c r="J3" s="4" t="n">
+        <v>0.9159999999999999</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>1.72</v>
@@ -6953,7 +6359,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23.67</v>
+        <v>24.44</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6975,8 +6381,8 @@
       <c r="I4" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="J4" s="9" t="n">
-        <v>0.528</v>
+      <c r="J4" s="4" t="n">
+        <v>0.48</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -7011,7 +6417,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>99.98</v>
+        <v>104.03</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -7033,8 +6439,8 @@
       <c r="I5" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="J5" s="9" t="n">
-        <v>0.419</v>
+      <c r="J5" s="4" t="n">
+        <v>0.363</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.24</v>
@@ -7067,7 +6473,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>35.37</v>
+        <v>37.72</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -7089,8 +6495,8 @@
       <c r="I6" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="J6" s="9" t="n">
-        <v>0.206</v>
+      <c r="J6" s="4" t="n">
+        <v>0.131</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.2</v>
@@ -7125,7 +6531,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>81.06</v>
+        <v>84.55</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -7147,8 +6553,8 @@
       <c r="I7" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="J7" s="9" t="n">
-        <v>0.165</v>
+      <c r="J7" s="4" t="n">
+        <v>0.117</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.32</v>
@@ -7181,7 +6587,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>57.52</v>
+        <v>59.98</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -7203,8 +6609,8 @@
       <c r="I8" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="J8" s="9" t="n">
-        <v>0.275</v>
+      <c r="J8" s="4" t="n">
+        <v>0.223</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>3.89</v>
@@ -7237,7 +6643,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>83.76000000000001</v>
+        <v>85.87</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -7259,8 +6665,8 @@
       <c r="I9" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="J9" s="9" t="n">
-        <v>0.618</v>
+      <c r="J9" s="4" t="n">
+        <v>0.578</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>2.68</v>
@@ -7293,7 +6699,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19.61</v>
+        <v>19.82</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -7307,16 +6713,16 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.819672</v>
+        <v>28.997198</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.15721</v>
+        <v>37.386097</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>21.916367</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>0.47</v>
+        <v>22.051369</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0.463</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>4.19</v>
@@ -7351,7 +6757,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>26.76</v>
+        <v>27.18</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -7373,8 +6779,8 @@
       <c r="I11" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J11" s="9" t="n">
-        <v>0.194</v>
+      <c r="J11" s="4" t="n">
+        <v>0.176</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>3.8</v>
@@ -7409,7 +6815,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>10.46</v>
+        <v>10.77</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -7431,8 +6837,8 @@
       <c r="I12" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="J12" s="9" t="n">
-        <v>0.6609999999999999</v>
+      <c r="J12" s="4" t="n">
+        <v>0.613</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>4.92</v>
@@ -7465,7 +6871,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -7487,8 +6893,8 @@
       <c r="I13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J13" s="9" t="n">
-        <v>0.198</v>
+      <c r="J13" s="4" t="n">
+        <v>0.159</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.71</v>
@@ -7514,16 +6920,16 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MLCO</t>
+          <t>BRSL</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Melco Resorts</t>
+          <t>Brightstar Lottery</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>5.46</v>
+        <v>13.23</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -7531,57 +6937,55 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1.84615</v>
+        <v>2</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>9.27308</v>
+        <v>18.08</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>12.3</v>
+        <v>22</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>0.698</v>
+        <v>15</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0.367</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.0388</v>
+        <v>0.0226</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0</v>
+        <v>0.48116</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.32467</v>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.46126</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>7.19</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0</v>
+        <v>8.8889</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>MLCO</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Penn Entertainment</t>
+          <t>Melco Resorts</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>13.67</v>
+        <v>5.54</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7589,34 +6993,34 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>2.15</v>
+        <v>1.84615</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>19.11111</v>
+        <v>9.27308</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>24</v>
+        <v>12.3</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>0.398</v>
+        <v>6.3</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0.674</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>4.18</v>
+        <v>2.08</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.16350001</v>
+        <v>0.0388</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>0.01867</v>
+        <v>0</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0.9865699999999999</v>
+        <v>0.32467</v>
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
@@ -7630,132 +7034,132 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Monarch Casino &amp; Resort</t>
+          <t>Penn Entertainment</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>96.5</v>
+        <v>14.76</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>2.15</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>107.66667</v>
+        <v>19.11111</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>0.116</v>
+        <v>15</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>0.295</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>2.53</v>
+        <v>4.18</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.026199998</v>
+        <v>0.16350001</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.3204</v>
+        <v>0.01867</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0.64762</v>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v>1.24</v>
+        <v>0.9865699999999999</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GENI</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>Monarch Casino &amp; Resort</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4.53</v>
+        <v>99.19</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>strong_buy</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>1.35294</v>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>11.76471</v>
+        <v>107.66667</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>1.597</v>
+        <v>93</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0.08500000000000001</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>1.77</v>
+        <v>2.53</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.0636</v>
+        <v>0.026199998</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0.09754</v>
+        <v>0.3204</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.95424</v>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.64762</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>1.24</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ACEL</t>
+          <t>GENI</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Accel Entertainment</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>10.92</v>
+        <v>4.74</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -7763,34 +7167,34 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1.5</v>
+        <v>1.35294</v>
       </c>
       <c r="F18" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>11.76471</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="I18" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>0.419</v>
+      <c r="J18" s="4" t="n">
+        <v>1.482</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>3.68</v>
+        <v>1.77</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.028099999</v>
+        <v>0.0636</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.13798</v>
+        <v>0.09754</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.76087</v>
+        <v>0.95424</v>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
@@ -7804,72 +7208,74 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GDEN</t>
+          <t>ACEL</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Golden Entertainment</t>
+          <t>Accel Entertainment</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>26.2</v>
+        <v>11.33</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>30.5</v>
+        <v>15.5</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>0.164</v>
+        <v>14</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0.368</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>2.5</v>
+        <v>3.68</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.0402</v>
+        <v>0.028099999</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>0.27324</v>
+        <v>0.13798</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.68561995</v>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v>3.81</v>
+        <v>0.76087</v>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="P19" s="5" t="n">
-        <v>4.5455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BALY</t>
+          <t>GDEN</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bally's Corporation</t>
+          <t>Golden Entertainment</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>12.04</v>
+        <v>26.58</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7877,92 +7283,90 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>15.66667</v>
+        <v>30.5</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>0.301</v>
+        <v>30</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0.147</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>9.16</v>
+        <v>2.5</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.1069</v>
+        <v>0.0402</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.12553</v>
+        <v>0.27324</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.77101</v>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.68561995</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>3.81</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0</v>
+        <v>4.5455</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>INSE</t>
+          <t>BALY</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Inspired Entertainment</t>
+          <t>Bally's Corporation</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>6.11</v>
+        <v>12.34</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1.66667</v>
+        <v>3.2</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>13.33333</v>
+        <v>15.66667</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>1.182</v>
+        <v>11</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0.27</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>13.9</v>
+        <v>9.16</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.0398</v>
+        <v>0.1069</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>0.07083</v>
+        <v>0.12553</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.80924004</v>
+        <v>0.77101</v>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
@@ -7976,16 +7380,16 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FLL</t>
+          <t>INSE</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Full House Resorts</t>
+          <t>Inspired Entertainment</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2.32</v>
+        <v>6.44</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -7993,34 +7397,34 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>2.25</v>
+        <v>1.66667</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>3.25</v>
+        <v>13.33333</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>0.401</v>
+        <v>10</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>1.07</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>5.72</v>
+        <v>13.9</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.024300002</v>
+        <v>0.0398</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>0.06769</v>
+        <v>0.07083</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0.40625</v>
+        <v>0.80924004</v>
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
@@ -8034,77 +7438,59 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>FLL</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>International Game Technology</t>
+          <t>Full House Resorts</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>0.024300002</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0.06769</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
       </c>
     </row>
     <row r="24">
@@ -8178,158 +7564,6 @@
         </is>
       </c>
       <c r="P24" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>EVRI</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Everi Holdings</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>AGS</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>PlayAGS</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8347,7 +7581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8461,10 +7695,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>35.788</v>
+        <v>37.032</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>22.523405</v>
+        <v>23.306385</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -8476,7 +7710,7 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.184</v>
+        <v>-0.156</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>10.611</v>
@@ -8505,7 +7739,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.462</v>
+        <v>5.547</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -8522,7 +7756,7 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.136</v>
+        <v>0.153</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>8.688000000000001</v>
@@ -8551,10 +7785,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>10.426</v>
+        <v>10.849</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>31.840765</v>
+        <v>33.130573</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.015</v>
@@ -8568,7 +7802,7 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.183</v>
+        <v>-0.149</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>11.286</v>
@@ -8597,10 +7831,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2.221</v>
+        <v>2.253</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>11.869565</v>
+        <v>12.040652</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -8614,7 +7848,7 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-0.273</v>
+        <v>-0.262</v>
       </c>
       <c r="J6" s="7" t="n">
         <v>10.572</v>
@@ -8643,10 +7877,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>9.673999999999999</v>
+        <v>10.317</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>46.539474</v>
+        <v>49.63158</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.06</v>
@@ -8658,7 +7892,7 @@
         <v>0.1489</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.031</v>
+        <v>0.034</v>
       </c>
       <c r="J7" s="7" t="n">
         <v>16.638</v>
@@ -8705,10 +7939,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.119</v>
+        <v>6.383</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.593085</v>
+        <v>3.747784</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -8720,7 +7954,7 @@
         <v>0.87788004</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-0.057</v>
+        <v>-0.017</v>
       </c>
       <c r="J10" s="7" t="n">
         <v>7.058</v>
@@ -8749,10 +7983,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5.838</v>
+        <v>5.985</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>15.833649</v>
+        <v>16.232515</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.067</v>
@@ -8764,7 +7998,7 @@
         <v>0.35709</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>-0.252</v>
+        <v>-0.233</v>
       </c>
       <c r="J11" s="7" t="n">
         <v>11.371</v>
@@ -8793,10 +8027,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1.726</v>
+        <v>1.774</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>17.771639</v>
+        <v>18.267036</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.041</v>
@@ -8808,7 +8042,7 @@
         <v>0.19214001</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.008</v>
+        <v>0.036</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>8.614000000000001</v>
@@ -8837,10 +8071,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5.915</v>
+        <v>6.168</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.435898</v>
+        <v>19.22436</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8852,7 +8086,7 @@
         <v>1.113</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.068</v>
+        <v>-0.028</v>
       </c>
       <c r="J13" s="7" t="n">
         <v>8.372999999999999</v>
@@ -8861,7 +8095,7 @@
         <v>7.3</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>61.9</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="14">
@@ -8881,7 +8115,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.826</v>
+        <v>1.97</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8898,7 +8132,7 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.006</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>17.049</v>
@@ -8907,7 +8141,7 @@
         <v>10.8</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>42.9</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="15">
@@ -8927,7 +8161,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.702</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -8944,7 +8178,7 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.032</v>
+        <v>-0.017</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>9.414</v>
@@ -8953,18 +8187,18 @@
         <v>7.2</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>40</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FLL</t>
+          <t>BALY</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Full House Resorts</t>
+          <t>Bally's Corporation</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -8973,7 +8207,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -8981,22 +8215,22 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.034</v>
+        <v>0.054</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.15241</v>
+        <v>0.12987</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-1.8681101</v>
+        <v>-1.1563</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.258</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>12.539</v>
+        <v>18.843</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>9</v>
+        <v>12.9</v>
       </c>
       <c r="L16" s="7" t="n">
         <v>22.9</v>
@@ -9005,12 +8239,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BALY</t>
+          <t>FLL</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Bally's Corporation</t>
+          <t>Full House Resorts</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -9019,7 +8253,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.592</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -9027,25 +8261,25 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.054</v>
+        <v>0.034</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.12987</v>
+        <v>0.15241</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-1.1563</v>
+        <v>-1.8681101</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.276</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>18.843</v>
+        <v>12.539</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>12.9</v>
+        <v>9</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>22.9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -9083,10 +8317,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.289</v>
+        <v>5.446</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>24.904762</v>
+        <v>25.642859</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -9098,7 +8332,7 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.09699999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>9.948</v>
@@ -9127,10 +8361,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.804</v>
+        <v>5.866</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>54.47222</v>
+        <v>55.055553</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -9142,7 +8376,7 @@
         <v>0.10515001</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.159</v>
+        <v>-0.15</v>
       </c>
       <c r="J21" s="7" t="n">
         <v>11.009</v>
@@ -9171,10 +8405,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4.819</v>
+        <v>4.982</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>66.77419</v>
+        <v>69.03225999999999</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -9186,7 +8420,7 @@
         <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.108</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
@@ -9219,7 +8453,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>11.782</v>
+        <v>12.166</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -9236,7 +8470,7 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.336</v>
+        <v>-0.315</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>45.556</v>
@@ -9265,7 +8499,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.372</v>
+        <v>19.462</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -9282,7 +8516,7 @@
         <v>-0.038829997</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-0.52</v>
+        <v>-0.491</v>
       </c>
       <c r="J24" s="7" t="n">
         <v>14.097</v>
@@ -9311,7 +8545,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.165</v>
+        <v>1.218</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -9328,7 +8562,7 @@
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.58</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="J25" s="7" t="n">
         <v>-7.181</v>
@@ -9363,12 +8597,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>ACEL</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>International Game Technology</t>
+          <t>Accel Entertainment</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -9377,54 +8611,42 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>18.883333</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.14208001</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.19236</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-0.004</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>6.422</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>4.5</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>80</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ACEL</t>
+          <t>BRSL</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Accel Entertainment</t>
+          <t>Brightstar Lottery</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -9433,42 +8655,44 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>18.199999</v>
+        <v>2.441</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.075</v>
+        <v>0.026</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.14208001</v>
+        <v>0.35125</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.19236</v>
+        <v>0.07395</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>6.422</v>
+        <v>6.721</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>56.7</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>EVRI</t>
+          <t>INSE</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Everi Holdings</t>
+          <t>Inspired Entertainment</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -9477,22 +8701,18 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0</v>
+        <v>0.174</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F30" s="5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.24433</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
@@ -9500,31 +8720,27 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-0.282</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>6.676</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>5.4</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>50</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>INSE</t>
+          <t>LNW</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Inspired Entertainment</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -9533,18 +8749,22 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F31" s="5" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.24433</v>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
@@ -9552,128 +8772,20 @@
         </is>
       </c>
       <c r="I31" s="5" t="n">
-        <v>-0.319</v>
-      </c>
-      <c r="J31" s="7" t="n">
-        <v>6.676</v>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>5.4</v>
+        <v>-0.239</v>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L31" s="7" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>LNW</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Light &amp; Wonder</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Gaming Equipment</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>-0.239</v>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>AGS</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>PlayAGS</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Gaming Equipment</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L33" s="7" t="n">
-        <v>30</v>
+        <v>16.6</v>
       </c>
     </row>
   </sheetData>
@@ -9688,7 +8800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10312,6 +9424,33 @@
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Online &amp; iGaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>BRSL</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Brightstar Lottery</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Gaming Equipment</t>
         </is>
       </c>
     </row>
@@ -10327,7 +9466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10703,281 +9842,271 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MLCO</t>
+          <t>BRSL</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Melco Resorts</t>
+          <t>Brightstar Lottery</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0</v>
+        <v>0.48116</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.32467</v>
+        <v>0.46126</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.0388</v>
+        <v>0.0226</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>5850965</v>
+        <v>4092356</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>MLCO</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Penn Entertainment</t>
+          <t>Melco Resorts</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.01867</v>
+        <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.9865699999999999</v>
+        <v>0.32467</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>4.18</v>
+        <v>2.08</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.16350001</v>
+        <v>0.0388</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>21492483</v>
+        <v>5850965</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Monarch Casino &amp; Resort</t>
+          <t>Penn Entertainment</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.3204</v>
+        <v>0.01867</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.64762</v>
+        <v>0.9865699999999999</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>2.53</v>
+        <v>4.18</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.026199998</v>
+        <v>0.16350001</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>307491</v>
+        <v>21492483</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GENI</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Genius Sports</t>
+          <t>Monarch Casino &amp; Resort</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.09754</v>
+        <v>0.3204</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.95424</v>
+        <v>0.64762</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1.77</v>
+        <v>2.53</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.0636</v>
+        <v>0.026199998</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>14353083</v>
+        <v>307491</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ACEL</t>
+          <t>GENI</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Accel Entertainment</t>
+          <t>Genius Sports</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.13798</v>
+        <v>0.09754</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.76087</v>
+        <v>0.95424</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>3.68</v>
+        <v>1.77</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.028099999</v>
+        <v>0.0636</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>1414201</v>
+        <v>14353083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GDEN</t>
+          <t>ACEL</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Golden Entertainment</t>
+          <t>Accel Entertainment</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.27324</v>
+        <v>0.13798</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.68561995</v>
+        <v>0.76087</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>2.5</v>
+        <v>3.68</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.0402</v>
+        <v>0.028099999</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>640591</v>
+        <v>1414201</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BALY</t>
+          <t>GDEN</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bally's Corporation</t>
+          <t>Golden Entertainment</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.12553</v>
+        <v>0.27324</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.77101</v>
+        <v>0.68561995</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>9.16</v>
+        <v>2.5</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.1069</v>
+        <v>0.0402</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>825105</v>
+        <v>640591</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>INSE</t>
+          <t>BALY</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Inspired Entertainment</t>
+          <t>Bally's Corporation</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.07083</v>
+        <v>0.12553</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.80924004</v>
+        <v>0.77101</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>13.9</v>
+        <v>9.16</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.0398</v>
+        <v>0.1069</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>882764</v>
+        <v>825105</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FLL</t>
+          <t>INSE</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Full House Resorts</t>
+          <t>Inspired Entertainment</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.06769</v>
+        <v>0.07083</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.40625</v>
+        <v>0.80924004</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>5.72</v>
+        <v>13.9</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.024300002</v>
+        <v>0.0398</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>830872</v>
+        <v>882764</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>FLL</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>International Game Technology</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Full House Resorts</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.06769</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.024300002</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>830872</v>
       </c>
     </row>
     <row r="24">
@@ -11012,80 +10141,6 @@
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>EVRI</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Everi Holdings</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>AGS</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>PlayAGS</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11137,962 +10192,958 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1286.26</v>
+        <v>1267.17</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>1230.45</v>
+        <v>1213.06</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>1074.91</v>
+        <v>1067.79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1286.2</v>
+        <v>1273.07</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1234.78</v>
+        <v>1212.93</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>1077.26</v>
+        <v>1068.57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1292.25</v>
+        <v>1262.7</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1234.66</v>
+        <v>1208.61</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>1078.05</v>
+        <v>1061.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1281.91</v>
+        <v>1257.63</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1230.26</v>
+        <v>1207.14</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1070.45</v>
+        <v>1059.21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1276.85</v>
+        <v>1250.32</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1228.75</v>
+        <v>1198.19</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1068.61</v>
+        <v>1061.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1269.23</v>
+        <v>1255.31</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1219.65</v>
+        <v>1200.39</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1071.24</v>
+        <v>1062.85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1274.54</v>
+        <v>1255.92</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1221.89</v>
+        <v>1208.38</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1072.28</v>
+        <v>1060.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1275.17</v>
+        <v>1241.2</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1230.02</v>
+        <v>1215.57</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1070.19</v>
+        <v>1054.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1259.53</v>
+        <v>1194.25</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1237.34</v>
+        <v>1211.65</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1063.63</v>
+        <v>1035.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1211.99</v>
+        <v>1219</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>1233.35</v>
+        <v>1211.53</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1044.24</v>
+        <v>1052.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1237.25</v>
+        <v>1190.56</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1233.23</v>
+        <v>1219.54</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1061.54</v>
+        <v>1044.66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1208.44</v>
+        <v>1186.19</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1241.38</v>
+        <v>1221.46</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>1053.94</v>
+        <v>1040.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1203.95</v>
+        <v>1178.42</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1243.33</v>
+        <v>1219.01</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>1049.74</v>
+        <v>1028.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1196.19</v>
+        <v>1176.06</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1240.85</v>
+        <v>1213.02</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1037.42</v>
+        <v>1030.89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1193.91</v>
+        <v>1194.85</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1234.75</v>
+        <v>1216.33</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1040.04</v>
+        <v>1042.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1213.3</v>
+        <v>1158.48</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1238.11</v>
+        <v>1215.31</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>1051.58</v>
+        <v>1022.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1176.22</v>
+        <v>1135.11</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1237.07</v>
+        <v>1190.57</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1031.13</v>
+        <v>1005.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1152.41</v>
+        <v>1141.57</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>1211.89</v>
+        <v>1204.31</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>1014.36</v>
+        <v>1007.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1158.87</v>
+        <v>1146.68</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1225.87</v>
+        <v>1210.6</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1016.19</v>
+        <v>1015.31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1163.96</v>
+        <v>1131.66</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1232.28</v>
+        <v>1211.04</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>1024.32</v>
+        <v>1008.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1148.26</v>
+        <v>1137.45</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1232.73</v>
+        <v>1217.19</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1017.24</v>
+        <v>1014.01</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1154.02</v>
+        <v>1124.52</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>1238.99</v>
+        <v>1222.04</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>1023.01</v>
+        <v>1010.37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1140.68</v>
+        <v>1126.23</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>1243.92</v>
+        <v>1221.91</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1019.34</v>
+        <v>1002.58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1142.67</v>
+        <v>1075.05</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>1243.8</v>
+        <v>1219.49</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>1011.48</v>
+        <v>986.21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1090.78</v>
+        <v>1063.27</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>1241.33</v>
+        <v>1215.85</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>994.96</v>
+        <v>964.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1077.92</v>
+        <v>1081.02</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>1237.63</v>
+        <v>1221.9</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>973.47</v>
+        <v>974.26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1096.04</v>
+        <v>1077.56</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>1243.78</v>
+        <v>1211.56</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>982.91</v>
+        <v>963.35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1092.43</v>
+        <v>1098.46</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1233.26</v>
+        <v>1205.7</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>971.9</v>
+        <v>984.65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1113.71</v>
+        <v>1073.99</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>1227.29</v>
+        <v>1190.64</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>993.39</v>
+        <v>965.42</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1088.55</v>
+        <v>1100.56</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>1211.96</v>
+        <v>1213.48</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>973.99</v>
+        <v>983.61</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1115.79</v>
+        <v>1102.5</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>1235.21</v>
+        <v>1219.33</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>992.34</v>
+        <v>990.88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1117.9</v>
+        <v>1099.53</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>1241.17</v>
+        <v>1216.12</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>999.6799999999999</v>
+        <v>992.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1114.7</v>
+        <v>1084.93</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>1237.89</v>
+        <v>1215.83</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>1001.51</v>
+        <v>985.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1099.59</v>
+        <v>1048.31</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>1237.61</v>
+        <v>1197.05</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>993.91</v>
+        <v>950.88</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1062.6</v>
+        <v>1038.65</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>1218.49</v>
+        <v>1197.89</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>959.3200000000001</v>
+        <v>938.66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1052.71</v>
+        <v>1053.24</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>1219.35</v>
+        <v>1199.83</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>947</v>
+        <v>940.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1068.01</v>
+        <v>1086.34</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>1221.31</v>
+        <v>1205.87</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>948.83</v>
+        <v>965.9400000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1102</v>
+        <v>1081.17</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>1227.47</v>
+        <v>1202.69</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>974.52</v>
+        <v>961.27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1096.86</v>
+        <v>1081.19</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>1224.23</v>
+        <v>1211.39</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>969.8</v>
+        <v>958.9299999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1097.1</v>
+        <v>1038.2</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>1233.08</v>
+        <v>1199.02</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>967.4400000000001</v>
+        <v>937.37</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1053.44</v>
+        <v>1052.66</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>1220.49</v>
+        <v>1207.73</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>945.6900000000001</v>
+        <v>945.42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1067.81</v>
+        <v>1056.56</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>1229.36</v>
+        <v>1217.93</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>953.8099999999999</v>
+        <v>946.72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1071.76</v>
+        <v>1085.23</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>1239.74</v>
+        <v>1211.16</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>955.12</v>
+        <v>949.0599999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1101.52</v>
+        <v>1072.45</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>1232.85</v>
+        <v>1205.34</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>957.48</v>
+        <v>953.21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1088.51</v>
+        <v>1067.28</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>1226.93</v>
+        <v>1206.03</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>961.67</v>
+        <v>944.64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1083.58</v>
+        <v>1063.33</v>
       </c>
       <c r="C47" s="13" t="n">
-        <v>1227.63</v>
+        <v>1195.4</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>953.02</v>
+        <v>938.14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1079.44</v>
+        <v>1078.77</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>1216.81</v>
+        <v>1203.83</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>946.47</v>
+        <v>943.86</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1095.37</v>
+        <v>1076.55</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>1225.39</v>
+        <v>1197.12</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>952.24</v>
+        <v>937.88</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1093.12</v>
+        <v>1045.24</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>1218.56</v>
+        <v>1181.43</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>946.21</v>
+        <v>928.27</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1061.17</v>
+        <v>1046.71</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>1202.59</v>
+        <v>1191.78</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>936.51</v>
+        <v>930.35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1062.83</v>
+        <v>1045.71</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>1213.12</v>
+        <v>1189.86</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>938.61</v>
+        <v>928.53</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1062.15</v>
+        <v>1060.13</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>1211.17</v>
+        <v>1188.37</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>936.77</v>
+        <v>932.95</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1076.79</v>
+        <v>1046.12</v>
       </c>
       <c r="C54" s="13" t="n">
-        <v>1209.65</v>
+        <v>1170.33</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>941.23</v>
+        <v>921.78</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1062.96</v>
+        <v>1048.15</v>
       </c>
       <c r="C55" s="13" t="n">
-        <v>1191.28</v>
+        <v>1163.7</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>929.96</v>
+        <v>919.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1064.93</v>
+        <v>1040.67</v>
       </c>
       <c r="C56" s="13" t="n">
-        <v>1184.54</v>
+        <v>1175.54</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>927.86</v>
+        <v>916.84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1056.94</v>
+        <v>1052.87</v>
       </c>
       <c r="C57" s="13" t="n">
-        <v>1196.6</v>
+        <v>1178.64</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>924.98</v>
+        <v>916.0599999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1069.58</v>
+        <v>1044.99</v>
       </c>
       <c r="C58" s="13" t="n">
-        <v>1199.74</v>
+        <v>1162.19</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>924.1900000000001</v>
+        <v>905.9299999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1061.65</v>
+        <v>1057.51</v>
       </c>
       <c r="C59" s="13" t="n">
-        <v>1183</v>
+        <v>1159.33</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>913.97</v>
+        <v>912.9400000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1074.28</v>
+        <v>1029.53</v>
       </c>
       <c r="C60" s="13" t="n">
-        <v>1180.09</v>
+        <v>1142.71</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>921.05</v>
+        <v>885.41</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1045.62</v>
-      </c>
-      <c r="C61" s="13" t="n">
-        <v>1163.17</v>
-      </c>
-      <c r="D61" s="13" t="n">
-        <v>893.28</v>
-      </c>
+        <v>1067.69</v>
+      </c>
+      <c r="C61" s="13" t="n"/>
+      <c r="D61" s="13" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
@@ -12101,7 +11152,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1045.62</v>
+        <v>1067.69</v>
       </c>
     </row>
     <row r="64">
@@ -12112,7 +11163,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-17.96%</t>
+          <t>-14.95%</t>
         </is>
       </c>
     </row>
@@ -12123,7 +11174,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66">
@@ -12133,7 +11184,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>134.7</v>
+        <v>142.4</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.77</v>
+        <v>54</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.034762897</v>
+        <v>0.0202154</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,34 +670,34 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.223</v>
+        <v>-0.233</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>37.032</v>
+        <v>36.511</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>48.099</v>
+        <v>48.818</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.306385</v>
+        <v>22.978724</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.576026</v>
+        <v>14.371104</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>10.611</v>
+        <v>10.77</v>
       </c>
       <c r="N2" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>0.888</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.347</v>
+        <v>0.328</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>-0.156</v>
+        <v>-0.168</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>111.03</v>
+        <v>109.38</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.059345493</v>
+        <v>0.0436027</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -729,10 +729,10 @@
         <v>99.95999999999999</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-0.6459999999999999</v>
+        <v>-0.6509999999999999</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>19.462</v>
+        <v>19.173</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>30.054</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>10.280394</v>
+        <v>10.127618</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14.097</v>
@@ -755,10 +755,10 @@
         <v>1.177</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>-0.55</v>
+        <v>-0.556</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>-0.491</v>
+        <v>-0.499</v>
       </c>
     </row>
     <row r="4">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24.44</v>
+        <v>23.96</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.03251691</v>
+        <v>0.0122518</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -790,13 +790,13 @@
         <v>21.01</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.499</v>
+        <v>-0.509</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>12.166</v>
+        <v>11.927</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>12.431</v>
+        <v>12.562</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
@@ -804,22 +804,22 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>12.557159</v>
+        <v>12.310537</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>45.556</v>
+        <v>46.034</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>1.682</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>-0.397</v>
+        <v>-0.409</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>-0.315</v>
+        <v>-0.328</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>104.03</v>
+        <v>101.13</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.040508056</v>
+        <v>0.0115022</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,22 +851,22 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.228</v>
+        <v>-0.249</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.849</v>
+        <v>10.546</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>19.746</v>
+        <v>19.864</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>33.130573</v>
+        <v>32.207005</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>17.508251</v>
+        <v>17.02018</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>11.286</v>
+        <v>11.354</v>
       </c>
       <c r="N5" s="7" t="n">
         <v>9.1</v>
@@ -875,10 +875,10 @@
         <v>1.034</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.237</v>
+        <v>0.202</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>-0.149</v>
+        <v>-0.173</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.72</v>
+        <v>36.95</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.066440554</v>
+        <v>0.04467069999999999</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,34 +910,34 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.061</v>
+        <v>-0.08</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10.317</v>
+        <v>10.106</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>39.176</v>
+        <v>39.58</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>49.63158</v>
+        <v>48.618423</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>16.098263</v>
+        <v>15.769639</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>16.638</v>
+        <v>16.81</v>
       </c>
       <c r="N6" s="7" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>1.396</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.163</v>
+        <v>0.14</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.034</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.55</v>
+        <v>81.94</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.043054595</v>
+        <v>0.0108562</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -969,19 +969,19 @@
         <v>58.94</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.08900000000000001</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.383</v>
+        <v>6.186</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>8.476000000000001</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.747784</v>
+        <v>3.6320925</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.377531</v>
+        <v>10.057183</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>7.058</v>
@@ -993,10 +993,10 @@
         <v>1.22</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.233</v>
+        <v>0.195</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>-0.017</v>
+        <v>-0.047</v>
       </c>
     </row>
     <row r="8">
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>59.98</v>
+        <v>58.08</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.042767715</v>
+        <v>0.9735770000000001</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1028,22 +1028,22 @@
         <v>35.09</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.131</v>
+        <v>-0.158</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.168</v>
+        <v>5.972</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>6.814</v>
+        <v>6.847</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>19.22436</v>
+        <v>18.615385</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>18.253584</v>
+        <v>17.675362</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>8.372999999999999</v>
+        <v>8.413</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>7.3</v>
@@ -1052,10 +1052,10 @@
         <v>1.453</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.403</v>
+        <v>0.359</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>-0.028</v>
+        <v>-0.059</v>
       </c>
     </row>
     <row r="9">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.87</v>
+        <v>84.62</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.025191028</v>
+        <v>0.0102674</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>118.46</v>
@@ -1087,19 +1087,19 @@
         <v>80.23999999999999</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.275</v>
+        <v>-0.286</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.985</v>
+        <v>5.898</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>10.878</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.232515</v>
+        <v>15.99622</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>11.564921</v>
+        <v>11.396572</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>11.371</v>
@@ -1111,10 +1111,10 @@
         <v>0.66</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>-0.242</v>
+        <v>-0.253</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>-0.233</v>
+        <v>-0.244</v>
       </c>
     </row>
     <row r="10">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0.010708776</v>
+        <v>19.53</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>-0.4079550000000001</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>32.22</v>
@@ -1146,154 +1146,154 @@
         <v>15.725</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.385</v>
+        <v>-0.394</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.866</v>
+        <v>5.78</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>5.587</v>
+        <v>5.563</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>55.055553</v>
+        <v>54.25</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>24.113943</v>
+        <v>23.811478</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>11.009</v>
+        <v>10.962</v>
       </c>
       <c r="N10" s="7" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>2.002</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>-0.138</v>
+        <v>-0.151</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>-0.15</v>
+        <v>-0.163</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>27.18</v>
+        <v>10.68</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.015508184</v>
+        <v>0.0210325</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>31.58</v>
+        <v>14.38</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>17.86</v>
+        <v>5.59</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.139</v>
+        <v>-0.257</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.547</v>
+        <v>5.4</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>30.363</v>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>4.993</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>25.428574</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>29.378378</v>
+        <v>12.312517</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>8.688000000000001</v>
+        <v>10.175</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>1.977</v>
-      </c>
-      <c r="P11" s="9" t="n">
-        <v>-0.034</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>0.153</v>
+        <v>1.1</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="Q11" s="9" t="n">
+        <v>-0.078</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0.02963675</v>
+        <v>26.44</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>-0.0119581</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>14.38</v>
+        <v>31.58</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>5.59</v>
+        <v>17.86</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.251</v>
+        <v>-0.163</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.446</v>
+        <v>5.397</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>4.882</v>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>25.642859</v>
+        <v>30.298</v>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L12" s="7" t="n">
-        <v>12.416274</v>
+        <v>28.583784</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>9.948</v>
+        <v>8.669</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0.5479999999999999</v>
-      </c>
-      <c r="Q12" s="9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.977</v>
+      </c>
+      <c r="P12" s="9" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>0.122</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.4</v>
+        <v>21.75</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.033816369</v>
+        <v>0.0507246</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.055</v>
+        <v>-0.04</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>4.982</v>
+        <v>5.063</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>69.03225999999999</v>
+        <v>70.16128999999999</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>28.59701</v>
+        <v>29.064718</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.887</v>
+        <v>0.9179999999999999</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.108</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="14">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13.23</v>
+        <v>13.05</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.034401844</v>
+        <v>0.0203284</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>18.57</v>
@@ -1390,10 +1390,10 @@
         <v>12.53</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-0.288</v>
+        <v>-0.297</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.441</v>
+        <v>2.408</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>5.928</v>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="L14" s="7" t="n">
-        <v>12.277966</v>
+        <v>12.110919</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>6.721</v>
@@ -1416,10 +1416,10 @@
         <v>1.082</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>-0.016</v>
+        <v>-0.03</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>-0.12</v>
+        <v>-0.132</v>
       </c>
     </row>
     <row r="15">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.54</v>
+        <v>5.47</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.014413931</v>
+        <v>0.183146</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>10.15</v>
@@ -1451,22 +1451,22 @@
         <v>4.55</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.454</v>
+        <v>-0.461</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.253</v>
+        <v>2.225</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>12.751</v>
+        <v>12.762</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>12.040652</v>
+        <v>11.891304</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>6.961752</v>
+        <v>6.8754005</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>10.572</v>
+        <v>10.582</v>
       </c>
       <c r="N15" s="7" t="n">
         <v>8.4</v>
@@ -1475,10 +1475,10 @@
         <v>0.603</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>-0.006</v>
+        <v>-0.018</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>-0.262</v>
+        <v>-0.272</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.76</v>
+        <v>14.44</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.079370885</v>
+        <v>0.0563277</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>20.61</v>
@@ -1510,13 +1510,13 @@
         <v>11.65</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.284</v>
+        <v>-0.299</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.97</v>
+        <v>1.928</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>12.313</v>
+        <v>12.411</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
@@ -1524,22 +1524,22 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>8.477302999999999</v>
+        <v>8.296322999999999</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>17.049</v>
+        <v>17.184</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>1.364</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>-0.15</v>
+        <v>-0.168</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>-0.006</v>
+        <v>-0.028</v>
       </c>
     </row>
     <row r="17">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>99.19</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.027875674</v>
+        <v>0.0182384</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>113.88</v>
@@ -1571,34 +1571,34 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.129</v>
+        <v>-0.137</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.774</v>
+        <v>1.757</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.643</v>
+        <v>1.674</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>18.267036</v>
+        <v>18.095766</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>16.684608</v>
+        <v>16.528175</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>8.614000000000001</v>
+        <v>8.779</v>
       </c>
       <c r="N17" s="7" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>1.376</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.238</v>
+        <v>0.226</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="18">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.045253844</v>
+        <v>0.0375275</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.73</v>
@@ -1630,13 +1630,13 @@
         <v>4.51</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.655</v>
+        <v>-0.6579999999999999</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.218</v>
+        <v>1.209</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.866</v>
+        <v>0.908</v>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>4.7828283</v>
+        <v>4.7474747</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>-7.181</v>
+        <v>-7.528</v>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
         <v>1.993</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>-0.5710000000000001</v>
+        <v>-0.574</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5639999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.33</v>
+        <v>11.26</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.037545774</v>
+        <v>0.0311355</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>13.31</v>
@@ -1693,34 +1693,34 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.149</v>
+        <v>-0.154</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.214</v>
+        <v>1.242</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>18.883333</v>
+        <v>18.766666</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>12.235025</v>
+        <v>12.159433</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>6.422</v>
+        <v>6.569</v>
       </c>
       <c r="N19" s="7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>1.07</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.114</v>
+        <v>0.107</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>-0.004</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="20">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.58</v>
+        <v>26.36</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.014503784</v>
+        <v>0.610686</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>32.74</v>
@@ -1752,13 +1752,13 @@
         <v>19.57</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.188</v>
+        <v>-0.195</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.702</v>
+        <v>0.696</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.149</v>
+        <v>1.153</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>21.966942</v>
+        <v>21.785124</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>9.414</v>
+        <v>9.449</v>
       </c>
       <c r="N20" s="7" t="n">
         <v>7.2</v>
@@ -1778,10 +1778,10 @@
         <v>1.412</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>-0.016</v>
+        <v>-0.024</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>-0.017</v>
+        <v>-0.026</v>
       </c>
     </row>
     <row r="21">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>12.34</v>
+        <v>12.11</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.02491696</v>
+        <v>0.581393</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>20.74</v>
@@ -1813,10 +1813,10 @@
         <v>8.455</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.405</v>
+        <v>-0.416</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.607</v>
+        <v>0.595</v>
       </c>
       <c r="J21" s="6" t="n">
         <v>6.095</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>-8.281879</v>
+        <v>-14.950617</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>18.843</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="P21" s="9" t="n">
-        <v>-0.296</v>
+        <v>-0.31</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>-0.258</v>
+        <v>-0.272</v>
       </c>
     </row>
     <row r="22">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.44</v>
+        <v>6.5</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.054009805</v>
+        <v>0.06382979999999999</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>9.949999999999999</v>
@@ -1876,13 +1876,13 @@
         <v>6.1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.353</v>
+        <v>-0.347</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.174</v>
+        <v>0.176</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.496</v>
+        <v>0.507</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
@@ -1890,22 +1890,22 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>8.596294</v>
+        <v>8.676384000000001</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>6.676</v>
+        <v>6.818</v>
       </c>
       <c r="N22" s="7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>1.206</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>-0.296</v>
+        <v>-0.29</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>-0.282</v>
+        <v>-0.275</v>
       </c>
     </row>
     <row r="23">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.77</v>
+        <v>54</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.034762897</v>
+        <v>0.0202154</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.156</v>
+        <v>-0.168</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.347</v>
+        <v>0.328</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>53.7</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.051</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.031</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.223</v>
+        <v>-0.233</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
@@ -2199,28 +2199,28 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>111.03</v>
+        <v>109.38</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.059345493</v>
+        <v>0.0436027</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0.491</v>
+        <v>-0.499</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.55</v>
+        <v>-0.556</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>-56</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.228</v>
+        <v>-0.24</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.517</v>
+        <v>-0.524</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.6459999999999999</v>
+        <v>-0.6509999999999999</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>1.177</v>
@@ -2246,28 +2246,28 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24.44</v>
+        <v>23.96</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.03251691</v>
+        <v>0.0122518</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.315</v>
+        <v>-0.328</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.397</v>
+        <v>-0.409</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>-35.6</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.1</v>
+        <v>-0.118</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.316</v>
+        <v>-0.329</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.499</v>
+        <v>-0.509</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
@@ -2293,28 +2293,28 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>104.03</v>
+        <v>101.13</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.040508056</v>
+        <v>0.0115022</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.149</v>
+        <v>-0.173</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.237</v>
+        <v>0.202</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>35.3</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.053</v>
+        <v>-0.08</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.09</v>
+        <v>-0.115</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.228</v>
+        <v>-0.249</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>1.034</v>
@@ -2340,28 +2340,28 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.72</v>
+        <v>36.95</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.066440554</v>
+        <v>0.04467069999999999</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.034</v>
+        <v>0.013</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.163</v>
+        <v>0.14</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>11.9</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.064</v>
+        <v>0.043</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.073</v>
+        <v>0.051</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.061</v>
+        <v>-0.08</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>1.396</v>
@@ -2387,28 +2387,28 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.55</v>
+        <v>81.94</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.043054595</v>
+        <v>0.0108562</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.047</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.233</v>
+        <v>0.195</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.024</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.021</v>
+        <v>-0.01</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.08900000000000001</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>1.22</v>
@@ -2434,28 +2434,28 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>59.98</v>
+        <v>58.08</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.042767715</v>
+        <v>0.9735770000000001</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.059</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.403</v>
+        <v>0.359</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.058</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.022</v>
+        <v>-0.011</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.131</v>
+        <v>-0.158</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>1.453</v>
@@ -2481,28 +2481,28 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.87</v>
+        <v>84.62</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.025191028</v>
+        <v>0.0102674</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.233</v>
+        <v>-0.244</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.242</v>
+        <v>-0.253</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.107</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.149</v>
+        <v>-0.162</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.275</v>
+        <v>-0.286</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>0.66</v>
@@ -2528,28 +2528,28 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.82</v>
+        <v>19.53</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.010708776</v>
+        <v>-0.4079550000000001</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.163</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.138</v>
+        <v>-0.151</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>-27.9</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.078</v>
+        <v>0.063</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-0.191</v>
+        <v>-0.203</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.385</v>
+        <v>-0.394</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>2.002</v>
@@ -2561,95 +2561,95 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>27.18</v>
+        <v>10.68</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.015508184</v>
+        <v>0.0210325</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.153</v>
+        <v>-0.078</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.034</v>
+        <v>0.535</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-23</v>
+        <v>27.9</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.159</v>
+        <v>0.062</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.102</v>
+        <v>-0.049</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.139</v>
+        <v>-0.257</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>1.977</v>
+        <v>1.1</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>6358500</v>
+        <v>1926430</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.77</v>
+        <v>26.44</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.02963675</v>
+        <v>-0.0119581</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.5479999999999999</v>
+        <v>-0.06</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>27.9</v>
+        <v>-23.1</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.128</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.04099999999999999</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.251</v>
+        <v>-0.163</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>1.1</v>
+        <v>1.977</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>1926430</v>
+        <v>6358500</v>
       </c>
     </row>
     <row r="13">
@@ -2669,28 +2669,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.4</v>
+        <v>21.75</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.033816369</v>
+        <v>0.0507246</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.108</v>
+        <v>0.126</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.887</v>
+        <v>0.9179999999999999</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.138</v>
+        <v>0.156</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.055</v>
+        <v>-0.04</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2716,28 +2716,28 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13.23</v>
+        <v>13.05</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.034401844</v>
+        <v>0.0203284</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.12</v>
+        <v>-0.132</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.03</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.04</v>
+        <v>-0.053</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.144</v>
+        <v>-0.155</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-0.288</v>
+        <v>-0.297</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>1.082</v>
@@ -2763,28 +2763,28 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.54</v>
+        <v>5.47</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.014413931</v>
+        <v>0.183146</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.262</v>
+        <v>-0.272</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.018</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.08</v>
+        <v>-0.091</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.294</v>
+        <v>-0.303</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.454</v>
+        <v>-0.461</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>0.603</v>
@@ -2810,28 +2810,28 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.76</v>
+        <v>14.44</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.079370885</v>
+        <v>0.0563277</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.028</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.168</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>-19.2</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.048</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.091</v>
+        <v>-0.111</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.284</v>
+        <v>-0.299</v>
       </c>
       <c r="L16" s="8" t="n">
         <v>1.364</v>
@@ -2857,28 +2857,28 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>99.19</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.027875674</v>
+        <v>0.0182384</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.238</v>
+        <v>0.226</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>20.7</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.045</v>
+        <v>0.036</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.129</v>
+        <v>-0.137</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.376</v>
@@ -2904,28 +2904,28 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.045253844</v>
+        <v>0.0375275</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.5710000000000001</v>
+        <v>-0.574</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>-31.1</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.342</v>
+        <v>-0.347</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.536</v>
+        <v>-0.54</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.655</v>
+        <v>-0.6579999999999999</v>
       </c>
       <c r="L18" s="8" t="n">
         <v>1.993</v>
@@ -2951,28 +2951,28 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.33</v>
+        <v>11.26</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.037545774</v>
+        <v>0.0311355</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.01</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.114</v>
+        <v>0.107</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>-1.2</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.003</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.149</v>
+        <v>-0.154</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.07</v>
@@ -2998,28 +2998,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.58</v>
+        <v>26.36</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.014503784</v>
+        <v>0.610686</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.026</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.024</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>5.3</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.049</v>
+        <v>-0.057</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.019</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.188</v>
+        <v>-0.195</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>1.412</v>
@@ -3045,28 +3045,28 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>12.34</v>
+        <v>12.11</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.02491696</v>
+        <v>0.581393</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.258</v>
+        <v>-0.272</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.296</v>
+        <v>-0.31</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.166</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.08900000000000001</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.405</v>
+        <v>-0.416</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -3094,28 +3094,28 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.44</v>
+        <v>6.5</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.054009805</v>
+        <v>0.06382979999999999</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.282</v>
+        <v>-0.275</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.296</v>
+        <v>-0.29</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.231</v>
+        <v>-0.224</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.248</v>
+        <v>-0.241</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.353</v>
+        <v>-0.347</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.206</v>
@@ -3200,7 +3200,7 @@
         <v>-0.239</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>-293.6</v>
+        <v>-288.9</v>
       </c>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
@@ -3342,31 +3342,31 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.77</v>
+        <v>54</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>37.032</v>
+        <v>36.511</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>23.306385</v>
+        <v>22.978724</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.576026</v>
+        <v>14.371104</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>10.611</v>
+        <v>10.77</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>3.695</v>
+        <v>3.75</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.24703</v>
+        <v>22.920204</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.8448865</v>
+        <v>2.8048906</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>111.03</v>
+        <v>109.38</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>19.462</v>
+        <v>19.173</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>10.280394</v>
+        <v>10.127618</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>14.097</v>
@@ -3418,10 +3418,10 @@
         <v>1.834</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.1525784</v>
+        <v>2.1205893</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1879625</v>
+        <v>1.1703084</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24.44</v>
+        <v>23.96</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>12.166</v>
+        <v>11.927</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3461,22 +3461,22 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>12.557159</v>
+        <v>12.310537</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>45.556</v>
+        <v>46.034</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>2.053</v>
+        <v>2.075</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>19.153605</v>
+        <v>18.777428</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>2.0093336</v>
+        <v>1.9698704</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3505,31 +3505,31 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>104.03</v>
+        <v>101.13</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.849</v>
+        <v>10.546</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>33.130573</v>
+        <v>32.207005</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>17.508251</v>
+        <v>17.02018</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>11.286</v>
+        <v>11.354</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>9.1</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>2.766</v>
+        <v>2.783</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-38.701637</v>
+        <v>-37.62277</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.5198523</v>
+        <v>1.477484</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3558,31 +3558,31 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.72</v>
+        <v>36.95</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.317</v>
+        <v>10.106</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>49.63158</v>
+        <v>48.618423</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>16.098263</v>
+        <v>15.769639</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>16.638</v>
+        <v>16.81</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>2.234</v>
+        <v>2.257</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>4.0097804</v>
+        <v>3.9279263</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.5882569</v>
+        <v>0.57624847</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3611,16 +3611,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.55</v>
+        <v>81.94</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.383</v>
+        <v>6.186</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.747784</v>
+        <v>3.6320925</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.377531</v>
+        <v>10.057183</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>7.058</v>
@@ -3632,10 +3632,10 @@
         <v>2.071</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.4753344</v>
+        <v>2.3989227</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5598445</v>
+        <v>1.5116932</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>22.56</v>
@@ -3664,31 +3664,31 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>59.98</v>
+        <v>58.08</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.168</v>
+        <v>5.972</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>19.22436</v>
+        <v>18.615385</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>18.253584</v>
+        <v>17.675362</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>8.372999999999999</v>
+        <v>8.413</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>7.3</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>3.388</v>
+        <v>3.404</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.791714</v>
+        <v>16.259798</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>3.066174</v>
+        <v>2.9690464</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>3.12</v>
@@ -3717,16 +3717,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.87</v>
+        <v>84.62</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.985</v>
+        <v>5.898</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>16.232515</v>
+        <v>15.99622</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>11.564921</v>
+        <v>11.396572</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>11.371</v>
@@ -3738,10 +3738,10 @@
         <v>3.718</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>5.9192114</v>
+        <v>5.8330464</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.0454657</v>
+        <v>2.01569</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>5.29</v>
@@ -3770,148 +3770,148 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.82</v>
+        <v>19.53</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.866</v>
+        <v>5.78</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>55.055553</v>
+        <v>54.25</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>24.113943</v>
+        <v>23.811478</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>11.009</v>
+        <v>10.962</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>4.331</v>
+        <v>4.312</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.251629</v>
+        <v>5.1857567</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>4.5472255</v>
+        <v>4.480692</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.36</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.8219311</v>
+        <v>0.82019275</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>3.7740672</v>
+        <v>3.7660851</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>27.18</v>
+        <v>10.68</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.547</v>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>5.4</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>25.428574</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>29.378378</v>
+        <v>12.312517</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>8.688000000000001</v>
+        <v>10.175</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>2.643</v>
+        <v>2.131</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>1.5714451</v>
+        <v>7.2505093</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.4829038</v>
+        <v>2.3049138</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-2.42</v>
+        <v>0.42</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.925</v>
+        <v>0.86741</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>17.293</v>
+        <v>1.473</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.77</v>
+        <v>26.44</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.446</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>25.642859</v>
+        <v>5.397</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>12.416274</v>
+        <v>28.583784</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>9.948</v>
+        <v>8.669</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>2.084</v>
+        <v>2.638</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>7.311609</v>
+        <v>1.5289425</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>2.324337</v>
+        <v>0.46984276</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.42</v>
+        <v>-2.42</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.86741</v>
+        <v>0.925</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>1.473</v>
+        <v>17.293</v>
       </c>
     </row>
     <row r="13">
@@ -3931,16 +3931,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.4</v>
+        <v>21.75</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4.982</v>
+        <v>5.063</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>69.03225999999999</v>
+        <v>70.16128999999999</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>28.59701</v>
+        <v>29.064718</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>14.528173</v>
+        <v>14.765783</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.3912787</v>
+        <v>4.4630985</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13.23</v>
+        <v>13.05</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.441</v>
+        <v>2.408</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>12.277966</v>
+        <v>12.110919</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>6.721</v>
@@ -4013,10 +4013,10 @@
         <v>2.361</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>2.8251119</v>
+        <v>2.7866752</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.9722474</v>
+        <v>0.9590196</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>-0.01</v>
@@ -4045,31 +4045,31 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.54</v>
+        <v>5.47</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.253</v>
+        <v>2.225</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>12.040652</v>
+        <v>11.891304</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.961752</v>
+        <v>6.8754005</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>10.572</v>
+        <v>10.582</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>8.4</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>2.47</v>
+        <v>2.472</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1.7357255</v>
+        <v>-1.7141961</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.4363681</v>
+        <v>0.43095556</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.46</v>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.76</v>
+        <v>14.44</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.97</v>
+        <v>1.928</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -4109,22 +4109,22 @@
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>8.477302999999999</v>
+        <v>8.296322999999999</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>17.049</v>
+        <v>17.184</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.769</v>
+        <v>1.783</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>1.0156949</v>
+        <v>0.9940111</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.2830736</v>
+        <v>0.27703032</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-5.83</v>
@@ -4153,31 +4153,31 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>99.19</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.774</v>
+        <v>1.757</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>18.267036</v>
+        <v>18.095766</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>16.684608</v>
+        <v>16.528175</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>8.614000000000001</v>
+        <v>8.779</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>3.014</v>
+        <v>3.071</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>3.2872672</v>
+        <v>3.2564461</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3.2545276</v>
+        <v>3.2240133</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>5.43</v>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1.218</v>
+        <v>1.209</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4.7828283</v>
+        <v>4.7474747</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-7.181</v>
+        <v>-7.528</v>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
@@ -4228,13 +4228,13 @@
         </is>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.293</v>
+        <v>1.356</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>1.6099967</v>
+        <v>1.5980958</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>1.8194169</v>
+        <v>1.8059682</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>-0.44</v>
@@ -4263,31 +4263,31 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.33</v>
+        <v>11.26</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>18.883333</v>
+        <v>18.766666</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>12.235025</v>
+        <v>12.159433</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>6.422</v>
+        <v>6.569</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.912</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>3.4574306</v>
+        <v>3.4360697</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.7083203</v>
+        <v>0.70394415</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0.6</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.58</v>
+        <v>26.36</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.702</v>
+        <v>0.696</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -4327,22 +4327,22 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>21.966942</v>
+        <v>21.785124</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>9.414</v>
+        <v>9.449</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>7.2</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.81</v>
+        <v>1.816</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.6536021</v>
+        <v>1.6399155</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>1.1051636</v>
+        <v>1.0960162</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.23</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>12.34</v>
+        <v>12.11</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.607</v>
+        <v>0.595</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-8.281879</v>
+        <v>-14.950617</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>18.843</v>
@@ -4394,16 +4394,16 @@
         <v>2.447</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>1.162506</v>
+        <v>1.1408384</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.24355991</v>
+        <v>0.23902032</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>-12.58</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-1.49</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>10.615</v>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.44</v>
+        <v>6.5</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.174</v>
+        <v>0.176</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -4437,22 +4437,22 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>8.596294</v>
+        <v>8.676384000000001</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>6.676</v>
+        <v>6.818</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.631</v>
+        <v>1.666</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-10.679934</v>
+        <v>-10.779436</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.57304716</v>
+        <v>0.5783861</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>-0.58</v>
@@ -5251,121 +5251,121 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>11.486</v>
+        <v>2.343</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.042</v>
+        <v>0.178</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.5</v>
+        <v>0.51058</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.1893</v>
+        <v>0.23518999</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.043709997</v>
+        <v>0.09804</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.30427998</v>
+        <v>0.20945999</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.10840999</v>
+        <v>0.32813</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.04044</v>
+        <v>0.23642</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>3.495</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.491</v>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>25.622</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.887</v>
+        <v>0.478</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>695.117</v>
+        <v>9.69</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2.343</v>
+        <v>11.486</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.178</v>
+        <v>0.042</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.51058</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.23518999</v>
+        <v>0.1893</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.09804</v>
+        <v>-0.043709997</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.20945999</v>
+        <v>0.30427998</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.32813</v>
+        <v>-0.10840999</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.23642</v>
+        <v>0.04044</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>3.495</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0.6929999999999999</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.07199999999999999</v>
+        <v>25.622</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.478</v>
+        <v>0.887</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>9.69</v>
+        <v>695.117</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>1.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13">
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>54.77</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>58</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.276</v>
+        <v>0.294</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>1.8</v>
@@ -6301,7 +6301,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>111.03</v>
+        <v>109.38</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.9159999999999999</v>
+        <v>0.945</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>1.72</v>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>24.44</v>
+        <v>23.96</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>104.03</v>
+        <v>101.13</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.363</v>
+        <v>0.402</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.24</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37.72</v>
+        <v>36.95</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.131</v>
+        <v>0.155</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.2</v>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>84.55</v>
+        <v>81.94</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>84</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.117</v>
+        <v>0.153</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.32</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>59.98</v>
+        <v>58.08</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>59</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.223</v>
+        <v>0.263</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>3.89</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>85.87</v>
+        <v>84.62</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>110</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.578</v>
+        <v>0.601</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>2.68</v>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19.82</v>
+        <v>19.53</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -6713,16 +6713,16 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.997198</v>
+        <v>28.926596</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.386097</v>
+        <v>37.29507</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>22.051369</v>
+        <v>21.99768</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.463</v>
+        <v>0.481</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>4.19</v>
@@ -6748,115 +6748,115 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>27.18</v>
+        <v>10.68</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1.82353</v>
+        <v>1.25</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>31.95778</v>
+        <v>17.375</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.176</v>
+        <v>0.627</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>3.8</v>
+        <v>4.92</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.1713</v>
+        <v>0.1039</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.010570001</v>
+        <v>0.68889</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>1.11968</v>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.19124001</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>1.63</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>0</v>
+        <v>0.2831</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>10.77</v>
+        <v>26.44</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>strong_buy</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1.25</v>
+        <v>1.82353</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>17.375</v>
+        <v>31.95778</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.613</v>
+        <v>0.209</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>4.92</v>
+        <v>3.8</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.1039</v>
+        <v>0.1713</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.68889</v>
+        <v>0.010570001</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0.19124001</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>1.63</v>
+        <v>1.11968</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.2831</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>21.4</v>
+        <v>21.75</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.159</v>
+        <v>0.14</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.71</v>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>13.23</v>
+        <v>13.05</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>15</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.367</v>
+        <v>0.385</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>2.42</v>
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5.54</v>
+        <v>5.47</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>6.3</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.674</v>
+        <v>0.695</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>2.08</v>
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14.76</v>
+        <v>14.44</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.295</v>
+        <v>0.323</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>4.18</v>
@@ -7101,7 +7101,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>99.19</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>93</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.096</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>2.53</v>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.482</v>
+        <v>1.503</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>1.77</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11.33</v>
+        <v>11.26</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.368</v>
+        <v>0.377</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>3.68</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>26.58</v>
+        <v>26.36</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>30</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.147</v>
+        <v>0.157</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>2.5</v>
@@ -7331,7 +7331,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>12.34</v>
+        <v>12.11</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>11</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.27</v>
+        <v>0.294</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>9.16</v>
@@ -7389,7 +7389,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6.44</v>
+        <v>6.5</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.07</v>
+        <v>1.051</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>13.9</v>
@@ -7695,10 +7695,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>37.032</v>
+        <v>36.511</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>23.306385</v>
+        <v>22.978724</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -7710,16 +7710,16 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.156</v>
+        <v>-0.168</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>10.611</v>
+        <v>10.77</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>82</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -7739,7 +7739,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.547</v>
+        <v>5.397</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -7756,13 +7756,13 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.153</v>
+        <v>0.122</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>8.688000000000001</v>
+        <v>8.669</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="L4" s="7" t="n">
         <v>45</v>
@@ -7771,12 +7771,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>MLCO</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Wynn Resorts</t>
+          <t>Melco Resorts</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7785,16 +7785,16 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>10.849</v>
+        <v>2.225</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>33.130573</v>
+        <v>11.891304</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.015</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.24510999</v>
+        <v>0.23358</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -7802,27 +7802,27 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.149</v>
+        <v>-0.272</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>11.286</v>
+        <v>10.582</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>41.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MLCO</t>
+          <t>MGM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Melco Resorts</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -7831,44 +7831,42 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2.253</v>
+        <v>10.106</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>12.040652</v>
+        <v>48.618423</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.23358</v>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.13426</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.1489</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-0.262</v>
+        <v>0.013</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>10.572</v>
+        <v>16.81</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>8.4</v>
+        <v>11.6</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MGM</t>
+          <t>WYNN</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Wynn Resorts</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7877,31 +7875,33 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.317</v>
+        <v>10.546</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>49.63158</v>
+        <v>32.207005</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.06</v>
+        <v>0.015</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.13426</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>0.1489</v>
+        <v>0.24510999</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.173</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>16.638</v>
+        <v>11.354</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>11.5</v>
+        <v>9.1</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>37.5</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="9">
@@ -7939,10 +7939,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.383</v>
+        <v>6.186</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.747784</v>
+        <v>3.6320925</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -7954,7 +7954,7 @@
         <v>0.87788004</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.047</v>
       </c>
       <c r="J10" s="7" t="n">
         <v>7.058</v>
@@ -7963,7 +7963,7 @@
         <v>5.9</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>71.40000000000001</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5.985</v>
+        <v>5.898</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>16.232515</v>
+        <v>15.99622</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.067</v>
@@ -7998,7 +7998,7 @@
         <v>0.35709</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>-0.233</v>
+        <v>-0.244</v>
       </c>
       <c r="J11" s="7" t="n">
         <v>11.371</v>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1.774</v>
+        <v>1.757</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>18.267036</v>
+        <v>18.095766</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.041</v>
@@ -8042,13 +8042,13 @@
         <v>0.19214001</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>8.614000000000001</v>
+        <v>8.779</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="L12" s="7" t="n">
         <v>62.7</v>
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6.168</v>
+        <v>5.972</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>19.22436</v>
+        <v>18.615385</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8086,10 +8086,10 @@
         <v>1.113</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.059</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>8.372999999999999</v>
+        <v>8.413</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>7.3</v>
@@ -8115,7 +8115,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.97</v>
+        <v>1.928</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8132,16 +8132,16 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.028</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>17.049</v>
+        <v>17.184</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>54.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="15">
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.702</v>
+        <v>0.696</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -8178,16 +8178,16 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.026</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>9.414</v>
+        <v>9.449</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>7.2</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>34.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.607</v>
+        <v>0.595</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>-1.1563</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.258</v>
+        <v>-0.272</v>
       </c>
       <c r="J16" s="7" t="n">
         <v>18.843</v>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.446</v>
+        <v>5.4</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.642859</v>
+        <v>25.428574</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -8332,13 +8332,13 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.078</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>9.948</v>
+        <v>10.175</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="L20" s="7" t="n">
         <v>66.7</v>
@@ -8361,10 +8361,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.866</v>
+        <v>5.78</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>55.055553</v>
+        <v>54.25</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -8376,13 +8376,13 @@
         <v>0.10515001</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.163</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>11.009</v>
+        <v>10.962</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>58.3</v>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4.982</v>
+        <v>5.063</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>69.03225999999999</v>
+        <v>70.16128999999999</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -8420,7 +8420,7 @@
         <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.108</v>
+        <v>0.126</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>12.166</v>
+        <v>11.927</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -8470,13 +8470,13 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.315</v>
+        <v>-0.328</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>45.556</v>
+        <v>46.034</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="L23" s="7" t="n">
         <v>52</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>19.462</v>
+        <v>19.173</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>-0.038829997</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-0.491</v>
+        <v>-0.499</v>
       </c>
       <c r="J24" s="7" t="n">
         <v>14.097</v>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.218</v>
+        <v>1.209</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -8562,10 +8562,10 @@
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>-7.181</v>
+        <v>-7.528</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
@@ -8611,10 +8611,10 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.883333</v>
+        <v>18.766666</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0.075</v>
@@ -8626,13 +8626,13 @@
         <v>0.19236</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.01</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>6.422</v>
+        <v>6.569</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L28" s="7" t="n">
         <v>69.5</v>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2.441</v>
+        <v>2.408</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>0.07395</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.12</v>
+        <v>-0.132</v>
       </c>
       <c r="J29" s="7" t="n">
         <v>6.721</v>
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.174</v>
+        <v>0.176</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
@@ -8720,13 +8720,13 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.282</v>
+        <v>-0.275</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>6.676</v>
+        <v>6.818</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L30" s="7" t="n">
         <v>20.8</v>
@@ -9761,55 +9761,55 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.010570001</v>
+        <v>0.68889</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1.11968</v>
+        <v>0.19124001</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3.8</v>
+        <v>4.92</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.1713</v>
+        <v>0.1039</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>30537844</v>
+        <v>16337061</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.68889</v>
+        <v>0.010570001</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.19124001</v>
+        <v>1.11968</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>4.92</v>
+        <v>3.8</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1039</v>
+        <v>0.1713</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>16337061</v>
+        <v>30537844</v>
       </c>
     </row>
     <row r="13">
@@ -10196,7 +10196,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1267.17</v>
+        <v>1267.92</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>1213.06</v>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1273.07</v>
+        <v>1273.82</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>1212.93</v>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1262.7</v>
+        <v>1263.51</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>1208.61</v>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1257.63</v>
+        <v>1258.49</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>1207.14</v>
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1250.32</v>
+        <v>1251.13</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>1198.19</v>
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1255.31</v>
+        <v>1256.04</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1200.39</v>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1255.92</v>
+        <v>1256.72</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1208.38</v>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1241.2</v>
+        <v>1241.94</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>1215.57</v>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1194.25</v>
+        <v>1194.87</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1211.65</v>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1219</v>
+        <v>1219.59</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1211.53</v>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1190.56</v>
+        <v>1191.13</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>1219.54</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1186.19</v>
+        <v>1186.74</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>1221.46</v>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1178.42</v>
+        <v>1178.93</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>1219.01</v>
@@ -10404,7 +10404,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1176.06</v>
+        <v>1176.59</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>1213.02</v>
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1194.85</v>
+        <v>1195.4</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>1216.33</v>
@@ -10436,7 +10436,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1158.48</v>
+        <v>1159.01</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>1215.31</v>
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1135.11</v>
+        <v>1135.68</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1190.57</v>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1141.57</v>
+        <v>1142.07</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>1204.31</v>
@@ -10484,7 +10484,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1146.68</v>
+        <v>1147.12</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>1210.6</v>
@@ -10500,7 +10500,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1131.66</v>
+        <v>1132.07</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>1211.04</v>
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1137.45</v>
+        <v>1137.87</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>1217.19</v>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1124.52</v>
+        <v>1124.98</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>1222.04</v>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1126.23</v>
+        <v>1126.66</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>1221.91</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1075.05</v>
+        <v>1075.46</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1219.49</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1063.27</v>
+        <v>1063.66</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>1215.85</v>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1081.02</v>
+        <v>1081.45</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>1221.9</v>
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1077.56</v>
+        <v>1077.92</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>1211.56</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1098.46</v>
+        <v>1098.74</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>1205.7</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1073.99</v>
+        <v>1074.24</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1190.64</v>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1100.56</v>
+        <v>1100.83</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1213.48</v>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1102.5</v>
+        <v>1102.78</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>1219.33</v>
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1099.53</v>
+        <v>1099.73</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>1216.12</v>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1084.93</v>
+        <v>1085.16</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>1215.83</v>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1048.31</v>
+        <v>1048.55</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>1197.05</v>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1038.65</v>
+        <v>1038.89</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>1197.89</v>
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1053.24</v>
+        <v>1053.54</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>1199.83</v>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1086.34</v>
+        <v>1086.67</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>1205.87</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1081.17</v>
+        <v>1081.55</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>1202.69</v>
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1081.19</v>
+        <v>1081.59</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>1211.39</v>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1038.2</v>
+        <v>1038.71</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>1199.02</v>
@@ -10836,7 +10836,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1052.66</v>
+        <v>1053.2</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>1207.73</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1056.56</v>
+        <v>1057.15</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>1217.93</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1085.23</v>
+        <v>1085.77</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>1211.16</v>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1072.45</v>
+        <v>1073.05</v>
       </c>
       <c r="C45" s="13" t="n">
         <v>1205.34</v>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1067.28</v>
+        <v>1068</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>1206.03</v>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1063.33</v>
+        <v>1064.05</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1195.4</v>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1078.77</v>
+        <v>1079.55</v>
       </c>
       <c r="C48" s="13" t="n">
         <v>1203.83</v>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1076.55</v>
+        <v>1077.3</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1197.12</v>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1045.24</v>
+        <v>1046.02</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>1181.43</v>
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1046.71</v>
+        <v>1047.49</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>1191.78</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1045.71</v>
+        <v>1046.49</v>
       </c>
       <c r="C52" s="13" t="n">
         <v>1189.86</v>
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1060.13</v>
+        <v>1060.88</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>1188.37</v>
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1046.12</v>
+        <v>1046.87</v>
       </c>
       <c r="C54" s="13" t="n">
         <v>1170.33</v>
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1048.15</v>
+        <v>1048.82</v>
       </c>
       <c r="C55" s="13" t="n">
         <v>1163.7</v>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1040.67</v>
+        <v>1041.35</v>
       </c>
       <c r="C56" s="13" t="n">
         <v>1175.54</v>
@@ -11076,7 +11076,7 @@
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1052.87</v>
+        <v>1053.53</v>
       </c>
       <c r="C57" s="13" t="n">
         <v>1178.64</v>
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1044.99</v>
+        <v>1045.66</v>
       </c>
       <c r="C58" s="13" t="n">
         <v>1162.19</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1057.51</v>
+        <v>1058.21</v>
       </c>
       <c r="C59" s="13" t="n">
         <v>1159.33</v>
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1029.53</v>
+        <v>1030.26</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>1142.71</v>
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1067.69</v>
+        <v>1051.97</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1067.69</v>
+        <v>1051.97</v>
       </c>
     </row>
     <row r="64">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-14.95%</t>
+          <t>-16.25%</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11184,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>142.4</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -732,10 +732,10 @@
         <v>-0.6509999999999999</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>19.173</v>
+        <v>19.156</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>30.054</v>
+        <v>30.856</v>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
         <v>10.127618</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>14.097</v>
+        <v>14.473</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>1.177</v>
@@ -796,7 +796,7 @@
         <v>11.927</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>12.562</v>
+        <v>12.574</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         <v>12.310537</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>46.034</v>
+        <v>46.079</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>1.682</v>
@@ -975,7 +975,7 @@
         <v>6.186</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>8.476000000000001</v>
+        <v>8.542999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.6320925</v>
@@ -984,7 +984,7 @@
         <v>10.057183</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>7.058</v>
+        <v>7.113</v>
       </c>
       <c r="N7" s="7" t="n">
         <v>5.9</v>
@@ -1093,7 +1093,7 @@
         <v>5.898</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>10.878</v>
+        <v>10.94</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>15.99622</v>
@@ -1102,10 +1102,10 @@
         <v>11.396572</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>11.371</v>
+        <v>11.435</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>0.66</v>
@@ -1396,7 +1396,7 @@
         <v>2.408</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>5.928</v>
+        <v>5.976</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
         <v>12.110919</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>6.721</v>
+        <v>6.776</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>1.082</v>
@@ -1696,7 +1696,7 @@
         <v>-0.154</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.919</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>1.242</v>
@@ -3398,7 +3398,7 @@
         <v>109.38</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>19.173</v>
+        <v>19.156</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3409,19 +3409,19 @@
         <v>10.127618</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>14.097</v>
+        <v>14.473</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.834</v>
+        <v>1.883</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>2.1205893</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1703084</v>
+        <v>1.1692576</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3464,13 +3464,13 @@
         <v>12.310537</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>46.034</v>
+        <v>46.079</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>2.075</v>
+        <v>2.077</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>18.777428</v>
@@ -3623,13 +3623,13 @@
         <v>10.057183</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>7.058</v>
+        <v>7.113</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>5.9</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>2.071</v>
+        <v>2.088</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>2.3989227</v>
@@ -3729,13 +3729,13 @@
         <v>11.396572</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>11.371</v>
+        <v>11.435</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>3.718</v>
+        <v>3.739</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>5.8330464</v>
@@ -4004,13 +4004,13 @@
         <v>12.110919</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>6.721</v>
+        <v>6.776</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>2.361</v>
+        <v>2.38</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>2.7866752</v>
@@ -4266,7 +4266,7 @@
         <v>11.26</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.919</v>
       </c>
       <c r="F19" s="7" t="n">
         <v>18.766666</v>
@@ -4287,7 +4287,7 @@
         <v>3.4360697</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.70394415</v>
+        <v>0.6901145</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0.6</v>
@@ -4400,7 +4400,7 @@
         <v>0.23902032</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-12.58</v>
+        <v>-12.65</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>-0.8100000000000001</v>
@@ -6283,7 +6283,7 @@
         <v>0.41693002</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="P2" s="5" t="n">
         <v>0.4255</v>
@@ -6455,7 +6455,7 @@
         <v>0.68557</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="P5" s="5" t="n">
         <v>0.3185</v>
@@ -6569,7 +6569,7 @@
         <v>0.73223996</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="P7" s="5" t="n">
         <v>0.0319</v>
@@ -6625,7 +6625,7 @@
         <v>0.88882005</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="P8" s="5" t="n">
         <v>0.32369998</v>
@@ -6713,13 +6713,13 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.926596</v>
+        <v>28.92324</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.29507</v>
+        <v>37.290745</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>21.99768</v>
+        <v>21.995129</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0.481</v>
@@ -6795,7 +6795,7 @@
         <v>0.19124001</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="P11" s="5" t="n">
         <v>0.2831</v>
@@ -6967,7 +6967,7 @@
         <v>0.46126</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>7.19</v>
+        <v>7.05</v>
       </c>
       <c r="P14" s="5" t="n">
         <v>8.8889</v>
@@ -7141,7 +7141,7 @@
         <v>0.64762</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P17" s="5" t="n">
         <v>0.221</v>
@@ -7313,7 +7313,7 @@
         <v>0.68561995</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="P20" s="5" t="n">
         <v>4.5455</v>
@@ -7957,7 +7957,7 @@
         <v>-0.047</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.058</v>
+        <v>7.113</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>5.9</v>
@@ -8001,10 +8001,10 @@
         <v>-0.244</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>11.371</v>
+        <v>11.435</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L11" s="7" t="n">
         <v>63.5</v>
@@ -8473,10 +8473,10 @@
         <v>-0.328</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>46.034</v>
+        <v>46.079</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="L23" s="7" t="n">
         <v>52</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>19.173</v>
+        <v>19.156</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8519,10 +8519,10 @@
         <v>-0.499</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>14.097</v>
+        <v>14.473</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="L24" s="7" t="n">
         <v>48</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.919</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>18.766666</v>
@@ -8675,10 +8675,10 @@
         <v>-0.132</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>6.721</v>
+        <v>6.776</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L29" s="7" t="n">
         <v>63.3</v>
@@ -10196,7 +10196,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1267.92</v>
+        <v>1267.98</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>1213.06</v>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1273.82</v>
+        <v>1273.89</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>1212.93</v>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1263.51</v>
+        <v>1263.57</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>1208.61</v>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1258.49</v>
+        <v>1258.56</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>1207.14</v>
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1251.13</v>
+        <v>1251.2</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>1198.19</v>
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1256.04</v>
+        <v>1256.1</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1200.39</v>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1256.72</v>
+        <v>1256.79</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1208.38</v>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1241.94</v>
+        <v>1242</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>1215.57</v>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1194.87</v>
+        <v>1194.92</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1211.65</v>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1219.59</v>
+        <v>1219.64</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1211.53</v>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1191.13</v>
+        <v>1191.17</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>1219.54</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1186.74</v>
+        <v>1186.79</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>1221.46</v>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1178.93</v>
+        <v>1178.98</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>1219.01</v>
@@ -10404,7 +10404,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1176.59</v>
+        <v>1176.64</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>1213.02</v>
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1195.4</v>
+        <v>1195.46</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>1216.33</v>
@@ -10436,7 +10436,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1159.01</v>
+        <v>1159.07</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>1215.31</v>
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1135.68</v>
+        <v>1135.73</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1190.57</v>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1142.07</v>
+        <v>1142.13</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>1204.31</v>
@@ -10484,7 +10484,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1147.12</v>
+        <v>1147.18</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>1210.6</v>
@@ -10500,7 +10500,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1132.07</v>
+        <v>1132.12</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>1211.04</v>
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1137.87</v>
+        <v>1137.93</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>1217.19</v>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1124.98</v>
+        <v>1125.04</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>1222.04</v>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1126.66</v>
+        <v>1126.72</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>1221.91</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1075.46</v>
+        <v>1075.5</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1219.49</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1063.66</v>
+        <v>1063.7</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>1215.85</v>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1081.45</v>
+        <v>1081.5</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>1221.9</v>
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1077.92</v>
+        <v>1077.98</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>1211.56</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1098.74</v>
+        <v>1098.8</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>1205.7</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1074.24</v>
+        <v>1074.29</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1190.64</v>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1100.83</v>
+        <v>1100.89</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1213.48</v>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1102.78</v>
+        <v>1102.84</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>1219.33</v>
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1099.73</v>
+        <v>1099.79</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>1216.12</v>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1085.16</v>
+        <v>1085.22</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>1215.83</v>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1048.55</v>
+        <v>1048.61</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>1197.05</v>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1038.89</v>
+        <v>1038.95</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>1197.89</v>
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1053.54</v>
+        <v>1053.61</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>1199.83</v>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1086.67</v>
+        <v>1086.74</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>1205.87</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1081.55</v>
+        <v>1081.62</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>1202.69</v>
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1081.59</v>
+        <v>1081.66</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>1211.39</v>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1038.71</v>
+        <v>1038.78</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>1199.02</v>
@@ -10836,7 +10836,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1053.2</v>
+        <v>1053.26</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>1207.73</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1057.15</v>
+        <v>1057.22</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>1217.93</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1085.77</v>
+        <v>1085.84</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>1211.16</v>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1073.05</v>
+        <v>1073.12</v>
       </c>
       <c r="C45" s="13" t="n">
         <v>1205.34</v>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1068</v>
+        <v>1068.07</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>1206.03</v>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1064.05</v>
+        <v>1064.12</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1195.4</v>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1079.55</v>
+        <v>1079.6</v>
       </c>
       <c r="C48" s="13" t="n">
         <v>1203.83</v>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1077.3</v>
+        <v>1077.36</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1197.12</v>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1046.02</v>
+        <v>1046.08</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>1181.43</v>
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1047.49</v>
+        <v>1047.55</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>1191.78</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1046.49</v>
+        <v>1046.55</v>
       </c>
       <c r="C52" s="13" t="n">
         <v>1189.86</v>
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1060.88</v>
+        <v>1060.94</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>1188.37</v>
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1046.87</v>
+        <v>1046.94</v>
       </c>
       <c r="C54" s="13" t="n">
         <v>1170.33</v>
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1048.82</v>
+        <v>1048.89</v>
       </c>
       <c r="C55" s="13" t="n">
         <v>1163.7</v>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1041.35</v>
+        <v>1041.42</v>
       </c>
       <c r="C56" s="13" t="n">
         <v>1175.54</v>
@@ -11076,7 +11076,7 @@
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1053.53</v>
+        <v>1053.6</v>
       </c>
       <c r="C57" s="13" t="n">
         <v>1178.64</v>
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1045.66</v>
+        <v>1045.73</v>
       </c>
       <c r="C58" s="13" t="n">
         <v>1162.19</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1058.21</v>
+        <v>1058.29</v>
       </c>
       <c r="C59" s="13" t="n">
         <v>1159.33</v>
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1030.26</v>
+        <v>1030.33</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>1142.71</v>
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1051.97</v>
+        <v>1052.04</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1051.97</v>
+        <v>1052.04</v>
       </c>
     </row>
     <row r="64">
@@ -11184,7 +11184,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>140</v>
+        <v>139.9</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54</v>
+        <v>54.75</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0202154</v>
+        <v>0.013888888</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,19 +670,19 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.233</v>
+        <v>-0.223</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>36.511</v>
+        <v>37.018</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>48.818</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.978724</v>
+        <v>23.297873</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.371104</v>
+        <v>14.5707035</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>10.77</v>
@@ -694,10 +694,10 @@
         <v>0.888</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.328</v>
+        <v>0.347</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>-0.168</v>
+        <v>-0.156</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>109.38</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0.0436027</v>
+        <v>107.69</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>-0.015464293</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -729,10 +729,10 @@
         <v>99.95999999999999</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-0.6509999999999999</v>
+        <v>-0.657</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>19.156</v>
+        <v>18.86</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>30.856</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>10.127618</v>
+        <v>9.97113</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14.473</v>
@@ -755,10 +755,10 @@
         <v>1.177</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>-0.556</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>-0.499</v>
+        <v>-0.507</v>
       </c>
     </row>
     <row r="4">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.96</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0.0122518</v>
+        <v>23.2</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>-0.030917058</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -790,10 +790,10 @@
         <v>21.01</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.509</v>
+        <v>-0.524</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11.927</v>
+        <v>11.546</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>12.574</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>12.310537</v>
+        <v>11.917484</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>46.079</v>
@@ -816,10 +816,10 @@
         <v>1.682</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>-0.409</v>
+        <v>-0.428</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>-0.328</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>101.13</v>
+        <v>102.04</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.0115022</v>
+        <v>0.8998355000000001</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,19 +851,19 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.249</v>
+        <v>-0.243</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.546</v>
+        <v>10.641</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>19.864</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.207005</v>
+        <v>32.496815</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>17.02018</v>
+        <v>17.173334</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>11.354</v>
@@ -875,10 +875,10 @@
         <v>1.034</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.202</v>
+        <v>0.213</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>-0.173</v>
+        <v>-0.166</v>
       </c>
     </row>
     <row r="6">
@@ -900,8 +900,8 @@
       <c r="D6" s="3" t="n">
         <v>36.95</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>0.04467069999999999</v>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>81.94</v>
+        <v>83.59</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.0108562</v>
+        <v>0.020136611</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -969,19 +969,19 @@
         <v>58.94</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.08900000000000001</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.186</v>
+        <v>6.31</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>8.542999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.6320925</v>
+        <v>3.7052305</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.057183</v>
+        <v>10.259701</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>7.113</v>
@@ -993,21 +993,21 @@
         <v>1.22</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.195</v>
+        <v>0.219</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>-0.047</v>
+        <v>-0.028</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1016,57 +1016,57 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.08</v>
+        <v>86.16</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.9735770000000001</v>
+        <v>0.018199017</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>68.98999999999999</v>
+        <v>118.46</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>35.09</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.158</v>
+        <v>-0.273</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>5.972</v>
+        <v>6.005</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>6.847</v>
+        <v>10.94</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>18.615385</v>
+        <v>16.287336</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>17.675362</v>
+        <v>11.603979</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>8.413</v>
+        <v>11.435</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>1.453</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>0.359</v>
+        <v>0.66</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>-0.239</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>-0.059</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1075,46 +1075,46 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>84.62</v>
+        <v>58.33</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.0102674</v>
+        <v>0.43044075</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>118.46</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>80.23999999999999</v>
+        <v>35.09</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.286</v>
+        <v>-0.155</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.898</v>
+        <v>5.998</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>10.94</v>
+        <v>6.847</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>15.99622</v>
+        <v>18.695515</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>11.396572</v>
+        <v>17.751444</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>11.435</v>
+        <v>8.413</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="P9" s="9" t="n">
-        <v>-0.253</v>
+        <v>1.453</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0.365</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>-0.244</v>
+        <v>-0.055</v>
       </c>
     </row>
     <row r="10">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.53</v>
+        <v>19.18</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-0.4079550000000001</v>
+        <v>-0.017939538</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>32.22</v>
@@ -1146,19 +1146,19 @@
         <v>15.725</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.394</v>
+        <v>-0.405</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.78</v>
+        <v>5.676</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>5.563</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>54.25</v>
+        <v>53.277775</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>23.811478</v>
+        <v>23.384747</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>10.962</v>
@@ -1170,10 +1170,10 @@
         <v>2.002</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>-0.151</v>
+        <v>-0.166</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>-0.163</v>
+        <v>-0.178</v>
       </c>
     </row>
     <row r="11">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.68</v>
+        <v>10.78</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.0210325</v>
+        <v>0.9363242000000001</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>14.38</v>
@@ -1205,19 +1205,19 @@
         <v>5.59</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.257</v>
+        <v>-0.25</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.4</v>
+        <v>5.451</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>4.993</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>25.428574</v>
+        <v>25.666666</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12.312517</v>
+        <v>12.427802</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>10.175</v>
@@ -1229,10 +1229,10 @@
         <v>1.1</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.535</v>
+        <v>0.5489999999999999</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>-0.078</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.44</v>
+        <v>26.36</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-0.0119581</v>
+        <v>-0.30257156</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>31.58</v>
@@ -1264,10 +1264,10 @@
         <v>17.86</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.163</v>
+        <v>-0.165</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.397</v>
+        <v>5.38</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>30.298</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="L12" s="7" t="n">
-        <v>28.583784</v>
+        <v>28.497297</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>8.669</v>
@@ -1290,10 +1290,10 @@
         <v>1.977</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>-0.06</v>
+        <v>-0.063</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.122</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0.0507246</v>
+        <v>21.73</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>-0.09195613</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.04</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.063</v>
+        <v>5.058</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>70.16128999999999</v>
+        <v>70.09677000000001</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>29.064718</v>
+        <v>29.03799</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.9179999999999999</v>
+        <v>0.9159999999999999</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.126</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="14">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>0.0203284</v>
+        <v>12.96</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>-0.6896563</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>18.57</v>
@@ -1390,10 +1390,10 @@
         <v>12.53</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-0.297</v>
+        <v>-0.302</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.408</v>
+        <v>2.391</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>5.976</v>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="L14" s="7" t="n">
-        <v>12.110919</v>
+        <v>12.027395</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>6.776</v>
@@ -1416,10 +1416,10 @@
         <v>1.082</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>-0.03</v>
+        <v>-0.036</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>-0.132</v>
+        <v>-0.138</v>
       </c>
     </row>
     <row r="15">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.183146</v>
+        <v>0.010968999</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>10.15</v>
@@ -1451,19 +1451,19 @@
         <v>4.55</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.461</v>
+        <v>-0.455</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.225</v>
+        <v>2.25</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>12.762</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>11.891304</v>
+        <v>12.021739</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>6.8754005</v>
+        <v>6.9508166</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>10.582</v>
@@ -1475,10 +1475,10 @@
         <v>0.603</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>-0.018</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>-0.272</v>
+        <v>-0.264</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0.0563277</v>
+        <v>14.4</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>-0.27700806</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>20.61</v>
@@ -1510,10 +1510,10 @@
         <v>11.65</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.299</v>
+        <v>-0.301</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.928</v>
+        <v>1.923</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>12.411</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>8.296322999999999</v>
+        <v>8.273342</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>17.184</v>
@@ -1536,10 +1536,10 @@
         <v>1.364</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>-0.168</v>
+        <v>-0.17</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>-0.028</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="17">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.26000000000001</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0.0182384</v>
+        <v>97.95</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>-0.3104013</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>113.88</v>
@@ -1571,19 +1571,19 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.137</v>
+        <v>-0.14</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.757</v>
+        <v>1.752</v>
       </c>
       <c r="J17" s="6" t="n">
         <v>1.674</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>18.095766</v>
+        <v>18.039597</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>16.528175</v>
+        <v>16.476871</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>8.779</v>
@@ -1595,10 +1595,10 @@
         <v>1.376</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.226</v>
+        <v>0.223</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.026</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="18">
@@ -1618,22 +1618,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0.0375275</v>
+        <v>4.47</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>-0.048936176</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.73</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>4.51</v>
+        <v>4.46</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.6579999999999999</v>
+        <v>-0.674</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.209</v>
+        <v>1.15</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>0.908</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>4.7474747</v>
+        <v>4.515151</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>-7.528</v>
@@ -1658,10 +1658,10 @@
         <v>1.993</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>-0.574</v>
+        <v>-0.595</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.585</v>
       </c>
     </row>
     <row r="19">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0.0311355</v>
+        <v>11.24</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>-0.17762396</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>13.31</v>
@@ -1693,19 +1693,19 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.156</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.919</v>
+        <v>0.917</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>1.242</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>18.766666</v>
+        <v>18.733332</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>12.159433</v>
+        <v>12.1378355</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>6.569</v>
@@ -1717,10 +1717,10 @@
         <v>1.07</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>-0.01</v>
+        <v>-0.011</v>
       </c>
     </row>
     <row r="20">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.36</v>
+        <v>26.67</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.610686</v>
+        <v>0.011760222</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>32.74</v>
@@ -1752,10 +1752,10 @@
         <v>19.57</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.195</v>
+        <v>-0.185</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.696</v>
+        <v>0.704</v>
       </c>
       <c r="J20" s="6" t="n">
         <v>1.153</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>21.785124</v>
+        <v>22.04132</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>9.449</v>
@@ -1778,10 +1778,10 @@
         <v>1.412</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>-0.024</v>
+        <v>-0.012</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>-0.026</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="21">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0.581393</v>
+        <v>11.83</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>-0.023121367</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>20.74</v>
@@ -1813,13 +1813,15 @@
         <v>8.455</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.416</v>
+        <v>-0.43</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>6.095</v>
+        <v>0.582</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
@@ -1827,13 +1829,17 @@
         </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>-14.950617</v>
-      </c>
-      <c r="M21" s="7" t="n">
-        <v>18.843</v>
-      </c>
-      <c r="N21" s="7" t="n">
-        <v>12.9</v>
+        <v>-14.6049385</v>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O21" s="8" t="inlineStr">
         <is>
@@ -1841,10 +1847,10 @@
         </is>
       </c>
       <c r="P21" s="9" t="n">
-        <v>-0.31</v>
+        <v>-0.326</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>-0.272</v>
+        <v>-0.289</v>
       </c>
     </row>
     <row r="22">
@@ -1864,10 +1870,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>0.06382979999999999</v>
+        <v>6.46</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>-0.69230884</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>9.949999999999999</v>
@@ -1876,10 +1882,10 @@
         <v>6.1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.347</v>
+        <v>-0.351</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.176</v>
+        <v>0.175</v>
       </c>
       <c r="J22" s="6" t="n">
         <v>0.507</v>
@@ -1890,7 +1896,7 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>8.676384000000001</v>
+        <v>8.616317</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>6.818</v>
@@ -1902,10 +1908,10 @@
         <v>1.206</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>-0.29</v>
+        <v>-0.295</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>-0.275</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="23">
@@ -1925,10 +1931,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>2.27</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>-0.021551704</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>4.95</v>
@@ -1937,10 +1943,10 @@
         <v>2.02</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-0.531</v>
+        <v>-0.541</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>0.578</v>
@@ -1951,7 +1957,7 @@
         </is>
       </c>
       <c r="L23" s="7" t="n">
-        <v>-5.6585364</v>
+        <v>-5.5365853</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>12.539</v>
@@ -1963,10 +1969,10 @@
         <v>1.327</v>
       </c>
       <c r="P23" s="9" t="n">
-        <v>-0.481</v>
+        <v>-0.492</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.092</v>
       </c>
     </row>
     <row r="24">
@@ -2152,28 +2158,28 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54</v>
+        <v>54.75</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0202154</v>
+        <v>0.013888888</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.168</v>
+        <v>-0.156</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.328</v>
+        <v>0.347</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>53.7</v>
+        <v>53.2</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.051</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.031</v>
+        <v>-0.017</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.233</v>
+        <v>-0.223</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
@@ -2199,28 +2205,28 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>109.38</v>
+        <v>107.69</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.0436027</v>
+        <v>-0.015464293</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0.499</v>
+        <v>-0.507</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.556</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-56</v>
+        <v>-56.8</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.24</v>
+        <v>-0.252</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.524</v>
+        <v>-0.532</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.6509999999999999</v>
+        <v>-0.657</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>1.177</v>
@@ -2246,28 +2252,28 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.96</v>
+        <v>23.2</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.0122518</v>
+        <v>-0.030917058</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.328</v>
+        <v>-0.35</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.409</v>
+        <v>-0.428</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-35.6</v>
+        <v>-36.1</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.118</v>
+        <v>-0.146</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.329</v>
+        <v>-0.35</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.509</v>
+        <v>-0.524</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
@@ -2293,28 +2299,28 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>101.13</v>
+        <v>102.04</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.0115022</v>
+        <v>0.8998355000000001</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.173</v>
+        <v>-0.166</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.202</v>
+        <v>0.213</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>35.3</v>
+        <v>34.7</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.08</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.115</v>
+        <v>-0.107</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.249</v>
+        <v>-0.243</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>1.034</v>
@@ -2343,7 +2349,7 @@
         <v>36.95</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.04467069999999999</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.013</v>
@@ -2387,28 +2393,28 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>81.94</v>
+        <v>83.59</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.0108562</v>
+        <v>0.020136611</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0.047</v>
+        <v>-0.028</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.195</v>
+        <v>0.219</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.004</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.08900000000000001</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>1.22</v>
@@ -2420,12 +2426,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2434,45 +2440,45 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.08</v>
+        <v>86.16</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.9735770000000001</v>
+        <v>0.018199017</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.059</v>
+        <v>-0.23</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.359</v>
+        <v>-0.239</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>39.4</v>
+        <v>-3.2</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.058</v>
+        <v>-0.091</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.147</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.158</v>
+        <v>-0.273</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>1.453</v>
+        <v>0.66</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>941430</v>
+        <v>1091240</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2481,34 +2487,34 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>84.62</v>
+        <v>58.33</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.0102674</v>
+        <v>0.43044075</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.244</v>
+        <v>-0.055</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.253</v>
+        <v>0.365</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-2.9</v>
+        <v>39.1</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.107</v>
+        <v>-0.05400000000000001</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.162</v>
+        <v>-0.006</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.286</v>
+        <v>-0.155</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.66</v>
+        <v>1.453</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>1091240</v>
+        <v>941430</v>
       </c>
     </row>
     <row r="10">
@@ -2528,28 +2534,28 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.53</v>
+        <v>19.18</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.4079550000000001</v>
+        <v>-0.017939538</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.163</v>
+        <v>-0.178</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.151</v>
+        <v>-0.166</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-27.9</v>
+        <v>-28.1</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.063</v>
+        <v>0.044</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-0.203</v>
+        <v>-0.218</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.394</v>
+        <v>-0.405</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>2.002</v>
@@ -2575,28 +2581,28 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.68</v>
+        <v>10.78</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.0210325</v>
+        <v>0.9363242000000001</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.078</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.535</v>
+        <v>0.5489999999999999</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>27.9</v>
+        <v>27.6</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.062</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.049</v>
+        <v>-0.04</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.257</v>
+        <v>-0.25</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>1.1</v>
@@ -2622,28 +2628,28 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.44</v>
+        <v>26.36</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.0119581</v>
+        <v>-0.30257156</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.122</v>
+        <v>0.119</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.063</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-23.1</v>
+        <v>-22.7</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.128</v>
+        <v>0.124</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.163</v>
+        <v>-0.165</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>1.977</v>
@@ -2669,28 +2675,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.75</v>
+        <v>21.73</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.0507246</v>
+        <v>-0.09195613</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.126</v>
+        <v>0.125</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.9179999999999999</v>
+        <v>0.9159999999999999</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>51.2</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.156</v>
+        <v>0.155</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.19</v>
+        <v>0.188</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.04</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2716,28 +2722,28 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13.05</v>
+        <v>12.96</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.0203284</v>
+        <v>-0.6896563</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.132</v>
+        <v>-0.138</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.03</v>
+        <v>-0.036</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.053</v>
+        <v>-0.06</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.155</v>
+        <v>-0.161</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-0.297</v>
+        <v>-0.302</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>1.082</v>
@@ -2763,28 +2769,28 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.183146</v>
+        <v>0.010968999</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.272</v>
+        <v>-0.264</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>9.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.091</v>
+        <v>-0.081</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.303</v>
+        <v>-0.296</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.461</v>
+        <v>-0.455</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>0.603</v>
@@ -2810,28 +2816,28 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.44</v>
+        <v>14.4</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.0563277</v>
+        <v>-0.27700806</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.03</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.168</v>
+        <v>-0.17</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-19.2</v>
+        <v>-19.3</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.111</v>
+        <v>-0.114</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.299</v>
+        <v>-0.301</v>
       </c>
       <c r="L16" s="8" t="n">
         <v>1.364</v>
@@ -2857,28 +2863,28 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.26000000000001</v>
+        <v>97.95</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.0182384</v>
+        <v>-0.3104013</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.026</v>
+        <v>0.023</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.226</v>
+        <v>0.223</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.036</v>
+        <v>0.032</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.137</v>
+        <v>-0.14</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.376</v>
@@ -2904,28 +2910,28 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.7</v>
+        <v>4.47</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.0375275</v>
+        <v>-0.048936176</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.585</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.574</v>
+        <v>-0.595</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-31.1</v>
+        <v>-32.1</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.347</v>
+        <v>-0.379</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.54</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.6579999999999999</v>
+        <v>-0.674</v>
       </c>
       <c r="L18" s="8" t="n">
         <v>1.993</v>
@@ -2951,28 +2957,28 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.26</v>
+        <v>11.24</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.0311355</v>
+        <v>-0.17762396</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.011</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>-1.2</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.156</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.07</v>
@@ -2998,28 +3004,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.36</v>
+        <v>26.67</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.610686</v>
+        <v>0.011760222</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.026</v>
+        <v>-0.014</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.012</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>5.3</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.057</v>
+        <v>-0.046</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.019</v>
+        <v>-0.008</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.195</v>
+        <v>-0.185</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>1.412</v>
@@ -3045,28 +3051,28 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>12.11</v>
+        <v>11.83</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.581393</v>
+        <v>-0.023121367</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.272</v>
+        <v>-0.289</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.31</v>
+        <v>-0.326</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>38.6</v>
+        <v>37.9</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.166</v>
+        <v>-0.185</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.08900000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.416</v>
+        <v>-0.43</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -3094,28 +3100,28 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.5</v>
+        <v>6.46</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.06382979999999999</v>
+        <v>-0.69230884</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.275</v>
+        <v>-0.28</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.29</v>
+        <v>-0.295</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.224</v>
+        <v>-0.229</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.241</v>
+        <v>-0.246</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.347</v>
+        <v>-0.351</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.206</v>
@@ -3141,28 +3147,28 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>-0.021551704</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.092</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.481</v>
+        <v>-0.492</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-52.9</v>
+        <v>-53</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.039</v>
+        <v>-0.06</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-0.247</v>
+        <v>-0.264</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>-0.531</v>
+        <v>-0.541</v>
       </c>
       <c r="L23" s="8" t="n">
         <v>1.327</v>
@@ -3342,16 +3348,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54</v>
+        <v>54.75</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>36.511</v>
+        <v>37.018</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>22.978724</v>
+        <v>23.297873</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.371104</v>
+        <v>14.5707035</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>10.77</v>
@@ -3363,10 +3369,10 @@
         <v>3.75</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.920204</v>
+        <v>23.23854</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.8048906</v>
+        <v>2.8438475</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3395,10 +3401,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>109.38</v>
+        <v>107.69</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>19.156</v>
+        <v>18.86</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3406,7 +3412,7 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>10.127618</v>
+        <v>9.97113</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>14.473</v>
@@ -3418,10 +3424,10 @@
         <v>1.883</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.1205893</v>
+        <v>2.0878227</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1692576</v>
+        <v>1.1511908</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3450,10 +3456,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.96</v>
+        <v>23.2</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.927</v>
+        <v>11.546</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3461,7 +3467,7 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>12.310537</v>
+        <v>11.917484</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>46.079</v>
@@ -3473,10 +3479,10 @@
         <v>2.077</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>18.777428</v>
+        <v>18.177898</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.9698704</v>
+        <v>1.906976</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3505,16 +3511,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>101.13</v>
+        <v>102.04</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.546</v>
+        <v>10.641</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.207005</v>
+        <v>32.496815</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>17.02018</v>
+        <v>17.173334</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>11.354</v>
@@ -3526,10 +3532,10 @@
         <v>2.783</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-37.62277</v>
+        <v>-37.96131</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.477484</v>
+        <v>1.4907789</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3611,16 +3617,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>81.94</v>
+        <v>83.59</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.186</v>
+        <v>6.31</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.6320925</v>
+        <v>3.7052305</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.057183</v>
+        <v>10.259701</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>7.113</v>
@@ -3632,10 +3638,10 @@
         <v>2.088</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.3989227</v>
+        <v>2.4472287</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5116932</v>
+        <v>1.5421335</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>22.56</v>
@@ -3650,12 +3656,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3664,51 +3670,51 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.08</v>
+        <v>86.16</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>5.972</v>
+        <v>6.005</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>18.615385</v>
+        <v>16.287336</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>17.675362</v>
+        <v>11.603979</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>8.413</v>
+        <v>11.435</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>3.404</v>
+        <v>3.739</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.259798</v>
+        <v>5.939202</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.9690464</v>
+        <v>2.0523736</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>3.12</v>
+        <v>5.29</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>3.28593</v>
+        <v>7.42504</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>3.572</v>
+        <v>14.507</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3717,40 +3723,40 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>84.62</v>
+        <v>58.33</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.898</v>
+        <v>5.998</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>15.99622</v>
+        <v>18.695515</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>11.396572</v>
+        <v>17.751444</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>11.435</v>
+        <v>8.413</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>3.739</v>
+        <v>3.404</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>5.8330464</v>
+        <v>16.329788</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.01569</v>
+        <v>2.9818263</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>5.29</v>
+        <v>3.12</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>7.42504</v>
+        <v>3.28593</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>14.507</v>
+        <v>3.572</v>
       </c>
     </row>
     <row r="10">
@@ -3770,16 +3776,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.53</v>
+        <v>19.18</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.78</v>
+        <v>5.676</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>54.25</v>
+        <v>53.277775</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>23.811478</v>
+        <v>23.384747</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>10.962</v>
@@ -3791,10 +3797,10 @@
         <v>4.312</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.1857567</v>
+        <v>5.0928216</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>4.480692</v>
+        <v>4.4003925</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.36</v>
@@ -3823,16 +3829,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.68</v>
+        <v>10.78</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.4</v>
+        <v>5.451</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>25.428574</v>
+        <v>25.666666</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>12.312517</v>
+        <v>12.427802</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>10.175</v>
@@ -3844,10 +3850,10 @@
         <v>2.131</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.2505093</v>
+        <v>7.3183975</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2.3049138</v>
+        <v>2.326495</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>0.42</v>
@@ -3876,10 +3882,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.44</v>
+        <v>26.36</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.397</v>
+        <v>5.38</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -3887,7 +3893,7 @@
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>28.583784</v>
+        <v>28.497297</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>8.669</v>
@@ -3899,10 +3905,10 @@
         <v>2.638</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>1.5289425</v>
+        <v>1.5243163</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.46984276</v>
+        <v>0.46842116</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>-2.42</v>
@@ -3931,16 +3937,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.75</v>
+        <v>21.73</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5.063</v>
+        <v>5.058</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>70.16128999999999</v>
+        <v>70.09677000000001</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>29.064718</v>
+        <v>29.03799</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -3958,10 +3964,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>14.765783</v>
+        <v>14.752206</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.4630985</v>
+        <v>4.4589944</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -3990,10 +3996,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13.05</v>
+        <v>12.96</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.408</v>
+        <v>2.391</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -4001,7 +4007,7 @@
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>12.110919</v>
+        <v>12.027395</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>6.776</v>
@@ -4013,10 +4019,10 @@
         <v>2.38</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>2.7866752</v>
+        <v>2.7674568</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.9590196</v>
+        <v>0.9524057</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>-0.01</v>
@@ -4045,16 +4051,16 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.225</v>
+        <v>2.25</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>11.891304</v>
+        <v>12.021739</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.8754005</v>
+        <v>6.9508166</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>10.582</v>
@@ -4066,10 +4072,10 @@
         <v>2.472</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1.7141961</v>
+        <v>-1.7329991</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.43095556</v>
+        <v>0.43568265</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.46</v>
@@ -4098,10 +4104,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.44</v>
+        <v>14.4</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.928</v>
+        <v>1.923</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -4109,7 +4115,7 @@
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>8.296322999999999</v>
+        <v>8.273342</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>17.184</v>
@@ -4121,10 +4127,10 @@
         <v>1.783</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.9940111</v>
+        <v>0.9912576</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.27703032</v>
+        <v>0.27626294</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-5.83</v>
@@ -4153,16 +4159,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.26000000000001</v>
+        <v>97.95</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.757</v>
+        <v>1.752</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>18.095766</v>
+        <v>18.039597</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>16.528175</v>
+        <v>16.476871</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>8.779</v>
@@ -4174,10 +4180,10 @@
         <v>3.071</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>3.2564461</v>
+        <v>3.246338</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3.2240133</v>
+        <v>3.214006</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>5.43</v>
@@ -4206,10 +4212,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.7</v>
+        <v>4.47</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1.209</v>
+        <v>1.15</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -4217,7 +4223,7 @@
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4.7474747</v>
+        <v>4.515151</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>-7.528</v>
@@ -4231,10 +4237,10 @@
         <v>1.356</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>1.5980958</v>
+        <v>1.5198911</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>1.8059682</v>
+        <v>1.7175908</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>-0.44</v>
@@ -4263,16 +4269,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.26</v>
+        <v>11.24</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.919</v>
+        <v>0.917</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>18.766666</v>
+        <v>18.733332</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>12.159433</v>
+        <v>12.1378355</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>6.569</v>
@@ -4284,10 +4290,10 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>3.4360697</v>
+        <v>3.4299664</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.6901145</v>
+        <v>0.68888867</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0.6</v>
@@ -4316,10 +4322,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.36</v>
+        <v>26.67</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.696</v>
+        <v>0.704</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -4327,7 +4333,7 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>21.785124</v>
+        <v>22.04132</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>9.449</v>
@@ -4339,10 +4345,10 @@
         <v>1.816</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.6399155</v>
+        <v>1.6592013</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>1.0960162</v>
+        <v>1.1089056</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.23</v>
@@ -4371,10 +4377,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>12.11</v>
+        <v>11.83</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.595</v>
+        <v>0.582</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -4382,22 +4388,28 @@
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-14.950617</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>18.843</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>2.447</v>
+        <v>-14.6049385</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K21" s="7" t="n">
-        <v>1.1408384</v>
+        <v>1.1144607</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.23902032</v>
+        <v>0.21891479</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>-12.65</v>
@@ -4426,10 +4438,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.5</v>
+        <v>6.46</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.176</v>
+        <v>0.175</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -4437,7 +4449,7 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>8.676384000000001</v>
+        <v>8.616317</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>6.818</v>
@@ -4449,10 +4461,10 @@
         <v>1.666</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-10.779436</v>
+        <v>-10.704809</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.5783861</v>
+        <v>0.5743819</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>-0.58</v>
@@ -4481,10 +4493,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -4492,7 +4504,7 @@
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-5.6585364</v>
+        <v>-5.5365853</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>12.539</v>
@@ -4504,10 +4516,10 @@
         <v>1.911</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>33.142857</v>
+        <v>32.42857</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.27761704</v>
+        <v>0.27163392</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-1.12</v>
@@ -5074,12 +5086,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -5088,57 +5100,57 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2.011</v>
+        <v>2.926</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.032</v>
+        <v>0.067</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.6747</v>
+        <v>0.33583</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.31768</v>
+        <v>0.18802</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.0935</v>
+        <v>0.1309</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.4046</v>
+        <v>0.32698002</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1.113</v>
+        <v>0.35709</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.09383000399999999</v>
+        <v>0.06236</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.193</v>
+        <v>0.082</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>3.475</v>
+        <v>5.197</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.142</v>
+        <v>0.201</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>1045.932</v>
+        <v>492.233</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>0.79</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -5147,46 +5159,46 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2.926</v>
+        <v>2.011</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.067</v>
+        <v>0.032</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.33583</v>
+        <v>0.6747</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.18802</v>
+        <v>0.31768</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.1309</v>
+        <v>0.0935</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.32698002</v>
+        <v>0.4046</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.35709</v>
+        <v>1.113</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.06236</v>
+        <v>0.09383000399999999</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.957</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.082</v>
+        <v>0.193</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>5.197</v>
+        <v>3.475</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.201</v>
+        <v>0.142</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>492.233</v>
+        <v>1045.932</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>0.604</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="10">
@@ -5867,46 +5879,46 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2.491</v>
+        <v>2.657</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.054</v>
+        <v>0.286</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.5516</v>
+        <v>0.54836</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.046469998</v>
+        <v>-0.24103001</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.1741</v>
+        <v>-0.26389998</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.12987</v>
+        <v>0.07475999999999999</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-1.1563</v>
+        <v>-0.5564</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.00361</v>
+        <v>-0.00855</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.323</v>
+        <v>0.199</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>-0.211</v>
+        <v>0.62</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>5.664</v>
+        <v>6.434</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.161</v>
+        <v>0.798</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>1085.198</v>
+        <v>252.846</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="22">
@@ -6245,7 +6257,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>54</v>
+        <v>54.75</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6268,7 +6280,7 @@
         <v>58</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.294</v>
+        <v>0.276</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>1.8</v>
@@ -6280,7 +6292,7 @@
         <v>0.57722</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>0.41693002</v>
+        <v>0.41691002</v>
       </c>
       <c r="O2" s="5" t="n">
         <v>1.94</v>
@@ -6301,7 +6313,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>109.38</v>
+        <v>107.69</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6324,7 +6336,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.945</v>
+        <v>0.975</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>1.72</v>
@@ -6336,7 +6348,7 @@
         <v>0.18823999</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>0.9117</v>
+        <v>0.91170996</v>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
@@ -6359,7 +6371,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23.96</v>
+        <v>23.2</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6382,7 +6394,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.51</v>
+        <v>0.5589999999999999</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -6417,7 +6429,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>101.13</v>
+        <v>102.04</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -6440,7 +6452,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.402</v>
+        <v>0.39</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.24</v>
@@ -6531,7 +6543,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>81.94</v>
+        <v>83.59</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -6554,7 +6566,7 @@
         <v>84</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.153</v>
+        <v>0.13</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.32</v>
@@ -6563,10 +6575,10 @@
         <v>0.0583</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.32334998</v>
+        <v>0.309</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>0.73223996</v>
+        <v>0.73225</v>
       </c>
       <c r="O7" s="5" t="n">
         <v>0.9</v>
@@ -6578,113 +6590,113 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>58.08</v>
+        <v>86.16</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>73.33333</v>
+        <v>135.5</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.263</v>
+        <v>0.573</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>3.89</v>
+        <v>2.68</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.0762</v>
+        <v>0.044499997</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.07935</v>
+        <v>0.06136</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0.88882005</v>
+        <v>0.81711</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>1.79</v>
+        <v>0.52</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.32369998</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>84.62</v>
+        <v>58.33</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>strong_buy</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>135.5</v>
+        <v>73.33333</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.601</v>
+        <v>0.257</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>2.68</v>
+        <v>3.89</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.044499997</v>
+        <v>0.0762</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.06136</v>
+        <v>0.07914</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0.81711</v>
+        <v>0.88882005</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>0.52</v>
+        <v>1.79</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.0828</v>
+        <v>0.32369998</v>
       </c>
     </row>
     <row r="10">
@@ -6699,7 +6711,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19.53</v>
+        <v>19.18</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -6713,16 +6725,16 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.92324</v>
+        <v>28.889751</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.290745</v>
+        <v>37.247566</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>21.995129</v>
+        <v>21.969662</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.481</v>
+        <v>0.506</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>4.19</v>
@@ -6757,7 +6769,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10.68</v>
+        <v>10.78</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6792,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.627</v>
+        <v>0.612</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4.92</v>
@@ -6813,7 +6825,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>26.44</v>
+        <v>26.36</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -6836,7 +6848,7 @@
         <v>22</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.209</v>
+        <v>0.212</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>3.8</v>
@@ -6871,7 +6883,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>21.75</v>
+        <v>21.73</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -6894,7 +6906,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.71</v>
@@ -6929,7 +6941,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>13.05</v>
+        <v>12.96</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -6952,7 +6964,7 @@
         <v>15</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.385</v>
+        <v>0.395</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>2.42</v>
@@ -6985,7 +6997,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7008,7 +7020,7 @@
         <v>6.3</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.695</v>
+        <v>0.677</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>2.08</v>
@@ -7043,7 +7055,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14.44</v>
+        <v>14.4</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7066,7 +7078,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.323</v>
+        <v>0.327</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>4.18</v>
@@ -7078,7 +7090,7 @@
         <v>0.01867</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0.9865699999999999</v>
+        <v>0.98657995</v>
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
@@ -7101,7 +7113,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>98.26000000000001</v>
+        <v>97.95</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7126,7 +7138,7 @@
         <v>93</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.096</v>
+        <v>0.099</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>2.53</v>
@@ -7138,7 +7150,7 @@
         <v>0.3204</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.64762</v>
+        <v>0.64763</v>
       </c>
       <c r="O17" s="5" t="n">
         <v>1.22</v>
@@ -7159,7 +7171,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4.7</v>
+        <v>4.47</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -7182,7 +7194,7 @@
         <v>6</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.503</v>
+        <v>1.632</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>1.77</v>
@@ -7217,7 +7229,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11.26</v>
+        <v>11.24</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7240,7 +7252,7 @@
         <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.377</v>
+        <v>0.379</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>3.68</v>
@@ -7275,7 +7287,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>26.36</v>
+        <v>26.67</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7298,7 +7310,7 @@
         <v>30</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.157</v>
+        <v>0.144</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>2.5</v>
@@ -7331,7 +7343,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>12.11</v>
+        <v>11.83</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -7354,7 +7366,7 @@
         <v>11</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.294</v>
+        <v>0.324</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>9.16</v>
@@ -7389,7 +7401,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6.5</v>
+        <v>6.46</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -7412,7 +7424,7 @@
         <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.051</v>
+        <v>1.064</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>13.9</v>
@@ -7447,7 +7459,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -7470,7 +7482,7 @@
         <v>2.5</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.401</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="K23" s="7" t="n">
         <v>5.72</v>
@@ -7695,10 +7707,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>36.511</v>
+        <v>37.018</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>22.978724</v>
+        <v>23.297873</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -7710,7 +7722,7 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.168</v>
+        <v>-0.156</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>10.77</v>
@@ -7739,7 +7751,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.397</v>
+        <v>5.38</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -7756,7 +7768,7 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.122</v>
+        <v>0.119</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>8.669</v>
@@ -7785,10 +7797,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.225</v>
+        <v>2.25</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>11.891304</v>
+        <v>12.021739</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -7802,7 +7814,7 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.272</v>
+        <v>-0.264</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>10.582</v>
@@ -7875,10 +7887,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.546</v>
+        <v>10.641</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>32.207005</v>
+        <v>32.496815</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.015</v>
@@ -7892,7 +7904,7 @@
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.173</v>
+        <v>-0.166</v>
       </c>
       <c r="J7" s="7" t="n">
         <v>11.354</v>
@@ -7939,10 +7951,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.186</v>
+        <v>6.31</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.6320925</v>
+        <v>3.7052305</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -7954,7 +7966,7 @@
         <v>0.87788004</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-0.047</v>
+        <v>-0.028</v>
       </c>
       <c r="J10" s="7" t="n">
         <v>7.113</v>
@@ -7963,7 +7975,7 @@
         <v>5.9</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>69</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -7983,10 +7995,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5.898</v>
+        <v>6.005</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>15.99622</v>
+        <v>16.287336</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.067</v>
@@ -7998,7 +8010,7 @@
         <v>0.35709</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>-0.244</v>
+        <v>-0.23</v>
       </c>
       <c r="J11" s="7" t="n">
         <v>11.435</v>
@@ -8027,10 +8039,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1.757</v>
+        <v>1.752</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>18.095766</v>
+        <v>18.039597</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.041</v>
@@ -8042,7 +8054,7 @@
         <v>0.19214001</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.026</v>
+        <v>0.023</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>8.779</v>
@@ -8071,10 +8083,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5.972</v>
+        <v>5.998</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.615385</v>
+        <v>18.695515</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8086,7 +8098,7 @@
         <v>1.113</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.059</v>
+        <v>-0.055</v>
       </c>
       <c r="J13" s="7" t="n">
         <v>8.413</v>
@@ -8095,7 +8107,7 @@
         <v>7.3</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>59.5</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="14">
@@ -8115,7 +8127,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.928</v>
+        <v>1.923</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8132,7 +8144,7 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.03</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>17.184</v>
@@ -8141,7 +8153,7 @@
         <v>10.9</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>51.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="15">
@@ -8161,7 +8173,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.696</v>
+        <v>0.704</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -8178,7 +8190,7 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.026</v>
+        <v>-0.014</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>9.449</v>
@@ -8207,7 +8219,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.595</v>
+        <v>0.582</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -8215,25 +8227,29 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.054</v>
+        <v>0.286</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.12987</v>
+        <v>0.07475999999999999</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-1.1563</v>
+        <v>-0.5564</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.272</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>18.843</v>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>12.9</v>
+        <v>-0.289</v>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>22.9</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="17">
@@ -8253,7 +8269,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -8270,7 +8286,7 @@
         <v>-1.8681101</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.092</v>
       </c>
       <c r="J17" s="7" t="n">
         <v>12.539</v>
@@ -8317,10 +8333,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.4</v>
+        <v>5.451</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.428574</v>
+        <v>25.666666</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -8332,7 +8348,7 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.078</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>10.175</v>
@@ -8361,10 +8377,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.78</v>
+        <v>5.676</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>54.25</v>
+        <v>53.277775</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -8376,7 +8392,7 @@
         <v>0.10515001</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.163</v>
+        <v>-0.178</v>
       </c>
       <c r="J21" s="7" t="n">
         <v>10.962</v>
@@ -8405,10 +8421,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.063</v>
+        <v>5.058</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>70.16128999999999</v>
+        <v>70.09677000000001</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -8420,7 +8436,7 @@
         <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.126</v>
+        <v>0.125</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
@@ -8453,7 +8469,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>11.927</v>
+        <v>11.546</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -8470,7 +8486,7 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.328</v>
+        <v>-0.35</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>46.079</v>
@@ -8499,7 +8515,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>19.156</v>
+        <v>18.86</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8516,7 +8532,7 @@
         <v>-0.038829997</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-0.499</v>
+        <v>-0.507</v>
       </c>
       <c r="J24" s="7" t="n">
         <v>14.473</v>
@@ -8545,7 +8561,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.209</v>
+        <v>1.15</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -8562,7 +8578,7 @@
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.585</v>
       </c>
       <c r="J25" s="7" t="n">
         <v>-7.528</v>
@@ -8611,10 +8627,10 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.919</v>
+        <v>0.917</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.766666</v>
+        <v>18.733332</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0.075</v>
@@ -8626,7 +8642,7 @@
         <v>0.19236</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.011</v>
       </c>
       <c r="J28" s="7" t="n">
         <v>6.569</v>
@@ -8655,7 +8671,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2.408</v>
+        <v>2.391</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -8672,7 +8688,7 @@
         <v>0.07395</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.132</v>
+        <v>-0.138</v>
       </c>
       <c r="J29" s="7" t="n">
         <v>6.776</v>
@@ -8701,7 +8717,7 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.176</v>
+        <v>0.175</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
@@ -8720,7 +8736,7 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.275</v>
+        <v>-0.28</v>
       </c>
       <c r="J30" s="7" t="n">
         <v>6.818</v>
@@ -9391,7 +9407,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -9530,7 +9546,7 @@
         <v>0.57722</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.41693002</v>
+        <v>0.41691002</v>
       </c>
       <c r="E2" s="7" t="n">
         <v>1.8</v>
@@ -9557,7 +9573,7 @@
         <v>0.18823999</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.9117</v>
+        <v>0.91170996</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>1.72</v>
@@ -9662,10 +9678,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.32334998</v>
+        <v>0.309</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.73223996</v>
+        <v>0.73225</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>3.32</v>
@@ -9680,55 +9696,55 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.07935</v>
+        <v>0.06136</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.88882005</v>
+        <v>0.81711</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>3.89</v>
+        <v>2.68</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.0762</v>
+        <v>0.044499997</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>3025746</v>
+        <v>2574942</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.06136</v>
+        <v>0.07914</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.81711</v>
+        <v>0.88882005</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2.68</v>
+        <v>3.89</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.044499997</v>
+        <v>0.0762</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>2574942</v>
+        <v>3025746</v>
       </c>
     </row>
     <row r="10">
@@ -9908,7 +9924,7 @@
         <v>0.01867</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.9865699999999999</v>
+        <v>0.98657995</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>4.18</v>
@@ -9935,7 +9951,7 @@
         <v>0.3204</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.64762</v>
+        <v>0.64763</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2.53</v>
@@ -10192,955 +10208,955 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1267.98</v>
+        <v>1277.61</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>1213.06</v>
+        <v>1212.93</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>1067.79</v>
+        <v>1068.57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1273.89</v>
+        <v>1267.27</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1212.93</v>
+        <v>1208.61</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>1068.57</v>
+        <v>1061.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1263.57</v>
+        <v>1262.13</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1208.61</v>
+        <v>1207.14</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>1061.03</v>
+        <v>1059.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1258.56</v>
+        <v>1254.82</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1207.14</v>
+        <v>1198.19</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1059.21</v>
+        <v>1061.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1251.2</v>
+        <v>1259.66</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1198.19</v>
+        <v>1200.39</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1061.81</v>
+        <v>1062.85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1256.1</v>
+        <v>1260.24</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1200.39</v>
+        <v>1208.38</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1062.85</v>
+        <v>1060.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1256.79</v>
+        <v>1245.52</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1208.38</v>
+        <v>1215.57</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1060.77</v>
+        <v>1054.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1242</v>
+        <v>1198.22</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1215.57</v>
+        <v>1211.65</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1054.28</v>
+        <v>1035.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1194.92</v>
+        <v>1222.89</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1211.65</v>
+        <v>1211.53</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1035.05</v>
+        <v>1052.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1219.64</v>
+        <v>1194.21</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>1211.53</v>
+        <v>1219.54</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1052.2</v>
+        <v>1044.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1191.17</v>
+        <v>1190</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1219.54</v>
+        <v>1221.46</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1044.66</v>
+        <v>1040.51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1186.79</v>
+        <v>1182.27</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1221.46</v>
+        <v>1219.01</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>1040.51</v>
+        <v>1028.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1178.98</v>
+        <v>1179.97</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1219.01</v>
+        <v>1213.02</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>1028.3</v>
+        <v>1030.89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1176.64</v>
+        <v>1198.78</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1213.02</v>
+        <v>1216.33</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1030.89</v>
+        <v>1042.33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1195.46</v>
+        <v>1162.54</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1216.33</v>
+        <v>1215.31</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1042.33</v>
+        <v>1022.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1159.07</v>
+        <v>1139.17</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1215.31</v>
+        <v>1190.57</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>1022.06</v>
+        <v>1005.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1135.73</v>
+        <v>1145.74</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1190.57</v>
+        <v>1204.31</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1005.43</v>
+        <v>1007.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1142.13</v>
+        <v>1150.84</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>1204.31</v>
+        <v>1210.6</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>1007.25</v>
+        <v>1015.31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1147.18</v>
+        <v>1135.92</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1210.6</v>
+        <v>1211.04</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1015.31</v>
+        <v>1008.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1132.12</v>
+        <v>1141.77</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1211.04</v>
+        <v>1217.19</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>1008.29</v>
+        <v>1014.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1137.93</v>
+        <v>1128.9</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1217.19</v>
+        <v>1222.04</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1014.01</v>
+        <v>1010.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1125.04</v>
+        <v>1130.69</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>1222.04</v>
+        <v>1221.91</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>1010.37</v>
+        <v>1002.58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1126.72</v>
+        <v>1078.7</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>1221.91</v>
+        <v>1219.49</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1002.58</v>
+        <v>986.21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1075.5</v>
+        <v>1067.1</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>1219.49</v>
+        <v>1215.85</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>986.21</v>
+        <v>964.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1063.7</v>
+        <v>1085.19</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>1215.85</v>
+        <v>1221.9</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>964.9</v>
+        <v>974.26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1081.5</v>
+        <v>1081.87</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>1221.9</v>
+        <v>1211.56</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>974.26</v>
+        <v>963.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1077.98</v>
+        <v>1102.76</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>1211.56</v>
+        <v>1205.7</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>963.35</v>
+        <v>984.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1098.8</v>
+        <v>1078.44</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1205.7</v>
+        <v>1190.64</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>984.65</v>
+        <v>965.42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1074.29</v>
+        <v>1105.07</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>1190.64</v>
+        <v>1213.48</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>965.42</v>
+        <v>983.61</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1100.89</v>
+        <v>1106.92</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>1213.48</v>
+        <v>1219.33</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>983.61</v>
+        <v>990.88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1102.84</v>
+        <v>1103.9</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>1219.33</v>
+        <v>1216.12</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>990.88</v>
+        <v>992.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1099.79</v>
+        <v>1089.47</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>1216.12</v>
+        <v>1215.83</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>992.7</v>
+        <v>985.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1085.22</v>
+        <v>1052.8</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>1215.83</v>
+        <v>1197.05</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>985.17</v>
+        <v>950.88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1048.61</v>
+        <v>1043.61</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>1197.05</v>
+        <v>1197.89</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>950.88</v>
+        <v>938.66</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1038.95</v>
+        <v>1058.28</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>1197.89</v>
+        <v>1199.83</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>938.66</v>
+        <v>940.48</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1053.61</v>
+        <v>1091.47</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>1199.83</v>
+        <v>1205.87</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>940.48</v>
+        <v>965.9400000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1086.74</v>
+        <v>1086.37</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>1205.87</v>
+        <v>1202.69</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>965.9400000000001</v>
+        <v>961.27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1081.62</v>
+        <v>1086.48</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>1202.69</v>
+        <v>1211.39</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>961.27</v>
+        <v>958.9299999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1081.66</v>
+        <v>1043.41</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>1211.39</v>
+        <v>1199.02</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>958.9299999999999</v>
+        <v>937.37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1038.78</v>
+        <v>1057.85</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>1199.02</v>
+        <v>1207.73</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>937.37</v>
+        <v>945.42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1053.26</v>
+        <v>1061.73</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>1207.73</v>
+        <v>1217.93</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>945.42</v>
+        <v>946.72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1057.22</v>
+        <v>1090.33</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>1217.93</v>
+        <v>1211.16</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>946.72</v>
+        <v>949.0599999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1085.84</v>
+        <v>1077.73</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>1211.16</v>
+        <v>1205.34</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>949.0599999999999</v>
+        <v>953.21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1073.12</v>
+        <v>1072.59</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>1205.34</v>
+        <v>1206.03</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>953.21</v>
+        <v>944.64</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1068.07</v>
+        <v>1068.53</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>1206.03</v>
+        <v>1195.4</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>944.64</v>
+        <v>938.14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1064.12</v>
+        <v>1083.93</v>
       </c>
       <c r="C47" s="13" t="n">
-        <v>1195.4</v>
+        <v>1203.83</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>938.14</v>
+        <v>943.86</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1079.6</v>
+        <v>1081.57</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>1203.83</v>
+        <v>1197.12</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>943.86</v>
+        <v>937.88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1077.36</v>
+        <v>1050.11</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>1197.12</v>
+        <v>1181.43</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>937.88</v>
+        <v>928.27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1046.08</v>
+        <v>1051.66</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>1181.43</v>
+        <v>1191.78</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>928.27</v>
+        <v>930.35</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1047.55</v>
+        <v>1050.75</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>1191.78</v>
+        <v>1189.86</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>930.35</v>
+        <v>928.53</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1046.55</v>
+        <v>1065.14</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>1189.86</v>
+        <v>1188.37</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>928.53</v>
+        <v>932.95</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1060.94</v>
+        <v>1051.01</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>1188.37</v>
+        <v>1170.33</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>932.95</v>
+        <v>921.78</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1046.94</v>
+        <v>1052.95</v>
       </c>
       <c r="C54" s="13" t="n">
-        <v>1170.33</v>
+        <v>1163.7</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>921.78</v>
+        <v>919.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1048.89</v>
+        <v>1045.55</v>
       </c>
       <c r="C55" s="13" t="n">
-        <v>1163.7</v>
+        <v>1175.54</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>919.7</v>
+        <v>916.84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1041.42</v>
+        <v>1057.81</v>
       </c>
       <c r="C56" s="13" t="n">
-        <v>1175.54</v>
+        <v>1178.64</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>916.84</v>
+        <v>916.0599999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1053.6</v>
+        <v>1049.92</v>
       </c>
       <c r="C57" s="13" t="n">
-        <v>1178.64</v>
+        <v>1162.19</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>916.0599999999999</v>
+        <v>905.9299999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1045.73</v>
+        <v>1062.51</v>
       </c>
       <c r="C58" s="13" t="n">
-        <v>1162.19</v>
+        <v>1159.33</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>905.9299999999999</v>
+        <v>912.9400000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1058.29</v>
+        <v>1034.47</v>
       </c>
       <c r="C59" s="13" t="n">
-        <v>1159.33</v>
+        <v>1142.71</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>912.9400000000001</v>
+        <v>885.41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1030.33</v>
+        <v>1056.25</v>
       </c>
       <c r="C60" s="13" t="n">
-        <v>1142.71</v>
+        <v>1154.7</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>885.41</v>
+        <v>922.8200000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1052.04</v>
+        <v>1060.9</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11152,7 +11168,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1052.04</v>
+        <v>1060.9</v>
       </c>
     </row>
     <row r="64">
@@ -11163,7 +11179,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-16.25%</t>
+          <t>-15.78%</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11200,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>139.9</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.69</v>
+        <v>107.66</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>-0.015464293</v>
+        <v>-0.015724937</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -732,7 +732,7 @@
         <v>-0.657</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.86</v>
+        <v>18.855</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>30.856</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.97113</v>
+        <v>9.968362000000001</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14.473</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.2</v>
+        <v>23.25</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>-0.030917058</v>
+        <v>-0.02882802</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -790,10 +790,10 @@
         <v>21.01</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.524</v>
+        <v>-0.523</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11.546</v>
+        <v>11.571</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>12.574</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>11.917484</v>
+        <v>11.943174</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>46.079</v>
@@ -816,10 +816,10 @@
         <v>1.682</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>-0.428</v>
+        <v>-0.426</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>-0.35</v>
+        <v>-0.348</v>
       </c>
     </row>
     <row r="5">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.95</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>36.96</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.027059056</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -913,16 +913,16 @@
         <v>-0.08</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10.106</v>
+        <v>10.109</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>39.58</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>48.618423</v>
+        <v>48.631577</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>15.769639</v>
+        <v>15.773907</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>16.81</v>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.59</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.020136611</v>
+        <v>0.01989257</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -972,16 +972,16 @@
         <v>-0.07099999999999999</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.31</v>
+        <v>6.309</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>8.542999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.7052305</v>
+        <v>3.704344</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.259701</v>
+        <v>10.257247</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>7.113</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>86.16</v>
+        <v>86.2</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.018199017</v>
+        <v>0.018730785</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>118.46</v>
@@ -1028,19 +1028,19 @@
         <v>80.23999999999999</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.273</v>
+        <v>-0.272</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.005</v>
+        <v>6.008</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>10.94</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.287336</v>
+        <v>16.295841</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>11.603979</v>
+        <v>11.610039</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>11.435</v>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>58.33</v>
+        <v>58.31</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.43044075</v>
+        <v>0.4046087999999999</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1090,16 +1090,16 @@
         <v>-0.155</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.998</v>
+        <v>5.996</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>6.847</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>18.695515</v>
+        <v>18.690706</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>17.751444</v>
+        <v>17.746878</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>8.413</v>
@@ -1111,7 +1111,7 @@
         <v>1.453</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="Q9" s="9" t="n">
         <v>-0.055</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.18</v>
+        <v>19.16</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-0.017939538</v>
+        <v>-0.018674841</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>32.22</v>
@@ -1149,16 +1149,16 @@
         <v>-0.405</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.676</v>
+        <v>5.672</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>5.563</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>53.277775</v>
+        <v>53.23611</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>23.384747</v>
+        <v>23.366459</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>10.962</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.78</v>
+        <v>10.79</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.9363242000000001</v>
+        <v>0.010299593</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>14.38</v>
@@ -1208,16 +1208,16 @@
         <v>-0.25</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.451</v>
+        <v>5.456</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>4.993</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>25.666666</v>
+        <v>25.690477</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12.427802</v>
+        <v>12.439331</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>10.175</v>
@@ -1229,10 +1229,10 @@
         <v>1.1</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5489999999999999</v>
+        <v>0.551</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06900000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.73</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>-0.09195613</v>
+        <v>21.77</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0.09195613</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.04099999999999999</v>
+        <v>-0.039</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.058</v>
+        <v>5.068</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>70.09677000000001</v>
+        <v>70.22581</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>29.03799</v>
+        <v>29.091444</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.9159999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.125</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="14">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>97.95</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>-0.3104013</v>
+        <v>98.3</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.040709257</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>113.88</v>
@@ -1571,19 +1571,19 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.14</v>
+        <v>-0.137</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.752</v>
+        <v>1.758</v>
       </c>
       <c r="J17" s="6" t="n">
         <v>1.674</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>18.039597</v>
+        <v>18.103132</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>16.476871</v>
+        <v>16.534903</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>8.779</v>
@@ -1595,10 +1595,10 @@
         <v>1.376</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.223</v>
+        <v>0.227</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.023</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="18">
@@ -1621,7 +1621,7 @@
         <v>4.47</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>-0.048936176</v>
+        <v>-0.04787232399999999</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.73</v>
@@ -1633,7 +1633,7 @@
         <v>-0.674</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.15</v>
+        <v>1.151</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>0.908</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>4.515151</v>
+        <v>4.5202017</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>-7.528</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.67</v>
+        <v>26.66</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.011760222</v>
+        <v>0.011380851</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>32.74</v>
@@ -1752,7 +1752,7 @@
         <v>19.57</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.185</v>
+        <v>-0.186</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0.704</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>22.04132</v>
+        <v>22.033056</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>9.449</v>
@@ -1778,10 +1778,10 @@
         <v>1.412</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>-0.012</v>
+        <v>-0.013</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>-0.014</v>
+        <v>-0.015</v>
       </c>
     </row>
     <row r="21">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.46</v>
+        <v>6.48</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>-0.69230884</v>
+        <v>-0.30769202</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>9.949999999999999</v>
@@ -1882,7 +1882,7 @@
         <v>6.1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.351</v>
+        <v>-0.349</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0.175</v>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>8.616317</v>
+        <v>8.649687999999999</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>6.818</v>
@@ -1908,10 +1908,10 @@
         <v>1.206</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>-0.295</v>
+        <v>-0.292</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>-0.28</v>
+        <v>-0.278</v>
       </c>
     </row>
     <row r="23">
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.69</v>
+        <v>107.66</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.015464293</v>
+        <v>-0.015724937</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>-0.507</v>
@@ -2252,28 +2252,28 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.2</v>
+        <v>23.25</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.030917058</v>
+        <v>-0.02882802</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.35</v>
+        <v>-0.348</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.428</v>
+        <v>-0.426</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-36.1</v>
+        <v>-36</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.146</v>
+        <v>-0.144</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.35</v>
+        <v>-0.349</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.524</v>
+        <v>-0.523</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
@@ -2346,10 +2346,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.95</v>
+        <v>36.96</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>0.027059056</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.013</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.59</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.020136611</v>
+        <v>0.01989257</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>-0.028</v>
@@ -2411,7 +2411,7 @@
         <v>-0.004</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>-0.07099999999999999</v>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>86.16</v>
+        <v>86.2</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.018199017</v>
+        <v>0.018730785</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>-0.23</v>
@@ -2458,10 +2458,10 @@
         <v>-0.091</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.147</v>
+        <v>-0.146</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.273</v>
+        <v>-0.272</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>0.66</v>
@@ -2487,16 +2487,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>58.33</v>
+        <v>58.31</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.43044075</v>
+        <v>0.4046087999999999</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>-0.055</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>39.1</v>
@@ -2505,7 +2505,7 @@
         <v>-0.05400000000000001</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>-0.155</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.18</v>
+        <v>19.16</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.017939538</v>
+        <v>-0.018674841</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>-0.178</v>
@@ -2549,7 +2549,7 @@
         <v>-28.1</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>-0.218</v>
@@ -2581,25 +2581,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.78</v>
+        <v>10.79</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.9363242000000001</v>
+        <v>0.010299593</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.5489999999999999</v>
+        <v>0.551</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>27.6</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.073</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.04</v>
+        <v>-0.039</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>-0.25</v>
@@ -2675,28 +2675,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.73</v>
+        <v>21.77</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-0.09195613</v>
+        <v>0.09195613</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.125</v>
+        <v>0.127</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.9159999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>51.2</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.155</v>
+        <v>0.157</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.188</v>
+        <v>0.191</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.04099999999999999</v>
+        <v>-0.039</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2863,28 +2863,28 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>97.95</v>
+        <v>98.3</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-0.3104013</v>
+        <v>0.040709257</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.023</v>
+        <v>0.027</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.223</v>
+        <v>0.227</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>20.6</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.032</v>
+        <v>0.036</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.019</v>
+        <v>0.023</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.14</v>
+        <v>-0.137</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.376</v>
@@ -2913,7 +2913,7 @@
         <v>4.47</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.048936176</v>
+        <v>-0.04787232399999999</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>-0.585</v>
@@ -3004,16 +3004,16 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.67</v>
+        <v>26.66</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.011760222</v>
+        <v>0.011380851</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.012</v>
+        <v>-0.013</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>5.3</v>
@@ -3025,7 +3025,7 @@
         <v>-0.008</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.185</v>
+        <v>-0.186</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>1.412</v>
@@ -3100,28 +3100,28 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.46</v>
+        <v>6.48</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.69230884</v>
+        <v>-0.30769202</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.28</v>
+        <v>-0.278</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.295</v>
+        <v>-0.292</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>4.5</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.229</v>
+        <v>-0.226</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.246</v>
+        <v>-0.243</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.351</v>
+        <v>-0.349</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.206</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.69</v>
+        <v>107.66</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.86</v>
+        <v>18.855</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.97113</v>
+        <v>9.968362000000001</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>14.473</v>
@@ -3424,10 +3424,10 @@
         <v>1.883</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.0878227</v>
+        <v>2.087243</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1511908</v>
+        <v>1.1508712</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.2</v>
+        <v>23.25</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.546</v>
+        <v>11.571</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>11.917484</v>
+        <v>11.943174</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>46.079</v>
@@ -3479,10 +3479,10 @@
         <v>2.077</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>18.177898</v>
+        <v>18.217085</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.906976</v>
+        <v>1.9110868</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3564,16 +3564,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.95</v>
+        <v>36.96</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.106</v>
+        <v>10.109</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>48.618423</v>
+        <v>48.631577</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>15.769639</v>
+        <v>15.773907</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>16.81</v>
@@ -3585,10 +3585,10 @@
         <v>2.257</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.9279263</v>
+        <v>3.9289892</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.57624847</v>
+        <v>0.5764044</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3617,16 +3617,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.59</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.31</v>
+        <v>6.309</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.7052305</v>
+        <v>3.704344</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.259701</v>
+        <v>10.257247</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>7.113</v>
@@ -3638,10 +3638,10 @@
         <v>2.088</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.4472287</v>
+        <v>2.4466434</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5421335</v>
+        <v>1.5417646</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>22.56</v>
@@ -3670,16 +3670,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>86.16</v>
+        <v>86.2</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.005</v>
+        <v>6.008</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>16.287336</v>
+        <v>16.295841</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>11.603979</v>
+        <v>11.610039</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>11.435</v>
@@ -3691,10 +3691,10 @@
         <v>3.739</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>5.939202</v>
+        <v>5.9423037</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.0523736</v>
+        <v>2.0534453</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>5.29</v>
@@ -3723,16 +3723,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>58.33</v>
+        <v>58.31</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.998</v>
+        <v>5.996</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>18.695515</v>
+        <v>18.690706</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>17.751444</v>
+        <v>17.746878</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>8.413</v>
@@ -3744,10 +3744,10 @@
         <v>3.404</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.329788</v>
+        <v>16.325588</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.9818263</v>
+        <v>2.9810596</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>3.12</v>
@@ -3776,16 +3776,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.18</v>
+        <v>19.16</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.676</v>
+        <v>5.672</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>53.277775</v>
+        <v>53.23611</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>23.384747</v>
+        <v>23.366459</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>10.962</v>
@@ -3797,10 +3797,10 @@
         <v>4.312</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.0928216</v>
+        <v>5.088839</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>4.4003925</v>
+        <v>4.396951</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.36</v>
@@ -3829,16 +3829,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.78</v>
+        <v>10.79</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.451</v>
+        <v>5.456</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>25.666666</v>
+        <v>25.690477</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>12.427802</v>
+        <v>12.439331</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>10.175</v>
@@ -3850,10 +3850,10 @@
         <v>2.131</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.3183975</v>
+        <v>7.3251863</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2.326495</v>
+        <v>2.328653</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>0.42</v>
@@ -3937,16 +3937,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.73</v>
+        <v>21.77</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5.058</v>
+        <v>5.068</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>70.09677000000001</v>
+        <v>70.22581</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>29.03799</v>
+        <v>29.091444</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>14.752206</v>
+        <v>14.779362</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.4589944</v>
+        <v>4.4672027</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>97.95</v>
+        <v>98.3</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.752</v>
+        <v>1.758</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>18.039597</v>
+        <v>18.103132</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>16.476871</v>
+        <v>16.534903</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>8.779</v>
@@ -4180,10 +4180,10 @@
         <v>3.071</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>3.246338</v>
+        <v>3.2577717</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3.214006</v>
+        <v>3.2253258</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>5.43</v>
@@ -4215,7 +4215,7 @@
         <v>4.47</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1.15</v>
+        <v>1.151</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4.515151</v>
+        <v>4.5202017</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>-7.528</v>
@@ -4237,10 +4237,10 @@
         <v>1.356</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>1.5198911</v>
+        <v>1.5215913</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>1.7175908</v>
+        <v>1.7195121</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>-0.44</v>
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.67</v>
+        <v>26.66</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0.704</v>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>22.04132</v>
+        <v>22.033056</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>9.449</v>
@@ -4345,10 +4345,10 @@
         <v>1.816</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.6592013</v>
+        <v>1.6585791</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>1.1089056</v>
+        <v>1.1084898</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.23</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.46</v>
+        <v>6.48</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0.175</v>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>8.616317</v>
+        <v>8.649687999999999</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>6.818</v>
@@ -4461,10 +4461,10 @@
         <v>1.666</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-10.704809</v>
+        <v>-10.746269</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.5743819</v>
+        <v>0.5766065</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>-0.58</v>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>107.69</v>
+        <v>107.66</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.975</v>
+        <v>0.976</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>1.72</v>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23.2</v>
+        <v>23.25</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.5589999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>36.95</v>
+        <v>36.96</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.2</v>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>83.59</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>86.16</v>
+        <v>86.2</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>110</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.573</v>
+        <v>0.5720000000000001</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>2.68</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>58.33</v>
+        <v>58.31</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>59</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.257</v>
+        <v>0.258</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>3.89</v>
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19.18</v>
+        <v>19.16</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -6725,16 +6725,16 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.889751</v>
+        <v>28.883062</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.247566</v>
+        <v>37.238945</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>21.969662</v>
+        <v>21.964575</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.506</v>
+        <v>0.507</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>4.19</v>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10.78</v>
+        <v>10.79</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.612</v>
+        <v>0.61</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4.92</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>21.73</v>
+        <v>21.77</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.141</v>
+        <v>0.139</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.71</v>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>97.95</v>
+        <v>98.3</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>93</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.099</v>
+        <v>0.095</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>2.53</v>
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>26.67</v>
+        <v>26.66</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6.46</v>
+        <v>6.48</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.064</v>
+        <v>1.058</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>13.9</v>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>10.106</v>
+        <v>10.109</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>48.618423</v>
+        <v>48.631577</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.06</v>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.31</v>
+        <v>6.309</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.7052305</v>
+        <v>3.704344</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6.005</v>
+        <v>6.008</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>16.287336</v>
+        <v>16.295841</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.067</v>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1.752</v>
+        <v>1.758</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>18.039597</v>
+        <v>18.103132</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.041</v>
@@ -8054,7 +8054,7 @@
         <v>0.19214001</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.023</v>
+        <v>0.027</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>8.779</v>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5.998</v>
+        <v>5.996</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.695515</v>
+        <v>18.690706</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8190,7 +8190,7 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>9.449</v>
@@ -8333,10 +8333,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.451</v>
+        <v>5.456</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.666666</v>
+        <v>25.690477</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -8348,7 +8348,7 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>10.175</v>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.676</v>
+        <v>5.672</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>53.277775</v>
+        <v>53.23611</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.058</v>
+        <v>5.068</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>70.09677000000001</v>
+        <v>70.22581</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -8436,7 +8436,7 @@
         <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.125</v>
+        <v>0.127</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>11.546</v>
+        <v>11.571</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.35</v>
+        <v>-0.348</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>46.079</v>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.86</v>
+        <v>18.855</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.15</v>
+        <v>1.151</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.28</v>
+        <v>-0.278</v>
       </c>
       <c r="J30" s="7" t="n">
         <v>6.818</v>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1277.61</v>
+        <v>1277.59</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>1212.93</v>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1267.27</v>
+        <v>1267.25</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>1208.61</v>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1262.13</v>
+        <v>1262.11</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>1207.14</v>
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1254.82</v>
+        <v>1254.8</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>1198.19</v>
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1259.66</v>
+        <v>1259.64</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>1200.39</v>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1260.24</v>
+        <v>1260.23</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1208.38</v>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1245.52</v>
+        <v>1245.5</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1215.57</v>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1198.22</v>
+        <v>1198.21</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>1211.65</v>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1222.89</v>
+        <v>1222.87</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1211.53</v>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1194.21</v>
+        <v>1194.2</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1219.54</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1190</v>
+        <v>1189.99</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>1221.46</v>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1182.27</v>
+        <v>1182.25</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>1219.01</v>
@@ -10404,7 +10404,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1179.97</v>
+        <v>1179.96</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>1213.02</v>
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1198.78</v>
+        <v>1198.77</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>1216.33</v>
@@ -10436,7 +10436,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1162.54</v>
+        <v>1162.53</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>1215.31</v>
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1139.17</v>
+        <v>1139.16</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>1190.57</v>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1145.74</v>
+        <v>1145.73</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1204.31</v>
@@ -10484,7 +10484,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1150.84</v>
+        <v>1150.82</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>1210.6</v>
@@ -10500,7 +10500,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1135.92</v>
+        <v>1135.9</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>1211.04</v>
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1141.77</v>
+        <v>1141.75</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>1217.19</v>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1128.9</v>
+        <v>1128.87</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>1222.04</v>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1130.69</v>
+        <v>1130.67</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>1221.91</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1067.1</v>
+        <v>1067.09</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1215.85</v>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1085.19</v>
+        <v>1085.17</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>1221.9</v>
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1081.87</v>
+        <v>1081.85</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>1211.56</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1102.76</v>
+        <v>1102.74</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>1205.7</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1078.44</v>
+        <v>1078.41</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>1190.64</v>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1105.07</v>
+        <v>1105.04</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1213.48</v>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1106.92</v>
+        <v>1106.89</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1219.33</v>
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1103.9</v>
+        <v>1103.87</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>1216.12</v>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1089.47</v>
+        <v>1089.45</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>1215.83</v>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1052.8</v>
+        <v>1052.77</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>1197.05</v>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1043.61</v>
+        <v>1043.57</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>1197.89</v>
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1058.28</v>
+        <v>1058.25</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>1199.83</v>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1091.47</v>
+        <v>1091.44</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>1205.87</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1086.37</v>
+        <v>1086.35</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>1202.69</v>
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1086.48</v>
+        <v>1086.45</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>1211.39</v>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1043.41</v>
+        <v>1043.39</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>1199.02</v>
@@ -10836,7 +10836,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1057.85</v>
+        <v>1057.83</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>1207.73</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1061.73</v>
+        <v>1061.72</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>1217.93</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1090.33</v>
+        <v>1090.32</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>1211.16</v>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1077.73</v>
+        <v>1077.72</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>1205.34</v>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1083.93</v>
+        <v>1083.94</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1203.83</v>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1081.57</v>
+        <v>1081.58</v>
       </c>
       <c r="C48" s="13" t="n">
         <v>1197.12</v>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1050.11</v>
+        <v>1050.13</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1181.43</v>
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1051.66</v>
+        <v>1051.68</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>1191.78</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1050.75</v>
+        <v>1050.76</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>1189.86</v>
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1065.14</v>
+        <v>1065.15</v>
       </c>
       <c r="C52" s="13" t="n">
         <v>1188.37</v>
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1051.01</v>
+        <v>1051.02</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>1170.33</v>
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1052.95</v>
+        <v>1052.97</v>
       </c>
       <c r="C54" s="13" t="n">
         <v>1163.7</v>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1045.55</v>
+        <v>1045.56</v>
       </c>
       <c r="C55" s="13" t="n">
         <v>1175.54</v>
@@ -11076,7 +11076,7 @@
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1057.81</v>
+        <v>1057.82</v>
       </c>
       <c r="C56" s="13" t="n">
         <v>1178.64</v>
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1049.92</v>
+        <v>1049.93</v>
       </c>
       <c r="C57" s="13" t="n">
         <v>1162.19</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1062.51</v>
+        <v>1062.52</v>
       </c>
       <c r="C58" s="13" t="n">
         <v>1159.33</v>
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1034.47</v>
+        <v>1034.48</v>
       </c>
       <c r="C59" s="13" t="n">
         <v>1142.71</v>
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1056.25</v>
+        <v>1056.26</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>1154.7</v>
@@ -11156,7 +11156,7 @@
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1060.9</v>
+        <v>1061.07</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11168,7 +11168,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1060.9</v>
+        <v>1061.07</v>
       </c>
     </row>
     <row r="64">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-15.78%</t>
+          <t>-15.76%</t>
         </is>
       </c>
     </row>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.75</v>
+        <v>54.78</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.013888888</v>
+        <v>0.014537034</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,19 +670,19 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.223</v>
+        <v>-0.222</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>37.018</v>
+        <v>37.042</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>48.818</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.297873</v>
+        <v>23.312767</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.5707035</v>
+        <v>14.580018</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>10.77</v>
@@ -694,10 +694,10 @@
         <v>0.888</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>-0.156</v>
+        <v>-0.155</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.66</v>
+        <v>107.75</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>-0.015724937</v>
+        <v>-0.014902151</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -732,7 +732,7 @@
         <v>-0.657</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.855</v>
+        <v>18.87</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>30.856</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.968362000000001</v>
+        <v>9.976694999999999</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14.473</v>
@@ -758,7 +758,7 @@
         <v>-0.5629999999999999</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>-0.507</v>
+        <v>-0.506</v>
       </c>
     </row>
     <row r="4">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.25</v>
+        <v>23.3</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>-0.02882802</v>
+        <v>-0.02673906</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -790,10 +790,10 @@
         <v>21.01</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.523</v>
+        <v>-0.522</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11.571</v>
+        <v>11.596</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>12.574</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>11.943174</v>
+        <v>11.9688635</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>46.079</v>
@@ -816,10 +816,10 @@
         <v>1.682</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>-0.426</v>
+        <v>-0.425</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>-0.348</v>
+        <v>-0.347</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.04</v>
+        <v>102.08</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.8998355000000001</v>
+        <v>0.9393895000000001</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,19 +851,19 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.243</v>
+        <v>-0.242</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.641</v>
+        <v>10.645</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>19.864</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.496815</v>
+        <v>32.509552</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>17.173334</v>
+        <v>17.180065</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>11.354</v>
@@ -875,10 +875,10 @@
         <v>1.034</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.213</v>
+        <v>0.214</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>-0.166</v>
+        <v>-0.165</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.96</v>
+        <v>36.99</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.027059056</v>
+        <v>0.10825688</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,19 +910,19 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.08</v>
+        <v>-0.079</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10.109</v>
+        <v>10.117</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>39.58</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>48.631577</v>
+        <v>48.671055</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>15.773907</v>
+        <v>15.786711</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>16.81</v>
@@ -934,10 +934,10 @@
         <v>1.396</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.56999999999999</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.01989257</v>
+        <v>0.019526464</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -972,16 +972,16 @@
         <v>-0.07099999999999999</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.309</v>
+        <v>6.307</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>8.542999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.704344</v>
+        <v>3.7030144</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.257247</v>
+        <v>10.253565</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>7.113</v>
@@ -1019,7 +1019,7 @@
         <v>86.2</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.018730785</v>
+        <v>0.01867164</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>118.46</v>
@@ -1037,10 +1037,10 @@
         <v>10.94</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.295841</v>
+        <v>16.294895</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>11.610039</v>
+        <v>11.609365</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>11.435</v>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>58.31</v>
+        <v>58.34</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4046087999999999</v>
+        <v>0.45650196</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1087,19 +1087,19 @@
         <v>35.09</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.155</v>
+        <v>-0.154</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.996</v>
+        <v>5.999</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>6.847</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>18.690706</v>
+        <v>18.700321</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>17.746878</v>
+        <v>17.756008</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>8.413</v>
@@ -1111,7 +1111,7 @@
         <v>1.453</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="Q9" s="9" t="n">
         <v>-0.055</v>
@@ -1137,7 +1137,7 @@
         <v>19.16</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-0.018674841</v>
+        <v>-0.018945255</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>32.22</v>
@@ -1149,16 +1149,16 @@
         <v>-0.405</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.672</v>
+        <v>5.67</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>5.563</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>53.23611</v>
+        <v>53.22222</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>23.366459</v>
+        <v>23.360363</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>10.962</v>
@@ -1170,7 +1170,7 @@
         <v>2.002</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>-0.166</v>
+        <v>-0.167</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>-0.178</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.79</v>
+        <v>10.8</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.010299593</v>
+        <v>0.01170412</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>14.38</v>
@@ -1205,19 +1205,19 @@
         <v>5.59</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.25</v>
+        <v>-0.249</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.456</v>
+        <v>5.463</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>4.993</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>25.690477</v>
+        <v>25.726192</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12.439331</v>
+        <v>12.456624</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>10.175</v>
@@ -1229,10 +1229,10 @@
         <v>1.1</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.551</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.067</v>
       </c>
     </row>
     <row r="12">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.77</v>
+        <v>21.78</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.09195613</v>
+        <v>0.1379342</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.039</v>
+        <v>-0.038</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.068</v>
+        <v>5.07</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>70.22581</v>
+        <v>70.258064</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>29.091444</v>
+        <v>29.104807</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.92</v>
+        <v>0.9209999999999999</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="14">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.53</v>
+        <v>5.54</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.010968999</v>
+        <v>0.01188301</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>10.15</v>
@@ -1451,19 +1451,19 @@
         <v>4.55</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.455</v>
+        <v>-0.454</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.25</v>
+        <v>2.252</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>12.762</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>12.021739</v>
+        <v>12.032608</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>6.9508166</v>
+        <v>6.957101</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>10.582</v>
@@ -1475,10 +1475,10 @@
         <v>0.603</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.006</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>-0.264</v>
+        <v>-0.263</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.4</v>
+        <v>14.41</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>-0.27700806</v>
+        <v>-0.17312756</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>20.61</v>
@@ -1513,7 +1513,7 @@
         <v>-0.301</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.923</v>
+        <v>1.925</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>12.411</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>8.273342</v>
+        <v>8.28196</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>17.184</v>
@@ -1536,10 +1536,10 @@
         <v>1.364</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>-0.17</v>
+        <v>-0.169</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>-0.03</v>
+        <v>-0.029</v>
       </c>
     </row>
     <row r="17">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>-0.17762396</v>
+        <v>11.26</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>13.31</v>
@@ -1693,19 +1693,19 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.156</v>
+        <v>-0.154</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.917</v>
+        <v>0.919</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>1.242</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>18.733332</v>
+        <v>18.766666</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>12.1378355</v>
+        <v>12.159433</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>6.569</v>
@@ -1717,10 +1717,10 @@
         <v>1.07</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="20">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>-0.30769202</v>
+        <v>-0.46154168</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>9.949999999999999</v>
@@ -1882,7 +1882,7 @@
         <v>6.1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.349</v>
+        <v>-0.35</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0.175</v>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>8.649687999999999</v>
+        <v>8.636339</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>6.818</v>
@@ -1908,10 +1908,10 @@
         <v>1.206</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>-0.292</v>
+        <v>-0.293</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>-0.278</v>
+        <v>-0.279</v>
       </c>
     </row>
     <row r="23">
@@ -2158,16 +2158,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.75</v>
+        <v>54.78</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.013888888</v>
+        <v>0.014537034</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.156</v>
+        <v>-0.155</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>53.2</v>
@@ -2179,7 +2179,7 @@
         <v>-0.017</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.223</v>
+        <v>-0.222</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.66</v>
+        <v>107.75</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.015724937</v>
+        <v>-0.014902151</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0.507</v>
+        <v>-0.506</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>-0.5629999999999999</v>
@@ -2220,10 +2220,10 @@
         <v>-56.8</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.252</v>
+        <v>-0.251</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.532</v>
+        <v>-0.531</v>
       </c>
       <c r="K3" s="5" t="n">
         <v>-0.657</v>
@@ -2252,28 +2252,28 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.25</v>
+        <v>23.3</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.02882802</v>
+        <v>-0.02673906</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.348</v>
+        <v>-0.347</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.426</v>
+        <v>-0.425</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>-36</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.144</v>
+        <v>-0.142</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.349</v>
+        <v>-0.348</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.523</v>
+        <v>-0.522</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
@@ -2299,28 +2299,28 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.04</v>
+        <v>102.08</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.8998355000000001</v>
+        <v>0.9393895000000001</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.166</v>
+        <v>-0.165</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.213</v>
+        <v>0.214</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>34.7</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>-0.107</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.243</v>
+        <v>-0.242</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>1.034</v>
@@ -2346,28 +2346,28 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.96</v>
+        <v>36.99</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.027059056</v>
+        <v>0.10825688</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>11.9</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.08</v>
+        <v>-0.079</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>1.396</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.56999999999999</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.01989257</v>
+        <v>0.019526464</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>-0.028</v>
@@ -2443,7 +2443,7 @@
         <v>86.2</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.018730785</v>
+        <v>0.01867164</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>-0.23</v>
@@ -2487,28 +2487,28 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>58.31</v>
+        <v>58.34</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.4046087999999999</v>
+        <v>0.45650196</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>-0.055</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>39.1</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.05400000000000001</v>
+        <v>-0.053</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.006</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.155</v>
+        <v>-0.154</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>1.453</v>
@@ -2537,13 +2537,13 @@
         <v>19.16</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.018674841</v>
+        <v>-0.018945255</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>-0.178</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.166</v>
+        <v>-0.167</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>-28.1</v>
@@ -2581,28 +2581,28 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.79</v>
+        <v>10.8</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.010299593</v>
+        <v>0.01170412</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.067</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.551</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>27.6</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.073</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.039</v>
+        <v>-0.038</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.25</v>
+        <v>-0.249</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>1.1</v>
@@ -2675,28 +2675,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.77</v>
+        <v>21.78</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.09195613</v>
+        <v>0.1379342</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.92</v>
+        <v>0.9209999999999999</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>51.2</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>0.191</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.039</v>
+        <v>-0.038</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2769,28 +2769,28 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.53</v>
+        <v>5.54</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.010968999</v>
+        <v>0.01188301</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.264</v>
+        <v>-0.263</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.006</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>8.6</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.081</v>
+        <v>-0.08</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.296</v>
+        <v>-0.294</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.455</v>
+        <v>-0.454</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>0.603</v>
@@ -2816,25 +2816,25 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.4</v>
+        <v>14.41</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.27700806</v>
+        <v>-0.17312756</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.03</v>
+        <v>-0.029</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.17</v>
+        <v>-0.169</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>-19.3</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.114</v>
+        <v>-0.113</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>-0.301</v>
@@ -2957,28 +2957,28 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.24</v>
+        <v>11.26</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-0.17762396</v>
+        <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.01</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>-1.2</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.156</v>
+        <v>-0.154</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.07</v>
@@ -3100,28 +3100,28 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.30769202</v>
+        <v>-0.46154168</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.278</v>
+        <v>-0.279</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.292</v>
+        <v>-0.293</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>4.5</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.226</v>
+        <v>-0.228</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.243</v>
+        <v>-0.244</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.349</v>
+        <v>-0.35</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.206</v>
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.75</v>
+        <v>54.78</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>37.018</v>
+        <v>37.042</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>23.297873</v>
+        <v>23.312767</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.5707035</v>
+        <v>14.580018</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>10.77</v>
@@ -3369,10 +3369,10 @@
         <v>3.75</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.23854</v>
+        <v>23.253397</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.8438475</v>
+        <v>2.8456655</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.66</v>
+        <v>107.75</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.855</v>
+        <v>18.87</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.968362000000001</v>
+        <v>9.976694999999999</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>14.473</v>
@@ -3424,10 +3424,10 @@
         <v>1.883</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.087243</v>
+        <v>2.0889878</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1508712</v>
+        <v>1.1518332</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.25</v>
+        <v>23.3</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.571</v>
+        <v>11.596</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>11.943174</v>
+        <v>11.9688635</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>46.079</v>
@@ -3479,10 +3479,10 @@
         <v>2.077</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>18.217085</v>
+        <v>18.25627</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.9110868</v>
+        <v>1.9151975</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3511,16 +3511,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.04</v>
+        <v>102.08</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.641</v>
+        <v>10.645</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.496815</v>
+        <v>32.509552</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>17.173334</v>
+        <v>17.180065</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>11.354</v>
@@ -3532,10 +3532,10 @@
         <v>2.783</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-37.96131</v>
+        <v>-37.976192</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.4907789</v>
+        <v>1.4913633</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3564,16 +3564,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.96</v>
+        <v>36.99</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.109</v>
+        <v>10.117</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>48.631577</v>
+        <v>48.671055</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>15.773907</v>
+        <v>15.786711</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>16.81</v>
@@ -3585,10 +3585,10 @@
         <v>2.257</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.9289892</v>
+        <v>3.9321785</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.5764044</v>
+        <v>0.5768723</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3617,16 +3617,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.56999999999999</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.309</v>
+        <v>6.307</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.704344</v>
+        <v>3.7030144</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.257247</v>
+        <v>10.253565</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>7.113</v>
@@ -3638,10 +3638,10 @@
         <v>2.088</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.4466434</v>
+        <v>2.445765</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5417646</v>
+        <v>1.5412111</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>22.56</v>
@@ -3676,10 +3676,10 @@
         <v>6.008</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>16.295841</v>
+        <v>16.294895</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>11.610039</v>
+        <v>11.609365</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>11.435</v>
@@ -3691,10 +3691,10 @@
         <v>3.739</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>5.9423037</v>
+        <v>5.941959</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.0534453</v>
+        <v>2.0533264</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>5.29</v>
@@ -3723,16 +3723,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>58.31</v>
+        <v>58.34</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.996</v>
+        <v>5.999</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>18.690706</v>
+        <v>18.700321</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>17.746878</v>
+        <v>17.756008</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>8.413</v>
@@ -3744,10 +3744,10 @@
         <v>3.404</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.325588</v>
+        <v>16.333986</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.9810596</v>
+        <v>2.982593</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>3.12</v>
@@ -3779,13 +3779,13 @@
         <v>19.16</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.672</v>
+        <v>5.67</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>53.23611</v>
+        <v>53.22222</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>23.366459</v>
+        <v>23.360363</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>10.962</v>
@@ -3797,10 +3797,10 @@
         <v>4.312</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.088839</v>
+        <v>5.087511</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>4.396951</v>
+        <v>4.395804</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.36</v>
@@ -3829,16 +3829,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.79</v>
+        <v>10.8</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.456</v>
+        <v>5.463</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>25.690477</v>
+        <v>25.726192</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>12.439331</v>
+        <v>12.456624</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>10.175</v>
@@ -3850,10 +3850,10 @@
         <v>2.131</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.3251863</v>
+        <v>7.33537</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2.328653</v>
+        <v>2.3318906</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>0.42</v>
@@ -3937,16 +3937,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.77</v>
+        <v>21.78</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5.068</v>
+        <v>5.07</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>70.22581</v>
+        <v>70.258064</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>29.091444</v>
+        <v>29.104807</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>14.779362</v>
+        <v>14.786151</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.4672027</v>
+        <v>4.4692545</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -4051,16 +4051,16 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.53</v>
+        <v>5.54</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.25</v>
+        <v>2.252</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>12.021739</v>
+        <v>12.032608</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.9508166</v>
+        <v>6.957101</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>10.582</v>
@@ -4072,10 +4072,10 @@
         <v>2.472</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1.7329991</v>
+        <v>-1.734566</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.43568265</v>
+        <v>0.43607658</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.46</v>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.4</v>
+        <v>14.41</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.923</v>
+        <v>1.925</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>8.273342</v>
+        <v>8.28196</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>17.184</v>
@@ -4127,10 +4127,10 @@
         <v>1.783</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.9912576</v>
+        <v>0.9922902</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.27626294</v>
+        <v>0.2765507</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-5.83</v>
@@ -4269,16 +4269,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.24</v>
+        <v>11.26</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.917</v>
+        <v>0.919</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>18.733332</v>
+        <v>18.766666</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>12.1378355</v>
+        <v>12.159433</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>6.569</v>
@@ -4290,10 +4290,10 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>3.4299664</v>
+        <v>3.4360697</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.68888867</v>
+        <v>0.6901145</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0.6</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0.175</v>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>8.649687999999999</v>
+        <v>8.636339</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>6.818</v>
@@ -4461,10 +4461,10 @@
         <v>1.666</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-10.746269</v>
+        <v>-10.729685</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.5766065</v>
+        <v>0.5757166</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>-0.58</v>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>54.75</v>
+        <v>54.78</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>107.66</v>
+        <v>107.75</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.976</v>
+        <v>0.9740000000000001</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>1.72</v>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23.25</v>
+        <v>23.3</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.556</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>102.04</v>
+        <v>102.08</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.39</v>
+        <v>0.389</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.24</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>36.96</v>
+        <v>36.99</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.2</v>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>83.56999999999999</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>84</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.32</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>58.31</v>
+        <v>58.34</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>59</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>3.89</v>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10.79</v>
+        <v>10.8</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.61</v>
+        <v>0.609</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4.92</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>21.77</v>
+        <v>21.78</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5.53</v>
+        <v>5.54</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>6.3</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.677</v>
+        <v>0.674</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>2.08</v>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14.4</v>
+        <v>14.41</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.327</v>
+        <v>0.326</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>4.18</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11.24</v>
+        <v>11.26</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.379</v>
+        <v>0.377</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>3.68</v>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.058</v>
+        <v>1.061</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>13.9</v>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>37.018</v>
+        <v>37.042</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>23.297873</v>
+        <v>23.312767</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -7722,7 +7722,7 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.156</v>
+        <v>-0.155</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>10.77</v>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.25</v>
+        <v>2.252</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>12.021739</v>
+        <v>12.032608</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.264</v>
+        <v>-0.263</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>10.582</v>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>10.109</v>
+        <v>10.117</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>48.631577</v>
+        <v>48.671055</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.06</v>
@@ -7858,7 +7858,7 @@
         <v>0.1489</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="J6" s="7" t="n">
         <v>16.81</v>
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.641</v>
+        <v>10.645</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>32.496815</v>
+        <v>32.509552</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.015</v>
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.166</v>
+        <v>-0.165</v>
       </c>
       <c r="J7" s="7" t="n">
         <v>11.354</v>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.309</v>
+        <v>6.307</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.704344</v>
+        <v>3.7030144</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -7998,7 +7998,7 @@
         <v>6.008</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>16.295841</v>
+        <v>16.294895</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.067</v>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5.996</v>
+        <v>5.999</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.690706</v>
+        <v>18.700321</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.923</v>
+        <v>1.925</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.03</v>
+        <v>-0.029</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>17.184</v>
@@ -8333,10 +8333,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.456</v>
+        <v>5.463</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.690477</v>
+        <v>25.726192</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -8348,7 +8348,7 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.067</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>10.175</v>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.672</v>
+        <v>5.67</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>53.23611</v>
+        <v>53.22222</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.068</v>
+        <v>5.07</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>70.22581</v>
+        <v>70.258064</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -8436,7 +8436,7 @@
         <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>11.571</v>
+        <v>11.596</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.348</v>
+        <v>-0.347</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>46.079</v>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.855</v>
+        <v>18.87</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>-0.038829997</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-0.507</v>
+        <v>-0.506</v>
       </c>
       <c r="J24" s="7" t="n">
         <v>14.473</v>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.917</v>
+        <v>0.919</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.733332</v>
+        <v>18.766666</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0.075</v>
@@ -8642,7 +8642,7 @@
         <v>0.19236</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.01</v>
       </c>
       <c r="J28" s="7" t="n">
         <v>6.569</v>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.278</v>
+        <v>-0.279</v>
       </c>
       <c r="J30" s="7" t="n">
         <v>6.818</v>
@@ -10212,10 +10212,10 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1277.59</v>
+        <v>1277.56</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>1212.93</v>
+        <v>1212.94</v>
       </c>
       <c r="D2" s="13" t="n">
         <v>1068.57</v>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1267.25</v>
+        <v>1267.23</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>1208.61</v>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1262.11</v>
+        <v>1262.08</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>1207.14</v>
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1254.8</v>
+        <v>1254.78</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>1198.19</v>
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1259.64</v>
+        <v>1259.62</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>1200.39</v>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1260.23</v>
+        <v>1260.2</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1208.38</v>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1245.5</v>
+        <v>1245.47</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1215.57</v>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1198.21</v>
+        <v>1198.18</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>1211.65</v>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1222.87</v>
+        <v>1222.85</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1211.53</v>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1194.2</v>
+        <v>1194.17</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1219.54</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1189.99</v>
+        <v>1189.97</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>1221.46</v>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1182.25</v>
+        <v>1182.22</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>1219.01</v>
@@ -10404,7 +10404,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1179.96</v>
+        <v>1179.93</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>1213.02</v>
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1198.77</v>
+        <v>1198.74</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>1216.33</v>
@@ -10436,7 +10436,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1162.53</v>
+        <v>1162.49</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>1215.31</v>
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1139.16</v>
+        <v>1139.13</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>1190.57</v>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1145.73</v>
+        <v>1145.7</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1204.31</v>
@@ -10484,7 +10484,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1150.82</v>
+        <v>1150.79</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>1210.6</v>
@@ -10500,7 +10500,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1135.9</v>
+        <v>1135.86</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>1211.04</v>
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1141.75</v>
+        <v>1141.72</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>1217.19</v>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1128.87</v>
+        <v>1128.84</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>1222.04</v>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1130.67</v>
+        <v>1130.63</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>1221.91</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1078.7</v>
+        <v>1078.66</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>1219.49</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1067.09</v>
+        <v>1067.04</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1215.85</v>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1085.17</v>
+        <v>1085.12</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>1221.9</v>
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1081.85</v>
+        <v>1081.8</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>1211.56</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1102.74</v>
+        <v>1102.69</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>1205.7</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1078.41</v>
+        <v>1078.36</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>1190.64</v>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1105.04</v>
+        <v>1105</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1213.48</v>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1106.89</v>
+        <v>1106.85</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1219.33</v>
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1103.87</v>
+        <v>1103.83</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>1216.12</v>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1089.45</v>
+        <v>1089.4</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>1215.83</v>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1052.77</v>
+        <v>1052.73</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>1197.05</v>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1043.57</v>
+        <v>1043.52</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>1197.89</v>
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1058.25</v>
+        <v>1058.2</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>1199.83</v>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1091.44</v>
+        <v>1091.38</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>1205.87</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1086.35</v>
+        <v>1086.28</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>1202.69</v>
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1086.45</v>
+        <v>1086.39</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>1211.39</v>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1043.39</v>
+        <v>1043.33</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>1199.02</v>
@@ -10836,7 +10836,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1057.83</v>
+        <v>1057.78</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>1207.73</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1061.72</v>
+        <v>1061.67</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>1217.93</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1090.32</v>
+        <v>1090.26</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>1211.16</v>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1077.72</v>
+        <v>1077.67</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>1205.34</v>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1072.59</v>
+        <v>1072.54</v>
       </c>
       <c r="C45" s="13" t="n">
         <v>1206.03</v>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1068.53</v>
+        <v>1068.49</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>1195.4</v>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1083.94</v>
+        <v>1083.89</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1203.83</v>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1081.58</v>
+        <v>1081.53</v>
       </c>
       <c r="C48" s="13" t="n">
         <v>1197.12</v>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1050.13</v>
+        <v>1050.08</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1181.43</v>
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1051.68</v>
+        <v>1051.63</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>1191.78</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1050.76</v>
+        <v>1050.72</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>1189.86</v>
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1065.15</v>
+        <v>1065.11</v>
       </c>
       <c r="C52" s="13" t="n">
         <v>1188.37</v>
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1051.02</v>
+        <v>1050.98</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>1170.33</v>
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1052.97</v>
+        <v>1052.92</v>
       </c>
       <c r="C54" s="13" t="n">
         <v>1163.7</v>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1045.56</v>
+        <v>1045.51</v>
       </c>
       <c r="C55" s="13" t="n">
         <v>1175.54</v>
@@ -11076,7 +11076,7 @@
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1057.82</v>
+        <v>1057.77</v>
       </c>
       <c r="C56" s="13" t="n">
         <v>1178.64</v>
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1049.93</v>
+        <v>1049.88</v>
       </c>
       <c r="C57" s="13" t="n">
         <v>1162.19</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1062.52</v>
+        <v>1062.47</v>
       </c>
       <c r="C58" s="13" t="n">
         <v>1159.33</v>
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1034.48</v>
+        <v>1034.43</v>
       </c>
       <c r="C59" s="13" t="n">
         <v>1142.71</v>
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1056.26</v>
+        <v>1056.21</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>1154.7</v>
@@ -11156,7 +11156,7 @@
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1061.07</v>
+        <v>1061.72</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11168,7 +11168,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1061.07</v>
+        <v>1061.72</v>
       </c>
     </row>
     <row r="64">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-15.76%</t>
+          <t>-15.71%</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>140</v>
+        <v>140.1</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.78</v>
+        <v>54.93</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.014537034</v>
+        <v>0.017222228</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,19 +670,19 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.222</v>
+        <v>-0.22</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>37.042</v>
+        <v>37.14</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>48.818</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.312767</v>
+        <v>23.37447</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.580018</v>
+        <v>14.618607</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>10.77</v>
@@ -694,10 +694,10 @@
         <v>0.888</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.348</v>
+        <v>0.351</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>-0.155</v>
+        <v>-0.153</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.75</v>
+        <v>107.92</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>-0.014902151</v>
+        <v>-0.013347954</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -729,10 +729,10 @@
         <v>99.95999999999999</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-0.657</v>
+        <v>-0.6559999999999999</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.87</v>
+        <v>18.9</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>30.856</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.976694999999999</v>
+        <v>9.992435</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14.473</v>
@@ -755,7 +755,7 @@
         <v>1.177</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>-0.506</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.3</v>
+        <v>23.43</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>-0.02673906</v>
+        <v>-0.021307719</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -790,10 +790,10 @@
         <v>21.01</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.522</v>
+        <v>-0.52</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11.596</v>
+        <v>11.66</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>12.574</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>11.9688635</v>
+        <v>12.035657</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>46.079</v>
@@ -816,10 +816,10 @@
         <v>1.682</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>-0.425</v>
+        <v>-0.422</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>-0.347</v>
+        <v>-0.343</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.08</v>
+        <v>102.95</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.9393895000000001</v>
+        <v>0.017996635</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,19 +851,19 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.242</v>
+        <v>-0.236</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.645</v>
+        <v>10.736</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>19.864</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.509552</v>
+        <v>32.78662</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>17.180065</v>
+        <v>17.326487</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>11.354</v>
@@ -875,10 +875,10 @@
         <v>1.034</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.214</v>
+        <v>0.224</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>-0.165</v>
+        <v>-0.158</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.99</v>
+        <v>37.23</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.10825688</v>
+        <v>0.75777745</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,19 +910,19 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.073</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10.117</v>
+        <v>10.183</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>39.58</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>48.671055</v>
+        <v>48.986843</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>15.786711</v>
+        <v>15.889138</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>16.81</v>
@@ -934,10 +934,10 @@
         <v>1.396</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.141</v>
+        <v>0.148</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.54000000000001</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.019526464</v>
+        <v>0.024286036</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -969,19 +969,19 @@
         <v>58.94</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.067</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.307</v>
+        <v>6.336</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>8.542999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.7030144</v>
+        <v>3.7203016</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.253565</v>
+        <v>10.301433</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>7.113</v>
@@ -993,21 +993,21 @@
         <v>1.22</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.219</v>
+        <v>0.224</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>-0.028</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1016,57 +1016,57 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>86.2</v>
+        <v>58.56</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.01867164</v>
+        <v>0.82644546</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>118.46</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>80.23999999999999</v>
+        <v>35.09</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.272</v>
+        <v>-0.151</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.008</v>
+        <v>6.022</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>10.94</v>
+        <v>6.847</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.294895</v>
+        <v>18.769232</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>11.609365</v>
+        <v>17.82144</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>11.435</v>
+        <v>8.413</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="P8" s="9" t="n">
-        <v>-0.239</v>
+        <v>1.453</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0.37</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>-0.23</v>
+        <v>-0.051</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1075,46 +1075,46 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>58.34</v>
+        <v>85.86</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.45650196</v>
+        <v>0.014712776</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>68.98999999999999</v>
+        <v>118.46</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>35.09</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.275</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.999</v>
+        <v>5.984</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>6.847</v>
+        <v>10.94</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>18.700321</v>
+        <v>16.23157</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>17.756008</v>
+        <v>11.564247</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>8.413</v>
+        <v>11.435</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>1.453</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0.365</v>
+        <v>0.66</v>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>-0.242</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>-0.055</v>
+        <v>-0.233</v>
       </c>
     </row>
     <row r="10">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.16</v>
+        <v>19.33</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-0.018945255</v>
+        <v>-0.010240694</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>32.22</v>
@@ -1146,19 +1146,19 @@
         <v>15.725</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.405</v>
+        <v>-0.4</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.67</v>
+        <v>5.721</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>5.563</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>53.22222</v>
+        <v>53.694443</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>23.360363</v>
+        <v>23.56763</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>10.962</v>
@@ -1170,10 +1170,10 @@
         <v>2.002</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>-0.167</v>
+        <v>-0.159</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>-0.178</v>
+        <v>-0.171</v>
       </c>
     </row>
     <row r="11">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.01170412</v>
+        <v>0.020599186</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>14.38</v>
@@ -1205,19 +1205,19 @@
         <v>5.59</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.249</v>
+        <v>-0.242</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.463</v>
+        <v>5.511</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>4.993</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>25.726192</v>
+        <v>25.952381</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12.456624</v>
+        <v>12.566145</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>10.175</v>
@@ -1229,10 +1229,10 @@
         <v>1.1</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>-0.067</v>
+        <v>-0.059</v>
       </c>
     </row>
     <row r="12">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.36</v>
+        <v>26.41</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-0.30257156</v>
+        <v>-0.09455226</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>31.58</v>
@@ -1264,10 +1264,10 @@
         <v>17.86</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.164</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.38</v>
+        <v>5.392</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>30.298</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="L12" s="7" t="n">
-        <v>28.497297</v>
+        <v>28.556757</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>8.669</v>
@@ -1290,10 +1290,10 @@
         <v>1.977</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>-0.063</v>
+        <v>-0.061</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.119</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.78</v>
+        <v>22.04</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1379342</v>
+        <v>0.013333375</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.038</v>
+        <v>-0.027</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.07</v>
+        <v>5.131</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>70.258064</v>
+        <v>71.09678</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>29.104807</v>
+        <v>29.452248</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.9209999999999999</v>
+        <v>0.9440000000000001</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.128</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="14">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>12.96</v>
+        <v>13</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>-0.6896563</v>
+        <v>-0.3831432200000001</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>18.57</v>
@@ -1390,10 +1390,10 @@
         <v>12.53</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-0.302</v>
+        <v>-0.3</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.391</v>
+        <v>2.399</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>5.976</v>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="L14" s="7" t="n">
-        <v>12.027395</v>
+        <v>12.064517</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>6.776</v>
@@ -1416,10 +1416,10 @@
         <v>1.082</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>-0.036</v>
+        <v>-0.033</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>-0.138</v>
+        <v>-0.135</v>
       </c>
     </row>
     <row r="15">
@@ -1442,7 +1442,7 @@
         <v>5.54</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.01188301</v>
+        <v>0.013711205</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>10.15</v>
@@ -1454,16 +1454,16 @@
         <v>-0.454</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.252</v>
+        <v>2.256</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>12.762</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>12.032608</v>
+        <v>12.054348</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>6.957101</v>
+        <v>6.969671</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>10.582</v>
@@ -1475,10 +1475,10 @@
         <v>0.603</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>-0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>-0.263</v>
+        <v>-0.262</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.41</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>-0.17312756</v>
+        <v>14.54</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0.6578966000000002</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>20.61</v>
@@ -1510,10 +1510,10 @@
         <v>11.65</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.301</v>
+        <v>-0.295</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.925</v>
+        <v>1.941</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>12.411</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>8.28196</v>
+        <v>8.350904</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>17.184</v>
@@ -1536,10 +1536,10 @@
         <v>1.364</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>-0.169</v>
+        <v>-0.162</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>-0.029</v>
+        <v>-0.021</v>
       </c>
     </row>
     <row r="17">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.3</v>
+        <v>98.72</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.040709257</v>
+        <v>0.4681448</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>113.88</v>
@@ -1571,19 +1571,19 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.137</v>
+        <v>-0.133</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.758</v>
+        <v>1.766</v>
       </c>
       <c r="J17" s="6" t="n">
         <v>1.674</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>18.103132</v>
+        <v>18.18048</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>16.534903</v>
+        <v>16.60555</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>8.779</v>
@@ -1595,10 +1595,10 @@
         <v>1.376</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.227</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.027</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="18">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.47</v>
+        <v>4.51</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>-0.04787232399999999</v>
+        <v>-0.039361691</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.73</v>
@@ -1630,10 +1630,10 @@
         <v>4.46</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.674</v>
+        <v>-0.672</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.151</v>
+        <v>1.161</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>0.908</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>4.5202017</v>
+        <v>4.560606</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>-7.528</v>
@@ -1658,10 +1658,10 @@
         <v>1.993</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>-0.595</v>
+        <v>-0.591</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>-0.585</v>
+        <v>-0.581</v>
       </c>
     </row>
     <row r="19">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>11.29</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0.26642746</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>13.31</v>
@@ -1693,19 +1693,19 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.152</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.919</v>
+        <v>0.921</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>1.242</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>18.766666</v>
+        <v>18.816666</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>12.159433</v>
+        <v>12.19183</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>6.569</v>
@@ -1717,10 +1717,10 @@
         <v>1.07</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.107</v>
+        <v>0.11</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>-0.01</v>
+        <v>-0.006999999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.66</v>
+        <v>26.72</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.011380851</v>
+        <v>0.013657007</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>32.74</v>
@@ -1752,10 +1752,10 @@
         <v>19.57</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.186</v>
+        <v>-0.184</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.704</v>
+        <v>0.705</v>
       </c>
       <c r="J20" s="6" t="n">
         <v>1.153</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>22.033056</v>
+        <v>22.082644</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>9.449</v>
@@ -1778,10 +1778,10 @@
         <v>1.412</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>-0.013</v>
+        <v>-0.011</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>-0.015</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="21">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.47</v>
+        <v>6.46</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>-0.46154168</v>
+        <v>-0.5388737300000001</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>9.949999999999999</v>
@@ -1882,7 +1882,7 @@
         <v>6.1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.35</v>
+        <v>-0.351</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0.175</v>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>8.636339</v>
+        <v>8.629664999999999</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>6.818</v>
@@ -1934,7 +1934,7 @@
         <v>2.27</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>-0.021551704</v>
+        <v>-0.02150854</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>4.95</v>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="L23" s="7" t="n">
-        <v>-5.5365853</v>
+        <v>-5.5368295</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>12.539</v>
@@ -2158,28 +2158,28 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.78</v>
+        <v>54.93</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.014537034</v>
+        <v>0.017222228</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.155</v>
+        <v>-0.153</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.348</v>
+        <v>0.351</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>53.2</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.034</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.014</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.222</v>
+        <v>-0.22</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
@@ -2205,28 +2205,28 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.75</v>
+        <v>107.92</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.014902151</v>
+        <v>-0.013347954</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>-0.506</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>-56.8</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.251</v>
+        <v>-0.25</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>-0.531</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.657</v>
+        <v>-0.6559999999999999</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>1.177</v>
@@ -2252,28 +2252,28 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.3</v>
+        <v>23.43</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.02673906</v>
+        <v>-0.021307719</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.347</v>
+        <v>-0.343</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.425</v>
+        <v>-0.422</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>-36</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.142</v>
+        <v>-0.137</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.348</v>
+        <v>-0.344</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.522</v>
+        <v>-0.52</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
@@ -2299,28 +2299,28 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.08</v>
+        <v>102.95</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.9393895000000001</v>
+        <v>0.017996635</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.158</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.214</v>
+        <v>0.224</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.063</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.107</v>
+        <v>-0.1</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.242</v>
+        <v>-0.236</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>1.034</v>
@@ -2346,28 +2346,28 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.99</v>
+        <v>37.23</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.10825688</v>
+        <v>0.75777745</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.141</v>
+        <v>0.148</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>11.9</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.044</v>
+        <v>0.05</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.052</v>
+        <v>0.059</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.073</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>1.396</v>
@@ -2393,28 +2393,28 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.54000000000001</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.019526464</v>
+        <v>0.024286036</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.024</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.219</v>
+        <v>0.224</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>20.5</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.067</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>1.22</v>
@@ -2426,12 +2426,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2440,45 +2440,45 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>86.2</v>
+        <v>58.56</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.01867164</v>
+        <v>0.82644546</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.23</v>
+        <v>-0.051</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.239</v>
+        <v>0.37</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>-3.2</v>
+        <v>39.1</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.091</v>
+        <v>-0.05</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.146</v>
+        <v>-0.002</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.272</v>
+        <v>-0.151</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.66</v>
+        <v>1.453</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>1091240</v>
+        <v>941430</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2487,34 +2487,34 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>58.34</v>
+        <v>85.86</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.45650196</v>
+        <v>0.014712776</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.055</v>
+        <v>-0.233</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.365</v>
+        <v>-0.242</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>39.1</v>
+        <v>-3.2</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.053</v>
+        <v>-0.094</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.15</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.275</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>1.453</v>
+        <v>0.66</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>941430</v>
+        <v>1091240</v>
       </c>
     </row>
     <row r="10">
@@ -2534,28 +2534,28 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.16</v>
+        <v>19.33</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.018945255</v>
+        <v>-0.010240694</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.178</v>
+        <v>-0.171</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.167</v>
+        <v>-0.159</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>-28.1</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.043</v>
+        <v>0.052</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-0.218</v>
+        <v>-0.211</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.405</v>
+        <v>-0.4</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>2.002</v>
@@ -2581,28 +2581,28 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.01170412</v>
+        <v>0.020599186</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.059</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>27.6</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.038</v>
+        <v>-0.029</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.249</v>
+        <v>-0.242</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>1.1</v>
@@ -2628,28 +2628,28 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.36</v>
+        <v>26.41</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.30257156</v>
+        <v>-0.09455226</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.119</v>
+        <v>0.121</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.063</v>
+        <v>-0.061</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>-22.7</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.124</v>
+        <v>0.126</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.164</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>1.977</v>
@@ -2675,28 +2675,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.78</v>
+        <v>22.04</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.1379342</v>
+        <v>0.013333375</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.128</v>
+        <v>0.141</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.9209999999999999</v>
+        <v>0.9440000000000001</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>51.2</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.158</v>
+        <v>0.172</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.191</v>
+        <v>0.205</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.038</v>
+        <v>-0.027</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2722,28 +2722,28 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>12.96</v>
+        <v>13</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.6896563</v>
+        <v>-0.3831432200000001</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.138</v>
+        <v>-0.135</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.036</v>
+        <v>-0.033</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>13.4</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.057</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.161</v>
+        <v>-0.159</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-0.302</v>
+        <v>-0.3</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>1.082</v>
@@ -2772,13 +2772,13 @@
         <v>5.54</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.01188301</v>
+        <v>0.013711205</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.263</v>
+        <v>-0.262</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>8.6</v>
@@ -2816,28 +2816,28 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.41</v>
+        <v>14.54</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.17312756</v>
+        <v>0.6578966000000002</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.021</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.169</v>
+        <v>-0.162</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>-19.3</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.046</v>
+        <v>0.055</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.113</v>
+        <v>-0.105</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.301</v>
+        <v>-0.295</v>
       </c>
       <c r="L16" s="8" t="n">
         <v>1.364</v>
@@ -2863,28 +2863,28 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.3</v>
+        <v>98.72</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.040709257</v>
+        <v>0.4681448</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.027</v>
+        <v>0.031</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.227</v>
+        <v>0.232</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>20.6</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.036</v>
+        <v>0.04</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.023</v>
+        <v>0.027</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.137</v>
+        <v>-0.133</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.376</v>
@@ -2910,28 +2910,28 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.47</v>
+        <v>4.51</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.04787232399999999</v>
+        <v>-0.039361691</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.585</v>
+        <v>-0.581</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.595</v>
+        <v>-0.591</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>-32.1</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.379</v>
+        <v>-0.374</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5589999999999999</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.674</v>
+        <v>-0.672</v>
       </c>
       <c r="L18" s="8" t="n">
         <v>1.993</v>
@@ -2957,28 +2957,28 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.26</v>
+        <v>11.29</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>0.26642746</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.107</v>
+        <v>0.11</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>-1.2</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.152</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.07</v>
@@ -3004,28 +3004,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.66</v>
+        <v>26.72</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.011380851</v>
+        <v>0.013657007</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.015</v>
+        <v>-0.012</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.013</v>
+        <v>-0.011</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>5.3</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.046</v>
+        <v>-0.044</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.006</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.186</v>
+        <v>-0.184</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>1.412</v>
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.47</v>
+        <v>6.46</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.46154168</v>
+        <v>-0.5388737300000001</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>-0.279</v>
@@ -3115,13 +3115,13 @@
         <v>4.5</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.228</v>
+        <v>-0.229</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.244</v>
+        <v>-0.246</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.35</v>
+        <v>-0.351</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.206</v>
@@ -3150,7 +3150,7 @@
         <v>2.27</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-0.021551704</v>
+        <v>-0.02150854</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>-0.092</v>
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.78</v>
+        <v>54.93</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>37.042</v>
+        <v>37.14</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>23.312767</v>
+        <v>23.37447</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.580018</v>
+        <v>14.618607</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>10.77</v>
@@ -3369,10 +3369,10 @@
         <v>3.75</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.253397</v>
+        <v>23.314941</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.8456655</v>
+        <v>2.853197</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.75</v>
+        <v>107.92</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.87</v>
+        <v>18.9</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.976694999999999</v>
+        <v>9.992435</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>14.473</v>
@@ -3424,10 +3424,10 @@
         <v>1.883</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.0889878</v>
+        <v>2.0922837</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1518332</v>
+        <v>1.1536504</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.3</v>
+        <v>23.43</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.596</v>
+        <v>11.66</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>11.9688635</v>
+        <v>12.035657</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>46.079</v>
@@ -3479,10 +3479,10 @@
         <v>2.077</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>18.25627</v>
+        <v>18.35815</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.9151975</v>
+        <v>1.9258853</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3511,16 +3511,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.08</v>
+        <v>102.95</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.645</v>
+        <v>10.736</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.509552</v>
+        <v>32.78662</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>17.180065</v>
+        <v>17.326487</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>11.354</v>
@@ -3532,10 +3532,10 @@
         <v>2.783</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-37.976192</v>
+        <v>-38.29985</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.4913633</v>
+        <v>1.5040737</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3564,16 +3564,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.99</v>
+        <v>37.23</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.117</v>
+        <v>10.183</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>48.671055</v>
+        <v>48.986843</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>15.786711</v>
+        <v>15.889138</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>16.81</v>
@@ -3585,10 +3585,10 @@
         <v>2.257</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.9321785</v>
+        <v>3.9576912</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.5768723</v>
+        <v>0.58061516</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3617,16 +3617,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.54000000000001</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.307</v>
+        <v>6.336</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.7030144</v>
+        <v>3.7203016</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.253565</v>
+        <v>10.301433</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>7.113</v>
@@ -3638,10 +3638,10 @@
         <v>2.088</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.445765</v>
+        <v>2.457183</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5412111</v>
+        <v>1.5484061</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>22.56</v>
@@ -3656,12 +3656,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3670,51 +3670,51 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>86.2</v>
+        <v>58.56</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.008</v>
+        <v>6.022</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>16.294895</v>
+        <v>18.769232</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>11.609365</v>
+        <v>17.82144</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>11.435</v>
+        <v>8.413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>3.739</v>
+        <v>3.404</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>5.941959</v>
+        <v>16.394176</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.0533264</v>
+        <v>2.9935842</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>5.29</v>
+        <v>3.12</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>7.42504</v>
+        <v>3.28593</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>14.507</v>
+        <v>3.572</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3723,40 +3723,40 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>58.34</v>
+        <v>85.86</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.999</v>
+        <v>5.984</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>18.700321</v>
+        <v>16.23157</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>17.756008</v>
+        <v>11.564247</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>8.413</v>
+        <v>11.435</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>3.404</v>
+        <v>3.739</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.333986</v>
+        <v>5.9188666</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.982593</v>
+        <v>2.0453465</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>3.12</v>
+        <v>5.29</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>3.28593</v>
+        <v>7.42504</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>3.572</v>
+        <v>14.507</v>
       </c>
     </row>
     <row r="10">
@@ -3776,16 +3776,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.16</v>
+        <v>19.33</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.67</v>
+        <v>5.721</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>53.22222</v>
+        <v>53.694443</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>23.360363</v>
+        <v>23.56763</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>10.962</v>
@@ -3797,10 +3797,10 @@
         <v>4.312</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.087511</v>
+        <v>5.132651</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>4.395804</v>
+        <v>4.4348063</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.36</v>
@@ -3829,16 +3829,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.463</v>
+        <v>5.511</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>25.726192</v>
+        <v>25.952381</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>12.456624</v>
+        <v>12.566145</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>10.175</v>
@@ -3850,10 +3850,10 @@
         <v>2.131</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.33537</v>
+        <v>7.3998637</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2.3318906</v>
+        <v>2.352393</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>0.42</v>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.36</v>
+        <v>26.41</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.38</v>
+        <v>5.392</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>28.497297</v>
+        <v>28.556757</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>8.669</v>
@@ -3905,10 +3905,10 @@
         <v>2.638</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>1.5243163</v>
+        <v>1.5274968</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.46842116</v>
+        <v>0.46939853</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>-2.42</v>
@@ -3937,16 +3937,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.78</v>
+        <v>22.04</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5.07</v>
+        <v>5.131</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>70.258064</v>
+        <v>71.09678</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>29.104807</v>
+        <v>29.452248</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>14.786151</v>
+        <v>14.962662</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.4692545</v>
+        <v>4.522607</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>12.96</v>
+        <v>13</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.391</v>
+        <v>2.399</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>12.027395</v>
+        <v>12.064517</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>6.776</v>
@@ -4019,10 +4019,10 @@
         <v>2.38</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>2.7674568</v>
+        <v>2.7759984</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.9524057</v>
+        <v>0.95534515</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>-0.01</v>
@@ -4054,13 +4054,13 @@
         <v>5.54</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.252</v>
+        <v>2.256</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>12.032608</v>
+        <v>12.054348</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.957101</v>
+        <v>6.969671</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>10.582</v>
@@ -4072,10 +4072,10 @@
         <v>2.472</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1.734566</v>
+        <v>-1.7376999</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.43607658</v>
+        <v>0.43686444</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.46</v>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.41</v>
+        <v>14.54</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.925</v>
+        <v>1.941</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>8.28196</v>
+        <v>8.350904</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>17.184</v>
@@ -4127,10 +4127,10 @@
         <v>1.783</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.9922902</v>
+        <v>1.0005506</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.2765507</v>
+        <v>0.2788529</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-5.83</v>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.3</v>
+        <v>98.72</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.758</v>
+        <v>1.766</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>18.103132</v>
+        <v>18.18048</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>16.534903</v>
+        <v>16.60555</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>8.779</v>
@@ -4180,10 +4180,10 @@
         <v>3.071</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>3.2577717</v>
+        <v>3.2716908</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3.2253258</v>
+        <v>3.2391062</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>5.43</v>
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.47</v>
+        <v>4.51</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1.151</v>
+        <v>1.161</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4.5202017</v>
+        <v>4.560606</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>-7.528</v>
@@ -4237,10 +4237,10 @@
         <v>1.356</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>1.5215913</v>
+        <v>1.5351921</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>1.7195121</v>
+        <v>1.7348821</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>-0.44</v>
@@ -4269,16 +4269,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.26</v>
+        <v>11.29</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.919</v>
+        <v>0.921</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>18.766666</v>
+        <v>18.816666</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>12.159433</v>
+        <v>12.19183</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>6.569</v>
@@ -4290,10 +4290,10 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>3.4360697</v>
+        <v>3.4452243</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.6901145</v>
+        <v>0.6919532</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0.6</v>
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.66</v>
+        <v>26.72</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.704</v>
+        <v>0.705</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>22.033056</v>
+        <v>22.082644</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>9.449</v>
@@ -4345,10 +4345,10 @@
         <v>1.816</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.6585791</v>
+        <v>1.6623118</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>1.1084898</v>
+        <v>1.1109846</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.23</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.47</v>
+        <v>6.46</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0.175</v>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>8.636339</v>
+        <v>8.629664999999999</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>6.818</v>
@@ -4461,10 +4461,10 @@
         <v>1.666</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-10.729685</v>
+        <v>-10.721394</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.5757166</v>
+        <v>0.5752718</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>-0.58</v>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-5.5365853</v>
+        <v>-5.5368295</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>12.539</v>
@@ -4516,10 +4516,10 @@
         <v>1.911</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>32.42857</v>
+        <v>32.43</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.27163392</v>
+        <v>0.27164587</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-1.12</v>
@@ -5086,12 +5086,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -5100,57 +5100,57 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2.926</v>
+        <v>2.011</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.067</v>
+        <v>0.032</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.33583</v>
+        <v>0.6747</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.18802</v>
+        <v>0.31768</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.1309</v>
+        <v>0.0935</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.32698002</v>
+        <v>0.4046</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.35709</v>
+        <v>1.113</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.06236</v>
+        <v>0.09383000399999999</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.957</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.082</v>
+        <v>0.193</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>5.197</v>
+        <v>3.475</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.201</v>
+        <v>0.142</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>492.233</v>
+        <v>1045.932</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>0.604</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -5159,46 +5159,46 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2.011</v>
+        <v>2.926</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.032</v>
+        <v>0.067</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.6747</v>
+        <v>0.33583</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.31768</v>
+        <v>0.18802</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.0935</v>
+        <v>0.1309</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.4046</v>
+        <v>0.32698002</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>1.113</v>
+        <v>0.35709</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.09383000399999999</v>
+        <v>0.06236</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.193</v>
+        <v>0.082</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>3.475</v>
+        <v>5.197</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.142</v>
+        <v>0.201</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>1045.932</v>
+        <v>492.233</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>0.79</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="10">
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>54.78</v>
+        <v>54.93</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>58</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.276</v>
+        <v>0.272</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>1.8</v>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>107.75</v>
+        <v>107.92</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.9740000000000001</v>
+        <v>0.971</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>1.72</v>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23.3</v>
+        <v>23.43</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.544</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>102.08</v>
+        <v>102.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.389</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.24</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>36.99</v>
+        <v>37.23</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.153</v>
+        <v>0.146</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.2</v>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>83.54000000000001</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>84</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.131</v>
+        <v>0.126</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.32</v>
@@ -6590,113 +6590,113 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>86.2</v>
+        <v>58.56</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>strong_buy</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1.25</v>
+        <v>1.5625</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>135.5</v>
+        <v>72.9375</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.246</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>2.68</v>
+        <v>3.89</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.044499997</v>
+        <v>0.0762</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.06136</v>
+        <v>0.07914</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0.81711</v>
+        <v>0.88882005</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>0.52</v>
+        <v>1.79</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.0828</v>
+        <v>0.32369998</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>58.34</v>
+        <v>85.86</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>73.33333</v>
+        <v>135.5</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.257</v>
+        <v>0.578</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>3.89</v>
+        <v>2.68</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.0762</v>
+        <v>0.044499997</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.07914</v>
+        <v>0.06136</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0.88882005</v>
+        <v>0.81711</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>1.79</v>
+        <v>0.52</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.32369998</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="10">
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19.16</v>
+        <v>19.33</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -6725,16 +6725,16 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.883062</v>
+        <v>28.919893</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.238945</v>
+        <v>37.286427</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>21.964575</v>
+        <v>21.992582</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.507</v>
+        <v>0.496</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>4.19</v>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.609</v>
+        <v>0.594</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4.92</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>26.36</v>
+        <v>26.41</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>22</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.212</v>
+        <v>0.21</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>3.8</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>21.78</v>
+        <v>22.04</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.139</v>
+        <v>0.125</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.71</v>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>12.96</v>
+        <v>13</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>15</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.395</v>
+        <v>0.391</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>2.42</v>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14.41</v>
+        <v>14.54</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.326</v>
+        <v>0.314</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>4.18</v>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>98.3</v>
+        <v>98.72</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>93</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.095</v>
+        <v>0.091</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>2.53</v>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4.47</v>
+        <v>4.51</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>6</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.632</v>
+        <v>1.609</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>1.77</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11.26</v>
+        <v>11.29</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.377</v>
+        <v>0.373</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>3.68</v>
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>26.66</v>
+        <v>26.72</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>30</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.144</v>
+        <v>0.141</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>2.5</v>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6.47</v>
+        <v>6.46</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.061</v>
+        <v>1.064</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>13.9</v>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>37.042</v>
+        <v>37.14</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>23.312767</v>
+        <v>23.37447</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -7722,7 +7722,7 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.155</v>
+        <v>-0.153</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>10.77</v>
@@ -7751,7 +7751,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.38</v>
+        <v>5.392</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.119</v>
+        <v>0.121</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>8.669</v>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.252</v>
+        <v>2.256</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>12.032608</v>
+        <v>12.054348</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.263</v>
+        <v>-0.262</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>10.582</v>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>10.117</v>
+        <v>10.183</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>48.671055</v>
+        <v>48.986843</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.06</v>
@@ -7858,7 +7858,7 @@
         <v>0.1489</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="J6" s="7" t="n">
         <v>16.81</v>
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.645</v>
+        <v>10.736</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>32.509552</v>
+        <v>32.78662</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.015</v>
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.158</v>
       </c>
       <c r="J7" s="7" t="n">
         <v>11.354</v>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.307</v>
+        <v>6.336</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.7030144</v>
+        <v>3.7203016</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -7966,7 +7966,7 @@
         <v>0.87788004</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.024</v>
       </c>
       <c r="J10" s="7" t="n">
         <v>7.113</v>
@@ -7975,18 +7975,18 @@
         <v>5.9</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>71.40000000000001</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Monarch Casino &amp; Resort</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7995,42 +7995,42 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6.008</v>
+        <v>1.766</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>16.294895</v>
+        <v>18.18048</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.067</v>
+        <v>0.041</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.32698002</v>
+        <v>0.34986</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.35709</v>
+        <v>0.19214001</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>-0.23</v>
+        <v>0.031</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>11.435</v>
+        <v>8.779</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>63.5</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Monarch Casino &amp; Resort</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -8039,31 +8039,31 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1.758</v>
+        <v>5.984</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>18.103132</v>
+        <v>16.23157</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.041</v>
+        <v>0.067</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.34986</v>
+        <v>0.32698002</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.19214001</v>
+        <v>0.35709</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.027</v>
+        <v>-0.233</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>8.779</v>
+        <v>11.435</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>62.7</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="13">
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5.999</v>
+        <v>6.022</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.700321</v>
+        <v>18.769232</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8098,7 +8098,7 @@
         <v>1.113</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.055</v>
+        <v>-0.051</v>
       </c>
       <c r="J13" s="7" t="n">
         <v>8.413</v>
@@ -8107,7 +8107,7 @@
         <v>7.3</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>57.1</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="14">
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.925</v>
+        <v>1.941</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.021</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>17.184</v>
@@ -8153,7 +8153,7 @@
         <v>10.9</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>48.6</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="15">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.704</v>
+        <v>0.705</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.015</v>
+        <v>-0.012</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>9.449</v>
@@ -8333,10 +8333,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.463</v>
+        <v>5.511</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.726192</v>
+        <v>25.952381</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -8348,7 +8348,7 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.059</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>10.175</v>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.67</v>
+        <v>5.721</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>53.22222</v>
+        <v>53.694443</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -8392,7 +8392,7 @@
         <v>0.10515001</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.178</v>
+        <v>-0.171</v>
       </c>
       <c r="J21" s="7" t="n">
         <v>10.962</v>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.07</v>
+        <v>5.131</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>70.258064</v>
+        <v>71.09678</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -8436,7 +8436,7 @@
         <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.128</v>
+        <v>0.141</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>11.596</v>
+        <v>11.66</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.347</v>
+        <v>-0.343</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>46.079</v>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.87</v>
+        <v>18.9</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.151</v>
+        <v>1.161</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.585</v>
+        <v>-0.581</v>
       </c>
       <c r="J25" s="7" t="n">
         <v>-7.528</v>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.919</v>
+        <v>0.921</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.766666</v>
+        <v>18.816666</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0.075</v>
@@ -8642,7 +8642,7 @@
         <v>0.19236</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="J28" s="7" t="n">
         <v>6.569</v>
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2.391</v>
+        <v>2.399</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>0.07395</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.138</v>
+        <v>-0.135</v>
       </c>
       <c r="J29" s="7" t="n">
         <v>6.776</v>
@@ -9696,55 +9696,55 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.06136</v>
+        <v>0.07914</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.81711</v>
+        <v>0.88882005</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>2.68</v>
+        <v>3.89</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.044499997</v>
+        <v>0.0762</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>2574942</v>
+        <v>3025746</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.07914</v>
+        <v>0.06136</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.88882005</v>
+        <v>0.81711</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3.89</v>
+        <v>2.68</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.0762</v>
+        <v>0.044499997</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>3025746</v>
+        <v>2574942</v>
       </c>
     </row>
     <row r="10">
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1277.56</v>
+        <v>1277.79</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>1212.94</v>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1267.23</v>
+        <v>1267.48</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>1208.61</v>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1262.08</v>
+        <v>1262.34</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>1207.14</v>
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1254.78</v>
+        <v>1255.02</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>1198.19</v>
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1259.62</v>
+        <v>1259.86</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>1200.39</v>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1260.2</v>
+        <v>1260.45</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1208.38</v>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1245.47</v>
+        <v>1245.7</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1215.57</v>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1198.18</v>
+        <v>1198.38</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>1211.65</v>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1222.85</v>
+        <v>1223.06</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1211.53</v>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1194.17</v>
+        <v>1194.42</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1219.54</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1189.97</v>
+        <v>1190.2</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>1221.46</v>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1182.22</v>
+        <v>1182.44</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>1219.01</v>
@@ -10404,7 +10404,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1179.93</v>
+        <v>1180.15</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>1213.02</v>
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1198.74</v>
+        <v>1198.99</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>1216.33</v>
@@ -10436,7 +10436,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1162.49</v>
+        <v>1162.74</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>1215.31</v>
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1139.13</v>
+        <v>1139.36</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>1190.57</v>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1145.7</v>
+        <v>1145.92</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1204.31</v>
@@ -10484,7 +10484,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1150.79</v>
+        <v>1151.01</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>1210.6</v>
@@ -10500,7 +10500,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1135.86</v>
+        <v>1136.05</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>1211.04</v>
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1141.72</v>
+        <v>1141.91</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>1217.19</v>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1128.84</v>
+        <v>1129.05</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>1222.04</v>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1130.63</v>
+        <v>1130.83</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>1221.91</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1078.66</v>
+        <v>1078.96</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>1219.49</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1067.04</v>
+        <v>1067.31</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1215.85</v>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1085.12</v>
+        <v>1085.38</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>1221.9</v>
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1081.8</v>
+        <v>1082.04</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>1211.56</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1102.69</v>
+        <v>1102.95</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>1205.7</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1078.36</v>
+        <v>1078.59</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>1190.64</v>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1105</v>
+        <v>1105.28</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1213.48</v>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1106.85</v>
+        <v>1107.13</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1219.33</v>
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1103.83</v>
+        <v>1104.09</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>1216.12</v>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1089.4</v>
+        <v>1089.64</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>1215.83</v>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1052.73</v>
+        <v>1052.93</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>1197.05</v>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1043.52</v>
+        <v>1043.77</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>1197.89</v>
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1058.2</v>
+        <v>1058.49</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>1199.83</v>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1091.38</v>
+        <v>1091.71</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>1205.87</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1086.28</v>
+        <v>1086.62</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>1202.69</v>
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1086.39</v>
+        <v>1086.73</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>1211.39</v>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1043.33</v>
+        <v>1043.65</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>1199.02</v>
@@ -10836,7 +10836,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1057.78</v>
+        <v>1058.14</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>1207.73</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1061.67</v>
+        <v>1062.04</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>1217.93</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1090.26</v>
+        <v>1090.68</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>1211.16</v>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1077.67</v>
+        <v>1078.08</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>1205.34</v>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1072.54</v>
+        <v>1072.95</v>
       </c>
       <c r="C45" s="13" t="n">
         <v>1206.03</v>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1068.49</v>
+        <v>1068.88</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>1195.4</v>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1083.89</v>
+        <v>1084.33</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1203.83</v>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1081.53</v>
+        <v>1081.99</v>
       </c>
       <c r="C48" s="13" t="n">
         <v>1197.12</v>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1050.08</v>
+        <v>1050.54</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1181.43</v>
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1051.63</v>
+        <v>1052.09</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>1191.78</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1050.72</v>
+        <v>1051.18</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>1189.86</v>
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1065.11</v>
+        <v>1065.55</v>
       </c>
       <c r="C52" s="13" t="n">
         <v>1188.37</v>
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1050.98</v>
+        <v>1051.44</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>1170.33</v>
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1052.92</v>
+        <v>1053.36</v>
       </c>
       <c r="C54" s="13" t="n">
         <v>1163.7</v>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1045.51</v>
+        <v>1045.94</v>
       </c>
       <c r="C55" s="13" t="n">
         <v>1175.54</v>
@@ -11076,7 +11076,7 @@
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1057.77</v>
+        <v>1058.22</v>
       </c>
       <c r="C56" s="13" t="n">
         <v>1178.64</v>
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1049.88</v>
+        <v>1050.33</v>
       </c>
       <c r="C57" s="13" t="n">
         <v>1162.19</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1062.47</v>
+        <v>1062.95</v>
       </c>
       <c r="C58" s="13" t="n">
         <v>1159.33</v>
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1034.43</v>
+        <v>1034.89</v>
       </c>
       <c r="C59" s="13" t="n">
         <v>1142.71</v>
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1056.21</v>
+        <v>1056.7</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>1154.7</v>
@@ -11156,7 +11156,7 @@
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1061.72</v>
+        <v>1067.31</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11168,7 +11168,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1061.72</v>
+        <v>1067.31</v>
       </c>
     </row>
     <row r="64">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-15.71%</t>
+          <t>-15.28%</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>140.1</v>
+        <v>140.7</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.93</v>
+        <v>54.89</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.017222228</v>
+        <v>0.01648147</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,19 +670,19 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.22</v>
+        <v>-0.221</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>37.14</v>
+        <v>37.113</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>48.818</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.37447</v>
+        <v>23.357447</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.618607</v>
+        <v>14.607962</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>10.77</v>
@@ -694,10 +694,10 @@
         <v>0.888</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>-0.153</v>
+        <v>-0.154</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.92</v>
+        <v>107.67</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>-0.013347954</v>
+        <v>-0.015633563</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -729,10 +729,10 @@
         <v>99.95999999999999</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-0.6559999999999999</v>
+        <v>-0.657</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.9</v>
+        <v>18.856</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>30.856</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.992435</v>
+        <v>9.969288000000001</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14.473</v>
@@ -755,10 +755,10 @@
         <v>1.177</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>-0.506</v>
+        <v>-0.507</v>
       </c>
     </row>
     <row r="4">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.43</v>
+        <v>23.4</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>-0.021307719</v>
+        <v>-0.022352197</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -793,7 +793,7 @@
         <v>-0.52</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11.66</v>
+        <v>11.648</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>12.574</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>12.035657</v>
+        <v>12.022812</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>46.079</v>
@@ -816,10 +816,10 @@
         <v>1.682</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>-0.422</v>
+        <v>-0.423</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>-0.343</v>
+        <v>-0.344</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.95</v>
+        <v>102.89</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.017996635</v>
+        <v>0.017403364</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -854,16 +854,16 @@
         <v>-0.236</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.736</v>
+        <v>10.73</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>19.864</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.78662</v>
+        <v>32.767513</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>17.326487</v>
+        <v>17.31639</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>11.354</v>
@@ -875,10 +875,10 @@
         <v>1.034</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.224</v>
+        <v>0.223</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>-0.158</v>
+        <v>-0.159</v>
       </c>
     </row>
     <row r="6">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.93000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.024286036</v>
+        <v>0.024102983</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -972,16 +972,16 @@
         <v>-0.067</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.336</v>
+        <v>6.335</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>8.542999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.7203016</v>
+        <v>3.7196367</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.301433</v>
+        <v>10.299592</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>7.113</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.56</v>
+        <v>58.63</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.82644546</v>
+        <v>0.9450702</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1028,19 +1028,19 @@
         <v>35.09</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.151</v>
+        <v>-0.15</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.022</v>
+        <v>6.029</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>6.847</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>18.769232</v>
+        <v>18.791315</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>17.82144</v>
+        <v>17.842407</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>8.413</v>
@@ -1052,10 +1052,10 @@
         <v>1.453</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.37</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>-0.051</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="9">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.86</v>
+        <v>85.83</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.014712776</v>
+        <v>0.014358264</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>118.46</v>
@@ -1090,16 +1090,16 @@
         <v>-0.275</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.984</v>
+        <v>5.982</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>10.94</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.23157</v>
+        <v>16.225899</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>11.564247</v>
+        <v>11.560207</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>11.435</v>
@@ -1137,7 +1137,7 @@
         <v>19.33</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-0.010240694</v>
+        <v>-0.010245773</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>32.22</v>
@@ -1155,10 +1155,10 @@
         <v>5.563</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>53.694443</v>
+        <v>53.694168</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>23.56763</v>
+        <v>23.56751</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>10.962</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.9</v>
+        <v>10.89</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.020599186</v>
+        <v>0.0201311</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>14.38</v>
@@ -1205,19 +1205,19 @@
         <v>5.59</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.242</v>
+        <v>-0.243</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.511</v>
+        <v>5.509</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>4.993</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>25.952381</v>
+        <v>25.940477</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12.566145</v>
+        <v>12.560381</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>10.175</v>
@@ -1232,7 +1232,7 @@
         <v>0.5660000000000001</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>-0.059</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="12">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.41</v>
+        <v>26.33</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-0.09455226</v>
+        <v>-0.4160386</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>31.58</v>
@@ -1264,10 +1264,10 @@
         <v>17.86</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.164</v>
+        <v>-0.166</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.392</v>
+        <v>5.374</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>30.298</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="L12" s="7" t="n">
-        <v>28.556757</v>
+        <v>28.464865</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>8.669</v>
@@ -1290,10 +1290,10 @@
         <v>1.977</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>-0.061</v>
+        <v>-0.064</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.121</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>22.04</v>
+        <v>22.11</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.013333375</v>
+        <v>0.016551752</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.024</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.131</v>
+        <v>5.147</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>71.09678</v>
+        <v>71.32258</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>29.452248</v>
+        <v>29.54579</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.9440000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.141</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="14">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13</v>
+        <v>13.01</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>-0.3831432200000001</v>
+        <v>-0.3065131</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>18.57</v>
@@ -1390,10 +1390,10 @@
         <v>12.53</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-0.3</v>
+        <v>-0.299</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.399</v>
+        <v>2.401</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>5.976</v>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="L14" s="7" t="n">
-        <v>12.064517</v>
+        <v>12.073797</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>6.776</v>
@@ -1442,7 +1442,7 @@
         <v>5.54</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.013711205</v>
+        <v>0.012797107</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>10.15</v>
@@ -1454,16 +1454,16 @@
         <v>-0.454</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.256</v>
+        <v>2.254</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>12.762</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>12.054348</v>
+        <v>12.043478</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>6.969671</v>
+        <v>6.9633856</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>10.582</v>
@@ -1475,7 +1475,7 @@
         <v>0.603</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>-0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>-0.262</v>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.54</v>
+        <v>14.53</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.6578966000000002</v>
+        <v>0.58864295</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>20.61</v>
@@ -1513,7 +1513,7 @@
         <v>-0.295</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.941</v>
+        <v>1.94</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>12.411</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>8.350904</v>
+        <v>8.345159000000001</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>17.184</v>
@@ -1536,10 +1536,10 @@
         <v>1.364</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>-0.162</v>
+        <v>-0.163</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>-0.021</v>
+        <v>-0.022</v>
       </c>
     </row>
     <row r="17">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.72</v>
+        <v>26.75</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.013657007</v>
+        <v>0.014795121</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>32.74</v>
@@ -1752,10 +1752,10 @@
         <v>19.57</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.184</v>
+        <v>-0.183</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.705</v>
+        <v>0.706</v>
       </c>
       <c r="J20" s="6" t="n">
         <v>1.153</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>22.082644</v>
+        <v>22.107437</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>9.449</v>
@@ -1778,10 +1778,10 @@
         <v>1.412</v>
       </c>
       <c r="P20" s="9" t="n">
+        <v>-0.009000000000000001</v>
+      </c>
+      <c r="Q20" s="9" t="n">
         <v>-0.011</v>
-      </c>
-      <c r="Q20" s="9" t="n">
-        <v>-0.012</v>
       </c>
     </row>
     <row r="21">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>-0.5388737300000001</v>
+        <v>-0.7692337</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>9.949999999999999</v>
@@ -1882,7 +1882,7 @@
         <v>6.1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.351</v>
+        <v>-0.352</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0.175</v>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>8.629664999999999</v>
+        <v>8.609643</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>6.818</v>
@@ -1908,10 +1908,10 @@
         <v>1.206</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>-0.293</v>
+        <v>-0.295</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>-0.279</v>
+        <v>-0.281</v>
       </c>
     </row>
     <row r="23">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>-0.02150854</v>
+        <v>-0.012919884</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>4.95</v>
@@ -1943,10 +1943,10 @@
         <v>2.02</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-0.541</v>
+        <v>-0.537</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.082</v>
+        <v>0.083</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>0.578</v>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="L23" s="7" t="n">
-        <v>-5.5368295</v>
+        <v>-5.585366</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>12.539</v>
@@ -1969,10 +1969,10 @@
         <v>1.327</v>
       </c>
       <c r="P23" s="9" t="n">
-        <v>-0.492</v>
+        <v>-0.488</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>-0.092</v>
+        <v>-0.08400000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -2158,28 +2158,28 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.93</v>
+        <v>54.89</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.017222228</v>
+        <v>0.01648147</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.153</v>
+        <v>-0.154</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>53.2</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.034</v>
+        <v>-0.035</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.22</v>
+        <v>-0.221</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
@@ -2205,28 +2205,28 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.92</v>
+        <v>107.67</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.013347954</v>
+        <v>-0.015633563</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0.506</v>
+        <v>-0.507</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>-56.8</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.25</v>
+        <v>-0.252</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.531</v>
+        <v>-0.532</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.6559999999999999</v>
+        <v>-0.657</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>1.177</v>
@@ -2252,25 +2252,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.43</v>
+        <v>23.4</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.021307719</v>
+        <v>-0.022352197</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.343</v>
+        <v>-0.344</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.422</v>
+        <v>-0.423</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>-36</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.137</v>
+        <v>-0.138</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.344</v>
+        <v>-0.345</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>-0.52</v>
@@ -2299,22 +2299,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.95</v>
+        <v>102.89</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.017996635</v>
+        <v>0.017403364</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.158</v>
+        <v>-0.159</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.224</v>
+        <v>0.223</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>34.8</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.063</v>
+        <v>-0.064</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>-0.1</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.93000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.024286036</v>
+        <v>0.024102983</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>-0.024</v>
@@ -2440,28 +2440,28 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.56</v>
+        <v>58.63</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.82644546</v>
+        <v>0.9450702</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.051</v>
+        <v>-0.05</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.37</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>39.1</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.05</v>
+        <v>-0.049</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.151</v>
+        <v>-0.15</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>1.453</v>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.86</v>
+        <v>85.83</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.014712776</v>
+        <v>0.014358264</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>-0.233</v>
@@ -2502,7 +2502,7 @@
         <v>-3.2</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.095</v>
       </c>
       <c r="J9" s="5" t="n">
         <v>-0.15</v>
@@ -2537,7 +2537,7 @@
         <v>19.33</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.010240694</v>
+        <v>-0.010245773</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>-0.171</v>
@@ -2581,13 +2581,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.9</v>
+        <v>10.89</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.020599186</v>
+        <v>0.0201311</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.059</v>
+        <v>-0.06</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0.5660000000000001</v>
@@ -2596,13 +2596,13 @@
         <v>27.6</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.03</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.242</v>
+        <v>-0.243</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>1.1</v>
@@ -2628,28 +2628,28 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.41</v>
+        <v>26.33</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.09455226</v>
+        <v>-0.4160386</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.121</v>
+        <v>0.118</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.061</v>
+        <v>-0.064</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>-22.7</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.126</v>
+        <v>0.123</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.164</v>
+        <v>-0.166</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>1.977</v>
@@ -2675,28 +2675,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>22.04</v>
+        <v>22.11</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.013333375</v>
+        <v>0.016551752</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.141</v>
+        <v>0.145</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.9440000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>51.2</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.172</v>
+        <v>0.175</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.205</v>
+        <v>0.209</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.024</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13</v>
+        <v>13.01</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.3831432200000001</v>
+        <v>-0.3065131</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>-0.135</v>
@@ -2737,13 +2737,13 @@
         <v>13.4</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.057</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.159</v>
+        <v>-0.158</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-0.3</v>
+        <v>-0.299</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>1.082</v>
@@ -2772,13 +2772,13 @@
         <v>5.54</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.013711205</v>
+        <v>0.012797107</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>-0.262</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>8.6</v>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.54</v>
+        <v>14.53</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.6578966000000002</v>
+        <v>0.58864295</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.022</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.162</v>
+        <v>-0.163</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>-19.3</v>
@@ -2834,7 +2834,7 @@
         <v>0.055</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.105</v>
+        <v>-0.106</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>-0.295</v>
@@ -3004,28 +3004,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.72</v>
+        <v>26.75</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.013657007</v>
+        <v>0.014795121</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.012</v>
+        <v>-0.011</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>5.3</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.044</v>
+        <v>-0.043</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.005</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.184</v>
+        <v>-0.183</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>1.412</v>
@@ -3100,28 +3100,28 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.5388737300000001</v>
+        <v>-0.7692337</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.279</v>
+        <v>-0.281</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.293</v>
+        <v>-0.295</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.229</v>
+        <v>-0.23</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.246</v>
+        <v>-0.247</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.351</v>
+        <v>-0.352</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.206</v>
@@ -3147,28 +3147,28 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-0.02150854</v>
+        <v>-0.012919884</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-0.092</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.492</v>
+        <v>-0.488</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>-53</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.052</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-0.264</v>
+        <v>-0.257</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>-0.541</v>
+        <v>-0.537</v>
       </c>
       <c r="L23" s="8" t="n">
         <v>1.327</v>
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.93</v>
+        <v>54.89</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>37.14</v>
+        <v>37.113</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>23.37447</v>
+        <v>23.357447</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.618607</v>
+        <v>14.607962</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>10.77</v>
@@ -3369,10 +3369,10 @@
         <v>3.75</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.314941</v>
+        <v>23.297962</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.853197</v>
+        <v>2.8511193</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.92</v>
+        <v>107.67</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.9</v>
+        <v>18.856</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.992435</v>
+        <v>9.969288000000001</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>14.473</v>
@@ -3424,10 +3424,10 @@
         <v>1.883</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.0922837</v>
+        <v>2.087437</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1536504</v>
+        <v>1.1509781</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.43</v>
+        <v>23.4</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.66</v>
+        <v>11.648</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>12.035657</v>
+        <v>12.022812</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>46.079</v>
@@ -3479,10 +3479,10 @@
         <v>2.077</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>18.35815</v>
+        <v>18.338558</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.9258853</v>
+        <v>1.9238299</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3511,16 +3511,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.95</v>
+        <v>102.89</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.736</v>
+        <v>10.73</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.78662</v>
+        <v>32.767513</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>17.326487</v>
+        <v>17.31639</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>11.354</v>
@@ -3532,10 +3532,10 @@
         <v>2.783</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-38.29985</v>
+        <v>-38.27753</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.5040737</v>
+        <v>1.5031972</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3617,16 +3617,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.93000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.336</v>
+        <v>6.335</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.7203016</v>
+        <v>3.7196367</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.301433</v>
+        <v>10.299592</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>7.113</v>
@@ -3638,10 +3638,10 @@
         <v>2.088</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.457183</v>
+        <v>2.4567437</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5484061</v>
+        <v>1.5481296</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>22.56</v>
@@ -3670,16 +3670,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.56</v>
+        <v>58.63</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.022</v>
+        <v>6.029</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>18.769232</v>
+        <v>18.791315</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>17.82144</v>
+        <v>17.842407</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>8.413</v>
@@ -3691,10 +3691,10 @@
         <v>3.404</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.394176</v>
+        <v>16.413465</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.9935842</v>
+        <v>2.9971058</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>3.12</v>
@@ -3723,16 +3723,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.86</v>
+        <v>85.83</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.984</v>
+        <v>5.982</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>16.23157</v>
+        <v>16.225899</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>11.564247</v>
+        <v>11.560207</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>11.435</v>
@@ -3744,10 +3744,10 @@
         <v>3.739</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>5.9188666</v>
+        <v>5.9167986</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.0453465</v>
+        <v>2.0446317</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>5.29</v>
@@ -3782,10 +3782,10 @@
         <v>5.721</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>53.694443</v>
+        <v>53.694168</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>23.56763</v>
+        <v>23.56751</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>10.962</v>
@@ -3797,10 +3797,10 @@
         <v>4.312</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.132651</v>
+        <v>5.1326246</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>4.4348063</v>
+        <v>4.4347835</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.36</v>
@@ -3829,16 +3829,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.9</v>
+        <v>10.89</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.511</v>
+        <v>5.509</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>25.952381</v>
+        <v>25.940477</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>12.566145</v>
+        <v>12.560381</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>10.175</v>
@@ -3850,10 +3850,10 @@
         <v>2.131</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.3998637</v>
+        <v>7.39647</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2.352393</v>
+        <v>2.351314</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>0.42</v>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.41</v>
+        <v>26.33</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.392</v>
+        <v>5.374</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>28.556757</v>
+        <v>28.464865</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>8.669</v>
@@ -3905,10 +3905,10 @@
         <v>2.638</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>1.5274968</v>
+        <v>1.5225815</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.46939853</v>
+        <v>0.46788803</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>-2.42</v>
@@ -3937,16 +3937,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>22.04</v>
+        <v>22.11</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5.131</v>
+        <v>5.147</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>71.09678</v>
+        <v>71.32258</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>29.452248</v>
+        <v>29.54579</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>14.962662</v>
+        <v>15.010183</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.522607</v>
+        <v>4.5369706</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13</v>
+        <v>13.01</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.399</v>
+        <v>2.401</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>12.064517</v>
+        <v>12.073797</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>6.776</v>
@@ -4019,10 +4019,10 @@
         <v>2.38</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>2.7759984</v>
+        <v>2.7781336</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.95534515</v>
+        <v>0.95608014</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>-0.01</v>
@@ -4054,13 +4054,13 @@
         <v>5.54</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.256</v>
+        <v>2.254</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>12.054348</v>
+        <v>12.043478</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.969671</v>
+        <v>6.9633856</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>10.582</v>
@@ -4072,10 +4072,10 @@
         <v>2.472</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1.7376999</v>
+        <v>-1.7361329</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.43686444</v>
+        <v>0.4364705</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.46</v>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.54</v>
+        <v>14.53</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.941</v>
+        <v>1.94</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>8.350904</v>
+        <v>8.345159000000001</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>17.184</v>
@@ -4127,10 +4127,10 @@
         <v>1.783</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>1.0005506</v>
+        <v>0.99986225</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.2788529</v>
+        <v>0.27866104</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-5.83</v>
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.72</v>
+        <v>26.75</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.705</v>
+        <v>0.706</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>22.082644</v>
+        <v>22.107437</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>9.449</v>
@@ -4345,10 +4345,10 @@
         <v>1.816</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.6623118</v>
+        <v>1.6641783</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>1.1109846</v>
+        <v>1.1122319</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.23</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0.175</v>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>8.629664999999999</v>
+        <v>8.609643</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>6.818</v>
@@ -4461,10 +4461,10 @@
         <v>1.666</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-10.721394</v>
+        <v>-10.696517</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.5752718</v>
+        <v>0.573937</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>-0.58</v>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.082</v>
+        <v>0.083</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-5.5368295</v>
+        <v>-5.585366</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>12.539</v>
@@ -4516,10 +4516,10 @@
         <v>1.911</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>32.43</v>
+        <v>32.714287</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.27164587</v>
+        <v>0.27402714</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-1.12</v>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>54.93</v>
+        <v>54.89</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>58</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.272</v>
+        <v>0.273</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>1.8</v>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>107.92</v>
+        <v>107.67</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.971</v>
+        <v>0.976</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>1.72</v>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23.43</v>
+        <v>23.4</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.544</v>
+        <v>0.546</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>102.95</v>
+        <v>102.89</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>83.93000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>58.56</v>
+        <v>58.63</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>59</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.246</v>
+        <v>0.244</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>3.89</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>85.86</v>
+        <v>85.83</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>110</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.578</v>
+        <v>0.579</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>2.68</v>
@@ -6725,13 +6725,13 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.919893</v>
+        <v>28.926596</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.286427</v>
+        <v>37.29507</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>21.992582</v>
+        <v>21.99768</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0.496</v>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10.9</v>
+        <v>10.89</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.594</v>
+        <v>0.596</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4.92</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>26.41</v>
+        <v>26.33</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>22</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.21</v>
+        <v>0.214</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>3.8</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>22.04</v>
+        <v>22.11</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.125</v>
+        <v>0.122</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.71</v>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>13</v>
+        <v>13.01</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>15</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.391</v>
+        <v>0.39</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>2.42</v>
@@ -7011,16 +7011,16 @@
         <v>13</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>9.27308</v>
+        <v>9.24231</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.674</v>
+        <v>0.6679999999999999</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>2.08</v>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14.54</v>
+        <v>14.53</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.314</v>
+        <v>0.315</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>4.18</v>
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>26.72</v>
+        <v>26.75</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>30</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.141</v>
+        <v>0.14</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>2.5</v>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.064</v>
+        <v>1.067</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>13.9</v>
@@ -7459,7 +7459,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>2.5</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.419</v>
       </c>
       <c r="K23" s="7" t="n">
         <v>5.72</v>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>37.14</v>
+        <v>37.113</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>23.37447</v>
+        <v>23.357447</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -7722,7 +7722,7 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.153</v>
+        <v>-0.154</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>10.77</v>
@@ -7751,7 +7751,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.392</v>
+        <v>5.374</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.121</v>
+        <v>0.118</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>8.669</v>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.256</v>
+        <v>2.254</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>12.054348</v>
+        <v>12.043478</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.736</v>
+        <v>10.73</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>32.78662</v>
+        <v>32.767513</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.015</v>
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.158</v>
+        <v>-0.159</v>
       </c>
       <c r="J7" s="7" t="n">
         <v>11.354</v>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.336</v>
+        <v>6.335</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.7203016</v>
+        <v>3.7196367</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5.984</v>
+        <v>5.982</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>16.23157</v>
+        <v>16.225899</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.067</v>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6.022</v>
+        <v>6.029</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.769232</v>
+        <v>18.791315</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8098,7 +8098,7 @@
         <v>1.113</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.051</v>
+        <v>-0.05</v>
       </c>
       <c r="J13" s="7" t="n">
         <v>8.413</v>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.941</v>
+        <v>1.94</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.022</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>17.184</v>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.705</v>
+        <v>0.706</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.012</v>
+        <v>-0.011</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>9.449</v>
@@ -8269,7 +8269,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.082</v>
+        <v>0.083</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>-1.8681101</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.092</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J17" s="7" t="n">
         <v>12.539</v>
@@ -8333,10 +8333,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.511</v>
+        <v>5.509</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.952381</v>
+        <v>25.940477</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -8348,7 +8348,7 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.059</v>
+        <v>-0.06</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>10.175</v>
@@ -8380,7 +8380,7 @@
         <v>5.721</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>53.694443</v>
+        <v>53.694168</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.131</v>
+        <v>5.147</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>71.09678</v>
+        <v>71.32258</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -8436,7 +8436,7 @@
         <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.141</v>
+        <v>0.145</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>11.66</v>
+        <v>11.648</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.343</v>
+        <v>-0.344</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>46.079</v>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.9</v>
+        <v>18.856</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>-0.038829997</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-0.506</v>
+        <v>-0.507</v>
       </c>
       <c r="J24" s="7" t="n">
         <v>14.473</v>
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2.399</v>
+        <v>2.401</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.279</v>
+        <v>-0.281</v>
       </c>
       <c r="J30" s="7" t="n">
         <v>6.818</v>
@@ -10212,10 +10212,10 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1277.79</v>
+        <v>1277.97</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>1212.94</v>
+        <v>1212.93</v>
       </c>
       <c r="D2" s="13" t="n">
         <v>1068.57</v>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1267.48</v>
+        <v>1267.67</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>1208.61</v>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1262.34</v>
+        <v>1262.54</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>1207.14</v>
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1255.02</v>
+        <v>1255.21</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>1198.19</v>
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1259.86</v>
+        <v>1260.04</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>1200.39</v>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1260.45</v>
+        <v>1260.63</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1208.38</v>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1245.7</v>
+        <v>1245.88</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1215.57</v>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1198.38</v>
+        <v>1198.55</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>1211.65</v>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1223.06</v>
+        <v>1223.23</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1211.53</v>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1194.42</v>
+        <v>1194.6</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1219.54</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1190.2</v>
+        <v>1190.38</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>1221.46</v>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1182.44</v>
+        <v>1182.62</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>1219.01</v>
@@ -10404,7 +10404,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1180.15</v>
+        <v>1180.34</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>1213.02</v>
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1198.99</v>
+        <v>1199.18</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>1216.33</v>
@@ -10436,7 +10436,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1162.74</v>
+        <v>1162.94</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>1215.31</v>
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1139.36</v>
+        <v>1139.56</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>1190.57</v>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1145.92</v>
+        <v>1146.12</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1204.31</v>
@@ -10484,7 +10484,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1151.01</v>
+        <v>1151.19</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>1210.6</v>
@@ -10500,7 +10500,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1136.05</v>
+        <v>1136.24</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>1211.04</v>
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1141.91</v>
+        <v>1142.09</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>1217.19</v>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1129.05</v>
+        <v>1129.25</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>1222.04</v>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1130.83</v>
+        <v>1131.02</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>1221.91</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1078.96</v>
+        <v>1079.17</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>1219.49</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1067.31</v>
+        <v>1067.53</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1215.85</v>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1085.38</v>
+        <v>1085.61</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>1221.9</v>
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1082.04</v>
+        <v>1082.26</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>1211.56</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1102.95</v>
+        <v>1103.18</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>1205.7</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1078.59</v>
+        <v>1078.82</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>1190.64</v>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1105.28</v>
+        <v>1105.51</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1213.48</v>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1107.13</v>
+        <v>1107.37</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1219.33</v>
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1104.09</v>
+        <v>1104.32</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>1216.12</v>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1089.64</v>
+        <v>1089.88</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>1215.83</v>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1052.93</v>
+        <v>1053.15</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>1197.05</v>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1043.77</v>
+        <v>1044.01</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>1197.89</v>
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1058.49</v>
+        <v>1058.74</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>1199.83</v>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1091.71</v>
+        <v>1091.97</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>1205.87</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1086.62</v>
+        <v>1086.89</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>1202.69</v>
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1086.73</v>
+        <v>1087.01</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>1211.39</v>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1043.65</v>
+        <v>1043.92</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>1199.02</v>
@@ -10836,7 +10836,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1058.14</v>
+        <v>1058.42</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>1207.73</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1062.04</v>
+        <v>1062.32</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>1217.93</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1090.68</v>
+        <v>1090.96</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>1211.16</v>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1078.08</v>
+        <v>1078.37</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>1205.34</v>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1072.95</v>
+        <v>1073.24</v>
       </c>
       <c r="C45" s="13" t="n">
         <v>1206.03</v>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1068.88</v>
+        <v>1069.16</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>1195.4</v>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1084.33</v>
+        <v>1084.62</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1203.83</v>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1081.99</v>
+        <v>1082.28</v>
       </c>
       <c r="C48" s="13" t="n">
         <v>1197.12</v>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1050.54</v>
+        <v>1050.82</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1181.43</v>
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1052.09</v>
+        <v>1052.38</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>1191.78</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1051.18</v>
+        <v>1051.46</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>1189.86</v>
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1065.55</v>
+        <v>1065.83</v>
       </c>
       <c r="C52" s="13" t="n">
         <v>1188.37</v>
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1051.44</v>
+        <v>1051.72</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>1170.33</v>
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1053.36</v>
+        <v>1053.63</v>
       </c>
       <c r="C54" s="13" t="n">
         <v>1163.7</v>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1045.94</v>
+        <v>1046.21</v>
       </c>
       <c r="C55" s="13" t="n">
         <v>1175.54</v>
@@ -11076,7 +11076,7 @@
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1058.22</v>
+        <v>1058.5</v>
       </c>
       <c r="C56" s="13" t="n">
         <v>1178.64</v>
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1050.33</v>
+        <v>1050.6</v>
       </c>
       <c r="C57" s="13" t="n">
         <v>1162.19</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1062.95</v>
+        <v>1063.24</v>
       </c>
       <c r="C58" s="13" t="n">
         <v>1159.33</v>
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1034.89</v>
+        <v>1035.18</v>
       </c>
       <c r="C59" s="13" t="n">
         <v>1142.71</v>
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1056.7</v>
+        <v>1056.99</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>1154.7</v>
@@ -11156,7 +11156,7 @@
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1067.31</v>
+        <v>1067.69</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11168,7 +11168,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1067.31</v>
+        <v>1067.69</v>
       </c>
     </row>
     <row r="64">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-15.28%</t>
+          <t>-15.27%</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>140.7</v>
+        <v>140.6</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.67</v>
+        <v>107.54</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>-0.015633563</v>
+        <v>-0.016821902</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -732,7 +732,7 @@
         <v>-0.657</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.856</v>
+        <v>18.834</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>30.856</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.969288000000001</v>
+        <v>9.957250999999999</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14.473</v>
@@ -755,7 +755,7 @@
         <v>1.177</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>-0.507</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.4</v>
+        <v>23.43</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>-0.022352197</v>
+        <v>-0.021307719</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -793,7 +793,7 @@
         <v>-0.52</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11.648</v>
+        <v>11.66</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>12.574</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>12.022812</v>
+        <v>12.035657</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>46.079</v>
@@ -816,10 +816,10 @@
         <v>1.682</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>-0.423</v>
+        <v>-0.422</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>-0.344</v>
+        <v>-0.343</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.89</v>
+        <v>102.97</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.017403364</v>
+        <v>0.018243858</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -854,16 +854,16 @@
         <v>-0.236</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.73</v>
+        <v>10.739</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>19.864</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.767513</v>
+        <v>32.794586</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>17.31639</v>
+        <v>17.330694</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>11.354</v>
@@ -875,10 +875,10 @@
         <v>1.034</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>-0.159</v>
+        <v>-0.158</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.23</v>
+        <v>37.09</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.75777745</v>
+        <v>0.39242342</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,19 +910,19 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.073</v>
+        <v>-0.076</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10.183</v>
+        <v>10.146</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>39.58</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>48.986843</v>
+        <v>48.80921</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>15.889138</v>
+        <v>15.831523</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>16.81</v>
@@ -934,10 +934,10 @@
         <v>1.396</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.148</v>
+        <v>0.144</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.92</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.024102983</v>
+        <v>0.028313396</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -969,19 +969,19 @@
         <v>58.94</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.063</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.335</v>
+        <v>6.361</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>8.542999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.7196367</v>
+        <v>3.7349293</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.299592</v>
+        <v>10.341937</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>7.113</v>
@@ -993,10 +993,10 @@
         <v>1.22</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.224</v>
+        <v>0.229</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>-0.024</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="8">
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.63</v>
+        <v>58.53</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.9450702</v>
+        <v>0.78339875</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1028,19 +1028,19 @@
         <v>35.09</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.152</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.029</v>
+        <v>6.019</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>6.847</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>18.791315</v>
+        <v>18.761219</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>17.842407</v>
+        <v>17.813831</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>8.413</v>
@@ -1052,10 +1052,10 @@
         <v>1.453</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.3720000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>-0.05</v>
+        <v>-0.052</v>
       </c>
     </row>
     <row r="9">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.83</v>
+        <v>85.92</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.014358264</v>
+        <v>0.015303688</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>118.46</v>
@@ -1090,16 +1090,16 @@
         <v>-0.275</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.982</v>
+        <v>5.988</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>10.94</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.225899</v>
+        <v>16.24102</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>11.560207</v>
+        <v>11.570982</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>11.435</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.33</v>
+        <v>19.37</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-0.010245773</v>
+        <v>-0.8192515999999999</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>32.22</v>
@@ -1146,19 +1146,19 @@
         <v>15.725</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.4</v>
+        <v>-0.399</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.721</v>
+        <v>5.733</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>5.563</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>53.694168</v>
+        <v>53.805557</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>23.56751</v>
+        <v>23.616402</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>10.962</v>
@@ -1170,10 +1170,10 @@
         <v>2.002</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>-0.159</v>
+        <v>-0.157</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>-0.171</v>
+        <v>-0.169</v>
       </c>
     </row>
     <row r="11">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.89</v>
+        <v>10.83</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.0201311</v>
+        <v>0.014044908</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>14.38</v>
@@ -1205,19 +1205,19 @@
         <v>5.59</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.243</v>
+        <v>-0.247</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.509</v>
+        <v>5.476</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>4.993</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>25.940477</v>
+        <v>25.785715</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12.560381</v>
+        <v>12.485445</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>10.175</v>
@@ -1229,10 +1229,10 @@
         <v>1.1</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5660000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>-0.06</v>
+        <v>-0.065</v>
       </c>
     </row>
     <row r="12">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.33</v>
+        <v>26.34</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-0.4160386</v>
+        <v>-0.39713106</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>31.58</v>
@@ -1267,7 +1267,7 @@
         <v>-0.166</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.374</v>
+        <v>5.375</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>30.298</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="L12" s="7" t="n">
-        <v>28.464865</v>
+        <v>28.470268</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>8.669</v>
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>22.11</v>
+        <v>22.02</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.016551752</v>
+        <v>0.012413814</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.028</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.147</v>
+        <v>5.126</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>71.32258</v>
+        <v>71.03225999999999</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>29.54579</v>
+        <v>29.425522</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.95</v>
+        <v>0.9420000000000001</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.145</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="14">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.54</v>
+        <v>5.55</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.012797107</v>
+        <v>0.014625303</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>10.15</v>
@@ -1451,19 +1451,19 @@
         <v>4.55</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.454</v>
+        <v>-0.453</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.254</v>
+        <v>2.258</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>12.762</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>12.043478</v>
+        <v>12.065218</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>6.9633856</v>
+        <v>6.9759555</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>10.582</v>
@@ -1475,10 +1475,10 @@
         <v>0.603</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>-0.262</v>
+        <v>-0.261</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.53</v>
+        <v>14.49</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.58864295</v>
+        <v>0.3462617</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>20.61</v>
@@ -1510,10 +1510,10 @@
         <v>11.65</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.295</v>
+        <v>-0.297</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.94</v>
+        <v>1.935</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>12.411</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>8.345159000000001</v>
+        <v>8.325049999999999</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>17.184</v>
@@ -1536,10 +1536,10 @@
         <v>1.364</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>-0.163</v>
+        <v>-0.165</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>-0.022</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="17">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.72</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4681448</v>
+        <v>0.23406851</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>113.88</v>
@@ -1571,19 +1571,19 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.133</v>
+        <v>-0.135</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.766</v>
+        <v>1.762</v>
       </c>
       <c r="J17" s="6" t="n">
         <v>1.674</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>18.18048</v>
+        <v>18.138123</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>16.60555</v>
+        <v>16.566862</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>8.779</v>
@@ -1595,10 +1595,10 @@
         <v>1.376</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.232</v>
+        <v>0.229</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="18">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.51</v>
+        <v>4.54</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>-0.039361691</v>
+        <v>-0.035143015</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.73</v>
@@ -1630,10 +1630,10 @@
         <v>4.46</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.672</v>
+        <v>-0.669</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.161</v>
+        <v>1.167</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>0.908</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>4.560606</v>
+        <v>4.5808077</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>-7.528</v>
@@ -1658,10 +1658,10 @@
         <v>1.993</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>-0.591</v>
+        <v>-0.589</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>-0.581</v>
+        <v>-0.579</v>
       </c>
     </row>
     <row r="19">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.29</v>
+        <v>11.27</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.26642746</v>
+        <v>0.08881198</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>13.31</v>
@@ -1693,19 +1693,19 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.152</v>
+        <v>-0.153</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>1.242</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>18.816666</v>
+        <v>18.783333</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>12.19183</v>
+        <v>12.170233</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>6.569</v>
@@ -1717,10 +1717,10 @@
         <v>1.07</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.009000000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.75</v>
+        <v>26.71</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.014795121</v>
+        <v>0.013467357</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>32.74</v>
@@ -1752,10 +1752,10 @@
         <v>19.57</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.183</v>
+        <v>-0.184</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.706</v>
+        <v>0.705</v>
       </c>
       <c r="J20" s="6" t="n">
         <v>1.153</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>22.107437</v>
+        <v>22.078512</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>9.449</v>
@@ -1778,10 +1778,10 @@
         <v>1.412</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>-0.009000000000000001</v>
+        <v>-0.011</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.013</v>
       </c>
     </row>
     <row r="21">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.83</v>
+        <v>11.76</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>-0.023121367</v>
+        <v>-0.02931458</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>20.74</v>
@@ -1813,10 +1813,10 @@
         <v>8.455</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.43</v>
+        <v>-0.433</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.582</v>
+        <v>0.578</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>-14.6049385</v>
+        <v>-14.512345</v>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="P21" s="9" t="n">
-        <v>-0.326</v>
+        <v>-0.33</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>-0.289</v>
+        <v>-0.294</v>
       </c>
     </row>
     <row r="22">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>-0.012919884</v>
+        <v>-0.023706822</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>4.95</v>
@@ -1943,10 +1943,10 @@
         <v>2.02</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-0.537</v>
+        <v>-0.541</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>0.578</v>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="L23" s="7" t="n">
-        <v>-5.585366</v>
+        <v>-5.5243907</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>12.539</v>
@@ -1969,10 +1969,10 @@
         <v>1.327</v>
       </c>
       <c r="P23" s="9" t="n">
-        <v>-0.488</v>
+        <v>-0.493</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.094</v>
       </c>
     </row>
     <row r="24">
@@ -2205,22 +2205,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.67</v>
+        <v>107.54</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.015633563</v>
+        <v>-0.016821902</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>-0.507</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>-56.8</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.252</v>
+        <v>-0.253</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>-0.532</v>
@@ -2252,25 +2252,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.4</v>
+        <v>23.43</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.022352197</v>
+        <v>-0.021307719</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.344</v>
+        <v>-0.343</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.423</v>
+        <v>-0.422</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>-36</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.138</v>
+        <v>-0.137</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.345</v>
+        <v>-0.344</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>-0.52</v>
@@ -2299,25 +2299,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.89</v>
+        <v>102.97</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.017403364</v>
+        <v>0.018243858</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.159</v>
+        <v>-0.158</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>34.8</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.064</v>
+        <v>-0.063</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1</v>
+        <v>-0.099</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>-0.236</v>
@@ -2346,28 +2346,28 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.23</v>
+        <v>37.09</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.75777745</v>
+        <v>0.39242342</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.148</v>
+        <v>0.144</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>11.9</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.05</v>
+        <v>0.046</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.059</v>
+        <v>0.055</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.073</v>
+        <v>-0.076</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>1.396</v>
@@ -2393,28 +2393,28 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.92</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.024102983</v>
+        <v>0.028313396</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.02</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.224</v>
+        <v>0.229</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>20.5</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.063</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>1.22</v>
@@ -2440,28 +2440,28 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.63</v>
+        <v>58.53</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.9450702</v>
+        <v>0.78339875</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.05</v>
+        <v>-0.052</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.3720000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>39.1</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.049</v>
+        <v>-0.05</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.152</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>1.453</v>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.83</v>
+        <v>85.92</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.014358264</v>
+        <v>0.015303688</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>-0.233</v>
@@ -2502,10 +2502,10 @@
         <v>-3.2</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.095</v>
+        <v>-0.094</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.149</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>-0.275</v>
@@ -2534,28 +2534,28 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.33</v>
+        <v>19.37</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.010245773</v>
+        <v>-0.8192515999999999</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.171</v>
+        <v>-0.169</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.159</v>
+        <v>-0.157</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>-28.1</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.052</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-0.211</v>
+        <v>-0.21</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.4</v>
+        <v>-0.399</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>2.002</v>
@@ -2581,28 +2581,28 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.89</v>
+        <v>10.83</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.0201311</v>
+        <v>0.014044908</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.065</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.5660000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>27.6</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.03</v>
+        <v>-0.036</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.243</v>
+        <v>-0.247</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>1.1</v>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.33</v>
+        <v>26.34</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.4160386</v>
+        <v>-0.39713106</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.118</v>
@@ -2675,28 +2675,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>22.11</v>
+        <v>22.02</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.016551752</v>
+        <v>0.012413814</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.145</v>
+        <v>0.14</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.95</v>
+        <v>0.9420000000000001</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>51.2</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.175</v>
+        <v>0.171</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.209</v>
+        <v>0.204</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.028</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2769,28 +2769,28 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.54</v>
+        <v>5.55</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.012797107</v>
+        <v>0.014625303</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.262</v>
+        <v>-0.261</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>8.6</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.08</v>
+        <v>-0.078</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.294</v>
+        <v>-0.293</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.454</v>
+        <v>-0.453</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>0.603</v>
@@ -2816,28 +2816,28 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.53</v>
+        <v>14.49</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.58864295</v>
+        <v>0.3462617</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.022</v>
+        <v>-0.024</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.163</v>
+        <v>-0.165</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>-19.3</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.055</v>
+        <v>0.052</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.106</v>
+        <v>-0.108</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.295</v>
+        <v>-0.297</v>
       </c>
       <c r="L16" s="8" t="n">
         <v>1.364</v>
@@ -2863,28 +2863,28 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.72</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.4681448</v>
+        <v>0.23406851</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.232</v>
+        <v>0.229</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>20.6</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.04</v>
+        <v>0.038</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.133</v>
+        <v>-0.135</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.376</v>
@@ -2910,28 +2910,28 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.51</v>
+        <v>4.54</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.039361691</v>
+        <v>-0.035143015</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.581</v>
+        <v>-0.579</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.591</v>
+        <v>-0.589</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>-32.1</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.374</v>
+        <v>-0.37</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.5589999999999999</v>
+        <v>-0.556</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.672</v>
+        <v>-0.669</v>
       </c>
       <c r="L18" s="8" t="n">
         <v>1.993</v>
@@ -2957,28 +2957,28 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.29</v>
+        <v>11.27</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.26642746</v>
+        <v>0.08881198</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>-1.2</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0</v>
+        <v>-0.002</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.152</v>
+        <v>-0.153</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.07</v>
@@ -3004,28 +3004,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.75</v>
+        <v>26.71</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.014795121</v>
+        <v>0.013467357</v>
       </c>
       <c r="F20" s="5" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="G20" s="5" t="n">
         <v>-0.011</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-0.009000000000000001</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>5.3</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.043</v>
+        <v>-0.044</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.006</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.183</v>
+        <v>-0.184</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>1.412</v>
@@ -3051,28 +3051,28 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.83</v>
+        <v>11.76</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-0.023121367</v>
+        <v>-0.02931458</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.289</v>
+        <v>-0.294</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.326</v>
+        <v>-0.33</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>37.9</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.185</v>
+        <v>-0.19</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.11</v>
+        <v>-0.115</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.43</v>
+        <v>-0.433</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -3147,28 +3147,28 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-0.012919884</v>
+        <v>-0.023706822</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.094</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.488</v>
+        <v>-0.493</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>-53</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.06</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-0.257</v>
+        <v>-0.264</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>-0.537</v>
+        <v>-0.541</v>
       </c>
       <c r="L23" s="8" t="n">
         <v>1.327</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.67</v>
+        <v>107.54</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.856</v>
+        <v>18.834</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.969288000000001</v>
+        <v>9.957250999999999</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>14.473</v>
@@ -3424,10 +3424,10 @@
         <v>1.883</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.087437</v>
+        <v>2.0849166</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1509781</v>
+        <v>1.1495883</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.4</v>
+        <v>23.43</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.648</v>
+        <v>11.66</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>12.022812</v>
+        <v>12.035657</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>46.079</v>
@@ -3479,10 +3479,10 @@
         <v>2.077</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>18.338558</v>
+        <v>18.35815</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.9238299</v>
+        <v>1.9258853</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3511,16 +3511,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.89</v>
+        <v>102.97</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.73</v>
+        <v>10.739</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.767513</v>
+        <v>32.794586</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>17.31639</v>
+        <v>17.330694</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>11.354</v>
@@ -3532,10 +3532,10 @@
         <v>2.783</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-38.27753</v>
+        <v>-38.30915</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.5031972</v>
+        <v>1.504439</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3564,16 +3564,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.23</v>
+        <v>37.09</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.183</v>
+        <v>10.146</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>48.986843</v>
+        <v>48.80921</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>15.889138</v>
+        <v>15.831523</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>16.81</v>
@@ -3585,10 +3585,10 @@
         <v>2.257</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.9576912</v>
+        <v>3.9433403</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.58061516</v>
+        <v>0.57850975</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3617,16 +3617,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83.92</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.335</v>
+        <v>6.361</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.7196367</v>
+        <v>3.7349293</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.299592</v>
+        <v>10.341937</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>7.113</v>
@@ -3638,10 +3638,10 @@
         <v>2.088</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.4567437</v>
+        <v>2.4668443</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5481296</v>
+        <v>1.5544944</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>22.56</v>
@@ -3670,16 +3670,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.63</v>
+        <v>58.53</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.029</v>
+        <v>6.019</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>18.791315</v>
+        <v>18.761219</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>17.842407</v>
+        <v>17.813831</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>8.413</v>
@@ -3691,10 +3691,10 @@
         <v>3.404</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.413465</v>
+        <v>16.387178</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.9971058</v>
+        <v>2.9923058</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>3.12</v>
@@ -3723,16 +3723,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.83</v>
+        <v>85.92</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.982</v>
+        <v>5.988</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>16.225899</v>
+        <v>16.24102</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>11.560207</v>
+        <v>11.570982</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>11.435</v>
@@ -3744,10 +3744,10 @@
         <v>3.739</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>5.9167986</v>
+        <v>5.922313</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.0446317</v>
+        <v>2.0465376</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>5.29</v>
@@ -3776,16 +3776,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.33</v>
+        <v>19.37</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.721</v>
+        <v>5.733</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>53.694168</v>
+        <v>53.805557</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>23.56751</v>
+        <v>23.616402</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>10.962</v>
@@ -3797,10 +3797,10 @@
         <v>4.312</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.1326246</v>
+        <v>5.143272</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>4.4347835</v>
+        <v>4.4439836</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.36</v>
@@ -3829,16 +3829,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.89</v>
+        <v>10.83</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.509</v>
+        <v>5.476</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>25.940477</v>
+        <v>25.785715</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>12.560381</v>
+        <v>12.485445</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>10.175</v>
@@ -3850,10 +3850,10 @@
         <v>2.131</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.39647</v>
+        <v>7.3523417</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2.351314</v>
+        <v>2.3372858</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>0.42</v>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.33</v>
+        <v>26.34</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.374</v>
+        <v>5.375</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>28.464865</v>
+        <v>28.470268</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>8.669</v>
@@ -3905,10 +3905,10 @@
         <v>2.638</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>1.5225815</v>
+        <v>1.5228705</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.46788803</v>
+        <v>0.46797687</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>-2.42</v>
@@ -3937,16 +3937,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>22.11</v>
+        <v>22.02</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5.147</v>
+        <v>5.126</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>71.32258</v>
+        <v>71.03225999999999</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>29.54579</v>
+        <v>29.425522</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>15.010183</v>
+        <v>14.949083</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.5369706</v>
+        <v>4.5185027</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -4051,16 +4051,16 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.54</v>
+        <v>5.55</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.254</v>
+        <v>2.258</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>12.043478</v>
+        <v>12.065218</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.9633856</v>
+        <v>6.9759555</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>10.582</v>
@@ -4072,10 +4072,10 @@
         <v>2.472</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1.7361329</v>
+        <v>-1.7392668</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.4364705</v>
+        <v>0.4372584</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.46</v>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.53</v>
+        <v>14.49</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.94</v>
+        <v>1.935</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>8.345159000000001</v>
+        <v>8.325049999999999</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>17.184</v>
@@ -4127,10 +4127,10 @@
         <v>1.783</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.99986225</v>
+        <v>0.997453</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.27866104</v>
+        <v>0.27798957</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-5.83</v>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.72</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.766</v>
+        <v>1.762</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>18.18048</v>
+        <v>18.138123</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>16.60555</v>
+        <v>16.566862</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>8.779</v>
@@ -4180,10 +4180,10 @@
         <v>3.071</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>3.2716908</v>
+        <v>3.2640684</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3.2391062</v>
+        <v>3.2315598</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>5.43</v>
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.51</v>
+        <v>4.54</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1.161</v>
+        <v>1.167</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4.560606</v>
+        <v>4.5808077</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>-7.528</v>
@@ -4237,10 +4237,10 @@
         <v>1.356</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>1.5351921</v>
+        <v>1.5419924</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>1.7348821</v>
+        <v>1.7425671</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>-0.44</v>
@@ -4269,16 +4269,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.29</v>
+        <v>11.27</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>18.816666</v>
+        <v>18.783333</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>12.19183</v>
+        <v>12.170233</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>6.569</v>
@@ -4290,10 +4290,10 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>3.4452243</v>
+        <v>3.4391212</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.6919532</v>
+        <v>0.6907274</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0.6</v>
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.75</v>
+        <v>26.71</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.706</v>
+        <v>0.705</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>22.107437</v>
+        <v>22.078512</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>9.449</v>
@@ -4345,10 +4345,10 @@
         <v>1.816</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.6641783</v>
+        <v>1.6620008</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>1.1122319</v>
+        <v>1.1107767</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.23</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.83</v>
+        <v>11.76</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.582</v>
+        <v>0.578</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-14.6049385</v>
+        <v>-14.512345</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="K21" s="7" t="n">
-        <v>1.1144607</v>
+        <v>1.1073952</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.21891479</v>
+        <v>0.21752691</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>-12.65</v>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-5.585366</v>
+        <v>-5.5243907</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>12.539</v>
@@ -4516,10 +4516,10 @@
         <v>1.911</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>32.714287</v>
+        <v>32.357143</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.27402714</v>
+        <v>0.2710356</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-1.12</v>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>107.67</v>
+        <v>107.54</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.976</v>
+        <v>0.978</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>1.72</v>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23.4</v>
+        <v>23.43</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.546</v>
+        <v>0.544</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>102.89</v>
+        <v>102.97</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.3779999999999999</v>
+        <v>0.377</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.24</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37.23</v>
+        <v>37.09</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.146</v>
+        <v>0.15</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.2</v>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>83.92</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>84</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.126</v>
+        <v>0.121</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.32</v>
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>58.63</v>
+        <v>58.53</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>59</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.244</v>
+        <v>0.246</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>3.89</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>85.83</v>
+        <v>85.92</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>110</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.579</v>
+        <v>0.5770000000000001</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>2.68</v>
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19.33</v>
+        <v>19.37</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -6725,16 +6725,16 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.926596</v>
+        <v>28.919893</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.29507</v>
+        <v>37.286427</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>21.99768</v>
+        <v>21.992582</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.496</v>
+        <v>0.493</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>4.19</v>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10.89</v>
+        <v>10.83</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.596</v>
+        <v>0.604</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4.92</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>26.33</v>
+        <v>26.34</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>22</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.214</v>
+        <v>0.213</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>3.8</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>22.11</v>
+        <v>22.02</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.122</v>
+        <v>0.126</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.71</v>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5.54</v>
+        <v>5.55</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>6</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6679999999999999</v>
+        <v>0.665</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>2.08</v>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14.53</v>
+        <v>14.49</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.315</v>
+        <v>0.319</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>4.18</v>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>98.72</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>93</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.091</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>2.53</v>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4.51</v>
+        <v>4.54</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>6</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.609</v>
+        <v>1.591</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>1.77</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11.29</v>
+        <v>11.27</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>3.68</v>
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>26.75</v>
+        <v>26.71</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>30</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.14</v>
+        <v>0.142</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>2.5</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>11.83</v>
+        <v>11.76</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>11</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.324</v>
+        <v>0.332</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>9.16</v>
@@ -7459,7 +7459,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>2.5</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.419</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="K23" s="7" t="n">
         <v>5.72</v>
@@ -7751,7 +7751,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.374</v>
+        <v>5.375</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.254</v>
+        <v>2.258</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>12.043478</v>
+        <v>12.065218</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.262</v>
+        <v>-0.261</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>10.582</v>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>10.183</v>
+        <v>10.146</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>48.986843</v>
+        <v>48.80921</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.06</v>
@@ -7858,7 +7858,7 @@
         <v>0.1489</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="J6" s="7" t="n">
         <v>16.81</v>
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.73</v>
+        <v>10.739</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>32.767513</v>
+        <v>32.794586</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.015</v>
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.159</v>
+        <v>-0.158</v>
       </c>
       <c r="J7" s="7" t="n">
         <v>11.354</v>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.335</v>
+        <v>6.361</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.7196367</v>
+        <v>3.7349293</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -7966,7 +7966,7 @@
         <v>0.87788004</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.02</v>
       </c>
       <c r="J10" s="7" t="n">
         <v>7.113</v>
@@ -7975,7 +7975,7 @@
         <v>5.9</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>69</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1.766</v>
+        <v>1.762</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>18.18048</v>
+        <v>18.138123</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.041</v>
@@ -8010,7 +8010,7 @@
         <v>0.19214001</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="J11" s="7" t="n">
         <v>8.779</v>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5.982</v>
+        <v>5.988</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>16.225899</v>
+        <v>16.24102</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.067</v>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6.029</v>
+        <v>6.019</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.791315</v>
+        <v>18.761219</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8098,7 +8098,7 @@
         <v>1.113</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.05</v>
+        <v>-0.052</v>
       </c>
       <c r="J13" s="7" t="n">
         <v>8.413</v>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.94</v>
+        <v>1.935</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.022</v>
+        <v>-0.024</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>17.184</v>
@@ -8153,7 +8153,7 @@
         <v>10.9</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>51.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="15">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.706</v>
+        <v>0.705</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.013</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>9.449</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.582</v>
+        <v>0.578</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>-0.5564</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.289</v>
+        <v>-0.294</v>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>-1.8681101</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.094</v>
       </c>
       <c r="J17" s="7" t="n">
         <v>12.539</v>
@@ -8333,10 +8333,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.509</v>
+        <v>5.476</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.940477</v>
+        <v>25.785715</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -8348,7 +8348,7 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.065</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>10.175</v>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.721</v>
+        <v>5.733</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>53.694168</v>
+        <v>53.805557</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -8392,7 +8392,7 @@
         <v>0.10515001</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.171</v>
+        <v>-0.169</v>
       </c>
       <c r="J21" s="7" t="n">
         <v>10.962</v>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.147</v>
+        <v>5.126</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>71.32258</v>
+        <v>71.03225999999999</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -8436,7 +8436,7 @@
         <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.145</v>
+        <v>0.14</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>11.648</v>
+        <v>11.66</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.344</v>
+        <v>-0.343</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>46.079</v>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.856</v>
+        <v>18.834</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.161</v>
+        <v>1.167</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.581</v>
+        <v>-0.579</v>
       </c>
       <c r="J25" s="7" t="n">
         <v>-7.528</v>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.816666</v>
+        <v>18.783333</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0.075</v>
@@ -8642,7 +8642,7 @@
         <v>0.19236</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="J28" s="7" t="n">
         <v>6.569</v>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1277.97</v>
+        <v>1277.85</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>1212.93</v>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1267.67</v>
+        <v>1267.54</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>1208.61</v>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1262.54</v>
+        <v>1262.41</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>1207.14</v>
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1255.21</v>
+        <v>1255.09</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>1198.19</v>
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1260.04</v>
+        <v>1259.93</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>1200.39</v>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1260.63</v>
+        <v>1260.51</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1208.38</v>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1245.88</v>
+        <v>1245.77</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1215.57</v>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1198.55</v>
+        <v>1198.47</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>1211.65</v>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1223.23</v>
+        <v>1223.15</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1211.53</v>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1194.6</v>
+        <v>1194.5</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1219.54</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1190.38</v>
+        <v>1190.29</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>1221.46</v>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1182.62</v>
+        <v>1182.54</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>1219.01</v>
@@ -10404,7 +10404,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1180.34</v>
+        <v>1180.26</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>1213.02</v>
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1199.18</v>
+        <v>1199.1</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>1216.33</v>
@@ -10436,7 +10436,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1162.94</v>
+        <v>1162.85</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>1215.31</v>
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1139.56</v>
+        <v>1139.47</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>1190.57</v>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1146.12</v>
+        <v>1146.03</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1204.31</v>
@@ -10484,7 +10484,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1151.19</v>
+        <v>1151.11</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>1210.6</v>
@@ -10500,7 +10500,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1136.24</v>
+        <v>1136.16</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>1211.04</v>
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1142.09</v>
+        <v>1142.02</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>1217.19</v>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1129.25</v>
+        <v>1129.17</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>1222.04</v>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1131.02</v>
+        <v>1130.96</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>1221.91</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1079.17</v>
+        <v>1079.06</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>1219.49</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1067.53</v>
+        <v>1067.42</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1215.85</v>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1085.61</v>
+        <v>1085.51</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>1221.9</v>
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1082.26</v>
+        <v>1082.17</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>1211.56</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1103.18</v>
+        <v>1103.09</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>1205.7</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1078.82</v>
+        <v>1078.72</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>1190.64</v>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1105.51</v>
+        <v>1105.39</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1213.48</v>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1107.37</v>
+        <v>1107.24</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1219.33</v>
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1104.32</v>
+        <v>1104.22</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>1216.12</v>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1089.88</v>
+        <v>1089.79</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>1215.83</v>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1053.15</v>
+        <v>1053.07</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>1197.05</v>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1044.01</v>
+        <v>1043.91</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>1197.89</v>
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1058.74</v>
+        <v>1058.63</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>1199.83</v>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1091.97</v>
+        <v>1091.84</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>1205.87</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1086.89</v>
+        <v>1086.76</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>1202.69</v>
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1087.01</v>
+        <v>1086.86</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>1211.39</v>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1043.92</v>
+        <v>1043.78</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>1199.02</v>
@@ -10836,7 +10836,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1058.42</v>
+        <v>1058.26</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>1207.73</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1062.32</v>
+        <v>1062.14</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>1217.93</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1090.96</v>
+        <v>1090.76</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>1211.16</v>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1078.37</v>
+        <v>1078.18</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>1205.34</v>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1073.24</v>
+        <v>1073.05</v>
       </c>
       <c r="C45" s="13" t="n">
         <v>1206.03</v>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1069.16</v>
+        <v>1068.95</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>1195.4</v>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1084.62</v>
+        <v>1084.39</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1203.83</v>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1082.28</v>
+        <v>1082.05</v>
       </c>
       <c r="C48" s="13" t="n">
         <v>1197.12</v>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1050.82</v>
+        <v>1050.6</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1181.43</v>
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1052.38</v>
+        <v>1052.16</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>1191.78</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1051.46</v>
+        <v>1051.25</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>1189.86</v>
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1065.83</v>
+        <v>1065.61</v>
       </c>
       <c r="C52" s="13" t="n">
         <v>1188.37</v>
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1051.72</v>
+        <v>1051.5</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>1170.33</v>
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1053.63</v>
+        <v>1053.43</v>
       </c>
       <c r="C54" s="13" t="n">
         <v>1163.7</v>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1046.21</v>
+        <v>1046.01</v>
       </c>
       <c r="C55" s="13" t="n">
         <v>1175.54</v>
@@ -11076,7 +11076,7 @@
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1058.5</v>
+        <v>1058.29</v>
       </c>
       <c r="C56" s="13" t="n">
         <v>1178.64</v>
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1050.6</v>
+        <v>1050.4</v>
       </c>
       <c r="C57" s="13" t="n">
         <v>1162.19</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1063.24</v>
+        <v>1063.03</v>
       </c>
       <c r="C58" s="13" t="n">
         <v>1159.33</v>
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1035.18</v>
+        <v>1034.97</v>
       </c>
       <c r="C59" s="13" t="n">
         <v>1142.71</v>
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1056.99</v>
+        <v>1056.76</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>1154.7</v>
@@ -11156,7 +11156,7 @@
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1067.69</v>
+        <v>1066.28</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11168,7 +11168,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1067.69</v>
+        <v>1066.28</v>
       </c>
     </row>
     <row r="64">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-15.27%</t>
+          <t>-15.37%</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>140.6</v>
+        <v>140.5</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.89</v>
+        <v>54.93</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.01648147</v>
+        <v>0.017222228</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,19 +670,19 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.221</v>
+        <v>-0.22</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>37.113</v>
+        <v>37.14</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>48.818</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.357447</v>
+        <v>23.37447</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.607962</v>
+        <v>14.618607</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>10.77</v>
@@ -694,10 +694,10 @@
         <v>0.888</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>-0.154</v>
+        <v>-0.153</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.54</v>
+        <v>107.47</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>-0.016821902</v>
+        <v>-0.017451072</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -732,7 +732,7 @@
         <v>-0.657</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.834</v>
+        <v>18.822</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>30.856</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.957250999999999</v>
+        <v>9.95088</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14.473</v>
@@ -758,7 +758,7 @@
         <v>-0.5639999999999999</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>-0.507</v>
+        <v>-0.508</v>
       </c>
     </row>
     <row r="4">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.43</v>
+        <v>23.36</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>-0.021307719</v>
+        <v>-0.02402335</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -790,10 +790,10 @@
         <v>21.01</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.52</v>
+        <v>-0.521</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11.66</v>
+        <v>11.628</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>12.574</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>12.035657</v>
+        <v>12.002261</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>46.079</v>
@@ -816,10 +816,10 @@
         <v>1.682</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>-0.422</v>
+        <v>-0.423</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>-0.343</v>
+        <v>-0.345</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.97</v>
+        <v>102.96</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.018243858</v>
+        <v>0.01809554</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -854,16 +854,16 @@
         <v>-0.236</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.739</v>
+        <v>10.737</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>19.864</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.794586</v>
+        <v>32.789806</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>17.330694</v>
+        <v>17.328169</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>11.354</v>
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.09</v>
+        <v>37.15</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.39242342</v>
+        <v>0.5412741</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,19 +910,19 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.076</v>
+        <v>-0.075</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10.146</v>
+        <v>10.161</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>39.58</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>48.80921</v>
+        <v>48.88158</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>15.831523</v>
+        <v>15.854997</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>16.81</v>
@@ -934,10 +934,10 @@
         <v>1.396</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.144</v>
+        <v>0.146</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.26000000000001</v>
+        <v>84.28</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.028313396</v>
+        <v>0.028618515</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -972,16 +972,16 @@
         <v>-0.063</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.361</v>
+        <v>6.363</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>8.542999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.7349293</v>
+        <v>3.7360375</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.341937</v>
+        <v>10.345005</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>7.113</v>
@@ -993,7 +993,7 @@
         <v>1.22</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.229</v>
+        <v>0.23</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>-0.02</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.53</v>
+        <v>58.52</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.78339875</v>
+        <v>0.75757337</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1031,16 +1031,16 @@
         <v>-0.152</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.019</v>
+        <v>6.017</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>6.847</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>18.761219</v>
+        <v>18.75641</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>17.813831</v>
+        <v>17.809267</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>8.413</v>
@@ -1052,7 +1052,7 @@
         <v>1.453</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="Q8" s="9" t="n">
         <v>-0.052</v>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.92</v>
+        <v>85.83</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.015303688</v>
+        <v>0.014240063</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>118.46</v>
@@ -1090,16 +1090,16 @@
         <v>-0.275</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.988</v>
+        <v>5.982</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>10.94</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.24102</v>
+        <v>16.224007</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>11.570982</v>
+        <v>11.55886</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>11.435</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.37</v>
+        <v>19.34</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-0.8192515999999999</v>
+        <v>-0.9728650000000001</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>32.22</v>
@@ -1146,19 +1146,19 @@
         <v>15.725</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.399</v>
+        <v>-0.4</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.733</v>
+        <v>5.724</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>5.563</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>53.805557</v>
+        <v>53.72222</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>23.616402</v>
+        <v>23.579823</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>10.962</v>
@@ -1170,10 +1170,10 @@
         <v>2.002</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>-0.157</v>
+        <v>-0.159</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>-0.169</v>
+        <v>-0.171</v>
       </c>
     </row>
     <row r="11">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.83</v>
+        <v>10.85</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.014044908</v>
+        <v>0.015449435</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>14.38</v>
@@ -1205,19 +1205,19 @@
         <v>5.59</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.247</v>
+        <v>-0.245</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.476</v>
+        <v>5.484</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>4.993</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>25.785715</v>
+        <v>25.82143</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12.485445</v>
+        <v>12.502738</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>10.175</v>
@@ -1229,10 +1229,10 @@
         <v>1.1</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.556</v>
+        <v>0.5589999999999999</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>-0.065</v>
+        <v>-0.064</v>
       </c>
     </row>
     <row r="12">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.34</v>
+        <v>26.36</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-0.39713106</v>
+        <v>-0.283664</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>31.58</v>
@@ -1264,10 +1264,10 @@
         <v>17.86</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.166</v>
+        <v>-0.165</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.375</v>
+        <v>5.381</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>30.298</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="L12" s="7" t="n">
-        <v>28.470268</v>
+        <v>28.502703</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>8.669</v>
@@ -1290,10 +1290,10 @@
         <v>1.977</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>-0.064</v>
+        <v>-0.063</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.118</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>22.02</v>
+        <v>21.96</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.012413814</v>
+        <v>0.96551305</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.03</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.126</v>
+        <v>5.112</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>71.03225999999999</v>
+        <v>70.83871000000001</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>29.425522</v>
+        <v>29.34534</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.9420000000000001</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.14</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="14">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13.01</v>
+        <v>13.02</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>-0.3065131</v>
+        <v>-0.26819807</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>18.57</v>
@@ -1393,7 +1393,7 @@
         <v>-0.299</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.401</v>
+        <v>2.402</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>5.976</v>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="L14" s="7" t="n">
-        <v>12.073797</v>
+        <v>12.078438</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>6.776</v>
@@ -1416,10 +1416,10 @@
         <v>1.082</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>-0.033</v>
+        <v>-0.032</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>-0.135</v>
+        <v>-0.134</v>
       </c>
     </row>
     <row r="15">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.55</v>
+        <v>5.56</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.014625303</v>
+        <v>0.016468464</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>10.15</v>
@@ -1451,19 +1451,19 @@
         <v>4.55</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.453</v>
+        <v>-0.452</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.258</v>
+        <v>2.262</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>12.762</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>12.065218</v>
+        <v>12.086956</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>6.9759555</v>
+        <v>6.9885244</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>10.582</v>
@@ -1475,10 +1475,10 @@
         <v>0.603</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>-0.004</v>
+        <v>-0.002</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>-0.261</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.49</v>
+        <v>14.48</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.3462617</v>
+        <v>0.3116349</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>20.61</v>
@@ -1513,7 +1513,7 @@
         <v>-0.297</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.935</v>
+        <v>1.934</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>12.411</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>8.325049999999999</v>
+        <v>8.322177999999999</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>17.184</v>
@@ -1539,7 +1539,7 @@
         <v>-0.165</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>-0.024</v>
+        <v>-0.025</v>
       </c>
     </row>
     <row r="17">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.48999999999999</v>
+        <v>98.41</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.23406851</v>
+        <v>0.15265776</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>113.88</v>
@@ -1571,19 +1571,19 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.135</v>
+        <v>-0.136</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.762</v>
+        <v>1.76</v>
       </c>
       <c r="J17" s="6" t="n">
         <v>1.674</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>18.138123</v>
+        <v>18.12339</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>16.566862</v>
+        <v>16.553406</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>8.779</v>
@@ -1595,10 +1595,10 @@
         <v>1.376</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.229</v>
+        <v>0.228</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="18">
@@ -1621,7 +1621,7 @@
         <v>4.54</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>-0.035143015</v>
+        <v>-0.032978668</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.73</v>
@@ -1633,7 +1633,7 @@
         <v>-0.669</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.167</v>
+        <v>1.169</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>0.908</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>4.5808077</v>
+        <v>4.590909</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>-7.528</v>
@@ -1658,10 +1658,10 @@
         <v>1.993</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>-0.589</v>
+        <v>-0.588</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>-0.579</v>
+        <v>-0.578</v>
       </c>
     </row>
     <row r="19">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.27</v>
+        <v>11.28</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.08881198</v>
+        <v>0.17761548</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>13.31</v>
@@ -1696,16 +1696,16 @@
         <v>-0.153</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.919</v>
+        <v>0.92</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>1.242</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>18.783333</v>
+        <v>18.8</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>12.170233</v>
+        <v>12.181031</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>6.569</v>
@@ -1717,10 +1717,10 @@
         <v>1.07</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.108</v>
+        <v>0.109</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>-0.009000000000000001</v>
+        <v>-0.008</v>
       </c>
     </row>
     <row r="20">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.71</v>
+        <v>26.74</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.013467357</v>
+        <v>0.014415749</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>32.74</v>
@@ -1752,10 +1752,10 @@
         <v>19.57</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.184</v>
+        <v>-0.183</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.705</v>
+        <v>0.706</v>
       </c>
       <c r="J20" s="6" t="n">
         <v>1.153</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>22.078512</v>
+        <v>22.099173</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>9.449</v>
@@ -1778,10 +1778,10 @@
         <v>1.412</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.01</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>-0.013</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="21">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.45</v>
+        <v>6.47</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>-0.7692337</v>
+        <v>-0.46154168</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>9.949999999999999</v>
@@ -1882,7 +1882,7 @@
         <v>6.1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.352</v>
+        <v>-0.35</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0.175</v>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>8.609643</v>
+        <v>8.636339</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>6.818</v>
@@ -1908,10 +1908,10 @@
         <v>1.206</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>-0.295</v>
+        <v>-0.293</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>-0.281</v>
+        <v>-0.279</v>
       </c>
     </row>
     <row r="23">
@@ -2158,28 +2158,28 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.89</v>
+        <v>54.93</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.01648147</v>
+        <v>0.017222228</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.153</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>53.2</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.035</v>
+        <v>-0.034</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.015</v>
+        <v>-0.014</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.221</v>
+        <v>-0.22</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.54</v>
+        <v>107.47</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.016821902</v>
+        <v>-0.017451072</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0.507</v>
+        <v>-0.508</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>-0.5639999999999999</v>
@@ -2223,7 +2223,7 @@
         <v>-0.253</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.532</v>
+        <v>-0.5329999999999999</v>
       </c>
       <c r="K3" s="5" t="n">
         <v>-0.657</v>
@@ -2252,28 +2252,28 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.43</v>
+        <v>23.36</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.021307719</v>
+        <v>-0.02402335</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.343</v>
+        <v>-0.345</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.422</v>
+        <v>-0.423</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>-36</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.137</v>
+        <v>-0.14</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.344</v>
+        <v>-0.346</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.52</v>
+        <v>-0.521</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.97</v>
+        <v>102.96</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.018243858</v>
+        <v>0.01809554</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>-0.158</v>
@@ -2346,28 +2346,28 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.09</v>
+        <v>37.15</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.39242342</v>
+        <v>0.5412741</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.144</v>
+        <v>0.146</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>11.9</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.046</v>
+        <v>0.048</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.055</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.076</v>
+        <v>-0.075</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>1.396</v>
@@ -2393,16 +2393,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.26000000000001</v>
+        <v>84.28</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.028313396</v>
+        <v>0.028618515</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>-0.02</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.229</v>
+        <v>0.23</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>20.5</v>
@@ -2440,16 +2440,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.53</v>
+        <v>58.52</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.78339875</v>
+        <v>0.75757337</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>-0.052</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>39.1</v>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.92</v>
+        <v>85.83</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.015303688</v>
+        <v>0.014240063</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>-0.233</v>
@@ -2502,10 +2502,10 @@
         <v>-3.2</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.095</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.149</v>
+        <v>-0.15</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>-0.275</v>
@@ -2534,28 +2534,28 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.37</v>
+        <v>19.34</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.8192515999999999</v>
+        <v>-0.9728650000000001</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.169</v>
+        <v>-0.171</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.157</v>
+        <v>-0.159</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>-28.1</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-0.21</v>
+        <v>-0.211</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.399</v>
+        <v>-0.4</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>2.002</v>
@@ -2581,28 +2581,28 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.83</v>
+        <v>10.85</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.014044908</v>
+        <v>0.015449435</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.065</v>
+        <v>-0.064</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.556</v>
+        <v>0.5589999999999999</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>27.6</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.077</v>
+        <v>0.079</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.036</v>
+        <v>-0.034</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.247</v>
+        <v>-0.245</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>1.1</v>
@@ -2628,28 +2628,28 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.34</v>
+        <v>26.36</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.39713106</v>
+        <v>-0.283664</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.118</v>
+        <v>0.119</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.064</v>
+        <v>-0.063</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>-22.7</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.123</v>
+        <v>0.124</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.068</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.166</v>
+        <v>-0.165</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>1.977</v>
@@ -2675,28 +2675,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>22.02</v>
+        <v>21.96</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.012413814</v>
+        <v>0.96551305</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.14</v>
+        <v>0.137</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.9420000000000001</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>51.2</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.171</v>
+        <v>0.167</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.204</v>
+        <v>0.201</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.03</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2722,25 +2722,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13.01</v>
+        <v>13.02</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.3065131</v>
+        <v>-0.26819807</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.135</v>
+        <v>-0.134</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.033</v>
+        <v>-0.032</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>13.4</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.055</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.158</v>
+        <v>-0.157</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>-0.299</v>
@@ -2769,28 +2769,28 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.55</v>
+        <v>5.56</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.014625303</v>
+        <v>0.016468464</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.261</v>
+        <v>-0.26</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.002</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>8.6</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.078</v>
+        <v>-0.076</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.293</v>
+        <v>-0.292</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.453</v>
+        <v>-0.452</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>0.603</v>
@@ -2816,13 +2816,13 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.49</v>
+        <v>14.48</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.3462617</v>
+        <v>0.3116349</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.025</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>-0.165</v>
@@ -2831,10 +2831,10 @@
         <v>-19.3</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.108</v>
+        <v>-0.109</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>-0.297</v>
@@ -2863,28 +2863,28 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.48999999999999</v>
+        <v>98.41</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.23406851</v>
+        <v>0.15265776</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.229</v>
+        <v>0.228</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>20.6</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.038</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.135</v>
+        <v>-0.136</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.376</v>
@@ -2913,13 +2913,13 @@
         <v>4.54</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.035143015</v>
+        <v>-0.032978668</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.579</v>
+        <v>-0.578</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.589</v>
+        <v>-0.588</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>-32.1</v>
@@ -2957,25 +2957,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.27</v>
+        <v>11.28</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.08881198</v>
+        <v>0.17761548</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.009000000000000001</v>
+        <v>-0.008</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.108</v>
+        <v>0.109</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>-1.2</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.006</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>-0.153</v>
@@ -3004,28 +3004,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.71</v>
+        <v>26.74</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.013467357</v>
+        <v>0.014415749</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.013</v>
+        <v>-0.012</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.01</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>5.3</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.044</v>
+        <v>-0.043</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.005</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.184</v>
+        <v>-0.183</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>1.412</v>
@@ -3100,28 +3100,28 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.45</v>
+        <v>6.47</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.7692337</v>
+        <v>-0.46154168</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.281</v>
+        <v>-0.279</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.295</v>
+        <v>-0.293</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.23</v>
+        <v>-0.228</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.247</v>
+        <v>-0.244</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.352</v>
+        <v>-0.35</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.206</v>
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.89</v>
+        <v>54.93</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>37.113</v>
+        <v>37.14</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>23.357447</v>
+        <v>23.37447</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.607962</v>
+        <v>14.618607</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>10.77</v>
@@ -3369,10 +3369,10 @@
         <v>3.75</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.297962</v>
+        <v>23.314941</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.8511193</v>
+        <v>2.853197</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.54</v>
+        <v>107.47</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.834</v>
+        <v>18.822</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.957250999999999</v>
+        <v>9.95088</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>14.473</v>
@@ -3424,10 +3424,10 @@
         <v>1.883</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.0849166</v>
+        <v>2.0835826</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1495883</v>
+        <v>1.148853</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.43</v>
+        <v>23.36</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.66</v>
+        <v>11.628</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>12.035657</v>
+        <v>12.002261</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>46.079</v>
@@ -3479,10 +3479,10 @@
         <v>2.077</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>18.35815</v>
+        <v>18.30721</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.9258853</v>
+        <v>1.9205415</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3511,16 +3511,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.97</v>
+        <v>102.96</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.739</v>
+        <v>10.737</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.794586</v>
+        <v>32.789806</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>17.330694</v>
+        <v>17.328169</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>11.354</v>
@@ -3532,10 +3532,10 @@
         <v>2.783</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-38.30915</v>
+        <v>-38.30357</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.504439</v>
+        <v>1.5042199</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3564,16 +3564,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.09</v>
+        <v>37.15</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.146</v>
+        <v>10.161</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>48.80921</v>
+        <v>48.88158</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>15.831523</v>
+        <v>15.854997</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>16.81</v>
@@ -3585,10 +3585,10 @@
         <v>2.257</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.9433403</v>
+        <v>3.949187</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.57850975</v>
+        <v>0.5793675</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3617,16 +3617,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.26000000000001</v>
+        <v>84.28</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.361</v>
+        <v>6.363</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.7349293</v>
+        <v>3.7360375</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.341937</v>
+        <v>10.345005</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>7.113</v>
@@ -3638,10 +3638,10 @@
         <v>2.088</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.4668443</v>
+        <v>2.4675763</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5544944</v>
+        <v>1.5549556</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>22.56</v>
@@ -3670,16 +3670,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.53</v>
+        <v>58.52</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.019</v>
+        <v>6.017</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>18.761219</v>
+        <v>18.75641</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>17.813831</v>
+        <v>17.809267</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>8.413</v>
@@ -3691,10 +3691,10 @@
         <v>3.404</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.387178</v>
+        <v>16.382978</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.9923058</v>
+        <v>2.991539</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>3.12</v>
@@ -3723,16 +3723,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.92</v>
+        <v>85.83</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.988</v>
+        <v>5.982</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>16.24102</v>
+        <v>16.224007</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>11.570982</v>
+        <v>11.55886</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>11.435</v>
@@ -3744,10 +3744,10 @@
         <v>3.739</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>5.922313</v>
+        <v>5.916109</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.0465376</v>
+        <v>2.0443935</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>5.29</v>
@@ -3776,16 +3776,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.37</v>
+        <v>19.34</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.733</v>
+        <v>5.724</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>53.805557</v>
+        <v>53.72222</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>23.616402</v>
+        <v>23.579823</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>10.962</v>
@@ -3797,10 +3797,10 @@
         <v>4.312</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.143272</v>
+        <v>5.1353064</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>4.4439836</v>
+        <v>4.437101</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.36</v>
@@ -3829,16 +3829,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.83</v>
+        <v>10.85</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.476</v>
+        <v>5.484</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>25.785715</v>
+        <v>25.82143</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>12.485445</v>
+        <v>12.502738</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>10.175</v>
@@ -3850,10 +3850,10 @@
         <v>2.131</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.3523417</v>
+        <v>7.3625255</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2.3372858</v>
+        <v>2.3405232</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>0.42</v>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.34</v>
+        <v>26.36</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.375</v>
+        <v>5.381</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>28.470268</v>
+        <v>28.502703</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>8.669</v>
@@ -3905,10 +3905,10 @@
         <v>2.638</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>1.5228705</v>
+        <v>1.5246054</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.46797687</v>
+        <v>0.46851</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>-2.42</v>
@@ -3937,16 +3937,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>22.02</v>
+        <v>21.96</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5.126</v>
+        <v>5.112</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>71.03225999999999</v>
+        <v>70.83871000000001</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>29.425522</v>
+        <v>29.34534</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>14.949083</v>
+        <v>14.908349</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.5185027</v>
+        <v>4.5061903</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13.01</v>
+        <v>13.02</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.401</v>
+        <v>2.402</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>12.073797</v>
+        <v>12.078438</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>6.776</v>
@@ -4019,10 +4019,10 @@
         <v>2.38</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>2.7781336</v>
+        <v>2.7792013</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.95608014</v>
+        <v>0.9564476</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>-0.01</v>
@@ -4051,16 +4051,16 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.55</v>
+        <v>5.56</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.258</v>
+        <v>2.262</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>12.065218</v>
+        <v>12.086956</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.9759555</v>
+        <v>6.9885244</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>10.582</v>
@@ -4072,10 +4072,10 @@
         <v>2.472</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1.7392668</v>
+        <v>-1.7424005</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.4372584</v>
+        <v>0.43804622</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.46</v>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.49</v>
+        <v>14.48</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.935</v>
+        <v>1.934</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>8.325049999999999</v>
+        <v>8.322177999999999</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>17.184</v>
@@ -4127,10 +4127,10 @@
         <v>1.783</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.997453</v>
+        <v>0.99710876</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.27798957</v>
+        <v>0.27789366</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-5.83</v>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.48999999999999</v>
+        <v>98.41</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.762</v>
+        <v>1.76</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>18.138123</v>
+        <v>18.12339</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>16.566862</v>
+        <v>16.553406</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>8.779</v>
@@ -4180,10 +4180,10 @@
         <v>3.071</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>3.2640684</v>
+        <v>3.2614172</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3.2315598</v>
+        <v>3.228935</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>5.43</v>
@@ -4215,7 +4215,7 @@
         <v>4.54</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1.167</v>
+        <v>1.169</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4.5808077</v>
+        <v>4.590909</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>-7.528</v>
@@ -4237,10 +4237,10 @@
         <v>1.356</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>1.5419924</v>
+        <v>1.5453928</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>1.7425671</v>
+        <v>1.7464095</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>-0.44</v>
@@ -4269,16 +4269,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.27</v>
+        <v>11.28</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.919</v>
+        <v>0.92</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>18.783333</v>
+        <v>18.8</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>12.170233</v>
+        <v>12.181031</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>6.569</v>
@@ -4290,10 +4290,10 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>3.4391212</v>
+        <v>3.4421728</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.6907274</v>
+        <v>0.69134027</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0.6</v>
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.71</v>
+        <v>26.74</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.705</v>
+        <v>0.706</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>22.078512</v>
+        <v>22.099173</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>9.449</v>
@@ -4345,10 +4345,10 @@
         <v>1.816</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.6620008</v>
+        <v>1.6635561</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>1.1107767</v>
+        <v>1.1118162</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.23</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.45</v>
+        <v>6.47</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0.175</v>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>8.609643</v>
+        <v>8.636339</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>6.818</v>
@@ -4461,10 +4461,10 @@
         <v>1.666</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-10.696517</v>
+        <v>-10.729685</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.573937</v>
+        <v>0.5757166</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>-0.58</v>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>54.89</v>
+        <v>54.93</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>58</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.273</v>
+        <v>0.272</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>1.8</v>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>107.54</v>
+        <v>107.47</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.978</v>
+        <v>0.98</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>1.72</v>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23.43</v>
+        <v>23.36</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.544</v>
+        <v>0.5489999999999999</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>1.74</v>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>102.97</v>
+        <v>102.96</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.377</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.24</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37.09</v>
+        <v>37.15</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.15</v>
+        <v>0.148</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.2</v>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>84.26000000000001</v>
+        <v>84.28</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>58.53</v>
+        <v>58.52</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>85.92</v>
+        <v>85.83</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>110</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.5770000000000001</v>
+        <v>0.579</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>2.68</v>
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19.37</v>
+        <v>19.34</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -6725,16 +6725,16 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.919893</v>
+        <v>28.913189</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.286427</v>
+        <v>37.277786</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>21.992582</v>
+        <v>21.987484</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.493</v>
+        <v>0.495</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>4.19</v>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10.83</v>
+        <v>10.85</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.604</v>
+        <v>0.601</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4.92</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>26.34</v>
+        <v>26.36</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>22</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>3.8</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>22.02</v>
+        <v>21.96</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.126</v>
+        <v>0.129</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.71</v>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>13.01</v>
+        <v>13.02</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>15</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.39</v>
+        <v>0.389</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>2.42</v>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5.55</v>
+        <v>5.56</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>6</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.665</v>
+        <v>0.662</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>2.08</v>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14.49</v>
+        <v>14.48</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.319</v>
+        <v>0.32</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>4.18</v>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>98.48999999999999</v>
+        <v>98.41</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>93</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.09300000000000001</v>
+        <v>0.094</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>2.53</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11.27</v>
+        <v>11.28</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.375</v>
+        <v>0.374</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>3.68</v>
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>26.71</v>
+        <v>26.74</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>30</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>2.5</v>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6.45</v>
+        <v>6.47</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.067</v>
+        <v>1.061</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>13.9</v>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>37.113</v>
+        <v>37.14</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>23.357447</v>
+        <v>23.37447</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -7722,7 +7722,7 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.153</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>10.77</v>
@@ -7751,7 +7751,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.375</v>
+        <v>5.381</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.118</v>
+        <v>0.119</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>8.669</v>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.258</v>
+        <v>2.262</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>12.065218</v>
+        <v>12.086956</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.261</v>
+        <v>-0.26</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>10.582</v>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>10.146</v>
+        <v>10.161</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>48.80921</v>
+        <v>48.88158</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.06</v>
@@ -7858,7 +7858,7 @@
         <v>0.1489</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="J6" s="7" t="n">
         <v>16.81</v>
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.739</v>
+        <v>10.737</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>32.794586</v>
+        <v>32.789806</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.015</v>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.361</v>
+        <v>6.363</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.7349293</v>
+        <v>3.7360375</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1.762</v>
+        <v>1.76</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>18.138123</v>
+        <v>18.12339</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.041</v>
@@ -8010,7 +8010,7 @@
         <v>0.19214001</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="J11" s="7" t="n">
         <v>8.779</v>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5.988</v>
+        <v>5.982</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>16.24102</v>
+        <v>16.224007</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.067</v>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6.019</v>
+        <v>6.017</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.761219</v>
+        <v>18.75641</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.935</v>
+        <v>1.934</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.025</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>17.184</v>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.705</v>
+        <v>0.706</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.013</v>
+        <v>-0.012</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>9.449</v>
@@ -8333,10 +8333,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.476</v>
+        <v>5.484</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.785715</v>
+        <v>25.82143</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -8348,7 +8348,7 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.065</v>
+        <v>-0.064</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>10.175</v>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.733</v>
+        <v>5.724</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>53.805557</v>
+        <v>53.72222</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -8392,7 +8392,7 @@
         <v>0.10515001</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.169</v>
+        <v>-0.171</v>
       </c>
       <c r="J21" s="7" t="n">
         <v>10.962</v>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.126</v>
+        <v>5.112</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>71.03225999999999</v>
+        <v>70.83871000000001</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -8436,7 +8436,7 @@
         <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.14</v>
+        <v>0.137</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>11.66</v>
+        <v>11.628</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.343</v>
+        <v>-0.345</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>46.079</v>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.834</v>
+        <v>18.822</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>-0.038829997</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-0.507</v>
+        <v>-0.508</v>
       </c>
       <c r="J24" s="7" t="n">
         <v>14.473</v>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.167</v>
+        <v>1.169</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.579</v>
+        <v>-0.578</v>
       </c>
       <c r="J25" s="7" t="n">
         <v>-7.528</v>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.919</v>
+        <v>0.92</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.783333</v>
+        <v>18.8</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0.075</v>
@@ -8642,7 +8642,7 @@
         <v>0.19236</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-0.009000000000000001</v>
+        <v>-0.008</v>
       </c>
       <c r="J28" s="7" t="n">
         <v>6.569</v>
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2.401</v>
+        <v>2.402</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>0.07395</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.135</v>
+        <v>-0.134</v>
       </c>
       <c r="J29" s="7" t="n">
         <v>6.776</v>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.281</v>
+        <v>-0.279</v>
       </c>
       <c r="J30" s="7" t="n">
         <v>6.818</v>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1277.85</v>
+        <v>1278.02</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>1212.93</v>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1267.54</v>
+        <v>1267.7</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>1208.61</v>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1262.41</v>
+        <v>1262.56</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>1207.14</v>
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1255.09</v>
+        <v>1255.24</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>1198.19</v>
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1259.93</v>
+        <v>1260.08</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>1200.39</v>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1260.51</v>
+        <v>1260.65</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1208.38</v>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1245.77</v>
+        <v>1245.91</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1215.57</v>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1198.47</v>
+        <v>1198.6</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>1211.65</v>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1223.15</v>
+        <v>1223.27</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1211.53</v>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1194.5</v>
+        <v>1194.61</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1219.54</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1190.29</v>
+        <v>1190.42</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>1221.46</v>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1182.54</v>
+        <v>1182.67</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>1219.01</v>
@@ -10404,7 +10404,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1180.26</v>
+        <v>1180.39</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>1213.02</v>
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1199.1</v>
+        <v>1199.22</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>1216.33</v>
@@ -10436,7 +10436,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1162.85</v>
+        <v>1162.98</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>1215.31</v>
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1139.47</v>
+        <v>1139.6</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>1190.57</v>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1146.03</v>
+        <v>1146.17</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1204.31</v>
@@ -10484,7 +10484,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1151.11</v>
+        <v>1151.26</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>1210.6</v>
@@ -10500,7 +10500,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1136.16</v>
+        <v>1136.33</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>1211.04</v>
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1142.02</v>
+        <v>1142.19</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>1217.19</v>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1129.17</v>
+        <v>1129.34</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>1222.04</v>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1130.96</v>
+        <v>1131.13</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>1221.91</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1079.06</v>
+        <v>1079.18</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>1219.49</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1067.42</v>
+        <v>1067.55</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1215.85</v>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1085.51</v>
+        <v>1085.65</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>1221.9</v>
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1082.17</v>
+        <v>1082.34</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>1211.56</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1103.09</v>
+        <v>1103.26</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>1205.7</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1078.72</v>
+        <v>1078.9</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>1190.64</v>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1105.39</v>
+        <v>1105.57</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1213.48</v>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1107.24</v>
+        <v>1107.42</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1219.33</v>
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1104.22</v>
+        <v>1104.39</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>1216.12</v>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1089.79</v>
+        <v>1089.97</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>1215.83</v>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1053.07</v>
+        <v>1053.25</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>1197.05</v>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1043.91</v>
+        <v>1044.12</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>1197.89</v>
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1058.63</v>
+        <v>1058.84</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>1199.83</v>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1091.84</v>
+        <v>1092.05</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>1205.87</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1086.76</v>
+        <v>1086.96</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>1202.69</v>
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1086.86</v>
+        <v>1087.07</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>1211.39</v>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1043.78</v>
+        <v>1043.97</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>1199.02</v>
@@ -10836,7 +10836,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1058.26</v>
+        <v>1058.45</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>1207.73</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1062.14</v>
+        <v>1062.33</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>1217.93</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1090.76</v>
+        <v>1090.96</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>1211.16</v>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1078.18</v>
+        <v>1078.38</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>1205.34</v>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1073.05</v>
+        <v>1073.24</v>
       </c>
       <c r="C45" s="13" t="n">
         <v>1206.03</v>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1068.95</v>
+        <v>1069.14</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>1195.4</v>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1084.39</v>
+        <v>1084.58</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1203.83</v>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1082.05</v>
+        <v>1082.23</v>
       </c>
       <c r="C48" s="13" t="n">
         <v>1197.12</v>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1050.6</v>
+        <v>1050.76</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1181.43</v>
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1052.16</v>
+        <v>1052.33</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>1191.78</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1051.25</v>
+        <v>1051.41</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>1189.86</v>
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1065.61</v>
+        <v>1065.78</v>
       </c>
       <c r="C52" s="13" t="n">
         <v>1188.37</v>
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1051.5</v>
+        <v>1051.67</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>1170.33</v>
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1053.43</v>
+        <v>1053.6</v>
       </c>
       <c r="C54" s="13" t="n">
         <v>1163.7</v>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1046.01</v>
+        <v>1046.18</v>
       </c>
       <c r="C55" s="13" t="n">
         <v>1175.54</v>
@@ -11076,7 +11076,7 @@
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1058.29</v>
+        <v>1058.46</v>
       </c>
       <c r="C56" s="13" t="n">
         <v>1178.64</v>
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1050.4</v>
+        <v>1050.57</v>
       </c>
       <c r="C57" s="13" t="n">
         <v>1162.19</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1063.03</v>
+        <v>1063.19</v>
       </c>
       <c r="C58" s="13" t="n">
         <v>1159.33</v>
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1034.97</v>
+        <v>1035.14</v>
       </c>
       <c r="C59" s="13" t="n">
         <v>1142.71</v>
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1056.76</v>
+        <v>1056.93</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>1154.7</v>
@@ -11156,7 +11156,7 @@
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1066.28</v>
+        <v>1066.6</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11168,7 +11168,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1066.28</v>
+        <v>1066.6</v>
       </c>
     </row>
     <row r="64">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-15.37%</t>
+          <t>-15.35%</t>
         </is>
       </c>
     </row>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.93</v>
+        <v>54.9</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.017222228</v>
+        <v>0.0166667</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,34 +670,34 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.22</v>
+        <v>-0.221</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>37.14</v>
+        <v>37.12</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>48.818</v>
+        <v>49.423</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.37447</v>
+        <v>23.361704</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.618607</v>
+        <v>14.610623</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>10.77</v>
+        <v>10.903</v>
       </c>
       <c r="N2" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>0.888</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.351</v>
+        <v>0.392</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>-0.153</v>
+        <v>-0.154</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.47</v>
+        <v>107.83</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>-0.017451072</v>
+        <v>-0.0141707</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -729,13 +729,13 @@
         <v>99.95999999999999</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-0.657</v>
+        <v>-0.6559999999999999</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.822</v>
+        <v>18.865</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>30.856</v>
+        <v>30.584</v>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.95088</v>
+        <v>9.984102</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>14.473</v>
+        <v>14.345</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>1.177</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5529999999999999</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>-0.508</v>
+        <v>-0.506</v>
       </c>
     </row>
     <row r="4">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.36</v>
+        <v>23.31</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>-0.02402335</v>
+        <v>-0.0261124</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -790,13 +790,13 @@
         <v>21.01</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.521</v>
+        <v>-0.522</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11.628</v>
+        <v>11.603</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>12.574</v>
+        <v>12.254</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
@@ -804,22 +804,22 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>12.002261</v>
+        <v>11.97657</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>46.079</v>
+        <v>44.905</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>1.682</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>-0.423</v>
+        <v>-0.402</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>-0.345</v>
+        <v>-0.346</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.96</v>
+        <v>102.77</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.01809554</v>
+        <v>0.0162167</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,34 +851,34 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.236</v>
+        <v>-0.237</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.737</v>
+        <v>10.717</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>19.864</v>
+        <v>20.033</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.789806</v>
+        <v>32.729298</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>17.328169</v>
+        <v>17.296192</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>11.354</v>
+        <v>11.45</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>1.034</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.224</v>
+        <v>0.206</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>-0.158</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.15</v>
+        <v>37.11</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.5412741</v>
+        <v>0.433017</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,22 +910,22 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.076</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10.161</v>
+        <v>10.15</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>39.58</v>
+        <v>39.621</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>48.88158</v>
+        <v>48.82895</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>15.854997</v>
+        <v>15.837925</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>16.81</v>
+        <v>16.827</v>
       </c>
       <c r="N6" s="7" t="n">
         <v>11.6</v>
@@ -934,10 +934,10 @@
         <v>1.396</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.146</v>
+        <v>0.158</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.28</v>
+        <v>84.47</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.028618515</v>
+        <v>0.0308762</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -969,34 +969,34 @@
         <v>58.94</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.063</v>
+        <v>-0.061</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.363</v>
+        <v>6.377</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>8.542999999999999</v>
+        <v>8.734</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.7360375</v>
+        <v>3.7442377</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.345005</v>
+        <v>10.367712</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>7.113</v>
+        <v>7.272</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>1.22</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.23</v>
+        <v>0.248</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>-0.02</v>
+        <v>-0.018</v>
       </c>
     </row>
     <row r="8">
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.52</v>
+        <v>58.74</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.75757337</v>
+        <v>0.0113636</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1028,34 +1028,34 @@
         <v>35.09</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.152</v>
+        <v>-0.149</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.017</v>
+        <v>6.04</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>6.847</v>
+        <v>6.886</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>18.75641</v>
+        <v>18.64762</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>17.809267</v>
+        <v>17.876219</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>8.413</v>
+        <v>8.461</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>1.453</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.369</v>
+        <v>0.389</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>-0.052</v>
+        <v>-0.049</v>
       </c>
     </row>
     <row r="9">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.83</v>
+        <v>86.05</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.014240063</v>
+        <v>0.0168991</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>118.46</v>
@@ -1087,34 +1087,34 @@
         <v>80.23999999999999</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.275</v>
+        <v>-0.274</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.982</v>
+        <v>5.997</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>10.94</v>
+        <v>11.04</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.224007</v>
+        <v>16.26654</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>11.55886</v>
+        <v>11.589164</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>11.435</v>
+        <v>11.54</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>0.66</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>-0.242</v>
+        <v>-0.236</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>-0.233</v>
+        <v>-0.231</v>
       </c>
     </row>
     <row r="10">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.34</v>
+        <v>19.3</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-0.9728650000000001</v>
+        <v>-0.0117768</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>32.22</v>
@@ -1146,34 +1146,34 @@
         <v>15.725</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.4</v>
+        <v>-0.401</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.724</v>
+        <v>5.712</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>5.563</v>
+        <v>5.494</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>53.72222</v>
+        <v>53.611107</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>23.579823</v>
+        <v>23.435766</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>10.962</v>
+        <v>10.826</v>
       </c>
       <c r="N10" s="7" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>2.002</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>-0.159</v>
+        <v>-0.155</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>-0.171</v>
+        <v>-0.172</v>
       </c>
     </row>
     <row r="11">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.85</v>
+        <v>10.98</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.015449435</v>
+        <v>0.0280898</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>14.38</v>
@@ -1205,34 +1205,34 @@
         <v>5.59</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.245</v>
+        <v>-0.236</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.484</v>
+        <v>5.552</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>4.993</v>
+        <v>5.145</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>25.82143</v>
+        <v>26.142857</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12.502738</v>
+        <v>12.658373</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>10.175</v>
+        <v>10.484</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="O11" s="8" t="n">
         <v>1.1</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5589999999999999</v>
+        <v>0.5920000000000001</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>-0.064</v>
+        <v>-0.052</v>
       </c>
     </row>
     <row r="12">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.36</v>
+        <v>26.31</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-0.283664</v>
+        <v>-0.4916829999999999</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>31.58</v>
@@ -1264,13 +1264,13 @@
         <v>17.86</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.167</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.381</v>
+        <v>5.37</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>30.298</v>
+        <v>30.272</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="L12" s="7" t="n">
-        <v>28.502703</v>
+        <v>28.443243</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>8.669</v>
+        <v>8.661</v>
       </c>
       <c r="N12" s="7" t="n">
         <v>7.2</v>
@@ -1290,10 +1290,10 @@
         <v>1.977</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>-0.063</v>
+        <v>-0.045</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.96</v>
+        <v>22.16</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.96551305</v>
+        <v>0.0188506</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.03</v>
+        <v>-0.022</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.112</v>
+        <v>5.159</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>70.83871000000001</v>
+        <v>71.48387</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>29.34534</v>
+        <v>29.612604</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.975</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.137</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="14">
@@ -1381,7 +1381,7 @@
         <v>13.02</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>-0.26819807</v>
+        <v>-0.229883</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>18.57</v>
@@ -1393,10 +1393,10 @@
         <v>-0.299</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.402</v>
+        <v>2.403</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>5.976</v>
+        <v>5.971</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="L14" s="7" t="n">
-        <v>12.078438</v>
+        <v>12.083078</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>6.776</v>
+        <v>6.769</v>
       </c>
       <c r="N14" s="7" t="n">
         <v>5.8</v>
@@ -1416,7 +1416,7 @@
         <v>1.082</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>-0.032</v>
+        <v>-0.021</v>
       </c>
       <c r="Q14" s="9" t="n">
         <v>-0.134</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.56</v>
+        <v>5.52</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.016468464</v>
+        <v>0.91408</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>10.15</v>
@@ -1451,34 +1451,34 @@
         <v>4.55</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.452</v>
+        <v>-0.456</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.262</v>
+        <v>2.245</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>12.762</v>
+        <v>12.821</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>12.086956</v>
+        <v>11.74468</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>6.9885244</v>
+        <v>6.938247</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>10.582</v>
+        <v>10.631</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>0.603</v>
       </c>
-      <c r="P15" s="9" t="n">
-        <v>-0.002</v>
+      <c r="P15" s="4" t="n">
+        <v>0.013</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>-0.26</v>
+        <v>-0.265</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.48</v>
+        <v>14.47</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.3116349</v>
+        <v>0.207761</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>20.61</v>
@@ -1510,13 +1510,13 @@
         <v>11.65</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.297</v>
+        <v>-0.298</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.934</v>
+        <v>1.932</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>12.411</v>
+        <v>12.414</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>8.322177999999999</v>
+        <v>8.313560000000001</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>17.184</v>
+        <v>17.19</v>
       </c>
       <c r="N16" s="7" t="n">
         <v>10.9</v>
@@ -1539,7 +1539,7 @@
         <v>-0.165</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>-0.025</v>
+        <v>-0.026</v>
       </c>
     </row>
     <row r="17">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.41</v>
+        <v>98.88</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.15265776</v>
+        <v>0.630974</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>113.88</v>
@@ -1571,22 +1571,22 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.136</v>
+        <v>-0.132</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.76</v>
+        <v>1.769</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.674</v>
+        <v>1.685</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>18.12339</v>
+        <v>18.209946</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>16.553406</v>
+        <v>16.632463</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>8.779</v>
+        <v>8.837</v>
       </c>
       <c r="N17" s="7" t="n">
         <v>7.5</v>
@@ -1595,10 +1595,10 @@
         <v>1.376</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.228</v>
+        <v>0.236</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.028</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="18">
@@ -1621,7 +1621,7 @@
         <v>4.54</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>-0.032978668</v>
+        <v>-0.0340425</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.73</v>
@@ -1633,10 +1633,10 @@
         <v>-0.669</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.169</v>
+        <v>1.168</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.908</v>
+        <v>0.868</v>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>4.590909</v>
+        <v>4.5858583</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>-7.528</v>
+        <v>-7.201</v>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
         <v>1.993</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>-0.588</v>
+        <v>-0.59</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>-0.578</v>
+        <v>-0.579</v>
       </c>
     </row>
     <row r="19">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.28</v>
+        <v>11.29</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.17761548</v>
+        <v>0.266427</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>13.31</v>
@@ -1693,22 +1693,22 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.153</v>
+        <v>-0.152</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.242</v>
+        <v>1.245</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>18.8</v>
+        <v>18.816666</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>12.181031</v>
+        <v>12.19183</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>6.569</v>
+        <v>6.582</v>
       </c>
       <c r="N19" s="7" t="n">
         <v>4.6</v>
@@ -1717,10 +1717,10 @@
         <v>1.07</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.109</v>
+        <v>0.116</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>-0.008</v>
+        <v>-0.006999999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.74</v>
+        <v>26.62</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.014415749</v>
+        <v>0.986344</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>32.74</v>
@@ -1752,13 +1752,13 @@
         <v>19.57</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.183</v>
+        <v>-0.187</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.706</v>
+        <v>0.703</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.153</v>
+        <v>1.16</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>22.099173</v>
+        <v>22</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>9.449</v>
+        <v>9.504</v>
       </c>
       <c r="N20" s="7" t="n">
         <v>7.2</v>
@@ -1778,10 +1778,10 @@
         <v>1.412</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>-0.012</v>
+        <v>-0.016</v>
       </c>
     </row>
     <row r="21">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.76</v>
+        <v>11.6</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>-0.02931458</v>
+        <v>-0.0421139</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>20.74</v>
@@ -1813,10 +1813,10 @@
         <v>8.455</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.433</v>
+        <v>-0.441</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.578</v>
+        <v>0.57</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>-14.512345</v>
+        <v>-14.320988</v>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="P21" s="9" t="n">
-        <v>-0.33</v>
+        <v>-0.282</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>-0.294</v>
+        <v>-0.303</v>
       </c>
     </row>
     <row r="22">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.47</v>
+        <v>6.45</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>-0.46154168</v>
+        <v>-0.769234</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>9.949999999999999</v>
@@ -1882,13 +1882,13 @@
         <v>6.1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.35</v>
+        <v>-0.352</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0.175</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.507</v>
+        <v>0.505</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>8.636339</v>
+        <v>8.609643</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>6.818</v>
+        <v>6.8</v>
       </c>
       <c r="N22" s="7" t="n">
         <v>5.5</v>
@@ -1908,10 +1908,10 @@
         <v>1.206</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>-0.293</v>
+        <v>-0.285</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>-0.279</v>
+        <v>-0.281</v>
       </c>
     </row>
     <row r="23">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>-0.023706822</v>
+        <v>-0.0431034</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>4.95</v>
@@ -1943,13 +1943,13 @@
         <v>2.02</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-0.541</v>
+        <v>-0.552</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.082</v>
+        <v>0.08</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.578</v>
+        <v>0.574</v>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
@@ -1957,22 +1957,22 @@
         </is>
       </c>
       <c r="L23" s="7" t="n">
-        <v>-5.5243907</v>
+        <v>-5.414634</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>12.539</v>
+        <v>12.461</v>
       </c>
       <c r="N23" s="7" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>1.327</v>
       </c>
       <c r="P23" s="9" t="n">
-        <v>-0.493</v>
+        <v>-0.504</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>-0.094</v>
+        <v>-0.112</v>
       </c>
     </row>
     <row r="24">
@@ -2158,28 +2158,28 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.93</v>
+        <v>54.9</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.017222228</v>
+        <v>0.0166667</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.153</v>
+        <v>-0.154</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.351</v>
+        <v>0.392</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.034</v>
+        <v>-0.035</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.22</v>
+        <v>-0.221</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
@@ -2205,28 +2205,28 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.47</v>
+        <v>107.83</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.017451072</v>
+        <v>-0.0141707</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0.508</v>
+        <v>-0.506</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5529999999999999</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-56.8</v>
+        <v>-57.3</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.253</v>
+        <v>-0.251</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.5329999999999999</v>
+        <v>-0.531</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.657</v>
+        <v>-0.6559999999999999</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>1.177</v>
@@ -2252,28 +2252,28 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.36</v>
+        <v>23.31</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.02402335</v>
+        <v>-0.0261124</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.345</v>
+        <v>-0.346</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.423</v>
+        <v>-0.402</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-36</v>
+        <v>-36.2</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.14</v>
+        <v>-0.142</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.346</v>
+        <v>-0.347</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.521</v>
+        <v>-0.522</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
@@ -2299,28 +2299,28 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.96</v>
+        <v>102.77</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.01809554</v>
+        <v>0.0162167</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.158</v>
+        <v>-0.16</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.224</v>
+        <v>0.206</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.063</v>
+        <v>-0.065</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.099</v>
+        <v>-0.101</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.236</v>
+        <v>-0.237</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>1.034</v>
@@ -2346,28 +2346,28 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.15</v>
+        <v>37.11</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.5412741</v>
+        <v>0.433017</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.146</v>
+        <v>0.158</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>11.9</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.076</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>1.396</v>
@@ -2393,28 +2393,28 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.28</v>
+        <v>84.47</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.028618515</v>
+        <v>0.0308762</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0.02</v>
+        <v>-0.018</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.23</v>
+        <v>0.248</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.004</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.063</v>
+        <v>-0.061</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>1.22</v>
@@ -2440,28 +2440,28 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.52</v>
+        <v>58.74</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.75757337</v>
+        <v>0.0113636</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.049</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.369</v>
+        <v>0.389</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.05</v>
+        <v>-0.047</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.001</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.152</v>
+        <v>-0.149</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>1.453</v>
@@ -2487,28 +2487,28 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.83</v>
+        <v>86.05</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.014240063</v>
+        <v>0.0168991</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.233</v>
+        <v>-0.231</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.242</v>
+        <v>-0.236</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-3.2</v>
+        <v>-2.9</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.095</v>
+        <v>-0.092</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.148</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.275</v>
+        <v>-0.274</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>0.66</v>
@@ -2534,28 +2534,28 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.34</v>
+        <v>19.3</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.9728650000000001</v>
+        <v>-0.0117768</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.171</v>
+        <v>-0.172</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.159</v>
+        <v>-0.155</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-28.1</v>
+        <v>-28.5</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-0.211</v>
+        <v>-0.213</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.4</v>
+        <v>-0.401</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>2.002</v>
@@ -2581,28 +2581,28 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.85</v>
+        <v>10.98</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.015449435</v>
+        <v>0.0280898</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.064</v>
+        <v>-0.052</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.5589999999999999</v>
+        <v>0.5920000000000001</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>27.6</v>
+        <v>27.1</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.079</v>
+        <v>0.092</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.034</v>
+        <v>-0.022</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.245</v>
+        <v>-0.236</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>1.1</v>
@@ -2628,28 +2628,28 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.36</v>
+        <v>26.31</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.283664</v>
+        <v>-0.4916829999999999</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.063</v>
+        <v>-0.045</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>-22.7</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.124</v>
+        <v>0.122</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.167</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>1.977</v>
@@ -2675,28 +2675,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.96</v>
+        <v>22.16</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.96551305</v>
+        <v>0.0188506</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.137</v>
+        <v>0.148</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.975</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.167</v>
+        <v>0.178</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.201</v>
+        <v>0.212</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.03</v>
+        <v>-0.022</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2725,13 +2725,13 @@
         <v>13.02</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.26819807</v>
+        <v>-0.229883</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>-0.134</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.032</v>
+        <v>-0.021</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>13.4</v>
@@ -2769,28 +2769,28 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.56</v>
+        <v>5.52</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.016468464</v>
+        <v>0.91408</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.26</v>
+        <v>-0.265</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.013</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.076</v>
+        <v>-0.083</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.292</v>
+        <v>-0.297</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.452</v>
+        <v>-0.456</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>0.603</v>
@@ -2816,13 +2816,13 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.48</v>
+        <v>14.47</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.3116349</v>
+        <v>0.207761</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.025</v>
+        <v>-0.026</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>-0.165</v>
@@ -2831,13 +2831,13 @@
         <v>-19.3</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>-0.109</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.297</v>
+        <v>-0.298</v>
       </c>
       <c r="L16" s="8" t="n">
         <v>1.364</v>
@@ -2863,28 +2863,28 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.41</v>
+        <v>98.88</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.15265776</v>
+        <v>0.630974</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.028</v>
+        <v>0.033</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.228</v>
+        <v>0.236</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.042</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.024</v>
+        <v>0.029</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.136</v>
+        <v>-0.132</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.376</v>
@@ -2913,16 +2913,16 @@
         <v>4.54</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.032978668</v>
+        <v>-0.0340425</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.578</v>
+        <v>-0.579</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.588</v>
+        <v>-0.59</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-32.1</v>
+        <v>-32.3</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>-0.37</v>
@@ -2957,28 +2957,28 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.28</v>
+        <v>11.29</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.17761548</v>
+        <v>0.266427</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.109</v>
+        <v>0.116</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.153</v>
+        <v>-0.152</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.07</v>
@@ -3004,28 +3004,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.74</v>
+        <v>26.62</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.014415749</v>
+        <v>0.986344</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.012</v>
+        <v>-0.016</v>
       </c>
       <c r="G20" s="5" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="H20" s="7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>-0.043</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>-0.005</v>
-      </c>
       <c r="K20" s="5" t="n">
-        <v>-0.183</v>
+        <v>-0.187</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>1.412</v>
@@ -3051,28 +3051,28 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.76</v>
+        <v>11.6</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-0.02931458</v>
+        <v>-0.0421139</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.294</v>
+        <v>-0.303</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.33</v>
+        <v>-0.282</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>37.9</v>
+        <v>39.2</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.19</v>
+        <v>-0.201</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.115</v>
+        <v>-0.127</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.433</v>
+        <v>-0.441</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -3100,28 +3100,28 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.47</v>
+        <v>6.45</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.46154168</v>
+        <v>-0.769234</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.279</v>
+        <v>-0.281</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.293</v>
+        <v>-0.285</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.228</v>
+        <v>-0.23</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.244</v>
+        <v>-0.247</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.35</v>
+        <v>-0.352</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.206</v>
@@ -3147,28 +3147,28 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-0.023706822</v>
+        <v>-0.0431034</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.112</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.493</v>
+        <v>-0.504</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-53</v>
+        <v>-52.7</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.081</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-0.264</v>
+        <v>-0.28</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>-0.541</v>
+        <v>-0.552</v>
       </c>
       <c r="L23" s="8" t="n">
         <v>1.327</v>
@@ -3206,7 +3206,7 @@
         <v>-0.239</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>-288.9</v>
+        <v>-285.9</v>
       </c>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
@@ -3348,31 +3348,31 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.93</v>
+        <v>54.9</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>37.14</v>
+        <v>37.12</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>23.37447</v>
+        <v>23.361704</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.618607</v>
+        <v>14.610623</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>10.77</v>
+        <v>10.903</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>3.75</v>
+        <v>3.797</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.314941</v>
+        <v>23.302208</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.853197</v>
+        <v>2.8516388</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.47</v>
+        <v>107.83</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.822</v>
+        <v>18.865</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3412,22 +3412,22 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.95088</v>
+        <v>9.984102</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>14.473</v>
+        <v>14.345</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.883</v>
+        <v>1.867</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.0835826</v>
+        <v>2.090539</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.148853</v>
+        <v>1.1515056</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.36</v>
+        <v>23.31</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.628</v>
+        <v>11.603</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3467,22 +3467,22 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>12.002261</v>
+        <v>11.97657</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>46.079</v>
+        <v>44.905</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>2.077</v>
+        <v>2.024</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>18.30721</v>
+        <v>18.268024</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.9205415</v>
+        <v>1.9164306</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3511,31 +3511,31 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.96</v>
+        <v>102.77</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.737</v>
+        <v>10.717</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.789806</v>
+        <v>32.729298</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>17.328169</v>
+        <v>17.296192</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>11.354</v>
+        <v>11.45</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>2.783</v>
+        <v>2.807</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-38.30357</v>
+        <v>-38.232887</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.5042199</v>
+        <v>1.501444</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3564,31 +3564,31 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.15</v>
+        <v>37.11</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.161</v>
+        <v>10.15</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>48.88158</v>
+        <v>48.82895</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>15.854997</v>
+        <v>15.837925</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>16.81</v>
+        <v>16.827</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>11.6</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>2.257</v>
+        <v>2.259</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.949187</v>
+        <v>3.9449348</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.5793675</v>
+        <v>0.5787437</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3617,31 +3617,31 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.28</v>
+        <v>84.47</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.363</v>
+        <v>6.377</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.7360375</v>
+        <v>3.7442377</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.345005</v>
+        <v>10.367712</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>7.113</v>
+        <v>7.272</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>2.088</v>
+        <v>2.134</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.4675763</v>
+        <v>2.4729922</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5549556</v>
+        <v>1.5583686</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>22.56</v>
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.52</v>
+        <v>58.74</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.017</v>
+        <v>6.04</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>18.75641</v>
+        <v>18.64762</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>17.809267</v>
+        <v>17.876219</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>8.413</v>
+        <v>8.461</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>3.404</v>
+        <v>3.423</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.382978</v>
+        <v>16.444569</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.991539</v>
+        <v>3.0027857</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>3.28593</v>
@@ -3723,31 +3723,31 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85.83</v>
+        <v>86.05</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.982</v>
+        <v>5.997</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>16.224007</v>
+        <v>16.26654</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>11.55886</v>
+        <v>11.589164</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>11.435</v>
+        <v>11.54</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>3.739</v>
+        <v>3.773</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>5.916109</v>
+        <v>5.9316196</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.0443935</v>
+        <v>2.0497534</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>5.29</v>
@@ -3776,40 +3776,40 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.34</v>
+        <v>19.3</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.724</v>
+        <v>5.712</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>53.72222</v>
+        <v>53.611107</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>23.579823</v>
+        <v>23.435766</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>10.962</v>
+        <v>10.826</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>4.312</v>
+        <v>4.259</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.1353064</v>
+        <v>5.103933</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>4.437101</v>
+        <v>4.427923</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.36</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.82019275</v>
+        <v>0.8235276</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>3.7660851</v>
+        <v>3.7813976</v>
       </c>
     </row>
     <row r="11">
@@ -3829,31 +3829,31 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.85</v>
+        <v>10.98</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.484</v>
+        <v>5.552</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>25.82143</v>
+        <v>26.142857</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>12.502738</v>
+        <v>12.658373</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10.175</v>
+        <v>10.484</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>2.131</v>
+        <v>2.196</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.3625255</v>
+        <v>7.4541745</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2.3405232</v>
+        <v>2.3696582</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>0.42</v>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.36</v>
+        <v>26.31</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.381</v>
+        <v>5.37</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -3893,22 +3893,22 @@
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>28.502703</v>
+        <v>28.443243</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>8.669</v>
+        <v>8.661</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>7.2</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>2.638</v>
+        <v>2.636</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>1.5246054</v>
+        <v>1.5214249</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.46851</v>
+        <v>0.46753263</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>-2.42</v>
@@ -3937,16 +3937,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.96</v>
+        <v>22.16</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5.112</v>
+        <v>5.159</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>70.83871000000001</v>
+        <v>71.48387</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>29.34534</v>
+        <v>29.612604</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>14.908349</v>
+        <v>15.044127</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.5061903</v>
+        <v>4.5472307</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -3999,7 +3999,7 @@
         <v>13.02</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.402</v>
+        <v>2.403</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -4007,22 +4007,22 @@
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>12.078438</v>
+        <v>12.083078</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>6.776</v>
+        <v>6.769</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>5.8</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>2.38</v>
+        <v>2.378</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>2.7792013</v>
+        <v>2.7802691</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.9564476</v>
+        <v>0.956815</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>-0.01</v>
@@ -4051,34 +4051,34 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.56</v>
+        <v>5.52</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.262</v>
+        <v>2.245</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>12.086956</v>
+        <v>11.74468</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.9885244</v>
+        <v>6.938247</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>10.582</v>
+        <v>10.631</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>2.472</v>
+        <v>2.483</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1.7424005</v>
+        <v>-1.7298652</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.43804622</v>
+        <v>0.43489477</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>0.79559</v>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.48</v>
+        <v>14.47</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.934</v>
+        <v>1.932</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>8.322177999999999</v>
+        <v>8.313560000000001</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>17.184</v>
+        <v>17.19</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>10.9</v>
@@ -4127,13 +4127,13 @@
         <v>1.783</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.99710876</v>
+        <v>0.9960763</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.27789366</v>
+        <v>0.2776059</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-5.83</v>
+        <v>-5.84</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1.74053</v>
@@ -4159,31 +4159,31 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.41</v>
+        <v>98.88</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.76</v>
+        <v>1.769</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>18.12339</v>
+        <v>18.209946</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>16.553406</v>
+        <v>16.632463</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>8.779</v>
+        <v>8.837</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>7.5</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>3.071</v>
+        <v>3.092</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>3.2614172</v>
+        <v>3.2769933</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3.228935</v>
+        <v>3.244356</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>5.43</v>
@@ -4215,7 +4215,7 @@
         <v>4.54</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1.169</v>
+        <v>1.168</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4.590909</v>
+        <v>4.5858583</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-7.528</v>
+        <v>-7.201</v>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
@@ -4234,13 +4234,13 @@
         </is>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.356</v>
+        <v>1.297</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>1.5453928</v>
+        <v>1.5436926</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>1.7464095</v>
+        <v>1.7444884</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>-0.44</v>
@@ -4269,31 +4269,31 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.28</v>
+        <v>11.29</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>18.8</v>
+        <v>18.816666</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>12.181031</v>
+        <v>12.19183</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>6.569</v>
+        <v>6.582</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>4.6</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>3.4421728</v>
+        <v>3.4452243</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.69134027</v>
+        <v>0.6919532</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0.6</v>
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.74</v>
+        <v>26.62</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.706</v>
+        <v>0.703</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -4333,22 +4333,22 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>22.099173</v>
+        <v>22</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>9.449</v>
+        <v>9.504</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>7.2</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.816</v>
+        <v>1.827</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.6635561</v>
+        <v>1.6560907</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>1.1118162</v>
+        <v>1.1068267</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.23</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.76</v>
+        <v>11.6</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.578</v>
+        <v>0.57</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-14.512345</v>
+        <v>-14.320988</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
@@ -4406,13 +4406,13 @@
         </is>
       </c>
       <c r="K21" s="7" t="n">
-        <v>1.1073952</v>
+        <v>1.0927932</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.21752691</v>
+        <v>0.21465862</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-12.65</v>
+        <v>-12.12</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>-0.8100000000000001</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.47</v>
+        <v>6.45</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0.175</v>
@@ -4449,22 +4449,22 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>8.636339</v>
+        <v>8.609643</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>6.818</v>
+        <v>6.8</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>5.5</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.666</v>
+        <v>1.661</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-10.729685</v>
+        <v>-10.696517</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.5757166</v>
+        <v>0.573937</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>-0.58</v>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.082</v>
+        <v>0.08</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -4504,22 +4504,22 @@
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-5.5243907</v>
+        <v>-5.414634</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>12.539</v>
+        <v>12.461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.911</v>
+        <v>1.899</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>32.357143</v>
+        <v>31.714287</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.2710356</v>
+        <v>0.26565078</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-1.12</v>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>54.93</v>
+        <v>54.9</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6280,13 +6280,13 @@
         <v>58</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.272</v>
+        <v>0.273</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>1.8</v>
+        <v>2.49</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>0.034</v>
+        <v>0.0312</v>
       </c>
       <c r="M2" s="5" t="n">
         <v>0.57722</v>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>107.47</v>
+        <v>107.83</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6336,13 +6336,13 @@
         <v>125</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.98</v>
+        <v>0.973</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>0.0517</v>
+        <v>0.0583</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>0.18823999</v>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23.36</v>
+        <v>23.31</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6394,13 +6394,13 @@
         <v>24</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.5489999999999999</v>
+        <v>0.552</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>1.74</v>
+        <v>2.13</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0.06670000399999999</v>
+        <v>0.078</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>0.02999</v>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>102.96</v>
+        <v>102.77</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -6452,13 +6452,13 @@
         <v>118</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.3779999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.0696</v>
+        <v>0.083500005</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>0.27027</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37.15</v>
+        <v>37.11</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -6508,13 +6508,13 @@
         <v>31</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.148</v>
+        <v>0.15</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.1497</v>
+        <v>0.1559</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>0.27018</v>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>84.28</v>
+        <v>84.47</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>84</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.121</v>
+        <v>0.118</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.32</v>
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>58.52</v>
+        <v>58.74</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -6622,13 +6622,13 @@
         <v>59</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.246</v>
+        <v>0.242</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>3.89</v>
+        <v>4.01</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.0762</v>
+        <v>0.084300004</v>
       </c>
       <c r="M8" s="5" t="n">
         <v>0.07914</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>85.83</v>
+        <v>86.05</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>110</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.579</v>
+        <v>0.575</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>2.68</v>
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19.34</v>
+        <v>19.3</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -6725,22 +6725,22 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.913189</v>
+        <v>29.015823</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.277786</v>
+        <v>37.347034</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>21.987484</v>
+        <v>23.055845</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.495</v>
+        <v>0.503</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>4.19</v>
+        <v>4.54</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.1088</v>
+        <v>0.1046</v>
       </c>
       <c r="M10" s="5" t="n">
         <v>0.01337</v>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10.85</v>
+        <v>10.98</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -6792,13 +6792,13 @@
         <v>16</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.601</v>
+        <v>0.5820000000000001</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>4.92</v>
+        <v>4.72</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.1039</v>
+        <v>0.095</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>0.68889</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>26.36</v>
+        <v>26.31</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -6848,13 +6848,13 @@
         <v>22</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.212</v>
+        <v>0.215</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>3.8</v>
+        <v>3.37</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.1713</v>
+        <v>0.1509</v>
       </c>
       <c r="M12" s="5" t="n">
         <v>0.010570001</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>21.96</v>
+        <v>22.16</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -6906,13 +6906,13 @@
         <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.129</v>
+        <v>0.119</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0.0498</v>
+        <v>0.043899998</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>0.07084</v>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5.56</v>
+        <v>5.52</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7020,13 +7020,13 @@
         <v>6</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.662</v>
+        <v>0.674</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.0388</v>
+        <v>0.0348</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>0</v>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14.48</v>
+        <v>14.47</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7078,13 +7078,13 @@
         <v>15</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.32</v>
+        <v>0.321</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>4.18</v>
+        <v>4.3</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.16350001</v>
+        <v>0.1659</v>
       </c>
       <c r="M16" s="5" t="n">
         <v>0.01867</v>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>98.41</v>
+        <v>98.88</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7138,13 +7138,13 @@
         <v>93</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.094</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.026199998</v>
+        <v>0.024600001</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>0.3204</v>
@@ -7197,10 +7197,10 @@
         <v>1.591</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>1.77</v>
+        <v>2.41</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.0636</v>
+        <v>0.069299996</v>
       </c>
       <c r="M18" s="5" t="n">
         <v>0.09754</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11.28</v>
+        <v>11.29</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7252,13 +7252,13 @@
         <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.374</v>
+        <v>0.373</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.028099999</v>
+        <v>0.0242</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0.13798</v>
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>26.74</v>
+        <v>26.62</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7310,13 +7310,13 @@
         <v>30</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.141</v>
+        <v>0.146</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>2.5</v>
+        <v>4.41</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.0402</v>
+        <v>0.04</v>
       </c>
       <c r="M20" s="5" t="n">
         <v>0.27324</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>11.76</v>
+        <v>11.6</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -7366,13 +7366,13 @@
         <v>11</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.332</v>
+        <v>0.351</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>9.16</v>
+        <v>8.01</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.1069</v>
+        <v>0.105500005</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0.12553</v>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6.47</v>
+        <v>6.45</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -7424,13 +7424,13 @@
         <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.061</v>
+        <v>1.067</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>13.9</v>
+        <v>9.81</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.0398</v>
+        <v>0.044099998</v>
       </c>
       <c r="M22" s="5" t="n">
         <v>0.07083</v>
@@ -7459,7 +7459,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -7482,13 +7482,13 @@
         <v>2.5</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.464</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>5.72</v>
+        <v>5.74</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.024300002</v>
+        <v>0.0225</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>0.06769</v>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>37.14</v>
+        <v>37.12</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>23.37447</v>
+        <v>23.361704</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -7722,13 +7722,13 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.153</v>
+        <v>-0.154</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>10.77</v>
+        <v>10.903</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>86.09999999999999</v>
@@ -7751,7 +7751,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.381</v>
+        <v>5.37</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -7768,10 +7768,10 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>8.669</v>
+        <v>8.661</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>7.2</v>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.262</v>
+        <v>2.245</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>12.086956</v>
+        <v>11.74468</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -7814,13 +7814,13 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.26</v>
+        <v>-0.265</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>10.582</v>
+        <v>10.631</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="L5" s="7" t="n">
         <v>40</v>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>10.161</v>
+        <v>10.15</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>48.88158</v>
+        <v>48.82895</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.06</v>
@@ -7858,10 +7858,10 @@
         <v>0.1489</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>16.81</v>
+        <v>16.827</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>11.6</v>
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.737</v>
+        <v>10.717</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>32.789806</v>
+        <v>32.729298</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.015</v>
@@ -7904,13 +7904,13 @@
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.158</v>
+        <v>-0.16</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>11.354</v>
+        <v>11.45</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L7" s="7" t="n">
         <v>36.7</v>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.363</v>
+        <v>6.377</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.7360375</v>
+        <v>3.7442377</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -7966,13 +7966,13 @@
         <v>0.87788004</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-0.02</v>
+        <v>-0.018</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.113</v>
+        <v>7.272</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L10" s="7" t="n">
         <v>71.40000000000001</v>
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1.76</v>
+        <v>1.769</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>18.12339</v>
+        <v>18.209946</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.041</v>
@@ -8010,10 +8010,10 @@
         <v>0.19214001</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.028</v>
+        <v>0.033</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>8.779</v>
+        <v>8.837</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>7.5</v>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5.982</v>
+        <v>5.997</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>16.224007</v>
+        <v>16.26654</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.067</v>
@@ -8054,13 +8054,13 @@
         <v>0.35709</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>-0.233</v>
+        <v>-0.231</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>11.435</v>
+        <v>11.54</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L12" s="7" t="n">
         <v>61.1</v>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6.017</v>
+        <v>6.04</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.75641</v>
+        <v>18.64762</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8098,13 +8098,13 @@
         <v>1.113</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.049</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>8.413</v>
+        <v>8.461</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="L13" s="7" t="n">
         <v>59.5</v>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.934</v>
+        <v>1.932</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8144,10 +8144,10 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.025</v>
+        <v>-0.026</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>17.184</v>
+        <v>17.19</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>10.9</v>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.706</v>
+        <v>0.703</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -8190,10 +8190,10 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.012</v>
+        <v>-0.016</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>9.449</v>
+        <v>9.504</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>7.2</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.578</v>
+        <v>0.57</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>-0.5564</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.294</v>
+        <v>-0.303</v>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.082</v>
+        <v>0.08</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -8286,13 +8286,13 @@
         <v>-1.8681101</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.112</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>12.539</v>
+        <v>12.461</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="L17" s="7" t="n">
         <v>20</v>
@@ -8333,10 +8333,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.484</v>
+        <v>5.552</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.82143</v>
+        <v>26.142857</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -8348,13 +8348,13 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.064</v>
+        <v>-0.052</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>10.175</v>
+        <v>10.484</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="L20" s="7" t="n">
         <v>66.7</v>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.724</v>
+        <v>5.712</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>53.72222</v>
+        <v>53.611107</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -8392,13 +8392,13 @@
         <v>0.10515001</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.171</v>
+        <v>-0.172</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>10.962</v>
+        <v>10.826</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>58.3</v>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.112</v>
+        <v>5.159</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>70.83871000000001</v>
+        <v>71.48387</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -8436,7 +8436,7 @@
         <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.137</v>
+        <v>0.148</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>11.628</v>
+        <v>11.603</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -8486,13 +8486,13 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.345</v>
+        <v>-0.346</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>46.079</v>
+        <v>44.905</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="L23" s="7" t="n">
         <v>52</v>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.822</v>
+        <v>18.865</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8532,13 +8532,13 @@
         <v>-0.038829997</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-0.508</v>
+        <v>-0.506</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>14.473</v>
+        <v>14.345</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L24" s="7" t="n">
         <v>48</v>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.169</v>
+        <v>1.168</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -8578,10 +8578,10 @@
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.578</v>
+        <v>-0.579</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>-7.528</v>
+        <v>-7.201</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.8</v>
+        <v>18.816666</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0.075</v>
@@ -8642,10 +8642,10 @@
         <v>0.19236</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>6.569</v>
+        <v>6.582</v>
       </c>
       <c r="K28" s="7" t="n">
         <v>4.6</v>
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2.402</v>
+        <v>2.403</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>-0.134</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>6.776</v>
+        <v>6.769</v>
       </c>
       <c r="K29" s="7" t="n">
         <v>5.8</v>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.279</v>
+        <v>-0.281</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>6.818</v>
+        <v>6.8</v>
       </c>
       <c r="K30" s="7" t="n">
         <v>5.5</v>
@@ -9549,13 +9549,13 @@
         <v>0.41691002</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>1.8</v>
+        <v>2.49</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.034</v>
+        <v>0.0312</v>
       </c>
       <c r="G2" s="10" t="n">
-        <v>11107798</v>
+        <v>10219140</v>
       </c>
     </row>
     <row r="3">
@@ -9576,13 +9576,13 @@
         <v>0.91170996</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.0517</v>
+        <v>0.0583</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>9052256</v>
+        <v>10212758</v>
       </c>
     </row>
     <row r="4">
@@ -9603,13 +9603,13 @@
         <v>0.88253</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>1.74</v>
+        <v>2.13</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.06670000399999999</v>
+        <v>0.078</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>32087867</v>
+        <v>37514956</v>
       </c>
     </row>
     <row r="5">
@@ -9630,13 +9630,13 @@
         <v>0.68557</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0696</v>
+        <v>0.083500005</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>5694412</v>
+        <v>6833602</v>
       </c>
     </row>
     <row r="6">
@@ -9657,13 +9657,13 @@
         <v>0.73356</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.1497</v>
+        <v>0.1559</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>22752018</v>
+        <v>23688418</v>
       </c>
     </row>
     <row r="7">
@@ -9711,13 +9711,13 @@
         <v>0.88882005</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>3.89</v>
+        <v>4.01</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.0762</v>
+        <v>0.084300004</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>3025746</v>
+        <v>3346495</v>
       </c>
     </row>
     <row r="9">
@@ -9765,13 +9765,13 @@
         <v>0.91643</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>4.19</v>
+        <v>4.54</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.1088</v>
+        <v>0.1046</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>11183802</v>
+        <v>10753999</v>
       </c>
     </row>
     <row r="11">
@@ -9792,13 +9792,13 @@
         <v>0.19124001</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>4.92</v>
+        <v>4.72</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.1039</v>
+        <v>0.095</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>16337061</v>
+        <v>14945381</v>
       </c>
     </row>
     <row r="12">
@@ -9819,13 +9819,13 @@
         <v>1.11968</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3.8</v>
+        <v>3.37</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1713</v>
+        <v>0.1509</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>30537844</v>
+        <v>26892014</v>
       </c>
     </row>
     <row r="13">
@@ -9846,13 +9846,13 @@
         <v>0.93144995</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.0498</v>
+        <v>0.043899998</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>4779469</v>
+        <v>4216183</v>
       </c>
     </row>
     <row r="14">
@@ -9900,13 +9900,13 @@
         <v>0.32467</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.0388</v>
+        <v>0.0348</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>5850965</v>
+        <v>5741767</v>
       </c>
     </row>
     <row r="16">
@@ -9927,13 +9927,13 @@
         <v>0.98657995</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4.18</v>
+        <v>4.3</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.16350001</v>
+        <v>0.1659</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>21492483</v>
+        <v>21810886</v>
       </c>
     </row>
     <row r="17">
@@ -9954,13 +9954,13 @@
         <v>0.64763</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.026199998</v>
+        <v>0.024600001</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>307491</v>
+        <v>289167</v>
       </c>
     </row>
     <row r="18">
@@ -9981,13 +9981,13 @@
         <v>0.95424</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1.77</v>
+        <v>2.41</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.0636</v>
+        <v>0.069299996</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>14353083</v>
+        <v>15654509</v>
       </c>
     </row>
     <row r="19">
@@ -10008,13 +10008,13 @@
         <v>0.76087</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.028099999</v>
+        <v>0.0242</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>1414201</v>
+        <v>1301175</v>
       </c>
     </row>
     <row r="20">
@@ -10035,13 +10035,13 @@
         <v>0.68561995</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>2.5</v>
+        <v>4.41</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.0402</v>
+        <v>0.04</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>640591</v>
+        <v>653244</v>
       </c>
     </row>
     <row r="21">
@@ -10062,13 +10062,13 @@
         <v>0.77101</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>9.16</v>
+        <v>8.01</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.1069</v>
+        <v>0.105500005</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>825105</v>
+        <v>814259</v>
       </c>
     </row>
     <row r="22">
@@ -10089,13 +10089,13 @@
         <v>0.80924004</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>13.9</v>
+        <v>9.81</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.0398</v>
+        <v>0.044099998</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>882764</v>
+        <v>984852</v>
       </c>
     </row>
     <row r="23">
@@ -10116,13 +10116,13 @@
         <v>0.40625</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>5.72</v>
+        <v>5.74</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.024300002</v>
+        <v>0.0225</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>830872</v>
+        <v>771157</v>
       </c>
     </row>
     <row r="24">
@@ -10212,13 +10212,13 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1278.02</v>
+        <v>1301.47</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>1212.93</v>
+        <v>1210.03</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>1068.57</v>
+        <v>1069.91</v>
       </c>
     </row>
     <row r="3">
@@ -10228,13 +10228,13 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1267.7</v>
+        <v>1290.96</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1208.61</v>
+        <v>1205.71</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>1061.03</v>
+        <v>1062.37</v>
       </c>
     </row>
     <row r="4">
@@ -10244,13 +10244,13 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1262.56</v>
+        <v>1285.75</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1207.14</v>
+        <v>1204.24</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>1059.21</v>
+        <v>1060.55</v>
       </c>
     </row>
     <row r="5">
@@ -10260,13 +10260,13 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1255.24</v>
+        <v>1278.31</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1198.19</v>
+        <v>1195.32</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1061.81</v>
+        <v>1063.15</v>
       </c>
     </row>
     <row r="6">
@@ -10276,13 +10276,13 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1260.08</v>
+        <v>1283.25</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1200.39</v>
+        <v>1197.51</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1062.85</v>
+        <v>1064.19</v>
       </c>
     </row>
     <row r="7">
@@ -10292,13 +10292,13 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1260.65</v>
+        <v>1283.92</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1208.38</v>
+        <v>1205.49</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1060.77</v>
+        <v>1062.11</v>
       </c>
     </row>
     <row r="8">
@@ -10308,13 +10308,13 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1245.91</v>
+        <v>1268.81</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1215.57</v>
+        <v>1212.66</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1054.28</v>
+        <v>1055.6</v>
       </c>
     </row>
     <row r="9">
@@ -10324,13 +10324,13 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1198.6</v>
+        <v>1220.65</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1211.65</v>
+        <v>1208.75</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1035.05</v>
+        <v>1036.35</v>
       </c>
     </row>
     <row r="10">
@@ -10340,13 +10340,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1223.27</v>
+        <v>1245.74</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1211.53</v>
+        <v>1208.62</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1052.2</v>
+        <v>1053.52</v>
       </c>
     </row>
     <row r="11">
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1194.61</v>
+        <v>1216.37</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>1219.54</v>
+        <v>1216.62</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1044.66</v>
+        <v>1045.98</v>
       </c>
     </row>
     <row r="12">
@@ -10372,13 +10372,13 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1190.42</v>
+        <v>1212.19</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1221.46</v>
+        <v>1218.53</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1040.51</v>
+        <v>1041.82</v>
       </c>
     </row>
     <row r="13">
@@ -10388,13 +10388,13 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1182.67</v>
+        <v>1204.3</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1219.01</v>
+        <v>1216.09</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>1028.3</v>
+        <v>1029.59</v>
       </c>
     </row>
     <row r="14">
@@ -10404,13 +10404,13 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1180.39</v>
+        <v>1201.96</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1213.02</v>
+        <v>1210.11</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>1030.89</v>
+        <v>1032.19</v>
       </c>
     </row>
     <row r="15">
@@ -10420,13 +10420,13 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1199.22</v>
+        <v>1221.18</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1216.33</v>
+        <v>1213.41</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1042.33</v>
+        <v>1043.64</v>
       </c>
     </row>
     <row r="16">
@@ -10436,13 +10436,13 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1162.98</v>
+        <v>1184.15</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1215.31</v>
+        <v>1212.39</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1022.06</v>
+        <v>1023.35</v>
       </c>
     </row>
     <row r="17">
@@ -10452,13 +10452,13 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1139.6</v>
+        <v>1160.45</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1190.57</v>
+        <v>1187.71</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>1005.43</v>
+        <v>1006.7</v>
       </c>
     </row>
     <row r="18">
@@ -10468,13 +10468,13 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1146.17</v>
+        <v>1167.1</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1204.31</v>
+        <v>1201.42</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1007.25</v>
+        <v>1008.52</v>
       </c>
     </row>
     <row r="19">
@@ -10484,13 +10484,13 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1151.26</v>
+        <v>1172.26</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>1210.6</v>
+        <v>1207.69</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>1015.31</v>
+        <v>1016.58</v>
       </c>
     </row>
     <row r="20">
@@ -10500,13 +10500,13 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1136.33</v>
+        <v>1157.04</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1211.04</v>
+        <v>1208.13</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1008.29</v>
+        <v>1009.56</v>
       </c>
     </row>
     <row r="21">
@@ -10516,13 +10516,13 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1142.19</v>
+        <v>1163.09</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1217.19</v>
+        <v>1214.27</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>1014.01</v>
+        <v>1015.28</v>
       </c>
     </row>
     <row r="22">
@@ -10532,13 +10532,13 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1129.34</v>
+        <v>1149.95</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1222.04</v>
+        <v>1219.11</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1010.37</v>
+        <v>1011.64</v>
       </c>
     </row>
     <row r="23">
@@ -10548,13 +10548,13 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1131.13</v>
+        <v>1151.88</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>1221.91</v>
+        <v>1218.98</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>1002.58</v>
+        <v>1003.84</v>
       </c>
     </row>
     <row r="24">
@@ -10564,13 +10564,13 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1079.18</v>
+        <v>1098.49</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>1219.49</v>
+        <v>1216.56</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>986.21</v>
+        <v>987.45</v>
       </c>
     </row>
     <row r="25">
@@ -10580,13 +10580,13 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1067.55</v>
+        <v>1086.6</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>1215.85</v>
+        <v>1212.94</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>964.9</v>
+        <v>966.12</v>
       </c>
     </row>
     <row r="26">
@@ -10596,13 +10596,13 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1085.65</v>
+        <v>1105.18</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>1221.9</v>
+        <v>1218.97</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>974.26</v>
+        <v>975.48</v>
       </c>
     </row>
     <row r="27">
@@ -10612,13 +10612,13 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1082.34</v>
+        <v>1101.83</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>1211.56</v>
+        <v>1208.66</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>963.35</v>
+        <v>964.5599999999999</v>
       </c>
     </row>
     <row r="28">
@@ -10628,13 +10628,13 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1103.26</v>
+        <v>1122.98</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>1205.7</v>
+        <v>1202.8</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>984.65</v>
+        <v>985.89</v>
       </c>
     </row>
     <row r="29">
@@ -10644,13 +10644,13 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1078.9</v>
+        <v>1098.17</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1190.64</v>
+        <v>1187.78</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>965.42</v>
+        <v>966.64</v>
       </c>
     </row>
     <row r="30">
@@ -10660,13 +10660,13 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1105.57</v>
+        <v>1125.24</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>1213.48</v>
+        <v>1210.57</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>983.61</v>
+        <v>984.85</v>
       </c>
     </row>
     <row r="31">
@@ -10676,13 +10676,13 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1107.42</v>
+        <v>1127.13</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>1219.33</v>
+        <v>1216.41</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>990.88</v>
+        <v>992.13</v>
       </c>
     </row>
     <row r="32">
@@ -10692,13 +10692,13 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1104.39</v>
+        <v>1124.01</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>1216.12</v>
+        <v>1213.2</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>992.7</v>
+        <v>993.95</v>
       </c>
     </row>
     <row r="33">
@@ -10708,13 +10708,13 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1089.97</v>
+        <v>1109.42</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>1215.83</v>
+        <v>1212.92</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>985.17</v>
+        <v>986.41</v>
       </c>
     </row>
     <row r="34">
@@ -10724,13 +10724,13 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1053.25</v>
+        <v>1072.26</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>1197.05</v>
+        <v>1194.18</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>950.88</v>
+        <v>952.0700000000001</v>
       </c>
     </row>
     <row r="35">
@@ -10740,13 +10740,13 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1044.12</v>
+        <v>1062.66</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>1197.89</v>
+        <v>1195.02</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>938.66</v>
+        <v>939.85</v>
       </c>
     </row>
     <row r="36">
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1058.84</v>
+        <v>1077.66</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>1199.83</v>
+        <v>1196.95</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>940.48</v>
+        <v>941.67</v>
       </c>
     </row>
     <row r="37">
@@ -10772,13 +10772,13 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1092.05</v>
+        <v>1111.43</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>1205.87</v>
+        <v>1202.98</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>965.9400000000001</v>
+        <v>967.16</v>
       </c>
     </row>
     <row r="38">
@@ -10788,13 +10788,13 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1086.96</v>
+        <v>1106.18</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>1202.69</v>
+        <v>1199.81</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>961.27</v>
+        <v>962.48</v>
       </c>
     </row>
     <row r="39">
@@ -10804,13 +10804,13 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1087.07</v>
+        <v>1106.29</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>1211.39</v>
+        <v>1208.48</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>958.9299999999999</v>
+        <v>960.14</v>
       </c>
     </row>
     <row r="40">
@@ -10820,13 +10820,13 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1043.97</v>
+        <v>1062.54</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>1199.02</v>
+        <v>1196.14</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>937.37</v>
+        <v>938.55</v>
       </c>
     </row>
     <row r="41">
@@ -10836,13 +10836,13 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1058.45</v>
+        <v>1077.13</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>1207.73</v>
+        <v>1204.84</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>945.42</v>
+        <v>946.61</v>
       </c>
     </row>
     <row r="42">
@@ -10852,13 +10852,13 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1062.33</v>
+        <v>1081.17</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>1217.93</v>
+        <v>1215</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>946.72</v>
+        <v>947.91</v>
       </c>
     </row>
     <row r="43">
@@ -10868,13 +10868,13 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1090.96</v>
+        <v>1110.26</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>1211.16</v>
+        <v>1208.26</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>949.0599999999999</v>
+        <v>950.25</v>
       </c>
     </row>
     <row r="44">
@@ -10884,13 +10884,13 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1078.38</v>
+        <v>1097.55</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>1205.34</v>
+        <v>1202.45</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>953.21</v>
+        <v>954.41</v>
       </c>
     </row>
     <row r="45">
@@ -10900,13 +10900,13 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1073.24</v>
+        <v>1092.42</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>1206.03</v>
+        <v>1203.14</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>944.64</v>
+        <v>945.83</v>
       </c>
     </row>
     <row r="46">
@@ -10916,13 +10916,13 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1069.14</v>
+        <v>1088.32</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>1195.4</v>
+        <v>1192.53</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>938.14</v>
+        <v>939.33</v>
       </c>
     </row>
     <row r="47">
@@ -10932,13 +10932,13 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1084.58</v>
+        <v>1104.04</v>
       </c>
       <c r="C47" s="13" t="n">
-        <v>1203.83</v>
+        <v>1200.95</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>943.86</v>
+        <v>945.05</v>
       </c>
     </row>
     <row r="48">
@@ -10948,13 +10948,13 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1082.23</v>
+        <v>1101.53</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>1197.12</v>
+        <v>1194.25</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>937.88</v>
+        <v>939.0700000000001</v>
       </c>
     </row>
     <row r="49">
@@ -10964,13 +10964,13 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1050.76</v>
+        <v>1069.57</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>1181.43</v>
+        <v>1178.6</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>928.27</v>
+        <v>929.4400000000001</v>
       </c>
     </row>
     <row r="50">
@@ -10980,13 +10980,13 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1052.33</v>
+        <v>1071.15</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>1191.78</v>
+        <v>1188.92</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>930.35</v>
+        <v>931.52</v>
       </c>
     </row>
     <row r="51">
@@ -10996,13 +10996,13 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1051.41</v>
+        <v>1070.26</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>1189.86</v>
+        <v>1187.01</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>928.53</v>
+        <v>929.7</v>
       </c>
     </row>
     <row r="52">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1065.78</v>
+        <v>1084.99</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>1188.37</v>
+        <v>1185.52</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>932.95</v>
+        <v>934.12</v>
       </c>
     </row>
     <row r="53">
@@ -11028,13 +11028,13 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1051.67</v>
+        <v>1070.56</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>1170.33</v>
+        <v>1167.52</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>921.78</v>
+        <v>922.9400000000001</v>
       </c>
     </row>
     <row r="54">
@@ -11044,13 +11044,13 @@
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1053.6</v>
+        <v>1072.48</v>
       </c>
       <c r="C54" s="13" t="n">
-        <v>1163.7</v>
+        <v>1160.91</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>919.7</v>
+        <v>920.86</v>
       </c>
     </row>
     <row r="55">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1046.18</v>
+        <v>1064.92</v>
       </c>
       <c r="C55" s="13" t="n">
-        <v>1175.54</v>
+        <v>1172.73</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>916.84</v>
+        <v>917.99</v>
       </c>
     </row>
     <row r="56">
@@ -11076,13 +11076,13 @@
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1058.46</v>
+        <v>1077.38</v>
       </c>
       <c r="C56" s="13" t="n">
-        <v>1178.64</v>
+        <v>1175.81</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>916.0599999999999</v>
+        <v>917.21</v>
       </c>
     </row>
     <row r="57">
@@ -11092,13 +11092,13 @@
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1050.57</v>
+        <v>1069.39</v>
       </c>
       <c r="C57" s="13" t="n">
-        <v>1162.19</v>
+        <v>1159.4</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>905.9299999999999</v>
+        <v>907.0700000000001</v>
       </c>
     </row>
     <row r="58">
@@ -11108,13 +11108,13 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1063.19</v>
+        <v>1082.11</v>
       </c>
       <c r="C58" s="13" t="n">
-        <v>1159.33</v>
+        <v>1156.55</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>912.9400000000001</v>
+        <v>914.09</v>
       </c>
     </row>
     <row r="59">
@@ -11124,13 +11124,13 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1035.14</v>
+        <v>1053.58</v>
       </c>
       <c r="C59" s="13" t="n">
-        <v>1142.71</v>
+        <v>1139.97</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>885.41</v>
+        <v>886.52</v>
       </c>
     </row>
     <row r="60">
@@ -11140,13 +11140,13 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1056.93</v>
+        <v>1075.79</v>
       </c>
       <c r="C60" s="13" t="n">
-        <v>1154.7</v>
+        <v>1151.94</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>922.8200000000001</v>
+        <v>923.98</v>
       </c>
     </row>
     <row r="61">
@@ -11156,7 +11156,7 @@
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1066.6</v>
+        <v>1086.8</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11168,7 +11168,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1066.6</v>
+        <v>1086.8</v>
       </c>
     </row>
     <row r="64">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-15.35%</t>
+          <t>-15.31%</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>140.5</v>
+        <v>140.6</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -6569,10 +6569,10 @@
         <v>0.118</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.32</v>
+        <v>3.91</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.0583</v>
+        <v>0.065</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0.309</v>
@@ -6581,7 +6581,7 @@
         <v>0.73225</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="P7" s="5" t="n">
         <v>0.0319</v>
@@ -6681,10 +6681,10 @@
         <v>0.575</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>2.68</v>
+        <v>2.17</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.044499997</v>
+        <v>0.0368</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>0.06136</v>
@@ -6693,7 +6693,7 @@
         <v>0.81711</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="P9" s="5" t="n">
         <v>0.0828</v>
@@ -6725,13 +6725,13 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>29.015823</v>
+        <v>29.005722</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.347034</v>
+        <v>37.33403</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>23.055845</v>
+        <v>23.04782</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0.503</v>
@@ -6807,7 +6807,7 @@
         <v>0.19124001</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="P11" s="5" t="n">
         <v>0.2831</v>
@@ -6967,10 +6967,10 @@
         <v>0.389</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.024600001</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>0.48116</v>
@@ -6979,7 +6979,7 @@
         <v>0.46126</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>7.05</v>
+        <v>7.07</v>
       </c>
       <c r="P14" s="5" t="n">
         <v>8.8889</v>
@@ -7325,7 +7325,7 @@
         <v>0.68561995</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="P20" s="5" t="n">
         <v>4.5455</v>
@@ -9684,13 +9684,13 @@
         <v>0.73225</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3.32</v>
+        <v>3.91</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0583</v>
+        <v>0.065</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>3367790</v>
+        <v>3749544</v>
       </c>
     </row>
     <row r="8">
@@ -9738,13 +9738,13 @@
         <v>0.81711</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2.68</v>
+        <v>2.17</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.044499997</v>
+        <v>0.0368</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>2574942</v>
+        <v>2415829</v>
       </c>
     </row>
     <row r="10">
@@ -9873,13 +9873,13 @@
         <v>0.46126</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.024600001</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>4092356</v>
+        <v>4452753</v>
       </c>
     </row>
     <row r="15">

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -61,13 +61,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00FF0000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FF0000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.9</v>
+        <v>54.17</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0166667</v>
+        <v>-0.013297</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,34 +670,34 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.221</v>
+        <v>-0.231</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>37.12</v>
+        <v>36.626</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>49.423</v>
+        <v>48.933</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.361704</v>
+        <v>23.051064</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.610623</v>
+        <v>14.416347</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>10.903</v>
+        <v>10.795</v>
       </c>
       <c r="N2" s="7" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>0.888</v>
       </c>
-      <c r="P2" s="4" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="Q2" s="9" t="n">
-        <v>-0.154</v>
+      <c r="P2" s="9" t="n">
+        <v>0.3720000000000001</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>-0.165</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.83</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>-0.0141707</v>
+        <v>103.4</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>-0.0410832</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -729,13 +729,13 @@
         <v>99.95999999999999</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-0.6559999999999999</v>
+        <v>-0.67</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.865</v>
+        <v>18.09</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>30.584</v>
+        <v>29.807</v>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.984102</v>
+        <v>9.713507999999999</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>14.345</v>
+        <v>13.981</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>1.177</v>
       </c>
-      <c r="P3" s="9" t="n">
-        <v>-0.5529999999999999</v>
-      </c>
-      <c r="Q3" s="9" t="n">
-        <v>-0.506</v>
+      <c r="P3" s="4" t="n">
+        <v>-0.5620000000000001</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>-0.526</v>
       </c>
     </row>
     <row r="4">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.31</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>-0.0261124</v>
+        <v>21.42</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>-0.0810811</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -790,13 +790,13 @@
         <v>21.01</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.522</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11.603</v>
+        <v>10.662</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>12.254</v>
+        <v>11.322</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
@@ -804,22 +804,22 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>11.97657</v>
+        <v>11.005498</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>44.905</v>
+        <v>41.491</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>19.3</v>
+        <v>17.8</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>1.682</v>
       </c>
-      <c r="P4" s="9" t="n">
-        <v>-0.402</v>
-      </c>
-      <c r="Q4" s="9" t="n">
-        <v>-0.346</v>
+      <c r="P4" s="4" t="n">
+        <v>-0.4320000000000001</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>-0.399</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.77</v>
+        <v>101.89</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.0162167</v>
+        <v>-0.856278</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,22 +851,22 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.237</v>
+        <v>-0.244</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.717</v>
+        <v>10.625</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>20.033</v>
+        <v>19.942</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.729298</v>
+        <v>32.449043</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>17.296192</v>
+        <v>17.148088</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>11.45</v>
+        <v>11.398</v>
       </c>
       <c r="N5" s="7" t="n">
         <v>9.199999999999999</v>
@@ -874,11 +874,11 @@
       <c r="O5" s="8" t="n">
         <v>1.034</v>
       </c>
-      <c r="P5" s="4" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="Q5" s="9" t="n">
-        <v>-0.16</v>
+      <c r="P5" s="9" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>-0.167</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.11</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0.433017</v>
+        <v>37.49</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0.0102399</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,34 +910,34 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.076</v>
+        <v>-0.066</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10.15</v>
+        <v>10.254</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>39.621</v>
+        <v>39.718</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>48.82895</v>
+        <v>49.32895</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>15.837925</v>
+        <v>16.000103</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>16.827</v>
+        <v>16.869</v>
       </c>
       <c r="N6" s="7" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>1.396</v>
       </c>
-      <c r="P6" s="4" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0.017</v>
+      <c r="P6" s="9" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Q6" s="9" t="n">
+        <v>0.027</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.47</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0.0308762</v>
+        <v>84.87</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>0.473543</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -969,45 +969,45 @@
         <v>58.94</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.061</v>
+        <v>-0.057</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.377</v>
+        <v>6.407</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>8.734</v>
+        <v>8.763999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.7442377</v>
+        <v>3.7437143</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.367712</v>
+        <v>10.416807</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>7.272</v>
+        <v>7.297</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>1.22</v>
       </c>
-      <c r="P7" s="4" t="n">
-        <v>0.248</v>
-      </c>
-      <c r="Q7" s="9" t="n">
-        <v>-0.018</v>
+      <c r="P7" s="9" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>-0.013</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1016,57 +1016,57 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.74</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0.0113636</v>
+        <v>87.2</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.0133643</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>68.98999999999999</v>
+        <v>118.46</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>35.09</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.149</v>
+        <v>-0.264</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.04</v>
+        <v>6.078</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>6.886</v>
+        <v>11.12</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>18.64762</v>
+        <v>16.268656</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>17.876219</v>
+        <v>11.744044</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>8.461</v>
+        <v>11.623</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>1.453</v>
+        <v>0.66</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="Q8" s="9" t="n">
-        <v>-0.049</v>
+        <v>-0.228</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>-0.221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1075,46 +1075,46 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>86.05</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0.0168991</v>
+        <v>58.75</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.0170213</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>118.46</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>80.23999999999999</v>
+        <v>35.09</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.274</v>
+        <v>-0.148</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.997</v>
+        <v>6.041</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>11.04</v>
+        <v>6.886</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.26654</v>
+        <v>18.83013</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>11.589164</v>
+        <v>17.879261</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>11.54</v>
+        <v>8.461</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>0.66</v>
+        <v>1.453</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>-0.236</v>
-      </c>
-      <c r="Q9" s="9" t="n">
-        <v>-0.231</v>
+        <v>0.391</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>-0.048</v>
       </c>
     </row>
     <row r="10">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>-0.0117768</v>
+        <v>18.51</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>-0.0409326</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>32.22</v>
@@ -1146,154 +1146,154 @@
         <v>15.725</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.401</v>
+        <v>-0.426</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.712</v>
+        <v>5.478</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>5.494</v>
+        <v>5.256</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>53.611107</v>
+        <v>51.416664</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>23.435766</v>
+        <v>22.463898</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>10.826</v>
+        <v>10.358</v>
       </c>
       <c r="N10" s="7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>2.002</v>
       </c>
-      <c r="P10" s="9" t="n">
-        <v>-0.155</v>
-      </c>
-      <c r="Q10" s="9" t="n">
-        <v>-0.172</v>
+      <c r="P10" s="4" t="n">
+        <v>-0.175</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>-0.206</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.98</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0.0280898</v>
+        <v>26.82</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.0193843</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>14.38</v>
+        <v>31.58</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5.59</v>
+        <v>17.86</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.236</v>
+        <v>-0.151</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.552</v>
+        <v>5.474</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>5.145</v>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>26.142857</v>
+        <v>30.375</v>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12.658373</v>
+        <v>26.14035</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>10.484</v>
+        <v>8.691000000000001</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>1.1</v>
+        <v>1.977</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5920000000000001</v>
+        <v>-0.028</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>-0.052</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.31</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>-0.4916829999999999</v>
+        <v>10.54</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>-0.0400728</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>31.58</v>
+        <v>14.38</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>17.86</v>
+        <v>5.59</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.167</v>
+        <v>-0.267</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.37</v>
+        <v>5.329</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>30.272</v>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>4.922</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>25.707317</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>28.443243</v>
+        <v>12.151116</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>8.661</v>
+        <v>10.031</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>1.977</v>
+        <v>1.1</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>-0.045</v>
+        <v>0.552</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.117</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>22.16</v>
+        <v>21.92</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.0188506</v>
+        <v>-0.0108303</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.022</v>
+        <v>-0.032</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.159</v>
+        <v>5.103</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>71.48387</v>
+        <v>70.70968000000001</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>29.612604</v>
+        <v>29.291891</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1354,11 +1354,11 @@
       <c r="O13" s="8" t="n">
         <v>1.552</v>
       </c>
-      <c r="P13" s="4" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>0.148</v>
+      <c r="P13" s="9" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>0.135</v>
       </c>
     </row>
     <row r="14">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13.02</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>-0.229883</v>
+        <v>12.94</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>-0.614446</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>18.57</v>
@@ -1390,13 +1390,13 @@
         <v>12.53</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-0.299</v>
+        <v>-0.303</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.403</v>
+        <v>2.388</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>5.971</v>
+        <v>5.956</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="L14" s="7" t="n">
-        <v>12.083078</v>
+        <v>12.008834</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>6.769</v>
+        <v>6.753</v>
       </c>
       <c r="N14" s="7" t="n">
         <v>5.8</v>
@@ -1415,11 +1415,11 @@
       <c r="O14" s="8" t="n">
         <v>1.082</v>
       </c>
-      <c r="P14" s="9" t="n">
-        <v>-0.021</v>
-      </c>
-      <c r="Q14" s="9" t="n">
-        <v>-0.134</v>
+      <c r="P14" s="4" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>-0.139</v>
       </c>
     </row>
     <row r="15">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.52</v>
+        <v>5.48</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.91408</v>
+        <v>-0.724637</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>10.15</v>
@@ -1451,34 +1451,34 @@
         <v>4.55</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.456</v>
+        <v>-0.46</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.245</v>
+        <v>2.229</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>12.821</v>
+        <v>12.774</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>11.74468</v>
+        <v>11.913043</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>6.938247</v>
+        <v>6.88797</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>10.631</v>
+        <v>10.592</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>0.603</v>
       </c>
-      <c r="P15" s="4" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="Q15" s="9" t="n">
-        <v>-0.265</v>
+      <c r="P15" s="9" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0.207761</v>
+        <v>14.66</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0.0131306</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>20.61</v>
@@ -1510,13 +1510,13 @@
         <v>11.65</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.298</v>
+        <v>-0.289</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.932</v>
+        <v>1.958</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>12.414</v>
+        <v>12.438</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>8.313560000000001</v>
+        <v>8.471393000000001</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>17.19</v>
+        <v>17.223</v>
       </c>
       <c r="N16" s="7" t="n">
         <v>10.9</v>
@@ -1535,11 +1535,11 @@
       <c r="O16" s="8" t="n">
         <v>1.364</v>
       </c>
-      <c r="P16" s="9" t="n">
-        <v>-0.165</v>
-      </c>
-      <c r="Q16" s="9" t="n">
-        <v>-0.026</v>
+      <c r="P16" s="4" t="n">
+        <v>-0.156</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>-0.013</v>
       </c>
     </row>
     <row r="17">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.88</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0.630974</v>
+        <v>99.47</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>0.596687</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>113.88</v>
@@ -1571,34 +1571,34 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.132</v>
+        <v>-0.127</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.769</v>
+        <v>1.779</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.685</v>
+        <v>1.696</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>18.209946</v>
+        <v>18.318602</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>16.632463</v>
+        <v>16.731707</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>8.837</v>
+        <v>8.893000000000001</v>
       </c>
       <c r="N17" s="7" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>1.376</v>
       </c>
-      <c r="P17" s="4" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>0.033</v>
+      <c r="P17" s="9" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>0.039</v>
       </c>
     </row>
     <row r="18">
@@ -1618,25 +1618,25 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>-0.0340425</v>
+        <v>0.0132158</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.73</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.669</v>
+        <v>-0.665</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.168</v>
+        <v>1.183</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.868</v>
+        <v>0.883</v>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>4.5858583</v>
+        <v>4.6464643</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>-7.201</v>
+        <v>-7.324</v>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
@@ -1657,11 +1657,11 @@
       <c r="O18" s="8" t="n">
         <v>1.993</v>
       </c>
-      <c r="P18" s="9" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="Q18" s="9" t="n">
-        <v>-0.579</v>
+      <c r="P18" s="4" t="n">
+        <v>-0.5670000000000001</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>-0.573</v>
       </c>
     </row>
     <row r="19">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.29</v>
+        <v>11.26</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.266427</v>
+        <v>-0.26572</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>13.31</v>
@@ -1693,22 +1693,22 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.152</v>
+        <v>-0.154</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.245</v>
+        <v>1.242</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>18.816666</v>
+        <v>18.766666</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>12.19183</v>
+        <v>12.159433</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>6.582</v>
+        <v>6.569</v>
       </c>
       <c r="N19" s="7" t="n">
         <v>4.6</v>
@@ -1716,11 +1716,11 @@
       <c r="O19" s="8" t="n">
         <v>1.07</v>
       </c>
-      <c r="P19" s="4" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="Q19" s="9" t="n">
-        <v>-0.006999999999999999</v>
+      <c r="P19" s="9" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="20">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.62</v>
+        <v>26.39</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.986344</v>
+        <v>-0.864017</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>32.74</v>
@@ -1752,13 +1752,13 @@
         <v>19.57</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.187</v>
+        <v>-0.194</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.703</v>
+        <v>0.697</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.16</v>
+        <v>1.154</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>22</v>
+        <v>21.809916</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>9.504</v>
+        <v>9.455</v>
       </c>
       <c r="N20" s="7" t="n">
         <v>7.2</v>
@@ -1778,10 +1778,10 @@
         <v>1.412</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="Q20" s="9" t="n">
-        <v>-0.016</v>
+        <v>0.004</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>-0.025</v>
       </c>
     </row>
     <row r="21">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.6</v>
+        <v>11.92</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>-0.0421139</v>
+        <v>0.0275862</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>20.74</v>
@@ -1813,15 +1813,13 @@
         <v>8.455</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.441</v>
+        <v>-0.425</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.586</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>7.795</v>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
@@ -1829,28 +1827,24 @@
         </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>-14.320988</v>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-14.716049</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>22.644</v>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>15.5</v>
       </c>
       <c r="O21" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="P21" s="9" t="n">
-        <v>-0.282</v>
-      </c>
-      <c r="Q21" s="9" t="n">
-        <v>-0.303</v>
+      <c r="P21" s="4" t="n">
+        <v>-0.145</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>-0.284</v>
       </c>
     </row>
     <row r="22">
@@ -1870,10 +1864,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.45</v>
+        <v>6.7</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>-0.769234</v>
+        <v>0.0387597</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>9.949999999999999</v>
@@ -1882,13 +1876,13 @@
         <v>6.1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.352</v>
+        <v>-0.327</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.175</v>
+        <v>0.181</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.505</v>
+        <v>0.512</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
@@ -1896,10 +1890,10 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>8.609643</v>
+        <v>8.943350000000001</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>6.8</v>
+        <v>6.891</v>
       </c>
       <c r="N22" s="7" t="n">
         <v>5.5</v>
@@ -1907,11 +1901,11 @@
       <c r="O22" s="8" t="n">
         <v>1.206</v>
       </c>
-      <c r="P22" s="9" t="n">
-        <v>-0.285</v>
-      </c>
-      <c r="Q22" s="9" t="n">
-        <v>-0.281</v>
+      <c r="P22" s="4" t="n">
+        <v>-0.253</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>-0.253</v>
       </c>
     </row>
     <row r="23">
@@ -1931,10 +1925,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>-0.0431034</v>
+        <v>0.036036</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>4.95</v>
@@ -1943,13 +1937,13 @@
         <v>2.02</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-0.552</v>
+        <v>-0.535</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.08</v>
+        <v>0.083</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.574</v>
+        <v>0.577</v>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
@@ -1957,22 +1951,22 @@
         </is>
       </c>
       <c r="L23" s="7" t="n">
-        <v>-5.414634</v>
+        <v>-5.609756</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>12.461</v>
+        <v>12.524</v>
       </c>
       <c r="N23" s="7" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>1.327</v>
       </c>
-      <c r="P23" s="9" t="n">
-        <v>-0.504</v>
-      </c>
-      <c r="Q23" s="9" t="n">
-        <v>-0.112</v>
+      <c r="P23" s="4" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="24">
@@ -2037,10 +2031,10 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="P24" s="9" t="n">
+      <c r="P24" s="4" t="n">
         <v>-0.239</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="4" t="n">
         <v>-0.239</v>
       </c>
     </row>
@@ -2158,28 +2152,28 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.9</v>
+        <v>54.17</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0166667</v>
+        <v>-0.013297</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.165</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.392</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>53.3</v>
+        <v>52.8</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.035</v>
+        <v>-0.048</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.015</v>
+        <v>-0.028</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.221</v>
+        <v>-0.231</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
@@ -2205,28 +2199,28 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.83</v>
+        <v>103.4</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.0141707</v>
+        <v>-0.0410832</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0.506</v>
+        <v>-0.526</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.5529999999999999</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-57.3</v>
+        <v>-58.6</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.251</v>
+        <v>-0.281</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.531</v>
+        <v>-0.55</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.6559999999999999</v>
+        <v>-0.67</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>1.177</v>
@@ -2252,28 +2246,28 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.31</v>
+        <v>21.42</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.0261124</v>
+        <v>-0.0810811</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.346</v>
+        <v>-0.399</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.402</v>
+        <v>-0.4320000000000001</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-36.2</v>
+        <v>-36.9</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.142</v>
+        <v>-0.211</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.347</v>
+        <v>-0.4</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.522</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
@@ -2299,28 +2293,28 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.77</v>
+        <v>101.89</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.0162167</v>
+        <v>-0.856278</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.16</v>
+        <v>-0.167</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.206</v>
+        <v>0.198</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.065</v>
+        <v>-0.073</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.101</v>
+        <v>-0.109</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.237</v>
+        <v>-0.244</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>1.034</v>
@@ -2346,28 +2340,28 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.11</v>
+        <v>37.49</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.433017</v>
+        <v>0.0102399</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.017</v>
+        <v>0.027</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.158</v>
+        <v>0.167</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.047</v>
+        <v>0.058</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.055</v>
+        <v>0.066</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.076</v>
+        <v>-0.066</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>1.396</v>
@@ -2393,28 +2387,28 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.47</v>
+        <v>84.87</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.0308762</v>
+        <v>0.473543</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.013</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.248</v>
+        <v>0.253</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.061</v>
+        <v>-0.057</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>1.22</v>
@@ -2426,12 +2420,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2440,45 +2434,45 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.74</v>
+        <v>87.2</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.0113636</v>
+        <v>0.0133643</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.049</v>
+        <v>-0.221</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.389</v>
+        <v>-0.228</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>39</v>
+        <v>-2.9</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.047</v>
+        <v>-0.08</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.136</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.149</v>
+        <v>-0.264</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>1.453</v>
+        <v>0.66</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>941430</v>
+        <v>1091240</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2487,34 +2481,34 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>86.05</v>
+        <v>58.75</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.0168991</v>
+        <v>0.0170213</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.231</v>
+        <v>-0.048</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.236</v>
+        <v>0.391</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-2.9</v>
+        <v>38.6</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.092</v>
+        <v>-0.047</v>
       </c>
       <c r="J9" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K9" s="5" t="n">
         <v>-0.148</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v>-0.274</v>
-      </c>
       <c r="L9" s="8" t="n">
-        <v>0.66</v>
+        <v>1.453</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>1091240</v>
+        <v>941430</v>
       </c>
     </row>
     <row r="10">
@@ -2534,28 +2528,28 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.3</v>
+        <v>18.51</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.0117768</v>
+        <v>-0.0409326</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.172</v>
+        <v>-0.206</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.155</v>
+        <v>-0.175</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-28.5</v>
+        <v>-29.3</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.05</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-0.213</v>
+        <v>-0.245</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.401</v>
+        <v>-0.426</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>2.002</v>
@@ -2567,95 +2561,95 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.98</v>
+        <v>26.82</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.0280898</v>
+        <v>0.0193843</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.052</v>
+        <v>0.138</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.5920000000000001</v>
+        <v>-0.028</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>27.1</v>
+        <v>-22.3</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.092</v>
+        <v>0.144</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.022</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.236</v>
+        <v>-0.151</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>1.1</v>
+        <v>1.977</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>1926430</v>
+        <v>6358500</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.31</v>
+        <v>10.54</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.4916829999999999</v>
+        <v>-0.0400728</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.117</v>
+        <v>-0.09</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.045</v>
+        <v>0.552</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-22.7</v>
+        <v>26.3</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.122</v>
+        <v>0.049</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.067</v>
+        <v>-0.061</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.167</v>
+        <v>-0.267</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>1.977</v>
+        <v>1.1</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>6358500</v>
+        <v>1926430</v>
       </c>
     </row>
     <row r="13">
@@ -2675,28 +2669,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>22.16</v>
+        <v>21.92</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.0188506</v>
+        <v>-0.0108303</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.148</v>
+        <v>0.135</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.975</v>
+        <v>1.009</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.178</v>
+        <v>0.165</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.212</v>
+        <v>0.199</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.022</v>
+        <v>-0.032</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2722,28 +2716,28 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13.02</v>
+        <v>12.94</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.229883</v>
+        <v>-0.614446</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.134</v>
+        <v>-0.139</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.032</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.055</v>
+        <v>-0.061</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.157</v>
+        <v>-0.162</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-0.299</v>
+        <v>-0.303</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>1.082</v>
@@ -2769,28 +2763,28 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.52</v>
+        <v>5.48</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.91408</v>
+        <v>-0.724637</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.265</v>
+        <v>-0.27</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.013</v>
+        <v>0.019</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.083</v>
+        <v>-0.08900000000000001</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.297</v>
+        <v>-0.302</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.456</v>
+        <v>-0.46</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>0.603</v>
@@ -2816,28 +2810,28 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.47</v>
+        <v>14.66</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.207761</v>
+        <v>0.0131306</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.026</v>
+        <v>-0.013</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.156</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>-19.3</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.05</v>
+        <v>0.064</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.109</v>
+        <v>-0.098</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.298</v>
+        <v>-0.289</v>
       </c>
       <c r="L16" s="8" t="n">
         <v>1.364</v>
@@ -2863,28 +2857,28 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.88</v>
+        <v>99.47</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.630974</v>
+        <v>0.596687</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.033</v>
+        <v>0.039</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.236</v>
+        <v>0.242</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.042</v>
+        <v>0.048</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.029</v>
+        <v>0.035</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.132</v>
+        <v>-0.127</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.376</v>
@@ -2910,28 +2904,28 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.0340425</v>
+        <v>0.0132158</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.579</v>
+        <v>-0.573</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.59</v>
+        <v>-0.5670000000000001</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-32.3</v>
+        <v>-33.5</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.37</v>
+        <v>-0.361</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.556</v>
+        <v>-0.55</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.669</v>
+        <v>-0.665</v>
       </c>
       <c r="L18" s="8" t="n">
         <v>1.993</v>
@@ -2957,28 +2951,28 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.29</v>
+        <v>11.26</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.266427</v>
+        <v>-0.26572</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.116</v>
+        <v>0.102</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0</v>
+        <v>-0.003</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.152</v>
+        <v>-0.154</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.07</v>
@@ -3004,28 +2998,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.62</v>
+        <v>26.39</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.986344</v>
+        <v>-0.864017</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.025</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>5.4</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.047</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.018</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.187</v>
+        <v>-0.194</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>1.412</v>
@@ -3051,28 +3045,28 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.6</v>
+        <v>11.92</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-0.0421139</v>
+        <v>0.0275862</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.303</v>
+        <v>-0.284</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.282</v>
+        <v>-0.145</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>39.2</v>
+        <v>39.6</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.201</v>
+        <v>-0.179</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.127</v>
+        <v>-0.103</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.441</v>
+        <v>-0.425</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -3100,28 +3094,28 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.45</v>
+        <v>6.7</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.769234</v>
+        <v>0.0387597</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.281</v>
+        <v>-0.253</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.285</v>
+        <v>-0.253</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.23</v>
+        <v>-0.2</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.247</v>
+        <v>-0.218</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.352</v>
+        <v>-0.327</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.206</v>
@@ -3147,28 +3141,28 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-0.0431034</v>
+        <v>0.036036</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-0.112</v>
+        <v>-0.08</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.504</v>
+        <v>-0.45</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-52.7</v>
+        <v>-52.5</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.081</v>
+        <v>-0.048</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-0.28</v>
+        <v>-0.254</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>-0.552</v>
+        <v>-0.535</v>
       </c>
       <c r="L23" s="8" t="n">
         <v>1.327</v>
@@ -3206,7 +3200,7 @@
         <v>-0.239</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>-285.9</v>
+        <v>-275.9</v>
       </c>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
@@ -3348,31 +3342,31 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.9</v>
+        <v>54.17</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>37.12</v>
+        <v>36.626</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>23.361704</v>
+        <v>23.051064</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.610623</v>
+        <v>14.416347</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>10.903</v>
+        <v>10.795</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>3.797</v>
+        <v>3.759</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.302208</v>
+        <v>22.99236</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.8516388</v>
+        <v>2.8137207</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3401,10 +3395,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>107.83</v>
+        <v>103.4</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.865</v>
+        <v>18.09</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3412,28 +3406,28 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.984102</v>
+        <v>9.713507999999999</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>14.345</v>
+        <v>13.981</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.867</v>
+        <v>1.819</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.090539</v>
+        <v>2.004653</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1515056</v>
+        <v>1.104198</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.68</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>10.80017</v>
+        <v>10.64497</v>
       </c>
       <c r="O3" s="3" t="n">
         <v>51.58</v>
@@ -3456,10 +3450,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>23.31</v>
+        <v>21.42</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>11.603</v>
+        <v>10.662</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3467,22 +3461,22 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>11.97657</v>
+        <v>11.005498</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>44.905</v>
+        <v>41.491</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>19.3</v>
+        <v>17.8</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>2.024</v>
+        <v>1.87</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>18.268024</v>
+        <v>16.786833</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.9164306</v>
+        <v>1.7610444</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3511,31 +3505,31 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.77</v>
+        <v>101.89</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.717</v>
+        <v>10.625</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.729298</v>
+        <v>32.449043</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>17.296192</v>
+        <v>17.148088</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>11.45</v>
+        <v>11.398</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>2.807</v>
+        <v>2.794</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-38.232887</v>
+        <v>-37.905506</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.501444</v>
+        <v>1.4885875</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3564,31 +3558,31 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.11</v>
+        <v>37.49</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.15</v>
+        <v>10.254</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>48.82895</v>
+        <v>49.32895</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>15.837925</v>
+        <v>16.000103</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>16.827</v>
+        <v>16.869</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>2.259</v>
+        <v>2.265</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.9449348</v>
+        <v>3.9853303</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.5787437</v>
+        <v>0.58466995</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3617,34 +3611,34 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.47</v>
+        <v>84.87</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.377</v>
+        <v>6.407</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.7442377</v>
+        <v>3.7437143</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.367712</v>
+        <v>10.416807</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>7.272</v>
+        <v>7.297</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>2.134</v>
+        <v>2.142</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.4729922</v>
+        <v>2.484703</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5583686</v>
+        <v>1.5657481</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>22.56</v>
+        <v>22.67</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>8.147410000000001</v>
@@ -3656,12 +3650,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3670,51 +3664,51 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>58.74</v>
+        <v>87.2</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.04</v>
+        <v>6.078</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>18.64762</v>
+        <v>16.268656</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>17.876219</v>
+        <v>11.744044</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>8.461</v>
+        <v>11.623</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>3.423</v>
+        <v>3.801</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.444569</v>
+        <v>6.010891</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>3.0027857</v>
+        <v>2.0771468</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>3.15</v>
+        <v>5.36</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>3.28593</v>
+        <v>7.42504</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>3.572</v>
+        <v>14.507</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3723,40 +3717,40 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>86.05</v>
+        <v>58.75</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.997</v>
+        <v>6.041</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>16.26654</v>
+        <v>18.83013</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>11.589164</v>
+        <v>17.879261</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>11.54</v>
+        <v>8.461</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>3.773</v>
+        <v>3.423</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>5.9316196</v>
+        <v>16.447369</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.0497534</v>
+        <v>3.0032966</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>5.29</v>
+        <v>3.12</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>7.42504</v>
+        <v>3.28593</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>14.507</v>
+        <v>3.572</v>
       </c>
     </row>
     <row r="10">
@@ -3776,148 +3770,148 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19.3</v>
+        <v>18.51</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.712</v>
+        <v>5.478</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>53.611107</v>
+        <v>51.416664</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>23.435766</v>
+        <v>22.463898</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>10.826</v>
+        <v>10.358</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>4.259</v>
+        <v>4.075</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5.103933</v>
+        <v>4.892276</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>4.427923</v>
+        <v>4.2466774</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.36</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.8235276</v>
+        <v>0.8239888</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>3.7813976</v>
+        <v>3.7835155</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.98</v>
+        <v>26.82</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.552</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>26.142857</v>
+        <v>5.474</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>12.658373</v>
+        <v>26.14035</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10.484</v>
+        <v>8.691000000000001</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>2.196</v>
+        <v>2.645</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.4541745</v>
+        <v>1.5509166</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2.3696582</v>
+        <v>0.4765954</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.42</v>
+        <v>-2.47</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.86741</v>
+        <v>1.026</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1.473</v>
+        <v>17.293</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>26.31</v>
+        <v>10.54</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>5.329</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>25.707317</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>28.443243</v>
+        <v>12.151116</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>8.661</v>
+        <v>10.031</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>2.636</v>
+        <v>2.101</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>1.5214249</v>
+        <v>7.1554646</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.46753263</v>
+        <v>2.2746992</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>-2.42</v>
+        <v>0.41</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.925</v>
+        <v>0.86741</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>17.293</v>
+        <v>1.473</v>
       </c>
     </row>
     <row r="13">
@@ -3937,16 +3931,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>22.16</v>
+        <v>21.92</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5.159</v>
+        <v>5.103</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>71.48387</v>
+        <v>70.70968000000001</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>29.612604</v>
+        <v>29.291891</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -3964,10 +3958,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>15.044127</v>
+        <v>14.881194</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.5472307</v>
+        <v>4.4979825</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -3996,10 +3990,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>13.02</v>
+        <v>12.94</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.403</v>
+        <v>2.388</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -4007,22 +4001,22 @@
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>12.083078</v>
+        <v>12.008834</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>6.769</v>
+        <v>6.753</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>5.8</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>2.378</v>
+        <v>2.372</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>2.7802691</v>
+        <v>2.7631857</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.956815</v>
+        <v>0.9509358999999999</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>-0.01</v>
@@ -4051,34 +4045,34 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.52</v>
+        <v>5.48</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.245</v>
+        <v>2.229</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>11.74468</v>
+        <v>11.913043</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.938247</v>
+        <v>6.88797</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>10.631</v>
+        <v>10.592</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>2.483</v>
+        <v>2.474</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1.7298652</v>
+        <v>-1.71733</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.43489477</v>
+        <v>0.43174338</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>0.79559</v>
@@ -4104,10 +4098,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.47</v>
+        <v>14.66</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.932</v>
+        <v>1.958</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -4115,28 +4109,28 @@
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>8.313560000000001</v>
+        <v>8.471393000000001</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>17.19</v>
+        <v>17.223</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>10.9</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.783</v>
+        <v>1.787</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.9960763</v>
+        <v>1.0091553</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.2776059</v>
+        <v>0.281251</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-5.84</v>
+        <v>-5.83</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1.74053</v>
+        <v>1.73053</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>14.527</v>
@@ -4159,31 +4153,31 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>98.88</v>
+        <v>99.47</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.769</v>
+        <v>1.779</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>18.209946</v>
+        <v>18.318602</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>16.632463</v>
+        <v>16.731707</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>8.837</v>
+        <v>8.893000000000001</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>3.092</v>
+        <v>3.111</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>3.2769933</v>
+        <v>3.2965467</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3.244356</v>
+        <v>3.2637146</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>5.43</v>
@@ -4212,10 +4206,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1.168</v>
+        <v>1.183</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -4223,10 +4217,10 @@
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4.5858583</v>
+        <v>4.6464643</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-7.201</v>
+        <v>-7.324</v>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
@@ -4234,16 +4228,16 @@
         </is>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.297</v>
+        <v>1.319</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>1.5436926</v>
+        <v>1.5640938</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>1.7444884</v>
+        <v>1.7675432</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>0.99</v>
@@ -4269,31 +4263,31 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.29</v>
+        <v>11.26</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>18.816666</v>
+        <v>18.766666</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>12.19183</v>
+        <v>12.159433</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>6.582</v>
+        <v>6.569</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>4.6</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>3.4452243</v>
+        <v>3.4360697</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.6919532</v>
+        <v>0.6901145</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0.6</v>
@@ -4322,10 +4316,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.62</v>
+        <v>26.39</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.703</v>
+        <v>0.697</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -4333,22 +4327,22 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>22</v>
+        <v>21.809916</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>9.504</v>
+        <v>9.455</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>7.2</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.827</v>
+        <v>1.818</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.6560907</v>
+        <v>1.6417818</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>1.1068267</v>
+        <v>1.0972635</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.23</v>
@@ -4377,10 +4371,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.6</v>
+        <v>11.92</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.57</v>
+        <v>0.586</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -4388,37 +4382,31 @@
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-14.320988</v>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-14.716049</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>22.644</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>2.934</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>1.0927932</v>
+        <v>0.5815202</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.21465862</v>
+        <v>0.22058024</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-12.12</v>
+        <v>-12.45</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>10.615</v>
+        <v>20.498</v>
       </c>
     </row>
     <row r="22">
@@ -4438,10 +4426,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.45</v>
+        <v>6.7</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.175</v>
+        <v>0.181</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -4449,22 +4437,22 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>8.609643</v>
+        <v>8.943350000000001</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>6.8</v>
+        <v>6.891</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>5.5</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.661</v>
+        <v>1.684</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-10.696517</v>
+        <v>-11.111111</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.573937</v>
+        <v>0.5961826</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>-0.58</v>
@@ -4493,10 +4481,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.08</v>
+        <v>0.083</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -4504,25 +4492,25 @@
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-5.414634</v>
+        <v>-5.609756</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>12.461</v>
+        <v>12.524</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.899</v>
+        <v>1.909</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>31.714287</v>
+        <v>32.857143</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.26565078</v>
+        <v>0.27522376</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.16</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-0.41</v>
@@ -5086,12 +5074,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -5100,57 +5088,57 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2.011</v>
+        <v>2.926</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.032</v>
+        <v>0.067</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.6747</v>
+        <v>0.33583</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.31768</v>
+        <v>0.18802</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.0935</v>
+        <v>0.1309</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.4046</v>
+        <v>0.32698002</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1.113</v>
+        <v>0.35709</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.09383000399999999</v>
+        <v>0.06236</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.193</v>
+        <v>0.082</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>3.475</v>
+        <v>5.197</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.142</v>
+        <v>0.201</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>1045.932</v>
+        <v>492.233</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>0.79</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -5159,46 +5147,46 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2.926</v>
+        <v>2.011</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.067</v>
+        <v>0.032</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.33583</v>
+        <v>0.6747</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.18802</v>
+        <v>0.31768</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.1309</v>
+        <v>0.0935</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.32698002</v>
+        <v>0.4046</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.35709</v>
+        <v>1.113</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.06236</v>
+        <v>0.09383000399999999</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.957</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.082</v>
+        <v>0.193</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>5.197</v>
+        <v>3.475</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.201</v>
+        <v>0.142</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>492.233</v>
+        <v>1045.932</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>0.604</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="10">
@@ -5263,121 +5251,121 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2.343</v>
+        <v>11.486</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.178</v>
+        <v>0.042</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.51058</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.23518999</v>
+        <v>0.1893</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.09804</v>
+        <v>-0.043709997</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.20945999</v>
+        <v>0.30427998</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.32813</v>
+        <v>-0.10840999</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.23642</v>
+        <v>0.04044</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>3.495</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>0.6929999999999999</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.07199999999999999</v>
+        <v>25.622</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.478</v>
+        <v>0.887</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>9.69</v>
+        <v>695.117</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>1.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>11.486</v>
+        <v>2.343</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.042</v>
+        <v>0.178</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.5</v>
+        <v>0.51058</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.1893</v>
+        <v>0.23518999</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.043709997</v>
+        <v>0.09804</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.30427998</v>
+        <v>0.20945999</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.10840999</v>
+        <v>0.32813</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.04044</v>
+        <v>0.23642</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>3.495</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.491</v>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>25.622</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.887</v>
+        <v>0.478</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>695.117</v>
+        <v>9.69</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="13">
@@ -5885,37 +5873,37 @@
         <v>0.286</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.54836</v>
+        <v>0.5986900000000001</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.24103001</v>
+        <v>-0.045900002</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>-0.26389998</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.07475999999999999</v>
+        <v>0.12956999</v>
       </c>
       <c r="J21" s="5" t="n">
         <v>-0.5564</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.00855</v>
+        <v>0.0021</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.199</v>
+        <v>0.344</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.62</v>
+        <v>0.739</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>6.434</v>
+        <v>6.464</v>
       </c>
       <c r="O21" s="6" t="n">
         <v>0.798</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>252.846</v>
+        <v>254.019</v>
       </c>
       <c r="Q21" s="7" t="n">
         <v>0.798</v>
@@ -6257,7 +6245,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>54.9</v>
+        <v>54.17</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6279,8 +6267,8 @@
       <c r="I2" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>0.273</v>
+      <c r="J2" s="9" t="n">
+        <v>0.29</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>2.49</v>
@@ -6313,7 +6301,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>107.83</v>
+        <v>103.4</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6335,8 +6323,8 @@
       <c r="I3" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>0.973</v>
+      <c r="J3" s="9" t="n">
+        <v>1.057</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>2.02</v>
@@ -6371,7 +6359,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23.31</v>
+        <v>21.42</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6393,8 +6381,8 @@
       <c r="I4" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>0.552</v>
+      <c r="J4" s="9" t="n">
+        <v>0.6890000000000001</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>2.13</v>
@@ -6406,7 +6394,7 @@
         <v>0.02999</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0.88253</v>
+        <v>0.88254</v>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
@@ -6429,7 +6417,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>102.77</v>
+        <v>101.89</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -6451,8 +6439,8 @@
       <c r="I5" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>0.38</v>
+      <c r="J5" s="9" t="n">
+        <v>0.392</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.38</v>
@@ -6467,7 +6455,7 @@
         <v>0.68557</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="P5" s="5" t="n">
         <v>0.3185</v>
@@ -6485,7 +6473,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37.11</v>
+        <v>37.49</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -6507,8 +6495,8 @@
       <c r="I6" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>0.15</v>
+      <c r="J6" s="9" t="n">
+        <v>0.138</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.85</v>
@@ -6543,7 +6531,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>84.47</v>
+        <v>84.87</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -6565,8 +6553,8 @@
       <c r="I7" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>0.118</v>
+      <c r="J7" s="9" t="n">
+        <v>0.113</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.91</v>
@@ -6575,10 +6563,10 @@
         <v>0.065</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.309</v>
+        <v>0.30977</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>0.73225</v>
+        <v>0.73407</v>
       </c>
       <c r="O7" s="5" t="n">
         <v>0.88</v>
@@ -6590,113 +6578,113 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>58.74</v>
+        <v>87.2</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1.5625</v>
+        <v>1.25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>72.9375</v>
+        <v>135.5</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>0.242</v>
+        <v>110</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.5539999999999999</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>4.01</v>
+        <v>2.17</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.084300004</v>
+        <v>0.0368</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.07914</v>
+        <v>0.06136</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0.88882005</v>
+        <v>0.81711</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>1.79</v>
+        <v>0.51</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.32369998</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>86.05</v>
+        <v>58.75</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>strong_buy</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1.25</v>
+        <v>1.5625</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>135.5</v>
+        <v>72.9375</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0.575</v>
+        <v>59</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0.241</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>2.17</v>
+        <v>4.01</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.0368</v>
+        <v>0.084300004</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.06136</v>
+        <v>0.07914</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0.81711</v>
+        <v>0.88883</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>0.51</v>
+        <v>1.77</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.0828</v>
+        <v>0.32369998</v>
       </c>
     </row>
     <row r="10">
@@ -6711,7 +6699,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19.3</v>
+        <v>18.51</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -6725,16 +6713,16 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>29.005722</v>
+        <v>28.905075</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.33403</v>
+        <v>37.204487</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>23.04782</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0.503</v>
+        <v>22.967846</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0.5620000000000001</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>4.54</v>
@@ -6760,115 +6748,115 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10.98</v>
+        <v>26.82</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>strong_buy</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1.25</v>
+        <v>1.82353</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>17.375</v>
+        <v>31.95778</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0.5820000000000001</v>
+        <v>22</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.192</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>4.72</v>
+        <v>3.37</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.095</v>
+        <v>0.1509</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.68889</v>
+        <v>0.010570001</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.19124001</v>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>1.55</v>
+        <v>1.1195099</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="P11" s="5" t="n">
-        <v>0.2831</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>26.31</v>
+        <v>10.54</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1.82353</v>
+        <v>1.25</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>31.95778</v>
+        <v>17.375</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0.215</v>
+        <v>16</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.648</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>3.37</v>
+        <v>4.72</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.1509</v>
+        <v>0.095</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.010570001</v>
+        <v>0.68889</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>1.11968</v>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.19124001</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>1.55</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0</v>
+        <v>0.2831</v>
       </c>
     </row>
     <row r="13">
@@ -6883,7 +6871,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>22.16</v>
+        <v>21.92</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -6905,8 +6893,8 @@
       <c r="I13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>0.119</v>
+      <c r="J13" s="9" t="n">
+        <v>0.131</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.89</v>
@@ -6918,7 +6906,7 @@
         <v>0.07084</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0.93144995</v>
+        <v>0.93138003</v>
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
@@ -6941,7 +6929,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>13.02</v>
+        <v>12.94</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -6963,8 +6951,8 @@
       <c r="I14" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>0.389</v>
+      <c r="J14" s="9" t="n">
+        <v>0.397</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>2.58</v>
@@ -6976,7 +6964,7 @@
         <v>0.48116</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.46126</v>
+        <v>0.46130002</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>7.07</v>
@@ -6997,7 +6985,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5.52</v>
+        <v>5.48</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7019,8 +7007,8 @@
       <c r="I15" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="J15" s="4" t="n">
-        <v>0.674</v>
+      <c r="J15" s="9" t="n">
+        <v>0.6870000000000001</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>2.37</v>
@@ -7055,7 +7043,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14.47</v>
+        <v>14.66</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7077,8 +7065,8 @@
       <c r="I16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J16" s="4" t="n">
-        <v>0.321</v>
+      <c r="J16" s="9" t="n">
+        <v>0.304</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>4.3</v>
@@ -7113,7 +7101,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>98.88</v>
+        <v>99.47</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7137,8 +7125,8 @@
       <c r="I17" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="J17" s="4" t="n">
-        <v>0.08900000000000001</v>
+      <c r="J17" s="9" t="n">
+        <v>0.08199999999999999</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>2.64</v>
@@ -7153,7 +7141,7 @@
         <v>0.64763</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P17" s="5" t="n">
         <v>0.221</v>
@@ -7171,7 +7159,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -7193,8 +7181,8 @@
       <c r="I18" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="J18" s="4" t="n">
-        <v>1.591</v>
+      <c r="J18" s="9" t="n">
+        <v>1.558</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>2.41</v>
@@ -7206,7 +7194,7 @@
         <v>0.09754</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.95424</v>
+        <v>0.95419997</v>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
@@ -7229,7 +7217,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11.29</v>
+        <v>11.26</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7251,8 +7239,8 @@
       <c r="I19" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>0.373</v>
+      <c r="J19" s="9" t="n">
+        <v>0.377</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>2.55</v>
@@ -7287,7 +7275,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>26.62</v>
+        <v>26.39</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7309,8 +7297,8 @@
       <c r="I20" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>0.146</v>
+      <c r="J20" s="9" t="n">
+        <v>0.156</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>4.41</v>
@@ -7322,10 +7310,10 @@
         <v>0.27324</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.68561995</v>
+        <v>0.68551004</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3.76</v>
+        <v>3.79</v>
       </c>
       <c r="P20" s="5" t="n">
         <v>4.5455</v>
@@ -7343,7 +7331,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>11.6</v>
+        <v>11.92</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -7365,8 +7353,8 @@
       <c r="I21" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="J21" s="4" t="n">
-        <v>0.351</v>
+      <c r="J21" s="9" t="n">
+        <v>0.314</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>8.01</v>
@@ -7375,10 +7363,10 @@
         <v>0.105500005</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>0.12553</v>
+        <v>0.12715</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.77101</v>
+        <v>0.78096</v>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
@@ -7401,7 +7389,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6.45</v>
+        <v>6.7</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -7423,8 +7411,8 @@
       <c r="I22" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="4" t="n">
-        <v>1.067</v>
+      <c r="J22" s="9" t="n">
+        <v>0.99</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>9.81</v>
@@ -7459,7 +7447,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -7481,8 +7469,8 @@
       <c r="I23" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>0.464</v>
+      <c r="J23" s="9" t="n">
+        <v>0.413</v>
       </c>
       <c r="K23" s="7" t="n">
         <v>5.74</v>
@@ -7707,10 +7695,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>37.12</v>
+        <v>36.626</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>23.361704</v>
+        <v>23.051064</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -7722,13 +7710,13 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.165</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>10.903</v>
+        <v>10.795</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>86.09999999999999</v>
@@ -7751,7 +7739,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.37</v>
+        <v>5.474</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -7768,13 +7756,13 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.117</v>
+        <v>0.138</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>8.661</v>
+        <v>8.691000000000001</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="L4" s="7" t="n">
         <v>45</v>
@@ -7797,10 +7785,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.245</v>
+        <v>2.229</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>11.74468</v>
+        <v>11.913043</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -7814,13 +7802,13 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.265</v>
+        <v>-0.27</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>10.631</v>
+        <v>10.592</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="L5" s="7" t="n">
         <v>40</v>
@@ -7843,10 +7831,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>10.15</v>
+        <v>10.254</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>48.82895</v>
+        <v>49.32895</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.06</v>
@@ -7858,13 +7846,13 @@
         <v>0.1489</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.017</v>
+        <v>0.027</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>16.827</v>
+        <v>16.869</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="L6" s="7" t="n">
         <v>37.5</v>
@@ -7887,10 +7875,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.717</v>
+        <v>10.625</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>32.729298</v>
+        <v>32.449043</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.015</v>
@@ -7904,10 +7892,10 @@
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.16</v>
+        <v>-0.167</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>11.45</v>
+        <v>11.398</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>9.199999999999999</v>
@@ -7951,10 +7939,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.377</v>
+        <v>6.407</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.7442377</v>
+        <v>3.7437143</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -7966,13 +7954,13 @@
         <v>0.87788004</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.013</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.272</v>
+        <v>7.297</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="L10" s="7" t="n">
         <v>71.40000000000001</v>
@@ -7981,12 +7969,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Monarch Casino &amp; Resort</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7995,42 +7983,42 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1.769</v>
+        <v>6.078</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>18.209946</v>
+        <v>16.268656</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.041</v>
+        <v>0.067</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.34986</v>
+        <v>0.32698002</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.19214001</v>
+        <v>0.35709</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.033</v>
+        <v>-0.221</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>8.837</v>
+        <v>11.623</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>62.7</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Monarch Casino &amp; Resort</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -8039,31 +8027,31 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5.997</v>
+        <v>1.779</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>16.26654</v>
+        <v>18.318602</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.067</v>
+        <v>0.041</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.32698002</v>
+        <v>0.34986</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.35709</v>
+        <v>0.19214001</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>-0.231</v>
+        <v>0.039</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>11.54</v>
+        <v>8.893000000000001</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>61.1</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="13">
@@ -8083,10 +8071,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6.04</v>
+        <v>6.041</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.64762</v>
+        <v>18.83013</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.032</v>
@@ -8098,7 +8086,7 @@
         <v>1.113</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.049</v>
+        <v>-0.048</v>
       </c>
       <c r="J13" s="7" t="n">
         <v>8.461</v>
@@ -8107,7 +8095,7 @@
         <v>7.4</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>59.5</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="14">
@@ -8127,7 +8115,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.932</v>
+        <v>1.958</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8144,16 +8132,16 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.026</v>
+        <v>-0.013</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>17.19</v>
+        <v>17.223</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>10.9</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>48.6</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="15">
@@ -8173,7 +8161,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.703</v>
+        <v>0.697</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -8190,16 +8178,16 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.025</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>9.504</v>
+        <v>9.455</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>7.2</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>40</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="16">
@@ -8219,7 +8207,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.57</v>
+        <v>0.586</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -8230,26 +8218,22 @@
         <v>0.286</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.07475999999999999</v>
+        <v>0.12956999</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>-0.5564</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.303</v>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-0.284</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>22.644</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>15.5</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>25.7</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="17">
@@ -8269,7 +8253,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.08</v>
+        <v>0.083</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -8286,13 +8270,13 @@
         <v>-1.8681101</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.112</v>
+        <v>-0.08</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>12.461</v>
+        <v>12.524</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="L17" s="7" t="n">
         <v>20</v>
@@ -8333,10 +8317,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.552</v>
+        <v>5.329</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>26.142857</v>
+        <v>25.707317</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -8348,13 +8332,13 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.09</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>10.484</v>
+        <v>10.031</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="L20" s="7" t="n">
         <v>66.7</v>
@@ -8377,10 +8361,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.712</v>
+        <v>5.478</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>53.611107</v>
+        <v>51.416664</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.201</v>
@@ -8392,13 +8376,13 @@
         <v>0.10515001</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.172</v>
+        <v>-0.206</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>10.826</v>
+        <v>10.358</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>58.3</v>
@@ -8421,10 +8405,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.159</v>
+        <v>5.103</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>71.48387</v>
+        <v>70.70968000000001</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.888</v>
@@ -8436,7 +8420,7 @@
         <v>0.29505</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.148</v>
+        <v>0.135</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
@@ -8469,7 +8453,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>11.603</v>
+        <v>10.662</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -8486,13 +8470,13 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.346</v>
+        <v>-0.399</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>44.905</v>
+        <v>41.491</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>19.3</v>
+        <v>17.8</v>
       </c>
       <c r="L23" s="7" t="n">
         <v>52</v>
@@ -8515,7 +8499,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.865</v>
+        <v>18.09</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8532,13 +8516,13 @@
         <v>-0.038829997</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-0.506</v>
+        <v>-0.526</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>14.345</v>
+        <v>13.981</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="L24" s="7" t="n">
         <v>48</v>
@@ -8561,7 +8545,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.168</v>
+        <v>1.183</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -8578,10 +8562,10 @@
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.579</v>
+        <v>-0.573</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>-7.201</v>
+        <v>-7.324</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
@@ -8627,10 +8611,10 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.816666</v>
+        <v>18.766666</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0.075</v>
@@ -8642,10 +8626,10 @@
         <v>0.19236</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>6.582</v>
+        <v>6.569</v>
       </c>
       <c r="K28" s="7" t="n">
         <v>4.6</v>
@@ -8671,7 +8655,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2.403</v>
+        <v>2.388</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -8688,10 +8672,10 @@
         <v>0.07395</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.134</v>
+        <v>-0.139</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>6.769</v>
+        <v>6.753</v>
       </c>
       <c r="K29" s="7" t="n">
         <v>5.8</v>
@@ -8717,7 +8701,7 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.175</v>
+        <v>0.181</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
@@ -8736,10 +8720,10 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.281</v>
+        <v>-0.253</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>6.8</v>
+        <v>6.891</v>
       </c>
       <c r="K30" s="7" t="n">
         <v>5.5</v>
@@ -9600,7 +9584,7 @@
         <v>0.02999</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.88253</v>
+        <v>0.88254</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>2.13</v>
@@ -9678,10 +9662,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.309</v>
+        <v>0.30977</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.73225</v>
+        <v>0.73407</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>3.91</v>
@@ -9696,55 +9680,55 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Churchill Downs</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.07914</v>
+        <v>0.06136</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.88882005</v>
+        <v>0.81711</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4.01</v>
+        <v>2.17</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.084300004</v>
+        <v>0.0368</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>3346495</v>
+        <v>2415829</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Churchill Downs</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.06136</v>
+        <v>0.07914</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.81711</v>
+        <v>0.88883</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2.17</v>
+        <v>4.01</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.0368</v>
+        <v>0.084300004</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>2415829</v>
+        <v>3346495</v>
       </c>
     </row>
     <row r="10">
@@ -9777,55 +9761,55 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.68889</v>
+        <v>0.010570001</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.19124001</v>
+        <v>1.1195099</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>4.72</v>
+        <v>3.37</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.095</v>
+        <v>0.1509</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>14945381</v>
+        <v>26892014</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.010570001</v>
+        <v>0.68889</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1.11968</v>
+        <v>0.19124001</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3.37</v>
+        <v>4.72</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1509</v>
+        <v>0.095</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>26892014</v>
+        <v>14945381</v>
       </c>
     </row>
     <row r="13">
@@ -9843,7 +9827,7 @@
         <v>0.07084</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.93144995</v>
+        <v>0.93138003</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>1.89</v>
@@ -9870,7 +9854,7 @@
         <v>0.48116</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.46126</v>
+        <v>0.46130002</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2.58</v>
@@ -9978,7 +9962,7 @@
         <v>0.09754</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.95424</v>
+        <v>0.95419997</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2.41</v>
@@ -10032,7 +10016,7 @@
         <v>0.27324</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.68561995</v>
+        <v>0.68551004</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>4.41</v>
@@ -10056,10 +10040,10 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.12553</v>
+        <v>0.12715</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.77101</v>
+        <v>0.78096</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>8.01</v>
@@ -10208,955 +10192,955 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1301.47</v>
+        <v>1302.33</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>1210.03</v>
+        <v>1220.28</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>1069.91</v>
+        <v>1072.08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1290.96</v>
+        <v>1297.05</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1205.71</v>
+        <v>1218.79</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>1062.37</v>
+        <v>1070.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1285.75</v>
+        <v>1289.5</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1204.24</v>
+        <v>1209.76</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>1060.55</v>
+        <v>1072.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1278.31</v>
+        <v>1294.38</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1195.32</v>
+        <v>1211.98</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1063.15</v>
+        <v>1073.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1283.25</v>
+        <v>1295.09</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1197.51</v>
+        <v>1220.05</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1064.19</v>
+        <v>1071.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1283.92</v>
+        <v>1279.99</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1205.49</v>
+        <v>1227.31</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1062.11</v>
+        <v>1065.26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1268.81</v>
+        <v>1231.37</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1212.66</v>
+        <v>1223.35</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1055.6</v>
+        <v>1045.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1220.65</v>
+        <v>1256.73</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1208.75</v>
+        <v>1223.23</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1036.35</v>
+        <v>1063.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1245.74</v>
+        <v>1227.23</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1208.62</v>
+        <v>1231.32</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1053.52</v>
+        <v>1055.54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1216.37</v>
+        <v>1223.05</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>1216.62</v>
+        <v>1233.25</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1045.98</v>
+        <v>1051.34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1212.19</v>
+        <v>1215.2</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1218.53</v>
+        <v>1230.78</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1041.82</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1204.3</v>
+        <v>1212.84</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1216.09</v>
+        <v>1224.74</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>1029.59</v>
+        <v>1041.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1201.96</v>
+        <v>1232.32</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1210.11</v>
+        <v>1228.07</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>1032.19</v>
+        <v>1053.18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1221.18</v>
+        <v>1195.23</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1213.41</v>
+        <v>1227.04</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1043.64</v>
+        <v>1032.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1184.15</v>
+        <v>1171.15</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1212.39</v>
+        <v>1202.06</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1023.35</v>
+        <v>1015.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1160.45</v>
+        <v>1177.91</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1187.71</v>
+        <v>1215.94</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>1006.7</v>
+        <v>1017.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1167.1</v>
+        <v>1183.07</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1201.42</v>
+        <v>1222.29</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1008.52</v>
+        <v>1025.88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1172.26</v>
+        <v>1167.84</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>1207.69</v>
+        <v>1222.73</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>1016.58</v>
+        <v>1018.79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1157.04</v>
+        <v>1173.8</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1208.13</v>
+        <v>1228.94</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1009.56</v>
+        <v>1024.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1163.09</v>
+        <v>1160.51</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1214.27</v>
+        <v>1233.84</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>1015.28</v>
+        <v>1020.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1149.95</v>
+        <v>1162.3</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1219.11</v>
+        <v>1233.71</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1011.64</v>
+        <v>1013.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1151.88</v>
+        <v>1108.84</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>1218.98</v>
+        <v>1231.26</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>1003.84</v>
+        <v>996.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1098.49</v>
+        <v>1097.12</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>1216.56</v>
+        <v>1227.59</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>987.45</v>
+        <v>974.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1086.6</v>
+        <v>1115.76</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>1212.94</v>
+        <v>1233.69</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>966.12</v>
+        <v>984.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1105.18</v>
+        <v>1112.4</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>1218.97</v>
+        <v>1223.26</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>975.48</v>
+        <v>973.38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1101.83</v>
+        <v>1133.94</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>1208.66</v>
+        <v>1217.34</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>964.5599999999999</v>
+        <v>994.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1122.98</v>
+        <v>1108.83</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>1202.8</v>
+        <v>1202.13</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>985.89</v>
+        <v>975.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1098.17</v>
+        <v>1136.19</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1187.78</v>
+        <v>1225.2</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>966.64</v>
+        <v>993.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1125.24</v>
+        <v>1138.02</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>1210.57</v>
+        <v>1231.1</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>984.85</v>
+        <v>1001.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1127.13</v>
+        <v>1134.97</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>1216.41</v>
+        <v>1227.86</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>992.13</v>
+        <v>1003.04</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1124.01</v>
+        <v>1120.2</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>1213.2</v>
+        <v>1227.57</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>993.95</v>
+        <v>995.4299999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1109.42</v>
+        <v>1082.47</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>1212.92</v>
+        <v>1208.61</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>986.41</v>
+        <v>960.78</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1072.26</v>
+        <v>1073.13</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>1194.18</v>
+        <v>1209.46</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>952.0700000000001</v>
+        <v>948.4400000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1062.66</v>
+        <v>1088.27</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>1195.02</v>
+        <v>1211.41</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>939.85</v>
+        <v>950.28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1077.66</v>
+        <v>1122.65</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>1196.95</v>
+        <v>1217.51</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>941.67</v>
+        <v>976</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1111.43</v>
+        <v>1117.52</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>1202.98</v>
+        <v>1214.3</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>967.16</v>
+        <v>971.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1106.18</v>
+        <v>1117.6</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>1199.81</v>
+        <v>1223.09</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>962.48</v>
+        <v>968.92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1106.29</v>
+        <v>1073.38</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>1208.48</v>
+        <v>1210.6</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>960.14</v>
+        <v>947.13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1062.54</v>
+        <v>1088.06</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>1196.14</v>
+        <v>1219.4</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>938.55</v>
+        <v>955.26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1077.13</v>
+        <v>1092.11</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>1204.84</v>
+        <v>1229.68</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>946.61</v>
+        <v>956.58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1081.17</v>
+        <v>1121.69</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>1215</v>
+        <v>1222.85</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>947.91</v>
+        <v>958.9400000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1110.26</v>
+        <v>1108.9</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>1208.26</v>
+        <v>1216.98</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>950.25</v>
+        <v>963.14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1097.55</v>
+        <v>1103.61</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>1202.45</v>
+        <v>1217.67</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>954.41</v>
+        <v>954.48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1092.42</v>
+        <v>1099.47</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>1203.14</v>
+        <v>1206.94</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>945.83</v>
+        <v>947.91</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1088.32</v>
+        <v>1115.19</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>1192.53</v>
+        <v>1215.46</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>939.33</v>
+        <v>953.6900000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1104.04</v>
+        <v>1112.82</v>
       </c>
       <c r="C47" s="13" t="n">
-        <v>1200.95</v>
+        <v>1208.68</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>945.05</v>
+        <v>947.65</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1101.53</v>
+        <v>1080.52</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>1194.25</v>
+        <v>1192.84</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>939.0700000000001</v>
+        <v>937.9400000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1069.57</v>
+        <v>1082.04</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>1178.6</v>
+        <v>1203.29</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>929.4400000000001</v>
+        <v>940.04</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1071.15</v>
+        <v>1081.09</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>1188.92</v>
+        <v>1201.35</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>931.52</v>
+        <v>938.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1070.26</v>
+        <v>1096.15</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>1187.01</v>
+        <v>1199.85</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>929.7</v>
+        <v>942.66</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1084.99</v>
+        <v>1081.53</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>1185.52</v>
+        <v>1181.63</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>934.12</v>
+        <v>931.38</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1070.56</v>
+        <v>1083.4</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>1167.52</v>
+        <v>1174.94</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>922.9400000000001</v>
+        <v>929.28</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1072.48</v>
+        <v>1075.81</v>
       </c>
       <c r="C54" s="13" t="n">
-        <v>1160.91</v>
+        <v>1186.89</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>920.86</v>
+        <v>926.39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1064.92</v>
+        <v>1088.4</v>
       </c>
       <c r="C55" s="13" t="n">
-        <v>1172.73</v>
+        <v>1190.02</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>917.99</v>
+        <v>925.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1077.38</v>
+        <v>1080.29</v>
       </c>
       <c r="C56" s="13" t="n">
-        <v>1175.81</v>
+        <v>1173.41</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>917.21</v>
+        <v>915.36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1069.39</v>
+        <v>1093.25</v>
       </c>
       <c r="C57" s="13" t="n">
-        <v>1159.4</v>
+        <v>1170.52</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>907.0700000000001</v>
+        <v>922.45</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1082.11</v>
+        <v>1064.4</v>
       </c>
       <c r="C58" s="13" t="n">
-        <v>1156.55</v>
+        <v>1153.74</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>914.09</v>
+        <v>894.63</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1053.58</v>
+        <v>1086.87</v>
       </c>
       <c r="C59" s="13" t="n">
-        <v>1139.97</v>
+        <v>1165.85</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>886.52</v>
+        <v>932.4299999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1075.79</v>
+        <v>1098.05</v>
       </c>
       <c r="C60" s="13" t="n">
-        <v>1151.94</v>
+        <v>1161.94</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>923.98</v>
+        <v>922.45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1086.8</v>
+        <v>1083.82</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11168,7 +11152,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1086.8</v>
+        <v>1083.82</v>
       </c>
     </row>
     <row r="64">
@@ -11179,7 +11163,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-15.31%</t>
+          <t>-16.27%</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11184,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>140.6</v>
+        <v>138.2</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -6713,13 +6713,13 @@
         <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.905075</v>
+        <v>28.918455</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.204487</v>
+        <v>37.221706</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>22.967846</v>
+        <v>22.978477</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>0.5620000000000001</v>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.17</v>
+        <v>52.49</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.013297</v>
+        <v>-0.031013412</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,19 +670,19 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.231</v>
+        <v>-0.255</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>36.626</v>
+        <v>35.49</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>48.933</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23.051064</v>
+        <v>22.336172</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>14.416347</v>
+        <v>13.969246</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>10.795</v>
@@ -694,10 +694,10 @@
         <v>0.888</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0.3720000000000001</v>
+        <v>0.329</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>-0.165</v>
+        <v>-0.191</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>103.4</v>
+        <v>103.19</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.0410832</v>
+        <v>-0.20309389</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -729,10 +729,10 @@
         <v>99.95999999999999</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-0.67</v>
+        <v>-0.6709999999999999</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.09</v>
+        <v>18.053</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>29.807</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.713507999999999</v>
+        <v>9.693781</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>13.981</v>
@@ -755,10 +755,10 @@
         <v>1.177</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>-0.526</v>
+        <v>-0.527</v>
       </c>
     </row>
     <row r="4">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>21.42</v>
+        <v>21.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.0810811</v>
+        <v>-0.010037355</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>21.01</v>
+        <v>20.89</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>10.662</v>
+        <v>10.555</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>11.322</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>11.005498</v>
+        <v>10.895031</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>41.491</v>
@@ -816,10 +816,10 @@
         <v>1.682</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.4320000000000001</v>
+        <v>-0.4370000000000001</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>-0.399</v>
+        <v>-0.405</v>
       </c>
     </row>
     <row r="5">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>101.89</v>
+        <v>99.36</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.856278</v>
+        <v>-0.024781642</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,19 +851,19 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.244</v>
+        <v>-0.262</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.625</v>
+        <v>10.362</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>19.942</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>32.449043</v>
+        <v>31.644903</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>17.148088</v>
+        <v>16.723131</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>11.398</v>
@@ -875,10 +875,10 @@
         <v>1.034</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>0.198</v>
+        <v>0.168</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>-0.167</v>
+        <v>-0.188</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.49</v>
+        <v>37.51</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.0102399</v>
+        <v>0.04000904</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -913,16 +913,16 @@
         <v>-0.066</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10.254</v>
+        <v>10.258</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>39.718</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>49.32895</v>
+        <v>49.348686</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>16.000103</v>
+        <v>16.006504</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>16.869</v>
@@ -934,10 +934,10 @@
         <v>1.396</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.167</v>
+        <v>0.168</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.87</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0.473543</v>
+        <v>82.97</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>-0.022321742</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -969,19 +969,19 @@
         <v>58.94</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.057</v>
+        <v>-0.078</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.407</v>
+        <v>6.264</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>8.763999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.7437143</v>
+        <v>3.67797</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.416807</v>
+        <v>10.184217</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>7.297</v>
@@ -993,10 +993,10 @@
         <v>1.22</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0.253</v>
+        <v>0.225</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.013</v>
+        <v>-0.035</v>
       </c>
     </row>
     <row r="8">
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>87.2</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.0133643</v>
+        <v>0.6192671</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>118.46</v>
@@ -1028,19 +1028,19 @@
         <v>80.23999999999999</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.264</v>
+        <v>-0.259</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.078</v>
+        <v>6.115</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>11.12</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.268656</v>
+        <v>16.586012</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>11.744044</v>
+        <v>11.8167715</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>11.623</v>
@@ -1052,10 +1052,10 @@
         <v>0.66</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.228</v>
+        <v>-0.223</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.221</v>
+        <v>-0.216</v>
       </c>
     </row>
     <row r="9">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>0.0170213</v>
+        <v>55.98</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>-0.04714895</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1087,19 +1087,19 @@
         <v>35.09</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.148</v>
+        <v>-0.189</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>6.041</v>
+        <v>5.756</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>6.886</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>18.83013</v>
+        <v>17.942308</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>17.879261</v>
+        <v>17.036274</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>8.461</v>
@@ -1111,141 +1111,141 @@
         <v>1.453</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>0.391</v>
+        <v>0.325</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.048</v>
+        <v>-0.09300000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>18.51</v>
+        <v>26.8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.0409326</v>
+        <v>-0.09322998</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>32.22</v>
+        <v>31.58</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>15.725</v>
+        <v>17.86</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.426</v>
+        <v>-0.151</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.478</v>
+        <v>5.469</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>5.256</v>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>51.416664</v>
+        <v>30.375</v>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L10" s="7" t="n">
-        <v>22.463898</v>
+        <v>26.115984</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>10.358</v>
+        <v>8.691000000000001</v>
       </c>
       <c r="N10" s="7" t="n">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>2.002</v>
+        <v>1.977</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.175</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>-0.206</v>
+        <v>-0.029</v>
+      </c>
+      <c r="Q10" s="9" t="n">
+        <v>0.137</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>26.82</v>
+        <v>10.56</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.0193843</v>
+        <v>0.18975766</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>31.58</v>
+        <v>14.38</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>17.86</v>
+        <v>5.59</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.151</v>
+        <v>-0.266</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.474</v>
+        <v>5.34</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>30.375</v>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>4.922</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>25.142859</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>26.14035</v>
+        <v>12.174174</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>8.691000000000001</v>
+        <v>10.031</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>1.977</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="Q11" s="9" t="n">
-        <v>0.138</v>
+        <v>1.1</v>
+      </c>
+      <c r="P11" s="9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>-0.08900000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1254,46 +1254,46 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.54</v>
+        <v>17.82</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.0400728</v>
+        <v>-0.037006993</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>14.38</v>
+        <v>32.22</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>5.59</v>
+        <v>15.725</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.267</v>
+        <v>-0.447</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.329</v>
+        <v>5.275</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>4.922</v>
+        <v>5.256</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>25.707317</v>
+        <v>49.51389</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>12.151116</v>
+        <v>21.632576</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>10.031</v>
+        <v>10.358</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P12" s="9" t="n">
-        <v>0.552</v>
+        <v>2.002</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>-0.205</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.09</v>
+        <v>-0.236</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.92</v>
+        <v>21.62</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.0108303</v>
+        <v>-0.013686097</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.032</v>
+        <v>-0.045</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.103</v>
+        <v>5.033</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>70.70968000000001</v>
+        <v>69.741936</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>29.291891</v>
+        <v>28.979681</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>1.009</v>
+        <v>0.982</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>0.135</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="14">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>12.94</v>
+        <v>12.86</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.614446</v>
+        <v>-0.61823744</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>18.57</v>
@@ -1390,10 +1390,10 @@
         <v>12.53</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-0.303</v>
+        <v>-0.307</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.388</v>
+        <v>2.373</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>5.956</v>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="L14" s="7" t="n">
-        <v>12.008834</v>
+        <v>11.934591</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>6.753</v>
@@ -1416,10 +1416,10 @@
         <v>1.082</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.032</v>
+        <v>-0.038</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.139</v>
+        <v>-0.145</v>
       </c>
     </row>
     <row r="15">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-0.724637</v>
+        <v>5.5</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.3649631400000001</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>10.15</v>
@@ -1451,19 +1451,19 @@
         <v>4.55</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.46</v>
+        <v>-0.458</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.229</v>
+        <v>2.237</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>12.774</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>11.913043</v>
+        <v>11.956522</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>6.88797</v>
+        <v>6.913109</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>10.592</v>
@@ -1475,10 +1475,10 @@
         <v>0.603</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.27</v>
+        <v>-0.268</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>0.0131306</v>
+        <v>14.51</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-0.01057297</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>20.61</v>
@@ -1510,10 +1510,10 @@
         <v>11.65</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.289</v>
+        <v>-0.296</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.958</v>
+        <v>1.937</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>12.438</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>8.471393000000001</v>
+        <v>8.381824999999999</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>17.223</v>
@@ -1536,10 +1536,10 @@
         <v>1.364</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.156</v>
+        <v>-0.164</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.013</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="17">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>99.47</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>0.596687</v>
+        <v>97.54000000000001</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>-0.019402838</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>113.88</v>
@@ -1571,19 +1571,19 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.127</v>
+        <v>-0.143</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.779</v>
+        <v>1.745</v>
       </c>
       <c r="J17" s="6" t="n">
         <v>1.696</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>18.318602</v>
+        <v>17.96317</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>16.731707</v>
+        <v>16.407064</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>8.893000000000001</v>
@@ -1595,10 +1595,10 @@
         <v>1.376</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>0.242</v>
+        <v>0.218</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>0.039</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="18">
@@ -1618,22 +1618,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.0132158</v>
+        <v>4.42</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>-0.0391304</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.73</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.665</v>
+        <v>-0.6779999999999999</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.183</v>
+        <v>1.137</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>0.883</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>4.6464643</v>
+        <v>4.4646463</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>-7.324</v>
@@ -1658,10 +1658,10 @@
         <v>1.993</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.5670000000000001</v>
+        <v>-0.584</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.573</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="19">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.26</v>
+        <v>11.06</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.26572</v>
+        <v>-0.017317997</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>13.31</v>
@@ -1693,19 +1693,19 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.169</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.919</v>
+        <v>0.903</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>1.242</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>18.766666</v>
+        <v>18.441666</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>12.159433</v>
+        <v>11.948856</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>6.569</v>
@@ -1717,10 +1717,10 @@
         <v>1.07</v>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0.102</v>
+        <v>0.083</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.027</v>
       </c>
     </row>
     <row r="20">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.39</v>
+        <v>26.38</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.864017</v>
+        <v>-0.03789401</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>32.74</v>
@@ -1755,7 +1755,7 @@
         <v>-0.194</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.697</v>
+        <v>0.696</v>
       </c>
       <c r="J20" s="6" t="n">
         <v>1.154</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>21.809916</v>
+        <v>21.801651</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>9.455</v>
@@ -1778,7 +1778,7 @@
         <v>1.412</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>-0.025</v>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>0.0275862</v>
+        <v>11.52</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-0.033976488</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>20.74</v>
@@ -1813,10 +1813,10 @@
         <v>8.455</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.425</v>
+        <v>-0.445</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.586</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="J21" s="6" t="n">
         <v>7.795</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>-14.716049</v>
+        <v>-14.21605</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>22.644</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.145</v>
+        <v>-0.174</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.284</v>
+        <v>-0.308</v>
       </c>
     </row>
     <row r="22">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.7</v>
+        <v>6.83</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.0387597</v>
+        <v>0.020149288</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>9.949999999999999</v>
@@ -1876,10 +1876,10 @@
         <v>6.1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.327</v>
+        <v>-0.314</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.181</v>
+        <v>0.185</v>
       </c>
       <c r="J22" s="6" t="n">
         <v>0.512</v>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>8.943350000000001</v>
+        <v>9.123552</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>6.891</v>
@@ -1902,10 +1902,10 @@
         <v>1.206</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.253</v>
+        <v>-0.238</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.253</v>
+        <v>-0.238</v>
       </c>
     </row>
     <row r="23">
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0.036036</v>
+        <v>2.27</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>-0.0130869</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>4.95</v>
@@ -1937,10 +1937,10 @@
         <v>2.02</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-0.535</v>
+        <v>-0.541</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>0.577</v>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="L23" s="7" t="n">
-        <v>-5.609756</v>
+        <v>-5.5363417</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>12.524</v>
@@ -1963,10 +1963,10 @@
         <v>1.327</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.45</v>
+        <v>-0.457</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.08</v>
+        <v>-0.092</v>
       </c>
     </row>
     <row r="24">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.17</v>
+        <v>52.49</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.013297</v>
+        <v>-0.031013412</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.191</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.3720000000000001</v>
+        <v>0.329</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>52.8</v>
+        <v>52.2</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.048</v>
+        <v>-0.077</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.058</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.231</v>
+        <v>-0.255</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
@@ -2199,28 +2199,28 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>103.4</v>
+        <v>103.19</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.0410832</v>
+        <v>-0.20309389</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0.526</v>
+        <v>-0.527</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-58.6</v>
+        <v>-59.4</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.281</v>
+        <v>-0.283</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.55</v>
+        <v>-0.551</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.67</v>
+        <v>-0.6709999999999999</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>1.177</v>
@@ -2246,28 +2246,28 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>21.42</v>
+        <v>21.2</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.0810811</v>
+        <v>-0.010037355</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.399</v>
+        <v>-0.405</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.4320000000000001</v>
+        <v>-0.4370000000000001</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-36.9</v>
+        <v>-37.5</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.211</v>
+        <v>-0.219</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.4</v>
+        <v>-0.406</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>1.682</v>
@@ -2293,28 +2293,28 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>101.89</v>
+        <v>99.36</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-0.856278</v>
+        <v>-0.024781642</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.167</v>
+        <v>-0.188</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.198</v>
+        <v>0.168</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>34</v>
+        <v>33.4</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.073</v>
+        <v>-0.096</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.109</v>
+        <v>-0.131</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.244</v>
+        <v>-0.262</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>1.034</v>
@@ -2340,16 +2340,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.49</v>
+        <v>37.51</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.0102399</v>
+        <v>0.04000904</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.167</v>
+        <v>0.168</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>12</v>
@@ -2358,7 +2358,7 @@
         <v>0.058</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.066</v>
+        <v>0.067</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>-0.066</v>
@@ -2387,28 +2387,28 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.87</v>
+        <v>82.97</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.473543</v>
+        <v>-0.022321742</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0.013</v>
+        <v>-0.035</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.253</v>
+        <v>0.225</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.011</v>
+        <v>-0.011</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.025</v>
+        <v>0.002</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.057</v>
+        <v>-0.078</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>1.22</v>
@@ -2434,28 +2434,28 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>87.2</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.0133643</v>
+        <v>0.6192671</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.221</v>
+        <v>-0.216</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.228</v>
+        <v>-0.223</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>-2.9</v>
+        <v>-3.2</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.08</v>
+        <v>-0.07400000000000001</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.136</v>
+        <v>-0.131</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.264</v>
+        <v>-0.259</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>0.66</v>
@@ -2481,28 +2481,28 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>58.75</v>
+        <v>55.98</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.0170213</v>
+        <v>-0.04714895</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.048</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.391</v>
+        <v>0.325</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>38.6</v>
+        <v>38.2</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.047</v>
+        <v>-0.092</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.046</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.148</v>
+        <v>-0.189</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>1.453</v>
@@ -2514,106 +2514,106 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>18.51</v>
+        <v>26.8</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.0409326</v>
+        <v>-0.09322998</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.206</v>
+        <v>0.137</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.175</v>
+        <v>-0.029</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-29.3</v>
+        <v>-21.9</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-0.245</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.426</v>
+        <v>-0.151</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>2.002</v>
+        <v>1.977</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>2485880</v>
+        <v>6358500</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>26.82</v>
+        <v>10.56</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.0193843</v>
+        <v>0.18975766</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.138</v>
+        <v>-0.08900000000000001</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.028</v>
+        <v>0.555</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-22.3</v>
+        <v>26</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.144</v>
+        <v>0.051</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.06</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.151</v>
+        <v>-0.266</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>1.977</v>
+        <v>1.1</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>6358500</v>
+        <v>1926430</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2622,34 +2622,34 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.54</v>
+        <v>17.82</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.0400728</v>
+        <v>-0.037006993</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-0.09</v>
+        <v>-0.236</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.552</v>
+        <v>-0.205</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>26.3</v>
+        <v>-29.6</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.049</v>
+        <v>-0.03</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.061</v>
+        <v>-0.273</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.267</v>
+        <v>-0.447</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>1.1</v>
+        <v>2.002</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>1926430</v>
+        <v>2485880</v>
       </c>
     </row>
     <row r="13">
@@ -2669,28 +2669,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.92</v>
+        <v>21.62</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-0.0108303</v>
+        <v>-0.013686097</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.135</v>
+        <v>0.12</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.009</v>
+        <v>0.982</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>50.7</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.165</v>
+        <v>0.149</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.199</v>
+        <v>0.182</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.032</v>
+        <v>-0.045</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2716,28 +2716,28 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>12.94</v>
+        <v>12.86</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.614446</v>
+        <v>-0.61823744</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.139</v>
+        <v>-0.145</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.032</v>
+        <v>-0.038</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.061</v>
+        <v>-0.067</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.162</v>
+        <v>-0.168</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-0.303</v>
+        <v>-0.307</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>1.082</v>
@@ -2763,28 +2763,28 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-0.724637</v>
+        <v>0.3649631400000001</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.27</v>
+        <v>-0.268</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.08900000000000001</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.302</v>
+        <v>-0.3</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.46</v>
+        <v>-0.458</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>0.603</v>
@@ -2810,28 +2810,28 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.66</v>
+        <v>14.51</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.0131306</v>
+        <v>-0.01057297</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.013</v>
+        <v>-0.023</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.156</v>
+        <v>-0.164</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>-19.3</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.064</v>
+        <v>0.053</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.098</v>
+        <v>-0.107</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.289</v>
+        <v>-0.296</v>
       </c>
       <c r="L16" s="8" t="n">
         <v>1.364</v>
@@ -2857,28 +2857,28 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>99.47</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.596687</v>
+        <v>-0.019402838</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.039</v>
+        <v>0.019</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.242</v>
+        <v>0.218</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.048</v>
+        <v>0.028</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.035</v>
+        <v>0.015</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.127</v>
+        <v>-0.143</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.376</v>
@@ -2904,28 +2904,28 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.6</v>
+        <v>4.42</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.0132158</v>
+        <v>-0.0391304</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.573</v>
+        <v>-0.59</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>-0.584</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>-34.5</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>-0.386</v>
+      </c>
+      <c r="J18" s="5" t="n">
         <v>-0.5670000000000001</v>
       </c>
-      <c r="H18" s="7" t="n">
-        <v>-33.5</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>-0.361</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>-0.55</v>
-      </c>
       <c r="K18" s="5" t="n">
-        <v>-0.665</v>
+        <v>-0.6779999999999999</v>
       </c>
       <c r="L18" s="8" t="n">
         <v>1.993</v>
@@ -2951,28 +2951,28 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.26</v>
+        <v>11.06</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-0.26572</v>
+        <v>-0.017317997</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.027</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.102</v>
+        <v>0.083</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>-1.6</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.021</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.012</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.169</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.07</v>
@@ -2998,16 +2998,16 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.39</v>
+        <v>26.38</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.864017</v>
+        <v>-0.03789401</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>-0.025</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>5.4</v>
@@ -3016,7 +3016,7 @@
         <v>-0.05599999999999999</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.019</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>-0.194</v>
@@ -3045,28 +3045,28 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.92</v>
+        <v>11.52</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.0275862</v>
+        <v>-0.033976488</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.284</v>
+        <v>-0.308</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.145</v>
+        <v>-0.174</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>39.6</v>
+        <v>38.9</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.179</v>
+        <v>-0.207</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.103</v>
+        <v>-0.133</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.425</v>
+        <v>-0.445</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -3094,28 +3094,28 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.7</v>
+        <v>6.83</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.0387597</v>
+        <v>0.020149288</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.253</v>
+        <v>-0.238</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.253</v>
+        <v>-0.238</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.2</v>
+        <v>-0.185</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.218</v>
+        <v>-0.202</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.327</v>
+        <v>-0.314</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.206</v>
@@ -3141,28 +3141,28 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.036036</v>
+        <v>-0.0130869</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-0.08</v>
+        <v>-0.092</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.45</v>
+        <v>-0.457</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-52.5</v>
+        <v>-52.6</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.048</v>
+        <v>-0.06</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-0.254</v>
+        <v>-0.264</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>-0.535</v>
+        <v>-0.541</v>
       </c>
       <c r="L23" s="8" t="n">
         <v>1.327</v>
@@ -3342,16 +3342,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.17</v>
+        <v>52.49</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>36.626</v>
+        <v>35.49</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>23.051064</v>
+        <v>22.336172</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>14.416347</v>
+        <v>13.969246</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>10.795</v>
@@ -3363,10 +3363,10 @@
         <v>3.759</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.99236</v>
+        <v>22.279287</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.8137207</v>
+        <v>2.7264578</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>103.4</v>
+        <v>103.19</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.09</v>
+        <v>18.053</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.713507999999999</v>
+        <v>9.693781</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>13.981</v>
@@ -3418,13 +3418,13 @@
         <v>1.819</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.004653</v>
+        <v>2.0005815</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.104198</v>
+        <v>1.1019554</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>-1.68</v>
+        <v>-1.75</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>10.64497</v>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>21.42</v>
+        <v>21.2</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>10.662</v>
+        <v>10.555</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>11.005498</v>
+        <v>10.895031</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>41.491</v>
@@ -3473,10 +3473,10 @@
         <v>1.87</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>16.786833</v>
+        <v>16.618338</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.7610444</v>
+        <v>1.7433681</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3505,16 +3505,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>101.89</v>
+        <v>99.36</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.625</v>
+        <v>10.362</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>32.449043</v>
+        <v>31.644903</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>17.148088</v>
+        <v>16.723131</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>11.398</v>
@@ -3526,10 +3526,10 @@
         <v>2.794</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-37.905506</v>
+        <v>-36.966145</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.4885875</v>
+        <v>1.4516978</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3558,16 +3558,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.49</v>
+        <v>37.51</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.254</v>
+        <v>10.258</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>49.32895</v>
+        <v>49.348686</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>16.000103</v>
+        <v>16.006504</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>16.869</v>
@@ -3579,10 +3579,10 @@
         <v>2.265</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.9853303</v>
+        <v>3.986925</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.58466995</v>
+        <v>0.58490384</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3611,16 +3611,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.87</v>
+        <v>82.97</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.407</v>
+        <v>6.264</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.7437143</v>
+        <v>3.67797</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.416807</v>
+        <v>10.184217</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>7.297</v>
@@ -3632,13 +3632,13 @@
         <v>2.142</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.484703</v>
+        <v>2.4292238</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5657481</v>
+        <v>1.5307875</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>22.67</v>
+        <v>22.56</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>8.147410000000001</v>
@@ -3664,16 +3664,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>87.2</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.078</v>
+        <v>6.115</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>16.268656</v>
+        <v>16.586012</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>11.744044</v>
+        <v>11.8167715</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>11.623</v>
@@ -3685,13 +3685,13 @@
         <v>3.801</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>6.010891</v>
+        <v>6.048115</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.0771468</v>
+        <v>2.09001</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>5.36</v>
+        <v>5.29</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>7.42504</v>
@@ -3717,16 +3717,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>58.75</v>
+        <v>55.98</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>6.041</v>
+        <v>5.756</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>18.83013</v>
+        <v>17.942308</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>17.879261</v>
+        <v>17.036274</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>8.461</v>
@@ -3738,10 +3738,10 @@
         <v>3.423</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>16.447369</v>
+        <v>15.671892</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>3.0032966</v>
+        <v>2.8616943</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>3.12</v>
@@ -3756,120 +3756,120 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>18.51</v>
+        <v>26.8</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.478</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>51.416664</v>
+        <v>5.469</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>22.463898</v>
+        <v>26.115984</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>10.358</v>
+        <v>8.691000000000001</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>4.075</v>
+        <v>2.645</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>4.892276</v>
+        <v>1.5494709</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>4.2466774</v>
+        <v>0.47615117</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.36</v>
+        <v>-2.42</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.8239888</v>
+        <v>1.026</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>3.7835155</v>
+        <v>17.293</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>26.82</v>
+        <v>10.56</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.474</v>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>5.34</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>25.142859</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>26.14035</v>
+        <v>12.174174</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>8.691000000000001</v>
+        <v>10.031</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>2.645</v>
+        <v>2.101</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>1.5509166</v>
+        <v>7.1690426</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.4765954</v>
+        <v>2.2790158</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-2.47</v>
+        <v>0.42</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.026</v>
+        <v>0.86741</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>17.293</v>
+        <v>1.473</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3878,40 +3878,40 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10.54</v>
+        <v>17.82</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.329</v>
+        <v>5.275</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>25.707317</v>
+        <v>49.51389</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>12.151116</v>
+        <v>21.632576</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10.031</v>
+        <v>10.358</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>2.101</v>
+        <v>4.075</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>7.1554646</v>
+        <v>4.711227</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>2.2746992</v>
+        <v>4.0895205</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.86741</v>
+        <v>0.8239888</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>1.473</v>
+        <v>3.7835155</v>
       </c>
     </row>
     <row r="13">
@@ -3931,16 +3931,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.92</v>
+        <v>21.62</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5.103</v>
+        <v>5.033</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>70.70968000000001</v>
+        <v>69.741936</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>29.291891</v>
+        <v>28.979681</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -3958,16 +3958,16 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>14.881194</v>
+        <v>14.677529</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.4979825</v>
+        <v>4.436423</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.7483300000000001</v>
+        <v>0.74604</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>1.473</v>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>12.94</v>
+        <v>12.86</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.388</v>
+        <v>2.373</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>12.008834</v>
+        <v>11.934591</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>6.753</v>
@@ -4013,10 +4013,10 @@
         <v>2.372</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>2.7631857</v>
+        <v>2.7461028</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.9509358999999999</v>
+        <v>0.94505686</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>-0.01</v>
@@ -4045,16 +4045,16 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.229</v>
+        <v>2.237</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>11.913043</v>
+        <v>11.956522</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.88797</v>
+        <v>6.913109</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>10.592</v>
@@ -4066,10 +4066,10 @@
         <v>2.474</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1.71733</v>
+        <v>-1.7235976</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.43174338</v>
+        <v>0.43331912</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.46</v>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.66</v>
+        <v>14.51</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.958</v>
+        <v>1.937</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>8.471393000000001</v>
+        <v>8.381824999999999</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>17.223</v>
@@ -4121,10 +4121,10 @@
         <v>1.787</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>1.0091553</v>
+        <v>0.99848557</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.281251</v>
+        <v>0.27827737</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-5.83</v>
@@ -4153,16 +4153,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>99.47</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.779</v>
+        <v>1.745</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>18.318602</v>
+        <v>17.96317</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>16.731707</v>
+        <v>16.407064</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>8.893000000000001</v>
@@ -4174,10 +4174,10 @@
         <v>3.111</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>3.2965467</v>
+        <v>3.2325845</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3.2637146</v>
+        <v>3.2003894</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>5.43</v>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.6</v>
+        <v>4.42</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1.183</v>
+        <v>1.137</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4.6464643</v>
+        <v>4.4646463</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>-7.324</v>
@@ -4231,13 +4231,13 @@
         <v>1.319</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>1.5640938</v>
+        <v>1.5028902</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>1.7675432</v>
+        <v>1.6983784</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>0.99</v>
@@ -4263,16 +4263,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.26</v>
+        <v>11.06</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.919</v>
+        <v>0.903</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>18.766666</v>
+        <v>18.441666</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>12.159433</v>
+        <v>11.948856</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>6.569</v>
@@ -4284,10 +4284,10 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>3.4360697</v>
+        <v>3.3765638</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.6901145</v>
+        <v>0.6781631</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0.6</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.39</v>
+        <v>26.38</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.697</v>
+        <v>0.696</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>21.809916</v>
+        <v>21.801651</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>9.455</v>
@@ -4339,10 +4339,10 @@
         <v>1.818</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.6417818</v>
+        <v>1.6411597</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>1.0972635</v>
+        <v>1.0968477</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.23</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.92</v>
+        <v>11.52</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.586</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-14.716049</v>
+        <v>-14.21605</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>22.644</v>
@@ -4394,10 +4394,10 @@
         <v>2.934</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.5815202</v>
+        <v>0.56176215</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.22058024</v>
+        <v>0.2130857</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>-12.45</v>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.7</v>
+        <v>6.83</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.181</v>
+        <v>0.185</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>8.943350000000001</v>
+        <v>9.123552</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>6.891</v>
@@ -4449,10 +4449,10 @@
         <v>1.684</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-11.111111</v>
+        <v>-11.334992</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.5961826</v>
+        <v>0.60819525</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>-0.58</v>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-5.609756</v>
+        <v>-5.5363417</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>12.524</v>
@@ -4504,13 +4504,13 @@
         <v>1.909</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>32.857143</v>
+        <v>32.427143</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.27522376</v>
+        <v>0.27162194</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>-1.16</v>
+        <v>-1.12</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-0.41</v>
@@ -5192,130 +5192,132 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Online &amp; iGaming</t>
+          <t>Integrated Resorts</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1.29</v>
+        <v>11.486</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.201</v>
+        <v>0.042</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.26816</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.15614</v>
+        <v>0.1893</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.07777000000000001</v>
+        <v>-0.043709997</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.39339</v>
+        <v>0.30427998</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.10515001</v>
+        <v>-0.10840999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.04121</v>
+        <v>0.04044</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.507</v>
+        <v>3.495</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.341</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.063</v>
+        <v>25.622</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.365</v>
+        <v>0.887</v>
       </c>
       <c r="P10" s="7" t="n">
-        <v>6.424</v>
+        <v>695.117</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>1.167</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Integrated Resorts</t>
+          <t>Online &amp; iGaming</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>11.486</v>
+        <v>2.343</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.042</v>
+        <v>0.178</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.5</v>
+        <v>0.51058</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.1893</v>
+        <v>0.23518999</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-0.043709997</v>
+        <v>0.09804</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.30427998</v>
+        <v>0.20945999</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.10840999</v>
+        <v>0.32813</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.04044</v>
+        <v>0.23642</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>3.495</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.491</v>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>25.622</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.887</v>
+        <v>0.478</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>695.117</v>
+        <v>9.69</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -5324,48 +5326,46 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2.343</v>
+        <v>1.29</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.178</v>
+        <v>0.201</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.51058</v>
+        <v>0.26816</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.23518999</v>
+        <v>0.15614</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.09804</v>
+        <v>0.07777000000000001</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.20945999</v>
+        <v>0.39339</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.32813</v>
+        <v>0.10515001</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.23642</v>
+        <v>0.04121</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.507</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0.341</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.478</v>
+        <v>0.365</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>9.69</v>
+        <v>6.424</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>1.75</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="13">
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>54.17</v>
+        <v>52.49</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>58</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>0.29</v>
+        <v>0.331</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>2.49</v>
@@ -6301,7 +6301,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>103.4</v>
+        <v>103.19</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>27</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>212.74074</v>
+        <v>207.44444</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>354</v>
@@ -6324,7 +6324,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>1.057</v>
+        <v>1.01</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>2.02</v>
@@ -6333,10 +6333,10 @@
         <v>0.0583</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>0.18823999</v>
+        <v>0.1886</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>0.91170996</v>
+        <v>0.91332</v>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>21.42</v>
+        <v>21.2</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.6890000000000001</v>
+        <v>0.706</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>2.13</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>101.89</v>
+        <v>99.36</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.392</v>
+        <v>0.427</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.38</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37.49</v>
+        <v>37.51</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.138</v>
+        <v>0.137</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.85</v>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>84.87</v>
+        <v>82.97</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>84</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.113</v>
+        <v>0.139</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.91</v>
@@ -6569,7 +6569,7 @@
         <v>0.73407</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="P7" s="5" t="n">
         <v>0.0319</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>87.2</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>110</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.5539999999999999</v>
+        <v>0.544</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>2.17</v>
@@ -6625,7 +6625,7 @@
         <v>0.81711</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="P8" s="5" t="n">
         <v>0.0828</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>58.75</v>
+        <v>55.98</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>59</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.241</v>
+        <v>0.303</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>4.01</v>
@@ -6690,51 +6690,51 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>18.51</v>
+        <v>26.8</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>strong_buy</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1.33333</v>
+        <v>1.82353</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28.918455</v>
+        <v>31.95778</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>37.221706</v>
+        <v>41</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>22.978477</v>
+        <v>22</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.192</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>4.54</v>
+        <v>3.37</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.1046</v>
+        <v>0.1509</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>0.01337</v>
+        <v>0.010570001</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0.91643</v>
+        <v>1.1195099</v>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
@@ -6748,74 +6748,72 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>26.82</v>
+        <v>10.56</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1.82353</v>
+        <v>1.25</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>31.95778</v>
+        <v>17.375</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.192</v>
+        <v>0.645</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>3.37</v>
+        <v>4.72</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.1509</v>
+        <v>0.095</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.010570001</v>
+        <v>0.68889</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>1.1195099</v>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.19124001</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>1.61</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>0</v>
+        <v>0.2831</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>10.54</v>
+        <v>17.82</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -6823,40 +6821,42 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1.25</v>
+        <v>1.33333</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>17.375</v>
+        <v>28.815092</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>20</v>
+        <v>37.088665</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>16</v>
+        <v>22.896345</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.648</v>
+        <v>0.617</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>4.72</v>
+        <v>4.54</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.095</v>
+        <v>0.1046</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.68889</v>
+        <v>0.01337</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0.19124001</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>1.55</v>
+        <v>0.91643</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.2831</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>21.92</v>
+        <v>21.62</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -6882,10 +6882,10 @@
         <v>1.4</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>24.8</v>
+        <v>24.90909</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>30</v>
@@ -6894,7 +6894,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.131</v>
+        <v>0.152</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.89</v>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>12.94</v>
+        <v>12.86</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>15</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.397</v>
+        <v>0.406</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>2.58</v>
@@ -6967,7 +6967,7 @@
         <v>0.46130002</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>7.07</v>
+        <v>7.11</v>
       </c>
       <c r="P14" s="5" t="n">
         <v>8.8889</v>
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>6</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>2.37</v>
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14.66</v>
+        <v>14.51</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.304</v>
+        <v>0.317</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>4.3</v>
@@ -7101,7 +7101,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>99.47</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>93</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.08199999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>2.64</v>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4.6</v>
+        <v>4.42</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1.558</v>
+        <v>1.662</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>2.41</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11.26</v>
+        <v>11.06</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>14</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.377</v>
+        <v>0.401</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>2.55</v>
@@ -7275,15 +7275,17 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>26.39</v>
+        <v>26.38</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>hold</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>3</v>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F20" s="10" t="n">
         <v>4</v>
@@ -7331,7 +7333,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>11.92</v>
+        <v>11.52</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -7354,7 +7356,7 @@
         <v>11</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.314</v>
+        <v>0.36</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>8.01</v>
@@ -7389,7 +7391,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6.7</v>
+        <v>6.83</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -7412,7 +7414,7 @@
         <v>10</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.99</v>
+        <v>0.9520000000000001</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>9.81</v>
@@ -7447,7 +7449,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -7470,7 +7472,7 @@
         <v>2.5</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.413</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="K23" s="7" t="n">
         <v>5.74</v>
@@ -7695,10 +7697,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>36.626</v>
+        <v>35.49</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>23.051064</v>
+        <v>22.336172</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -7710,7 +7712,7 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.191</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>10.795</v>
@@ -7719,7 +7721,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>86.09999999999999</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
@@ -7739,7 +7741,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.474</v>
+        <v>5.469</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -7756,7 +7758,7 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.138</v>
+        <v>0.137</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>8.691000000000001</v>
@@ -7771,12 +7773,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MLCO</t>
+          <t>WYNN</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Melco Resorts</t>
+          <t>Wynn Resorts</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7785,16 +7787,16 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.229</v>
+        <v>10.362</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>11.913043</v>
+        <v>31.644903</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.23358</v>
+        <v>0.24510999</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -7802,27 +7804,27 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.27</v>
+        <v>-0.188</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>10.592</v>
+        <v>11.398</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>40</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MGM</t>
+          <t>MLCO</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Melco Resorts</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -7831,42 +7833,44 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>10.254</v>
+        <v>2.237</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>49.32895</v>
+        <v>11.956522</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.06</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.13426</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>0.1489</v>
+        <v>0.23358</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.027</v>
+        <v>-0.268</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>16.869</v>
+        <v>10.592</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>11.7</v>
+        <v>8.4</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>MGM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Wynn Resorts</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7875,33 +7879,31 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.625</v>
+        <v>10.258</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>32.449043</v>
+        <v>49.348686</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.015</v>
+        <v>0.06</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.24510999</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.13426</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.1489</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.167</v>
+        <v>0.028</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>11.398</v>
+        <v>16.869</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>36.7</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="9">
@@ -7939,10 +7941,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.407</v>
+        <v>6.264</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.7437143</v>
+        <v>3.67797</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -7954,7 +7956,7 @@
         <v>0.87788004</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-0.013</v>
+        <v>-0.035</v>
       </c>
       <c r="J10" s="7" t="n">
         <v>7.297</v>
@@ -7963,7 +7965,7 @@
         <v>6.1</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>71.40000000000001</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -7983,10 +7985,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6.078</v>
+        <v>6.115</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>16.268656</v>
+        <v>16.586012</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.067</v>
@@ -7998,7 +8000,7 @@
         <v>0.35709</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>-0.221</v>
+        <v>-0.216</v>
       </c>
       <c r="J11" s="7" t="n">
         <v>11.623</v>
@@ -8013,12 +8015,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Monarch Casino &amp; Resort</t>
+          <t>Red Rock Resorts</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -8027,42 +8029,42 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1.779</v>
+        <v>5.756</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>18.318602</v>
+        <v>17.942308</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.041</v>
+        <v>0.032</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.34986</v>
+        <v>0.4046</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.19214001</v>
+        <v>1.113</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.039</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>8.893000000000001</v>
+        <v>8.461</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>62.7</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RRR</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Red Rock Resorts</t>
+          <t>Monarch Casino &amp; Resort</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -8071,28 +8073,28 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6.041</v>
+        <v>1.745</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18.83013</v>
+        <v>17.96317</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.032</v>
+        <v>0.041</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.4046</v>
+        <v>0.34986</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>1.113</v>
+        <v>0.19214001</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.048</v>
+        <v>0.019</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>8.461</v>
+        <v>8.893000000000001</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L13" s="7" t="n">
         <v>57.1</v>
@@ -8115,7 +8117,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.958</v>
+        <v>1.937</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8132,7 +8134,7 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.013</v>
+        <v>-0.023</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>17.223</v>
@@ -8161,7 +8163,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.697</v>
+        <v>0.696</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -8187,7 +8189,7 @@
         <v>7.2</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>34.3</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="16">
@@ -8207,7 +8209,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.586</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -8224,7 +8226,7 @@
         <v>-0.5564</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.284</v>
+        <v>-0.308</v>
       </c>
       <c r="J16" s="7" t="n">
         <v>22.644</v>
@@ -8253,7 +8255,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -8270,7 +8272,7 @@
         <v>-1.8681101</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.08</v>
+        <v>-0.092</v>
       </c>
       <c r="J17" s="7" t="n">
         <v>12.524</v>
@@ -8279,7 +8281,7 @@
         <v>9</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>20</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="19">
@@ -8317,10 +8319,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.329</v>
+        <v>5.34</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.707317</v>
+        <v>25.142859</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -8332,7 +8334,7 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.09</v>
+        <v>-0.08900000000000001</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>10.031</v>
@@ -8341,18 +8343,18 @@
         <v>7.8</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>66.7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>RSI</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Rush Street Interactive</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -8361,42 +8363,46 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.478</v>
+        <v>5.033</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>51.416664</v>
+        <v>69.741936</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.201</v>
+        <v>0.888</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.39339</v>
+        <v>0.11229999</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.10515001</v>
+        <v>0.29505</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.206</v>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>10.358</v>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>9</v>
+        <v>0.12</v>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>58.3</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RSI</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Rush Street Interactive</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -8405,35 +8411,31 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.103</v>
+        <v>5.275</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>70.70968000000001</v>
+        <v>49.51389</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.888</v>
+        <v>0.201</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.11229999</v>
+        <v>0.39339</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.29505</v>
+        <v>0.10515001</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-0.236</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>10.358</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>9</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>56.7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
@@ -8453,7 +8455,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>10.662</v>
+        <v>10.555</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -8470,7 +8472,7 @@
         <v>0.00452</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.399</v>
+        <v>-0.405</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>41.491</v>
@@ -8499,7 +8501,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.09</v>
+        <v>18.053</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8516,7 +8518,7 @@
         <v>-0.038829997</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-0.526</v>
+        <v>-0.527</v>
       </c>
       <c r="J24" s="7" t="n">
         <v>13.981</v>
@@ -8545,7 +8547,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.183</v>
+        <v>1.137</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -8562,7 +8564,7 @@
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.573</v>
+        <v>-0.59</v>
       </c>
       <c r="J25" s="7" t="n">
         <v>-7.324</v>
@@ -8611,10 +8613,10 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.919</v>
+        <v>0.903</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.766666</v>
+        <v>18.441666</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0.075</v>
@@ -8626,7 +8628,7 @@
         <v>0.19236</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.027</v>
       </c>
       <c r="J28" s="7" t="n">
         <v>6.569</v>
@@ -8655,7 +8657,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2.388</v>
+        <v>2.373</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -8672,7 +8674,7 @@
         <v>0.07395</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.139</v>
+        <v>-0.145</v>
       </c>
       <c r="J29" s="7" t="n">
         <v>6.753</v>
@@ -8701,7 +8703,7 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.181</v>
+        <v>0.185</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
@@ -8720,7 +8722,7 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.253</v>
+        <v>-0.238</v>
       </c>
       <c r="J30" s="7" t="n">
         <v>6.891</v>
@@ -8729,7 +8731,7 @@
         <v>5.5</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>20.8</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="31">
@@ -8785,7 +8787,7 @@
         </is>
       </c>
       <c r="L31" s="7" t="n">
-        <v>16.6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9554,10 +9556,10 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.18823999</v>
+        <v>0.1886</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.91170996</v>
+        <v>0.91332</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>2.02</v>
@@ -9734,82 +9736,82 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sportradar Group</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.01337</v>
+        <v>0.010570001</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.91643</v>
+        <v>1.1195099</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>4.54</v>
+        <v>3.37</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.1046</v>
+        <v>0.1509</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>10753999</v>
+        <v>26892014</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Super Group</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.010570001</v>
+        <v>0.68889</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1.1195099</v>
+        <v>0.19124001</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3.37</v>
+        <v>4.72</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.1509</v>
+        <v>0.095</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>26892014</v>
+        <v>14945381</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Super Group</t>
+          <t>Sportradar Group</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.68889</v>
+        <v>0.01337</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.19124001</v>
+        <v>0.91643</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>4.72</v>
+        <v>4.54</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.095</v>
+        <v>0.1046</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>14945381</v>
+        <v>10753999</v>
       </c>
     </row>
     <row r="13">
@@ -10192,955 +10194,955 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1302.33</v>
+        <v>1294.3</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>1220.28</v>
+        <v>1218.79</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>1072.08</v>
+        <v>1070.24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1297.05</v>
+        <v>1286.75</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1218.79</v>
+        <v>1209.76</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>1070.24</v>
+        <v>1072.87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1289.5</v>
+        <v>1291.58</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1209.76</v>
+        <v>1211.98</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>1072.87</v>
+        <v>1073.92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1294.38</v>
+        <v>1292.47</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1211.98</v>
+        <v>1220.05</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1073.92</v>
+        <v>1071.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1295.09</v>
+        <v>1277.41</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1220.05</v>
+        <v>1227.31</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1071.82</v>
+        <v>1065.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1279.99</v>
+        <v>1228.74</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1227.31</v>
+        <v>1223.35</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1065.26</v>
+        <v>1045.83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1231.37</v>
+        <v>1254.15</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1223.35</v>
+        <v>1223.23</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1045.83</v>
+        <v>1063.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1256.73</v>
+        <v>1224.86</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1223.23</v>
+        <v>1231.32</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1063.16</v>
+        <v>1055.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1227.23</v>
+        <v>1220.54</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1231.32</v>
+        <v>1233.25</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1055.54</v>
+        <v>1051.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1223.05</v>
+        <v>1212.6</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>1233.25</v>
+        <v>1230.78</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1051.34</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1215.2</v>
+        <v>1210.23</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1230.78</v>
+        <v>1224.74</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1039</v>
+        <v>1041.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1212.84</v>
+        <v>1229.68</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1224.74</v>
+        <v>1228.07</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>1041.63</v>
+        <v>1053.18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1232.32</v>
+        <v>1192.58</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1228.07</v>
+        <v>1227.04</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>1053.18</v>
+        <v>1032.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1195.23</v>
+        <v>1168.44</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1227.04</v>
+        <v>1202.06</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1032.7</v>
+        <v>1015.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1171.15</v>
+        <v>1175.05</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1202.06</v>
+        <v>1215.94</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1015.9</v>
+        <v>1017.74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1177.91</v>
+        <v>1180.25</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1215.94</v>
+        <v>1222.29</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>1017.74</v>
+        <v>1025.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1183.07</v>
+        <v>1164.92</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1222.29</v>
+        <v>1222.73</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1025.88</v>
+        <v>1018.79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1167.84</v>
+        <v>1170.76</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>1222.73</v>
+        <v>1228.94</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>1018.79</v>
+        <v>1024.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1173.8</v>
+        <v>1157.44</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1228.94</v>
+        <v>1233.84</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1024.57</v>
+        <v>1020.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1160.51</v>
+        <v>1159.06</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1233.84</v>
+        <v>1233.71</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>1020.89</v>
+        <v>1013.02</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1162.3</v>
+        <v>1106.46</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1233.71</v>
+        <v>1231.26</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1013.02</v>
+        <v>996.48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1108.84</v>
+        <v>1094.61</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>1231.26</v>
+        <v>1227.59</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>996.48</v>
+        <v>974.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1097.12</v>
+        <v>1112.91</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>1227.59</v>
+        <v>1233.69</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>974.95</v>
+        <v>984.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1115.76</v>
+        <v>1109.31</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>1233.69</v>
+        <v>1223.26</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>984.4</v>
+        <v>973.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1112.4</v>
+        <v>1130.92</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>1223.26</v>
+        <v>1217.34</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>973.38</v>
+        <v>994.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1133.94</v>
+        <v>1105.79</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>1217.34</v>
+        <v>1202.13</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>994.9</v>
+        <v>975.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1108.83</v>
+        <v>1133.12</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>1202.13</v>
+        <v>1225.2</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>975.48</v>
+        <v>993.85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1136.19</v>
+        <v>1135.04</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1225.2</v>
+        <v>1231.1</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>993.85</v>
+        <v>1001.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1138.02</v>
+        <v>1131.89</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>1231.1</v>
+        <v>1227.86</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>1001.2</v>
+        <v>1003.04</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1134.97</v>
+        <v>1116.94</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>1227.86</v>
+        <v>1227.57</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>1003.04</v>
+        <v>995.4299999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1120.2</v>
+        <v>1079.22</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>1227.57</v>
+        <v>1208.61</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>995.4299999999999</v>
+        <v>960.78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1082.47</v>
+        <v>1069.65</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>1208.61</v>
+        <v>1209.46</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>960.78</v>
+        <v>948.4400000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1073.13</v>
+        <v>1084.77</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>1209.46</v>
+        <v>1211.41</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>948.4400000000001</v>
+        <v>950.28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1088.27</v>
+        <v>1119.15</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>1211.41</v>
+        <v>1217.51</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>950.28</v>
+        <v>976</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1122.65</v>
+        <v>1114.05</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>1217.51</v>
+        <v>1214.3</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>976</v>
+        <v>971.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1117.52</v>
+        <v>1114.21</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>1214.3</v>
+        <v>1223.09</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>971.28</v>
+        <v>968.92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1117.6</v>
+        <v>1070.18</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>1223.09</v>
+        <v>1210.6</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>968.92</v>
+        <v>947.13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1073.38</v>
+        <v>1085.06</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>1210.6</v>
+        <v>1219.4</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>947.13</v>
+        <v>955.26</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1088.06</v>
+        <v>1089.21</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>1219.4</v>
+        <v>1229.68</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>955.26</v>
+        <v>956.58</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1092.11</v>
+        <v>1118.8</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>1229.68</v>
+        <v>1222.85</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>956.58</v>
+        <v>958.9400000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1121.69</v>
+        <v>1105.87</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>1222.85</v>
+        <v>1216.98</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>958.9400000000001</v>
+        <v>963.14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1108.9</v>
+        <v>1100.6</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>1216.98</v>
+        <v>1217.67</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>963.14</v>
+        <v>954.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1103.61</v>
+        <v>1096.67</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>1217.67</v>
+        <v>1206.94</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>954.48</v>
+        <v>947.91</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1099.47</v>
+        <v>1112.41</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>1206.94</v>
+        <v>1215.46</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>947.91</v>
+        <v>953.6900000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1115.19</v>
+        <v>1110.13</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>1215.46</v>
+        <v>1208.68</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>953.6900000000001</v>
+        <v>947.65</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1112.82</v>
+        <v>1077.88</v>
       </c>
       <c r="C47" s="13" t="n">
-        <v>1208.68</v>
+        <v>1192.84</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>947.65</v>
+        <v>937.9400000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1080.52</v>
+        <v>1079.36</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>1192.84</v>
+        <v>1203.29</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>937.9400000000001</v>
+        <v>940.04</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1082.04</v>
+        <v>1078.33</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>1203.29</v>
+        <v>1201.35</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>940.04</v>
+        <v>938.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1081.09</v>
+        <v>1093.51</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>1201.35</v>
+        <v>1199.85</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>938.2</v>
+        <v>942.66</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1096.15</v>
+        <v>1078.92</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>1199.85</v>
+        <v>1181.63</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>942.66</v>
+        <v>931.38</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1081.53</v>
+        <v>1080.83</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>1181.63</v>
+        <v>1174.94</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>931.38</v>
+        <v>929.28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1083.4</v>
+        <v>1073.18</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>1174.94</v>
+        <v>1186.89</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>929.28</v>
+        <v>926.39</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1075.81</v>
+        <v>1085.74</v>
       </c>
       <c r="C54" s="13" t="n">
-        <v>1186.89</v>
+        <v>1190.02</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>926.39</v>
+        <v>925.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1088.4</v>
+        <v>1077.62</v>
       </c>
       <c r="C55" s="13" t="n">
-        <v>1190.02</v>
+        <v>1173.41</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>925.6</v>
+        <v>915.36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1080.29</v>
+        <v>1090.51</v>
       </c>
       <c r="C56" s="13" t="n">
-        <v>1173.41</v>
+        <v>1170.52</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>915.36</v>
+        <v>922.45</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1093.25</v>
+        <v>1061.69</v>
       </c>
       <c r="C57" s="13" t="n">
-        <v>1170.52</v>
+        <v>1153.74</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>922.45</v>
+        <v>894.63</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1064.4</v>
+        <v>1084.18</v>
       </c>
       <c r="C58" s="13" t="n">
-        <v>1153.74</v>
+        <v>1165.85</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>894.63</v>
+        <v>932.4299999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1086.87</v>
+        <v>1095.28</v>
       </c>
       <c r="C59" s="13" t="n">
-        <v>1165.85</v>
+        <v>1161.94</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>932.4299999999999</v>
+        <v>922.45</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1098.05</v>
+        <v>1081.07</v>
       </c>
       <c r="C60" s="13" t="n">
-        <v>1161.94</v>
+        <v>1168.42</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>922.45</v>
+        <v>916.41</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1083.82</v>
+        <v>1060</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11152,7 +11154,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1083.82</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="64">
@@ -11163,7 +11165,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-16.27%</t>
+          <t>-17.93%</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11186,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>138.2</v>
+        <v>135.8</v>
       </c>
     </row>
   </sheetData>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>52.49</v>
+        <v>52.47</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.031013412</v>
+        <v>-0.03147495</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -673,16 +673,16 @@
         <v>-0.255</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>35.49</v>
+        <v>35.473</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>48.933</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.336172</v>
+        <v>22.325533</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>13.969246</v>
+        <v>13.962593</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>10.795</v>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>103.19</v>
+        <v>103.27</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.20309389</v>
+        <v>-0.12573005</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -732,7 +732,7 @@
         <v>-0.6709999999999999</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.053</v>
+        <v>18.067</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>29.807</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.693781</v>
+        <v>9.701295</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>13.981</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>21.2</v>
+        <v>21.23</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.010037355</v>
+        <v>-0.8636763</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -793,7 +793,7 @@
         <v>-0.5649999999999999</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>10.555</v>
+        <v>10.57</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>11.322</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>10.895031</v>
+        <v>10.910445</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>41.491</v>
@@ -816,7 +816,7 @@
         <v>1.682</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.4370000000000001</v>
+        <v>-0.436</v>
       </c>
       <c r="Q4" s="4" t="n">
         <v>-0.405</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>99.36</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.024781642</v>
+        <v>-0.0244381</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -854,16 +854,16 @@
         <v>-0.262</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.362</v>
+        <v>10.366</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>19.942</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>31.644903</v>
+        <v>31.65605</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>16.723131</v>
+        <v>16.729021</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>11.398</v>
@@ -875,10 +875,10 @@
         <v>1.034</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>0.168</v>
+        <v>0.169</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>-0.188</v>
+        <v>-0.187</v>
       </c>
     </row>
     <row r="6">
@@ -901,7 +901,7 @@
         <v>37.51</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.04000904</v>
+        <v>0.053338602</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -913,16 +913,16 @@
         <v>-0.066</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10.258</v>
+        <v>10.259</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>39.718</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>49.348686</v>
+        <v>49.355263</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>16.006504</v>
+        <v>16.008636</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>16.869</v>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>82.97</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.022321742</v>
+        <v>-0.022858517</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -972,16 +972,16 @@
         <v>-0.078</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.264</v>
+        <v>6.261</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>8.763999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.67797</v>
+        <v>3.6759753</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.184217</v>
+        <v>10.178695</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>7.297</v>
@@ -993,7 +993,7 @@
         <v>1.22</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0.225</v>
+        <v>0.224</v>
       </c>
       <c r="Q7" s="4" t="n">
         <v>-0.035</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>87.73999999999999</v>
+        <v>87.72</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.6192671</v>
+        <v>0.5963352</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>118.46</v>
@@ -1031,16 +1031,16 @@
         <v>-0.259</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.115</v>
+        <v>6.114</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>11.12</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.586012</v>
+        <v>16.582232</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>11.8167715</v>
+        <v>11.814078</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>11.623</v>
@@ -1052,7 +1052,7 @@
         <v>0.66</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.223</v>
+        <v>-0.224</v>
       </c>
       <c r="Q8" s="4" t="n">
         <v>-0.216</v>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>55.98</v>
+        <v>55.96</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.04714895</v>
+        <v>-0.047489376</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1090,16 +1090,16 @@
         <v>-0.189</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.756</v>
+        <v>5.754</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>6.886</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>17.942308</v>
+        <v>17.935898</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>17.036274</v>
+        <v>17.030186</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>8.461</v>
@@ -1114,7 +1114,7 @@
         <v>0.325</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.09300000000000001</v>
+        <v>-0.094</v>
       </c>
     </row>
     <row r="10">
@@ -1137,7 +1137,7 @@
         <v>26.8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.09322998</v>
+        <v>-0.055926137</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>31.58</v>
@@ -1149,7 +1149,7 @@
         <v>-0.151</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.469</v>
+        <v>5.471</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>30.375</v>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="L10" s="7" t="n">
-        <v>26.115984</v>
+        <v>26.12573</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>8.691000000000001</v>
@@ -1175,7 +1175,7 @@
         <v>-0.029</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="11">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.56</v>
+        <v>10.55</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.18975766</v>
+        <v>0.09487883</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>14.38</v>
@@ -1210,16 +1210,16 @@
         <v>-0.266</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.34</v>
+        <v>5.334</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>4.922</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>25.142859</v>
+        <v>25.11905</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12.174174</v>
+        <v>12.162645</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>10.031</v>
@@ -1231,7 +1231,7 @@
         <v>1.1</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>0.555</v>
+        <v>0.5539999999999999</v>
       </c>
       <c r="Q11" s="4" t="n">
         <v>-0.08900000000000001</v>
@@ -1257,7 +1257,7 @@
         <v>17.82</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.037006993</v>
+        <v>-0.037277176</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>32.22</v>
@@ -1269,16 +1269,16 @@
         <v>-0.447</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.275</v>
+        <v>5.274</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>5.256</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>49.51389</v>
+        <v>49.499996</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>21.632576</v>
+        <v>21.626507</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>10.358</v>
@@ -1442,7 +1442,7 @@
         <v>5.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.3649631400000001</v>
+        <v>0.4562061</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>10.15</v>
@@ -1454,16 +1454,16 @@
         <v>-0.458</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.237</v>
+        <v>2.239</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>12.774</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>11.956522</v>
+        <v>11.967391</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>6.913109</v>
+        <v>6.9193935</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>10.592</v>
@@ -1475,10 +1475,10 @@
         <v>0.603</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.268</v>
+        <v>-0.267</v>
       </c>
     </row>
     <row r="16">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.06</v>
+        <v>11.07</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.017317997</v>
+        <v>-0.016429877</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>13.31</v>
@@ -1693,7 +1693,7 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.169</v>
+        <v>-0.168</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0.903</v>
@@ -1702,10 +1702,10 @@
         <v>1.242</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>18.441666</v>
+        <v>18.458332</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>11.948856</v>
+        <v>11.959656</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>6.569</v>
@@ -1717,10 +1717,10 @@
         <v>1.07</v>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0.083</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.027</v>
+        <v>-0.026</v>
       </c>
     </row>
     <row r="20">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.38</v>
+        <v>26.36</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.03789401</v>
+        <v>-0.113674805</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>32.74</v>
@@ -1752,7 +1752,7 @@
         <v>19.57</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.194</v>
+        <v>-0.195</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0.696</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>21.801651</v>
+        <v>21.785124</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>9.455</v>
@@ -1781,7 +1781,7 @@
         <v>0.003</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.025</v>
+        <v>-0.026</v>
       </c>
     </row>
     <row r="21">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.52</v>
+        <v>11.42</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.033976488</v>
+        <v>-0.041946306</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>20.74</v>
@@ -1813,10 +1813,10 @@
         <v>8.455</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.445</v>
+        <v>-0.449</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="J21" s="6" t="n">
         <v>7.795</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>-14.21605</v>
+        <v>-14.098765</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>22.644</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.174</v>
+        <v>-0.181</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.308</v>
+        <v>-0.314</v>
       </c>
     </row>
     <row r="22">
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>52.49</v>
+        <v>52.47</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.031013412</v>
+        <v>-0.03147495</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>-0.191</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>103.19</v>
+        <v>103.27</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.20309389</v>
+        <v>-0.12573005</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>-0.527</v>
@@ -2214,7 +2214,7 @@
         <v>-59.4</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.283</v>
+        <v>-0.282</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>-0.551</v>
@@ -2246,22 +2246,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>21.2</v>
+        <v>21.23</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.010037355</v>
+        <v>-0.8636763</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>-0.405</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.4370000000000001</v>
+        <v>-0.436</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>-37.5</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.219</v>
+        <v>-0.218</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>-0.406</v>
@@ -2293,16 +2293,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>99.36</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-0.024781642</v>
+        <v>-0.0244381</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.188</v>
+        <v>-0.187</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.168</v>
+        <v>0.169</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>33.4</v>
@@ -2343,7 +2343,7 @@
         <v>37.51</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.04000904</v>
+        <v>0.053338602</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.028</v>
@@ -2387,22 +2387,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>82.97</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-0.022321742</v>
+        <v>-0.022858517</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>-0.035</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.225</v>
+        <v>0.224</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>20.1</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.012</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>0.002</v>
@@ -2434,22 +2434,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>87.73999999999999</v>
+        <v>87.72</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.6192671</v>
+        <v>0.5963352</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>-0.216</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.223</v>
+        <v>-0.224</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>-3.2</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.07400000000000001</v>
+        <v>-0.075</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>-0.131</v>
@@ -2481,13 +2481,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>55.98</v>
+        <v>55.96</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-0.04714895</v>
+        <v>-0.047489376</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.09300000000000001</v>
+        <v>-0.094</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0.325</v>
@@ -2499,7 +2499,7 @@
         <v>-0.092</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.046</v>
+        <v>-0.047</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>-0.189</v>
@@ -2531,10 +2531,10 @@
         <v>26.8</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.09322998</v>
+        <v>-0.055926137</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>-0.029</v>
@@ -2575,25 +2575,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.56</v>
+        <v>10.55</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.18975766</v>
+        <v>0.09487883</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>-0.08900000000000001</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.555</v>
+        <v>0.5539999999999999</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>26</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.061</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>-0.266</v>
@@ -2625,7 +2625,7 @@
         <v>17.82</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.037006993</v>
+        <v>-0.037277176</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>-0.236</v>
@@ -2766,13 +2766,13 @@
         <v>5.5</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.3649631400000001</v>
+        <v>0.4562061</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.268</v>
+        <v>-0.267</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>6.2</v>
@@ -2951,28 +2951,28 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.06</v>
+        <v>11.07</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-0.017317997</v>
+        <v>-0.016429877</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.026</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.083</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>-1.6</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.02</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.012</v>
+        <v>-0.011</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.169</v>
+        <v>-0.168</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.07</v>
@@ -2998,13 +2998,13 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.38</v>
+        <v>26.36</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.03789401</v>
+        <v>-0.113674805</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.025</v>
+        <v>-0.026</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0.003</v>
@@ -3013,13 +3013,13 @@
         <v>5.4</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.057</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>-0.019</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.194</v>
+        <v>-0.195</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>1.412</v>
@@ -3045,28 +3045,28 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.52</v>
+        <v>11.42</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-0.033976488</v>
+        <v>-0.041946306</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.308</v>
+        <v>-0.314</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.174</v>
+        <v>-0.181</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.207</v>
+        <v>-0.214</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.133</v>
+        <v>-0.141</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.445</v>
+        <v>-0.449</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -3342,16 +3342,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>52.49</v>
+        <v>52.47</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>35.49</v>
+        <v>35.473</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>22.336172</v>
+        <v>22.325533</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>13.969246</v>
+        <v>13.962593</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>10.795</v>
@@ -3363,10 +3363,10 @@
         <v>3.759</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.279287</v>
+        <v>22.268677</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.7264578</v>
+        <v>2.7251592</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>103.19</v>
+        <v>103.27</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.053</v>
+        <v>18.067</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.693781</v>
+        <v>9.701295</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>13.981</v>
@@ -3418,10 +3418,10 @@
         <v>1.819</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.0005815</v>
+        <v>2.0021324</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1019554</v>
+        <v>1.1028097</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>21.2</v>
+        <v>21.23</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>10.555</v>
+        <v>10.57</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>10.895031</v>
+        <v>10.910445</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>41.491</v>
@@ -3473,10 +3473,10 @@
         <v>1.87</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>16.618338</v>
+        <v>16.64185</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.7433681</v>
+        <v>1.7458347</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3505,16 +3505,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>99.36</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.362</v>
+        <v>10.366</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>31.644903</v>
+        <v>31.65605</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>16.723131</v>
+        <v>16.729021</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>11.398</v>
@@ -3526,10 +3526,10 @@
         <v>2.794</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-36.966145</v>
+        <v>-36.979168</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.4516978</v>
+        <v>1.4522092</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3561,13 +3561,13 @@
         <v>37.51</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.258</v>
+        <v>10.259</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>49.348686</v>
+        <v>49.355263</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>16.006504</v>
+        <v>16.008636</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>16.869</v>
@@ -3579,10 +3579,10 @@
         <v>2.265</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.986925</v>
+        <v>3.987456</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.58490384</v>
+        <v>0.5849818</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3611,16 +3611,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>82.97</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.264</v>
+        <v>6.261</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.67797</v>
+        <v>3.6759753</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.184217</v>
+        <v>10.178695</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>7.297</v>
@@ -3632,10 +3632,10 @@
         <v>2.142</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.4292238</v>
+        <v>2.4279063</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5307875</v>
+        <v>1.5299574</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>22.56</v>
@@ -3664,16 +3664,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>87.73999999999999</v>
+        <v>87.72</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.115</v>
+        <v>6.114</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>16.586012</v>
+        <v>16.582232</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>11.8167715</v>
+        <v>11.814078</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>11.623</v>
@@ -3685,10 +3685,10 @@
         <v>3.801</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>6.048115</v>
+        <v>6.0467362</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.09001</v>
+        <v>2.0895336</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>5.29</v>
@@ -3717,16 +3717,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>55.98</v>
+        <v>55.96</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.756</v>
+        <v>5.754</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>17.942308</v>
+        <v>17.935898</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>17.036274</v>
+        <v>17.030186</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>8.461</v>
@@ -3738,10 +3738,10 @@
         <v>3.423</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>15.671892</v>
+        <v>15.666293</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.8616943</v>
+        <v>2.860672</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>3.12</v>
@@ -3773,7 +3773,7 @@
         <v>26.8</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.469</v>
+        <v>5.471</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>26.115984</v>
+        <v>26.12573</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>8.691000000000001</v>
@@ -3793,10 +3793,10 @@
         <v>2.645</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>1.5494709</v>
+        <v>1.5500492</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.47615117</v>
+        <v>0.47632885</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>-2.42</v>
@@ -3825,16 +3825,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.56</v>
+        <v>10.55</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.34</v>
+        <v>5.334</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>25.142859</v>
+        <v>25.11905</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>12.174174</v>
+        <v>12.162645</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>10.031</v>
@@ -3846,10 +3846,10 @@
         <v>2.101</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.1690426</v>
+        <v>7.162254</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2.2790158</v>
+        <v>2.2768576</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>0.42</v>
@@ -3881,13 +3881,13 @@
         <v>17.82</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.275</v>
+        <v>5.274</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>49.51389</v>
+        <v>49.499996</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>21.632576</v>
+        <v>21.626507</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>10.358</v>
@@ -3899,7 +3899,7 @@
         <v>4.075</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>4.711227</v>
+        <v>4.709905</v>
       </c>
       <c r="L12" s="7" t="n">
         <v>4.0895205</v>
@@ -4048,13 +4048,13 @@
         <v>5.5</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.237</v>
+        <v>2.239</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>11.956522</v>
+        <v>11.967391</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.913109</v>
+        <v>6.9193935</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>10.592</v>
@@ -4066,10 +4066,10 @@
         <v>2.474</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1.7235976</v>
+        <v>-1.7251645</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.43331912</v>
+        <v>0.43371302</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.46</v>
@@ -4263,16 +4263,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.06</v>
+        <v>11.07</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>0.903</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>18.441666</v>
+        <v>18.458332</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>11.948856</v>
+        <v>11.959656</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>6.569</v>
@@ -4284,10 +4284,10 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>3.3765638</v>
+        <v>3.3796155</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.6781631</v>
+        <v>0.67877597</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0.6</v>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.38</v>
+        <v>26.36</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0.696</v>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>21.801651</v>
+        <v>21.785124</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>9.455</v>
@@ -4339,10 +4339,10 @@
         <v>1.818</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.6411597</v>
+        <v>1.6399155</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>1.0968477</v>
+        <v>1.0960162</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.23</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.52</v>
+        <v>11.42</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-14.21605</v>
+        <v>-14.098765</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>22.644</v>
@@ -4394,10 +4394,10 @@
         <v>2.934</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.56176215</v>
+        <v>0.55712754</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.2130857</v>
+        <v>0.21132772</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>-12.45</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>52.49</v>
+        <v>52.47</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>58</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>2.49</v>
@@ -6301,7 +6301,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>103.19</v>
+        <v>103.27</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>1.01</v>
+        <v>1.009</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>2.02</v>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>21.2</v>
+        <v>21.23</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.706</v>
+        <v>0.7040000000000001</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>2.13</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>99.36</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>82.97</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>87.73999999999999</v>
+        <v>87.72</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>110</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.544</v>
+        <v>0.545</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>2.17</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>55.98</v>
+        <v>55.96</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10.56</v>
+        <v>10.55</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.645</v>
+        <v>0.647</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4.72</v>
@@ -6827,13 +6827,13 @@
         <v>21</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>28.815092</v>
+        <v>28.81177</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>37.088665</v>
+        <v>37.08439</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>22.896345</v>
+        <v>22.893705</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>0.617</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11.06</v>
+        <v>11.07</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>14</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.401</v>
+        <v>0.4</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>2.55</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>26.38</v>
+        <v>26.36</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>30</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.156</v>
+        <v>0.157</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>4.41</v>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>11.52</v>
+        <v>11.42</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>11</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.36</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>8.01</v>
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>35.49</v>
+        <v>35.473</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>22.336172</v>
+        <v>22.325533</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.469</v>
+        <v>5.471</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>8.691000000000001</v>
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>10.362</v>
+        <v>10.366</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>31.644903</v>
+        <v>31.65605</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.015</v>
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.188</v>
+        <v>-0.187</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>11.398</v>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2.237</v>
+        <v>2.239</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>11.956522</v>
+        <v>11.967391</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-0.268</v>
+        <v>-0.267</v>
       </c>
       <c r="J6" s="7" t="n">
         <v>10.592</v>
@@ -7879,10 +7879,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.258</v>
+        <v>10.259</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>49.348686</v>
+        <v>49.355263</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.06</v>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.264</v>
+        <v>6.261</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.67797</v>
+        <v>3.6759753</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6.115</v>
+        <v>6.114</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>16.586012</v>
+        <v>16.582232</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.067</v>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5.756</v>
+        <v>5.754</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>17.942308</v>
+        <v>17.935898</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.032</v>
@@ -8044,7 +8044,7 @@
         <v>1.113</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>-0.09300000000000001</v>
+        <v>-0.094</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>8.461</v>
@@ -8180,7 +8180,7 @@
         <v>-0.0135</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.025</v>
+        <v>-0.026</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>9.455</v>
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>-0.5564</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.308</v>
+        <v>-0.314</v>
       </c>
       <c r="J16" s="7" t="n">
         <v>22.644</v>
@@ -8319,10 +8319,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.34</v>
+        <v>5.334</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.142859</v>
+        <v>25.11905</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -8411,10 +8411,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.275</v>
+        <v>5.274</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>49.51389</v>
+        <v>49.499996</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.201</v>
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>10.555</v>
+        <v>10.57</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.053</v>
+        <v>18.067</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>0.903</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.441666</v>
+        <v>18.458332</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0.075</v>
@@ -8628,7 +8628,7 @@
         <v>0.19236</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.026</v>
       </c>
       <c r="J28" s="7" t="n">
         <v>6.569</v>
@@ -10198,7 +10198,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1294.3</v>
+        <v>1294.16</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>1218.79</v>
@@ -10214,7 +10214,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1286.75</v>
+        <v>1286.61</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>1209.76</v>
@@ -10230,7 +10230,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1291.58</v>
+        <v>1291.45</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>1211.98</v>
@@ -10246,7 +10246,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1292.47</v>
+        <v>1292.34</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>1220.05</v>
@@ -10262,7 +10262,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1277.41</v>
+        <v>1277.28</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>1227.31</v>
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1228.74</v>
+        <v>1228.62</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1223.35</v>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1254.15</v>
+        <v>1254.03</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1223.23</v>
@@ -10310,7 +10310,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1224.86</v>
+        <v>1224.75</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>1231.32</v>
@@ -10326,7 +10326,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1220.54</v>
+        <v>1220.43</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1233.25</v>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1212.6</v>
+        <v>1212.48</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1230.78</v>
@@ -10358,7 +10358,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1210.23</v>
+        <v>1210.11</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>1224.74</v>
@@ -10374,7 +10374,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1229.68</v>
+        <v>1229.57</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>1228.07</v>
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1192.58</v>
+        <v>1192.46</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>1227.04</v>
@@ -10406,7 +10406,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1168.44</v>
+        <v>1168.32</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>1202.06</v>
@@ -10422,7 +10422,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1175.05</v>
+        <v>1174.92</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>1215.94</v>
@@ -10438,7 +10438,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1180.25</v>
+        <v>1180.12</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>1222.29</v>
@@ -10454,7 +10454,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1164.92</v>
+        <v>1164.78</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1222.73</v>
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1170.76</v>
+        <v>1170.62</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>1228.94</v>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1157.44</v>
+        <v>1157.29</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>1233.84</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1159.06</v>
+        <v>1158.92</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>1233.71</v>
@@ -10518,7 +10518,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1106.46</v>
+        <v>1106.34</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>1231.26</v>
@@ -10534,7 +10534,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1094.61</v>
+        <v>1094.49</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>1227.59</v>
@@ -10550,7 +10550,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1112.91</v>
+        <v>1112.78</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>1233.69</v>
@@ -10566,7 +10566,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1109.31</v>
+        <v>1109.17</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1223.26</v>
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1130.92</v>
+        <v>1130.78</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>1217.34</v>
@@ -10598,7 +10598,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1105.79</v>
+        <v>1105.65</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>1202.13</v>
@@ -10614,7 +10614,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1133.12</v>
+        <v>1132.97</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>1225.2</v>
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1135.04</v>
+        <v>1134.91</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>1231.1</v>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1131.89</v>
+        <v>1131.75</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1227.86</v>
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1116.94</v>
+        <v>1116.8</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1227.57</v>
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1079.22</v>
+        <v>1079.08</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>1208.61</v>
@@ -10694,7 +10694,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1069.65</v>
+        <v>1069.48</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>1209.46</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1084.77</v>
+        <v>1084.6</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>1211.41</v>
@@ -10726,7 +10726,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1119.15</v>
+        <v>1118.98</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>1217.51</v>
@@ -10742,7 +10742,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1114.05</v>
+        <v>1113.88</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>1214.3</v>
@@ -10758,7 +10758,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1114.21</v>
+        <v>1114.03</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>1223.09</v>
@@ -10774,7 +10774,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1070.18</v>
+        <v>1070.01</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>1210.6</v>
@@ -10790,7 +10790,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1085.06</v>
+        <v>1084.89</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>1219.4</v>
@@ -10806,7 +10806,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1089.21</v>
+        <v>1089.04</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>1229.68</v>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1118.8</v>
+        <v>1118.64</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>1222.85</v>
@@ -10838,7 +10838,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1105.87</v>
+        <v>1105.69</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>1216.98</v>
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1100.6</v>
+        <v>1100.43</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>1217.67</v>
@@ -10870,7 +10870,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1096.67</v>
+        <v>1096.5</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>1206.94</v>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1112.41</v>
+        <v>1112.24</v>
       </c>
       <c r="C45" s="13" t="n">
         <v>1215.46</v>
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1110.13</v>
+        <v>1109.96</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>1208.68</v>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1077.88</v>
+        <v>1077.73</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1192.84</v>
@@ -10934,7 +10934,7 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1079.36</v>
+        <v>1079.2</v>
       </c>
       <c r="C48" s="13" t="n">
         <v>1203.29</v>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1078.33</v>
+        <v>1078.17</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1201.35</v>
@@ -10966,7 +10966,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1093.51</v>
+        <v>1093.35</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>1199.85</v>
@@ -10982,7 +10982,7 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1078.92</v>
+        <v>1078.76</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>1181.63</v>
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1080.83</v>
+        <v>1080.68</v>
       </c>
       <c r="C52" s="13" t="n">
         <v>1174.94</v>
@@ -11014,7 +11014,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1073.18</v>
+        <v>1073.02</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>1186.89</v>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1085.74</v>
+        <v>1085.58</v>
       </c>
       <c r="C54" s="13" t="n">
         <v>1190.02</v>
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1077.62</v>
+        <v>1077.47</v>
       </c>
       <c r="C55" s="13" t="n">
         <v>1173.41</v>
@@ -11062,7 +11062,7 @@
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1090.51</v>
+        <v>1090.35</v>
       </c>
       <c r="C56" s="13" t="n">
         <v>1170.52</v>
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1061.69</v>
+        <v>1061.53</v>
       </c>
       <c r="C57" s="13" t="n">
         <v>1153.74</v>
@@ -11094,7 +11094,7 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1084.18</v>
+        <v>1084.02</v>
       </c>
       <c r="C58" s="13" t="n">
         <v>1165.85</v>
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1095.28</v>
+        <v>1095.11</v>
       </c>
       <c r="C59" s="13" t="n">
         <v>1161.94</v>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1081.07</v>
+        <v>1080.9</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>1168.42</v>
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1060</v>
+        <v>1060.02</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11154,7 +11154,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1060</v>
+        <v>1060.02</v>
       </c>
     </row>
     <row r="64">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-17.93%</t>
+          <t>-17.92%</t>
         </is>
       </c>
     </row>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>52.47</v>
+        <v>52.36</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.03147495</v>
+        <v>-0.033413284</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,19 +670,19 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.255</v>
+        <v>-0.257</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>35.473</v>
+        <v>35.402</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>48.933</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.325533</v>
+        <v>22.280851</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>13.962593</v>
+        <v>13.9346485</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>10.795</v>
@@ -694,10 +694,10 @@
         <v>0.888</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0.329</v>
+        <v>0.326</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>-0.191</v>
+        <v>-0.193</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>103.27</v>
+        <v>103.32</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.12573005</v>
+        <v>-0.07735625</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -732,7 +732,7 @@
         <v>-0.6709999999999999</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.067</v>
+        <v>18.076</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>29.807</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.701295</v>
+        <v>9.705992999999999</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>13.981</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>21.23</v>
+        <v>21.22</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.8636763</v>
+        <v>-0.9337104000000001</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -793,7 +793,7 @@
         <v>-0.5649999999999999</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>10.57</v>
+        <v>10.563</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>11.322</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>10.910445</v>
+        <v>10.902738</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>41.491</v>
@@ -816,7 +816,7 @@
         <v>1.682</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.436</v>
+        <v>-0.4370000000000001</v>
       </c>
       <c r="Q4" s="4" t="n">
         <v>-0.405</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>99.40000000000001</v>
+        <v>99.31</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.0244381</v>
+        <v>-0.025321443</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,19 +851,19 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.262</v>
+        <v>-0.263</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.366</v>
+        <v>10.356</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>19.942</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>31.65605</v>
+        <v>31.627386</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>16.729021</v>
+        <v>16.713875</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>11.398</v>
@@ -875,10 +875,10 @@
         <v>1.034</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>0.169</v>
+        <v>0.168</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>-0.187</v>
+        <v>-0.188</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.51</v>
+        <v>37.56</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.053338602</v>
+        <v>0.18671563</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,19 +910,19 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.066</v>
+        <v>-0.065</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10.259</v>
+        <v>10.273</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>39.718</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>49.355263</v>
+        <v>49.421055</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>16.008636</v>
+        <v>16.029978</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>16.869</v>
@@ -934,10 +934,10 @@
         <v>1.396</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.168</v>
+        <v>0.169</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>82.93000000000001</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.022858517</v>
+        <v>-0.022151582</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -969,19 +969,19 @@
         <v>58.94</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.078</v>
+        <v>-0.077</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.261</v>
+        <v>6.265</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>8.763999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.6759753</v>
+        <v>3.6786346</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.178695</v>
+        <v>10.186058</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>7.297</v>
@@ -993,7 +993,7 @@
         <v>1.22</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0.224</v>
+        <v>0.225</v>
       </c>
       <c r="Q7" s="4" t="n">
         <v>-0.035</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>87.72</v>
+        <v>87.8</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.5963352</v>
+        <v>0.68521065</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>118.46</v>
@@ -1031,16 +1031,16 @@
         <v>-0.259</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.114</v>
+        <v>6.119</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>11.12</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.582232</v>
+        <v>16.596882</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>11.814078</v>
+        <v>11.824516</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>11.623</v>
@@ -1052,7 +1052,7 @@
         <v>0.66</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.224</v>
+        <v>-0.223</v>
       </c>
       <c r="Q8" s="4" t="n">
         <v>-0.216</v>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>55.96</v>
+        <v>55.9</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.047489376</v>
+        <v>-0.04851061299999999</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1087,19 +1087,19 @@
         <v>35.09</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.189</v>
+        <v>-0.19</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.754</v>
+        <v>5.748</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>6.886</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>17.935898</v>
+        <v>17.916668</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>17.030186</v>
+        <v>17.011927</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>8.461</v>
@@ -1111,10 +1111,10 @@
         <v>1.453</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>0.325</v>
+        <v>0.323</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.094</v>
+        <v>-0.095</v>
       </c>
     </row>
     <row r="10">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-0.055926137</v>
+        <v>26.87</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>0.1864323</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>31.58</v>
@@ -1146,10 +1146,10 @@
         <v>17.86</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-0.151</v>
+        <v>-0.149</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.471</v>
+        <v>5.484</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>30.375</v>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="L10" s="7" t="n">
-        <v>26.12573</v>
+        <v>26.189085</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>8.691000000000001</v>
@@ -1172,10 +1172,10 @@
         <v>1.977</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.029</v>
+        <v>-0.026</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>0.138</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="11">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.55</v>
+        <v>10.56</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.09487883</v>
+        <v>0.23718803</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>14.38</v>
@@ -1210,16 +1210,16 @@
         <v>-0.266</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.334</v>
+        <v>5.342</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>4.922</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>25.11905</v>
+        <v>25.154762</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>12.162645</v>
+        <v>12.179937</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>10.031</v>
@@ -1231,10 +1231,10 @@
         <v>1.1</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>0.5539999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.08900000000000001</v>
+        <v>-0.08800000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>17.82</v>
+        <v>17.93</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.037277176</v>
+        <v>-0.031064332</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>32.22</v>
@@ -1266,19 +1266,19 @@
         <v>15.725</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.447</v>
+        <v>-0.444</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5.274</v>
+        <v>5.308</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>5.256</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>49.499996</v>
+        <v>49.819443</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>21.626507</v>
+        <v>21.766071</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>10.358</v>
@@ -1290,10 +1290,10 @@
         <v>2.002</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.205</v>
+        <v>-0.2</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.236</v>
+        <v>-0.231</v>
       </c>
     </row>
     <row r="13">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.62</v>
+        <v>21.68</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.013686097</v>
+        <v>-0.010948895</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.65</v>
@@ -1325,10 +1325,10 @@
         <v>9.66</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.045</v>
+        <v>-0.043</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.033</v>
+        <v>5.047</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>69.741936</v>
+        <v>69.935486</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>28.979681</v>
+        <v>29.060104</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         <v>1.552</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0.982</v>
+        <v>0.987</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>0.12</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="14">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.61823744</v>
+        <v>-0.5795967</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>18.57</v>
@@ -1393,7 +1393,7 @@
         <v>-0.307</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.373</v>
+        <v>2.374</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>5.956</v>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="L14" s="7" t="n">
-        <v>11.934591</v>
+        <v>11.939231</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>6.753</v>
@@ -1416,10 +1416,10 @@
         <v>1.082</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.038</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.145</v>
+        <v>-0.144</v>
       </c>
     </row>
     <row r="15">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.5</v>
+        <v>5.51</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.4562061</v>
+        <v>0.6386833</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>10.15</v>
@@ -1451,19 +1451,19 @@
         <v>4.55</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.458</v>
+        <v>-0.457</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.239</v>
+        <v>2.243</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>12.774</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>11.967391</v>
+        <v>11.98913</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>6.9193935</v>
+        <v>6.9319625</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>10.592</v>
@@ -1475,10 +1475,10 @@
         <v>0.603</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>0.023</v>
+        <v>0.025</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.267</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.51</v>
+        <v>14.5</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.01057297</v>
+        <v>-0.010917765</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>20.61</v>
@@ -1513,7 +1513,7 @@
         <v>-0.296</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.937</v>
+        <v>1.936</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>12.438</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>8.381824999999999</v>
+        <v>8.378935999999999</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>17.223</v>
@@ -1536,10 +1536,10 @@
         <v>1.364</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.164</v>
+        <v>-0.165</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.023</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="17">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>97.54000000000001</v>
+        <v>97.36</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.019402838</v>
+        <v>-0.021162193</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>113.88</v>
@@ -1571,19 +1571,19 @@
         <v>69.98999999999999</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.143</v>
+        <v>-0.145</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.745</v>
+        <v>1.741</v>
       </c>
       <c r="J17" s="6" t="n">
         <v>1.696</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>17.96317</v>
+        <v>17.930939</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>16.407064</v>
+        <v>16.377628</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>8.893000000000001</v>
@@ -1595,10 +1595,10 @@
         <v>1.376</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>0.218</v>
+        <v>0.215</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="18">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.0391304</v>
+        <v>-0.04130436000000001</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>13.73</v>
@@ -1630,10 +1630,10 @@
         <v>4.4</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.6779999999999999</v>
+        <v>-0.679</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.137</v>
+        <v>1.134</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>0.883</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>4.4646463</v>
+        <v>4.454545</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>-7.324</v>
@@ -1658,10 +1658,10 @@
         <v>1.993</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.584</v>
+        <v>-0.585</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.59</v>
+        <v>-0.591</v>
       </c>
     </row>
     <row r="19">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.07</v>
+        <v>11.06</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.016429877</v>
+        <v>-0.017761972</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>13.31</v>
@@ -1693,19 +1693,19 @@
         <v>9.015000000000001</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.168</v>
+        <v>-0.169</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.903</v>
+        <v>0.902</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>1.242</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>18.458332</v>
+        <v>18.433332</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>11.959656</v>
+        <v>11.943459</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>6.569</v>
@@ -1717,10 +1717,10 @@
         <v>1.07</v>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.026</v>
+        <v>-0.027</v>
       </c>
     </row>
     <row r="20">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.36</v>
+        <v>26.35</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.113674805</v>
+        <v>-0.15156882</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>32.74</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>21.785124</v>
+        <v>21.77686</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>9.455</v>
@@ -1778,7 +1778,7 @@
         <v>1.412</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>-0.026</v>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.42</v>
+        <v>11.38</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.041946306</v>
+        <v>-0.044882536</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>20.74</v>
@@ -1813,10 +1813,10 @@
         <v>8.455</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.449</v>
+        <v>-0.451</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J21" s="6" t="n">
         <v>7.795</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>-14.098765</v>
+        <v>-14.055555</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>22.644</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.181</v>
+        <v>-0.183</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.314</v>
+        <v>-0.316</v>
       </c>
     </row>
     <row r="22">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.83</v>
+        <v>6.87</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.020149288</v>
+        <v>0.025373147</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>9.949999999999999</v>
@@ -1876,10 +1876,10 @@
         <v>6.1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.314</v>
+        <v>-0.31</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.185</v>
+        <v>0.186</v>
       </c>
       <c r="J22" s="6" t="n">
         <v>0.512</v>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>9.123552</v>
+        <v>9.170271</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>6.891</v>
@@ -1902,10 +1902,10 @@
         <v>1.206</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.238</v>
+        <v>-0.234</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.238</v>
+        <v>-0.234</v>
       </c>
     </row>
     <row r="23">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>52.47</v>
+        <v>52.36</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.03147495</v>
+        <v>-0.033413284</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.191</v>
+        <v>-0.193</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.329</v>
+        <v>0.326</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>52.2</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>-0.077</v>
+        <v>-0.079</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.058</v>
+        <v>-0.06</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.255</v>
+        <v>-0.257</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0.888</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>103.27</v>
+        <v>103.32</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.12573005</v>
+        <v>-0.07735625</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>-0.527</v>
@@ -2246,22 +2246,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>21.23</v>
+        <v>21.22</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.8636763</v>
+        <v>-0.9337104000000001</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>-0.405</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.436</v>
+        <v>-0.4370000000000001</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>-37.5</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>-0.218</v>
+        <v>-0.219</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>-0.406</v>
@@ -2293,16 +2293,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>99.40000000000001</v>
+        <v>99.31</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-0.0244381</v>
+        <v>-0.025321443</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.187</v>
+        <v>-0.188</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.169</v>
+        <v>0.168</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>33.4</v>
@@ -2314,7 +2314,7 @@
         <v>-0.131</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.262</v>
+        <v>-0.263</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>1.034</v>
@@ -2340,28 +2340,28 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.51</v>
+        <v>37.56</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.053338602</v>
+        <v>0.18671563</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.168</v>
+        <v>0.169</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>12</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.066</v>
+        <v>-0.065</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>1.396</v>
@@ -2387,28 +2387,28 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>82.93000000000001</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-0.022858517</v>
+        <v>-0.022151582</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>-0.035</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.224</v>
+        <v>0.225</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>20.1</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-0.012</v>
+        <v>-0.011</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>0.002</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.078</v>
+        <v>-0.077</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>1.22</v>
@@ -2434,25 +2434,25 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>87.72</v>
+        <v>87.8</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.5963352</v>
+        <v>0.68521065</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>-0.216</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.224</v>
+        <v>-0.223</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>-3.2</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.07400000000000001</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.131</v>
+        <v>-0.13</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>-0.259</v>
@@ -2481,28 +2481,28 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>55.96</v>
+        <v>55.9</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-0.047489376</v>
+        <v>-0.04851061299999999</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.095</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.325</v>
+        <v>0.323</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>38.2</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.092</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.047</v>
+        <v>-0.048</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.189</v>
+        <v>-0.19</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>1.453</v>
@@ -2528,28 +2528,28 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>26.8</v>
+        <v>26.87</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.055926137</v>
+        <v>0.1864323</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.138</v>
+        <v>0.14</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.026</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>-21.9</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.143</v>
+        <v>0.146</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.151</v>
+        <v>-0.149</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>1.977</v>
@@ -2575,25 +2575,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.55</v>
+        <v>10.56</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.09487883</v>
+        <v>0.23718803</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.08900000000000001</v>
+        <v>-0.08800000000000001</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.5539999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>26</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.061</v>
+        <v>-0.06</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>-0.266</v>
@@ -2622,28 +2622,28 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>17.82</v>
+        <v>17.93</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.037277176</v>
+        <v>-0.031064332</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-0.236</v>
+        <v>-0.231</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.205</v>
+        <v>-0.2</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>-29.6</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>-0.03</v>
+        <v>-0.024</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.273</v>
+        <v>-0.269</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.447</v>
+        <v>-0.444</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>2.002</v>
@@ -2669,28 +2669,28 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.62</v>
+        <v>21.68</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-0.013686097</v>
+        <v>-0.010948895</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.12</v>
+        <v>0.123</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.982</v>
+        <v>0.987</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>50.7</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.149</v>
+        <v>0.153</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.182</v>
+        <v>0.186</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.045</v>
+        <v>-0.043</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.552</v>
@@ -2716,25 +2716,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.61823744</v>
+        <v>-0.5795967</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.145</v>
+        <v>-0.144</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.038</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>12.6</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.066</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.168</v>
+        <v>-0.167</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>-0.307</v>
@@ -2763,28 +2763,28 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.5</v>
+        <v>5.51</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.4562061</v>
+        <v>0.6386833</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.267</v>
+        <v>-0.266</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.023</v>
+        <v>0.025</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>6.2</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.3</v>
+        <v>-0.298</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.458</v>
+        <v>-0.457</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>0.603</v>
@@ -2810,22 +2810,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.51</v>
+        <v>14.5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.01057297</v>
+        <v>-0.010917765</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.023</v>
+        <v>-0.024</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.164</v>
+        <v>-0.165</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-19.3</v>
+        <v>-19.4</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>-0.107</v>
@@ -2857,28 +2857,28 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>97.54000000000001</v>
+        <v>97.36</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-0.019402838</v>
+        <v>-0.021162193</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.218</v>
+        <v>0.215</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>20.3</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.143</v>
+        <v>-0.145</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.376</v>
@@ -2904,28 +2904,28 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.0391304</v>
+        <v>-0.04130436000000001</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.59</v>
+        <v>-0.591</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.584</v>
+        <v>-0.585</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>-34.5</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.386</v>
+        <v>-0.388</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.5670000000000001</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.6779999999999999</v>
+        <v>-0.679</v>
       </c>
       <c r="L18" s="8" t="n">
         <v>1.993</v>
@@ -2951,28 +2951,28 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.07</v>
+        <v>11.06</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-0.016429877</v>
+        <v>-0.017761972</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.026</v>
+        <v>-0.027</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>-1.6</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.02</v>
+        <v>-0.021</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.012</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.168</v>
+        <v>-0.169</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.07</v>
@@ -2998,16 +2998,16 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.36</v>
+        <v>26.35</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.113674805</v>
+        <v>-0.15156882</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>-0.026</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>5.4</v>
@@ -3016,7 +3016,7 @@
         <v>-0.057</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.019</v>
+        <v>-0.02</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>-0.195</v>
@@ -3045,28 +3045,28 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.42</v>
+        <v>11.38</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-0.041946306</v>
+        <v>-0.044882536</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-0.314</v>
+        <v>-0.316</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.181</v>
+        <v>-0.183</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>38.8</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-0.214</v>
+        <v>-0.216</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.141</v>
+        <v>-0.144</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.449</v>
+        <v>-0.451</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -3094,28 +3094,28 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.83</v>
+        <v>6.87</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.020149288</v>
+        <v>0.025373147</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.238</v>
+        <v>-0.234</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.238</v>
+        <v>-0.234</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>3.9</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.185</v>
+        <v>-0.18</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.202</v>
+        <v>-0.198</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.314</v>
+        <v>-0.31</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>1.206</v>
@@ -3342,16 +3342,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>52.47</v>
+        <v>52.36</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>35.473</v>
+        <v>35.402</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>22.325533</v>
+        <v>22.280851</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>13.962593</v>
+        <v>13.9346485</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>10.795</v>
@@ -3363,10 +3363,10 @@
         <v>3.759</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.268677</v>
+        <v>22.22411</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>2.7251592</v>
+        <v>2.719705</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>2.35</v>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>103.27</v>
+        <v>103.32</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>18.067</v>
+        <v>18.076</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9.701295</v>
+        <v>9.705992999999999</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>13.981</v>
@@ -3418,10 +3418,10 @@
         <v>1.819</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.0021324</v>
+        <v>2.0031018</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.1028097</v>
+        <v>1.1033436</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>-1.75</v>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>21.23</v>
+        <v>21.22</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>10.57</v>
+        <v>10.563</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>10.910445</v>
+        <v>10.902738</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>41.491</v>
@@ -3473,10 +3473,10 @@
         <v>1.87</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>16.64185</v>
+        <v>16.630093</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>1.7458347</v>
+        <v>1.7446012</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.01</v>
@@ -3505,16 +3505,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>99.40000000000001</v>
+        <v>99.31</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.366</v>
+        <v>10.356</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>31.65605</v>
+        <v>31.627386</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>16.729021</v>
+        <v>16.713875</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>11.398</v>
@@ -3526,10 +3526,10 @@
         <v>2.794</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-36.979168</v>
+        <v>-36.945683</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.4522092</v>
+        <v>1.4508944</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>3.14</v>
@@ -3558,16 +3558,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.51</v>
+        <v>37.56</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.259</v>
+        <v>10.273</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>49.355263</v>
+        <v>49.421055</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>16.008636</v>
+        <v>16.029978</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>16.869</v>
@@ -3579,10 +3579,10 @@
         <v>2.265</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>3.987456</v>
+        <v>3.9927716</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.5849818</v>
+        <v>0.5857616</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0.76</v>
@@ -3611,16 +3611,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>82.93000000000001</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6.261</v>
+        <v>6.265</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.6759753</v>
+        <v>3.6786346</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>10.178695</v>
+        <v>10.186058</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>7.297</v>
@@ -3632,10 +3632,10 @@
         <v>2.142</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2.4279063</v>
+        <v>2.429663</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.5299574</v>
+        <v>1.5310643</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>22.56</v>
@@ -3664,16 +3664,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>87.72</v>
+        <v>87.8</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.114</v>
+        <v>6.119</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>16.582232</v>
+        <v>16.596882</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>11.814078</v>
+        <v>11.824516</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>11.623</v>
@@ -3685,10 +3685,10 @@
         <v>3.801</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>6.0467362</v>
+        <v>6.0520782</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>2.0895336</v>
+        <v>2.0913796</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>5.29</v>
@@ -3717,16 +3717,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>55.96</v>
+        <v>55.9</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.754</v>
+        <v>5.748</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>17.935898</v>
+        <v>17.916668</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>17.030186</v>
+        <v>17.011927</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>8.461</v>
@@ -3738,10 +3738,10 @@
         <v>3.423</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>15.666293</v>
+        <v>15.649496</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>2.860672</v>
+        <v>2.857605</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>3.12</v>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>26.8</v>
+        <v>26.87</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.471</v>
+        <v>5.484</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>26.12573</v>
+        <v>26.189085</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>8.691000000000001</v>
@@ -3793,10 +3793,10 @@
         <v>2.645</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>1.5500492</v>
+        <v>1.553808</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.47632885</v>
+        <v>0.4774839</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>-2.42</v>
@@ -3825,16 +3825,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10.55</v>
+        <v>10.56</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.334</v>
+        <v>5.342</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>25.11905</v>
+        <v>25.154762</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>12.162645</v>
+        <v>12.179937</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>10.031</v>
@@ -3846,10 +3846,10 @@
         <v>2.101</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.162254</v>
+        <v>7.1724367</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2.2768576</v>
+        <v>2.2800946</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>0.42</v>
@@ -3878,16 +3878,16 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>17.82</v>
+        <v>17.93</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.274</v>
+        <v>5.308</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>49.499996</v>
+        <v>49.819443</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>21.626507</v>
+        <v>21.766071</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>10.358</v>
@@ -3899,10 +3899,10 @@
         <v>4.075</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>4.709905</v>
+        <v>4.7403</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>4.0895205</v>
+        <v>4.114757</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0.36</v>
@@ -3931,16 +3931,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21.62</v>
+        <v>21.68</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5.033</v>
+        <v>5.047</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>69.741936</v>
+        <v>69.935486</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>28.979681</v>
+        <v>29.060104</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>14.677529</v>
+        <v>14.718262</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.436423</v>
+        <v>4.4487348</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0.31</v>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.373</v>
+        <v>2.374</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>11.934591</v>
+        <v>11.939231</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>6.753</v>
@@ -4013,10 +4013,10 @@
         <v>2.372</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>2.7461028</v>
+        <v>2.7471704</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.94505686</v>
+        <v>0.94542426</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>-0.01</v>
@@ -4045,16 +4045,16 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.5</v>
+        <v>5.51</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.239</v>
+        <v>2.243</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>11.967391</v>
+        <v>11.98913</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.9193935</v>
+        <v>6.9319625</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>10.592</v>
@@ -4066,10 +4066,10 @@
         <v>2.474</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1.7251645</v>
+        <v>-1.7282983</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.43371302</v>
+        <v>0.43450087</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.46</v>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.51</v>
+        <v>14.5</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1.937</v>
+        <v>1.936</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>8.381824999999999</v>
+        <v>8.378935999999999</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>17.223</v>
@@ -4121,10 +4121,10 @@
         <v>1.787</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.99848557</v>
+        <v>0.99814135</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.27827737</v>
+        <v>0.27818143</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-5.83</v>
@@ -4153,16 +4153,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>97.54000000000001</v>
+        <v>97.36</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.745</v>
+        <v>1.741</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>17.96317</v>
+        <v>17.930939</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>16.407064</v>
+        <v>16.377628</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>8.893000000000001</v>
@@ -4174,10 +4174,10 @@
         <v>3.111</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>3.2325845</v>
+        <v>3.2267847</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3.2003894</v>
+        <v>3.194647</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>5.43</v>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1.137</v>
+        <v>1.134</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4.4646463</v>
+        <v>4.454545</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>-7.324</v>
@@ -4231,10 +4231,10 @@
         <v>1.319</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>1.5028902</v>
+        <v>1.4994899</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>1.6983784</v>
+        <v>1.694536</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>-0.44</v>
@@ -4263,16 +4263,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11.07</v>
+        <v>11.06</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.903</v>
+        <v>0.902</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>18.458332</v>
+        <v>18.433332</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>11.959656</v>
+        <v>11.943459</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>6.569</v>
@@ -4284,10 +4284,10 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>3.3796155</v>
+        <v>3.3750384</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.67877597</v>
+        <v>0.6778567</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0.6</v>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>26.36</v>
+        <v>26.35</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0.696</v>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>21.785124</v>
+        <v>21.77686</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>9.455</v>
@@ -4339,10 +4339,10 @@
         <v>1.818</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.6399155</v>
+        <v>1.6392933</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>1.0960162</v>
+        <v>1.0956004</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.23</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11.42</v>
+        <v>11.38</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-14.098765</v>
+        <v>-14.055555</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>22.644</v>
@@ -4394,10 +4394,10 @@
         <v>2.934</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.55712754</v>
+        <v>0.5554201</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.21132772</v>
+        <v>0.21068002</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>-12.45</v>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.83</v>
+        <v>6.87</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.185</v>
+        <v>0.186</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>9.123552</v>
+        <v>9.170271</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>6.891</v>
@@ -4449,10 +4449,10 @@
         <v>1.684</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-11.334992</v>
+        <v>-11.393035</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.60819525</v>
+        <v>0.61130965</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>-0.58</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>52.47</v>
+        <v>52.36</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>58</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>0.332</v>
+        <v>0.334</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>2.49</v>
@@ -6301,7 +6301,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>103.27</v>
+        <v>103.32</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>1.009</v>
+        <v>1.008</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>2.02</v>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>21.23</v>
+        <v>21.22</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.7040000000000001</v>
+        <v>0.705</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>2.13</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>99.40000000000001</v>
+        <v>99.31</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.427</v>
+        <v>0.428</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>3.38</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37.51</v>
+        <v>37.56</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.137</v>
+        <v>0.136</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4.85</v>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>82.93000000000001</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>84</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.139</v>
+        <v>0.138</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>3.91</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>87.72</v>
+        <v>87.8</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>110</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.545</v>
+        <v>0.5429999999999999</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>2.17</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>55.96</v>
+        <v>55.9</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>59</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.303</v>
+        <v>0.305</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>4.01</v>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>26.8</v>
+        <v>26.87</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>22</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.192</v>
+        <v>0.189</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>3.37</v>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10.55</v>
+        <v>10.56</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.647</v>
+        <v>0.645</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4.72</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>17.82</v>
+        <v>17.93</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -6827,16 +6827,16 @@
         <v>21</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>28.81177</v>
+        <v>28.805126</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>37.08439</v>
+        <v>37.07584</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>22.893705</v>
+        <v>22.888426</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.617</v>
+        <v>0.607</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>4.54</v>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>21.62</v>
+        <v>21.68</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>1.89</v>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>15</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.406</v>
+        <v>0.405</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>2.58</v>
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5.5</v>
+        <v>5.51</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>6</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.68</v>
+        <v>0.677</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>2.37</v>
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14.51</v>
+        <v>14.5</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.317</v>
+        <v>0.318</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>4.3</v>
@@ -7101,7 +7101,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>97.54000000000001</v>
+        <v>97.36</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>93</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>2.64</v>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1.662</v>
+        <v>1.668</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>2.41</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11.07</v>
+        <v>11.06</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>14</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.4</v>
+        <v>0.401</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>2.55</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>26.36</v>
+        <v>26.35</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>11.42</v>
+        <v>11.38</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>11</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.3720000000000001</v>
+        <v>0.377</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>8.01</v>
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6.83</v>
+        <v>6.87</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>10</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.9520000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>9.81</v>
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>35.473</v>
+        <v>35.402</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>22.325533</v>
+        <v>22.280851</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.26</v>
@@ -7712,7 +7712,7 @@
         <v>0.73263</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-0.191</v>
+        <v>-0.193</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>10.795</v>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.471</v>
+        <v>5.484</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>-0.10840999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.138</v>
+        <v>0.14</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>8.691000000000001</v>
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>10.366</v>
+        <v>10.356</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>31.65605</v>
+        <v>31.627386</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.015</v>
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-0.187</v>
+        <v>-0.188</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>11.398</v>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2.239</v>
+        <v>2.243</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>11.967391</v>
+        <v>11.98913</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.08599999999999999</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-0.267</v>
+        <v>-0.266</v>
       </c>
       <c r="J6" s="7" t="n">
         <v>10.592</v>
@@ -7879,10 +7879,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.259</v>
+        <v>10.273</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>49.355263</v>
+        <v>49.421055</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.06</v>
@@ -7894,7 +7894,7 @@
         <v>0.1489</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="J7" s="7" t="n">
         <v>16.869</v>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.261</v>
+        <v>6.265</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3.6759753</v>
+        <v>3.6786346</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.02</v>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6.114</v>
+        <v>6.119</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>16.582232</v>
+        <v>16.596882</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.067</v>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5.754</v>
+        <v>5.748</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>17.935898</v>
+        <v>17.916668</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.032</v>
@@ -8044,7 +8044,7 @@
         <v>1.113</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.095</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>8.461</v>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1.745</v>
+        <v>1.741</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>17.96317</v>
+        <v>17.930939</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.041</v>
@@ -8088,7 +8088,7 @@
         <v>0.19214001</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="J13" s="7" t="n">
         <v>8.893000000000001</v>
@@ -8117,7 +8117,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.937</v>
+        <v>1.936</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>-0.36078</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.023</v>
+        <v>-0.024</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>17.223</v>
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>-0.5564</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.314</v>
+        <v>-0.316</v>
       </c>
       <c r="J16" s="7" t="n">
         <v>22.644</v>
@@ -8319,10 +8319,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5.334</v>
+        <v>5.342</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>25.11905</v>
+        <v>25.154762</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.178</v>
@@ -8334,7 +8334,7 @@
         <v>0.32813</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.08900000000000001</v>
+        <v>-0.08800000000000001</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>10.031</v>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5.033</v>
+        <v>5.047</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>69.741936</v>
+        <v>69.935486</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.888</v>
@@ -8378,7 +8378,7 @@
         <v>0.29505</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.12</v>
+        <v>0.123</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
@@ -8411,10 +8411,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.274</v>
+        <v>5.308</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>49.499996</v>
+        <v>49.819443</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.201</v>
@@ -8426,7 +8426,7 @@
         <v>0.10515001</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.236</v>
+        <v>-0.231</v>
       </c>
       <c r="J22" s="7" t="n">
         <v>10.358</v>
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>10.57</v>
+        <v>10.563</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.067</v>
+        <v>18.076</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.137</v>
+        <v>1.134</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>-0.17208</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-0.59</v>
+        <v>-0.591</v>
       </c>
       <c r="J25" s="7" t="n">
         <v>-7.324</v>
@@ -8613,10 +8613,10 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.903</v>
+        <v>0.902</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.458332</v>
+        <v>18.433332</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0.075</v>
@@ -8628,7 +8628,7 @@
         <v>0.19236</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-0.026</v>
+        <v>-0.027</v>
       </c>
       <c r="J28" s="7" t="n">
         <v>6.569</v>
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2.373</v>
+        <v>2.374</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>0.07395</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.145</v>
+        <v>-0.144</v>
       </c>
       <c r="J29" s="7" t="n">
         <v>6.753</v>
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.185</v>
+        <v>0.186</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.238</v>
+        <v>-0.234</v>
       </c>
       <c r="J30" s="7" t="n">
         <v>6.891</v>
@@ -10198,7 +10198,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1294.16</v>
+        <v>1293.93</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>1218.79</v>
@@ -10214,7 +10214,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1286.61</v>
+        <v>1286.37</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>1209.76</v>
@@ -10230,7 +10230,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1291.45</v>
+        <v>1291.19</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>1211.98</v>
@@ -10246,7 +10246,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1292.34</v>
+        <v>1292.1</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>1220.05</v>
@@ -10262,7 +10262,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1277.28</v>
+        <v>1277.03</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>1227.31</v>
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1228.62</v>
+        <v>1228.37</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1223.35</v>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1254.03</v>
+        <v>1253.79</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1223.23</v>
@@ -10310,7 +10310,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1224.75</v>
+        <v>1224.54</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>1231.32</v>
@@ -10326,7 +10326,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1220.43</v>
+        <v>1220.2</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1233.25</v>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1212.48</v>
+        <v>1212.24</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1230.78</v>
@@ -10358,7 +10358,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1210.11</v>
+        <v>1209.87</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>1224.74</v>
@@ -10374,7 +10374,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>1229.57</v>
+        <v>1229.33</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>1228.07</v>
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1192.46</v>
+        <v>1192.22</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>1227.04</v>
@@ -10406,7 +10406,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1168.32</v>
+        <v>1168.07</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>1202.06</v>
@@ -10422,7 +10422,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1174.92</v>
+        <v>1174.65</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>1215.94</v>
@@ -10438,7 +10438,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1180.12</v>
+        <v>1179.84</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>1222.29</v>
@@ -10454,7 +10454,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1164.78</v>
+        <v>1164.5</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1222.73</v>
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1170.62</v>
+        <v>1170.32</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>1228.94</v>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1157.29</v>
+        <v>1157</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>1233.84</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1158.92</v>
+        <v>1158.6</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>1233.71</v>
@@ -10518,7 +10518,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1106.34</v>
+        <v>1106.15</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>1231.26</v>
@@ -10534,7 +10534,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1094.49</v>
+        <v>1094.29</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>1227.59</v>
@@ -10550,7 +10550,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1112.78</v>
+        <v>1112.55</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>1233.69</v>
@@ -10566,7 +10566,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1109.17</v>
+        <v>1108.9</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1223.26</v>
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1130.78</v>
+        <v>1130.52</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>1217.34</v>
@@ -10598,7 +10598,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1105.65</v>
+        <v>1105.38</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>1202.13</v>
@@ -10614,7 +10614,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1132.97</v>
+        <v>1132.7</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>1225.2</v>
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>1134.91</v>
+        <v>1134.64</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>1231.1</v>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>1131.75</v>
+        <v>1131.48</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1227.86</v>
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>1116.8</v>
+        <v>1116.5</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1227.57</v>
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1079.08</v>
+        <v>1078.77</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>1208.61</v>
@@ -10694,7 +10694,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1069.48</v>
+        <v>1069.17</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>1209.46</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>1084.6</v>
+        <v>1084.3</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>1211.41</v>
@@ -10726,7 +10726,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>1118.98</v>
+        <v>1118.69</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>1217.51</v>
@@ -10742,7 +10742,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>1113.88</v>
+        <v>1113.61</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>1214.3</v>
@@ -10758,7 +10758,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>1114.03</v>
+        <v>1113.78</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>1223.09</v>
@@ -10774,7 +10774,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>1070.01</v>
+        <v>1069.77</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>1210.6</v>
@@ -10790,7 +10790,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1084.89</v>
+        <v>1084.67</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>1219.4</v>
@@ -10806,7 +10806,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>1089.04</v>
+        <v>1088.84</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>1229.68</v>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1118.64</v>
+        <v>1118.45</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>1222.85</v>
@@ -10838,7 +10838,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1105.69</v>
+        <v>1105.49</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>1216.98</v>
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>1100.43</v>
+        <v>1100.25</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>1217.67</v>
@@ -10870,7 +10870,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>1096.5</v>
+        <v>1096.31</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>1206.94</v>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>1112.24</v>
+        <v>1112.07</v>
       </c>
       <c r="C45" s="13" t="n">
         <v>1215.46</v>
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>1109.96</v>
+        <v>1109.81</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>1208.68</v>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>1077.73</v>
+        <v>1077.58</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1192.84</v>
@@ -10934,7 +10934,7 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>1079.2</v>
+        <v>1079.05</v>
       </c>
       <c r="C48" s="13" t="n">
         <v>1203.29</v>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>1078.17</v>
+        <v>1078.01</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1201.35</v>
@@ -10966,7 +10966,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>1093.35</v>
+        <v>1093.19</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>1199.85</v>
@@ -10982,7 +10982,7 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1078.76</v>
+        <v>1078.63</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>1181.63</v>
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>1080.68</v>
+        <v>1080.54</v>
       </c>
       <c r="C52" s="13" t="n">
         <v>1174.94</v>
@@ -11014,7 +11014,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>1073.02</v>
+        <v>1072.87</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>1186.89</v>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="B54" s="13" t="n">
-        <v>1085.58</v>
+        <v>1085.43</v>
       </c>
       <c r="C54" s="13" t="n">
         <v>1190.02</v>
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="B55" s="13" t="n">
-        <v>1077.47</v>
+        <v>1077.32</v>
       </c>
       <c r="C55" s="13" t="n">
         <v>1173.41</v>
@@ -11062,7 +11062,7 @@
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>1090.35</v>
+        <v>1090.23</v>
       </c>
       <c r="C56" s="13" t="n">
         <v>1170.52</v>
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="B57" s="13" t="n">
-        <v>1061.53</v>
+        <v>1061.41</v>
       </c>
       <c r="C57" s="13" t="n">
         <v>1153.74</v>
@@ -11094,7 +11094,7 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>1084.02</v>
+        <v>1083.9</v>
       </c>
       <c r="C58" s="13" t="n">
         <v>1165.85</v>
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>1095.11</v>
+        <v>1094.98</v>
       </c>
       <c r="C59" s="13" t="n">
         <v>1161.94</v>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1080.9</v>
+        <v>1080.77</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>1168.42</v>
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>1060.02</v>
+        <v>1059.88</v>
       </c>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
@@ -11154,7 +11154,7 @@
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>1060.02</v>
+        <v>1059.88</v>
       </c>
     </row>
     <row r="64">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-17.92%</t>
+          <t>-17.91%</t>
         </is>
       </c>
     </row>

--- a/Gaming_Equities.xlsx
+++ b/Gaming_Equities.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>52.36</v>
+        <v>52.29</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.033413284</v>
+        <v>-0.034705508</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>70.45</v>
@@ -670,19 +670,19 @@
         <v>30.18</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.257</v>
+        <v>-0.258</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>35.402</v>
+        <v>35.355</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>48.933</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22.280851</v>
+        <v>22.251064</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>13.9346485</v>
+        <v>13.916019</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>10.795</v>
@@ -694,10 +694,10 @@
         <v>0.888</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0.326</v>
+        <v>0.324</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>-0.193</v>
+        <v>-0.194</v>
       </c>
     </row>
     <row r="3">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>103.32</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>-0.07735625</v>
+        <v>103.47</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>0.08703708</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>313.685</v>
@@ -729,10 +729,10 @@
         <v>99.95999999999999</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-0.6709999999999999</v>
+        <v>-0.67</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>18.076</v>
+        <v>18.106</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>29.807</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="L3" s="7" t="n">
-        <v>9.705992999999999</v>
+        <v>9.721962</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>13.981</v>
@@ -755,10 +755,10 @@
         <v>1.177</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>-0.527</v>
+        <v>-0.526</v>
       </c>
     </row>
     <row r="4">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>21.22</v>
+        <v>21.21</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.9337104000000001</v>
+        <v>-0.95704913</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>48.78</v>
@@ -793,7 +793,7 @@
         <v>-0.5649999999999999</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>10.563</v>
+        <v>10.56</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>11.322</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>10.902738</v>
+        <v>10.900169</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>41.491</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>99.31</v>
+        <v>99.19</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.025321443</v>
+        <v>-0.02645009</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>134.72</v>
@@ -851,19 +851,19 @@
         <v>65.25</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.263</v>
+        <v>-0.264</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>10.356</v>
+        <v>10.344</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>19.942</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>31.627386</v>
+        <v>31.590763</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>16.713875</v>
+        <v>16.69452</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>11.398</v>
@@ -875,10 +875,10 @@
         <v>1.034</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>0.168</v>
+        <v>0.166</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>-0.188</v>
+        <v>-0.189</v>
       </c>
     </row>
     <row r="6">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.56</v>
+        <v>37.52</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.18671563</v>
+        <v>0.08001808000000001</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>40.16</v>
@@ -910,19 +910,19 @@
         <v>25.3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-0.065</v>
+        <v>-0.066</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10.273</v>
+        <v>10.262</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>39.718</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>49.421055</v>
+        <v>49.368423</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>16.029978</v>
+        <v>16.012905</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>16.869</v>
@@ -934,10 +934,10 @@
         <v>1.396</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.169</v>
+        <v>0.168</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="7">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>82.98999999999999</v>
+        <v>82.94</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.022151582</v>
+        <v>-0.022799637</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>89.95999999999999</v>
@@ -969,19 +969,19 @@
         <v>58.94</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.077</v>
+        <v>-0.078</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.265</v>
+        <v>6.261</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>8.763999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3.6786346</v>
+        <v>3.6761968</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>10.186058</v>
+        <v>10.179308</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>7.297</v>
@@ -993,7 +993,7 @@
         <v>1.22</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0.225</v>
+        <v>0.224</v>
       </c>
       <c r="Q7" s="4" t="n">
         <v>-0.035</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>87.8</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.68521065</v>
+        <v>0.35551056</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>118.46</v>
@@ -1028,19 +1028,19 @@
         <v>80.23999999999999</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.259</v>
+        <v>-0.261</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.119</v>
+        <v>6.099</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>11.12</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.596882</v>
+        <v>16.542534</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>11.824516</v>
+        <v>11.785796</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>11.623</v>
@@ -1052,10 +1052,10 @@
         <v>0.66</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.223</v>
+        <v>-0.226</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.216</v>
+        <v>-0.218</v>
       </c>
     </row>
     <row r="9">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>55.9</v>
+        <v>55.73</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.04851061299999999</v>
+        <v>-0.051489387</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>68.98999999999999</v>
@@ -1087,19 +1087,19 @@
         <v>35.09</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.19</v>
+        <v>-0.192</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.748</v>
+        <v>5.73</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>6.886</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>17.916668</v>
+        <v>17.860577</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>17.011927</v>
+        <v>16.95867</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>8.461</v>
@@ -1111,10 +1111,10 @@
         <v>1.453</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>0.323</v>
+        <v>0.319</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.095</v>
+        <v>-0.09699999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>26.87</v>
+        <v>26.86</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1864323</v>
+        <v>0.14914584</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>31.58</v>
@@ -1149,7 +1149,7 @@
         <v>-0.149</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.484</v>
+        <v>5.